--- a/AAII_Financials/Quarterly/WF_QTR_FIN.xlsx
+++ b/AAII_Financials/Quarterly/WF_QTR_FIN.xlsx
@@ -5,7 +5,7 @@
   <workbookPr codeName="ThisWorkbook" defaultThemeVersion="124226"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\sundeep\Stocks_Automation\AAII_Financials\Quarterly\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\sundeep\Private\Investing\Automation\AAII\AAII_Financials\Quarterly\"/>
     </mc:Choice>
   </mc:AlternateContent>
   <bookViews>
@@ -17,12 +17,12 @@
   <definedNames>
     <definedName name="Ticker">#REF!</definedName>
   </definedNames>
-  <calcPr calcId="152511" calcMode="manual" concurrentCalc="0"/>
+  <calcPr calcId="152511" calcMode="manual"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="182" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="185" uniqueCount="92">
   <si>
     <t>WF</t>
   </si>
@@ -656,217 +656,224 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet2"/>
-  <dimension ref="A5:AF102"/>
+  <dimension ref="A5:AG102"/>
   <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="5" style="1" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="26.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="69.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="16" style="1" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="17" style="1" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="16" style="1" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="17" style="1" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="16" style="1" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="17" style="1" bestFit="1" customWidth="1"/>
-    <col min="10" max="32" width="16" style="1" bestFit="1" customWidth="1"/>
-    <col min="33" max="16384" width="9.140625" style="1"/>
+    <col min="4" max="4" width="17" style="1" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="16" style="1" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="17" style="1" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="16" style="1" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="17" style="1" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="16" style="1" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="17" style="1" bestFit="1" customWidth="1"/>
+    <col min="11" max="33" width="16" style="1" bestFit="1" customWidth="1"/>
+    <col min="34" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
-    <row r="5" spans="1:32" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:33" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:32" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:33" x14ac:dyDescent="0.2">
       <c r="B6" s="1" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:32" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:33" x14ac:dyDescent="0.2">
       <c r="C7" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D7" s="2">
+        <v>45291</v>
+      </c>
+      <c r="E7" s="2">
         <v>45199</v>
       </c>
-      <c r="E7" s="2">
+      <c r="F7" s="2">
         <v>45107</v>
       </c>
-      <c r="F7" s="2">
+      <c r="G7" s="2">
         <v>45016</v>
       </c>
-      <c r="G7" s="2">
+      <c r="H7" s="2">
         <v>44926</v>
       </c>
-      <c r="H7" s="2">
+      <c r="I7" s="2">
         <v>44834</v>
       </c>
-      <c r="I7" s="2">
+      <c r="J7" s="2">
         <v>44742</v>
       </c>
-      <c r="J7" s="2">
+      <c r="K7" s="2">
         <v>44651</v>
       </c>
-      <c r="K7" s="2">
+      <c r="L7" s="2">
         <v>44561</v>
       </c>
-      <c r="L7" s="2">
+      <c r="M7" s="2">
         <v>44469</v>
       </c>
-      <c r="M7" s="2">
+      <c r="N7" s="2">
         <v>44377</v>
       </c>
-      <c r="N7" s="2">
+      <c r="O7" s="2">
         <v>44286</v>
       </c>
-      <c r="O7" s="2">
+      <c r="P7" s="2">
         <v>44196</v>
       </c>
-      <c r="P7" s="2">
+      <c r="Q7" s="2">
         <v>44104</v>
       </c>
-      <c r="Q7" s="2">
+      <c r="R7" s="2">
         <v>44012</v>
       </c>
-      <c r="R7" s="2">
+      <c r="S7" s="2">
         <v>43921</v>
       </c>
-      <c r="S7" s="2">
+      <c r="T7" s="2">
         <v>43830</v>
       </c>
-      <c r="T7" s="2">
+      <c r="U7" s="2">
         <v>43738</v>
       </c>
-      <c r="U7" s="2">
+      <c r="V7" s="2">
         <v>43646</v>
       </c>
-      <c r="V7" s="2">
+      <c r="W7" s="2">
         <v>43555</v>
       </c>
-      <c r="W7" s="2">
+      <c r="X7" s="2">
         <v>43465</v>
       </c>
-      <c r="X7" s="2">
+      <c r="Y7" s="2">
         <v>43373</v>
       </c>
-      <c r="Y7" s="2">
+      <c r="Z7" s="2">
         <v>43281</v>
       </c>
-      <c r="Z7" s="2">
+      <c r="AA7" s="2">
         <v>43190</v>
       </c>
-      <c r="AA7" s="2">
+      <c r="AB7" s="2">
         <v>43100</v>
       </c>
-      <c r="AB7" s="2">
+      <c r="AC7" s="2">
         <v>43008</v>
       </c>
-      <c r="AC7" s="2">
+      <c r="AD7" s="2">
         <v>42916</v>
       </c>
-      <c r="AD7" s="2">
+      <c r="AE7" s="2">
         <v>42825</v>
       </c>
-      <c r="AE7" s="2">
+      <c r="AF7" s="2">
         <v>42735</v>
       </c>
-      <c r="AF7" s="2">
+      <c r="AG7" s="2">
         <v>42643</v>
       </c>
     </row>
-    <row r="8" spans="1:32" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:33" x14ac:dyDescent="0.2">
       <c r="C8" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D8" s="3">
-        <v>4034200</v>
+        <v>4122500</v>
       </c>
       <c r="E8" s="3">
-        <v>3887500</v>
+        <v>3981800</v>
       </c>
       <c r="F8" s="3">
-        <v>3795400</v>
+        <v>3837000</v>
       </c>
       <c r="G8" s="3">
-        <v>3554500</v>
+        <v>3746100</v>
       </c>
       <c r="H8" s="3">
-        <v>2945200</v>
+        <v>3508300</v>
       </c>
       <c r="I8" s="3">
-        <v>2519900</v>
+        <v>2906900</v>
       </c>
       <c r="J8" s="3">
+        <v>2487200</v>
+      </c>
+      <c r="K8" s="3">
         <v>2264400</v>
       </c>
-      <c r="K8" s="3">
+      <c r="L8" s="3">
         <v>2026000</v>
       </c>
-      <c r="L8" s="3">
+      <c r="M8" s="3">
         <v>1862200</v>
       </c>
-      <c r="M8" s="3">
+      <c r="N8" s="3">
         <v>1787500</v>
       </c>
-      <c r="N8" s="3">
+      <c r="O8" s="3">
         <v>1722100</v>
       </c>
-      <c r="O8" s="3">
+      <c r="P8" s="3">
         <v>1728200</v>
       </c>
-      <c r="P8" s="3">
+      <c r="Q8" s="3">
         <v>1749800</v>
       </c>
-      <c r="Q8" s="3">
+      <c r="R8" s="3">
         <v>1857400</v>
       </c>
-      <c r="R8" s="3">
+      <c r="S8" s="3">
         <v>2028100</v>
       </c>
-      <c r="S8" s="3">
+      <c r="T8" s="3">
         <v>2216400</v>
       </c>
-      <c r="T8" s="3">
+      <c r="U8" s="3">
         <v>2287800</v>
       </c>
-      <c r="U8" s="3">
+      <c r="V8" s="3">
         <v>2353100</v>
       </c>
-      <c r="V8" s="3">
+      <c r="W8" s="3">
         <v>2369400</v>
       </c>
-      <c r="W8" s="3">
+      <c r="X8" s="3">
         <v>2154000</v>
       </c>
-      <c r="X8" s="3">
+      <c r="Y8" s="3">
         <v>2006200</v>
       </c>
-      <c r="Y8" s="3">
+      <c r="Z8" s="3">
         <v>1989700</v>
       </c>
-      <c r="Z8" s="3">
+      <c r="AA8" s="3">
         <v>1910800</v>
       </c>
-      <c r="AA8" s="3">
+      <c r="AB8" s="3">
         <v>1912500</v>
       </c>
-      <c r="AB8" s="3">
+      <c r="AC8" s="3">
         <v>1925300</v>
       </c>
-      <c r="AC8" s="3">
+      <c r="AD8" s="3">
         <v>1853100</v>
       </c>
-      <c r="AD8" s="3">
+      <c r="AE8" s="3">
         <v>1833700</v>
       </c>
-      <c r="AE8" s="3">
+      <c r="AF8" s="3">
         <v>1898800</v>
       </c>
-      <c r="AF8" s="3">
+      <c r="AG8" s="3">
         <v>1898000</v>
       </c>
     </row>
-    <row r="9" spans="1:32" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:33" x14ac:dyDescent="0.2">
       <c r="C9" s="1" t="s">
         <v>4</v>
       </c>
@@ -957,8 +964,11 @@
       <c r="AF9" s="3" t="s">
         <v>5</v>
       </c>
-    </row>
-    <row r="10" spans="1:32" x14ac:dyDescent="0.2">
+      <c r="AG9" s="3" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="10" spans="1:33" x14ac:dyDescent="0.2">
       <c r="C10" s="1" t="s">
         <v>6</v>
       </c>
@@ -1049,8 +1059,11 @@
       <c r="AF10" s="3" t="s">
         <v>5</v>
       </c>
-    </row>
-    <row r="11" spans="1:32" x14ac:dyDescent="0.2">
+      <c r="AG10" s="3" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="11" spans="1:33" x14ac:dyDescent="0.2">
       <c r="C11" s="1" t="s">
         <v>7</v>
       </c>
@@ -1083,8 +1096,9 @@
       <c r="AD11" s="3"/>
       <c r="AE11" s="3"/>
       <c r="AF11" s="3"/>
-    </row>
-    <row r="12" spans="1:32" x14ac:dyDescent="0.2">
+      <c r="AG11" s="3"/>
+    </row>
+    <row r="12" spans="1:33" x14ac:dyDescent="0.2">
       <c r="C12" s="1" t="s">
         <v>8</v>
       </c>
@@ -1175,8 +1189,11 @@
       <c r="AF12" s="3" t="s">
         <v>5</v>
       </c>
-    </row>
-    <row r="13" spans="1:32" x14ac:dyDescent="0.2">
+      <c r="AG12" s="3" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="13" spans="1:33" x14ac:dyDescent="0.2">
       <c r="C13" s="1" t="s">
         <v>9</v>
       </c>
@@ -1267,8 +1284,11 @@
       <c r="AF13" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="14" spans="1:32" x14ac:dyDescent="0.2">
+      <c r="AG13" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="14" spans="1:33" x14ac:dyDescent="0.2">
       <c r="C14" s="1" t="s">
         <v>10</v>
       </c>
@@ -1359,100 +1379,106 @@
       <c r="AF14" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="15" spans="1:32" x14ac:dyDescent="0.2">
+      <c r="AG14" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="15" spans="1:33" x14ac:dyDescent="0.2">
       <c r="C15" s="1" t="s">
         <v>11</v>
       </c>
       <c r="D15" s="3">
-        <v>-90600</v>
+        <v>-100000</v>
       </c>
       <c r="E15" s="3">
-        <v>-97300</v>
+        <v>-89500</v>
       </c>
       <c r="F15" s="3">
-        <v>-102200</v>
+        <v>-96000</v>
       </c>
       <c r="G15" s="3">
-        <v>-104200</v>
+        <v>-100900</v>
       </c>
       <c r="H15" s="3">
-        <v>-97200</v>
+        <v>-102800</v>
       </c>
       <c r="I15" s="3">
-        <v>-102000</v>
+        <v>-95900</v>
       </c>
       <c r="J15" s="3">
+        <v>-100700</v>
+      </c>
+      <c r="K15" s="3">
         <v>-101400</v>
       </c>
-      <c r="K15" s="3">
+      <c r="L15" s="3">
         <v>-98200</v>
       </c>
-      <c r="L15" s="3">
+      <c r="M15" s="3">
         <v>-97600</v>
       </c>
-      <c r="M15" s="3">
+      <c r="N15" s="3">
         <v>-97400</v>
       </c>
-      <c r="N15" s="3">
+      <c r="O15" s="3">
         <v>-100600</v>
       </c>
-      <c r="O15" s="3">
+      <c r="P15" s="3">
         <v>-99400</v>
       </c>
-      <c r="P15" s="3">
+      <c r="Q15" s="3">
         <v>-99600</v>
       </c>
-      <c r="Q15" s="3">
+      <c r="R15" s="3">
         <v>-96100</v>
       </c>
-      <c r="R15" s="3">
+      <c r="S15" s="3">
         <v>-109500</v>
       </c>
-      <c r="S15" s="3">
+      <c r="T15" s="3">
         <v>-115200</v>
       </c>
-      <c r="T15" s="3">
+      <c r="U15" s="3">
         <v>-112100</v>
       </c>
-      <c r="U15" s="3">
+      <c r="V15" s="3">
         <v>-104100</v>
       </c>
-      <c r="V15" s="3">
+      <c r="W15" s="3">
         <v>-88900</v>
       </c>
-      <c r="W15" s="3">
+      <c r="X15" s="3">
         <v>-50500</v>
       </c>
-      <c r="X15" s="3">
+      <c r="Y15" s="3">
         <v>-47800</v>
       </c>
-      <c r="Y15" s="3">
+      <c r="Z15" s="3">
         <v>-44700</v>
       </c>
-      <c r="Z15" s="3">
+      <c r="AA15" s="3">
         <v>-40700</v>
       </c>
-      <c r="AA15" s="3">
+      <c r="AB15" s="3">
         <v>-39500</v>
       </c>
-      <c r="AB15" s="3">
+      <c r="AC15" s="3">
         <v>-40300</v>
       </c>
-      <c r="AC15" s="3">
+      <c r="AD15" s="3">
         <v>-40800</v>
       </c>
-      <c r="AD15" s="3">
+      <c r="AE15" s="3">
         <v>-44500</v>
       </c>
-      <c r="AE15" s="3">
+      <c r="AF15" s="3">
         <v>-54800</v>
       </c>
-      <c r="AF15" s="3">
+      <c r="AG15" s="3">
         <v>-53700</v>
       </c>
     </row>
-    <row r="16" spans="1:32" x14ac:dyDescent="0.2">
+    <row r="16" spans="1:33" x14ac:dyDescent="0.2">
       <c r="D16" s="3"/>
       <c r="E16" s="3"/>
       <c r="F16" s="3"/>
@@ -1482,192 +1508,199 @@
       <c r="AD16" s="3"/>
       <c r="AE16" s="3"/>
       <c r="AF16" s="3"/>
-    </row>
-    <row r="17" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG16" s="3"/>
+    </row>
+    <row r="17" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C17" s="1" t="s">
         <v>12</v>
       </c>
       <c r="D17" s="3">
-        <v>2551100</v>
+        <v>3114600</v>
       </c>
       <c r="E17" s="3">
-        <v>2626300</v>
+        <v>2517900</v>
       </c>
       <c r="F17" s="3">
-        <v>2288400</v>
+        <v>2592200</v>
       </c>
       <c r="G17" s="3">
-        <v>1948500</v>
+        <v>2258600</v>
       </c>
       <c r="H17" s="3">
-        <v>1313400</v>
+        <v>1923200</v>
       </c>
       <c r="I17" s="3">
-        <v>1136200</v>
+        <v>1296400</v>
       </c>
       <c r="J17" s="3">
+        <v>1121400</v>
+      </c>
+      <c r="K17" s="3">
         <v>861300</v>
       </c>
-      <c r="K17" s="3">
+      <c r="L17" s="3">
         <v>772200</v>
       </c>
-      <c r="L17" s="3">
+      <c r="M17" s="3">
         <v>616800</v>
       </c>
-      <c r="M17" s="3">
+      <c r="N17" s="3">
         <v>573600</v>
       </c>
-      <c r="N17" s="3">
+      <c r="O17" s="3">
         <v>625700</v>
       </c>
-      <c r="O17" s="3">
+      <c r="P17" s="3">
         <v>727900</v>
       </c>
-      <c r="P17" s="3">
+      <c r="Q17" s="3">
         <v>721100</v>
       </c>
-      <c r="Q17" s="3">
+      <c r="R17" s="3">
         <v>966200</v>
       </c>
-      <c r="R17" s="3">
+      <c r="S17" s="3">
         <v>926000</v>
       </c>
-      <c r="S17" s="3">
+      <c r="T17" s="3">
         <v>1019500</v>
       </c>
-      <c r="T17" s="3">
+      <c r="U17" s="3">
         <v>1190700</v>
       </c>
-      <c r="U17" s="3">
+      <c r="V17" s="3">
         <v>1111900</v>
       </c>
-      <c r="V17" s="3">
+      <c r="W17" s="3">
         <v>1098300</v>
       </c>
-      <c r="W17" s="3">
+      <c r="X17" s="3">
         <v>1157200</v>
       </c>
-      <c r="X17" s="3">
+      <c r="Y17" s="3">
         <v>918800</v>
       </c>
-      <c r="Y17" s="3">
+      <c r="Z17" s="3">
         <v>752200</v>
       </c>
-      <c r="Z17" s="3">
+      <c r="AA17" s="3">
         <v>877900</v>
       </c>
-      <c r="AA17" s="3">
+      <c r="AB17" s="3">
         <v>1026000</v>
       </c>
-      <c r="AB17" s="3">
+      <c r="AC17" s="3">
         <v>926800</v>
       </c>
-      <c r="AC17" s="3">
+      <c r="AD17" s="3">
         <v>906500</v>
       </c>
-      <c r="AD17" s="3">
+      <c r="AE17" s="3">
         <v>830000</v>
       </c>
-      <c r="AE17" s="3">
+      <c r="AF17" s="3">
         <v>903100</v>
       </c>
-      <c r="AF17" s="3">
+      <c r="AG17" s="3">
         <v>963600</v>
       </c>
     </row>
-    <row r="18" spans="3:32" x14ac:dyDescent="0.2">
+    <row r="18" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C18" s="1" t="s">
         <v>13</v>
       </c>
       <c r="D18" s="3">
-        <v>1483200</v>
+        <v>1008000</v>
       </c>
       <c r="E18" s="3">
-        <v>1261200</v>
+        <v>1463900</v>
       </c>
       <c r="F18" s="3">
-        <v>1507100</v>
+        <v>1244800</v>
       </c>
       <c r="G18" s="3">
-        <v>1606000</v>
+        <v>1487500</v>
       </c>
       <c r="H18" s="3">
-        <v>1631700</v>
+        <v>1585100</v>
       </c>
       <c r="I18" s="3">
-        <v>1383700</v>
+        <v>1610600</v>
       </c>
       <c r="J18" s="3">
+        <v>1365800</v>
+      </c>
+      <c r="K18" s="3">
         <v>1403000</v>
       </c>
-      <c r="K18" s="3">
+      <c r="L18" s="3">
         <v>1253800</v>
       </c>
-      <c r="L18" s="3">
+      <c r="M18" s="3">
         <v>1245400</v>
       </c>
-      <c r="M18" s="3">
+      <c r="N18" s="3">
         <v>1213900</v>
       </c>
-      <c r="N18" s="3">
+      <c r="O18" s="3">
         <v>1096400</v>
       </c>
-      <c r="O18" s="3">
+      <c r="P18" s="3">
         <v>1000300</v>
       </c>
-      <c r="P18" s="3">
+      <c r="Q18" s="3">
         <v>1028700</v>
       </c>
-      <c r="Q18" s="3">
+      <c r="R18" s="3">
         <v>891200</v>
       </c>
-      <c r="R18" s="3">
+      <c r="S18" s="3">
         <v>1102100</v>
       </c>
-      <c r="S18" s="3">
+      <c r="T18" s="3">
         <v>1196900</v>
       </c>
-      <c r="T18" s="3">
+      <c r="U18" s="3">
         <v>1097100</v>
       </c>
-      <c r="U18" s="3">
+      <c r="V18" s="3">
         <v>1241200</v>
       </c>
-      <c r="V18" s="3">
+      <c r="W18" s="3">
         <v>1271100</v>
       </c>
-      <c r="W18" s="3">
+      <c r="X18" s="3">
         <v>996800</v>
       </c>
-      <c r="X18" s="3">
+      <c r="Y18" s="3">
         <v>1087400</v>
       </c>
-      <c r="Y18" s="3">
+      <c r="Z18" s="3">
         <v>1237400</v>
       </c>
-      <c r="Z18" s="3">
+      <c r="AA18" s="3">
         <v>1032900</v>
       </c>
-      <c r="AA18" s="3">
+      <c r="AB18" s="3">
         <v>886500</v>
       </c>
-      <c r="AB18" s="3">
+      <c r="AC18" s="3">
         <v>998500</v>
       </c>
-      <c r="AC18" s="3">
+      <c r="AD18" s="3">
         <v>946600</v>
       </c>
-      <c r="AD18" s="3">
+      <c r="AE18" s="3">
         <v>1003700</v>
       </c>
-      <c r="AE18" s="3">
+      <c r="AF18" s="3">
         <v>995700</v>
       </c>
-      <c r="AF18" s="3">
+      <c r="AG18" s="3">
         <v>934400</v>
       </c>
     </row>
-    <row r="19" spans="3:32" x14ac:dyDescent="0.2">
+    <row r="19" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C19" s="1" t="s">
         <v>14</v>
       </c>
@@ -1700,192 +1733,199 @@
       <c r="AD19" s="3"/>
       <c r="AE19" s="3"/>
       <c r="AF19" s="3"/>
-    </row>
-    <row r="20" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG19" s="3"/>
+    </row>
+    <row r="20" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C20" s="1" t="s">
         <v>15</v>
       </c>
       <c r="D20" s="3">
-        <v>-523100</v>
+        <v>-915100</v>
       </c>
       <c r="E20" s="3">
-        <v>-585000</v>
+        <v>-516400</v>
       </c>
       <c r="F20" s="3">
-        <v>-528900</v>
+        <v>-577400</v>
       </c>
       <c r="G20" s="3">
-        <v>-1044500</v>
+        <v>-522100</v>
       </c>
       <c r="H20" s="3">
-        <v>-639800</v>
+        <v>-1030900</v>
       </c>
       <c r="I20" s="3">
-        <v>-380600</v>
+        <v>-631500</v>
       </c>
       <c r="J20" s="3">
+        <v>-375600</v>
+      </c>
+      <c r="K20" s="3">
         <v>-505900</v>
       </c>
-      <c r="K20" s="3">
+      <c r="L20" s="3">
         <v>-806400</v>
       </c>
-      <c r="L20" s="3">
+      <c r="M20" s="3">
         <v>-394200</v>
       </c>
-      <c r="M20" s="3">
+      <c r="N20" s="3">
         <v>-406900</v>
       </c>
-      <c r="N20" s="3">
+      <c r="O20" s="3">
         <v>-399500</v>
       </c>
-      <c r="O20" s="3">
+      <c r="P20" s="3">
         <v>-784600</v>
       </c>
-      <c r="P20" s="3">
+      <c r="Q20" s="3">
         <v>-508200</v>
       </c>
-      <c r="Q20" s="3">
+      <c r="R20" s="3">
         <v>-674600</v>
       </c>
-      <c r="R20" s="3">
+      <c r="S20" s="3">
         <v>-492400</v>
       </c>
-      <c r="S20" s="3">
+      <c r="T20" s="3">
         <v>-920900</v>
       </c>
-      <c r="T20" s="3">
+      <c r="U20" s="3">
         <v>-527400</v>
       </c>
-      <c r="U20" s="3">
+      <c r="V20" s="3">
         <v>-447200</v>
       </c>
-      <c r="V20" s="3">
+      <c r="W20" s="3">
         <v>-519600</v>
       </c>
-      <c r="W20" s="3">
+      <c r="X20" s="3">
         <v>-847700</v>
       </c>
-      <c r="X20" s="3">
+      <c r="Y20" s="3">
         <v>-418500</v>
       </c>
-      <c r="Y20" s="3">
+      <c r="Z20" s="3">
         <v>-401200</v>
       </c>
-      <c r="Z20" s="3">
+      <c r="AA20" s="3">
         <v>-355800</v>
       </c>
-      <c r="AA20" s="3">
+      <c r="AB20" s="3">
         <v>-756300</v>
       </c>
-      <c r="AB20" s="3">
+      <c r="AC20" s="3">
         <v>-671500</v>
       </c>
-      <c r="AC20" s="3">
+      <c r="AD20" s="3">
         <v>-417500</v>
       </c>
-      <c r="AD20" s="3">
+      <c r="AE20" s="3">
         <v>-274500</v>
       </c>
-      <c r="AE20" s="3">
+      <c r="AF20" s="3">
         <v>-821100</v>
       </c>
-      <c r="AF20" s="3">
+      <c r="AG20" s="3">
         <v>-531000</v>
       </c>
     </row>
-    <row r="21" spans="3:32" x14ac:dyDescent="0.2">
+    <row r="21" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C21" s="1" t="s">
         <v>16</v>
       </c>
       <c r="D21" s="3">
-        <v>1145000</v>
+        <v>293400</v>
       </c>
       <c r="E21" s="3">
-        <v>863400</v>
+        <v>1130200</v>
       </c>
       <c r="F21" s="3">
-        <v>1167600</v>
+        <v>852100</v>
       </c>
       <c r="G21" s="3">
-        <v>751700</v>
+        <v>1152400</v>
       </c>
       <c r="H21" s="3">
-        <v>1170900</v>
+        <v>741900</v>
       </c>
       <c r="I21" s="3">
-        <v>1181100</v>
+        <v>1155700</v>
       </c>
       <c r="J21" s="3">
+        <v>1165700</v>
+      </c>
+      <c r="K21" s="3">
         <v>1065700</v>
       </c>
-      <c r="K21" s="3">
+      <c r="L21" s="3">
         <v>603300</v>
       </c>
-      <c r="L21" s="3">
+      <c r="M21" s="3">
         <v>1000500</v>
       </c>
-      <c r="M21" s="3">
+      <c r="N21" s="3">
         <v>991500</v>
       </c>
-      <c r="N21" s="3">
+      <c r="O21" s="3">
         <v>799800</v>
       </c>
-      <c r="O21" s="3">
+      <c r="P21" s="3">
         <v>316900</v>
       </c>
-      <c r="P21" s="3">
+      <c r="Q21" s="3">
         <v>622000</v>
       </c>
-      <c r="Q21" s="3">
+      <c r="R21" s="3">
         <v>315300</v>
       </c>
-      <c r="R21" s="3">
+      <c r="S21" s="3">
         <v>721900</v>
       </c>
-      <c r="S21" s="3">
+      <c r="T21" s="3">
         <v>396300</v>
       </c>
-      <c r="T21" s="3">
+      <c r="U21" s="3">
         <v>686600</v>
       </c>
-      <c r="U21" s="3">
+      <c r="V21" s="3">
         <v>902900</v>
       </c>
-      <c r="V21" s="3">
+      <c r="W21" s="3">
         <v>845100</v>
       </c>
-      <c r="W21" s="3">
+      <c r="X21" s="3">
         <v>210800</v>
       </c>
-      <c r="X21" s="3">
+      <c r="Y21" s="3">
         <v>727400</v>
       </c>
-      <c r="Y21" s="3">
+      <c r="Z21" s="3">
         <v>892200</v>
       </c>
-      <c r="Z21" s="3">
+      <c r="AA21" s="3">
         <v>727700</v>
       </c>
-      <c r="AA21" s="3">
+      <c r="AB21" s="3">
         <v>180100</v>
       </c>
-      <c r="AB21" s="3">
+      <c r="AC21" s="3">
         <v>377800</v>
       </c>
-      <c r="AC21" s="3">
+      <c r="AD21" s="3">
         <v>580800</v>
       </c>
-      <c r="AD21" s="3">
+      <c r="AE21" s="3">
         <v>784400</v>
       </c>
-      <c r="AE21" s="3">
+      <c r="AF21" s="3">
         <v>229400</v>
       </c>
-      <c r="AF21" s="3">
+      <c r="AG21" s="3">
         <v>457200</v>
       </c>
     </row>
-    <row r="22" spans="3:32" x14ac:dyDescent="0.2">
+    <row r="22" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C22" s="1" t="s">
         <v>17</v>
       </c>
@@ -1976,192 +2016,201 @@
       <c r="AF22" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="23" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG22" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="23" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C23" s="1" t="s">
         <v>18</v>
       </c>
       <c r="D23" s="3">
-        <v>960000</v>
+        <v>92800</v>
       </c>
       <c r="E23" s="3">
-        <v>676200</v>
+        <v>947600</v>
       </c>
       <c r="F23" s="3">
-        <v>978100</v>
+        <v>667400</v>
       </c>
       <c r="G23" s="3">
-        <v>561500</v>
+        <v>965400</v>
       </c>
       <c r="H23" s="3">
-        <v>991900</v>
+        <v>554200</v>
       </c>
       <c r="I23" s="3">
-        <v>1003200</v>
+        <v>979000</v>
       </c>
       <c r="J23" s="3">
+        <v>990200</v>
+      </c>
+      <c r="K23" s="3">
         <v>897100</v>
       </c>
-      <c r="K23" s="3">
+      <c r="L23" s="3">
         <v>447400</v>
       </c>
-      <c r="L23" s="3">
+      <c r="M23" s="3">
         <v>851200</v>
       </c>
-      <c r="M23" s="3">
+      <c r="N23" s="3">
         <v>807000</v>
       </c>
-      <c r="N23" s="3">
+      <c r="O23" s="3">
         <v>696900</v>
       </c>
-      <c r="O23" s="3">
+      <c r="P23" s="3">
         <v>215700</v>
       </c>
-      <c r="P23" s="3">
+      <c r="Q23" s="3">
         <v>520500</v>
       </c>
-      <c r="Q23" s="3">
+      <c r="R23" s="3">
         <v>216600</v>
       </c>
-      <c r="R23" s="3">
+      <c r="S23" s="3">
         <v>609600</v>
       </c>
-      <c r="S23" s="3">
+      <c r="T23" s="3">
         <v>276000</v>
       </c>
-      <c r="T23" s="3">
+      <c r="U23" s="3">
         <v>569700</v>
       </c>
-      <c r="U23" s="3">
+      <c r="V23" s="3">
         <v>794000</v>
       </c>
-      <c r="V23" s="3">
+      <c r="W23" s="3">
         <v>751500</v>
       </c>
-      <c r="W23" s="3">
+      <c r="X23" s="3">
         <v>149100</v>
       </c>
-      <c r="X23" s="3">
+      <c r="Y23" s="3">
         <v>668900</v>
       </c>
-      <c r="Y23" s="3">
+      <c r="Z23" s="3">
         <v>836200</v>
       </c>
-      <c r="Z23" s="3">
+      <c r="AA23" s="3">
         <v>677100</v>
       </c>
-      <c r="AA23" s="3">
+      <c r="AB23" s="3">
         <v>130200</v>
       </c>
-      <c r="AB23" s="3">
+      <c r="AC23" s="3">
         <v>327000</v>
       </c>
-      <c r="AC23" s="3">
+      <c r="AD23" s="3">
         <v>529200</v>
       </c>
-      <c r="AD23" s="3">
+      <c r="AE23" s="3">
         <v>729200</v>
       </c>
-      <c r="AE23" s="3">
+      <c r="AF23" s="3">
         <v>174600</v>
       </c>
-      <c r="AF23" s="3">
+      <c r="AG23" s="3">
         <v>403400</v>
       </c>
     </row>
-    <row r="24" spans="3:32" x14ac:dyDescent="0.2">
+    <row r="24" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C24" s="1" t="s">
         <v>19</v>
       </c>
       <c r="D24" s="3">
-        <v>253100</v>
+        <v>20700</v>
       </c>
       <c r="E24" s="3">
-        <v>162500</v>
+        <v>249800</v>
       </c>
       <c r="F24" s="3">
-        <v>249200</v>
+        <v>160400</v>
       </c>
       <c r="G24" s="3">
-        <v>152400</v>
+        <v>246000</v>
       </c>
       <c r="H24" s="3">
-        <v>273200</v>
+        <v>150500</v>
       </c>
       <c r="I24" s="3">
-        <v>243300</v>
+        <v>269700</v>
       </c>
       <c r="J24" s="3">
+        <v>240200</v>
+      </c>
+      <c r="K24" s="3">
         <v>225300</v>
       </c>
-      <c r="K24" s="3">
+      <c r="L24" s="3">
         <v>113100</v>
       </c>
-      <c r="L24" s="3">
+      <c r="M24" s="3">
         <v>232900</v>
       </c>
-      <c r="M24" s="3">
+      <c r="N24" s="3">
         <v>193200</v>
       </c>
-      <c r="N24" s="3">
+      <c r="O24" s="3">
         <v>164900</v>
       </c>
-      <c r="O24" s="3">
+      <c r="P24" s="3">
         <v>53200</v>
       </c>
-      <c r="P24" s="3">
+      <c r="Q24" s="3">
         <v>118800</v>
       </c>
-      <c r="Q24" s="3">
+      <c r="R24" s="3">
         <v>50000</v>
       </c>
-      <c r="R24" s="3">
+      <c r="S24" s="3">
         <v>157800</v>
       </c>
-      <c r="S24" s="3">
+      <c r="T24" s="3">
         <v>79200</v>
       </c>
-      <c r="T24" s="3">
+      <c r="U24" s="3">
         <v>115700</v>
       </c>
-      <c r="U24" s="3">
+      <c r="V24" s="3">
         <v>215500</v>
       </c>
-      <c r="V24" s="3">
+      <c r="W24" s="3">
         <v>192300</v>
       </c>
-      <c r="W24" s="3">
+      <c r="X24" s="3">
         <v>39300</v>
       </c>
-      <c r="X24" s="3">
+      <c r="Y24" s="3">
         <v>179200</v>
       </c>
-      <c r="Y24" s="3">
+      <c r="Z24" s="3">
         <v>229900</v>
       </c>
-      <c r="Z24" s="3">
+      <c r="AA24" s="3">
         <v>177700</v>
       </c>
-      <c r="AA24" s="3">
+      <c r="AB24" s="3">
         <v>9000</v>
       </c>
-      <c r="AB24" s="3">
+      <c r="AC24" s="3">
         <v>77600</v>
       </c>
-      <c r="AC24" s="3">
+      <c r="AD24" s="3">
         <v>118800</v>
       </c>
-      <c r="AD24" s="3">
+      <c r="AE24" s="3">
         <v>163600</v>
       </c>
-      <c r="AE24" s="3">
+      <c r="AF24" s="3">
         <v>30300</v>
       </c>
-      <c r="AF24" s="3">
+      <c r="AG24" s="3">
         <v>80000</v>
       </c>
     </row>
-    <row r="25" spans="3:32" x14ac:dyDescent="0.2">
+    <row r="25" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C25" s="1" t="s">
         <v>20</v>
       </c>
@@ -2252,192 +2301,201 @@
       <c r="AF25" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="26" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG25" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="26" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C26" s="1" t="s">
         <v>21</v>
       </c>
       <c r="D26" s="3">
-        <v>706900</v>
+        <v>72200</v>
       </c>
       <c r="E26" s="3">
-        <v>513700</v>
+        <v>697800</v>
       </c>
       <c r="F26" s="3">
-        <v>728900</v>
+        <v>507100</v>
       </c>
       <c r="G26" s="3">
-        <v>409100</v>
+        <v>719400</v>
       </c>
       <c r="H26" s="3">
-        <v>718700</v>
+        <v>403800</v>
       </c>
       <c r="I26" s="3">
-        <v>759900</v>
+        <v>709400</v>
       </c>
       <c r="J26" s="3">
+        <v>750000</v>
+      </c>
+      <c r="K26" s="3">
         <v>671800</v>
       </c>
-      <c r="K26" s="3">
+      <c r="L26" s="3">
         <v>334300</v>
       </c>
-      <c r="L26" s="3">
+      <c r="M26" s="3">
         <v>618300</v>
       </c>
-      <c r="M26" s="3">
+      <c r="N26" s="3">
         <v>613800</v>
       </c>
-      <c r="N26" s="3">
+      <c r="O26" s="3">
         <v>532000</v>
       </c>
-      <c r="O26" s="3">
+      <c r="P26" s="3">
         <v>162400</v>
       </c>
-      <c r="P26" s="3">
+      <c r="Q26" s="3">
         <v>401700</v>
       </c>
-      <c r="Q26" s="3">
+      <c r="R26" s="3">
         <v>166500</v>
       </c>
-      <c r="R26" s="3">
+      <c r="S26" s="3">
         <v>451800</v>
       </c>
-      <c r="S26" s="3">
+      <c r="T26" s="3">
         <v>196800</v>
       </c>
-      <c r="T26" s="3">
+      <c r="U26" s="3">
         <v>454000</v>
       </c>
-      <c r="U26" s="3">
+      <c r="V26" s="3">
         <v>578500</v>
       </c>
-      <c r="V26" s="3">
+      <c r="W26" s="3">
         <v>559200</v>
       </c>
-      <c r="W26" s="3">
+      <c r="X26" s="3">
         <v>109900</v>
       </c>
-      <c r="X26" s="3">
+      <c r="Y26" s="3">
         <v>489700</v>
       </c>
-      <c r="Y26" s="3">
+      <c r="Z26" s="3">
         <v>606300</v>
       </c>
-      <c r="Z26" s="3">
+      <c r="AA26" s="3">
         <v>499400</v>
       </c>
-      <c r="AA26" s="3">
+      <c r="AB26" s="3">
         <v>121100</v>
       </c>
-      <c r="AB26" s="3">
+      <c r="AC26" s="3">
         <v>249400</v>
       </c>
-      <c r="AC26" s="3">
+      <c r="AD26" s="3">
         <v>410300</v>
       </c>
-      <c r="AD26" s="3">
+      <c r="AE26" s="3">
         <v>565600</v>
       </c>
-      <c r="AE26" s="3">
+      <c r="AF26" s="3">
         <v>144300</v>
       </c>
-      <c r="AF26" s="3">
+      <c r="AG26" s="3">
         <v>323500</v>
       </c>
     </row>
-    <row r="27" spans="3:32" x14ac:dyDescent="0.2">
+    <row r="27" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C27" s="1" t="s">
         <v>22</v>
       </c>
       <c r="D27" s="3">
-        <v>667300</v>
+        <v>25000</v>
       </c>
       <c r="E27" s="3">
-        <v>456200</v>
+        <v>658600</v>
       </c>
       <c r="F27" s="3">
-        <v>680100</v>
+        <v>450300</v>
       </c>
       <c r="G27" s="3">
-        <v>347900</v>
+        <v>671300</v>
       </c>
       <c r="H27" s="3">
-        <v>675700</v>
+        <v>343400</v>
       </c>
       <c r="I27" s="3">
-        <v>693400</v>
+        <v>667000</v>
       </c>
       <c r="J27" s="3">
+        <v>684400</v>
+      </c>
+      <c r="K27" s="3">
         <v>631400</v>
       </c>
-      <c r="K27" s="3">
+      <c r="L27" s="3">
         <v>279500</v>
       </c>
-      <c r="L27" s="3">
+      <c r="M27" s="3">
         <v>570700</v>
       </c>
-      <c r="M27" s="3">
+      <c r="N27" s="3">
         <v>552600</v>
       </c>
-      <c r="N27" s="3">
+      <c r="O27" s="3">
         <v>482000</v>
       </c>
-      <c r="O27" s="3">
+      <c r="P27" s="3">
         <v>112600</v>
       </c>
-      <c r="P27" s="3">
+      <c r="Q27" s="3">
         <v>358800</v>
       </c>
-      <c r="Q27" s="3">
+      <c r="R27" s="3">
         <v>100500</v>
       </c>
-      <c r="R27" s="3">
+      <c r="S27" s="3">
         <v>412900</v>
       </c>
-      <c r="S27" s="3">
+      <c r="T27" s="3">
         <v>174900</v>
       </c>
-      <c r="T27" s="3">
+      <c r="U27" s="3">
         <v>410100</v>
       </c>
-      <c r="U27" s="3">
+      <c r="V27" s="3">
         <v>537700</v>
       </c>
-      <c r="V27" s="3">
+      <c r="W27" s="3">
         <v>517500</v>
       </c>
-      <c r="W27" s="3">
+      <c r="X27" s="3">
         <v>76800</v>
       </c>
-      <c r="X27" s="3">
+      <c r="Y27" s="3">
         <v>453900</v>
       </c>
-      <c r="Y27" s="3">
+      <c r="Z27" s="3">
         <v>569900</v>
       </c>
-      <c r="Z27" s="3">
+      <c r="AA27" s="3">
         <v>463600</v>
       </c>
-      <c r="AA27" s="3">
+      <c r="AB27" s="3">
         <v>84900</v>
       </c>
-      <c r="AB27" s="3">
+      <c r="AC27" s="3">
         <v>212100</v>
       </c>
-      <c r="AC27" s="3">
+      <c r="AD27" s="3">
         <v>369000</v>
       </c>
-      <c r="AD27" s="3">
+      <c r="AE27" s="3">
         <v>517600</v>
       </c>
-      <c r="AE27" s="3">
+      <c r="AF27" s="3">
         <v>88500</v>
       </c>
-      <c r="AF27" s="3">
+      <c r="AG27" s="3">
         <v>275700</v>
       </c>
     </row>
-    <row r="28" spans="3:32" x14ac:dyDescent="0.2">
+    <row r="28" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C28" s="1" t="s">
         <v>23</v>
       </c>
@@ -2528,8 +2586,11 @@
       <c r="AF28" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="29" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG28" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="29" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C29" s="1" t="s">
         <v>24</v>
       </c>
@@ -2620,8 +2681,11 @@
       <c r="AF29" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="30" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG29" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="30" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C30" s="1" t="s">
         <v>25</v>
       </c>
@@ -2712,8 +2776,11 @@
       <c r="AF30" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="31" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG30" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="31" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C31" s="1" t="s">
         <v>26</v>
       </c>
@@ -2804,192 +2871,201 @@
       <c r="AF31" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="32" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG31" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="32" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C32" s="1" t="s">
         <v>27</v>
       </c>
       <c r="D32" s="3">
-        <v>523100</v>
+        <v>915100</v>
       </c>
       <c r="E32" s="3">
-        <v>585000</v>
+        <v>516400</v>
       </c>
       <c r="F32" s="3">
-        <v>528900</v>
+        <v>577400</v>
       </c>
       <c r="G32" s="3">
-        <v>1044500</v>
+        <v>522100</v>
       </c>
       <c r="H32" s="3">
-        <v>639800</v>
+        <v>1030900</v>
       </c>
       <c r="I32" s="3">
-        <v>380600</v>
+        <v>631500</v>
       </c>
       <c r="J32" s="3">
+        <v>375600</v>
+      </c>
+      <c r="K32" s="3">
         <v>505900</v>
       </c>
-      <c r="K32" s="3">
+      <c r="L32" s="3">
         <v>806400</v>
       </c>
-      <c r="L32" s="3">
+      <c r="M32" s="3">
         <v>394200</v>
       </c>
-      <c r="M32" s="3">
+      <c r="N32" s="3">
         <v>406900</v>
       </c>
-      <c r="N32" s="3">
+      <c r="O32" s="3">
         <v>399500</v>
       </c>
-      <c r="O32" s="3">
+      <c r="P32" s="3">
         <v>784600</v>
       </c>
-      <c r="P32" s="3">
+      <c r="Q32" s="3">
         <v>508200</v>
       </c>
-      <c r="Q32" s="3">
+      <c r="R32" s="3">
         <v>674600</v>
       </c>
-      <c r="R32" s="3">
+      <c r="S32" s="3">
         <v>492400</v>
       </c>
-      <c r="S32" s="3">
+      <c r="T32" s="3">
         <v>920900</v>
       </c>
-      <c r="T32" s="3">
+      <c r="U32" s="3">
         <v>527400</v>
       </c>
-      <c r="U32" s="3">
+      <c r="V32" s="3">
         <v>447200</v>
       </c>
-      <c r="V32" s="3">
+      <c r="W32" s="3">
         <v>519600</v>
       </c>
-      <c r="W32" s="3">
+      <c r="X32" s="3">
         <v>847700</v>
       </c>
-      <c r="X32" s="3">
+      <c r="Y32" s="3">
         <v>418500</v>
       </c>
-      <c r="Y32" s="3">
+      <c r="Z32" s="3">
         <v>401200</v>
       </c>
-      <c r="Z32" s="3">
+      <c r="AA32" s="3">
         <v>355800</v>
       </c>
-      <c r="AA32" s="3">
+      <c r="AB32" s="3">
         <v>756300</v>
       </c>
-      <c r="AB32" s="3">
+      <c r="AC32" s="3">
         <v>671500</v>
       </c>
-      <c r="AC32" s="3">
+      <c r="AD32" s="3">
         <v>417500</v>
       </c>
-      <c r="AD32" s="3">
+      <c r="AE32" s="3">
         <v>274500</v>
       </c>
-      <c r="AE32" s="3">
+      <c r="AF32" s="3">
         <v>821100</v>
       </c>
-      <c r="AF32" s="3">
+      <c r="AG32" s="3">
         <v>531000</v>
       </c>
     </row>
-    <row r="33" spans="2:32" x14ac:dyDescent="0.2">
+    <row r="33" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C33" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D33" s="3">
-        <v>667300</v>
+        <v>25000</v>
       </c>
       <c r="E33" s="3">
-        <v>456200</v>
+        <v>658600</v>
       </c>
       <c r="F33" s="3">
-        <v>680100</v>
+        <v>450300</v>
       </c>
       <c r="G33" s="3">
-        <v>347900</v>
+        <v>671300</v>
       </c>
       <c r="H33" s="3">
-        <v>675700</v>
+        <v>343400</v>
       </c>
       <c r="I33" s="3">
-        <v>693400</v>
+        <v>667000</v>
       </c>
       <c r="J33" s="3">
+        <v>684400</v>
+      </c>
+      <c r="K33" s="3">
         <v>631400</v>
       </c>
-      <c r="K33" s="3">
+      <c r="L33" s="3">
         <v>279500</v>
       </c>
-      <c r="L33" s="3">
+      <c r="M33" s="3">
         <v>570700</v>
       </c>
-      <c r="M33" s="3">
+      <c r="N33" s="3">
         <v>552600</v>
       </c>
-      <c r="N33" s="3">
+      <c r="O33" s="3">
         <v>482000</v>
       </c>
-      <c r="O33" s="3">
+      <c r="P33" s="3">
         <v>112600</v>
       </c>
-      <c r="P33" s="3">
+      <c r="Q33" s="3">
         <v>358800</v>
       </c>
-      <c r="Q33" s="3">
+      <c r="R33" s="3">
         <v>100500</v>
       </c>
-      <c r="R33" s="3">
+      <c r="S33" s="3">
         <v>412900</v>
       </c>
-      <c r="S33" s="3">
+      <c r="T33" s="3">
         <v>174900</v>
       </c>
-      <c r="T33" s="3">
+      <c r="U33" s="3">
         <v>410100</v>
       </c>
-      <c r="U33" s="3">
+      <c r="V33" s="3">
         <v>537700</v>
       </c>
-      <c r="V33" s="3">
+      <c r="W33" s="3">
         <v>517500</v>
       </c>
-      <c r="W33" s="3">
+      <c r="X33" s="3">
         <v>76800</v>
       </c>
-      <c r="X33" s="3">
+      <c r="Y33" s="3">
         <v>453900</v>
       </c>
-      <c r="Y33" s="3">
+      <c r="Z33" s="3">
         <v>569900</v>
       </c>
-      <c r="Z33" s="3">
+      <c r="AA33" s="3">
         <v>463600</v>
       </c>
-      <c r="AA33" s="3">
+      <c r="AB33" s="3">
         <v>84900</v>
       </c>
-      <c r="AB33" s="3">
+      <c r="AC33" s="3">
         <v>212100</v>
       </c>
-      <c r="AC33" s="3">
+      <c r="AD33" s="3">
         <v>369000</v>
       </c>
-      <c r="AD33" s="3">
+      <c r="AE33" s="3">
         <v>517600</v>
       </c>
-      <c r="AE33" s="3">
+      <c r="AF33" s="3">
         <v>88500</v>
       </c>
-      <c r="AF33" s="3">
+      <c r="AG33" s="3">
         <v>275700</v>
       </c>
     </row>
-    <row r="34" spans="2:32" x14ac:dyDescent="0.2">
+    <row r="34" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C34" s="1" t="s">
         <v>29</v>
       </c>
@@ -3080,197 +3156,206 @@
       <c r="AF34" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="35" spans="2:32" x14ac:dyDescent="0.2">
+      <c r="AG34" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="35" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C35" s="1" t="s">
         <v>30</v>
       </c>
       <c r="D35" s="3">
-        <v>667300</v>
+        <v>25000</v>
       </c>
       <c r="E35" s="3">
-        <v>456200</v>
+        <v>658600</v>
       </c>
       <c r="F35" s="3">
-        <v>680100</v>
+        <v>450300</v>
       </c>
       <c r="G35" s="3">
-        <v>347900</v>
+        <v>671300</v>
       </c>
       <c r="H35" s="3">
-        <v>675700</v>
+        <v>343400</v>
       </c>
       <c r="I35" s="3">
-        <v>693400</v>
+        <v>667000</v>
       </c>
       <c r="J35" s="3">
+        <v>684400</v>
+      </c>
+      <c r="K35" s="3">
         <v>631400</v>
       </c>
-      <c r="K35" s="3">
+      <c r="L35" s="3">
         <v>279500</v>
       </c>
-      <c r="L35" s="3">
+      <c r="M35" s="3">
         <v>570700</v>
       </c>
-      <c r="M35" s="3">
+      <c r="N35" s="3">
         <v>552600</v>
       </c>
-      <c r="N35" s="3">
+      <c r="O35" s="3">
         <v>482000</v>
       </c>
-      <c r="O35" s="3">
+      <c r="P35" s="3">
         <v>112600</v>
       </c>
-      <c r="P35" s="3">
+      <c r="Q35" s="3">
         <v>358800</v>
       </c>
-      <c r="Q35" s="3">
+      <c r="R35" s="3">
         <v>100500</v>
       </c>
-      <c r="R35" s="3">
+      <c r="S35" s="3">
         <v>412900</v>
       </c>
-      <c r="S35" s="3">
+      <c r="T35" s="3">
         <v>174900</v>
       </c>
-      <c r="T35" s="3">
+      <c r="U35" s="3">
         <v>410100</v>
       </c>
-      <c r="U35" s="3">
+      <c r="V35" s="3">
         <v>537700</v>
       </c>
-      <c r="V35" s="3">
+      <c r="W35" s="3">
         <v>517500</v>
       </c>
-      <c r="W35" s="3">
+      <c r="X35" s="3">
         <v>76800</v>
       </c>
-      <c r="X35" s="3">
+      <c r="Y35" s="3">
         <v>453900</v>
       </c>
-      <c r="Y35" s="3">
+      <c r="Z35" s="3">
         <v>569900</v>
       </c>
-      <c r="Z35" s="3">
+      <c r="AA35" s="3">
         <v>463600</v>
       </c>
-      <c r="AA35" s="3">
+      <c r="AB35" s="3">
         <v>84900</v>
       </c>
-      <c r="AB35" s="3">
+      <c r="AC35" s="3">
         <v>212100</v>
       </c>
-      <c r="AC35" s="3">
+      <c r="AD35" s="3">
         <v>369000</v>
       </c>
-      <c r="AD35" s="3">
+      <c r="AE35" s="3">
         <v>517600</v>
       </c>
-      <c r="AE35" s="3">
+      <c r="AF35" s="3">
         <v>88500</v>
       </c>
-      <c r="AF35" s="3">
+      <c r="AG35" s="3">
         <v>275700</v>
       </c>
     </row>
-    <row r="37" spans="2:32" x14ac:dyDescent="0.2">
+    <row r="37" spans="2:33" x14ac:dyDescent="0.2">
       <c r="B37" s="1" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="38" spans="2:32" x14ac:dyDescent="0.2">
+    <row r="38" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C38" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D38" s="2">
+        <v>45291</v>
+      </c>
+      <c r="E38" s="2">
         <v>45199</v>
       </c>
-      <c r="E38" s="2">
+      <c r="F38" s="2">
         <v>45107</v>
       </c>
-      <c r="F38" s="2">
+      <c r="G38" s="2">
         <v>45016</v>
       </c>
-      <c r="G38" s="2">
+      <c r="H38" s="2">
         <v>44926</v>
       </c>
-      <c r="H38" s="2">
+      <c r="I38" s="2">
         <v>44834</v>
       </c>
-      <c r="I38" s="2">
+      <c r="J38" s="2">
         <v>44742</v>
       </c>
-      <c r="J38" s="2">
+      <c r="K38" s="2">
         <v>44651</v>
       </c>
-      <c r="K38" s="2">
+      <c r="L38" s="2">
         <v>44561</v>
       </c>
-      <c r="L38" s="2">
+      <c r="M38" s="2">
         <v>44469</v>
       </c>
-      <c r="M38" s="2">
+      <c r="N38" s="2">
         <v>44377</v>
       </c>
-      <c r="N38" s="2">
+      <c r="O38" s="2">
         <v>44286</v>
       </c>
-      <c r="O38" s="2">
+      <c r="P38" s="2">
         <v>44196</v>
       </c>
-      <c r="P38" s="2">
+      <c r="Q38" s="2">
         <v>44104</v>
       </c>
-      <c r="Q38" s="2">
+      <c r="R38" s="2">
         <v>44012</v>
       </c>
-      <c r="R38" s="2">
+      <c r="S38" s="2">
         <v>43921</v>
       </c>
-      <c r="S38" s="2">
+      <c r="T38" s="2">
         <v>43830</v>
       </c>
-      <c r="T38" s="2">
+      <c r="U38" s="2">
         <v>43738</v>
       </c>
-      <c r="U38" s="2">
+      <c r="V38" s="2">
         <v>43646</v>
       </c>
-      <c r="V38" s="2">
+      <c r="W38" s="2">
         <v>43555</v>
       </c>
-      <c r="W38" s="2">
+      <c r="X38" s="2">
         <v>43465</v>
       </c>
-      <c r="X38" s="2">
+      <c r="Y38" s="2">
         <v>43373</v>
       </c>
-      <c r="Y38" s="2">
+      <c r="Z38" s="2">
         <v>43281</v>
       </c>
-      <c r="Z38" s="2">
+      <c r="AA38" s="2">
         <v>43190</v>
       </c>
-      <c r="AA38" s="2">
+      <c r="AB38" s="2">
         <v>43100</v>
       </c>
-      <c r="AB38" s="2">
+      <c r="AC38" s="2">
         <v>43008</v>
       </c>
-      <c r="AC38" s="2">
+      <c r="AD38" s="2">
         <v>42916</v>
       </c>
-      <c r="AD38" s="2">
+      <c r="AE38" s="2">
         <v>42825</v>
       </c>
-      <c r="AE38" s="2">
+      <c r="AF38" s="2">
         <v>42735</v>
       </c>
-      <c r="AF38" s="2">
+      <c r="AG38" s="2">
         <v>42643</v>
       </c>
     </row>
-    <row r="39" spans="2:32" x14ac:dyDescent="0.2">
+    <row r="39" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C39" s="1" t="s">
         <v>32</v>
       </c>
@@ -3303,8 +3388,9 @@
       <c r="AD39" s="3"/>
       <c r="AE39" s="3"/>
       <c r="AF39" s="3"/>
-    </row>
-    <row r="40" spans="2:32" x14ac:dyDescent="0.2">
+      <c r="AG39" s="3"/>
+    </row>
+    <row r="40" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C40" s="1" t="s">
         <v>33</v>
       </c>
@@ -3337,192 +3423,199 @@
       <c r="AD40" s="3"/>
       <c r="AE40" s="3"/>
       <c r="AF40" s="3"/>
-    </row>
-    <row r="41" spans="2:32" x14ac:dyDescent="0.2">
+      <c r="AG40" s="3"/>
+    </row>
+    <row r="41" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C41" s="1" t="s">
         <v>34</v>
       </c>
       <c r="D41" s="3">
-        <v>19794600</v>
+        <v>23125700</v>
       </c>
       <c r="E41" s="3">
-        <v>16475400</v>
+        <v>19537600</v>
       </c>
       <c r="F41" s="3">
-        <v>23717800</v>
+        <v>16261400</v>
       </c>
       <c r="G41" s="3">
-        <v>26279400</v>
+        <v>23409800</v>
       </c>
       <c r="H41" s="3">
-        <v>6864300</v>
+        <v>25938100</v>
       </c>
       <c r="I41" s="3">
-        <v>7474200</v>
+        <v>6775100</v>
       </c>
       <c r="J41" s="3">
+        <v>7377100</v>
+      </c>
+      <c r="K41" s="3">
         <v>9785500</v>
       </c>
-      <c r="K41" s="3">
+      <c r="L41" s="3">
         <v>5555400</v>
       </c>
-      <c r="L41" s="3">
+      <c r="M41" s="3">
         <v>7893500</v>
       </c>
-      <c r="M41" s="3">
+      <c r="N41" s="3">
         <v>7303900</v>
       </c>
-      <c r="N41" s="3">
+      <c r="O41" s="3">
         <v>7996900</v>
       </c>
-      <c r="O41" s="3">
+      <c r="P41" s="3">
         <v>6985700</v>
       </c>
-      <c r="P41" s="3">
+      <c r="Q41" s="3">
         <v>6452400</v>
       </c>
-      <c r="Q41" s="3">
+      <c r="R41" s="3">
         <v>6934700</v>
       </c>
-      <c r="R41" s="3">
+      <c r="S41" s="3">
         <v>7810800</v>
       </c>
-      <c r="S41" s="3">
+      <c r="T41" s="3">
         <v>5327800</v>
       </c>
-      <c r="T41" s="3">
+      <c r="U41" s="3">
         <v>7069900</v>
       </c>
-      <c r="U41" s="3">
+      <c r="V41" s="3">
         <v>5777500</v>
       </c>
-      <c r="V41" s="3">
+      <c r="W41" s="3">
         <v>4361000</v>
       </c>
-      <c r="W41" s="3">
+      <c r="X41" s="3">
         <v>5329900</v>
       </c>
-      <c r="X41" s="3">
+      <c r="Y41" s="3">
         <v>4608100</v>
       </c>
-      <c r="Y41" s="3">
+      <c r="Z41" s="3">
         <v>4589200</v>
       </c>
-      <c r="Z41" s="3">
+      <c r="AA41" s="3">
         <v>4387400</v>
       </c>
-      <c r="AA41" s="3">
+      <c r="AB41" s="3">
         <v>5323900</v>
       </c>
-      <c r="AB41" s="3">
+      <c r="AC41" s="3">
         <v>5337600</v>
       </c>
-      <c r="AC41" s="3">
+      <c r="AD41" s="3">
         <v>5780800</v>
       </c>
-      <c r="AD41" s="3">
+      <c r="AE41" s="3">
         <v>6495200</v>
       </c>
-      <c r="AE41" s="3">
+      <c r="AF41" s="3">
         <v>6385500</v>
       </c>
-      <c r="AF41" s="3">
+      <c r="AG41" s="3">
         <v>7024600</v>
       </c>
     </row>
-    <row r="42" spans="2:32" x14ac:dyDescent="0.2">
+    <row r="42" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C42" s="1" t="s">
         <v>35</v>
       </c>
       <c r="D42" s="3">
-        <v>41369000</v>
+        <v>43799200</v>
       </c>
       <c r="E42" s="3">
-        <v>48517300</v>
+        <v>40831700</v>
       </c>
       <c r="F42" s="3">
-        <v>39536200</v>
+        <v>47887300</v>
       </c>
       <c r="G42" s="3">
-        <v>42179700</v>
+        <v>39022800</v>
       </c>
       <c r="H42" s="3">
-        <v>50722900</v>
+        <v>41631900</v>
       </c>
       <c r="I42" s="3">
-        <v>45498600</v>
+        <v>50064200</v>
       </c>
       <c r="J42" s="3">
+        <v>44907700</v>
+      </c>
+      <c r="K42" s="3">
         <v>44616700</v>
       </c>
-      <c r="K42" s="3">
+      <c r="L42" s="3">
         <v>44083500</v>
       </c>
-      <c r="L42" s="3">
+      <c r="M42" s="3">
         <v>38326100</v>
       </c>
-      <c r="M42" s="3">
+      <c r="N42" s="3">
         <v>33800600</v>
       </c>
-      <c r="N42" s="3">
+      <c r="O42" s="3">
         <v>32013900</v>
       </c>
-      <c r="O42" s="3">
+      <c r="P42" s="3">
         <v>39170300</v>
       </c>
-      <c r="P42" s="3">
+      <c r="Q42" s="3">
         <v>33273800</v>
       </c>
-      <c r="Q42" s="3">
+      <c r="R42" s="3">
         <v>36396600</v>
       </c>
-      <c r="R42" s="3">
+      <c r="S42" s="3">
         <v>38606200</v>
       </c>
-      <c r="S42" s="3">
+      <c r="T42" s="3">
         <v>37680800</v>
       </c>
-      <c r="T42" s="3">
+      <c r="U42" s="3">
         <v>39232200</v>
       </c>
-      <c r="U42" s="3">
+      <c r="V42" s="3">
         <v>36892000</v>
       </c>
-      <c r="V42" s="3">
+      <c r="W42" s="3">
         <v>30905300</v>
       </c>
-      <c r="W42" s="3">
+      <c r="X42" s="3">
         <v>29776700</v>
       </c>
-      <c r="X42" s="3">
+      <c r="Y42" s="3">
         <v>20883600</v>
       </c>
-      <c r="Y42" s="3">
+      <c r="Z42" s="3">
         <v>22286700</v>
       </c>
-      <c r="Z42" s="3">
+      <c r="AA42" s="3">
         <v>21840100</v>
       </c>
-      <c r="AA42" s="3">
+      <c r="AB42" s="3">
         <v>20932300</v>
       </c>
-      <c r="AB42" s="3">
+      <c r="AC42" s="3">
         <v>12488600</v>
       </c>
-      <c r="AC42" s="3">
+      <c r="AD42" s="3">
         <v>14955900</v>
       </c>
-      <c r="AD42" s="3">
+      <c r="AE42" s="3">
         <v>13350900</v>
       </c>
-      <c r="AE42" s="3">
+      <c r="AF42" s="3">
         <v>14204100</v>
       </c>
-      <c r="AF42" s="3">
+      <c r="AG42" s="3">
         <v>16154100</v>
       </c>
     </row>
-    <row r="43" spans="2:32" x14ac:dyDescent="0.2">
+    <row r="43" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C43" s="1" t="s">
         <v>36</v>
       </c>
@@ -3613,8 +3706,11 @@
       <c r="AF43" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="44" spans="2:32" x14ac:dyDescent="0.2">
+      <c r="AG43" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="44" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C44" s="1" t="s">
         <v>37</v>
       </c>
@@ -3705,8 +3801,11 @@
       <c r="AF44" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="45" spans="2:32" x14ac:dyDescent="0.2">
+      <c r="AG44" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="45" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C45" s="1" t="s">
         <v>38</v>
       </c>
@@ -3797,8 +3896,11 @@
       <c r="AF45" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="46" spans="2:32" x14ac:dyDescent="0.2">
+      <c r="AG45" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="46" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C46" s="1" t="s">
         <v>39</v>
       </c>
@@ -3889,284 +3991,296 @@
       <c r="AF46" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="47" spans="2:32" x14ac:dyDescent="0.2">
+      <c r="AG46" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="47" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C47" s="1" t="s">
         <v>40</v>
       </c>
       <c r="D47" s="3">
-        <v>1352700</v>
+        <v>1364500</v>
       </c>
       <c r="E47" s="3">
-        <v>1248700</v>
+        <v>1335100</v>
       </c>
       <c r="F47" s="3">
-        <v>1141900</v>
+        <v>1232500</v>
       </c>
       <c r="G47" s="3">
-        <v>1005300</v>
+        <v>1127100</v>
       </c>
       <c r="H47" s="3">
-        <v>1030300</v>
+        <v>992300</v>
       </c>
       <c r="I47" s="3">
-        <v>1048600</v>
+        <v>1017000</v>
       </c>
       <c r="J47" s="3">
+        <v>1035000</v>
+      </c>
+      <c r="K47" s="3">
         <v>1011300</v>
       </c>
-      <c r="K47" s="3">
+      <c r="L47" s="3">
         <v>1001400</v>
       </c>
-      <c r="L47" s="3">
+      <c r="M47" s="3">
         <v>896000</v>
       </c>
-      <c r="M47" s="3">
+      <c r="N47" s="3">
         <v>881500</v>
       </c>
-      <c r="N47" s="3">
+      <c r="O47" s="3">
         <v>775800</v>
       </c>
-      <c r="O47" s="3">
+      <c r="P47" s="3">
         <v>735000</v>
       </c>
-      <c r="P47" s="3">
+      <c r="Q47" s="3">
         <v>829200</v>
       </c>
-      <c r="Q47" s="3">
+      <c r="R47" s="3">
         <v>714700</v>
       </c>
-      <c r="R47" s="3">
+      <c r="S47" s="3">
         <v>674300</v>
       </c>
-      <c r="S47" s="3">
+      <c r="T47" s="3">
         <v>685400</v>
       </c>
-      <c r="T47" s="3">
+      <c r="U47" s="3">
         <v>322100</v>
       </c>
-      <c r="U47" s="3">
+      <c r="V47" s="3">
         <v>311500</v>
       </c>
-      <c r="V47" s="3">
+      <c r="W47" s="3">
         <v>316200</v>
       </c>
-      <c r="W47" s="3">
+      <c r="X47" s="3">
         <v>303600</v>
       </c>
-      <c r="X47" s="3">
+      <c r="Y47" s="3">
         <v>276700</v>
       </c>
-      <c r="Y47" s="3">
+      <c r="Z47" s="3">
         <v>346900</v>
       </c>
-      <c r="Z47" s="3">
+      <c r="AA47" s="3">
         <v>348200</v>
       </c>
-      <c r="AA47" s="3">
+      <c r="AB47" s="3">
         <v>367000</v>
       </c>
-      <c r="AB47" s="3">
+      <c r="AC47" s="3">
         <v>490900</v>
       </c>
-      <c r="AC47" s="3">
+      <c r="AD47" s="3">
         <v>326300</v>
       </c>
-      <c r="AD47" s="3">
+      <c r="AE47" s="3">
         <v>351100</v>
       </c>
-      <c r="AE47" s="3">
+      <c r="AF47" s="3">
         <v>395100</v>
       </c>
-      <c r="AF47" s="3">
+      <c r="AG47" s="3">
         <v>377600</v>
       </c>
     </row>
-    <row r="48" spans="2:32" x14ac:dyDescent="0.2">
+    <row r="48" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C48" s="1" t="s">
         <v>41</v>
       </c>
       <c r="D48" s="3">
-        <v>2781600</v>
+        <v>2773600</v>
       </c>
       <c r="E48" s="3">
-        <v>2777800</v>
+        <v>2745500</v>
       </c>
       <c r="F48" s="3">
-        <v>2801500</v>
+        <v>2741700</v>
       </c>
       <c r="G48" s="3">
-        <v>2718600</v>
+        <v>2765100</v>
       </c>
       <c r="H48" s="3">
-        <v>2732200</v>
+        <v>2683300</v>
       </c>
       <c r="I48" s="3">
-        <v>2724600</v>
+        <v>2696700</v>
       </c>
       <c r="J48" s="3">
+        <v>2689200</v>
+      </c>
+      <c r="K48" s="3">
         <v>2729900</v>
       </c>
-      <c r="K48" s="3">
+      <c r="L48" s="3">
         <v>2673200</v>
       </c>
-      <c r="L48" s="3">
+      <c r="M48" s="3">
         <v>2701000</v>
       </c>
-      <c r="M48" s="3">
+      <c r="N48" s="3">
         <v>2682600</v>
       </c>
-      <c r="N48" s="3">
+      <c r="O48" s="3">
         <v>2700600</v>
       </c>
-      <c r="O48" s="3">
+      <c r="P48" s="3">
         <v>2719200</v>
       </c>
-      <c r="P48" s="3">
+      <c r="Q48" s="3">
         <v>2764300</v>
       </c>
-      <c r="Q48" s="3">
+      <c r="R48" s="3">
         <v>2790300</v>
       </c>
-      <c r="R48" s="3">
+      <c r="S48" s="3">
         <v>2961700</v>
       </c>
-      <c r="S48" s="3">
+      <c r="T48" s="3">
         <v>3098200</v>
       </c>
-      <c r="T48" s="3">
+      <c r="U48" s="3">
         <v>3089800</v>
       </c>
-      <c r="U48" s="3">
+      <c r="V48" s="3">
         <v>3058200</v>
       </c>
-      <c r="V48" s="3">
+      <c r="W48" s="3">
         <v>3080600</v>
       </c>
-      <c r="W48" s="3">
+      <c r="X48" s="3">
         <v>2368100</v>
       </c>
-      <c r="X48" s="3">
+      <c r="Y48" s="3">
         <v>2284800</v>
       </c>
-      <c r="Y48" s="3">
+      <c r="Z48" s="3">
         <v>2378800</v>
       </c>
-      <c r="Z48" s="3">
+      <c r="AA48" s="3">
         <v>2384000</v>
       </c>
-      <c r="AA48" s="3">
+      <c r="AB48" s="3">
         <v>2507000</v>
       </c>
-      <c r="AB48" s="3">
+      <c r="AC48" s="3">
         <v>2509800</v>
       </c>
-      <c r="AC48" s="3">
+      <c r="AD48" s="3">
         <v>2480800</v>
       </c>
-      <c r="AD48" s="3">
+      <c r="AE48" s="3">
         <v>2470200</v>
       </c>
-      <c r="AE48" s="3">
+      <c r="AF48" s="3">
         <v>2534900</v>
       </c>
-      <c r="AF48" s="3">
+      <c r="AG48" s="3">
         <v>2525400</v>
       </c>
     </row>
-    <row r="49" spans="3:32" x14ac:dyDescent="0.2">
+    <row r="49" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C49" s="1" t="s">
         <v>42</v>
       </c>
       <c r="D49" s="3">
-        <v>758200</v>
+        <v>757600</v>
       </c>
       <c r="E49" s="3">
-        <v>761900</v>
+        <v>748400</v>
       </c>
       <c r="F49" s="3">
-        <v>739400</v>
+        <v>752000</v>
       </c>
       <c r="G49" s="3">
-        <v>653800</v>
+        <v>729800</v>
       </c>
       <c r="H49" s="3">
-        <v>674200</v>
+        <v>645300</v>
       </c>
       <c r="I49" s="3">
-        <v>604400</v>
+        <v>665500</v>
       </c>
       <c r="J49" s="3">
+        <v>596500</v>
+      </c>
+      <c r="K49" s="3">
         <v>608700</v>
       </c>
-      <c r="K49" s="3">
+      <c r="L49" s="3">
         <v>589000</v>
       </c>
-      <c r="L49" s="3">
+      <c r="M49" s="3">
         <v>586400</v>
       </c>
-      <c r="M49" s="3">
+      <c r="N49" s="3">
         <v>581700</v>
       </c>
-      <c r="N49" s="3">
+      <c r="O49" s="3">
         <v>582600</v>
       </c>
-      <c r="O49" s="3">
+      <c r="P49" s="3">
         <v>586100</v>
       </c>
-      <c r="P49" s="3">
+      <c r="Q49" s="3">
         <v>615800</v>
       </c>
-      <c r="Q49" s="3">
+      <c r="R49" s="3">
         <v>631700</v>
       </c>
-      <c r="R49" s="3">
+      <c r="S49" s="3">
         <v>668000</v>
       </c>
-      <c r="S49" s="3">
+      <c r="T49" s="3">
         <v>717500</v>
       </c>
-      <c r="T49" s="3">
+      <c r="U49" s="3">
         <v>590200</v>
       </c>
-      <c r="U49" s="3">
+      <c r="V49" s="3">
         <v>565800</v>
       </c>
-      <c r="V49" s="3">
+      <c r="W49" s="3">
         <v>588900</v>
       </c>
-      <c r="W49" s="3">
+      <c r="X49" s="3">
         <v>493300</v>
       </c>
-      <c r="X49" s="3">
+      <c r="Y49" s="3">
         <v>502400</v>
       </c>
-      <c r="Y49" s="3">
+      <c r="Z49" s="3">
         <v>549000</v>
       </c>
-      <c r="Z49" s="3">
+      <c r="AA49" s="3">
         <v>452700</v>
       </c>
-      <c r="AA49" s="3">
+      <c r="AB49" s="3">
         <v>456400</v>
       </c>
-      <c r="AB49" s="3">
+      <c r="AC49" s="3">
         <v>461900</v>
       </c>
-      <c r="AC49" s="3">
+      <c r="AD49" s="3">
         <v>446100</v>
       </c>
-      <c r="AD49" s="3">
+      <c r="AE49" s="3">
         <v>415100</v>
       </c>
-      <c r="AE49" s="3">
+      <c r="AF49" s="3">
         <v>435400</v>
       </c>
-      <c r="AF49" s="3">
+      <c r="AG49" s="3">
         <v>376700</v>
       </c>
     </row>
-    <row r="50" spans="3:32" x14ac:dyDescent="0.2">
+    <row r="50" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C50" s="1" t="s">
         <v>43</v>
       </c>
@@ -4257,8 +4371,11 @@
       <c r="AF50" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="51" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG50" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="51" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C51" s="1" t="s">
         <v>44</v>
       </c>
@@ -4349,100 +4466,106 @@
       <c r="AF51" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="52" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG51" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="52" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C52" s="1" t="s">
         <v>45</v>
       </c>
       <c r="D52" s="3">
-        <v>321100</v>
+        <v>269000</v>
       </c>
       <c r="E52" s="3">
-        <v>305100</v>
+        <v>316900</v>
       </c>
       <c r="F52" s="3">
-        <v>158900</v>
+        <v>301100</v>
       </c>
       <c r="G52" s="3">
-        <v>340600</v>
+        <v>156900</v>
       </c>
       <c r="H52" s="3">
-        <v>300100</v>
+        <v>336200</v>
       </c>
       <c r="I52" s="3">
-        <v>168600</v>
+        <v>296200</v>
       </c>
       <c r="J52" s="3">
+        <v>166400</v>
+      </c>
+      <c r="K52" s="3">
         <v>58400</v>
       </c>
-      <c r="K52" s="3">
+      <c r="L52" s="3">
         <v>59100</v>
       </c>
-      <c r="L52" s="3">
+      <c r="M52" s="3">
         <v>41100</v>
       </c>
-      <c r="M52" s="3">
+      <c r="N52" s="3">
         <v>56000</v>
       </c>
-      <c r="N52" s="3">
+      <c r="O52" s="3">
         <v>73700</v>
       </c>
-      <c r="O52" s="3">
+      <c r="P52" s="3">
         <v>82700</v>
       </c>
-      <c r="P52" s="3">
+      <c r="Q52" s="3">
         <v>74500</v>
       </c>
-      <c r="Q52" s="3">
+      <c r="R52" s="3">
         <v>37800</v>
       </c>
-      <c r="R52" s="3">
+      <c r="S52" s="3">
         <v>38200</v>
       </c>
-      <c r="S52" s="3">
+      <c r="T52" s="3">
         <v>44800</v>
       </c>
-      <c r="T52" s="3">
+      <c r="U52" s="3">
         <v>82300</v>
       </c>
-      <c r="U52" s="3">
+      <c r="V52" s="3">
         <v>69500</v>
       </c>
-      <c r="V52" s="3">
+      <c r="W52" s="3">
         <v>68200</v>
       </c>
-      <c r="W52" s="3">
+      <c r="X52" s="3">
         <v>120400</v>
       </c>
-      <c r="X52" s="3">
+      <c r="Y52" s="3">
         <v>36800</v>
       </c>
-      <c r="Y52" s="3">
+      <c r="Z52" s="3">
         <v>91100</v>
       </c>
-      <c r="Z52" s="3">
+      <c r="AA52" s="3">
         <v>177600</v>
       </c>
-      <c r="AA52" s="3">
+      <c r="AB52" s="3">
         <v>289300</v>
       </c>
-      <c r="AB52" s="3">
+      <c r="AC52" s="3">
         <v>234800</v>
       </c>
-      <c r="AC52" s="3">
+      <c r="AD52" s="3">
         <v>221100</v>
       </c>
-      <c r="AD52" s="3">
+      <c r="AE52" s="3">
         <v>262700</v>
       </c>
-      <c r="AE52" s="3">
+      <c r="AF52" s="3">
         <v>274800</v>
       </c>
-      <c r="AF52" s="3">
+      <c r="AG52" s="3">
         <v>143800</v>
       </c>
     </row>
-    <row r="53" spans="3:32" x14ac:dyDescent="0.2">
+    <row r="53" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C53" s="1" t="s">
         <v>46</v>
       </c>
@@ -4533,100 +4656,106 @@
       <c r="AF53" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="54" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG53" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="54" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C54" s="1" t="s">
         <v>47</v>
       </c>
       <c r="D54" s="3">
-        <v>374156100</v>
+        <v>378483800</v>
       </c>
       <c r="E54" s="3">
-        <v>371841900</v>
+        <v>369296900</v>
       </c>
       <c r="F54" s="3">
-        <v>368121000</v>
+        <v>367012800</v>
       </c>
       <c r="G54" s="3">
-        <v>369965300</v>
+        <v>363340200</v>
       </c>
       <c r="H54" s="3">
-        <v>386593100</v>
+        <v>365160500</v>
       </c>
       <c r="I54" s="3">
-        <v>373408200</v>
+        <v>381572400</v>
       </c>
       <c r="J54" s="3">
+        <v>368558700</v>
+      </c>
+      <c r="K54" s="3">
         <v>358592300</v>
       </c>
-      <c r="K54" s="3">
+      <c r="L54" s="3">
         <v>335387900</v>
       </c>
-      <c r="L54" s="3">
+      <c r="M54" s="3">
         <v>328638700</v>
       </c>
-      <c r="M54" s="3">
+      <c r="N54" s="3">
         <v>315953000</v>
       </c>
-      <c r="N54" s="3">
+      <c r="O54" s="3">
         <v>307917200</v>
       </c>
-      <c r="O54" s="3">
+      <c r="P54" s="3">
         <v>295320000</v>
       </c>
-      <c r="P54" s="3">
+      <c r="Q54" s="3">
         <v>293246000</v>
       </c>
-      <c r="Q54" s="3">
+      <c r="R54" s="3">
         <v>292659600</v>
       </c>
-      <c r="R54" s="3">
+      <c r="S54" s="3">
         <v>306353500</v>
       </c>
-      <c r="S54" s="3">
+      <c r="T54" s="3">
         <v>307683600</v>
       </c>
-      <c r="T54" s="3">
+      <c r="U54" s="3">
         <v>314996600</v>
       </c>
-      <c r="U54" s="3">
+      <c r="V54" s="3">
         <v>316273500</v>
       </c>
-      <c r="V54" s="3">
+      <c r="W54" s="3">
         <v>314085600</v>
       </c>
-      <c r="W54" s="3">
+      <c r="X54" s="3">
         <v>285975600</v>
       </c>
-      <c r="X54" s="3">
+      <c r="Y54" s="3">
         <v>267139300</v>
       </c>
-      <c r="Y54" s="3">
+      <c r="Z54" s="3">
         <v>274311500</v>
       </c>
-      <c r="Z54" s="3">
+      <c r="AA54" s="3">
         <v>273668600</v>
       </c>
-      <c r="AA54" s="3">
+      <c r="AB54" s="3">
         <v>278340000</v>
       </c>
-      <c r="AB54" s="3">
+      <c r="AC54" s="3">
         <v>279730100</v>
       </c>
-      <c r="AC54" s="3">
+      <c r="AD54" s="3">
         <v>278137400</v>
       </c>
-      <c r="AD54" s="3">
+      <c r="AE54" s="3">
         <v>273600800</v>
       </c>
-      <c r="AE54" s="3">
+      <c r="AF54" s="3">
         <v>279614500</v>
       </c>
-      <c r="AF54" s="3">
+      <c r="AG54" s="3">
         <v>281548700</v>
       </c>
     </row>
-    <row r="55" spans="3:32" x14ac:dyDescent="0.2">
+    <row r="55" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C55" s="1" t="s">
         <v>48</v>
       </c>
@@ -4659,8 +4788,9 @@
       <c r="AD55" s="3"/>
       <c r="AE55" s="3"/>
       <c r="AF55" s="3"/>
-    </row>
-    <row r="56" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG55" s="3"/>
+    </row>
+    <row r="56" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C56" s="1" t="s">
         <v>49</v>
       </c>
@@ -4693,100 +4823,104 @@
       <c r="AD56" s="3"/>
       <c r="AE56" s="3"/>
       <c r="AF56" s="3"/>
-    </row>
-    <row r="57" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG56" s="3"/>
+    </row>
+    <row r="57" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C57" s="1" t="s">
         <v>50</v>
       </c>
       <c r="D57" s="3">
-        <v>14685300</v>
+        <v>9471700</v>
       </c>
       <c r="E57" s="3">
-        <v>14967400</v>
+        <v>14494600</v>
       </c>
       <c r="F57" s="3">
-        <v>14044700</v>
+        <v>14773000</v>
       </c>
       <c r="G57" s="3">
-        <v>8821300</v>
+        <v>13862300</v>
       </c>
       <c r="H57" s="3">
-        <v>13433900</v>
+        <v>8706700</v>
       </c>
       <c r="I57" s="3">
-        <v>12703000</v>
+        <v>13259500</v>
       </c>
       <c r="J57" s="3">
+        <v>12538100</v>
+      </c>
+      <c r="K57" s="3">
         <v>11104000</v>
       </c>
-      <c r="K57" s="3">
+      <c r="L57" s="3">
         <v>10844700</v>
       </c>
-      <c r="L57" s="3">
+      <c r="M57" s="3">
         <v>7957500</v>
       </c>
-      <c r="M57" s="3">
+      <c r="N57" s="3">
         <v>9468900</v>
       </c>
-      <c r="N57" s="3">
+      <c r="O57" s="3">
         <v>7995800</v>
       </c>
-      <c r="O57" s="3">
+      <c r="P57" s="3">
         <v>3698600</v>
       </c>
-      <c r="P57" s="3">
+      <c r="Q57" s="3">
         <v>7530800</v>
       </c>
-      <c r="Q57" s="3">
+      <c r="R57" s="3">
         <v>8467000</v>
       </c>
-      <c r="R57" s="3">
+      <c r="S57" s="3">
         <v>9538600</v>
       </c>
-      <c r="S57" s="3">
+      <c r="T57" s="3">
         <v>7264700</v>
       </c>
-      <c r="T57" s="3">
+      <c r="U57" s="3">
         <v>13339700</v>
       </c>
-      <c r="U57" s="3">
+      <c r="V57" s="3">
         <v>15138200</v>
       </c>
-      <c r="V57" s="3">
+      <c r="W57" s="3">
         <v>14778600</v>
       </c>
-      <c r="W57" s="3">
+      <c r="X57" s="3">
         <v>10988500</v>
       </c>
-      <c r="X57" s="3">
+      <c r="Y57" s="3">
         <v>12068900</v>
       </c>
-      <c r="Y57" s="3">
+      <c r="Z57" s="3">
         <v>11638400</v>
       </c>
-      <c r="Z57" s="3">
+      <c r="AA57" s="3">
         <v>12317300</v>
       </c>
-      <c r="AA57" s="3">
+      <c r="AB57" s="3">
         <v>5801500</v>
       </c>
-      <c r="AB57" s="3">
+      <c r="AC57" s="3">
         <v>13814400</v>
       </c>
-      <c r="AC57" s="3">
+      <c r="AD57" s="3">
         <v>14756900</v>
       </c>
-      <c r="AD57" s="3">
+      <c r="AE57" s="3">
         <v>10823000</v>
       </c>
-      <c r="AE57" s="3">
+      <c r="AF57" s="3">
         <v>13329400</v>
       </c>
-      <c r="AF57" s="3">
+      <c r="AG57" s="3">
         <v>15356600</v>
       </c>
     </row>
-    <row r="58" spans="3:32" x14ac:dyDescent="0.2">
+    <row r="58" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C58" s="1" t="s">
         <v>51</v>
       </c>
@@ -4877,100 +5011,106 @@
       <c r="AF58" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="59" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG58" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="59" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C59" s="1" t="s">
         <v>52</v>
       </c>
       <c r="D59" s="3">
-        <v>3565400</v>
+        <v>3376700</v>
       </c>
       <c r="E59" s="3">
-        <v>3158300</v>
+        <v>3519100</v>
       </c>
       <c r="F59" s="3">
-        <v>3346400</v>
+        <v>3117300</v>
       </c>
       <c r="G59" s="3">
-        <v>3128400</v>
+        <v>3302900</v>
       </c>
       <c r="H59" s="3">
-        <v>2351900</v>
+        <v>3087800</v>
       </c>
       <c r="I59" s="3">
-        <v>1994200</v>
+        <v>2321300</v>
       </c>
       <c r="J59" s="3">
+        <v>1968300</v>
+      </c>
+      <c r="K59" s="3">
         <v>2093100</v>
       </c>
-      <c r="K59" s="3">
+      <c r="L59" s="3">
         <v>1991300</v>
       </c>
-      <c r="L59" s="3">
+      <c r="M59" s="3">
         <v>1538600</v>
       </c>
-      <c r="M59" s="3">
+      <c r="N59" s="3">
         <v>1446500</v>
       </c>
-      <c r="N59" s="3">
+      <c r="O59" s="3">
         <v>1600800</v>
       </c>
-      <c r="O59" s="3">
+      <c r="P59" s="3">
         <v>1790900</v>
       </c>
-      <c r="P59" s="3">
+      <c r="Q59" s="3">
         <v>1521700</v>
       </c>
-      <c r="Q59" s="3">
+      <c r="R59" s="3">
         <v>1545300</v>
       </c>
-      <c r="R59" s="3">
+      <c r="S59" s="3">
         <v>1892000</v>
       </c>
-      <c r="S59" s="3">
+      <c r="T59" s="3">
         <v>2294100</v>
       </c>
-      <c r="T59" s="3">
+      <c r="U59" s="3">
         <v>2199800</v>
       </c>
-      <c r="U59" s="3">
+      <c r="V59" s="3">
         <v>2064700</v>
       </c>
-      <c r="V59" s="3">
+      <c r="W59" s="3">
         <v>2149400</v>
       </c>
-      <c r="W59" s="3">
+      <c r="X59" s="3">
         <v>1989900</v>
       </c>
-      <c r="X59" s="3">
+      <c r="Y59" s="3">
         <v>1798500</v>
       </c>
-      <c r="Y59" s="3">
+      <c r="Z59" s="3">
         <v>1649500</v>
       </c>
-      <c r="Z59" s="3">
+      <c r="AA59" s="3">
         <v>1642100</v>
       </c>
-      <c r="AA59" s="3">
+      <c r="AB59" s="3">
         <v>2008600</v>
       </c>
-      <c r="AB59" s="3">
+      <c r="AC59" s="3">
         <v>2057400</v>
       </c>
-      <c r="AC59" s="3">
+      <c r="AD59" s="3">
         <v>1681400</v>
       </c>
-      <c r="AD59" s="3">
+      <c r="AE59" s="3">
         <v>1880000</v>
       </c>
-      <c r="AE59" s="3">
+      <c r="AF59" s="3">
         <v>2004400</v>
       </c>
-      <c r="AF59" s="3">
+      <c r="AG59" s="3">
         <v>1813400</v>
       </c>
     </row>
-    <row r="60" spans="3:32" x14ac:dyDescent="0.2">
+    <row r="60" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C60" s="1" t="s">
         <v>53</v>
       </c>
@@ -5061,192 +5201,201 @@
       <c r="AF60" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="61" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG60" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="61" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C61" s="1" t="s">
         <v>54</v>
       </c>
       <c r="D61" s="3">
-        <v>54582700</v>
+        <v>53441800</v>
       </c>
       <c r="E61" s="3">
-        <v>54803700</v>
+        <v>53873800</v>
       </c>
       <c r="F61" s="3">
-        <v>54692900</v>
+        <v>54091900</v>
       </c>
       <c r="G61" s="3">
-        <v>54074700</v>
+        <v>53982600</v>
       </c>
       <c r="H61" s="3">
-        <v>62040700</v>
+        <v>53372400</v>
       </c>
       <c r="I61" s="3">
-        <v>59182000</v>
+        <v>61234900</v>
       </c>
       <c r="J61" s="3">
+        <v>58413400</v>
+      </c>
+      <c r="K61" s="3">
         <v>54512100</v>
       </c>
-      <c r="K61" s="3">
+      <c r="L61" s="3">
         <v>51506600</v>
       </c>
-      <c r="L61" s="3">
+      <c r="M61" s="3">
         <v>49335300</v>
       </c>
-      <c r="M61" s="3">
+      <c r="N61" s="3">
         <v>46999300</v>
       </c>
-      <c r="N61" s="3">
+      <c r="O61" s="3">
         <v>43329900</v>
       </c>
-      <c r="O61" s="3">
+      <c r="P61" s="3">
         <v>42586400</v>
       </c>
-      <c r="P61" s="3">
+      <c r="Q61" s="3">
         <v>38230600</v>
       </c>
-      <c r="Q61" s="3">
+      <c r="R61" s="3">
         <v>39214800</v>
       </c>
-      <c r="R61" s="3">
+      <c r="S61" s="3">
         <v>43080800</v>
       </c>
-      <c r="S61" s="3">
+      <c r="T61" s="3">
         <v>42129500</v>
       </c>
-      <c r="T61" s="3">
+      <c r="U61" s="3">
         <v>44185000</v>
       </c>
-      <c r="U61" s="3">
+      <c r="V61" s="3">
         <v>43142100</v>
       </c>
-      <c r="V61" s="3">
+      <c r="W61" s="3">
         <v>40307800</v>
       </c>
-      <c r="W61" s="3">
+      <c r="X61" s="3">
         <v>36868700</v>
       </c>
-      <c r="X61" s="3">
+      <c r="Y61" s="3">
         <v>34955700</v>
       </c>
-      <c r="Y61" s="3">
+      <c r="Z61" s="3">
         <v>35115500</v>
       </c>
-      <c r="Z61" s="3">
+      <c r="AA61" s="3">
         <v>34009900</v>
       </c>
-      <c r="AA61" s="3">
+      <c r="AB61" s="3">
         <v>36941800</v>
       </c>
-      <c r="AB61" s="3">
+      <c r="AC61" s="3">
         <v>37408900</v>
       </c>
-      <c r="AC61" s="3">
+      <c r="AD61" s="3">
         <v>35000000</v>
       </c>
-      <c r="AD61" s="3">
+      <c r="AE61" s="3">
         <v>33280700</v>
       </c>
-      <c r="AE61" s="3">
+      <c r="AF61" s="3">
         <v>34538700</v>
       </c>
-      <c r="AF61" s="3">
+      <c r="AG61" s="3">
         <v>33926000</v>
       </c>
     </row>
-    <row r="62" spans="3:32" x14ac:dyDescent="0.2">
+    <row r="62" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C62" s="1" t="s">
         <v>55</v>
       </c>
       <c r="D62" s="3">
-        <v>842200</v>
+        <v>975300</v>
       </c>
       <c r="E62" s="3">
-        <v>800600</v>
+        <v>831300</v>
       </c>
       <c r="F62" s="3">
-        <v>605100</v>
+        <v>790200</v>
       </c>
       <c r="G62" s="3">
-        <v>471900</v>
+        <v>597200</v>
       </c>
       <c r="H62" s="3">
-        <v>462100</v>
+        <v>465800</v>
       </c>
       <c r="I62" s="3">
-        <v>476100</v>
+        <v>456100</v>
       </c>
       <c r="J62" s="3">
+        <v>469900</v>
+      </c>
+      <c r="K62" s="3">
         <v>523500</v>
       </c>
-      <c r="K62" s="3">
+      <c r="L62" s="3">
         <v>608300</v>
       </c>
-      <c r="L62" s="3">
+      <c r="M62" s="3">
         <v>663300</v>
       </c>
-      <c r="M62" s="3">
+      <c r="N62" s="3">
         <v>620300</v>
       </c>
-      <c r="N62" s="3">
+      <c r="O62" s="3">
         <v>542300</v>
       </c>
-      <c r="O62" s="3">
+      <c r="P62" s="3">
         <v>528500</v>
       </c>
-      <c r="P62" s="3">
+      <c r="Q62" s="3">
         <v>720700</v>
       </c>
-      <c r="Q62" s="3">
+      <c r="R62" s="3">
         <v>691400</v>
       </c>
-      <c r="R62" s="3">
+      <c r="S62" s="3">
         <v>680000</v>
       </c>
-      <c r="S62" s="3">
+      <c r="T62" s="3">
         <v>570200</v>
       </c>
-      <c r="T62" s="3">
+      <c r="U62" s="3">
         <v>714600</v>
       </c>
-      <c r="U62" s="3">
+      <c r="V62" s="3">
         <v>648100</v>
       </c>
-      <c r="V62" s="3">
+      <c r="W62" s="3">
         <v>618700</v>
       </c>
-      <c r="W62" s="3">
+      <c r="X62" s="3">
         <v>520300</v>
       </c>
-      <c r="X62" s="3">
+      <c r="Y62" s="3">
         <v>418500</v>
       </c>
-      <c r="Y62" s="3">
+      <c r="Z62" s="3">
         <v>420800</v>
       </c>
-      <c r="Z62" s="3">
+      <c r="AA62" s="3">
         <v>527700</v>
       </c>
-      <c r="AA62" s="3">
+      <c r="AB62" s="3">
         <v>419200</v>
       </c>
-      <c r="AB62" s="3">
+      <c r="AC62" s="3">
         <v>395900</v>
       </c>
-      <c r="AC62" s="3">
+      <c r="AD62" s="3">
         <v>382900</v>
       </c>
-      <c r="AD62" s="3">
+      <c r="AE62" s="3">
         <v>400700</v>
       </c>
-      <c r="AE62" s="3">
+      <c r="AF62" s="3">
         <v>463600</v>
       </c>
-      <c r="AF62" s="3">
+      <c r="AG62" s="3">
         <v>459900</v>
       </c>
     </row>
-    <row r="63" spans="3:32" x14ac:dyDescent="0.2">
+    <row r="63" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C63" s="1" t="s">
         <v>56</v>
       </c>
@@ -5337,8 +5486,11 @@
       <c r="AF63" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="64" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG63" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="64" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C64" s="1" t="s">
         <v>20</v>
       </c>
@@ -5429,8 +5581,11 @@
       <c r="AF64" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="65" spans="2:32" x14ac:dyDescent="0.2">
+      <c r="AG64" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="65" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C65" s="1" t="s">
         <v>57</v>
       </c>
@@ -5521,100 +5676,106 @@
       <c r="AF65" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="66" spans="2:32" x14ac:dyDescent="0.2">
+      <c r="AG65" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="66" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C66" s="1" t="s">
         <v>58</v>
       </c>
       <c r="D66" s="3">
-        <v>349835500</v>
+        <v>354416900</v>
       </c>
       <c r="E66" s="3">
-        <v>348553500</v>
+        <v>345292200</v>
       </c>
       <c r="F66" s="3">
-        <v>345283100</v>
+        <v>344026900</v>
       </c>
       <c r="G66" s="3">
-        <v>347818600</v>
+        <v>340798900</v>
       </c>
       <c r="H66" s="3">
-        <v>364838600</v>
+        <v>343301500</v>
       </c>
       <c r="I66" s="3">
-        <v>352598100</v>
+        <v>360100400</v>
       </c>
       <c r="J66" s="3">
+        <v>348018900</v>
+      </c>
+      <c r="K66" s="3">
         <v>338354200</v>
       </c>
-      <c r="K66" s="3">
+      <c r="L66" s="3">
         <v>316006400</v>
       </c>
-      <c r="L66" s="3">
+      <c r="M66" s="3">
         <v>309651700</v>
       </c>
-      <c r="M66" s="3">
+      <c r="N66" s="3">
         <v>297533600</v>
       </c>
-      <c r="N66" s="3">
+      <c r="O66" s="3">
         <v>290517700</v>
       </c>
-      <c r="O66" s="3">
+      <c r="P66" s="3">
         <v>278260300</v>
       </c>
-      <c r="P66" s="3">
+      <c r="Q66" s="3">
         <v>275726000</v>
       </c>
-      <c r="Q66" s="3">
+      <c r="R66" s="3">
         <v>275487700</v>
       </c>
-      <c r="R66" s="3">
+      <c r="S66" s="3">
         <v>288675900</v>
       </c>
-      <c r="S66" s="3">
+      <c r="T66" s="3">
         <v>289399800</v>
       </c>
-      <c r="T66" s="3">
+      <c r="U66" s="3">
         <v>297278600</v>
       </c>
-      <c r="U66" s="3">
+      <c r="V66" s="3">
         <v>299163500</v>
       </c>
-      <c r="V66" s="3">
+      <c r="W66" s="3">
         <v>296968200</v>
       </c>
-      <c r="W66" s="3">
+      <c r="X66" s="3">
         <v>267714100</v>
       </c>
-      <c r="X66" s="3">
+      <c r="Y66" s="3">
         <v>249559900</v>
       </c>
-      <c r="Y66" s="3">
+      <c r="Z66" s="3">
         <v>256847800</v>
       </c>
-      <c r="Z66" s="3">
+      <c r="AA66" s="3">
         <v>256582900</v>
       </c>
-      <c r="AA66" s="3">
+      <c r="AB66" s="3">
         <v>260418000</v>
       </c>
-      <c r="AB66" s="3">
+      <c r="AC66" s="3">
         <v>261733600</v>
       </c>
-      <c r="AC66" s="3">
+      <c r="AD66" s="3">
         <v>260311800</v>
       </c>
-      <c r="AD66" s="3">
+      <c r="AE66" s="3">
         <v>255640700</v>
       </c>
-      <c r="AE66" s="3">
+      <c r="AF66" s="3">
         <v>261266900</v>
       </c>
-      <c r="AF66" s="3">
+      <c r="AG66" s="3">
         <v>263136400</v>
       </c>
     </row>
-    <row r="67" spans="2:32" x14ac:dyDescent="0.2">
+    <row r="67" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C67" s="1" t="s">
         <v>59</v>
       </c>
@@ -5647,8 +5808,9 @@
       <c r="AD67" s="3"/>
       <c r="AE67" s="3"/>
       <c r="AF67" s="3"/>
-    </row>
-    <row r="68" spans="2:32" x14ac:dyDescent="0.2">
+      <c r="AG67" s="3"/>
+    </row>
+    <row r="68" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C68" s="1" t="s">
         <v>60</v>
       </c>
@@ -5739,8 +5901,11 @@
       <c r="AF68" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="69" spans="2:32" x14ac:dyDescent="0.2">
+      <c r="AG68" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="69" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C69" s="1" t="s">
         <v>61</v>
       </c>
@@ -5831,8 +5996,11 @@
       <c r="AF69" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="70" spans="2:32" x14ac:dyDescent="0.2">
+      <c r="AG69" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="70" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C70" s="1" t="s">
         <v>62</v>
       </c>
@@ -5923,8 +6091,11 @@
       <c r="AF70" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="71" spans="2:32" x14ac:dyDescent="0.2">
+      <c r="AG70" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="71" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C71" s="1" t="s">
         <v>63</v>
       </c>
@@ -6015,100 +6186,106 @@
       <c r="AF71" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="72" spans="2:32" x14ac:dyDescent="0.2">
+      <c r="AG71" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="72" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C72" s="1" t="s">
         <v>64</v>
       </c>
       <c r="D72" s="3">
-        <v>19394600</v>
+        <v>18989700</v>
       </c>
       <c r="E72" s="3">
-        <v>18828100</v>
+        <v>19142700</v>
       </c>
       <c r="F72" s="3">
-        <v>18371900</v>
+        <v>18583600</v>
       </c>
       <c r="G72" s="3">
-        <v>18287600</v>
+        <v>18133300</v>
       </c>
       <c r="H72" s="3">
-        <v>17939700</v>
+        <v>18050100</v>
       </c>
       <c r="I72" s="3">
-        <v>17356000</v>
+        <v>17706700</v>
       </c>
       <c r="J72" s="3">
+        <v>17130600</v>
+      </c>
+      <c r="K72" s="3">
         <v>16662400</v>
       </c>
-      <c r="K72" s="3">
+      <c r="L72" s="3">
         <v>16044400</v>
       </c>
-      <c r="L72" s="3">
+      <c r="M72" s="3">
         <v>15764300</v>
       </c>
-      <c r="M72" s="3">
+      <c r="N72" s="3">
         <v>15298800</v>
       </c>
-      <c r="N72" s="3">
+      <c r="O72" s="3">
         <v>14524300</v>
       </c>
-      <c r="O72" s="3">
+      <c r="P72" s="3">
         <v>14258500</v>
       </c>
-      <c r="P72" s="3">
+      <c r="Q72" s="3">
         <v>14719300</v>
       </c>
-      <c r="Q72" s="3">
+      <c r="R72" s="3">
         <v>14362200</v>
       </c>
-      <c r="R72" s="3">
+      <c r="S72" s="3">
         <v>15002800</v>
       </c>
-      <c r="S72" s="3">
+      <c r="T72" s="3">
         <v>15745800</v>
       </c>
-      <c r="T72" s="3">
+      <c r="U72" s="3">
         <v>15573800</v>
       </c>
-      <c r="U72" s="3">
+      <c r="V72" s="3">
         <v>15698600</v>
       </c>
-      <c r="V72" s="3">
+      <c r="W72" s="3">
         <v>15678000</v>
       </c>
-      <c r="W72" s="3">
+      <c r="X72" s="3">
         <v>14384700</v>
       </c>
-      <c r="X72" s="3">
+      <c r="Y72" s="3">
         <v>13795900</v>
       </c>
-      <c r="Y72" s="3">
+      <c r="Z72" s="3">
         <v>13837700</v>
       </c>
-      <c r="Z72" s="3">
+      <c r="AA72" s="3">
         <v>13273900</v>
       </c>
-      <c r="AA72" s="3">
+      <c r="AB72" s="3">
         <v>13745600</v>
       </c>
-      <c r="AB72" s="3">
+      <c r="AC72" s="3">
         <v>13660700</v>
       </c>
-      <c r="AC72" s="3">
+      <c r="AD72" s="3">
         <v>13507800</v>
       </c>
-      <c r="AD72" s="3">
+      <c r="AE72" s="3">
         <v>13138800</v>
       </c>
-      <c r="AE72" s="3">
+      <c r="AF72" s="3">
         <v>13150400</v>
       </c>
-      <c r="AF72" s="3">
+      <c r="AG72" s="3">
         <v>13062800</v>
       </c>
     </row>
-    <row r="73" spans="2:32" x14ac:dyDescent="0.2">
+    <row r="73" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C73" s="1" t="s">
         <v>65</v>
       </c>
@@ -6199,8 +6376,11 @@
       <c r="AF73" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="74" spans="2:32" x14ac:dyDescent="0.2">
+      <c r="AG73" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="74" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C74" s="1" t="s">
         <v>66</v>
       </c>
@@ -6291,8 +6471,11 @@
       <c r="AF74" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="75" spans="2:32" x14ac:dyDescent="0.2">
+      <c r="AG74" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="75" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C75" s="1" t="s">
         <v>67</v>
       </c>
@@ -6383,100 +6566,106 @@
       <c r="AF75" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="76" spans="2:32" x14ac:dyDescent="0.2">
+      <c r="AG75" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="76" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C76" s="1" t="s">
         <v>68</v>
       </c>
       <c r="D76" s="3">
-        <v>24320600</v>
+        <v>24066800</v>
       </c>
       <c r="E76" s="3">
-        <v>23288400</v>
+        <v>24004800</v>
       </c>
       <c r="F76" s="3">
-        <v>22837900</v>
+        <v>22986000</v>
       </c>
       <c r="G76" s="3">
-        <v>22146700</v>
+        <v>22541300</v>
       </c>
       <c r="H76" s="3">
-        <v>21754500</v>
+        <v>21859000</v>
       </c>
       <c r="I76" s="3">
-        <v>20810100</v>
+        <v>21472000</v>
       </c>
       <c r="J76" s="3">
+        <v>20539800</v>
+      </c>
+      <c r="K76" s="3">
         <v>20238100</v>
       </c>
-      <c r="K76" s="3">
+      <c r="L76" s="3">
         <v>19381500</v>
       </c>
-      <c r="L76" s="3">
+      <c r="M76" s="3">
         <v>18987000</v>
       </c>
-      <c r="M76" s="3">
+      <c r="N76" s="3">
         <v>18419400</v>
       </c>
-      <c r="N76" s="3">
+      <c r="O76" s="3">
         <v>17399500</v>
       </c>
-      <c r="O76" s="3">
+      <c r="P76" s="3">
         <v>17059700</v>
       </c>
-      <c r="P76" s="3">
+      <c r="Q76" s="3">
         <v>17519900</v>
       </c>
-      <c r="Q76" s="3">
+      <c r="R76" s="3">
         <v>17171900</v>
       </c>
-      <c r="R76" s="3">
+      <c r="S76" s="3">
         <v>17677500</v>
       </c>
-      <c r="S76" s="3">
+      <c r="T76" s="3">
         <v>18283800</v>
       </c>
-      <c r="T76" s="3">
+      <c r="U76" s="3">
         <v>17718000</v>
       </c>
-      <c r="U76" s="3">
+      <c r="V76" s="3">
         <v>17110000</v>
       </c>
-      <c r="V76" s="3">
+      <c r="W76" s="3">
         <v>17117400</v>
       </c>
-      <c r="W76" s="3">
+      <c r="X76" s="3">
         <v>18261500</v>
       </c>
-      <c r="X76" s="3">
+      <c r="Y76" s="3">
         <v>17579400</v>
       </c>
-      <c r="Y76" s="3">
+      <c r="Z76" s="3">
         <v>17463800</v>
       </c>
-      <c r="Z76" s="3">
+      <c r="AA76" s="3">
         <v>17085700</v>
       </c>
-      <c r="AA76" s="3">
+      <c r="AB76" s="3">
         <v>17922000</v>
       </c>
-      <c r="AB76" s="3">
+      <c r="AC76" s="3">
         <v>17996500</v>
       </c>
-      <c r="AC76" s="3">
+      <c r="AD76" s="3">
         <v>17825600</v>
       </c>
-      <c r="AD76" s="3">
+      <c r="AE76" s="3">
         <v>17960100</v>
       </c>
-      <c r="AE76" s="3">
+      <c r="AF76" s="3">
         <v>18347500</v>
       </c>
-      <c r="AF76" s="3">
+      <c r="AG76" s="3">
         <v>18412300</v>
       </c>
     </row>
-    <row r="77" spans="2:32" x14ac:dyDescent="0.2">
+    <row r="77" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C77" s="1" t="s">
         <v>69</v>
       </c>
@@ -6567,197 +6756,206 @@
       <c r="AF77" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="79" spans="2:32" x14ac:dyDescent="0.2">
+      <c r="AG77" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="79" spans="2:33" x14ac:dyDescent="0.2">
       <c r="B79" s="1" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="80" spans="2:32" x14ac:dyDescent="0.2">
+    <row r="80" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C80" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D80" s="2">
+        <v>45291</v>
+      </c>
+      <c r="E80" s="2">
         <v>45199</v>
       </c>
-      <c r="E80" s="2">
+      <c r="F80" s="2">
         <v>45107</v>
       </c>
-      <c r="F80" s="2">
+      <c r="G80" s="2">
         <v>45016</v>
       </c>
-      <c r="G80" s="2">
+      <c r="H80" s="2">
         <v>44926</v>
       </c>
-      <c r="H80" s="2">
+      <c r="I80" s="2">
         <v>44834</v>
       </c>
-      <c r="I80" s="2">
+      <c r="J80" s="2">
         <v>44742</v>
       </c>
-      <c r="J80" s="2">
+      <c r="K80" s="2">
         <v>44651</v>
       </c>
-      <c r="K80" s="2">
+      <c r="L80" s="2">
         <v>44561</v>
       </c>
-      <c r="L80" s="2">
+      <c r="M80" s="2">
         <v>44469</v>
       </c>
-      <c r="M80" s="2">
+      <c r="N80" s="2">
         <v>44377</v>
       </c>
-      <c r="N80" s="2">
+      <c r="O80" s="2">
         <v>44286</v>
       </c>
-      <c r="O80" s="2">
+      <c r="P80" s="2">
         <v>44196</v>
       </c>
-      <c r="P80" s="2">
+      <c r="Q80" s="2">
         <v>44104</v>
       </c>
-      <c r="Q80" s="2">
+      <c r="R80" s="2">
         <v>44012</v>
       </c>
-      <c r="R80" s="2">
+      <c r="S80" s="2">
         <v>43921</v>
       </c>
-      <c r="S80" s="2">
+      <c r="T80" s="2">
         <v>43830</v>
       </c>
-      <c r="T80" s="2">
+      <c r="U80" s="2">
         <v>43738</v>
       </c>
-      <c r="U80" s="2">
+      <c r="V80" s="2">
         <v>43646</v>
       </c>
-      <c r="V80" s="2">
+      <c r="W80" s="2">
         <v>43555</v>
       </c>
-      <c r="W80" s="2">
+      <c r="X80" s="2">
         <v>43465</v>
       </c>
-      <c r="X80" s="2">
+      <c r="Y80" s="2">
         <v>43373</v>
       </c>
-      <c r="Y80" s="2">
+      <c r="Z80" s="2">
         <v>43281</v>
       </c>
-      <c r="Z80" s="2">
+      <c r="AA80" s="2">
         <v>43190</v>
       </c>
-      <c r="AA80" s="2">
+      <c r="AB80" s="2">
         <v>43100</v>
       </c>
-      <c r="AB80" s="2">
+      <c r="AC80" s="2">
         <v>43008</v>
       </c>
-      <c r="AC80" s="2">
+      <c r="AD80" s="2">
         <v>42916</v>
       </c>
-      <c r="AD80" s="2">
+      <c r="AE80" s="2">
         <v>42825</v>
       </c>
-      <c r="AE80" s="2">
+      <c r="AF80" s="2">
         <v>42735</v>
       </c>
-      <c r="AF80" s="2">
+      <c r="AG80" s="2">
         <v>42643</v>
       </c>
     </row>
-    <row r="81" spans="3:32" x14ac:dyDescent="0.2">
+    <row r="81" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C81" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D81" s="3">
-        <v>667300</v>
+        <v>25000</v>
       </c>
       <c r="E81" s="3">
-        <v>456200</v>
+        <v>658600</v>
       </c>
       <c r="F81" s="3">
-        <v>680100</v>
+        <v>450300</v>
       </c>
       <c r="G81" s="3">
-        <v>347900</v>
+        <v>671300</v>
       </c>
       <c r="H81" s="3">
-        <v>675700</v>
+        <v>343400</v>
       </c>
       <c r="I81" s="3">
-        <v>693400</v>
+        <v>667000</v>
       </c>
       <c r="J81" s="3">
+        <v>684400</v>
+      </c>
+      <c r="K81" s="3">
         <v>631400</v>
       </c>
-      <c r="K81" s="3">
+      <c r="L81" s="3">
         <v>279500</v>
       </c>
-      <c r="L81" s="3">
+      <c r="M81" s="3">
         <v>570700</v>
       </c>
-      <c r="M81" s="3">
+      <c r="N81" s="3">
         <v>552600</v>
       </c>
-      <c r="N81" s="3">
+      <c r="O81" s="3">
         <v>482000</v>
       </c>
-      <c r="O81" s="3">
+      <c r="P81" s="3">
         <v>112600</v>
       </c>
-      <c r="P81" s="3">
+      <c r="Q81" s="3">
         <v>358800</v>
       </c>
-      <c r="Q81" s="3">
+      <c r="R81" s="3">
         <v>100500</v>
       </c>
-      <c r="R81" s="3">
+      <c r="S81" s="3">
         <v>412900</v>
       </c>
-      <c r="S81" s="3">
+      <c r="T81" s="3">
         <v>174900</v>
       </c>
-      <c r="T81" s="3">
+      <c r="U81" s="3">
         <v>410100</v>
       </c>
-      <c r="U81" s="3">
+      <c r="V81" s="3">
         <v>537700</v>
       </c>
-      <c r="V81" s="3">
+      <c r="W81" s="3">
         <v>517500</v>
       </c>
-      <c r="W81" s="3">
+      <c r="X81" s="3">
         <v>76800</v>
       </c>
-      <c r="X81" s="3">
+      <c r="Y81" s="3">
         <v>453900</v>
       </c>
-      <c r="Y81" s="3">
+      <c r="Z81" s="3">
         <v>569900</v>
       </c>
-      <c r="Z81" s="3">
+      <c r="AA81" s="3">
         <v>463600</v>
       </c>
-      <c r="AA81" s="3">
+      <c r="AB81" s="3">
         <v>84900</v>
       </c>
-      <c r="AB81" s="3">
+      <c r="AC81" s="3">
         <v>212100</v>
       </c>
-      <c r="AC81" s="3">
+      <c r="AD81" s="3">
         <v>369000</v>
       </c>
-      <c r="AD81" s="3">
+      <c r="AE81" s="3">
         <v>517600</v>
       </c>
-      <c r="AE81" s="3">
+      <c r="AF81" s="3">
         <v>88500</v>
       </c>
-      <c r="AF81" s="3">
+      <c r="AG81" s="3">
         <v>275700</v>
       </c>
     </row>
-    <row r="82" spans="3:32" x14ac:dyDescent="0.2">
+    <row r="82" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C82" s="1" t="s">
         <v>71</v>
       </c>
@@ -6790,100 +6988,104 @@
       <c r="AD82" s="3"/>
       <c r="AE82" s="3"/>
       <c r="AF82" s="3"/>
-    </row>
-    <row r="83" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG82" s="3"/>
+    </row>
+    <row r="83" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C83" s="1" t="s">
         <v>72</v>
       </c>
       <c r="D83" s="3">
-        <v>185000</v>
+        <v>200600</v>
       </c>
       <c r="E83" s="3">
-        <v>187100</v>
+        <v>182600</v>
       </c>
       <c r="F83" s="3">
-        <v>189400</v>
+        <v>184700</v>
       </c>
       <c r="G83" s="3">
-        <v>190200</v>
+        <v>186900</v>
       </c>
       <c r="H83" s="3">
-        <v>179000</v>
+        <v>187700</v>
       </c>
       <c r="I83" s="3">
-        <v>177900</v>
+        <v>176600</v>
       </c>
       <c r="J83" s="3">
+        <v>175600</v>
+      </c>
+      <c r="K83" s="3">
         <v>168600</v>
       </c>
-      <c r="K83" s="3">
+      <c r="L83" s="3">
         <v>155900</v>
       </c>
-      <c r="L83" s="3">
+      <c r="M83" s="3">
         <v>149200</v>
       </c>
-      <c r="M83" s="3">
+      <c r="N83" s="3">
         <v>184500</v>
       </c>
-      <c r="N83" s="3">
+      <c r="O83" s="3">
         <v>102900</v>
       </c>
-      <c r="O83" s="3">
+      <c r="P83" s="3">
         <v>101300</v>
       </c>
-      <c r="P83" s="3">
+      <c r="Q83" s="3">
         <v>101500</v>
       </c>
-      <c r="Q83" s="3">
+      <c r="R83" s="3">
         <v>98700</v>
       </c>
-      <c r="R83" s="3">
+      <c r="S83" s="3">
         <v>112300</v>
       </c>
-      <c r="S83" s="3">
+      <c r="T83" s="3">
         <v>120400</v>
       </c>
-      <c r="T83" s="3">
+      <c r="U83" s="3">
         <v>116900</v>
       </c>
-      <c r="U83" s="3">
+      <c r="V83" s="3">
         <v>108900</v>
       </c>
-      <c r="V83" s="3">
+      <c r="W83" s="3">
         <v>93600</v>
       </c>
-      <c r="W83" s="3">
+      <c r="X83" s="3">
         <v>61600</v>
       </c>
-      <c r="X83" s="3">
+      <c r="Y83" s="3">
         <v>58600</v>
       </c>
-      <c r="Y83" s="3">
+      <c r="Z83" s="3">
         <v>56000</v>
       </c>
-      <c r="Z83" s="3">
+      <c r="AA83" s="3">
         <v>50600</v>
       </c>
-      <c r="AA83" s="3">
+      <c r="AB83" s="3">
         <v>49900</v>
       </c>
-      <c r="AB83" s="3">
+      <c r="AC83" s="3">
         <v>50800</v>
       </c>
-      <c r="AC83" s="3">
+      <c r="AD83" s="3">
         <v>51600</v>
       </c>
-      <c r="AD83" s="3">
+      <c r="AE83" s="3">
         <v>55200</v>
       </c>
-      <c r="AE83" s="3">
+      <c r="AF83" s="3">
         <v>54800</v>
       </c>
-      <c r="AF83" s="3">
+      <c r="AG83" s="3">
         <v>53700</v>
       </c>
     </row>
-    <row r="84" spans="3:32" x14ac:dyDescent="0.2">
+    <row r="84" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C84" s="1" t="s">
         <v>73</v>
       </c>
@@ -6974,8 +7176,11 @@
       <c r="AF84" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="85" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG84" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="85" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C85" s="1" t="s">
         <v>74</v>
       </c>
@@ -7066,8 +7271,11 @@
       <c r="AF85" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="86" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG85" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="86" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C86" s="1" t="s">
         <v>75</v>
       </c>
@@ -7158,8 +7366,11 @@
       <c r="AF86" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="87" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG86" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="87" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C87" s="1" t="s">
         <v>76</v>
       </c>
@@ -7250,8 +7461,11 @@
       <c r="AF87" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="88" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG87" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="88" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C88" s="1" t="s">
         <v>77</v>
       </c>
@@ -7342,100 +7556,106 @@
       <c r="AF88" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="89" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG88" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="89" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C89" s="1" t="s">
         <v>78</v>
       </c>
       <c r="D89" s="3">
-        <v>4769000</v>
+        <v>4808900</v>
       </c>
       <c r="E89" s="3">
-        <v>-5734700</v>
+        <v>4707100</v>
       </c>
       <c r="F89" s="3">
-        <v>-2657700</v>
+        <v>-5660200</v>
       </c>
       <c r="G89" s="3">
-        <v>12332300</v>
+        <v>-2623200</v>
       </c>
       <c r="H89" s="3">
-        <v>-3533900</v>
+        <v>12172100</v>
       </c>
       <c r="I89" s="3">
-        <v>-2158400</v>
+        <v>-3488000</v>
       </c>
       <c r="J89" s="3">
+        <v>-2130300</v>
+      </c>
+      <c r="K89" s="3">
         <v>7700600</v>
       </c>
-      <c r="K89" s="3">
+      <c r="L89" s="3">
         <v>4027400</v>
       </c>
-      <c r="L89" s="3">
+      <c r="M89" s="3">
         <v>2586700</v>
       </c>
-      <c r="M89" s="3">
+      <c r="N89" s="3">
         <v>-4607300</v>
       </c>
-      <c r="N89" s="3">
+      <c r="O89" s="3">
         <v>831700</v>
       </c>
-      <c r="O89" s="3">
+      <c r="P89" s="3">
         <v>1545900</v>
       </c>
-      <c r="P89" s="3">
+      <c r="Q89" s="3">
         <v>-766500</v>
       </c>
-      <c r="Q89" s="3">
+      <c r="R89" s="3">
         <v>2718500</v>
       </c>
-      <c r="R89" s="3">
+      <c r="S89" s="3">
         <v>-824700</v>
       </c>
-      <c r="S89" s="3">
+      <c r="T89" s="3">
         <v>-153300</v>
       </c>
-      <c r="T89" s="3">
+      <c r="U89" s="3">
         <v>-428600</v>
       </c>
-      <c r="U89" s="3">
+      <c r="V89" s="3">
         <v>3501700</v>
       </c>
-      <c r="V89" s="3">
+      <c r="W89" s="3">
         <v>-1296100</v>
       </c>
-      <c r="W89" s="3">
+      <c r="X89" s="3">
         <v>5231600</v>
       </c>
-      <c r="X89" s="3">
+      <c r="Y89" s="3">
         <v>908000</v>
       </c>
-      <c r="Y89" s="3">
+      <c r="Z89" s="3">
         <v>643600</v>
       </c>
-      <c r="Z89" s="3">
+      <c r="AA89" s="3">
         <v>877700</v>
       </c>
-      <c r="AA89" s="3">
+      <c r="AB89" s="3">
         <v>-506300</v>
       </c>
-      <c r="AB89" s="3">
+      <c r="AC89" s="3">
         <v>-2456000</v>
       </c>
-      <c r="AC89" s="3">
+      <c r="AD89" s="3">
         <v>-340700</v>
       </c>
-      <c r="AD89" s="3">
+      <c r="AE89" s="3">
         <v>1561500</v>
       </c>
-      <c r="AE89" s="3">
+      <c r="AF89" s="3">
         <v>108800</v>
       </c>
-      <c r="AF89" s="3">
+      <c r="AG89" s="3">
         <v>3807600</v>
       </c>
     </row>
-    <row r="90" spans="3:32" x14ac:dyDescent="0.2">
+    <row r="90" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C90" s="1" t="s">
         <v>79</v>
       </c>
@@ -7468,100 +7688,104 @@
       <c r="AD90" s="3"/>
       <c r="AE90" s="3"/>
       <c r="AF90" s="3"/>
-    </row>
-    <row r="91" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG90" s="3"/>
+    </row>
+    <row r="91" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C91" s="1" t="s">
         <v>80</v>
       </c>
       <c r="D91" s="3">
+        <v>-161762000</v>
+      </c>
+      <c r="E91" s="3">
         <v>-68486000</v>
       </c>
-      <c r="E91" s="3">
+      <c r="F91" s="3">
         <v>-103704000</v>
       </c>
-      <c r="F91" s="3">
+      <c r="G91" s="3">
         <v>-59247000</v>
       </c>
-      <c r="G91" s="3">
+      <c r="H91" s="3">
         <v>-113722000</v>
       </c>
-      <c r="H91" s="3">
+      <c r="I91" s="3">
         <v>-77226000</v>
       </c>
-      <c r="I91" s="3">
+      <c r="J91" s="3">
         <v>-104059000</v>
       </c>
-      <c r="J91" s="3">
+      <c r="K91" s="3">
         <v>-52618000</v>
       </c>
-      <c r="K91" s="3">
+      <c r="L91" s="3">
         <v>-74615000</v>
       </c>
-      <c r="L91" s="3">
+      <c r="M91" s="3">
         <v>-81614000</v>
       </c>
-      <c r="M91" s="3">
+      <c r="N91" s="3">
         <v>-15900</v>
       </c>
-      <c r="N91" s="3">
+      <c r="O91" s="3">
         <v>-14300</v>
       </c>
-      <c r="O91" s="3">
+      <c r="P91" s="3">
         <v>-43600</v>
       </c>
-      <c r="P91" s="3">
+      <c r="Q91" s="3">
         <v>-25600</v>
       </c>
-      <c r="Q91" s="3">
+      <c r="R91" s="3">
         <v>-24800</v>
       </c>
-      <c r="R91" s="3">
+      <c r="S91" s="3">
         <v>-20300</v>
       </c>
-      <c r="S91" s="3">
+      <c r="T91" s="3">
         <v>-190900</v>
       </c>
-      <c r="T91" s="3">
+      <c r="U91" s="3">
         <v>-91000</v>
       </c>
-      <c r="U91" s="3">
+      <c r="V91" s="3">
         <v>-55400</v>
       </c>
-      <c r="V91" s="3">
+      <c r="W91" s="3">
         <v>-31700</v>
       </c>
-      <c r="W91" s="3">
+      <c r="X91" s="3">
         <v>-43000</v>
       </c>
-      <c r="X91" s="3">
+      <c r="Y91" s="3">
         <v>-20100</v>
       </c>
-      <c r="Y91" s="3">
+      <c r="Z91" s="3">
         <v>-18000</v>
       </c>
-      <c r="Z91" s="3">
+      <c r="AA91" s="3">
         <v>-17800</v>
       </c>
-      <c r="AA91" s="3">
+      <c r="AB91" s="3">
         <v>-25100</v>
       </c>
-      <c r="AB91" s="3">
+      <c r="AC91" s="3">
         <v>-57300</v>
       </c>
-      <c r="AC91" s="3">
+      <c r="AD91" s="3">
         <v>-37900</v>
       </c>
-      <c r="AD91" s="3">
+      <c r="AE91" s="3">
         <v>-22400</v>
       </c>
-      <c r="AE91" s="3">
+      <c r="AF91" s="3">
         <v>-111600</v>
       </c>
-      <c r="AF91" s="3">
+      <c r="AG91" s="3">
         <v>-90400</v>
       </c>
     </row>
-    <row r="92" spans="3:32" x14ac:dyDescent="0.2">
+    <row r="92" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C92" s="1" t="s">
         <v>81</v>
       </c>
@@ -7652,8 +7876,11 @@
       <c r="AF92" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="93" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG92" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="93" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C93" s="1" t="s">
         <v>82</v>
       </c>
@@ -7744,100 +7971,106 @@
       <c r="AF93" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="94" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG93" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="94" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C94" s="1" t="s">
         <v>83</v>
       </c>
       <c r="D94" s="3">
-        <v>-1148000</v>
+        <v>-616300</v>
       </c>
       <c r="E94" s="3">
-        <v>-265300</v>
+        <v>-1133100</v>
       </c>
       <c r="F94" s="3">
-        <v>302000</v>
+        <v>-261800</v>
       </c>
       <c r="G94" s="3">
-        <v>-2988000</v>
+        <v>298100</v>
       </c>
       <c r="H94" s="3">
-        <v>-2483900</v>
+        <v>-2949200</v>
       </c>
       <c r="I94" s="3">
-        <v>2384800</v>
+        <v>-2451700</v>
       </c>
       <c r="J94" s="3">
+        <v>2353800</v>
+      </c>
+      <c r="K94" s="3">
         <v>-2278800</v>
       </c>
-      <c r="K94" s="3">
+      <c r="L94" s="3">
         <v>-4489600</v>
       </c>
-      <c r="L94" s="3">
+      <c r="M94" s="3">
         <v>-3902300</v>
       </c>
-      <c r="M94" s="3">
+      <c r="N94" s="3">
         <v>1124900</v>
       </c>
-      <c r="N94" s="3">
+      <c r="O94" s="3">
         <v>-723400</v>
       </c>
-      <c r="O94" s="3">
+      <c r="P94" s="3">
         <v>-365200</v>
       </c>
-      <c r="P94" s="3">
+      <c r="Q94" s="3">
         <v>-124500</v>
       </c>
-      <c r="Q94" s="3">
+      <c r="R94" s="3">
         <v>-446100</v>
       </c>
-      <c r="R94" s="3">
+      <c r="S94" s="3">
         <v>-179800</v>
       </c>
-      <c r="S94" s="3">
+      <c r="T94" s="3">
         <v>-962200</v>
       </c>
-      <c r="T94" s="3">
+      <c r="U94" s="3">
         <v>-913600</v>
       </c>
-      <c r="U94" s="3">
+      <c r="V94" s="3">
         <v>-5520900</v>
       </c>
-      <c r="V94" s="3">
+      <c r="W94" s="3">
         <v>-97900</v>
       </c>
-      <c r="W94" s="3">
+      <c r="X94" s="3">
         <v>-5105000</v>
       </c>
-      <c r="X94" s="3">
+      <c r="Y94" s="3">
         <v>-2452600</v>
       </c>
-      <c r="Y94" s="3">
+      <c r="Z94" s="3">
         <v>-1063800</v>
       </c>
-      <c r="Z94" s="3">
+      <c r="AA94" s="3">
         <v>-587600</v>
       </c>
-      <c r="AA94" s="3">
+      <c r="AB94" s="3">
         <v>1277600</v>
       </c>
-      <c r="AB94" s="3">
+      <c r="AC94" s="3">
         <v>-195600</v>
       </c>
-      <c r="AC94" s="3">
+      <c r="AD94" s="3">
         <v>183200</v>
       </c>
-      <c r="AD94" s="3">
+      <c r="AE94" s="3">
         <v>392500</v>
       </c>
-      <c r="AE94" s="3">
+      <c r="AF94" s="3">
         <v>-2371700</v>
       </c>
-      <c r="AF94" s="3">
+      <c r="AG94" s="3">
         <v>694800</v>
       </c>
     </row>
-    <row r="95" spans="3:32" x14ac:dyDescent="0.2">
+    <row r="95" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C95" s="1" t="s">
         <v>84</v>
       </c>
@@ -7870,16 +8103,17 @@
       <c r="AD95" s="3"/>
       <c r="AE95" s="3"/>
       <c r="AF95" s="3"/>
-    </row>
-    <row r="96" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG95" s="3"/>
+    </row>
+    <row r="96" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C96" s="1" t="s">
         <v>85</v>
       </c>
       <c r="D96" s="3">
-        <v>-100600</v>
+        <v>-102300</v>
       </c>
       <c r="E96" s="3">
-        <v>0</v>
+        <v>-99300</v>
       </c>
       <c r="F96" s="3">
         <v>0</v>
@@ -7888,10 +8122,10 @@
         <v>0</v>
       </c>
       <c r="H96" s="3">
-        <v>-84100</v>
+        <v>0</v>
       </c>
       <c r="I96" s="3">
-        <v>0</v>
+        <v>-83000</v>
       </c>
       <c r="J96" s="3">
         <v>0</v>
@@ -7900,11 +8134,11 @@
         <v>0</v>
       </c>
       <c r="L96" s="3">
+        <v>0</v>
+      </c>
+      <c r="M96" s="3">
         <v>-81300</v>
       </c>
-      <c r="M96" s="3">
-        <v>0</v>
-      </c>
       <c r="N96" s="3">
         <v>0</v>
       </c>
@@ -7948,22 +8182,25 @@
         <v>0</v>
       </c>
       <c r="AB96" s="3">
+        <v>0</v>
+      </c>
+      <c r="AC96" s="3">
         <v>-59200</v>
       </c>
-      <c r="AC96" s="3">
+      <c r="AD96" s="3">
         <v>-237000</v>
       </c>
-      <c r="AD96" s="3">
-        <v>0</v>
-      </c>
       <c r="AE96" s="3">
+        <v>0</v>
+      </c>
+      <c r="AF96" s="3">
         <v>-38100</v>
       </c>
-      <c r="AF96" s="3">
+      <c r="AG96" s="3">
         <v>-22800</v>
       </c>
     </row>
-    <row r="97" spans="3:32" x14ac:dyDescent="0.2">
+    <row r="97" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C97" s="1" t="s">
         <v>86</v>
       </c>
@@ -8054,8 +8291,11 @@
       <c r="AF97" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="98" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG97" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="98" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C98" s="1" t="s">
         <v>87</v>
       </c>
@@ -8146,8 +8386,11 @@
       <c r="AF98" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="99" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG98" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="99" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C99" s="1" t="s">
         <v>88</v>
       </c>
@@ -8238,280 +8481,292 @@
       <c r="AF99" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="100" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG99" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="100" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C100" s="1" t="s">
         <v>89</v>
       </c>
       <c r="D100" s="3">
-        <v>-414200</v>
+        <v>-470600</v>
       </c>
       <c r="E100" s="3">
-        <v>-1052000</v>
+        <v>-408800</v>
       </c>
       <c r="F100" s="3">
-        <v>-259300</v>
+        <v>-1038300</v>
       </c>
       <c r="G100" s="3">
-        <v>-5284600</v>
+        <v>-256000</v>
       </c>
       <c r="H100" s="3">
-        <v>1790300</v>
+        <v>-5215900</v>
       </c>
       <c r="I100" s="3">
-        <v>3039800</v>
+        <v>1767000</v>
       </c>
       <c r="J100" s="3">
+        <v>3000400</v>
+      </c>
+      <c r="K100" s="3">
         <v>1932700</v>
       </c>
-      <c r="K100" s="3">
+      <c r="L100" s="3">
         <v>2031800</v>
       </c>
-      <c r="L100" s="3">
+      <c r="M100" s="3">
         <v>1404600</v>
       </c>
-      <c r="M100" s="3">
+      <c r="N100" s="3">
         <v>2911000</v>
       </c>
-      <c r="N100" s="3">
+      <c r="O100" s="3">
         <v>453200</v>
       </c>
-      <c r="O100" s="3">
+      <c r="P100" s="3">
         <v>261800</v>
       </c>
-      <c r="P100" s="3">
+      <c r="Q100" s="3">
         <v>553800</v>
       </c>
-      <c r="Q100" s="3">
+      <c r="R100" s="3">
         <v>-2356000</v>
       </c>
-      <c r="R100" s="3">
+      <c r="S100" s="3">
         <v>3526800</v>
       </c>
-      <c r="S100" s="3">
+      <c r="T100" s="3">
         <v>-950700</v>
       </c>
-      <c r="T100" s="3">
+      <c r="U100" s="3">
         <v>3000500</v>
       </c>
-      <c r="U100" s="3">
+      <c r="V100" s="3">
         <v>3588600</v>
       </c>
-      <c r="V100" s="3">
+      <c r="W100" s="3">
         <v>-289800</v>
       </c>
-      <c r="W100" s="3">
+      <c r="X100" s="3">
         <v>491400</v>
       </c>
-      <c r="X100" s="3">
+      <c r="Y100" s="3">
         <v>1689200</v>
       </c>
-      <c r="Y100" s="3">
+      <c r="Z100" s="3">
         <v>354700</v>
       </c>
-      <c r="Z100" s="3">
+      <c r="AA100" s="3">
         <v>-1323700</v>
       </c>
-      <c r="AA100" s="3">
+      <c r="AB100" s="3">
         <v>-309500</v>
       </c>
-      <c r="AB100" s="3">
+      <c r="AC100" s="3">
         <v>2140800</v>
       </c>
-      <c r="AC100" s="3">
+      <c r="AD100" s="3">
         <v>-384900</v>
       </c>
-      <c r="AD100" s="3">
+      <c r="AE100" s="3">
         <v>-1500100</v>
       </c>
-      <c r="AE100" s="3">
+      <c r="AF100" s="3">
         <v>1503800</v>
       </c>
-      <c r="AF100" s="3">
+      <c r="AG100" s="3">
         <v>-1778900</v>
       </c>
     </row>
-    <row r="101" spans="3:32" x14ac:dyDescent="0.2">
+    <row r="101" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C101" s="1" t="s">
         <v>90</v>
       </c>
       <c r="D101" s="3">
-        <v>28300</v>
+        <v>-176700</v>
       </c>
       <c r="E101" s="3">
-        <v>-106600</v>
+        <v>27900</v>
       </c>
       <c r="F101" s="3">
-        <v>126300</v>
+        <v>-105200</v>
       </c>
       <c r="G101" s="3">
-        <v>-1518600</v>
+        <v>124700</v>
       </c>
       <c r="H101" s="3">
-        <v>673600</v>
+        <v>-1498900</v>
       </c>
       <c r="I101" s="3">
-        <v>665700</v>
+        <v>664800</v>
       </c>
       <c r="J101" s="3">
+        <v>657000</v>
+      </c>
+      <c r="K101" s="3">
         <v>203100</v>
       </c>
-      <c r="K101" s="3">
+      <c r="L101" s="3">
         <v>68900</v>
       </c>
-      <c r="L101" s="3">
+      <c r="M101" s="3">
         <v>409500</v>
       </c>
-      <c r="M101" s="3">
+      <c r="N101" s="3">
         <v>18100</v>
       </c>
-      <c r="N101" s="3">
+      <c r="O101" s="3">
         <v>295500</v>
       </c>
-      <c r="O101" s="3">
+      <c r="P101" s="3">
         <v>-571700</v>
       </c>
-      <c r="P101" s="3">
+      <c r="Q101" s="3">
         <v>-142900</v>
       </c>
-      <c r="Q101" s="3">
+      <c r="R101" s="3">
         <v>-159900</v>
       </c>
-      <c r="R101" s="3">
+      <c r="S101" s="3">
         <v>200400</v>
       </c>
-      <c r="S101" s="3">
+      <c r="T101" s="3">
         <v>369400</v>
       </c>
-      <c r="T101" s="3">
+      <c r="U101" s="3">
         <v>-340600</v>
       </c>
-      <c r="U101" s="3">
+      <c r="V101" s="3">
         <v>51200</v>
       </c>
-      <c r="V101" s="3">
+      <c r="W101" s="3">
         <v>90500</v>
       </c>
-      <c r="W101" s="3">
+      <c r="X101" s="3">
         <v>6400</v>
       </c>
-      <c r="X101" s="3">
+      <c r="Y101" s="3">
         <v>-76600</v>
       </c>
-      <c r="Y101" s="3">
+      <c r="Z101" s="3">
         <v>218900</v>
       </c>
-      <c r="Z101" s="3">
+      <c r="AA101" s="3">
         <v>50500</v>
       </c>
-      <c r="AA101" s="3">
+      <c r="AB101" s="3">
         <v>-377500</v>
       </c>
-      <c r="AB101" s="3">
+      <c r="AC101" s="3">
         <v>14000</v>
       </c>
-      <c r="AC101" s="3">
+      <c r="AD101" s="3">
         <v>8400</v>
       </c>
-      <c r="AD101" s="3">
+      <c r="AE101" s="3">
         <v>-108300</v>
       </c>
-      <c r="AE101" s="3">
+      <c r="AF101" s="3">
         <v>138000</v>
       </c>
-      <c r="AF101" s="3">
+      <c r="AG101" s="3">
         <v>-105900</v>
       </c>
     </row>
-    <row r="102" spans="3:32" x14ac:dyDescent="0.2">
+    <row r="102" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C102" s="1" t="s">
         <v>91</v>
       </c>
       <c r="D102" s="3">
-        <v>3235100</v>
+        <v>3545200</v>
       </c>
       <c r="E102" s="3">
-        <v>-7158500</v>
+        <v>3193100</v>
       </c>
       <c r="F102" s="3">
-        <v>-2488700</v>
+        <v>-7065500</v>
       </c>
       <c r="G102" s="3">
-        <v>2541100</v>
+        <v>-2456400</v>
       </c>
       <c r="H102" s="3">
-        <v>-3554000</v>
+        <v>2508100</v>
       </c>
       <c r="I102" s="3">
-        <v>3931900</v>
+        <v>-3507800</v>
       </c>
       <c r="J102" s="3">
+        <v>3880900</v>
+      </c>
+      <c r="K102" s="3">
         <v>7557600</v>
       </c>
-      <c r="K102" s="3">
+      <c r="L102" s="3">
         <v>1638600</v>
       </c>
-      <c r="L102" s="3">
+      <c r="M102" s="3">
         <v>498500</v>
       </c>
-      <c r="M102" s="3">
+      <c r="N102" s="3">
         <v>-553300</v>
       </c>
-      <c r="N102" s="3">
+      <c r="O102" s="3">
         <v>857000</v>
       </c>
-      <c r="O102" s="3">
+      <c r="P102" s="3">
         <v>870800</v>
       </c>
-      <c r="P102" s="3">
+      <c r="Q102" s="3">
         <v>-480000</v>
       </c>
-      <c r="Q102" s="3">
+      <c r="R102" s="3">
         <v>-243500</v>
       </c>
-      <c r="R102" s="3">
+      <c r="S102" s="3">
         <v>2722600</v>
       </c>
-      <c r="S102" s="3">
+      <c r="T102" s="3">
         <v>-1696800</v>
       </c>
-      <c r="T102" s="3">
+      <c r="U102" s="3">
         <v>1317700</v>
       </c>
-      <c r="U102" s="3">
+      <c r="V102" s="3">
         <v>1620600</v>
       </c>
-      <c r="V102" s="3">
+      <c r="W102" s="3">
         <v>-1593300</v>
       </c>
-      <c r="W102" s="3">
+      <c r="X102" s="3">
         <v>624400</v>
       </c>
-      <c r="X102" s="3">
+      <c r="Y102" s="3">
         <v>68000</v>
       </c>
-      <c r="Y102" s="3">
+      <c r="Z102" s="3">
         <v>153400</v>
       </c>
-      <c r="Z102" s="3">
+      <c r="AA102" s="3">
         <v>-983000</v>
       </c>
-      <c r="AA102" s="3">
+      <c r="AB102" s="3">
         <v>84300</v>
       </c>
-      <c r="AB102" s="3">
+      <c r="AC102" s="3">
         <v>-496900</v>
       </c>
-      <c r="AC102" s="3">
+      <c r="AD102" s="3">
         <v>-534100</v>
       </c>
-      <c r="AD102" s="3">
+      <c r="AE102" s="3">
         <v>345600</v>
       </c>
-      <c r="AE102" s="3">
+      <c r="AF102" s="3">
         <v>-621200</v>
       </c>
-      <c r="AF102" s="3">
+      <c r="AG102" s="3">
         <v>2617600</v>
       </c>
     </row>

--- a/AAII_Financials/Quarterly/WF_QTR_FIN.xlsx
+++ b/AAII_Financials/Quarterly/WF_QTR_FIN.xlsx
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="185" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="200" uniqueCount="92">
   <si>
     <t>WF</t>
   </si>
@@ -656,224 +656,231 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet2"/>
-  <dimension ref="A5:AG102"/>
+  <dimension ref="A5:AH102"/>
   <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="5" style="1" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="26.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="69.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="17" style="1" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="16" style="1" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="17" style="1" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="16" style="1" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="17" style="1" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="16" style="1" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="17" style="1" bestFit="1" customWidth="1"/>
-    <col min="11" max="33" width="16" style="1" bestFit="1" customWidth="1"/>
-    <col min="34" max="16384" width="9.140625" style="1"/>
+    <col min="4" max="4" width="16" style="1" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="17" style="1" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="16" style="1" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="17" style="1" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="16" style="1" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="17" style="1" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="16" style="1" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="17" style="1" bestFit="1" customWidth="1"/>
+    <col min="12" max="34" width="16" style="1" bestFit="1" customWidth="1"/>
+    <col min="35" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
-    <row r="5" spans="1:33" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:34" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:33" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:34" x14ac:dyDescent="0.2">
       <c r="B6" s="1" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:33" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:34" x14ac:dyDescent="0.2">
       <c r="C7" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D7" s="2">
+        <v>45382</v>
+      </c>
+      <c r="E7" s="2">
         <v>45291</v>
       </c>
-      <c r="E7" s="2">
+      <c r="F7" s="2">
         <v>45199</v>
       </c>
-      <c r="F7" s="2">
+      <c r="G7" s="2">
         <v>45107</v>
       </c>
-      <c r="G7" s="2">
+      <c r="H7" s="2">
         <v>45016</v>
       </c>
-      <c r="H7" s="2">
+      <c r="I7" s="2">
         <v>44926</v>
       </c>
-      <c r="I7" s="2">
+      <c r="J7" s="2">
         <v>44834</v>
       </c>
-      <c r="J7" s="2">
+      <c r="K7" s="2">
         <v>44742</v>
       </c>
-      <c r="K7" s="2">
+      <c r="L7" s="2">
         <v>44651</v>
       </c>
-      <c r="L7" s="2">
+      <c r="M7" s="2">
         <v>44561</v>
       </c>
-      <c r="M7" s="2">
+      <c r="N7" s="2">
         <v>44469</v>
       </c>
-      <c r="N7" s="2">
+      <c r="O7" s="2">
         <v>44377</v>
       </c>
-      <c r="O7" s="2">
+      <c r="P7" s="2">
         <v>44286</v>
       </c>
-      <c r="P7" s="2">
+      <c r="Q7" s="2">
         <v>44196</v>
       </c>
-      <c r="Q7" s="2">
+      <c r="R7" s="2">
         <v>44104</v>
       </c>
-      <c r="R7" s="2">
+      <c r="S7" s="2">
         <v>44012</v>
       </c>
-      <c r="S7" s="2">
+      <c r="T7" s="2">
         <v>43921</v>
       </c>
-      <c r="T7" s="2">
+      <c r="U7" s="2">
         <v>43830</v>
       </c>
-      <c r="U7" s="2">
+      <c r="V7" s="2">
         <v>43738</v>
       </c>
-      <c r="V7" s="2">
+      <c r="W7" s="2">
         <v>43646</v>
       </c>
-      <c r="W7" s="2">
+      <c r="X7" s="2">
         <v>43555</v>
       </c>
-      <c r="X7" s="2">
+      <c r="Y7" s="2">
         <v>43465</v>
       </c>
-      <c r="Y7" s="2">
+      <c r="Z7" s="2">
         <v>43373</v>
       </c>
-      <c r="Z7" s="2">
+      <c r="AA7" s="2">
         <v>43281</v>
       </c>
-      <c r="AA7" s="2">
+      <c r="AB7" s="2">
         <v>43190</v>
       </c>
-      <c r="AB7" s="2">
+      <c r="AC7" s="2">
         <v>43100</v>
       </c>
-      <c r="AC7" s="2">
+      <c r="AD7" s="2">
         <v>43008</v>
       </c>
-      <c r="AD7" s="2">
+      <c r="AE7" s="2">
         <v>42916</v>
       </c>
-      <c r="AE7" s="2">
+      <c r="AF7" s="2">
         <v>42825</v>
       </c>
-      <c r="AF7" s="2">
+      <c r="AG7" s="2">
         <v>42735</v>
       </c>
-      <c r="AG7" s="2">
+      <c r="AH7" s="2">
         <v>42643</v>
       </c>
     </row>
-    <row r="8" spans="1:33" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:34" x14ac:dyDescent="0.2">
       <c r="C8" s="1" t="s">
         <v>3</v>
       </c>
-      <c r="D8" s="3">
-        <v>4122500</v>
+      <c r="D8" s="3" t="s">
+        <v>5</v>
       </c>
       <c r="E8" s="3">
-        <v>3981800</v>
+        <v>3959800</v>
       </c>
       <c r="F8" s="3">
-        <v>3837000</v>
+        <v>3824700</v>
       </c>
       <c r="G8" s="3">
-        <v>3746100</v>
+        <v>3685600</v>
       </c>
       <c r="H8" s="3">
-        <v>3508300</v>
+        <v>3598300</v>
       </c>
       <c r="I8" s="3">
-        <v>2906900</v>
+        <v>3369900</v>
       </c>
       <c r="J8" s="3">
+        <v>2792200</v>
+      </c>
+      <c r="K8" s="3">
         <v>2487200</v>
       </c>
-      <c r="K8" s="3">
+      <c r="L8" s="3">
         <v>2264400</v>
       </c>
-      <c r="L8" s="3">
+      <c r="M8" s="3">
         <v>2026000</v>
       </c>
-      <c r="M8" s="3">
+      <c r="N8" s="3">
         <v>1862200</v>
       </c>
-      <c r="N8" s="3">
+      <c r="O8" s="3">
         <v>1787500</v>
       </c>
-      <c r="O8" s="3">
+      <c r="P8" s="3">
         <v>1722100</v>
       </c>
-      <c r="P8" s="3">
+      <c r="Q8" s="3">
         <v>1728200</v>
       </c>
-      <c r="Q8" s="3">
+      <c r="R8" s="3">
         <v>1749800</v>
       </c>
-      <c r="R8" s="3">
+      <c r="S8" s="3">
         <v>1857400</v>
       </c>
-      <c r="S8" s="3">
+      <c r="T8" s="3">
         <v>2028100</v>
       </c>
-      <c r="T8" s="3">
+      <c r="U8" s="3">
         <v>2216400</v>
       </c>
-      <c r="U8" s="3">
+      <c r="V8" s="3">
         <v>2287800</v>
       </c>
-      <c r="V8" s="3">
+      <c r="W8" s="3">
         <v>2353100</v>
       </c>
-      <c r="W8" s="3">
+      <c r="X8" s="3">
         <v>2369400</v>
       </c>
-      <c r="X8" s="3">
+      <c r="Y8" s="3">
         <v>2154000</v>
       </c>
-      <c r="Y8" s="3">
+      <c r="Z8" s="3">
         <v>2006200</v>
       </c>
-      <c r="Z8" s="3">
+      <c r="AA8" s="3">
         <v>1989700</v>
       </c>
-      <c r="AA8" s="3">
+      <c r="AB8" s="3">
         <v>1910800</v>
       </c>
-      <c r="AB8" s="3">
+      <c r="AC8" s="3">
         <v>1912500</v>
       </c>
-      <c r="AC8" s="3">
+      <c r="AD8" s="3">
         <v>1925300</v>
       </c>
-      <c r="AD8" s="3">
+      <c r="AE8" s="3">
         <v>1853100</v>
       </c>
-      <c r="AE8" s="3">
+      <c r="AF8" s="3">
         <v>1833700</v>
       </c>
-      <c r="AF8" s="3">
+      <c r="AG8" s="3">
         <v>1898800</v>
       </c>
-      <c r="AG8" s="3">
+      <c r="AH8" s="3">
         <v>1898000</v>
       </c>
     </row>
-    <row r="9" spans="1:33" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:34" x14ac:dyDescent="0.2">
       <c r="C9" s="1" t="s">
         <v>4</v>
       </c>
@@ -967,8 +974,11 @@
       <c r="AG9" s="3" t="s">
         <v>5</v>
       </c>
-    </row>
-    <row r="10" spans="1:33" x14ac:dyDescent="0.2">
+      <c r="AH9" s="3" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="10" spans="1:34" x14ac:dyDescent="0.2">
       <c r="C10" s="1" t="s">
         <v>6</v>
       </c>
@@ -1062,8 +1072,11 @@
       <c r="AG10" s="3" t="s">
         <v>5</v>
       </c>
-    </row>
-    <row r="11" spans="1:33" x14ac:dyDescent="0.2">
+      <c r="AH10" s="3" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="11" spans="1:34" x14ac:dyDescent="0.2">
       <c r="C11" s="1" t="s">
         <v>7</v>
       </c>
@@ -1097,8 +1110,9 @@
       <c r="AE11" s="3"/>
       <c r="AF11" s="3"/>
       <c r="AG11" s="3"/>
-    </row>
-    <row r="12" spans="1:33" x14ac:dyDescent="0.2">
+      <c r="AH11" s="3"/>
+    </row>
+    <row r="12" spans="1:34" x14ac:dyDescent="0.2">
       <c r="C12" s="1" t="s">
         <v>8</v>
       </c>
@@ -1192,8 +1206,11 @@
       <c r="AG12" s="3" t="s">
         <v>5</v>
       </c>
-    </row>
-    <row r="13" spans="1:33" x14ac:dyDescent="0.2">
+      <c r="AH12" s="3" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="13" spans="1:34" x14ac:dyDescent="0.2">
       <c r="C13" s="1" t="s">
         <v>9</v>
       </c>
@@ -1287,8 +1304,11 @@
       <c r="AG13" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="14" spans="1:33" x14ac:dyDescent="0.2">
+      <c r="AH13" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="14" spans="1:34" x14ac:dyDescent="0.2">
       <c r="C14" s="1" t="s">
         <v>10</v>
       </c>
@@ -1382,103 +1402,109 @@
       <c r="AG14" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="15" spans="1:33" x14ac:dyDescent="0.2">
+      <c r="AH14" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="15" spans="1:34" x14ac:dyDescent="0.2">
       <c r="C15" s="1" t="s">
         <v>11</v>
       </c>
       <c r="D15" s="3">
-        <v>-100000</v>
+        <v>-94800</v>
       </c>
       <c r="E15" s="3">
-        <v>-89500</v>
+        <v>-96100</v>
       </c>
       <c r="F15" s="3">
-        <v>-96000</v>
+        <v>-85900</v>
       </c>
       <c r="G15" s="3">
-        <v>-100900</v>
+        <v>-92200</v>
       </c>
       <c r="H15" s="3">
-        <v>-102800</v>
+        <v>-96900</v>
       </c>
       <c r="I15" s="3">
-        <v>-95900</v>
+        <v>-98800</v>
       </c>
       <c r="J15" s="3">
+        <v>-92100</v>
+      </c>
+      <c r="K15" s="3">
         <v>-100700</v>
       </c>
-      <c r="K15" s="3">
+      <c r="L15" s="3">
         <v>-101400</v>
       </c>
-      <c r="L15" s="3">
+      <c r="M15" s="3">
         <v>-98200</v>
       </c>
-      <c r="M15" s="3">
+      <c r="N15" s="3">
         <v>-97600</v>
       </c>
-      <c r="N15" s="3">
+      <c r="O15" s="3">
         <v>-97400</v>
       </c>
-      <c r="O15" s="3">
+      <c r="P15" s="3">
         <v>-100600</v>
       </c>
-      <c r="P15" s="3">
+      <c r="Q15" s="3">
         <v>-99400</v>
       </c>
-      <c r="Q15" s="3">
+      <c r="R15" s="3">
         <v>-99600</v>
       </c>
-      <c r="R15" s="3">
+      <c r="S15" s="3">
         <v>-96100</v>
       </c>
-      <c r="S15" s="3">
+      <c r="T15" s="3">
         <v>-109500</v>
       </c>
-      <c r="T15" s="3">
+      <c r="U15" s="3">
         <v>-115200</v>
       </c>
-      <c r="U15" s="3">
+      <c r="V15" s="3">
         <v>-112100</v>
       </c>
-      <c r="V15" s="3">
+      <c r="W15" s="3">
         <v>-104100</v>
       </c>
-      <c r="W15" s="3">
+      <c r="X15" s="3">
         <v>-88900</v>
       </c>
-      <c r="X15" s="3">
+      <c r="Y15" s="3">
         <v>-50500</v>
       </c>
-      <c r="Y15" s="3">
+      <c r="Z15" s="3">
         <v>-47800</v>
       </c>
-      <c r="Z15" s="3">
+      <c r="AA15" s="3">
         <v>-44700</v>
       </c>
-      <c r="AA15" s="3">
+      <c r="AB15" s="3">
         <v>-40700</v>
       </c>
-      <c r="AB15" s="3">
+      <c r="AC15" s="3">
         <v>-39500</v>
       </c>
-      <c r="AC15" s="3">
+      <c r="AD15" s="3">
         <v>-40300</v>
       </c>
-      <c r="AD15" s="3">
+      <c r="AE15" s="3">
         <v>-40800</v>
       </c>
-      <c r="AE15" s="3">
+      <c r="AF15" s="3">
         <v>-44500</v>
       </c>
-      <c r="AF15" s="3">
+      <c r="AG15" s="3">
         <v>-54800</v>
       </c>
-      <c r="AG15" s="3">
+      <c r="AH15" s="3">
         <v>-53700</v>
       </c>
     </row>
-    <row r="16" spans="1:33" x14ac:dyDescent="0.2">
+    <row r="16" spans="1:34" x14ac:dyDescent="0.2">
       <c r="D16" s="3"/>
       <c r="E16" s="3"/>
       <c r="F16" s="3"/>
@@ -1509,198 +1535,205 @@
       <c r="AE16" s="3"/>
       <c r="AF16" s="3"/>
       <c r="AG16" s="3"/>
-    </row>
-    <row r="17" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH16" s="3"/>
+    </row>
+    <row r="17" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C17" s="1" t="s">
         <v>12</v>
       </c>
-      <c r="D17" s="3">
-        <v>3114600</v>
+      <c r="D17" s="3" t="s">
+        <v>5</v>
       </c>
       <c r="E17" s="3">
-        <v>2517900</v>
+        <v>2991600</v>
       </c>
       <c r="F17" s="3">
-        <v>2592200</v>
+        <v>2418600</v>
       </c>
       <c r="G17" s="3">
-        <v>2258600</v>
+        <v>2489900</v>
       </c>
       <c r="H17" s="3">
-        <v>1923200</v>
+        <v>2169500</v>
       </c>
       <c r="I17" s="3">
-        <v>1296400</v>
+        <v>1847300</v>
       </c>
       <c r="J17" s="3">
+        <v>1245200</v>
+      </c>
+      <c r="K17" s="3">
         <v>1121400</v>
       </c>
-      <c r="K17" s="3">
+      <c r="L17" s="3">
         <v>861300</v>
       </c>
-      <c r="L17" s="3">
+      <c r="M17" s="3">
         <v>772200</v>
       </c>
-      <c r="M17" s="3">
+      <c r="N17" s="3">
         <v>616800</v>
       </c>
-      <c r="N17" s="3">
+      <c r="O17" s="3">
         <v>573600</v>
       </c>
-      <c r="O17" s="3">
+      <c r="P17" s="3">
         <v>625700</v>
       </c>
-      <c r="P17" s="3">
+      <c r="Q17" s="3">
         <v>727900</v>
       </c>
-      <c r="Q17" s="3">
+      <c r="R17" s="3">
         <v>721100</v>
       </c>
-      <c r="R17" s="3">
+      <c r="S17" s="3">
         <v>966200</v>
       </c>
-      <c r="S17" s="3">
+      <c r="T17" s="3">
         <v>926000</v>
       </c>
-      <c r="T17" s="3">
+      <c r="U17" s="3">
         <v>1019500</v>
       </c>
-      <c r="U17" s="3">
+      <c r="V17" s="3">
         <v>1190700</v>
       </c>
-      <c r="V17" s="3">
+      <c r="W17" s="3">
         <v>1111900</v>
       </c>
-      <c r="W17" s="3">
+      <c r="X17" s="3">
         <v>1098300</v>
       </c>
-      <c r="X17" s="3">
+      <c r="Y17" s="3">
         <v>1157200</v>
       </c>
-      <c r="Y17" s="3">
+      <c r="Z17" s="3">
         <v>918800</v>
       </c>
-      <c r="Z17" s="3">
+      <c r="AA17" s="3">
         <v>752200</v>
       </c>
-      <c r="AA17" s="3">
+      <c r="AB17" s="3">
         <v>877900</v>
       </c>
-      <c r="AB17" s="3">
+      <c r="AC17" s="3">
         <v>1026000</v>
       </c>
-      <c r="AC17" s="3">
+      <c r="AD17" s="3">
         <v>926800</v>
       </c>
-      <c r="AD17" s="3">
+      <c r="AE17" s="3">
         <v>906500</v>
       </c>
-      <c r="AE17" s="3">
+      <c r="AF17" s="3">
         <v>830000</v>
       </c>
-      <c r="AF17" s="3">
+      <c r="AG17" s="3">
         <v>903100</v>
       </c>
-      <c r="AG17" s="3">
+      <c r="AH17" s="3">
         <v>963600</v>
       </c>
     </row>
-    <row r="18" spans="3:33" x14ac:dyDescent="0.2">
+    <row r="18" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C18" s="1" t="s">
         <v>13</v>
       </c>
-      <c r="D18" s="3">
-        <v>1008000</v>
+      <c r="D18" s="3" t="s">
+        <v>5</v>
       </c>
       <c r="E18" s="3">
-        <v>1463900</v>
+        <v>968200</v>
       </c>
       <c r="F18" s="3">
-        <v>1244800</v>
+        <v>1406100</v>
       </c>
       <c r="G18" s="3">
-        <v>1487500</v>
+        <v>1195700</v>
       </c>
       <c r="H18" s="3">
-        <v>1585100</v>
+        <v>1428800</v>
       </c>
       <c r="I18" s="3">
-        <v>1610600</v>
+        <v>1522600</v>
       </c>
       <c r="J18" s="3">
+        <v>1547000</v>
+      </c>
+      <c r="K18" s="3">
         <v>1365800</v>
       </c>
-      <c r="K18" s="3">
+      <c r="L18" s="3">
         <v>1403000</v>
       </c>
-      <c r="L18" s="3">
+      <c r="M18" s="3">
         <v>1253800</v>
       </c>
-      <c r="M18" s="3">
+      <c r="N18" s="3">
         <v>1245400</v>
       </c>
-      <c r="N18" s="3">
+      <c r="O18" s="3">
         <v>1213900</v>
       </c>
-      <c r="O18" s="3">
+      <c r="P18" s="3">
         <v>1096400</v>
       </c>
-      <c r="P18" s="3">
+      <c r="Q18" s="3">
         <v>1000300</v>
       </c>
-      <c r="Q18" s="3">
+      <c r="R18" s="3">
         <v>1028700</v>
       </c>
-      <c r="R18" s="3">
+      <c r="S18" s="3">
         <v>891200</v>
       </c>
-      <c r="S18" s="3">
+      <c r="T18" s="3">
         <v>1102100</v>
       </c>
-      <c r="T18" s="3">
+      <c r="U18" s="3">
         <v>1196900</v>
       </c>
-      <c r="U18" s="3">
+      <c r="V18" s="3">
         <v>1097100</v>
       </c>
-      <c r="V18" s="3">
+      <c r="W18" s="3">
         <v>1241200</v>
       </c>
-      <c r="W18" s="3">
+      <c r="X18" s="3">
         <v>1271100</v>
       </c>
-      <c r="X18" s="3">
+      <c r="Y18" s="3">
         <v>996800</v>
       </c>
-      <c r="Y18" s="3">
+      <c r="Z18" s="3">
         <v>1087400</v>
       </c>
-      <c r="Z18" s="3">
+      <c r="AA18" s="3">
         <v>1237400</v>
       </c>
-      <c r="AA18" s="3">
+      <c r="AB18" s="3">
         <v>1032900</v>
       </c>
-      <c r="AB18" s="3">
+      <c r="AC18" s="3">
         <v>886500</v>
       </c>
-      <c r="AC18" s="3">
+      <c r="AD18" s="3">
         <v>998500</v>
       </c>
-      <c r="AD18" s="3">
+      <c r="AE18" s="3">
         <v>946600</v>
       </c>
-      <c r="AE18" s="3">
+      <c r="AF18" s="3">
         <v>1003700</v>
       </c>
-      <c r="AF18" s="3">
+      <c r="AG18" s="3">
         <v>995700</v>
       </c>
-      <c r="AG18" s="3">
+      <c r="AH18" s="3">
         <v>934400</v>
       </c>
     </row>
-    <row r="19" spans="3:33" x14ac:dyDescent="0.2">
+    <row r="19" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C19" s="1" t="s">
         <v>14</v>
       </c>
@@ -1734,198 +1767,205 @@
       <c r="AE19" s="3"/>
       <c r="AF19" s="3"/>
       <c r="AG19" s="3"/>
-    </row>
-    <row r="20" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH19" s="3"/>
+    </row>
+    <row r="20" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C20" s="1" t="s">
         <v>15</v>
       </c>
-      <c r="D20" s="3">
-        <v>-915100</v>
+      <c r="D20" s="3" t="s">
+        <v>5</v>
       </c>
       <c r="E20" s="3">
-        <v>-516400</v>
+        <v>-879000</v>
       </c>
       <c r="F20" s="3">
-        <v>-577400</v>
+        <v>-496000</v>
       </c>
       <c r="G20" s="3">
-        <v>-522100</v>
+        <v>-554600</v>
       </c>
       <c r="H20" s="3">
-        <v>-1030900</v>
+        <v>-501500</v>
       </c>
       <c r="I20" s="3">
-        <v>-631500</v>
+        <v>-990200</v>
       </c>
       <c r="J20" s="3">
+        <v>-606600</v>
+      </c>
+      <c r="K20" s="3">
         <v>-375600</v>
       </c>
-      <c r="K20" s="3">
+      <c r="L20" s="3">
         <v>-505900</v>
       </c>
-      <c r="L20" s="3">
+      <c r="M20" s="3">
         <v>-806400</v>
       </c>
-      <c r="M20" s="3">
+      <c r="N20" s="3">
         <v>-394200</v>
       </c>
-      <c r="N20" s="3">
+      <c r="O20" s="3">
         <v>-406900</v>
       </c>
-      <c r="O20" s="3">
+      <c r="P20" s="3">
         <v>-399500</v>
       </c>
-      <c r="P20" s="3">
+      <c r="Q20" s="3">
         <v>-784600</v>
       </c>
-      <c r="Q20" s="3">
+      <c r="R20" s="3">
         <v>-508200</v>
       </c>
-      <c r="R20" s="3">
+      <c r="S20" s="3">
         <v>-674600</v>
       </c>
-      <c r="S20" s="3">
+      <c r="T20" s="3">
         <v>-492400</v>
       </c>
-      <c r="T20" s="3">
+      <c r="U20" s="3">
         <v>-920900</v>
       </c>
-      <c r="U20" s="3">
+      <c r="V20" s="3">
         <v>-527400</v>
       </c>
-      <c r="V20" s="3">
+      <c r="W20" s="3">
         <v>-447200</v>
       </c>
-      <c r="W20" s="3">
+      <c r="X20" s="3">
         <v>-519600</v>
       </c>
-      <c r="X20" s="3">
+      <c r="Y20" s="3">
         <v>-847700</v>
       </c>
-      <c r="Y20" s="3">
+      <c r="Z20" s="3">
         <v>-418500</v>
       </c>
-      <c r="Z20" s="3">
+      <c r="AA20" s="3">
         <v>-401200</v>
       </c>
-      <c r="AA20" s="3">
+      <c r="AB20" s="3">
         <v>-355800</v>
       </c>
-      <c r="AB20" s="3">
+      <c r="AC20" s="3">
         <v>-756300</v>
       </c>
-      <c r="AC20" s="3">
+      <c r="AD20" s="3">
         <v>-671500</v>
       </c>
-      <c r="AD20" s="3">
+      <c r="AE20" s="3">
         <v>-417500</v>
       </c>
-      <c r="AE20" s="3">
+      <c r="AF20" s="3">
         <v>-274500</v>
       </c>
-      <c r="AF20" s="3">
+      <c r="AG20" s="3">
         <v>-821100</v>
       </c>
-      <c r="AG20" s="3">
+      <c r="AH20" s="3">
         <v>-531000</v>
       </c>
     </row>
-    <row r="21" spans="3:33" x14ac:dyDescent="0.2">
+    <row r="21" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C21" s="1" t="s">
         <v>16</v>
       </c>
-      <c r="D21" s="3">
-        <v>293400</v>
+      <c r="D21" s="3" t="s">
+        <v>5</v>
       </c>
       <c r="E21" s="3">
-        <v>1130200</v>
+        <v>281800</v>
       </c>
       <c r="F21" s="3">
-        <v>852100</v>
+        <v>1085500</v>
       </c>
       <c r="G21" s="3">
-        <v>1152400</v>
+        <v>818500</v>
       </c>
       <c r="H21" s="3">
-        <v>741900</v>
+        <v>1106900</v>
       </c>
       <c r="I21" s="3">
-        <v>1155700</v>
+        <v>712600</v>
       </c>
       <c r="J21" s="3">
+        <v>1110000</v>
+      </c>
+      <c r="K21" s="3">
         <v>1165700</v>
       </c>
-      <c r="K21" s="3">
+      <c r="L21" s="3">
         <v>1065700</v>
       </c>
-      <c r="L21" s="3">
+      <c r="M21" s="3">
         <v>603300</v>
       </c>
-      <c r="M21" s="3">
+      <c r="N21" s="3">
         <v>1000500</v>
       </c>
-      <c r="N21" s="3">
+      <c r="O21" s="3">
         <v>991500</v>
       </c>
-      <c r="O21" s="3">
+      <c r="P21" s="3">
         <v>799800</v>
       </c>
-      <c r="P21" s="3">
+      <c r="Q21" s="3">
         <v>316900</v>
       </c>
-      <c r="Q21" s="3">
+      <c r="R21" s="3">
         <v>622000</v>
       </c>
-      <c r="R21" s="3">
+      <c r="S21" s="3">
         <v>315300</v>
       </c>
-      <c r="S21" s="3">
+      <c r="T21" s="3">
         <v>721900</v>
       </c>
-      <c r="T21" s="3">
+      <c r="U21" s="3">
         <v>396300</v>
       </c>
-      <c r="U21" s="3">
+      <c r="V21" s="3">
         <v>686600</v>
       </c>
-      <c r="V21" s="3">
+      <c r="W21" s="3">
         <v>902900</v>
       </c>
-      <c r="W21" s="3">
+      <c r="X21" s="3">
         <v>845100</v>
       </c>
-      <c r="X21" s="3">
+      <c r="Y21" s="3">
         <v>210800</v>
       </c>
-      <c r="Y21" s="3">
+      <c r="Z21" s="3">
         <v>727400</v>
       </c>
-      <c r="Z21" s="3">
+      <c r="AA21" s="3">
         <v>892200</v>
       </c>
-      <c r="AA21" s="3">
+      <c r="AB21" s="3">
         <v>727700</v>
       </c>
-      <c r="AB21" s="3">
+      <c r="AC21" s="3">
         <v>180100</v>
       </c>
-      <c r="AC21" s="3">
+      <c r="AD21" s="3">
         <v>377800</v>
       </c>
-      <c r="AD21" s="3">
+      <c r="AE21" s="3">
         <v>580800</v>
       </c>
-      <c r="AE21" s="3">
+      <c r="AF21" s="3">
         <v>784400</v>
       </c>
-      <c r="AF21" s="3">
+      <c r="AG21" s="3">
         <v>229400</v>
       </c>
-      <c r="AG21" s="3">
+      <c r="AH21" s="3">
         <v>457200</v>
       </c>
     </row>
-    <row r="22" spans="3:33" x14ac:dyDescent="0.2">
+    <row r="22" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C22" s="1" t="s">
         <v>17</v>
       </c>
@@ -2019,198 +2059,207 @@
       <c r="AG22" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="23" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH22" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="23" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C23" s="1" t="s">
         <v>18</v>
       </c>
       <c r="D23" s="3">
-        <v>92800</v>
+        <v>835100</v>
       </c>
       <c r="E23" s="3">
-        <v>947600</v>
+        <v>89200</v>
       </c>
       <c r="F23" s="3">
-        <v>667400</v>
+        <v>910100</v>
       </c>
       <c r="G23" s="3">
-        <v>965400</v>
+        <v>641100</v>
       </c>
       <c r="H23" s="3">
-        <v>554200</v>
+        <v>927300</v>
       </c>
       <c r="I23" s="3">
-        <v>979000</v>
+        <v>532400</v>
       </c>
       <c r="J23" s="3">
+        <v>940400</v>
+      </c>
+      <c r="K23" s="3">
         <v>990200</v>
       </c>
-      <c r="K23" s="3">
+      <c r="L23" s="3">
         <v>897100</v>
       </c>
-      <c r="L23" s="3">
+      <c r="M23" s="3">
         <v>447400</v>
       </c>
-      <c r="M23" s="3">
+      <c r="N23" s="3">
         <v>851200</v>
       </c>
-      <c r="N23" s="3">
+      <c r="O23" s="3">
         <v>807000</v>
       </c>
-      <c r="O23" s="3">
+      <c r="P23" s="3">
         <v>696900</v>
       </c>
-      <c r="P23" s="3">
+      <c r="Q23" s="3">
         <v>215700</v>
       </c>
-      <c r="Q23" s="3">
+      <c r="R23" s="3">
         <v>520500</v>
       </c>
-      <c r="R23" s="3">
+      <c r="S23" s="3">
         <v>216600</v>
       </c>
-      <c r="S23" s="3">
+      <c r="T23" s="3">
         <v>609600</v>
       </c>
-      <c r="T23" s="3">
+      <c r="U23" s="3">
         <v>276000</v>
       </c>
-      <c r="U23" s="3">
+      <c r="V23" s="3">
         <v>569700</v>
       </c>
-      <c r="V23" s="3">
+      <c r="W23" s="3">
         <v>794000</v>
       </c>
-      <c r="W23" s="3">
+      <c r="X23" s="3">
         <v>751500</v>
       </c>
-      <c r="X23" s="3">
+      <c r="Y23" s="3">
         <v>149100</v>
       </c>
-      <c r="Y23" s="3">
+      <c r="Z23" s="3">
         <v>668900</v>
       </c>
-      <c r="Z23" s="3">
+      <c r="AA23" s="3">
         <v>836200</v>
       </c>
-      <c r="AA23" s="3">
+      <c r="AB23" s="3">
         <v>677100</v>
       </c>
-      <c r="AB23" s="3">
+      <c r="AC23" s="3">
         <v>130200</v>
       </c>
-      <c r="AC23" s="3">
+      <c r="AD23" s="3">
         <v>327000</v>
       </c>
-      <c r="AD23" s="3">
+      <c r="AE23" s="3">
         <v>529200</v>
       </c>
-      <c r="AE23" s="3">
+      <c r="AF23" s="3">
         <v>729200</v>
       </c>
-      <c r="AF23" s="3">
+      <c r="AG23" s="3">
         <v>174600</v>
       </c>
-      <c r="AG23" s="3">
+      <c r="AH23" s="3">
         <v>403400</v>
       </c>
     </row>
-    <row r="24" spans="3:33" x14ac:dyDescent="0.2">
+    <row r="24" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C24" s="1" t="s">
         <v>19</v>
       </c>
       <c r="D24" s="3">
-        <v>20700</v>
+        <v>222700</v>
       </c>
       <c r="E24" s="3">
-        <v>249800</v>
+        <v>19800</v>
       </c>
       <c r="F24" s="3">
-        <v>160400</v>
+        <v>239900</v>
       </c>
       <c r="G24" s="3">
-        <v>246000</v>
+        <v>154000</v>
       </c>
       <c r="H24" s="3">
-        <v>150500</v>
+        <v>236300</v>
       </c>
       <c r="I24" s="3">
-        <v>269700</v>
+        <v>144500</v>
       </c>
       <c r="J24" s="3">
+        <v>259000</v>
+      </c>
+      <c r="K24" s="3">
         <v>240200</v>
       </c>
-      <c r="K24" s="3">
+      <c r="L24" s="3">
         <v>225300</v>
       </c>
-      <c r="L24" s="3">
+      <c r="M24" s="3">
         <v>113100</v>
       </c>
-      <c r="M24" s="3">
+      <c r="N24" s="3">
         <v>232900</v>
       </c>
-      <c r="N24" s="3">
+      <c r="O24" s="3">
         <v>193200</v>
       </c>
-      <c r="O24" s="3">
+      <c r="P24" s="3">
         <v>164900</v>
       </c>
-      <c r="P24" s="3">
+      <c r="Q24" s="3">
         <v>53200</v>
       </c>
-      <c r="Q24" s="3">
+      <c r="R24" s="3">
         <v>118800</v>
       </c>
-      <c r="R24" s="3">
+      <c r="S24" s="3">
         <v>50000</v>
       </c>
-      <c r="S24" s="3">
+      <c r="T24" s="3">
         <v>157800</v>
       </c>
-      <c r="T24" s="3">
+      <c r="U24" s="3">
         <v>79200</v>
       </c>
-      <c r="U24" s="3">
+      <c r="V24" s="3">
         <v>115700</v>
       </c>
-      <c r="V24" s="3">
+      <c r="W24" s="3">
         <v>215500</v>
       </c>
-      <c r="W24" s="3">
+      <c r="X24" s="3">
         <v>192300</v>
       </c>
-      <c r="X24" s="3">
+      <c r="Y24" s="3">
         <v>39300</v>
       </c>
-      <c r="Y24" s="3">
+      <c r="Z24" s="3">
         <v>179200</v>
       </c>
-      <c r="Z24" s="3">
+      <c r="AA24" s="3">
         <v>229900</v>
       </c>
-      <c r="AA24" s="3">
+      <c r="AB24" s="3">
         <v>177700</v>
       </c>
-      <c r="AB24" s="3">
+      <c r="AC24" s="3">
         <v>9000</v>
       </c>
-      <c r="AC24" s="3">
+      <c r="AD24" s="3">
         <v>77600</v>
       </c>
-      <c r="AD24" s="3">
+      <c r="AE24" s="3">
         <v>118800</v>
       </c>
-      <c r="AE24" s="3">
+      <c r="AF24" s="3">
         <v>163600</v>
       </c>
-      <c r="AF24" s="3">
+      <c r="AG24" s="3">
         <v>30300</v>
       </c>
-      <c r="AG24" s="3">
+      <c r="AH24" s="3">
         <v>80000</v>
       </c>
     </row>
-    <row r="25" spans="3:33" x14ac:dyDescent="0.2">
+    <row r="25" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C25" s="1" t="s">
         <v>20</v>
       </c>
@@ -2304,198 +2353,207 @@
       <c r="AG25" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="26" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH25" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="26" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C26" s="1" t="s">
         <v>21</v>
       </c>
-      <c r="D26" s="3">
-        <v>72200</v>
+      <c r="D26" s="3" t="s">
+        <v>5</v>
       </c>
       <c r="E26" s="3">
-        <v>697800</v>
+        <v>69300</v>
       </c>
       <c r="F26" s="3">
-        <v>507100</v>
+        <v>670200</v>
       </c>
       <c r="G26" s="3">
-        <v>719400</v>
+        <v>487000</v>
       </c>
       <c r="H26" s="3">
-        <v>403800</v>
+        <v>691000</v>
       </c>
       <c r="I26" s="3">
-        <v>709400</v>
+        <v>387800</v>
       </c>
       <c r="J26" s="3">
+        <v>681400</v>
+      </c>
+      <c r="K26" s="3">
         <v>750000</v>
       </c>
-      <c r="K26" s="3">
+      <c r="L26" s="3">
         <v>671800</v>
       </c>
-      <c r="L26" s="3">
+      <c r="M26" s="3">
         <v>334300</v>
       </c>
-      <c r="M26" s="3">
+      <c r="N26" s="3">
         <v>618300</v>
       </c>
-      <c r="N26" s="3">
+      <c r="O26" s="3">
         <v>613800</v>
       </c>
-      <c r="O26" s="3">
+      <c r="P26" s="3">
         <v>532000</v>
       </c>
-      <c r="P26" s="3">
+      <c r="Q26" s="3">
         <v>162400</v>
       </c>
-      <c r="Q26" s="3">
+      <c r="R26" s="3">
         <v>401700</v>
       </c>
-      <c r="R26" s="3">
+      <c r="S26" s="3">
         <v>166500</v>
       </c>
-      <c r="S26" s="3">
+      <c r="T26" s="3">
         <v>451800</v>
       </c>
-      <c r="T26" s="3">
+      <c r="U26" s="3">
         <v>196800</v>
       </c>
-      <c r="U26" s="3">
+      <c r="V26" s="3">
         <v>454000</v>
       </c>
-      <c r="V26" s="3">
+      <c r="W26" s="3">
         <v>578500</v>
       </c>
-      <c r="W26" s="3">
+      <c r="X26" s="3">
         <v>559200</v>
       </c>
-      <c r="X26" s="3">
+      <c r="Y26" s="3">
         <v>109900</v>
       </c>
-      <c r="Y26" s="3">
+      <c r="Z26" s="3">
         <v>489700</v>
       </c>
-      <c r="Z26" s="3">
+      <c r="AA26" s="3">
         <v>606300</v>
       </c>
-      <c r="AA26" s="3">
+      <c r="AB26" s="3">
         <v>499400</v>
       </c>
-      <c r="AB26" s="3">
+      <c r="AC26" s="3">
         <v>121100</v>
       </c>
-      <c r="AC26" s="3">
+      <c r="AD26" s="3">
         <v>249400</v>
       </c>
-      <c r="AD26" s="3">
+      <c r="AE26" s="3">
         <v>410300</v>
       </c>
-      <c r="AE26" s="3">
+      <c r="AF26" s="3">
         <v>565600</v>
       </c>
-      <c r="AF26" s="3">
+      <c r="AG26" s="3">
         <v>144300</v>
       </c>
-      <c r="AG26" s="3">
+      <c r="AH26" s="3">
         <v>323500</v>
       </c>
     </row>
-    <row r="27" spans="3:33" x14ac:dyDescent="0.2">
+    <row r="27" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C27" s="1" t="s">
         <v>22</v>
       </c>
-      <c r="D27" s="3">
-        <v>25000</v>
+      <c r="D27" s="3" t="s">
+        <v>5</v>
       </c>
       <c r="E27" s="3">
-        <v>658600</v>
+        <v>24000</v>
       </c>
       <c r="F27" s="3">
-        <v>450300</v>
+        <v>632600</v>
       </c>
       <c r="G27" s="3">
-        <v>671300</v>
+        <v>432500</v>
       </c>
       <c r="H27" s="3">
-        <v>343400</v>
+        <v>644800</v>
       </c>
       <c r="I27" s="3">
-        <v>667000</v>
+        <v>329800</v>
       </c>
       <c r="J27" s="3">
+        <v>640600</v>
+      </c>
+      <c r="K27" s="3">
         <v>684400</v>
       </c>
-      <c r="K27" s="3">
+      <c r="L27" s="3">
         <v>631400</v>
       </c>
-      <c r="L27" s="3">
+      <c r="M27" s="3">
         <v>279500</v>
       </c>
-      <c r="M27" s="3">
+      <c r="N27" s="3">
         <v>570700</v>
       </c>
-      <c r="N27" s="3">
+      <c r="O27" s="3">
         <v>552600</v>
       </c>
-      <c r="O27" s="3">
+      <c r="P27" s="3">
         <v>482000</v>
       </c>
-      <c r="P27" s="3">
+      <c r="Q27" s="3">
         <v>112600</v>
       </c>
-      <c r="Q27" s="3">
+      <c r="R27" s="3">
         <v>358800</v>
       </c>
-      <c r="R27" s="3">
+      <c r="S27" s="3">
         <v>100500</v>
       </c>
-      <c r="S27" s="3">
+      <c r="T27" s="3">
         <v>412900</v>
       </c>
-      <c r="T27" s="3">
+      <c r="U27" s="3">
         <v>174900</v>
       </c>
-      <c r="U27" s="3">
+      <c r="V27" s="3">
         <v>410100</v>
       </c>
-      <c r="V27" s="3">
+      <c r="W27" s="3">
         <v>537700</v>
       </c>
-      <c r="W27" s="3">
+      <c r="X27" s="3">
         <v>517500</v>
       </c>
-      <c r="X27" s="3">
+      <c r="Y27" s="3">
         <v>76800</v>
       </c>
-      <c r="Y27" s="3">
+      <c r="Z27" s="3">
         <v>453900</v>
       </c>
-      <c r="Z27" s="3">
+      <c r="AA27" s="3">
         <v>569900</v>
       </c>
-      <c r="AA27" s="3">
+      <c r="AB27" s="3">
         <v>463600</v>
       </c>
-      <c r="AB27" s="3">
+      <c r="AC27" s="3">
         <v>84900</v>
       </c>
-      <c r="AC27" s="3">
+      <c r="AD27" s="3">
         <v>212100</v>
       </c>
-      <c r="AD27" s="3">
+      <c r="AE27" s="3">
         <v>369000</v>
       </c>
-      <c r="AE27" s="3">
+      <c r="AF27" s="3">
         <v>517600</v>
       </c>
-      <c r="AF27" s="3">
+      <c r="AG27" s="3">
         <v>88500</v>
       </c>
-      <c r="AG27" s="3">
+      <c r="AH27" s="3">
         <v>275700</v>
       </c>
     </row>
-    <row r="28" spans="3:33" x14ac:dyDescent="0.2">
+    <row r="28" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C28" s="1" t="s">
         <v>23</v>
       </c>
@@ -2589,8 +2647,11 @@
       <c r="AG28" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="29" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH28" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="29" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C29" s="1" t="s">
         <v>24</v>
       </c>
@@ -2684,8 +2745,11 @@
       <c r="AG29" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="30" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH29" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="30" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C30" s="1" t="s">
         <v>25</v>
       </c>
@@ -2779,8 +2843,11 @@
       <c r="AG30" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="31" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH30" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="31" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C31" s="1" t="s">
         <v>26</v>
       </c>
@@ -2874,198 +2941,207 @@
       <c r="AG31" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="32" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH31" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="32" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C32" s="1" t="s">
         <v>27</v>
       </c>
-      <c r="D32" s="3">
-        <v>915100</v>
+      <c r="D32" s="3" t="s">
+        <v>5</v>
       </c>
       <c r="E32" s="3">
-        <v>516400</v>
+        <v>879000</v>
       </c>
       <c r="F32" s="3">
-        <v>577400</v>
+        <v>496000</v>
       </c>
       <c r="G32" s="3">
-        <v>522100</v>
+        <v>554600</v>
       </c>
       <c r="H32" s="3">
-        <v>1030900</v>
+        <v>501500</v>
       </c>
       <c r="I32" s="3">
-        <v>631500</v>
+        <v>990200</v>
       </c>
       <c r="J32" s="3">
+        <v>606600</v>
+      </c>
+      <c r="K32" s="3">
         <v>375600</v>
       </c>
-      <c r="K32" s="3">
+      <c r="L32" s="3">
         <v>505900</v>
       </c>
-      <c r="L32" s="3">
+      <c r="M32" s="3">
         <v>806400</v>
       </c>
-      <c r="M32" s="3">
+      <c r="N32" s="3">
         <v>394200</v>
       </c>
-      <c r="N32" s="3">
+      <c r="O32" s="3">
         <v>406900</v>
       </c>
-      <c r="O32" s="3">
+      <c r="P32" s="3">
         <v>399500</v>
       </c>
-      <c r="P32" s="3">
+      <c r="Q32" s="3">
         <v>784600</v>
       </c>
-      <c r="Q32" s="3">
+      <c r="R32" s="3">
         <v>508200</v>
       </c>
-      <c r="R32" s="3">
+      <c r="S32" s="3">
         <v>674600</v>
       </c>
-      <c r="S32" s="3">
+      <c r="T32" s="3">
         <v>492400</v>
       </c>
-      <c r="T32" s="3">
+      <c r="U32" s="3">
         <v>920900</v>
       </c>
-      <c r="U32" s="3">
+      <c r="V32" s="3">
         <v>527400</v>
       </c>
-      <c r="V32" s="3">
+      <c r="W32" s="3">
         <v>447200</v>
       </c>
-      <c r="W32" s="3">
+      <c r="X32" s="3">
         <v>519600</v>
       </c>
-      <c r="X32" s="3">
+      <c r="Y32" s="3">
         <v>847700</v>
       </c>
-      <c r="Y32" s="3">
+      <c r="Z32" s="3">
         <v>418500</v>
       </c>
-      <c r="Z32" s="3">
+      <c r="AA32" s="3">
         <v>401200</v>
       </c>
-      <c r="AA32" s="3">
+      <c r="AB32" s="3">
         <v>355800</v>
       </c>
-      <c r="AB32" s="3">
+      <c r="AC32" s="3">
         <v>756300</v>
       </c>
-      <c r="AC32" s="3">
+      <c r="AD32" s="3">
         <v>671500</v>
       </c>
-      <c r="AD32" s="3">
+      <c r="AE32" s="3">
         <v>417500</v>
       </c>
-      <c r="AE32" s="3">
+      <c r="AF32" s="3">
         <v>274500</v>
       </c>
-      <c r="AF32" s="3">
+      <c r="AG32" s="3">
         <v>821100</v>
       </c>
-      <c r="AG32" s="3">
+      <c r="AH32" s="3">
         <v>531000</v>
       </c>
     </row>
-    <row r="33" spans="2:33" x14ac:dyDescent="0.2">
+    <row r="33" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C33" s="1" t="s">
         <v>28</v>
       </c>
-      <c r="D33" s="3">
-        <v>25000</v>
+      <c r="D33" s="3" t="s">
+        <v>5</v>
       </c>
       <c r="E33" s="3">
-        <v>658600</v>
+        <v>24000</v>
       </c>
       <c r="F33" s="3">
-        <v>450300</v>
+        <v>632600</v>
       </c>
       <c r="G33" s="3">
-        <v>671300</v>
+        <v>432500</v>
       </c>
       <c r="H33" s="3">
-        <v>343400</v>
+        <v>644800</v>
       </c>
       <c r="I33" s="3">
-        <v>667000</v>
+        <v>329800</v>
       </c>
       <c r="J33" s="3">
+        <v>640600</v>
+      </c>
+      <c r="K33" s="3">
         <v>684400</v>
       </c>
-      <c r="K33" s="3">
+      <c r="L33" s="3">
         <v>631400</v>
       </c>
-      <c r="L33" s="3">
+      <c r="M33" s="3">
         <v>279500</v>
       </c>
-      <c r="M33" s="3">
+      <c r="N33" s="3">
         <v>570700</v>
       </c>
-      <c r="N33" s="3">
+      <c r="O33" s="3">
         <v>552600</v>
       </c>
-      <c r="O33" s="3">
+      <c r="P33" s="3">
         <v>482000</v>
       </c>
-      <c r="P33" s="3">
+      <c r="Q33" s="3">
         <v>112600</v>
       </c>
-      <c r="Q33" s="3">
+      <c r="R33" s="3">
         <v>358800</v>
       </c>
-      <c r="R33" s="3">
+      <c r="S33" s="3">
         <v>100500</v>
       </c>
-      <c r="S33" s="3">
+      <c r="T33" s="3">
         <v>412900</v>
       </c>
-      <c r="T33" s="3">
+      <c r="U33" s="3">
         <v>174900</v>
       </c>
-      <c r="U33" s="3">
+      <c r="V33" s="3">
         <v>410100</v>
       </c>
-      <c r="V33" s="3">
+      <c r="W33" s="3">
         <v>537700</v>
       </c>
-      <c r="W33" s="3">
+      <c r="X33" s="3">
         <v>517500</v>
       </c>
-      <c r="X33" s="3">
+      <c r="Y33" s="3">
         <v>76800</v>
       </c>
-      <c r="Y33" s="3">
+      <c r="Z33" s="3">
         <v>453900</v>
       </c>
-      <c r="Z33" s="3">
+      <c r="AA33" s="3">
         <v>569900</v>
       </c>
-      <c r="AA33" s="3">
+      <c r="AB33" s="3">
         <v>463600</v>
       </c>
-      <c r="AB33" s="3">
+      <c r="AC33" s="3">
         <v>84900</v>
       </c>
-      <c r="AC33" s="3">
+      <c r="AD33" s="3">
         <v>212100</v>
       </c>
-      <c r="AD33" s="3">
+      <c r="AE33" s="3">
         <v>369000</v>
       </c>
-      <c r="AE33" s="3">
+      <c r="AF33" s="3">
         <v>517600</v>
       </c>
-      <c r="AF33" s="3">
+      <c r="AG33" s="3">
         <v>88500</v>
       </c>
-      <c r="AG33" s="3">
+      <c r="AH33" s="3">
         <v>275700</v>
       </c>
     </row>
-    <row r="34" spans="2:33" x14ac:dyDescent="0.2">
+    <row r="34" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C34" s="1" t="s">
         <v>29</v>
       </c>
@@ -3159,203 +3235,212 @@
       <c r="AG34" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="35" spans="2:33" x14ac:dyDescent="0.2">
+      <c r="AH34" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="35" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C35" s="1" t="s">
         <v>30</v>
       </c>
-      <c r="D35" s="3">
-        <v>25000</v>
+      <c r="D35" s="3" t="s">
+        <v>5</v>
       </c>
       <c r="E35" s="3">
-        <v>658600</v>
+        <v>24000</v>
       </c>
       <c r="F35" s="3">
-        <v>450300</v>
+        <v>632600</v>
       </c>
       <c r="G35" s="3">
-        <v>671300</v>
+        <v>432500</v>
       </c>
       <c r="H35" s="3">
-        <v>343400</v>
+        <v>644800</v>
       </c>
       <c r="I35" s="3">
-        <v>667000</v>
+        <v>329800</v>
       </c>
       <c r="J35" s="3">
+        <v>640600</v>
+      </c>
+      <c r="K35" s="3">
         <v>684400</v>
       </c>
-      <c r="K35" s="3">
+      <c r="L35" s="3">
         <v>631400</v>
       </c>
-      <c r="L35" s="3">
+      <c r="M35" s="3">
         <v>279500</v>
       </c>
-      <c r="M35" s="3">
+      <c r="N35" s="3">
         <v>570700</v>
       </c>
-      <c r="N35" s="3">
+      <c r="O35" s="3">
         <v>552600</v>
       </c>
-      <c r="O35" s="3">
+      <c r="P35" s="3">
         <v>482000</v>
       </c>
-      <c r="P35" s="3">
+      <c r="Q35" s="3">
         <v>112600</v>
       </c>
-      <c r="Q35" s="3">
+      <c r="R35" s="3">
         <v>358800</v>
       </c>
-      <c r="R35" s="3">
+      <c r="S35" s="3">
         <v>100500</v>
       </c>
-      <c r="S35" s="3">
+      <c r="T35" s="3">
         <v>412900</v>
       </c>
-      <c r="T35" s="3">
+      <c r="U35" s="3">
         <v>174900</v>
       </c>
-      <c r="U35" s="3">
+      <c r="V35" s="3">
         <v>410100</v>
       </c>
-      <c r="V35" s="3">
+      <c r="W35" s="3">
         <v>537700</v>
       </c>
-      <c r="W35" s="3">
+      <c r="X35" s="3">
         <v>517500</v>
       </c>
-      <c r="X35" s="3">
+      <c r="Y35" s="3">
         <v>76800</v>
       </c>
-      <c r="Y35" s="3">
+      <c r="Z35" s="3">
         <v>453900</v>
       </c>
-      <c r="Z35" s="3">
+      <c r="AA35" s="3">
         <v>569900</v>
       </c>
-      <c r="AA35" s="3">
+      <c r="AB35" s="3">
         <v>463600</v>
       </c>
-      <c r="AB35" s="3">
+      <c r="AC35" s="3">
         <v>84900</v>
       </c>
-      <c r="AC35" s="3">
+      <c r="AD35" s="3">
         <v>212100</v>
       </c>
-      <c r="AD35" s="3">
+      <c r="AE35" s="3">
         <v>369000</v>
       </c>
-      <c r="AE35" s="3">
+      <c r="AF35" s="3">
         <v>517600</v>
       </c>
-      <c r="AF35" s="3">
+      <c r="AG35" s="3">
         <v>88500</v>
       </c>
-      <c r="AG35" s="3">
+      <c r="AH35" s="3">
         <v>275700</v>
       </c>
     </row>
-    <row r="37" spans="2:33" x14ac:dyDescent="0.2">
+    <row r="37" spans="2:34" x14ac:dyDescent="0.2">
       <c r="B37" s="1" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="38" spans="2:33" x14ac:dyDescent="0.2">
+    <row r="38" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C38" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D38" s="2">
+        <v>45382</v>
+      </c>
+      <c r="E38" s="2">
         <v>45291</v>
       </c>
-      <c r="E38" s="2">
+      <c r="F38" s="2">
         <v>45199</v>
       </c>
-      <c r="F38" s="2">
+      <c r="G38" s="2">
         <v>45107</v>
       </c>
-      <c r="G38" s="2">
+      <c r="H38" s="2">
         <v>45016</v>
       </c>
-      <c r="H38" s="2">
+      <c r="I38" s="2">
         <v>44926</v>
       </c>
-      <c r="I38" s="2">
+      <c r="J38" s="2">
         <v>44834</v>
       </c>
-      <c r="J38" s="2">
+      <c r="K38" s="2">
         <v>44742</v>
       </c>
-      <c r="K38" s="2">
+      <c r="L38" s="2">
         <v>44651</v>
       </c>
-      <c r="L38" s="2">
+      <c r="M38" s="2">
         <v>44561</v>
       </c>
-      <c r="M38" s="2">
+      <c r="N38" s="2">
         <v>44469</v>
       </c>
-      <c r="N38" s="2">
+      <c r="O38" s="2">
         <v>44377</v>
       </c>
-      <c r="O38" s="2">
+      <c r="P38" s="2">
         <v>44286</v>
       </c>
-      <c r="P38" s="2">
+      <c r="Q38" s="2">
         <v>44196</v>
       </c>
-      <c r="Q38" s="2">
+      <c r="R38" s="2">
         <v>44104</v>
       </c>
-      <c r="R38" s="2">
+      <c r="S38" s="2">
         <v>44012</v>
       </c>
-      <c r="S38" s="2">
+      <c r="T38" s="2">
         <v>43921</v>
       </c>
-      <c r="T38" s="2">
+      <c r="U38" s="2">
         <v>43830</v>
       </c>
-      <c r="U38" s="2">
+      <c r="V38" s="2">
         <v>43738</v>
       </c>
-      <c r="V38" s="2">
+      <c r="W38" s="2">
         <v>43646</v>
       </c>
-      <c r="W38" s="2">
+      <c r="X38" s="2">
         <v>43555</v>
       </c>
-      <c r="X38" s="2">
+      <c r="Y38" s="2">
         <v>43465</v>
       </c>
-      <c r="Y38" s="2">
+      <c r="Z38" s="2">
         <v>43373</v>
       </c>
-      <c r="Z38" s="2">
+      <c r="AA38" s="2">
         <v>43281</v>
       </c>
-      <c r="AA38" s="2">
+      <c r="AB38" s="2">
         <v>43190</v>
       </c>
-      <c r="AB38" s="2">
+      <c r="AC38" s="2">
         <v>43100</v>
       </c>
-      <c r="AC38" s="2">
+      <c r="AD38" s="2">
         <v>43008</v>
       </c>
-      <c r="AD38" s="2">
+      <c r="AE38" s="2">
         <v>42916</v>
       </c>
-      <c r="AE38" s="2">
+      <c r="AF38" s="2">
         <v>42825</v>
       </c>
-      <c r="AF38" s="2">
+      <c r="AG38" s="2">
         <v>42735</v>
       </c>
-      <c r="AG38" s="2">
+      <c r="AH38" s="2">
         <v>42643</v>
       </c>
     </row>
-    <row r="39" spans="2:33" x14ac:dyDescent="0.2">
+    <row r="39" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C39" s="1" t="s">
         <v>32</v>
       </c>
@@ -3389,8 +3474,9 @@
       <c r="AE39" s="3"/>
       <c r="AF39" s="3"/>
       <c r="AG39" s="3"/>
-    </row>
-    <row r="40" spans="2:33" x14ac:dyDescent="0.2">
+      <c r="AH39" s="3"/>
+    </row>
+    <row r="40" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C40" s="1" t="s">
         <v>33</v>
       </c>
@@ -3424,198 +3510,205 @@
       <c r="AE40" s="3"/>
       <c r="AF40" s="3"/>
       <c r="AG40" s="3"/>
-    </row>
-    <row r="41" spans="2:33" x14ac:dyDescent="0.2">
+      <c r="AH40" s="3"/>
+    </row>
+    <row r="41" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C41" s="1" t="s">
         <v>34</v>
       </c>
       <c r="D41" s="3">
-        <v>23125700</v>
+        <v>23124000</v>
       </c>
       <c r="E41" s="3">
-        <v>19537600</v>
+        <v>22212800</v>
       </c>
       <c r="F41" s="3">
-        <v>16261400</v>
+        <v>18766400</v>
       </c>
       <c r="G41" s="3">
-        <v>23409800</v>
+        <v>15619500</v>
       </c>
       <c r="H41" s="3">
-        <v>25938100</v>
+        <v>22485700</v>
       </c>
       <c r="I41" s="3">
-        <v>6775100</v>
+        <v>24914300</v>
       </c>
       <c r="J41" s="3">
+        <v>6507700</v>
+      </c>
+      <c r="K41" s="3">
         <v>7377100</v>
       </c>
-      <c r="K41" s="3">
+      <c r="L41" s="3">
         <v>9785500</v>
       </c>
-      <c r="L41" s="3">
+      <c r="M41" s="3">
         <v>5555400</v>
       </c>
-      <c r="M41" s="3">
+      <c r="N41" s="3">
         <v>7893500</v>
       </c>
-      <c r="N41" s="3">
+      <c r="O41" s="3">
         <v>7303900</v>
       </c>
-      <c r="O41" s="3">
+      <c r="P41" s="3">
         <v>7996900</v>
       </c>
-      <c r="P41" s="3">
+      <c r="Q41" s="3">
         <v>6985700</v>
       </c>
-      <c r="Q41" s="3">
+      <c r="R41" s="3">
         <v>6452400</v>
       </c>
-      <c r="R41" s="3">
+      <c r="S41" s="3">
         <v>6934700</v>
       </c>
-      <c r="S41" s="3">
+      <c r="T41" s="3">
         <v>7810800</v>
       </c>
-      <c r="T41" s="3">
+      <c r="U41" s="3">
         <v>5327800</v>
       </c>
-      <c r="U41" s="3">
+      <c r="V41" s="3">
         <v>7069900</v>
       </c>
-      <c r="V41" s="3">
+      <c r="W41" s="3">
         <v>5777500</v>
       </c>
-      <c r="W41" s="3">
+      <c r="X41" s="3">
         <v>4361000</v>
       </c>
-      <c r="X41" s="3">
+      <c r="Y41" s="3">
         <v>5329900</v>
       </c>
-      <c r="Y41" s="3">
+      <c r="Z41" s="3">
         <v>4608100</v>
       </c>
-      <c r="Z41" s="3">
+      <c r="AA41" s="3">
         <v>4589200</v>
       </c>
-      <c r="AA41" s="3">
+      <c r="AB41" s="3">
         <v>4387400</v>
       </c>
-      <c r="AB41" s="3">
+      <c r="AC41" s="3">
         <v>5323900</v>
       </c>
-      <c r="AC41" s="3">
+      <c r="AD41" s="3">
         <v>5337600</v>
       </c>
-      <c r="AD41" s="3">
+      <c r="AE41" s="3">
         <v>5780800</v>
       </c>
-      <c r="AE41" s="3">
+      <c r="AF41" s="3">
         <v>6495200</v>
       </c>
-      <c r="AF41" s="3">
+      <c r="AG41" s="3">
         <v>6385500</v>
       </c>
-      <c r="AG41" s="3">
+      <c r="AH41" s="3">
         <v>7024600</v>
       </c>
     </row>
-    <row r="42" spans="2:33" x14ac:dyDescent="0.2">
+    <row r="42" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C42" s="1" t="s">
         <v>35</v>
       </c>
       <c r="D42" s="3">
-        <v>43799200</v>
+        <v>17164500</v>
       </c>
       <c r="E42" s="3">
-        <v>40831700</v>
+        <v>42070300</v>
       </c>
       <c r="F42" s="3">
-        <v>47887300</v>
+        <v>39219900</v>
       </c>
       <c r="G42" s="3">
-        <v>39022800</v>
+        <v>45997000</v>
       </c>
       <c r="H42" s="3">
-        <v>41631900</v>
+        <v>37482400</v>
       </c>
       <c r="I42" s="3">
-        <v>50064200</v>
+        <v>39988600</v>
       </c>
       <c r="J42" s="3">
+        <v>48087900</v>
+      </c>
+      <c r="K42" s="3">
         <v>44907700</v>
       </c>
-      <c r="K42" s="3">
+      <c r="L42" s="3">
         <v>44616700</v>
       </c>
-      <c r="L42" s="3">
+      <c r="M42" s="3">
         <v>44083500</v>
       </c>
-      <c r="M42" s="3">
+      <c r="N42" s="3">
         <v>38326100</v>
       </c>
-      <c r="N42" s="3">
+      <c r="O42" s="3">
         <v>33800600</v>
       </c>
-      <c r="O42" s="3">
+      <c r="P42" s="3">
         <v>32013900</v>
       </c>
-      <c r="P42" s="3">
+      <c r="Q42" s="3">
         <v>39170300</v>
       </c>
-      <c r="Q42" s="3">
+      <c r="R42" s="3">
         <v>33273800</v>
       </c>
-      <c r="R42" s="3">
+      <c r="S42" s="3">
         <v>36396600</v>
       </c>
-      <c r="S42" s="3">
+      <c r="T42" s="3">
         <v>38606200</v>
       </c>
-      <c r="T42" s="3">
+      <c r="U42" s="3">
         <v>37680800</v>
       </c>
-      <c r="U42" s="3">
+      <c r="V42" s="3">
         <v>39232200</v>
       </c>
-      <c r="V42" s="3">
+      <c r="W42" s="3">
         <v>36892000</v>
       </c>
-      <c r="W42" s="3">
+      <c r="X42" s="3">
         <v>30905300</v>
       </c>
-      <c r="X42" s="3">
+      <c r="Y42" s="3">
         <v>29776700</v>
       </c>
-      <c r="Y42" s="3">
+      <c r="Z42" s="3">
         <v>20883600</v>
       </c>
-      <c r="Z42" s="3">
+      <c r="AA42" s="3">
         <v>22286700</v>
       </c>
-      <c r="AA42" s="3">
+      <c r="AB42" s="3">
         <v>21840100</v>
       </c>
-      <c r="AB42" s="3">
+      <c r="AC42" s="3">
         <v>20932300</v>
       </c>
-      <c r="AC42" s="3">
+      <c r="AD42" s="3">
         <v>12488600</v>
       </c>
-      <c r="AD42" s="3">
+      <c r="AE42" s="3">
         <v>14955900</v>
       </c>
-      <c r="AE42" s="3">
+      <c r="AF42" s="3">
         <v>13350900</v>
       </c>
-      <c r="AF42" s="3">
+      <c r="AG42" s="3">
         <v>14204100</v>
       </c>
-      <c r="AG42" s="3">
+      <c r="AH42" s="3">
         <v>16154100</v>
       </c>
     </row>
-    <row r="43" spans="2:33" x14ac:dyDescent="0.2">
+    <row r="43" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C43" s="1" t="s">
         <v>36</v>
       </c>
@@ -3709,8 +3802,11 @@
       <c r="AG43" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="44" spans="2:33" x14ac:dyDescent="0.2">
+      <c r="AH43" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="44" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C44" s="1" t="s">
         <v>37</v>
       </c>
@@ -3804,8 +3900,11 @@
       <c r="AG44" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="45" spans="2:33" x14ac:dyDescent="0.2">
+      <c r="AH44" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="45" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C45" s="1" t="s">
         <v>38</v>
       </c>
@@ -3899,8 +3998,11 @@
       <c r="AG45" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="46" spans="2:33" x14ac:dyDescent="0.2">
+      <c r="AH45" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="46" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C46" s="1" t="s">
         <v>39</v>
       </c>
@@ -3994,293 +4096,305 @@
       <c r="AG46" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="47" spans="2:33" x14ac:dyDescent="0.2">
+      <c r="AH46" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="47" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C47" s="1" t="s">
         <v>40</v>
       </c>
       <c r="D47" s="3">
-        <v>1364500</v>
+        <v>1451300</v>
       </c>
       <c r="E47" s="3">
-        <v>1335100</v>
+        <v>1310600</v>
       </c>
       <c r="F47" s="3">
-        <v>1232500</v>
+        <v>1282400</v>
       </c>
       <c r="G47" s="3">
-        <v>1127100</v>
+        <v>1183800</v>
       </c>
       <c r="H47" s="3">
-        <v>992300</v>
+        <v>1082600</v>
       </c>
       <c r="I47" s="3">
-        <v>1017000</v>
+        <v>953100</v>
       </c>
       <c r="J47" s="3">
+        <v>976800</v>
+      </c>
+      <c r="K47" s="3">
         <v>1035000</v>
       </c>
-      <c r="K47" s="3">
+      <c r="L47" s="3">
         <v>1011300</v>
       </c>
-      <c r="L47" s="3">
+      <c r="M47" s="3">
         <v>1001400</v>
       </c>
-      <c r="M47" s="3">
+      <c r="N47" s="3">
         <v>896000</v>
       </c>
-      <c r="N47" s="3">
+      <c r="O47" s="3">
         <v>881500</v>
       </c>
-      <c r="O47" s="3">
+      <c r="P47" s="3">
         <v>775800</v>
       </c>
-      <c r="P47" s="3">
+      <c r="Q47" s="3">
         <v>735000</v>
       </c>
-      <c r="Q47" s="3">
+      <c r="R47" s="3">
         <v>829200</v>
       </c>
-      <c r="R47" s="3">
+      <c r="S47" s="3">
         <v>714700</v>
       </c>
-      <c r="S47" s="3">
+      <c r="T47" s="3">
         <v>674300</v>
       </c>
-      <c r="T47" s="3">
+      <c r="U47" s="3">
         <v>685400</v>
       </c>
-      <c r="U47" s="3">
+      <c r="V47" s="3">
         <v>322100</v>
       </c>
-      <c r="V47" s="3">
+      <c r="W47" s="3">
         <v>311500</v>
       </c>
-      <c r="W47" s="3">
+      <c r="X47" s="3">
         <v>316200</v>
       </c>
-      <c r="X47" s="3">
+      <c r="Y47" s="3">
         <v>303600</v>
       </c>
-      <c r="Y47" s="3">
+      <c r="Z47" s="3">
         <v>276700</v>
       </c>
-      <c r="Z47" s="3">
+      <c r="AA47" s="3">
         <v>346900</v>
       </c>
-      <c r="AA47" s="3">
+      <c r="AB47" s="3">
         <v>348200</v>
       </c>
-      <c r="AB47" s="3">
+      <c r="AC47" s="3">
         <v>367000</v>
       </c>
-      <c r="AC47" s="3">
+      <c r="AD47" s="3">
         <v>490900</v>
       </c>
-      <c r="AD47" s="3">
+      <c r="AE47" s="3">
         <v>326300</v>
       </c>
-      <c r="AE47" s="3">
+      <c r="AF47" s="3">
         <v>351100</v>
       </c>
-      <c r="AF47" s="3">
+      <c r="AG47" s="3">
         <v>395100</v>
       </c>
-      <c r="AG47" s="3">
+      <c r="AH47" s="3">
         <v>377600</v>
       </c>
     </row>
-    <row r="48" spans="2:33" x14ac:dyDescent="0.2">
+    <row r="48" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C48" s="1" t="s">
         <v>41</v>
       </c>
       <c r="D48" s="3">
-        <v>2773600</v>
+        <v>2668700</v>
       </c>
       <c r="E48" s="3">
-        <v>2745500</v>
+        <v>2664200</v>
       </c>
       <c r="F48" s="3">
-        <v>2741700</v>
+        <v>2637100</v>
       </c>
       <c r="G48" s="3">
-        <v>2765100</v>
+        <v>2633500</v>
       </c>
       <c r="H48" s="3">
-        <v>2683300</v>
+        <v>2656000</v>
       </c>
       <c r="I48" s="3">
-        <v>2696700</v>
+        <v>2577400</v>
       </c>
       <c r="J48" s="3">
+        <v>2590300</v>
+      </c>
+      <c r="K48" s="3">
         <v>2689200</v>
       </c>
-      <c r="K48" s="3">
+      <c r="L48" s="3">
         <v>2729900</v>
       </c>
-      <c r="L48" s="3">
+      <c r="M48" s="3">
         <v>2673200</v>
       </c>
-      <c r="M48" s="3">
+      <c r="N48" s="3">
         <v>2701000</v>
       </c>
-      <c r="N48" s="3">
+      <c r="O48" s="3">
         <v>2682600</v>
       </c>
-      <c r="O48" s="3">
+      <c r="P48" s="3">
         <v>2700600</v>
       </c>
-      <c r="P48" s="3">
+      <c r="Q48" s="3">
         <v>2719200</v>
       </c>
-      <c r="Q48" s="3">
+      <c r="R48" s="3">
         <v>2764300</v>
       </c>
-      <c r="R48" s="3">
+      <c r="S48" s="3">
         <v>2790300</v>
       </c>
-      <c r="S48" s="3">
+      <c r="T48" s="3">
         <v>2961700</v>
       </c>
-      <c r="T48" s="3">
+      <c r="U48" s="3">
         <v>3098200</v>
       </c>
-      <c r="U48" s="3">
+      <c r="V48" s="3">
         <v>3089800</v>
       </c>
-      <c r="V48" s="3">
+      <c r="W48" s="3">
         <v>3058200</v>
       </c>
-      <c r="W48" s="3">
+      <c r="X48" s="3">
         <v>3080600</v>
       </c>
-      <c r="X48" s="3">
+      <c r="Y48" s="3">
         <v>2368100</v>
       </c>
-      <c r="Y48" s="3">
+      <c r="Z48" s="3">
         <v>2284800</v>
       </c>
-      <c r="Z48" s="3">
+      <c r="AA48" s="3">
         <v>2378800</v>
       </c>
-      <c r="AA48" s="3">
+      <c r="AB48" s="3">
         <v>2384000</v>
       </c>
-      <c r="AB48" s="3">
+      <c r="AC48" s="3">
         <v>2507000</v>
       </c>
-      <c r="AC48" s="3">
+      <c r="AD48" s="3">
         <v>2509800</v>
       </c>
-      <c r="AD48" s="3">
+      <c r="AE48" s="3">
         <v>2480800</v>
       </c>
-      <c r="AE48" s="3">
+      <c r="AF48" s="3">
         <v>2470200</v>
       </c>
-      <c r="AF48" s="3">
+      <c r="AG48" s="3">
         <v>2534900</v>
       </c>
-      <c r="AG48" s="3">
+      <c r="AH48" s="3">
         <v>2525400</v>
       </c>
     </row>
-    <row r="49" spans="3:33" x14ac:dyDescent="0.2">
+    <row r="49" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C49" s="1" t="s">
         <v>42</v>
       </c>
       <c r="D49" s="3">
-        <v>757600</v>
+        <v>729900</v>
       </c>
       <c r="E49" s="3">
-        <v>748400</v>
+        <v>727700</v>
       </c>
       <c r="F49" s="3">
-        <v>752000</v>
+        <v>718800</v>
       </c>
       <c r="G49" s="3">
-        <v>729800</v>
+        <v>722300</v>
       </c>
       <c r="H49" s="3">
-        <v>645300</v>
+        <v>701000</v>
       </c>
       <c r="I49" s="3">
-        <v>665500</v>
+        <v>619900</v>
       </c>
       <c r="J49" s="3">
+        <v>639200</v>
+      </c>
+      <c r="K49" s="3">
         <v>596500</v>
       </c>
-      <c r="K49" s="3">
+      <c r="L49" s="3">
         <v>608700</v>
       </c>
-      <c r="L49" s="3">
+      <c r="M49" s="3">
         <v>589000</v>
       </c>
-      <c r="M49" s="3">
+      <c r="N49" s="3">
         <v>586400</v>
       </c>
-      <c r="N49" s="3">
+      <c r="O49" s="3">
         <v>581700</v>
       </c>
-      <c r="O49" s="3">
+      <c r="P49" s="3">
         <v>582600</v>
       </c>
-      <c r="P49" s="3">
+      <c r="Q49" s="3">
         <v>586100</v>
       </c>
-      <c r="Q49" s="3">
+      <c r="R49" s="3">
         <v>615800</v>
       </c>
-      <c r="R49" s="3">
+      <c r="S49" s="3">
         <v>631700</v>
       </c>
-      <c r="S49" s="3">
+      <c r="T49" s="3">
         <v>668000</v>
       </c>
-      <c r="T49" s="3">
+      <c r="U49" s="3">
         <v>717500</v>
       </c>
-      <c r="U49" s="3">
+      <c r="V49" s="3">
         <v>590200</v>
       </c>
-      <c r="V49" s="3">
+      <c r="W49" s="3">
         <v>565800</v>
       </c>
-      <c r="W49" s="3">
+      <c r="X49" s="3">
         <v>588900</v>
       </c>
-      <c r="X49" s="3">
+      <c r="Y49" s="3">
         <v>493300</v>
       </c>
-      <c r="Y49" s="3">
+      <c r="Z49" s="3">
         <v>502400</v>
       </c>
-      <c r="Z49" s="3">
+      <c r="AA49" s="3">
         <v>549000</v>
       </c>
-      <c r="AA49" s="3">
+      <c r="AB49" s="3">
         <v>452700</v>
       </c>
-      <c r="AB49" s="3">
+      <c r="AC49" s="3">
         <v>456400</v>
       </c>
-      <c r="AC49" s="3">
+      <c r="AD49" s="3">
         <v>461900</v>
       </c>
-      <c r="AD49" s="3">
+      <c r="AE49" s="3">
         <v>446100</v>
       </c>
-      <c r="AE49" s="3">
+      <c r="AF49" s="3">
         <v>415100</v>
       </c>
-      <c r="AF49" s="3">
+      <c r="AG49" s="3">
         <v>435400</v>
       </c>
-      <c r="AG49" s="3">
+      <c r="AH49" s="3">
         <v>376700</v>
       </c>
     </row>
-    <row r="50" spans="3:33" x14ac:dyDescent="0.2">
+    <row r="50" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C50" s="1" t="s">
         <v>43</v>
       </c>
@@ -4374,8 +4488,11 @@
       <c r="AG50" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="51" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH50" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="51" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C51" s="1" t="s">
         <v>44</v>
       </c>
@@ -4469,103 +4586,109 @@
       <c r="AG51" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="52" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH51" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="52" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C52" s="1" t="s">
         <v>45</v>
       </c>
       <c r="D52" s="3">
-        <v>269000</v>
+        <v>211800</v>
       </c>
       <c r="E52" s="3">
-        <v>316900</v>
+        <v>258400</v>
       </c>
       <c r="F52" s="3">
-        <v>301100</v>
+        <v>304400</v>
       </c>
       <c r="G52" s="3">
-        <v>156900</v>
+        <v>289200</v>
       </c>
       <c r="H52" s="3">
-        <v>336200</v>
+        <v>150700</v>
       </c>
       <c r="I52" s="3">
-        <v>296200</v>
+        <v>322900</v>
       </c>
       <c r="J52" s="3">
+        <v>284500</v>
+      </c>
+      <c r="K52" s="3">
         <v>166400</v>
       </c>
-      <c r="K52" s="3">
+      <c r="L52" s="3">
         <v>58400</v>
       </c>
-      <c r="L52" s="3">
+      <c r="M52" s="3">
         <v>59100</v>
       </c>
-      <c r="M52" s="3">
+      <c r="N52" s="3">
         <v>41100</v>
       </c>
-      <c r="N52" s="3">
+      <c r="O52" s="3">
         <v>56000</v>
       </c>
-      <c r="O52" s="3">
+      <c r="P52" s="3">
         <v>73700</v>
       </c>
-      <c r="P52" s="3">
+      <c r="Q52" s="3">
         <v>82700</v>
       </c>
-      <c r="Q52" s="3">
+      <c r="R52" s="3">
         <v>74500</v>
       </c>
-      <c r="R52" s="3">
+      <c r="S52" s="3">
         <v>37800</v>
       </c>
-      <c r="S52" s="3">
+      <c r="T52" s="3">
         <v>38200</v>
       </c>
-      <c r="T52" s="3">
+      <c r="U52" s="3">
         <v>44800</v>
       </c>
-      <c r="U52" s="3">
+      <c r="V52" s="3">
         <v>82300</v>
       </c>
-      <c r="V52" s="3">
+      <c r="W52" s="3">
         <v>69500</v>
       </c>
-      <c r="W52" s="3">
+      <c r="X52" s="3">
         <v>68200</v>
       </c>
-      <c r="X52" s="3">
+      <c r="Y52" s="3">
         <v>120400</v>
       </c>
-      <c r="Y52" s="3">
+      <c r="Z52" s="3">
         <v>36800</v>
       </c>
-      <c r="Z52" s="3">
+      <c r="AA52" s="3">
         <v>91100</v>
       </c>
-      <c r="AA52" s="3">
+      <c r="AB52" s="3">
         <v>177600</v>
       </c>
-      <c r="AB52" s="3">
+      <c r="AC52" s="3">
         <v>289300</v>
       </c>
-      <c r="AC52" s="3">
+      <c r="AD52" s="3">
         <v>234800</v>
       </c>
-      <c r="AD52" s="3">
+      <c r="AE52" s="3">
         <v>221100</v>
       </c>
-      <c r="AE52" s="3">
+      <c r="AF52" s="3">
         <v>262700</v>
       </c>
-      <c r="AF52" s="3">
+      <c r="AG52" s="3">
         <v>274800</v>
       </c>
-      <c r="AG52" s="3">
+      <c r="AH52" s="3">
         <v>143800</v>
       </c>
     </row>
-    <row r="53" spans="3:33" x14ac:dyDescent="0.2">
+    <row r="53" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C53" s="1" t="s">
         <v>46</v>
       </c>
@@ -4659,103 +4782,109 @@
       <c r="AG53" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="54" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH53" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="54" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C54" s="1" t="s">
         <v>47</v>
       </c>
       <c r="D54" s="3">
-        <v>378483800</v>
+        <v>368480200</v>
       </c>
       <c r="E54" s="3">
-        <v>369296900</v>
+        <v>363543600</v>
       </c>
       <c r="F54" s="3">
-        <v>367012800</v>
+        <v>354719400</v>
       </c>
       <c r="G54" s="3">
-        <v>363340200</v>
+        <v>352525500</v>
       </c>
       <c r="H54" s="3">
-        <v>365160500</v>
+        <v>348997900</v>
       </c>
       <c r="I54" s="3">
-        <v>381572400</v>
+        <v>350746300</v>
       </c>
       <c r="J54" s="3">
+        <v>366510300</v>
+      </c>
+      <c r="K54" s="3">
         <v>368558700</v>
       </c>
-      <c r="K54" s="3">
+      <c r="L54" s="3">
         <v>358592300</v>
       </c>
-      <c r="L54" s="3">
+      <c r="M54" s="3">
         <v>335387900</v>
       </c>
-      <c r="M54" s="3">
+      <c r="N54" s="3">
         <v>328638700</v>
       </c>
-      <c r="N54" s="3">
+      <c r="O54" s="3">
         <v>315953000</v>
       </c>
-      <c r="O54" s="3">
+      <c r="P54" s="3">
         <v>307917200</v>
       </c>
-      <c r="P54" s="3">
+      <c r="Q54" s="3">
         <v>295320000</v>
       </c>
-      <c r="Q54" s="3">
+      <c r="R54" s="3">
         <v>293246000</v>
       </c>
-      <c r="R54" s="3">
+      <c r="S54" s="3">
         <v>292659600</v>
       </c>
-      <c r="S54" s="3">
+      <c r="T54" s="3">
         <v>306353500</v>
       </c>
-      <c r="T54" s="3">
+      <c r="U54" s="3">
         <v>307683600</v>
       </c>
-      <c r="U54" s="3">
+      <c r="V54" s="3">
         <v>314996600</v>
       </c>
-      <c r="V54" s="3">
+      <c r="W54" s="3">
         <v>316273500</v>
       </c>
-      <c r="W54" s="3">
+      <c r="X54" s="3">
         <v>314085600</v>
       </c>
-      <c r="X54" s="3">
+      <c r="Y54" s="3">
         <v>285975600</v>
       </c>
-      <c r="Y54" s="3">
+      <c r="Z54" s="3">
         <v>267139300</v>
       </c>
-      <c r="Z54" s="3">
+      <c r="AA54" s="3">
         <v>274311500</v>
       </c>
-      <c r="AA54" s="3">
+      <c r="AB54" s="3">
         <v>273668600</v>
       </c>
-      <c r="AB54" s="3">
+      <c r="AC54" s="3">
         <v>278340000</v>
       </c>
-      <c r="AC54" s="3">
+      <c r="AD54" s="3">
         <v>279730100</v>
       </c>
-      <c r="AD54" s="3">
+      <c r="AE54" s="3">
         <v>278137400</v>
       </c>
-      <c r="AE54" s="3">
+      <c r="AF54" s="3">
         <v>273600800</v>
       </c>
-      <c r="AF54" s="3">
+      <c r="AG54" s="3">
         <v>279614500</v>
       </c>
-      <c r="AG54" s="3">
+      <c r="AH54" s="3">
         <v>281548700</v>
       </c>
     </row>
-    <row r="55" spans="3:33" x14ac:dyDescent="0.2">
+    <row r="55" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C55" s="1" t="s">
         <v>48</v>
       </c>
@@ -4789,8 +4918,9 @@
       <c r="AE55" s="3"/>
       <c r="AF55" s="3"/>
       <c r="AG55" s="3"/>
-    </row>
-    <row r="56" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH55" s="3"/>
+    </row>
+    <row r="56" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C56" s="1" t="s">
         <v>49</v>
       </c>
@@ -4824,103 +4954,107 @@
       <c r="AE56" s="3"/>
       <c r="AF56" s="3"/>
       <c r="AG56" s="3"/>
-    </row>
-    <row r="57" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH56" s="3"/>
+    </row>
+    <row r="57" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C57" s="1" t="s">
         <v>50</v>
       </c>
-      <c r="D57" s="3">
-        <v>9471700</v>
+      <c r="D57" s="3" t="s">
+        <v>5</v>
       </c>
       <c r="E57" s="3">
-        <v>14494600</v>
+        <v>9097800</v>
       </c>
       <c r="F57" s="3">
-        <v>14773000</v>
+        <v>13922400</v>
       </c>
       <c r="G57" s="3">
-        <v>13862300</v>
+        <v>14189900</v>
       </c>
       <c r="H57" s="3">
-        <v>8706700</v>
+        <v>13315100</v>
       </c>
       <c r="I57" s="3">
-        <v>13259500</v>
+        <v>8363000</v>
       </c>
       <c r="J57" s="3">
+        <v>12736100</v>
+      </c>
+      <c r="K57" s="3">
         <v>12538100</v>
       </c>
-      <c r="K57" s="3">
+      <c r="L57" s="3">
         <v>11104000</v>
       </c>
-      <c r="L57" s="3">
+      <c r="M57" s="3">
         <v>10844700</v>
       </c>
-      <c r="M57" s="3">
+      <c r="N57" s="3">
         <v>7957500</v>
       </c>
-      <c r="N57" s="3">
+      <c r="O57" s="3">
         <v>9468900</v>
       </c>
-      <c r="O57" s="3">
+      <c r="P57" s="3">
         <v>7995800</v>
       </c>
-      <c r="P57" s="3">
+      <c r="Q57" s="3">
         <v>3698600</v>
       </c>
-      <c r="Q57" s="3">
+      <c r="R57" s="3">
         <v>7530800</v>
       </c>
-      <c r="R57" s="3">
+      <c r="S57" s="3">
         <v>8467000</v>
       </c>
-      <c r="S57" s="3">
+      <c r="T57" s="3">
         <v>9538600</v>
       </c>
-      <c r="T57" s="3">
+      <c r="U57" s="3">
         <v>7264700</v>
       </c>
-      <c r="U57" s="3">
+      <c r="V57" s="3">
         <v>13339700</v>
       </c>
-      <c r="V57" s="3">
+      <c r="W57" s="3">
         <v>15138200</v>
       </c>
-      <c r="W57" s="3">
+      <c r="X57" s="3">
         <v>14778600</v>
       </c>
-      <c r="X57" s="3">
+      <c r="Y57" s="3">
         <v>10988500</v>
       </c>
-      <c r="Y57" s="3">
+      <c r="Z57" s="3">
         <v>12068900</v>
       </c>
-      <c r="Z57" s="3">
+      <c r="AA57" s="3">
         <v>11638400</v>
       </c>
-      <c r="AA57" s="3">
+      <c r="AB57" s="3">
         <v>12317300</v>
       </c>
-      <c r="AB57" s="3">
+      <c r="AC57" s="3">
         <v>5801500</v>
       </c>
-      <c r="AC57" s="3">
+      <c r="AD57" s="3">
         <v>13814400</v>
       </c>
-      <c r="AD57" s="3">
+      <c r="AE57" s="3">
         <v>14756900</v>
       </c>
-      <c r="AE57" s="3">
+      <c r="AF57" s="3">
         <v>10823000</v>
       </c>
-      <c r="AF57" s="3">
+      <c r="AG57" s="3">
         <v>13329400</v>
       </c>
-      <c r="AG57" s="3">
+      <c r="AH57" s="3">
         <v>15356600</v>
       </c>
     </row>
-    <row r="58" spans="3:33" x14ac:dyDescent="0.2">
+    <row r="58" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C58" s="1" t="s">
         <v>51</v>
       </c>
@@ -5014,103 +5148,109 @@
       <c r="AG58" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="59" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH58" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="59" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C59" s="1" t="s">
         <v>52</v>
       </c>
       <c r="D59" s="3">
-        <v>3376700</v>
+        <v>56000</v>
       </c>
       <c r="E59" s="3">
-        <v>3519100</v>
+        <v>3243400</v>
       </c>
       <c r="F59" s="3">
-        <v>3117300</v>
+        <v>3380200</v>
       </c>
       <c r="G59" s="3">
-        <v>3302900</v>
+        <v>2994300</v>
       </c>
       <c r="H59" s="3">
-        <v>3087800</v>
+        <v>3172500</v>
       </c>
       <c r="I59" s="3">
-        <v>2321300</v>
+        <v>2965900</v>
       </c>
       <c r="J59" s="3">
+        <v>2229700</v>
+      </c>
+      <c r="K59" s="3">
         <v>1968300</v>
       </c>
-      <c r="K59" s="3">
+      <c r="L59" s="3">
         <v>2093100</v>
       </c>
-      <c r="L59" s="3">
+      <c r="M59" s="3">
         <v>1991300</v>
       </c>
-      <c r="M59" s="3">
+      <c r="N59" s="3">
         <v>1538600</v>
       </c>
-      <c r="N59" s="3">
+      <c r="O59" s="3">
         <v>1446500</v>
       </c>
-      <c r="O59" s="3">
+      <c r="P59" s="3">
         <v>1600800</v>
       </c>
-      <c r="P59" s="3">
+      <c r="Q59" s="3">
         <v>1790900</v>
       </c>
-      <c r="Q59" s="3">
+      <c r="R59" s="3">
         <v>1521700</v>
       </c>
-      <c r="R59" s="3">
+      <c r="S59" s="3">
         <v>1545300</v>
       </c>
-      <c r="S59" s="3">
+      <c r="T59" s="3">
         <v>1892000</v>
       </c>
-      <c r="T59" s="3">
+      <c r="U59" s="3">
         <v>2294100</v>
       </c>
-      <c r="U59" s="3">
+      <c r="V59" s="3">
         <v>2199800</v>
       </c>
-      <c r="V59" s="3">
+      <c r="W59" s="3">
         <v>2064700</v>
       </c>
-      <c r="W59" s="3">
+      <c r="X59" s="3">
         <v>2149400</v>
       </c>
-      <c r="X59" s="3">
+      <c r="Y59" s="3">
         <v>1989900</v>
       </c>
-      <c r="Y59" s="3">
+      <c r="Z59" s="3">
         <v>1798500</v>
       </c>
-      <c r="Z59" s="3">
+      <c r="AA59" s="3">
         <v>1649500</v>
       </c>
-      <c r="AA59" s="3">
+      <c r="AB59" s="3">
         <v>1642100</v>
       </c>
-      <c r="AB59" s="3">
+      <c r="AC59" s="3">
         <v>2008600</v>
       </c>
-      <c r="AC59" s="3">
+      <c r="AD59" s="3">
         <v>2057400</v>
       </c>
-      <c r="AD59" s="3">
+      <c r="AE59" s="3">
         <v>1681400</v>
       </c>
-      <c r="AE59" s="3">
+      <c r="AF59" s="3">
         <v>1880000</v>
       </c>
-      <c r="AF59" s="3">
+      <c r="AG59" s="3">
         <v>2004400</v>
       </c>
-      <c r="AG59" s="3">
+      <c r="AH59" s="3">
         <v>1813400</v>
       </c>
     </row>
-    <row r="60" spans="3:33" x14ac:dyDescent="0.2">
+    <row r="60" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C60" s="1" t="s">
         <v>53</v>
       </c>
@@ -5204,198 +5344,207 @@
       <c r="AG60" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="61" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH60" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="61" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C61" s="1" t="s">
         <v>54</v>
       </c>
       <c r="D61" s="3">
-        <v>53441800</v>
+        <v>52456500</v>
       </c>
       <c r="E61" s="3">
-        <v>53873800</v>
+        <v>51332300</v>
       </c>
       <c r="F61" s="3">
-        <v>54091900</v>
+        <v>51747200</v>
       </c>
       <c r="G61" s="3">
-        <v>53982600</v>
+        <v>51956700</v>
       </c>
       <c r="H61" s="3">
-        <v>53372400</v>
+        <v>51851700</v>
       </c>
       <c r="I61" s="3">
-        <v>61234900</v>
+        <v>51265600</v>
       </c>
       <c r="J61" s="3">
+        <v>58817800</v>
+      </c>
+      <c r="K61" s="3">
         <v>58413400</v>
       </c>
-      <c r="K61" s="3">
+      <c r="L61" s="3">
         <v>54512100</v>
       </c>
-      <c r="L61" s="3">
+      <c r="M61" s="3">
         <v>51506600</v>
       </c>
-      <c r="M61" s="3">
+      <c r="N61" s="3">
         <v>49335300</v>
       </c>
-      <c r="N61" s="3">
+      <c r="O61" s="3">
         <v>46999300</v>
       </c>
-      <c r="O61" s="3">
+      <c r="P61" s="3">
         <v>43329900</v>
       </c>
-      <c r="P61" s="3">
+      <c r="Q61" s="3">
         <v>42586400</v>
       </c>
-      <c r="Q61" s="3">
+      <c r="R61" s="3">
         <v>38230600</v>
       </c>
-      <c r="R61" s="3">
+      <c r="S61" s="3">
         <v>39214800</v>
       </c>
-      <c r="S61" s="3">
+      <c r="T61" s="3">
         <v>43080800</v>
       </c>
-      <c r="T61" s="3">
+      <c r="U61" s="3">
         <v>42129500</v>
       </c>
-      <c r="U61" s="3">
+      <c r="V61" s="3">
         <v>44185000</v>
       </c>
-      <c r="V61" s="3">
+      <c r="W61" s="3">
         <v>43142100</v>
       </c>
-      <c r="W61" s="3">
+      <c r="X61" s="3">
         <v>40307800</v>
       </c>
-      <c r="X61" s="3">
+      <c r="Y61" s="3">
         <v>36868700</v>
       </c>
-      <c r="Y61" s="3">
+      <c r="Z61" s="3">
         <v>34955700</v>
       </c>
-      <c r="Z61" s="3">
+      <c r="AA61" s="3">
         <v>35115500</v>
       </c>
-      <c r="AA61" s="3">
+      <c r="AB61" s="3">
         <v>34009900</v>
       </c>
-      <c r="AB61" s="3">
+      <c r="AC61" s="3">
         <v>36941800</v>
       </c>
-      <c r="AC61" s="3">
+      <c r="AD61" s="3">
         <v>37408900</v>
       </c>
-      <c r="AD61" s="3">
+      <c r="AE61" s="3">
         <v>35000000</v>
       </c>
-      <c r="AE61" s="3">
+      <c r="AF61" s="3">
         <v>33280700</v>
       </c>
-      <c r="AF61" s="3">
+      <c r="AG61" s="3">
         <v>34538700</v>
       </c>
-      <c r="AG61" s="3">
+      <c r="AH61" s="3">
         <v>33926000</v>
       </c>
     </row>
-    <row r="62" spans="3:33" x14ac:dyDescent="0.2">
+    <row r="62" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C62" s="1" t="s">
         <v>55</v>
       </c>
       <c r="D62" s="3">
-        <v>975300</v>
+        <v>843300</v>
       </c>
       <c r="E62" s="3">
-        <v>831300</v>
+        <v>936800</v>
       </c>
       <c r="F62" s="3">
-        <v>790200</v>
+        <v>798500</v>
       </c>
       <c r="G62" s="3">
-        <v>597200</v>
+        <v>759100</v>
       </c>
       <c r="H62" s="3">
-        <v>465800</v>
+        <v>573600</v>
       </c>
       <c r="I62" s="3">
-        <v>456100</v>
+        <v>447400</v>
       </c>
       <c r="J62" s="3">
+        <v>438000</v>
+      </c>
+      <c r="K62" s="3">
         <v>469900</v>
       </c>
-      <c r="K62" s="3">
+      <c r="L62" s="3">
         <v>523500</v>
       </c>
-      <c r="L62" s="3">
+      <c r="M62" s="3">
         <v>608300</v>
       </c>
-      <c r="M62" s="3">
+      <c r="N62" s="3">
         <v>663300</v>
       </c>
-      <c r="N62" s="3">
+      <c r="O62" s="3">
         <v>620300</v>
       </c>
-      <c r="O62" s="3">
+      <c r="P62" s="3">
         <v>542300</v>
       </c>
-      <c r="P62" s="3">
+      <c r="Q62" s="3">
         <v>528500</v>
       </c>
-      <c r="Q62" s="3">
+      <c r="R62" s="3">
         <v>720700</v>
       </c>
-      <c r="R62" s="3">
+      <c r="S62" s="3">
         <v>691400</v>
       </c>
-      <c r="S62" s="3">
+      <c r="T62" s="3">
         <v>680000</v>
       </c>
-      <c r="T62" s="3">
+      <c r="U62" s="3">
         <v>570200</v>
       </c>
-      <c r="U62" s="3">
+      <c r="V62" s="3">
         <v>714600</v>
       </c>
-      <c r="V62" s="3">
+      <c r="W62" s="3">
         <v>648100</v>
       </c>
-      <c r="W62" s="3">
+      <c r="X62" s="3">
         <v>618700</v>
       </c>
-      <c r="X62" s="3">
+      <c r="Y62" s="3">
         <v>520300</v>
       </c>
-      <c r="Y62" s="3">
+      <c r="Z62" s="3">
         <v>418500</v>
       </c>
-      <c r="Z62" s="3">
+      <c r="AA62" s="3">
         <v>420800</v>
       </c>
-      <c r="AA62" s="3">
+      <c r="AB62" s="3">
         <v>527700</v>
       </c>
-      <c r="AB62" s="3">
+      <c r="AC62" s="3">
         <v>419200</v>
       </c>
-      <c r="AC62" s="3">
+      <c r="AD62" s="3">
         <v>395900</v>
       </c>
-      <c r="AD62" s="3">
+      <c r="AE62" s="3">
         <v>382900</v>
       </c>
-      <c r="AE62" s="3">
+      <c r="AF62" s="3">
         <v>400700</v>
       </c>
-      <c r="AF62" s="3">
+      <c r="AG62" s="3">
         <v>463600</v>
       </c>
-      <c r="AG62" s="3">
+      <c r="AH62" s="3">
         <v>459900</v>
       </c>
     </row>
-    <row r="63" spans="3:33" x14ac:dyDescent="0.2">
+    <row r="63" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C63" s="1" t="s">
         <v>56</v>
       </c>
@@ -5489,8 +5638,11 @@
       <c r="AG63" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="64" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH63" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="64" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C64" s="1" t="s">
         <v>20</v>
       </c>
@@ -5584,8 +5736,11 @@
       <c r="AG64" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="65" spans="2:33" x14ac:dyDescent="0.2">
+      <c r="AH64" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="65" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C65" s="1" t="s">
         <v>57</v>
       </c>
@@ -5679,103 +5834,109 @@
       <c r="AG65" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="66" spans="2:33" x14ac:dyDescent="0.2">
+      <c r="AH65" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="66" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C66" s="1" t="s">
         <v>58</v>
       </c>
       <c r="D66" s="3">
-        <v>354416900</v>
+        <v>344956800</v>
       </c>
       <c r="E66" s="3">
-        <v>345292200</v>
+        <v>340426800</v>
       </c>
       <c r="F66" s="3">
-        <v>344026900</v>
+        <v>331662200</v>
       </c>
       <c r="G66" s="3">
-        <v>340798900</v>
+        <v>330446900</v>
       </c>
       <c r="H66" s="3">
-        <v>343301500</v>
+        <v>327346300</v>
       </c>
       <c r="I66" s="3">
-        <v>360100400</v>
+        <v>329750100</v>
       </c>
       <c r="J66" s="3">
+        <v>345885900</v>
+      </c>
+      <c r="K66" s="3">
         <v>348018900</v>
       </c>
-      <c r="K66" s="3">
+      <c r="L66" s="3">
         <v>338354200</v>
       </c>
-      <c r="L66" s="3">
+      <c r="M66" s="3">
         <v>316006400</v>
       </c>
-      <c r="M66" s="3">
+      <c r="N66" s="3">
         <v>309651700</v>
       </c>
-      <c r="N66" s="3">
+      <c r="O66" s="3">
         <v>297533600</v>
       </c>
-      <c r="O66" s="3">
+      <c r="P66" s="3">
         <v>290517700</v>
       </c>
-      <c r="P66" s="3">
+      <c r="Q66" s="3">
         <v>278260300</v>
       </c>
-      <c r="Q66" s="3">
+      <c r="R66" s="3">
         <v>275726000</v>
       </c>
-      <c r="R66" s="3">
+      <c r="S66" s="3">
         <v>275487700</v>
       </c>
-      <c r="S66" s="3">
+      <c r="T66" s="3">
         <v>288675900</v>
       </c>
-      <c r="T66" s="3">
+      <c r="U66" s="3">
         <v>289399800</v>
       </c>
-      <c r="U66" s="3">
+      <c r="V66" s="3">
         <v>297278600</v>
       </c>
-      <c r="V66" s="3">
+      <c r="W66" s="3">
         <v>299163500</v>
       </c>
-      <c r="W66" s="3">
+      <c r="X66" s="3">
         <v>296968200</v>
       </c>
-      <c r="X66" s="3">
+      <c r="Y66" s="3">
         <v>267714100</v>
       </c>
-      <c r="Y66" s="3">
+      <c r="Z66" s="3">
         <v>249559900</v>
       </c>
-      <c r="Z66" s="3">
+      <c r="AA66" s="3">
         <v>256847800</v>
       </c>
-      <c r="AA66" s="3">
+      <c r="AB66" s="3">
         <v>256582900</v>
       </c>
-      <c r="AB66" s="3">
+      <c r="AC66" s="3">
         <v>260418000</v>
       </c>
-      <c r="AC66" s="3">
+      <c r="AD66" s="3">
         <v>261733600</v>
       </c>
-      <c r="AD66" s="3">
+      <c r="AE66" s="3">
         <v>260311800</v>
       </c>
-      <c r="AE66" s="3">
+      <c r="AF66" s="3">
         <v>255640700</v>
       </c>
-      <c r="AF66" s="3">
+      <c r="AG66" s="3">
         <v>261266900</v>
       </c>
-      <c r="AG66" s="3">
+      <c r="AH66" s="3">
         <v>263136400</v>
       </c>
     </row>
-    <row r="67" spans="2:33" x14ac:dyDescent="0.2">
+    <row r="67" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C67" s="1" t="s">
         <v>59</v>
       </c>
@@ -5809,8 +5970,9 @@
       <c r="AE67" s="3"/>
       <c r="AF67" s="3"/>
       <c r="AG67" s="3"/>
-    </row>
-    <row r="68" spans="2:33" x14ac:dyDescent="0.2">
+      <c r="AH67" s="3"/>
+    </row>
+    <row r="68" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C68" s="1" t="s">
         <v>60</v>
       </c>
@@ -5904,8 +6066,11 @@
       <c r="AG68" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="69" spans="2:33" x14ac:dyDescent="0.2">
+      <c r="AH68" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="69" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C69" s="1" t="s">
         <v>61</v>
       </c>
@@ -5999,8 +6164,11 @@
       <c r="AG69" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="70" spans="2:33" x14ac:dyDescent="0.2">
+      <c r="AH69" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="70" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C70" s="1" t="s">
         <v>62</v>
       </c>
@@ -6094,8 +6262,11 @@
       <c r="AG70" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="71" spans="2:33" x14ac:dyDescent="0.2">
+      <c r="AH70" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="71" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C71" s="1" t="s">
         <v>63</v>
       </c>
@@ -6189,103 +6360,109 @@
       <c r="AG71" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="72" spans="2:33" x14ac:dyDescent="0.2">
+      <c r="AH71" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="72" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C72" s="1" t="s">
         <v>64</v>
       </c>
       <c r="D72" s="3">
-        <v>18989700</v>
+        <v>18364800</v>
       </c>
       <c r="E72" s="3">
-        <v>19142700</v>
+        <v>18240100</v>
       </c>
       <c r="F72" s="3">
-        <v>18583600</v>
+        <v>18387100</v>
       </c>
       <c r="G72" s="3">
-        <v>18133300</v>
+        <v>17850100</v>
       </c>
       <c r="H72" s="3">
-        <v>18050100</v>
+        <v>17417600</v>
       </c>
       <c r="I72" s="3">
-        <v>17706700</v>
+        <v>17337600</v>
       </c>
       <c r="J72" s="3">
+        <v>17007700</v>
+      </c>
+      <c r="K72" s="3">
         <v>17130600</v>
       </c>
-      <c r="K72" s="3">
+      <c r="L72" s="3">
         <v>16662400</v>
       </c>
-      <c r="L72" s="3">
+      <c r="M72" s="3">
         <v>16044400</v>
       </c>
-      <c r="M72" s="3">
+      <c r="N72" s="3">
         <v>15764300</v>
       </c>
-      <c r="N72" s="3">
+      <c r="O72" s="3">
         <v>15298800</v>
       </c>
-      <c r="O72" s="3">
+      <c r="P72" s="3">
         <v>14524300</v>
       </c>
-      <c r="P72" s="3">
+      <c r="Q72" s="3">
         <v>14258500</v>
       </c>
-      <c r="Q72" s="3">
+      <c r="R72" s="3">
         <v>14719300</v>
       </c>
-      <c r="R72" s="3">
+      <c r="S72" s="3">
         <v>14362200</v>
       </c>
-      <c r="S72" s="3">
+      <c r="T72" s="3">
         <v>15002800</v>
       </c>
-      <c r="T72" s="3">
+      <c r="U72" s="3">
         <v>15745800</v>
       </c>
-      <c r="U72" s="3">
+      <c r="V72" s="3">
         <v>15573800</v>
       </c>
-      <c r="V72" s="3">
+      <c r="W72" s="3">
         <v>15698600</v>
       </c>
-      <c r="W72" s="3">
+      <c r="X72" s="3">
         <v>15678000</v>
       </c>
-      <c r="X72" s="3">
+      <c r="Y72" s="3">
         <v>14384700</v>
       </c>
-      <c r="Y72" s="3">
+      <c r="Z72" s="3">
         <v>13795900</v>
       </c>
-      <c r="Z72" s="3">
+      <c r="AA72" s="3">
         <v>13837700</v>
       </c>
-      <c r="AA72" s="3">
+      <c r="AB72" s="3">
         <v>13273900</v>
       </c>
-      <c r="AB72" s="3">
+      <c r="AC72" s="3">
         <v>13745600</v>
       </c>
-      <c r="AC72" s="3">
+      <c r="AD72" s="3">
         <v>13660700</v>
       </c>
-      <c r="AD72" s="3">
+      <c r="AE72" s="3">
         <v>13507800</v>
       </c>
-      <c r="AE72" s="3">
+      <c r="AF72" s="3">
         <v>13138800</v>
       </c>
-      <c r="AF72" s="3">
+      <c r="AG72" s="3">
         <v>13150400</v>
       </c>
-      <c r="AG72" s="3">
+      <c r="AH72" s="3">
         <v>13062800</v>
       </c>
     </row>
-    <row r="73" spans="2:33" x14ac:dyDescent="0.2">
+    <row r="73" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C73" s="1" t="s">
         <v>65</v>
       </c>
@@ -6379,8 +6556,11 @@
       <c r="AG73" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="74" spans="2:33" x14ac:dyDescent="0.2">
+      <c r="AH73" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="74" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C74" s="1" t="s">
         <v>66</v>
       </c>
@@ -6474,8 +6654,11 @@
       <c r="AG74" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="75" spans="2:33" x14ac:dyDescent="0.2">
+      <c r="AH74" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="75" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C75" s="1" t="s">
         <v>67</v>
       </c>
@@ -6569,103 +6752,109 @@
       <c r="AG75" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="76" spans="2:33" x14ac:dyDescent="0.2">
+      <c r="AH75" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="76" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C76" s="1" t="s">
         <v>68</v>
       </c>
       <c r="D76" s="3">
-        <v>24066800</v>
+        <v>23523400</v>
       </c>
       <c r="E76" s="3">
-        <v>24004800</v>
+        <v>23116800</v>
       </c>
       <c r="F76" s="3">
-        <v>22986000</v>
+        <v>23057200</v>
       </c>
       <c r="G76" s="3">
-        <v>22541300</v>
+        <v>22078600</v>
       </c>
       <c r="H76" s="3">
-        <v>21859000</v>
+        <v>21651600</v>
       </c>
       <c r="I76" s="3">
-        <v>21472000</v>
+        <v>20996200</v>
       </c>
       <c r="J76" s="3">
+        <v>20624400</v>
+      </c>
+      <c r="K76" s="3">
         <v>20539800</v>
       </c>
-      <c r="K76" s="3">
+      <c r="L76" s="3">
         <v>20238100</v>
       </c>
-      <c r="L76" s="3">
+      <c r="M76" s="3">
         <v>19381500</v>
       </c>
-      <c r="M76" s="3">
+      <c r="N76" s="3">
         <v>18987000</v>
       </c>
-      <c r="N76" s="3">
+      <c r="O76" s="3">
         <v>18419400</v>
       </c>
-      <c r="O76" s="3">
+      <c r="P76" s="3">
         <v>17399500</v>
       </c>
-      <c r="P76" s="3">
+      <c r="Q76" s="3">
         <v>17059700</v>
       </c>
-      <c r="Q76" s="3">
+      <c r="R76" s="3">
         <v>17519900</v>
       </c>
-      <c r="R76" s="3">
+      <c r="S76" s="3">
         <v>17171900</v>
       </c>
-      <c r="S76" s="3">
+      <c r="T76" s="3">
         <v>17677500</v>
       </c>
-      <c r="T76" s="3">
+      <c r="U76" s="3">
         <v>18283800</v>
       </c>
-      <c r="U76" s="3">
+      <c r="V76" s="3">
         <v>17718000</v>
       </c>
-      <c r="V76" s="3">
+      <c r="W76" s="3">
         <v>17110000</v>
       </c>
-      <c r="W76" s="3">
+      <c r="X76" s="3">
         <v>17117400</v>
       </c>
-      <c r="X76" s="3">
+      <c r="Y76" s="3">
         <v>18261500</v>
       </c>
-      <c r="Y76" s="3">
+      <c r="Z76" s="3">
         <v>17579400</v>
       </c>
-      <c r="Z76" s="3">
+      <c r="AA76" s="3">
         <v>17463800</v>
       </c>
-      <c r="AA76" s="3">
+      <c r="AB76" s="3">
         <v>17085700</v>
       </c>
-      <c r="AB76" s="3">
+      <c r="AC76" s="3">
         <v>17922000</v>
       </c>
-      <c r="AC76" s="3">
+      <c r="AD76" s="3">
         <v>17996500</v>
       </c>
-      <c r="AD76" s="3">
+      <c r="AE76" s="3">
         <v>17825600</v>
       </c>
-      <c r="AE76" s="3">
+      <c r="AF76" s="3">
         <v>17960100</v>
       </c>
-      <c r="AF76" s="3">
+      <c r="AG76" s="3">
         <v>18347500</v>
       </c>
-      <c r="AG76" s="3">
+      <c r="AH76" s="3">
         <v>18412300</v>
       </c>
     </row>
-    <row r="77" spans="2:33" x14ac:dyDescent="0.2">
+    <row r="77" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C77" s="1" t="s">
         <v>69</v>
       </c>
@@ -6759,203 +6948,212 @@
       <c r="AG77" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="79" spans="2:33" x14ac:dyDescent="0.2">
+      <c r="AH77" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="79" spans="2:34" x14ac:dyDescent="0.2">
       <c r="B79" s="1" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="80" spans="2:33" x14ac:dyDescent="0.2">
+    <row r="80" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C80" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D80" s="2">
+        <v>45382</v>
+      </c>
+      <c r="E80" s="2">
         <v>45291</v>
       </c>
-      <c r="E80" s="2">
+      <c r="F80" s="2">
         <v>45199</v>
       </c>
-      <c r="F80" s="2">
+      <c r="G80" s="2">
         <v>45107</v>
       </c>
-      <c r="G80" s="2">
+      <c r="H80" s="2">
         <v>45016</v>
       </c>
-      <c r="H80" s="2">
+      <c r="I80" s="2">
         <v>44926</v>
       </c>
-      <c r="I80" s="2">
+      <c r="J80" s="2">
         <v>44834</v>
       </c>
-      <c r="J80" s="2">
+      <c r="K80" s="2">
         <v>44742</v>
       </c>
-      <c r="K80" s="2">
+      <c r="L80" s="2">
         <v>44651</v>
       </c>
-      <c r="L80" s="2">
+      <c r="M80" s="2">
         <v>44561</v>
       </c>
-      <c r="M80" s="2">
+      <c r="N80" s="2">
         <v>44469</v>
       </c>
-      <c r="N80" s="2">
+      <c r="O80" s="2">
         <v>44377</v>
       </c>
-      <c r="O80" s="2">
+      <c r="P80" s="2">
         <v>44286</v>
       </c>
-      <c r="P80" s="2">
+      <c r="Q80" s="2">
         <v>44196</v>
       </c>
-      <c r="Q80" s="2">
+      <c r="R80" s="2">
         <v>44104</v>
       </c>
-      <c r="R80" s="2">
+      <c r="S80" s="2">
         <v>44012</v>
       </c>
-      <c r="S80" s="2">
+      <c r="T80" s="2">
         <v>43921</v>
       </c>
-      <c r="T80" s="2">
+      <c r="U80" s="2">
         <v>43830</v>
       </c>
-      <c r="U80" s="2">
+      <c r="V80" s="2">
         <v>43738</v>
       </c>
-      <c r="V80" s="2">
+      <c r="W80" s="2">
         <v>43646</v>
       </c>
-      <c r="W80" s="2">
+      <c r="X80" s="2">
         <v>43555</v>
       </c>
-      <c r="X80" s="2">
+      <c r="Y80" s="2">
         <v>43465</v>
       </c>
-      <c r="Y80" s="2">
+      <c r="Z80" s="2">
         <v>43373</v>
       </c>
-      <c r="Z80" s="2">
+      <c r="AA80" s="2">
         <v>43281</v>
       </c>
-      <c r="AA80" s="2">
+      <c r="AB80" s="2">
         <v>43190</v>
       </c>
-      <c r="AB80" s="2">
+      <c r="AC80" s="2">
         <v>43100</v>
       </c>
-      <c r="AC80" s="2">
+      <c r="AD80" s="2">
         <v>43008</v>
       </c>
-      <c r="AD80" s="2">
+      <c r="AE80" s="2">
         <v>42916</v>
       </c>
-      <c r="AE80" s="2">
+      <c r="AF80" s="2">
         <v>42825</v>
       </c>
-      <c r="AF80" s="2">
+      <c r="AG80" s="2">
         <v>42735</v>
       </c>
-      <c r="AG80" s="2">
+      <c r="AH80" s="2">
         <v>42643</v>
       </c>
     </row>
-    <row r="81" spans="3:33" x14ac:dyDescent="0.2">
+    <row r="81" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C81" s="1" t="s">
         <v>28</v>
       </c>
-      <c r="D81" s="3">
-        <v>25000</v>
+      <c r="D81" s="3" t="s">
+        <v>5</v>
       </c>
       <c r="E81" s="3">
-        <v>658600</v>
+        <v>24000</v>
       </c>
       <c r="F81" s="3">
-        <v>450300</v>
+        <v>632600</v>
       </c>
       <c r="G81" s="3">
-        <v>671300</v>
+        <v>432500</v>
       </c>
       <c r="H81" s="3">
-        <v>343400</v>
+        <v>644800</v>
       </c>
       <c r="I81" s="3">
-        <v>667000</v>
+        <v>329800</v>
       </c>
       <c r="J81" s="3">
+        <v>640600</v>
+      </c>
+      <c r="K81" s="3">
         <v>684400</v>
       </c>
-      <c r="K81" s="3">
+      <c r="L81" s="3">
         <v>631400</v>
       </c>
-      <c r="L81" s="3">
+      <c r="M81" s="3">
         <v>279500</v>
       </c>
-      <c r="M81" s="3">
+      <c r="N81" s="3">
         <v>570700</v>
       </c>
-      <c r="N81" s="3">
+      <c r="O81" s="3">
         <v>552600</v>
       </c>
-      <c r="O81" s="3">
+      <c r="P81" s="3">
         <v>482000</v>
       </c>
-      <c r="P81" s="3">
+      <c r="Q81" s="3">
         <v>112600</v>
       </c>
-      <c r="Q81" s="3">
+      <c r="R81" s="3">
         <v>358800</v>
       </c>
-      <c r="R81" s="3">
+      <c r="S81" s="3">
         <v>100500</v>
       </c>
-      <c r="S81" s="3">
+      <c r="T81" s="3">
         <v>412900</v>
       </c>
-      <c r="T81" s="3">
+      <c r="U81" s="3">
         <v>174900</v>
       </c>
-      <c r="U81" s="3">
+      <c r="V81" s="3">
         <v>410100</v>
       </c>
-      <c r="V81" s="3">
+      <c r="W81" s="3">
         <v>537700</v>
       </c>
-      <c r="W81" s="3">
+      <c r="X81" s="3">
         <v>517500</v>
       </c>
-      <c r="X81" s="3">
+      <c r="Y81" s="3">
         <v>76800</v>
       </c>
-      <c r="Y81" s="3">
+      <c r="Z81" s="3">
         <v>453900</v>
       </c>
-      <c r="Z81" s="3">
+      <c r="AA81" s="3">
         <v>569900</v>
       </c>
-      <c r="AA81" s="3">
+      <c r="AB81" s="3">
         <v>463600</v>
       </c>
-      <c r="AB81" s="3">
+      <c r="AC81" s="3">
         <v>84900</v>
       </c>
-      <c r="AC81" s="3">
+      <c r="AD81" s="3">
         <v>212100</v>
       </c>
-      <c r="AD81" s="3">
+      <c r="AE81" s="3">
         <v>369000</v>
       </c>
-      <c r="AE81" s="3">
+      <c r="AF81" s="3">
         <v>517600</v>
       </c>
-      <c r="AF81" s="3">
+      <c r="AG81" s="3">
         <v>88500</v>
       </c>
-      <c r="AG81" s="3">
+      <c r="AH81" s="3">
         <v>275700</v>
       </c>
     </row>
-    <row r="82" spans="3:33" x14ac:dyDescent="0.2">
+    <row r="82" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C82" s="1" t="s">
         <v>71</v>
       </c>
@@ -6989,103 +7187,107 @@
       <c r="AE82" s="3"/>
       <c r="AF82" s="3"/>
       <c r="AG82" s="3"/>
-    </row>
-    <row r="83" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH82" s="3"/>
+    </row>
+    <row r="83" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C83" s="1" t="s">
         <v>72</v>
       </c>
       <c r="D83" s="3">
-        <v>200600</v>
+        <v>201500</v>
       </c>
       <c r="E83" s="3">
-        <v>182600</v>
+        <v>192600</v>
       </c>
       <c r="F83" s="3">
-        <v>184700</v>
+        <v>175400</v>
       </c>
       <c r="G83" s="3">
-        <v>186900</v>
+        <v>177400</v>
       </c>
       <c r="H83" s="3">
-        <v>187700</v>
+        <v>179600</v>
       </c>
       <c r="I83" s="3">
-        <v>176600</v>
+        <v>180300</v>
       </c>
       <c r="J83" s="3">
+        <v>169700</v>
+      </c>
+      <c r="K83" s="3">
         <v>175600</v>
       </c>
-      <c r="K83" s="3">
+      <c r="L83" s="3">
         <v>168600</v>
       </c>
-      <c r="L83" s="3">
+      <c r="M83" s="3">
         <v>155900</v>
       </c>
-      <c r="M83" s="3">
+      <c r="N83" s="3">
         <v>149200</v>
       </c>
-      <c r="N83" s="3">
+      <c r="O83" s="3">
         <v>184500</v>
       </c>
-      <c r="O83" s="3">
+      <c r="P83" s="3">
         <v>102900</v>
       </c>
-      <c r="P83" s="3">
+      <c r="Q83" s="3">
         <v>101300</v>
       </c>
-      <c r="Q83" s="3">
+      <c r="R83" s="3">
         <v>101500</v>
       </c>
-      <c r="R83" s="3">
+      <c r="S83" s="3">
         <v>98700</v>
       </c>
-      <c r="S83" s="3">
+      <c r="T83" s="3">
         <v>112300</v>
       </c>
-      <c r="T83" s="3">
+      <c r="U83" s="3">
         <v>120400</v>
       </c>
-      <c r="U83" s="3">
+      <c r="V83" s="3">
         <v>116900</v>
       </c>
-      <c r="V83" s="3">
+      <c r="W83" s="3">
         <v>108900</v>
       </c>
-      <c r="W83" s="3">
+      <c r="X83" s="3">
         <v>93600</v>
       </c>
-      <c r="X83" s="3">
+      <c r="Y83" s="3">
         <v>61600</v>
       </c>
-      <c r="Y83" s="3">
+      <c r="Z83" s="3">
         <v>58600</v>
       </c>
-      <c r="Z83" s="3">
+      <c r="AA83" s="3">
         <v>56000</v>
       </c>
-      <c r="AA83" s="3">
+      <c r="AB83" s="3">
         <v>50600</v>
       </c>
-      <c r="AB83" s="3">
+      <c r="AC83" s="3">
         <v>49900</v>
       </c>
-      <c r="AC83" s="3">
+      <c r="AD83" s="3">
         <v>50800</v>
       </c>
-      <c r="AD83" s="3">
+      <c r="AE83" s="3">
         <v>51600</v>
       </c>
-      <c r="AE83" s="3">
+      <c r="AF83" s="3">
         <v>55200</v>
       </c>
-      <c r="AF83" s="3">
+      <c r="AG83" s="3">
         <v>54800</v>
       </c>
-      <c r="AG83" s="3">
+      <c r="AH83" s="3">
         <v>53700</v>
       </c>
     </row>
-    <row r="84" spans="3:33" x14ac:dyDescent="0.2">
+    <row r="84" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C84" s="1" t="s">
         <v>73</v>
       </c>
@@ -7179,8 +7381,11 @@
       <c r="AG84" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="85" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH84" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="85" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C85" s="1" t="s">
         <v>74</v>
       </c>
@@ -7274,8 +7479,11 @@
       <c r="AG85" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="86" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH85" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="86" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C86" s="1" t="s">
         <v>75</v>
       </c>
@@ -7369,8 +7577,11 @@
       <c r="AG86" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="87" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH86" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="87" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C87" s="1" t="s">
         <v>76</v>
       </c>
@@ -7464,8 +7675,11 @@
       <c r="AG87" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="88" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH87" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="88" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C88" s="1" t="s">
         <v>77</v>
       </c>
@@ -7559,103 +7773,109 @@
       <c r="AG88" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="89" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH88" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="89" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C89" s="1" t="s">
         <v>78</v>
       </c>
       <c r="D89" s="3">
-        <v>4808900</v>
+        <v>-161100</v>
       </c>
       <c r="E89" s="3">
-        <v>4707100</v>
+        <v>4619100</v>
       </c>
       <c r="F89" s="3">
-        <v>-5660200</v>
+        <v>4521300</v>
       </c>
       <c r="G89" s="3">
-        <v>-2623200</v>
+        <v>-5436700</v>
       </c>
       <c r="H89" s="3">
-        <v>12172100</v>
+        <v>-2519600</v>
       </c>
       <c r="I89" s="3">
-        <v>-3488000</v>
+        <v>11691600</v>
       </c>
       <c r="J89" s="3">
+        <v>-3350300</v>
+      </c>
+      <c r="K89" s="3">
         <v>-2130300</v>
       </c>
-      <c r="K89" s="3">
+      <c r="L89" s="3">
         <v>7700600</v>
       </c>
-      <c r="L89" s="3">
+      <c r="M89" s="3">
         <v>4027400</v>
       </c>
-      <c r="M89" s="3">
+      <c r="N89" s="3">
         <v>2586700</v>
       </c>
-      <c r="N89" s="3">
+      <c r="O89" s="3">
         <v>-4607300</v>
       </c>
-      <c r="O89" s="3">
+      <c r="P89" s="3">
         <v>831700</v>
       </c>
-      <c r="P89" s="3">
+      <c r="Q89" s="3">
         <v>1545900</v>
       </c>
-      <c r="Q89" s="3">
+      <c r="R89" s="3">
         <v>-766500</v>
       </c>
-      <c r="R89" s="3">
+      <c r="S89" s="3">
         <v>2718500</v>
       </c>
-      <c r="S89" s="3">
+      <c r="T89" s="3">
         <v>-824700</v>
       </c>
-      <c r="T89" s="3">
+      <c r="U89" s="3">
         <v>-153300</v>
       </c>
-      <c r="U89" s="3">
+      <c r="V89" s="3">
         <v>-428600</v>
       </c>
-      <c r="V89" s="3">
+      <c r="W89" s="3">
         <v>3501700</v>
       </c>
-      <c r="W89" s="3">
+      <c r="X89" s="3">
         <v>-1296100</v>
       </c>
-      <c r="X89" s="3">
+      <c r="Y89" s="3">
         <v>5231600</v>
       </c>
-      <c r="Y89" s="3">
+      <c r="Z89" s="3">
         <v>908000</v>
       </c>
-      <c r="Z89" s="3">
+      <c r="AA89" s="3">
         <v>643600</v>
       </c>
-      <c r="AA89" s="3">
+      <c r="AB89" s="3">
         <v>877700</v>
       </c>
-      <c r="AB89" s="3">
+      <c r="AC89" s="3">
         <v>-506300</v>
       </c>
-      <c r="AC89" s="3">
+      <c r="AD89" s="3">
         <v>-2456000</v>
       </c>
-      <c r="AD89" s="3">
+      <c r="AE89" s="3">
         <v>-340700</v>
       </c>
-      <c r="AE89" s="3">
+      <c r="AF89" s="3">
         <v>1561500</v>
       </c>
-      <c r="AF89" s="3">
+      <c r="AG89" s="3">
         <v>108800</v>
       </c>
-      <c r="AG89" s="3">
+      <c r="AH89" s="3">
         <v>3807600</v>
       </c>
     </row>
-    <row r="90" spans="3:33" x14ac:dyDescent="0.2">
+    <row r="90" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C90" s="1" t="s">
         <v>79</v>
       </c>
@@ -7689,103 +7909,107 @@
       <c r="AE90" s="3"/>
       <c r="AF90" s="3"/>
       <c r="AG90" s="3"/>
-    </row>
-    <row r="91" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH90" s="3"/>
+    </row>
+    <row r="91" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C91" s="1" t="s">
         <v>80</v>
       </c>
       <c r="D91" s="3">
+        <v>-77550000</v>
+      </c>
+      <c r="E91" s="3">
         <v>-161762000</v>
       </c>
-      <c r="E91" s="3">
+      <c r="F91" s="3">
         <v>-68486000</v>
       </c>
-      <c r="F91" s="3">
+      <c r="G91" s="3">
         <v>-103704000</v>
       </c>
-      <c r="G91" s="3">
+      <c r="H91" s="3">
         <v>-59247000</v>
       </c>
-      <c r="H91" s="3">
+      <c r="I91" s="3">
         <v>-113722000</v>
       </c>
-      <c r="I91" s="3">
+      <c r="J91" s="3">
         <v>-77226000</v>
       </c>
-      <c r="J91" s="3">
+      <c r="K91" s="3">
         <v>-104059000</v>
       </c>
-      <c r="K91" s="3">
+      <c r="L91" s="3">
         <v>-52618000</v>
       </c>
-      <c r="L91" s="3">
+      <c r="M91" s="3">
         <v>-74615000</v>
       </c>
-      <c r="M91" s="3">
+      <c r="N91" s="3">
         <v>-81614000</v>
       </c>
-      <c r="N91" s="3">
+      <c r="O91" s="3">
         <v>-15900</v>
       </c>
-      <c r="O91" s="3">
+      <c r="P91" s="3">
         <v>-14300</v>
       </c>
-      <c r="P91" s="3">
+      <c r="Q91" s="3">
         <v>-43600</v>
       </c>
-      <c r="Q91" s="3">
+      <c r="R91" s="3">
         <v>-25600</v>
       </c>
-      <c r="R91" s="3">
+      <c r="S91" s="3">
         <v>-24800</v>
       </c>
-      <c r="S91" s="3">
+      <c r="T91" s="3">
         <v>-20300</v>
       </c>
-      <c r="T91" s="3">
+      <c r="U91" s="3">
         <v>-190900</v>
       </c>
-      <c r="U91" s="3">
+      <c r="V91" s="3">
         <v>-91000</v>
       </c>
-      <c r="V91" s="3">
+      <c r="W91" s="3">
         <v>-55400</v>
       </c>
-      <c r="W91" s="3">
+      <c r="X91" s="3">
         <v>-31700</v>
       </c>
-      <c r="X91" s="3">
+      <c r="Y91" s="3">
         <v>-43000</v>
       </c>
-      <c r="Y91" s="3">
+      <c r="Z91" s="3">
         <v>-20100</v>
       </c>
-      <c r="Z91" s="3">
+      <c r="AA91" s="3">
         <v>-18000</v>
       </c>
-      <c r="AA91" s="3">
+      <c r="AB91" s="3">
         <v>-17800</v>
       </c>
-      <c r="AB91" s="3">
+      <c r="AC91" s="3">
         <v>-25100</v>
       </c>
-      <c r="AC91" s="3">
+      <c r="AD91" s="3">
         <v>-57300</v>
       </c>
-      <c r="AD91" s="3">
+      <c r="AE91" s="3">
         <v>-37900</v>
       </c>
-      <c r="AE91" s="3">
+      <c r="AF91" s="3">
         <v>-22400</v>
       </c>
-      <c r="AF91" s="3">
+      <c r="AG91" s="3">
         <v>-111600</v>
       </c>
-      <c r="AG91" s="3">
+      <c r="AH91" s="3">
         <v>-90400</v>
       </c>
     </row>
-    <row r="92" spans="3:33" x14ac:dyDescent="0.2">
+    <row r="92" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C92" s="1" t="s">
         <v>81</v>
       </c>
@@ -7879,8 +8103,11 @@
       <c r="AG92" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="93" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH92" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="93" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C93" s="1" t="s">
         <v>82</v>
       </c>
@@ -7974,103 +8201,109 @@
       <c r="AG93" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="94" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH93" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="94" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C94" s="1" t="s">
         <v>83</v>
       </c>
       <c r="D94" s="3">
-        <v>-616300</v>
+        <v>1806200</v>
       </c>
       <c r="E94" s="3">
-        <v>-1133100</v>
+        <v>-592000</v>
       </c>
       <c r="F94" s="3">
-        <v>-261800</v>
+        <v>-1088400</v>
       </c>
       <c r="G94" s="3">
-        <v>298100</v>
+        <v>-251500</v>
       </c>
       <c r="H94" s="3">
-        <v>-2949200</v>
+        <v>286300</v>
       </c>
       <c r="I94" s="3">
-        <v>-2451700</v>
+        <v>-2832800</v>
       </c>
       <c r="J94" s="3">
+        <v>-2354900</v>
+      </c>
+      <c r="K94" s="3">
         <v>2353800</v>
       </c>
-      <c r="K94" s="3">
+      <c r="L94" s="3">
         <v>-2278800</v>
       </c>
-      <c r="L94" s="3">
+      <c r="M94" s="3">
         <v>-4489600</v>
       </c>
-      <c r="M94" s="3">
+      <c r="N94" s="3">
         <v>-3902300</v>
       </c>
-      <c r="N94" s="3">
+      <c r="O94" s="3">
         <v>1124900</v>
       </c>
-      <c r="O94" s="3">
+      <c r="P94" s="3">
         <v>-723400</v>
       </c>
-      <c r="P94" s="3">
+      <c r="Q94" s="3">
         <v>-365200</v>
       </c>
-      <c r="Q94" s="3">
+      <c r="R94" s="3">
         <v>-124500</v>
       </c>
-      <c r="R94" s="3">
+      <c r="S94" s="3">
         <v>-446100</v>
       </c>
-      <c r="S94" s="3">
+      <c r="T94" s="3">
         <v>-179800</v>
       </c>
-      <c r="T94" s="3">
+      <c r="U94" s="3">
         <v>-962200</v>
       </c>
-      <c r="U94" s="3">
+      <c r="V94" s="3">
         <v>-913600</v>
       </c>
-      <c r="V94" s="3">
+      <c r="W94" s="3">
         <v>-5520900</v>
       </c>
-      <c r="W94" s="3">
+      <c r="X94" s="3">
         <v>-97900</v>
       </c>
-      <c r="X94" s="3">
+      <c r="Y94" s="3">
         <v>-5105000</v>
       </c>
-      <c r="Y94" s="3">
+      <c r="Z94" s="3">
         <v>-2452600</v>
       </c>
-      <c r="Z94" s="3">
+      <c r="AA94" s="3">
         <v>-1063800</v>
       </c>
-      <c r="AA94" s="3">
+      <c r="AB94" s="3">
         <v>-587600</v>
       </c>
-      <c r="AB94" s="3">
+      <c r="AC94" s="3">
         <v>1277600</v>
       </c>
-      <c r="AC94" s="3">
+      <c r="AD94" s="3">
         <v>-195600</v>
       </c>
-      <c r="AD94" s="3">
+      <c r="AE94" s="3">
         <v>183200</v>
       </c>
-      <c r="AE94" s="3">
+      <c r="AF94" s="3">
         <v>392500</v>
       </c>
-      <c r="AF94" s="3">
+      <c r="AG94" s="3">
         <v>-2371700</v>
       </c>
-      <c r="AG94" s="3">
+      <c r="AH94" s="3">
         <v>694800</v>
       </c>
     </row>
-    <row r="95" spans="3:33" x14ac:dyDescent="0.2">
+    <row r="95" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C95" s="1" t="s">
         <v>84</v>
       </c>
@@ -8104,19 +8337,20 @@
       <c r="AE95" s="3"/>
       <c r="AF95" s="3"/>
       <c r="AG95" s="3"/>
-    </row>
-    <row r="96" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH95" s="3"/>
+    </row>
+    <row r="96" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C96" s="1" t="s">
         <v>85</v>
       </c>
       <c r="D96" s="3">
-        <v>-102300</v>
+        <v>0</v>
       </c>
       <c r="E96" s="3">
-        <v>-99300</v>
+        <v>-98200</v>
       </c>
       <c r="F96" s="3">
-        <v>0</v>
+        <v>-95400</v>
       </c>
       <c r="G96" s="3">
         <v>0</v>
@@ -8125,10 +8359,10 @@
         <v>0</v>
       </c>
       <c r="I96" s="3">
-        <v>-83000</v>
+        <v>0</v>
       </c>
       <c r="J96" s="3">
-        <v>0</v>
+        <v>-79700</v>
       </c>
       <c r="K96" s="3">
         <v>0</v>
@@ -8137,11 +8371,11 @@
         <v>0</v>
       </c>
       <c r="M96" s="3">
+        <v>0</v>
+      </c>
+      <c r="N96" s="3">
         <v>-81300</v>
       </c>
-      <c r="N96" s="3">
-        <v>0</v>
-      </c>
       <c r="O96" s="3">
         <v>0</v>
       </c>
@@ -8185,22 +8419,25 @@
         <v>0</v>
       </c>
       <c r="AC96" s="3">
+        <v>0</v>
+      </c>
+      <c r="AD96" s="3">
         <v>-59200</v>
       </c>
-      <c r="AD96" s="3">
+      <c r="AE96" s="3">
         <v>-237000</v>
       </c>
-      <c r="AE96" s="3">
-        <v>0</v>
-      </c>
       <c r="AF96" s="3">
+        <v>0</v>
+      </c>
+      <c r="AG96" s="3">
         <v>-38100</v>
       </c>
-      <c r="AG96" s="3">
+      <c r="AH96" s="3">
         <v>-22800</v>
       </c>
     </row>
-    <row r="97" spans="3:33" x14ac:dyDescent="0.2">
+    <row r="97" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C97" s="1" t="s">
         <v>86</v>
       </c>
@@ -8294,8 +8531,11 @@
       <c r="AG97" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="98" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH97" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="98" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C98" s="1" t="s">
         <v>87</v>
       </c>
@@ -8389,8 +8629,11 @@
       <c r="AG98" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="99" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH98" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="99" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C99" s="1" t="s">
         <v>88</v>
       </c>
@@ -8484,289 +8727,301 @@
       <c r="AG99" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="100" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH99" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="100" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C100" s="1" t="s">
         <v>89</v>
       </c>
       <c r="D100" s="3">
-        <v>-470600</v>
+        <v>-897200</v>
       </c>
       <c r="E100" s="3">
-        <v>-408800</v>
+        <v>-452100</v>
       </c>
       <c r="F100" s="3">
-        <v>-1038300</v>
+        <v>-392700</v>
       </c>
       <c r="G100" s="3">
-        <v>-256000</v>
+        <v>-997300</v>
       </c>
       <c r="H100" s="3">
-        <v>-5215900</v>
+        <v>-245900</v>
       </c>
       <c r="I100" s="3">
-        <v>1767000</v>
+        <v>-5010000</v>
       </c>
       <c r="J100" s="3">
+        <v>1697300</v>
+      </c>
+      <c r="K100" s="3">
         <v>3000400</v>
       </c>
-      <c r="K100" s="3">
+      <c r="L100" s="3">
         <v>1932700</v>
       </c>
-      <c r="L100" s="3">
+      <c r="M100" s="3">
         <v>2031800</v>
       </c>
-      <c r="M100" s="3">
+      <c r="N100" s="3">
         <v>1404600</v>
       </c>
-      <c r="N100" s="3">
+      <c r="O100" s="3">
         <v>2911000</v>
       </c>
-      <c r="O100" s="3">
+      <c r="P100" s="3">
         <v>453200</v>
       </c>
-      <c r="P100" s="3">
+      <c r="Q100" s="3">
         <v>261800</v>
       </c>
-      <c r="Q100" s="3">
+      <c r="R100" s="3">
         <v>553800</v>
       </c>
-      <c r="R100" s="3">
+      <c r="S100" s="3">
         <v>-2356000</v>
       </c>
-      <c r="S100" s="3">
+      <c r="T100" s="3">
         <v>3526800</v>
       </c>
-      <c r="T100" s="3">
+      <c r="U100" s="3">
         <v>-950700</v>
       </c>
-      <c r="U100" s="3">
+      <c r="V100" s="3">
         <v>3000500</v>
       </c>
-      <c r="V100" s="3">
+      <c r="W100" s="3">
         <v>3588600</v>
       </c>
-      <c r="W100" s="3">
+      <c r="X100" s="3">
         <v>-289800</v>
       </c>
-      <c r="X100" s="3">
+      <c r="Y100" s="3">
         <v>491400</v>
       </c>
-      <c r="Y100" s="3">
+      <c r="Z100" s="3">
         <v>1689200</v>
       </c>
-      <c r="Z100" s="3">
+      <c r="AA100" s="3">
         <v>354700</v>
       </c>
-      <c r="AA100" s="3">
+      <c r="AB100" s="3">
         <v>-1323700</v>
       </c>
-      <c r="AB100" s="3">
+      <c r="AC100" s="3">
         <v>-309500</v>
       </c>
-      <c r="AC100" s="3">
+      <c r="AD100" s="3">
         <v>2140800</v>
       </c>
-      <c r="AD100" s="3">
+      <c r="AE100" s="3">
         <v>-384900</v>
       </c>
-      <c r="AE100" s="3">
+      <c r="AF100" s="3">
         <v>-1500100</v>
       </c>
-      <c r="AF100" s="3">
+      <c r="AG100" s="3">
         <v>1503800</v>
       </c>
-      <c r="AG100" s="3">
+      <c r="AH100" s="3">
         <v>-1778900</v>
       </c>
     </row>
-    <row r="101" spans="3:33" x14ac:dyDescent="0.2">
+    <row r="101" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C101" s="1" t="s">
         <v>90</v>
       </c>
       <c r="D101" s="3">
-        <v>-176700</v>
+        <v>257800</v>
       </c>
       <c r="E101" s="3">
-        <v>27900</v>
+        <v>-169700</v>
       </c>
       <c r="F101" s="3">
-        <v>-105200</v>
+        <v>26800</v>
       </c>
       <c r="G101" s="3">
-        <v>124700</v>
+        <v>-101100</v>
       </c>
       <c r="H101" s="3">
-        <v>-1498900</v>
+        <v>119800</v>
       </c>
       <c r="I101" s="3">
-        <v>664800</v>
+        <v>-1439700</v>
       </c>
       <c r="J101" s="3">
+        <v>638600</v>
+      </c>
+      <c r="K101" s="3">
         <v>657000</v>
       </c>
-      <c r="K101" s="3">
+      <c r="L101" s="3">
         <v>203100</v>
       </c>
-      <c r="L101" s="3">
+      <c r="M101" s="3">
         <v>68900</v>
       </c>
-      <c r="M101" s="3">
+      <c r="N101" s="3">
         <v>409500</v>
       </c>
-      <c r="N101" s="3">
+      <c r="O101" s="3">
         <v>18100</v>
       </c>
-      <c r="O101" s="3">
+      <c r="P101" s="3">
         <v>295500</v>
       </c>
-      <c r="P101" s="3">
+      <c r="Q101" s="3">
         <v>-571700</v>
       </c>
-      <c r="Q101" s="3">
+      <c r="R101" s="3">
         <v>-142900</v>
       </c>
-      <c r="R101" s="3">
+      <c r="S101" s="3">
         <v>-159900</v>
       </c>
-      <c r="S101" s="3">
+      <c r="T101" s="3">
         <v>200400</v>
       </c>
-      <c r="T101" s="3">
+      <c r="U101" s="3">
         <v>369400</v>
       </c>
-      <c r="U101" s="3">
+      <c r="V101" s="3">
         <v>-340600</v>
       </c>
-      <c r="V101" s="3">
+      <c r="W101" s="3">
         <v>51200</v>
       </c>
-      <c r="W101" s="3">
+      <c r="X101" s="3">
         <v>90500</v>
       </c>
-      <c r="X101" s="3">
+      <c r="Y101" s="3">
         <v>6400</v>
       </c>
-      <c r="Y101" s="3">
+      <c r="Z101" s="3">
         <v>-76600</v>
       </c>
-      <c r="Z101" s="3">
+      <c r="AA101" s="3">
         <v>218900</v>
       </c>
-      <c r="AA101" s="3">
+      <c r="AB101" s="3">
         <v>50500</v>
       </c>
-      <c r="AB101" s="3">
+      <c r="AC101" s="3">
         <v>-377500</v>
       </c>
-      <c r="AC101" s="3">
+      <c r="AD101" s="3">
         <v>14000</v>
       </c>
-      <c r="AD101" s="3">
+      <c r="AE101" s="3">
         <v>8400</v>
       </c>
-      <c r="AE101" s="3">
+      <c r="AF101" s="3">
         <v>-108300</v>
       </c>
-      <c r="AF101" s="3">
+      <c r="AG101" s="3">
         <v>138000</v>
       </c>
-      <c r="AG101" s="3">
+      <c r="AH101" s="3">
         <v>-105900</v>
       </c>
     </row>
-    <row r="102" spans="3:33" x14ac:dyDescent="0.2">
+    <row r="102" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C102" s="1" t="s">
         <v>91</v>
       </c>
       <c r="D102" s="3">
-        <v>3545200</v>
+        <v>1005700</v>
       </c>
       <c r="E102" s="3">
-        <v>3193100</v>
+        <v>3405300</v>
       </c>
       <c r="F102" s="3">
-        <v>-7065500</v>
+        <v>3067100</v>
       </c>
       <c r="G102" s="3">
-        <v>-2456400</v>
+        <v>-6786600</v>
       </c>
       <c r="H102" s="3">
-        <v>2508100</v>
+        <v>-2359400</v>
       </c>
       <c r="I102" s="3">
-        <v>-3507800</v>
+        <v>2409100</v>
       </c>
       <c r="J102" s="3">
+        <v>-3369400</v>
+      </c>
+      <c r="K102" s="3">
         <v>3880900</v>
       </c>
-      <c r="K102" s="3">
+      <c r="L102" s="3">
         <v>7557600</v>
       </c>
-      <c r="L102" s="3">
+      <c r="M102" s="3">
         <v>1638600</v>
       </c>
-      <c r="M102" s="3">
+      <c r="N102" s="3">
         <v>498500</v>
       </c>
-      <c r="N102" s="3">
+      <c r="O102" s="3">
         <v>-553300</v>
       </c>
-      <c r="O102" s="3">
+      <c r="P102" s="3">
         <v>857000</v>
       </c>
-      <c r="P102" s="3">
+      <c r="Q102" s="3">
         <v>870800</v>
       </c>
-      <c r="Q102" s="3">
+      <c r="R102" s="3">
         <v>-480000</v>
       </c>
-      <c r="R102" s="3">
+      <c r="S102" s="3">
         <v>-243500</v>
       </c>
-      <c r="S102" s="3">
+      <c r="T102" s="3">
         <v>2722600</v>
       </c>
-      <c r="T102" s="3">
+      <c r="U102" s="3">
         <v>-1696800</v>
       </c>
-      <c r="U102" s="3">
+      <c r="V102" s="3">
         <v>1317700</v>
       </c>
-      <c r="V102" s="3">
+      <c r="W102" s="3">
         <v>1620600</v>
       </c>
-      <c r="W102" s="3">
+      <c r="X102" s="3">
         <v>-1593300</v>
       </c>
-      <c r="X102" s="3">
+      <c r="Y102" s="3">
         <v>624400</v>
       </c>
-      <c r="Y102" s="3">
+      <c r="Z102" s="3">
         <v>68000</v>
       </c>
-      <c r="Z102" s="3">
+      <c r="AA102" s="3">
         <v>153400</v>
       </c>
-      <c r="AA102" s="3">
+      <c r="AB102" s="3">
         <v>-983000</v>
       </c>
-      <c r="AB102" s="3">
+      <c r="AC102" s="3">
         <v>84300</v>
       </c>
-      <c r="AC102" s="3">
+      <c r="AD102" s="3">
         <v>-496900</v>
       </c>
-      <c r="AD102" s="3">
+      <c r="AE102" s="3">
         <v>-534100</v>
       </c>
-      <c r="AE102" s="3">
+      <c r="AF102" s="3">
         <v>345600</v>
       </c>
-      <c r="AF102" s="3">
+      <c r="AG102" s="3">
         <v>-621200</v>
       </c>
-      <c r="AG102" s="3">
+      <c r="AH102" s="3">
         <v>2617600</v>
       </c>
     </row>

--- a/AAII_Financials/Quarterly/WF_QTR_FIN.xlsx
+++ b/AAII_Financials/Quarterly/WF_QTR_FIN.xlsx
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="200" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="203" uniqueCount="92">
   <si>
     <t>WF</t>
   </si>
@@ -656,133 +656,137 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet2"/>
-  <dimension ref="A5:AH102"/>
+  <dimension ref="A5:AI102"/>
   <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="5" style="1" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="26.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="69.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="16" style="1" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="17" style="1" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="16" style="1" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="17" style="1" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="16" style="1" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="17" style="1" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="16" style="1" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="17" style="1" bestFit="1" customWidth="1"/>
-    <col min="12" max="34" width="16" style="1" bestFit="1" customWidth="1"/>
-    <col min="35" max="16384" width="9.140625" style="1"/>
+    <col min="4" max="4" width="17" style="1" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="16" style="1" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="17" style="1" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="16" style="1" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="17" style="1" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="16" style="1" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="17" style="1" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="16" style="1" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="17" style="1" bestFit="1" customWidth="1"/>
+    <col min="13" max="35" width="16" style="1" bestFit="1" customWidth="1"/>
+    <col min="36" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
-    <row r="5" spans="1:34" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:35" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:34" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:35" x14ac:dyDescent="0.2">
       <c r="B6" s="1" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:34" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:35" x14ac:dyDescent="0.2">
       <c r="C7" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D7" s="2">
+        <v>45473</v>
+      </c>
+      <c r="E7" s="2">
         <v>45382</v>
       </c>
-      <c r="E7" s="2">
+      <c r="F7" s="2">
         <v>45291</v>
       </c>
-      <c r="F7" s="2">
+      <c r="G7" s="2">
         <v>45199</v>
       </c>
-      <c r="G7" s="2">
+      <c r="H7" s="2">
         <v>45107</v>
       </c>
-      <c r="H7" s="2">
+      <c r="I7" s="2">
         <v>45016</v>
       </c>
-      <c r="I7" s="2">
+      <c r="J7" s="2">
         <v>44926</v>
       </c>
-      <c r="J7" s="2">
+      <c r="K7" s="2">
         <v>44834</v>
       </c>
-      <c r="K7" s="2">
+      <c r="L7" s="2">
         <v>44742</v>
       </c>
-      <c r="L7" s="2">
+      <c r="M7" s="2">
         <v>44651</v>
       </c>
-      <c r="M7" s="2">
+      <c r="N7" s="2">
         <v>44561</v>
       </c>
-      <c r="N7" s="2">
+      <c r="O7" s="2">
         <v>44469</v>
       </c>
-      <c r="O7" s="2">
+      <c r="P7" s="2">
         <v>44377</v>
       </c>
-      <c r="P7" s="2">
+      <c r="Q7" s="2">
         <v>44286</v>
       </c>
-      <c r="Q7" s="2">
+      <c r="R7" s="2">
         <v>44196</v>
       </c>
-      <c r="R7" s="2">
+      <c r="S7" s="2">
         <v>44104</v>
       </c>
-      <c r="S7" s="2">
+      <c r="T7" s="2">
         <v>44012</v>
       </c>
-      <c r="T7" s="2">
+      <c r="U7" s="2">
         <v>43921</v>
       </c>
-      <c r="U7" s="2">
+      <c r="V7" s="2">
         <v>43830</v>
       </c>
-      <c r="V7" s="2">
+      <c r="W7" s="2">
         <v>43738</v>
       </c>
-      <c r="W7" s="2">
+      <c r="X7" s="2">
         <v>43646</v>
       </c>
-      <c r="X7" s="2">
+      <c r="Y7" s="2">
         <v>43555</v>
       </c>
-      <c r="Y7" s="2">
+      <c r="Z7" s="2">
         <v>43465</v>
       </c>
-      <c r="Z7" s="2">
+      <c r="AA7" s="2">
         <v>43373</v>
       </c>
-      <c r="AA7" s="2">
+      <c r="AB7" s="2">
         <v>43281</v>
       </c>
-      <c r="AB7" s="2">
+      <c r="AC7" s="2">
         <v>43190</v>
       </c>
-      <c r="AC7" s="2">
+      <c r="AD7" s="2">
         <v>43100</v>
       </c>
-      <c r="AD7" s="2">
+      <c r="AE7" s="2">
         <v>43008</v>
       </c>
-      <c r="AE7" s="2">
+      <c r="AF7" s="2">
         <v>42916</v>
       </c>
-      <c r="AF7" s="2">
+      <c r="AG7" s="2">
         <v>42825</v>
       </c>
-      <c r="AG7" s="2">
+      <c r="AH7" s="2">
         <v>42735</v>
       </c>
-      <c r="AH7" s="2">
+      <c r="AI7" s="2">
         <v>42643</v>
       </c>
     </row>
-    <row r="8" spans="1:34" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:35" x14ac:dyDescent="0.2">
       <c r="C8" s="1" t="s">
         <v>3</v>
       </c>
@@ -790,97 +794,100 @@
         <v>5</v>
       </c>
       <c r="E8" s="3">
-        <v>3959800</v>
+        <v>4102100</v>
       </c>
       <c r="F8" s="3">
-        <v>3824700</v>
+        <v>4068300</v>
       </c>
       <c r="G8" s="3">
-        <v>3685600</v>
+        <v>3929500</v>
       </c>
       <c r="H8" s="3">
-        <v>3598300</v>
+        <v>3786600</v>
       </c>
       <c r="I8" s="3">
-        <v>3369900</v>
+        <v>3696900</v>
       </c>
       <c r="J8" s="3">
+        <v>3462200</v>
+      </c>
+      <c r="K8" s="3">
         <v>2792200</v>
       </c>
-      <c r="K8" s="3">
+      <c r="L8" s="3">
         <v>2487200</v>
       </c>
-      <c r="L8" s="3">
+      <c r="M8" s="3">
         <v>2264400</v>
       </c>
-      <c r="M8" s="3">
+      <c r="N8" s="3">
         <v>2026000</v>
       </c>
-      <c r="N8" s="3">
+      <c r="O8" s="3">
         <v>1862200</v>
       </c>
-      <c r="O8" s="3">
+      <c r="P8" s="3">
         <v>1787500</v>
       </c>
-      <c r="P8" s="3">
+      <c r="Q8" s="3">
         <v>1722100</v>
       </c>
-      <c r="Q8" s="3">
+      <c r="R8" s="3">
         <v>1728200</v>
       </c>
-      <c r="R8" s="3">
+      <c r="S8" s="3">
         <v>1749800</v>
       </c>
-      <c r="S8" s="3">
+      <c r="T8" s="3">
         <v>1857400</v>
       </c>
-      <c r="T8" s="3">
+      <c r="U8" s="3">
         <v>2028100</v>
       </c>
-      <c r="U8" s="3">
+      <c r="V8" s="3">
         <v>2216400</v>
       </c>
-      <c r="V8" s="3">
+      <c r="W8" s="3">
         <v>2287800</v>
       </c>
-      <c r="W8" s="3">
+      <c r="X8" s="3">
         <v>2353100</v>
       </c>
-      <c r="X8" s="3">
+      <c r="Y8" s="3">
         <v>2369400</v>
       </c>
-      <c r="Y8" s="3">
+      <c r="Z8" s="3">
         <v>2154000</v>
       </c>
-      <c r="Z8" s="3">
+      <c r="AA8" s="3">
         <v>2006200</v>
       </c>
-      <c r="AA8" s="3">
+      <c r="AB8" s="3">
         <v>1989700</v>
       </c>
-      <c r="AB8" s="3">
+      <c r="AC8" s="3">
         <v>1910800</v>
       </c>
-      <c r="AC8" s="3">
+      <c r="AD8" s="3">
         <v>1912500</v>
       </c>
-      <c r="AD8" s="3">
+      <c r="AE8" s="3">
         <v>1925300</v>
       </c>
-      <c r="AE8" s="3">
+      <c r="AF8" s="3">
         <v>1853100</v>
       </c>
-      <c r="AF8" s="3">
+      <c r="AG8" s="3">
         <v>1833700</v>
       </c>
-      <c r="AG8" s="3">
+      <c r="AH8" s="3">
         <v>1898800</v>
       </c>
-      <c r="AH8" s="3">
+      <c r="AI8" s="3">
         <v>1898000</v>
       </c>
     </row>
-    <row r="9" spans="1:34" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:35" x14ac:dyDescent="0.2">
       <c r="C9" s="1" t="s">
         <v>4</v>
       </c>
@@ -977,8 +984,11 @@
       <c r="AH9" s="3" t="s">
         <v>5</v>
       </c>
-    </row>
-    <row r="10" spans="1:34" x14ac:dyDescent="0.2">
+      <c r="AI9" s="3" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="10" spans="1:35" x14ac:dyDescent="0.2">
       <c r="C10" s="1" t="s">
         <v>6</v>
       </c>
@@ -1075,8 +1085,11 @@
       <c r="AH10" s="3" t="s">
         <v>5</v>
       </c>
-    </row>
-    <row r="11" spans="1:34" x14ac:dyDescent="0.2">
+      <c r="AI10" s="3" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="11" spans="1:35" x14ac:dyDescent="0.2">
       <c r="C11" s="1" t="s">
         <v>7</v>
       </c>
@@ -1111,8 +1124,9 @@
       <c r="AF11" s="3"/>
       <c r="AG11" s="3"/>
       <c r="AH11" s="3"/>
-    </row>
-    <row r="12" spans="1:34" x14ac:dyDescent="0.2">
+      <c r="AI11" s="3"/>
+    </row>
+    <row r="12" spans="1:35" x14ac:dyDescent="0.2">
       <c r="C12" s="1" t="s">
         <v>8</v>
       </c>
@@ -1209,8 +1223,11 @@
       <c r="AH12" s="3" t="s">
         <v>5</v>
       </c>
-    </row>
-    <row r="13" spans="1:34" x14ac:dyDescent="0.2">
+      <c r="AI12" s="3" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="13" spans="1:35" x14ac:dyDescent="0.2">
       <c r="C13" s="1" t="s">
         <v>9</v>
       </c>
@@ -1307,8 +1324,11 @@
       <c r="AH13" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="14" spans="1:34" x14ac:dyDescent="0.2">
+      <c r="AI13" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="14" spans="1:35" x14ac:dyDescent="0.2">
       <c r="C14" s="1" t="s">
         <v>10</v>
       </c>
@@ -1405,106 +1425,112 @@
       <c r="AH14" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="15" spans="1:34" x14ac:dyDescent="0.2">
+      <c r="AI14" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="15" spans="1:35" x14ac:dyDescent="0.2">
       <c r="C15" s="1" t="s">
         <v>11</v>
       </c>
       <c r="D15" s="3">
+        <v>-103500</v>
+      </c>
+      <c r="E15" s="3">
+        <v>-100200</v>
+      </c>
+      <c r="F15" s="3">
+        <v>-98700</v>
+      </c>
+      <c r="G15" s="3">
+        <v>-88300</v>
+      </c>
+      <c r="H15" s="3">
         <v>-94800</v>
       </c>
-      <c r="E15" s="3">
+      <c r="I15" s="3">
+        <v>-99600</v>
+      </c>
+      <c r="J15" s="3">
+        <v>-101500</v>
+      </c>
+      <c r="K15" s="3">
+        <v>-92100</v>
+      </c>
+      <c r="L15" s="3">
+        <v>-100700</v>
+      </c>
+      <c r="M15" s="3">
+        <v>-101400</v>
+      </c>
+      <c r="N15" s="3">
+        <v>-98200</v>
+      </c>
+      <c r="O15" s="3">
+        <v>-97600</v>
+      </c>
+      <c r="P15" s="3">
+        <v>-97400</v>
+      </c>
+      <c r="Q15" s="3">
+        <v>-100600</v>
+      </c>
+      <c r="R15" s="3">
+        <v>-99400</v>
+      </c>
+      <c r="S15" s="3">
+        <v>-99600</v>
+      </c>
+      <c r="T15" s="3">
         <v>-96100</v>
       </c>
-      <c r="F15" s="3">
-        <v>-85900</v>
-      </c>
-      <c r="G15" s="3">
-        <v>-92200</v>
-      </c>
-      <c r="H15" s="3">
-        <v>-96900</v>
-      </c>
-      <c r="I15" s="3">
-        <v>-98800</v>
-      </c>
-      <c r="J15" s="3">
-        <v>-92100</v>
-      </c>
-      <c r="K15" s="3">
-        <v>-100700</v>
-      </c>
-      <c r="L15" s="3">
-        <v>-101400</v>
-      </c>
-      <c r="M15" s="3">
-        <v>-98200</v>
-      </c>
-      <c r="N15" s="3">
-        <v>-97600</v>
-      </c>
-      <c r="O15" s="3">
-        <v>-97400</v>
-      </c>
-      <c r="P15" s="3">
-        <v>-100600</v>
-      </c>
-      <c r="Q15" s="3">
-        <v>-99400</v>
-      </c>
-      <c r="R15" s="3">
-        <v>-99600</v>
-      </c>
-      <c r="S15" s="3">
-        <v>-96100</v>
-      </c>
-      <c r="T15" s="3">
+      <c r="U15" s="3">
         <v>-109500</v>
       </c>
-      <c r="U15" s="3">
+      <c r="V15" s="3">
         <v>-115200</v>
       </c>
-      <c r="V15" s="3">
+      <c r="W15" s="3">
         <v>-112100</v>
       </c>
-      <c r="W15" s="3">
+      <c r="X15" s="3">
         <v>-104100</v>
       </c>
-      <c r="X15" s="3">
+      <c r="Y15" s="3">
         <v>-88900</v>
       </c>
-      <c r="Y15" s="3">
+      <c r="Z15" s="3">
         <v>-50500</v>
       </c>
-      <c r="Z15" s="3">
+      <c r="AA15" s="3">
         <v>-47800</v>
       </c>
-      <c r="AA15" s="3">
+      <c r="AB15" s="3">
         <v>-44700</v>
       </c>
-      <c r="AB15" s="3">
+      <c r="AC15" s="3">
         <v>-40700</v>
       </c>
-      <c r="AC15" s="3">
+      <c r="AD15" s="3">
         <v>-39500</v>
       </c>
-      <c r="AD15" s="3">
+      <c r="AE15" s="3">
         <v>-40300</v>
       </c>
-      <c r="AE15" s="3">
+      <c r="AF15" s="3">
         <v>-40800</v>
       </c>
-      <c r="AF15" s="3">
+      <c r="AG15" s="3">
         <v>-44500</v>
       </c>
-      <c r="AG15" s="3">
+      <c r="AH15" s="3">
         <v>-54800</v>
       </c>
-      <c r="AH15" s="3">
+      <c r="AI15" s="3">
         <v>-53700</v>
       </c>
     </row>
-    <row r="16" spans="1:34" x14ac:dyDescent="0.2">
+    <row r="16" spans="1:35" x14ac:dyDescent="0.2">
       <c r="D16" s="3"/>
       <c r="E16" s="3"/>
       <c r="F16" s="3"/>
@@ -1536,8 +1562,9 @@
       <c r="AF16" s="3"/>
       <c r="AG16" s="3"/>
       <c r="AH16" s="3"/>
-    </row>
-    <row r="17" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI16" s="3"/>
+    </row>
+    <row r="17" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C17" s="1" t="s">
         <v>12</v>
       </c>
@@ -1545,97 +1572,100 @@
         <v>5</v>
       </c>
       <c r="E17" s="3">
-        <v>2991600</v>
+        <v>2728400</v>
       </c>
       <c r="F17" s="3">
-        <v>2418600</v>
+        <v>3073600</v>
       </c>
       <c r="G17" s="3">
-        <v>2489900</v>
+        <v>2484800</v>
       </c>
       <c r="H17" s="3">
-        <v>2169500</v>
+        <v>2558100</v>
       </c>
       <c r="I17" s="3">
-        <v>1847300</v>
+        <v>2228900</v>
       </c>
       <c r="J17" s="3">
+        <v>1897900</v>
+      </c>
+      <c r="K17" s="3">
         <v>1245200</v>
       </c>
-      <c r="K17" s="3">
+      <c r="L17" s="3">
         <v>1121400</v>
       </c>
-      <c r="L17" s="3">
+      <c r="M17" s="3">
         <v>861300</v>
       </c>
-      <c r="M17" s="3">
+      <c r="N17" s="3">
         <v>772200</v>
       </c>
-      <c r="N17" s="3">
+      <c r="O17" s="3">
         <v>616800</v>
       </c>
-      <c r="O17" s="3">
+      <c r="P17" s="3">
         <v>573600</v>
       </c>
-      <c r="P17" s="3">
+      <c r="Q17" s="3">
         <v>625700</v>
       </c>
-      <c r="Q17" s="3">
+      <c r="R17" s="3">
         <v>727900</v>
       </c>
-      <c r="R17" s="3">
+      <c r="S17" s="3">
         <v>721100</v>
       </c>
-      <c r="S17" s="3">
+      <c r="T17" s="3">
         <v>966200</v>
       </c>
-      <c r="T17" s="3">
+      <c r="U17" s="3">
         <v>926000</v>
       </c>
-      <c r="U17" s="3">
+      <c r="V17" s="3">
         <v>1019500</v>
       </c>
-      <c r="V17" s="3">
+      <c r="W17" s="3">
         <v>1190700</v>
       </c>
-      <c r="W17" s="3">
+      <c r="X17" s="3">
         <v>1111900</v>
       </c>
-      <c r="X17" s="3">
+      <c r="Y17" s="3">
         <v>1098300</v>
       </c>
-      <c r="Y17" s="3">
+      <c r="Z17" s="3">
         <v>1157200</v>
       </c>
-      <c r="Z17" s="3">
+      <c r="AA17" s="3">
         <v>918800</v>
       </c>
-      <c r="AA17" s="3">
+      <c r="AB17" s="3">
         <v>752200</v>
       </c>
-      <c r="AB17" s="3">
+      <c r="AC17" s="3">
         <v>877900</v>
       </c>
-      <c r="AC17" s="3">
+      <c r="AD17" s="3">
         <v>1026000</v>
       </c>
-      <c r="AD17" s="3">
+      <c r="AE17" s="3">
         <v>926800</v>
       </c>
-      <c r="AE17" s="3">
+      <c r="AF17" s="3">
         <v>906500</v>
       </c>
-      <c r="AF17" s="3">
+      <c r="AG17" s="3">
         <v>830000</v>
       </c>
-      <c r="AG17" s="3">
+      <c r="AH17" s="3">
         <v>903100</v>
       </c>
-      <c r="AH17" s="3">
+      <c r="AI17" s="3">
         <v>963600</v>
       </c>
     </row>
-    <row r="18" spans="3:34" x14ac:dyDescent="0.2">
+    <row r="18" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C18" s="1" t="s">
         <v>13</v>
       </c>
@@ -1643,97 +1673,100 @@
         <v>5</v>
       </c>
       <c r="E18" s="3">
-        <v>968200</v>
+        <v>1373800</v>
       </c>
       <c r="F18" s="3">
-        <v>1406100</v>
+        <v>994700</v>
       </c>
       <c r="G18" s="3">
-        <v>1195700</v>
+        <v>1444600</v>
       </c>
       <c r="H18" s="3">
-        <v>1428800</v>
+        <v>1228400</v>
       </c>
       <c r="I18" s="3">
-        <v>1522600</v>
+        <v>1467900</v>
       </c>
       <c r="J18" s="3">
+        <v>1564300</v>
+      </c>
+      <c r="K18" s="3">
         <v>1547000</v>
       </c>
-      <c r="K18" s="3">
+      <c r="L18" s="3">
         <v>1365800</v>
       </c>
-      <c r="L18" s="3">
+      <c r="M18" s="3">
         <v>1403000</v>
       </c>
-      <c r="M18" s="3">
+      <c r="N18" s="3">
         <v>1253800</v>
       </c>
-      <c r="N18" s="3">
+      <c r="O18" s="3">
         <v>1245400</v>
       </c>
-      <c r="O18" s="3">
+      <c r="P18" s="3">
         <v>1213900</v>
       </c>
-      <c r="P18" s="3">
+      <c r="Q18" s="3">
         <v>1096400</v>
       </c>
-      <c r="Q18" s="3">
+      <c r="R18" s="3">
         <v>1000300</v>
       </c>
-      <c r="R18" s="3">
+      <c r="S18" s="3">
         <v>1028700</v>
       </c>
-      <c r="S18" s="3">
+      <c r="T18" s="3">
         <v>891200</v>
       </c>
-      <c r="T18" s="3">
+      <c r="U18" s="3">
         <v>1102100</v>
       </c>
-      <c r="U18" s="3">
+      <c r="V18" s="3">
         <v>1196900</v>
       </c>
-      <c r="V18" s="3">
+      <c r="W18" s="3">
         <v>1097100</v>
       </c>
-      <c r="W18" s="3">
+      <c r="X18" s="3">
         <v>1241200</v>
       </c>
-      <c r="X18" s="3">
+      <c r="Y18" s="3">
         <v>1271100</v>
       </c>
-      <c r="Y18" s="3">
+      <c r="Z18" s="3">
         <v>996800</v>
       </c>
-      <c r="Z18" s="3">
+      <c r="AA18" s="3">
         <v>1087400</v>
       </c>
-      <c r="AA18" s="3">
+      <c r="AB18" s="3">
         <v>1237400</v>
       </c>
-      <c r="AB18" s="3">
+      <c r="AC18" s="3">
         <v>1032900</v>
       </c>
-      <c r="AC18" s="3">
+      <c r="AD18" s="3">
         <v>886500</v>
       </c>
-      <c r="AD18" s="3">
+      <c r="AE18" s="3">
         <v>998500</v>
       </c>
-      <c r="AE18" s="3">
+      <c r="AF18" s="3">
         <v>946600</v>
       </c>
-      <c r="AF18" s="3">
+      <c r="AG18" s="3">
         <v>1003700</v>
       </c>
-      <c r="AG18" s="3">
+      <c r="AH18" s="3">
         <v>995700</v>
       </c>
-      <c r="AH18" s="3">
+      <c r="AI18" s="3">
         <v>934400</v>
       </c>
     </row>
-    <row r="19" spans="3:34" x14ac:dyDescent="0.2">
+    <row r="19" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C19" s="1" t="s">
         <v>14</v>
       </c>
@@ -1768,8 +1801,9 @@
       <c r="AF19" s="3"/>
       <c r="AG19" s="3"/>
       <c r="AH19" s="3"/>
-    </row>
-    <row r="20" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI19" s="3"/>
+    </row>
+    <row r="20" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C20" s="1" t="s">
         <v>15</v>
       </c>
@@ -1777,97 +1811,100 @@
         <v>5</v>
       </c>
       <c r="E20" s="3">
-        <v>-879000</v>
+        <v>-515800</v>
       </c>
       <c r="F20" s="3">
-        <v>-496000</v>
+        <v>-903100</v>
       </c>
       <c r="G20" s="3">
-        <v>-554600</v>
+        <v>-509600</v>
       </c>
       <c r="H20" s="3">
-        <v>-501500</v>
+        <v>-569800</v>
       </c>
       <c r="I20" s="3">
-        <v>-990200</v>
+        <v>-515200</v>
       </c>
       <c r="J20" s="3">
+        <v>-1017300</v>
+      </c>
+      <c r="K20" s="3">
         <v>-606600</v>
       </c>
-      <c r="K20" s="3">
+      <c r="L20" s="3">
         <v>-375600</v>
       </c>
-      <c r="L20" s="3">
+      <c r="M20" s="3">
         <v>-505900</v>
       </c>
-      <c r="M20" s="3">
+      <c r="N20" s="3">
         <v>-806400</v>
       </c>
-      <c r="N20" s="3">
+      <c r="O20" s="3">
         <v>-394200</v>
       </c>
-      <c r="O20" s="3">
+      <c r="P20" s="3">
         <v>-406900</v>
       </c>
-      <c r="P20" s="3">
+      <c r="Q20" s="3">
         <v>-399500</v>
       </c>
-      <c r="Q20" s="3">
+      <c r="R20" s="3">
         <v>-784600</v>
       </c>
-      <c r="R20" s="3">
+      <c r="S20" s="3">
         <v>-508200</v>
       </c>
-      <c r="S20" s="3">
+      <c r="T20" s="3">
         <v>-674600</v>
       </c>
-      <c r="T20" s="3">
+      <c r="U20" s="3">
         <v>-492400</v>
       </c>
-      <c r="U20" s="3">
+      <c r="V20" s="3">
         <v>-920900</v>
       </c>
-      <c r="V20" s="3">
+      <c r="W20" s="3">
         <v>-527400</v>
       </c>
-      <c r="W20" s="3">
+      <c r="X20" s="3">
         <v>-447200</v>
       </c>
-      <c r="X20" s="3">
+      <c r="Y20" s="3">
         <v>-519600</v>
       </c>
-      <c r="Y20" s="3">
+      <c r="Z20" s="3">
         <v>-847700</v>
       </c>
-      <c r="Z20" s="3">
+      <c r="AA20" s="3">
         <v>-418500</v>
       </c>
-      <c r="AA20" s="3">
+      <c r="AB20" s="3">
         <v>-401200</v>
       </c>
-      <c r="AB20" s="3">
+      <c r="AC20" s="3">
         <v>-355800</v>
       </c>
-      <c r="AC20" s="3">
+      <c r="AD20" s="3">
         <v>-756300</v>
       </c>
-      <c r="AD20" s="3">
+      <c r="AE20" s="3">
         <v>-671500</v>
       </c>
-      <c r="AE20" s="3">
+      <c r="AF20" s="3">
         <v>-417500</v>
       </c>
-      <c r="AF20" s="3">
+      <c r="AG20" s="3">
         <v>-274500</v>
       </c>
-      <c r="AG20" s="3">
+      <c r="AH20" s="3">
         <v>-821100</v>
       </c>
-      <c r="AH20" s="3">
+      <c r="AI20" s="3">
         <v>-531000</v>
       </c>
     </row>
-    <row r="21" spans="3:34" x14ac:dyDescent="0.2">
+    <row r="21" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C21" s="1" t="s">
         <v>16</v>
       </c>
@@ -1875,97 +1912,100 @@
         <v>5</v>
       </c>
       <c r="E21" s="3">
-        <v>281800</v>
+        <v>1065000</v>
       </c>
       <c r="F21" s="3">
-        <v>1085500</v>
+        <v>289500</v>
       </c>
       <c r="G21" s="3">
-        <v>818500</v>
+        <v>1115300</v>
       </c>
       <c r="H21" s="3">
-        <v>1106900</v>
+        <v>840900</v>
       </c>
       <c r="I21" s="3">
-        <v>712600</v>
+        <v>1137200</v>
       </c>
       <c r="J21" s="3">
+        <v>732200</v>
+      </c>
+      <c r="K21" s="3">
         <v>1110000</v>
       </c>
-      <c r="K21" s="3">
+      <c r="L21" s="3">
         <v>1165700</v>
       </c>
-      <c r="L21" s="3">
+      <c r="M21" s="3">
         <v>1065700</v>
       </c>
-      <c r="M21" s="3">
+      <c r="N21" s="3">
         <v>603300</v>
       </c>
-      <c r="N21" s="3">
+      <c r="O21" s="3">
         <v>1000500</v>
       </c>
-      <c r="O21" s="3">
+      <c r="P21" s="3">
         <v>991500</v>
       </c>
-      <c r="P21" s="3">
+      <c r="Q21" s="3">
         <v>799800</v>
       </c>
-      <c r="Q21" s="3">
+      <c r="R21" s="3">
         <v>316900</v>
       </c>
-      <c r="R21" s="3">
+      <c r="S21" s="3">
         <v>622000</v>
       </c>
-      <c r="S21" s="3">
+      <c r="T21" s="3">
         <v>315300</v>
       </c>
-      <c r="T21" s="3">
+      <c r="U21" s="3">
         <v>721900</v>
       </c>
-      <c r="U21" s="3">
+      <c r="V21" s="3">
         <v>396300</v>
       </c>
-      <c r="V21" s="3">
+      <c r="W21" s="3">
         <v>686600</v>
       </c>
-      <c r="W21" s="3">
+      <c r="X21" s="3">
         <v>902900</v>
       </c>
-      <c r="X21" s="3">
+      <c r="Y21" s="3">
         <v>845100</v>
       </c>
-      <c r="Y21" s="3">
+      <c r="Z21" s="3">
         <v>210800</v>
       </c>
-      <c r="Z21" s="3">
+      <c r="AA21" s="3">
         <v>727400</v>
       </c>
-      <c r="AA21" s="3">
+      <c r="AB21" s="3">
         <v>892200</v>
       </c>
-      <c r="AB21" s="3">
+      <c r="AC21" s="3">
         <v>727700</v>
       </c>
-      <c r="AC21" s="3">
+      <c r="AD21" s="3">
         <v>180100</v>
       </c>
-      <c r="AD21" s="3">
+      <c r="AE21" s="3">
         <v>377800</v>
       </c>
-      <c r="AE21" s="3">
+      <c r="AF21" s="3">
         <v>580800</v>
       </c>
-      <c r="AF21" s="3">
+      <c r="AG21" s="3">
         <v>784400</v>
       </c>
-      <c r="AG21" s="3">
+      <c r="AH21" s="3">
         <v>229400</v>
       </c>
-      <c r="AH21" s="3">
+      <c r="AI21" s="3">
         <v>457200</v>
       </c>
     </row>
-    <row r="22" spans="3:34" x14ac:dyDescent="0.2">
+    <row r="22" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C22" s="1" t="s">
         <v>17</v>
       </c>
@@ -2062,204 +2102,213 @@
       <c r="AH22" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="23" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI22" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="23" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C23" s="1" t="s">
         <v>18</v>
       </c>
       <c r="D23" s="3">
-        <v>835100</v>
+        <v>935200</v>
       </c>
       <c r="E23" s="3">
-        <v>89200</v>
+        <v>858000</v>
       </c>
       <c r="F23" s="3">
-        <v>910100</v>
+        <v>91600</v>
       </c>
       <c r="G23" s="3">
-        <v>641100</v>
+        <v>935100</v>
       </c>
       <c r="H23" s="3">
-        <v>927300</v>
+        <v>658700</v>
       </c>
       <c r="I23" s="3">
-        <v>532400</v>
+        <v>952700</v>
       </c>
       <c r="J23" s="3">
+        <v>546900</v>
+      </c>
+      <c r="K23" s="3">
         <v>940400</v>
       </c>
-      <c r="K23" s="3">
+      <c r="L23" s="3">
         <v>990200</v>
       </c>
-      <c r="L23" s="3">
+      <c r="M23" s="3">
         <v>897100</v>
       </c>
-      <c r="M23" s="3">
+      <c r="N23" s="3">
         <v>447400</v>
       </c>
-      <c r="N23" s="3">
+      <c r="O23" s="3">
         <v>851200</v>
       </c>
-      <c r="O23" s="3">
+      <c r="P23" s="3">
         <v>807000</v>
       </c>
-      <c r="P23" s="3">
+      <c r="Q23" s="3">
         <v>696900</v>
       </c>
-      <c r="Q23" s="3">
+      <c r="R23" s="3">
         <v>215700</v>
       </c>
-      <c r="R23" s="3">
+      <c r="S23" s="3">
         <v>520500</v>
       </c>
-      <c r="S23" s="3">
+      <c r="T23" s="3">
         <v>216600</v>
       </c>
-      <c r="T23" s="3">
+      <c r="U23" s="3">
         <v>609600</v>
       </c>
-      <c r="U23" s="3">
+      <c r="V23" s="3">
         <v>276000</v>
       </c>
-      <c r="V23" s="3">
+      <c r="W23" s="3">
         <v>569700</v>
       </c>
-      <c r="W23" s="3">
+      <c r="X23" s="3">
         <v>794000</v>
       </c>
-      <c r="X23" s="3">
+      <c r="Y23" s="3">
         <v>751500</v>
       </c>
-      <c r="Y23" s="3">
+      <c r="Z23" s="3">
         <v>149100</v>
       </c>
-      <c r="Z23" s="3">
+      <c r="AA23" s="3">
         <v>668900</v>
       </c>
-      <c r="AA23" s="3">
+      <c r="AB23" s="3">
         <v>836200</v>
       </c>
-      <c r="AB23" s="3">
+      <c r="AC23" s="3">
         <v>677100</v>
       </c>
-      <c r="AC23" s="3">
+      <c r="AD23" s="3">
         <v>130200</v>
       </c>
-      <c r="AD23" s="3">
+      <c r="AE23" s="3">
         <v>327000</v>
       </c>
-      <c r="AE23" s="3">
+      <c r="AF23" s="3">
         <v>529200</v>
       </c>
-      <c r="AF23" s="3">
+      <c r="AG23" s="3">
         <v>729200</v>
       </c>
-      <c r="AG23" s="3">
+      <c r="AH23" s="3">
         <v>174600</v>
       </c>
-      <c r="AH23" s="3">
+      <c r="AI23" s="3">
         <v>403400</v>
       </c>
     </row>
-    <row r="24" spans="3:34" x14ac:dyDescent="0.2">
+    <row r="24" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C24" s="1" t="s">
         <v>19</v>
       </c>
       <c r="D24" s="3">
-        <v>222700</v>
+        <v>214000</v>
       </c>
       <c r="E24" s="3">
-        <v>19800</v>
+        <v>228800</v>
       </c>
       <c r="F24" s="3">
-        <v>239900</v>
+        <v>20400</v>
       </c>
       <c r="G24" s="3">
-        <v>154000</v>
+        <v>246500</v>
       </c>
       <c r="H24" s="3">
-        <v>236300</v>
+        <v>158300</v>
       </c>
       <c r="I24" s="3">
-        <v>144500</v>
+        <v>242800</v>
       </c>
       <c r="J24" s="3">
+        <v>148500</v>
+      </c>
+      <c r="K24" s="3">
         <v>259000</v>
       </c>
-      <c r="K24" s="3">
+      <c r="L24" s="3">
         <v>240200</v>
       </c>
-      <c r="L24" s="3">
+      <c r="M24" s="3">
         <v>225300</v>
       </c>
-      <c r="M24" s="3">
+      <c r="N24" s="3">
         <v>113100</v>
       </c>
-      <c r="N24" s="3">
+      <c r="O24" s="3">
         <v>232900</v>
       </c>
-      <c r="O24" s="3">
+      <c r="P24" s="3">
         <v>193200</v>
       </c>
-      <c r="P24" s="3">
+      <c r="Q24" s="3">
         <v>164900</v>
       </c>
-      <c r="Q24" s="3">
+      <c r="R24" s="3">
         <v>53200</v>
       </c>
-      <c r="R24" s="3">
+      <c r="S24" s="3">
         <v>118800</v>
       </c>
-      <c r="S24" s="3">
+      <c r="T24" s="3">
         <v>50000</v>
       </c>
-      <c r="T24" s="3">
+      <c r="U24" s="3">
         <v>157800</v>
       </c>
-      <c r="U24" s="3">
+      <c r="V24" s="3">
         <v>79200</v>
       </c>
-      <c r="V24" s="3">
+      <c r="W24" s="3">
         <v>115700</v>
       </c>
-      <c r="W24" s="3">
+      <c r="X24" s="3">
         <v>215500</v>
       </c>
-      <c r="X24" s="3">
+      <c r="Y24" s="3">
         <v>192300</v>
       </c>
-      <c r="Y24" s="3">
+      <c r="Z24" s="3">
         <v>39300</v>
       </c>
-      <c r="Z24" s="3">
+      <c r="AA24" s="3">
         <v>179200</v>
       </c>
-      <c r="AA24" s="3">
+      <c r="AB24" s="3">
         <v>229900</v>
       </c>
-      <c r="AB24" s="3">
+      <c r="AC24" s="3">
         <v>177700</v>
       </c>
-      <c r="AC24" s="3">
+      <c r="AD24" s="3">
         <v>9000</v>
       </c>
-      <c r="AD24" s="3">
+      <c r="AE24" s="3">
         <v>77600</v>
       </c>
-      <c r="AE24" s="3">
+      <c r="AF24" s="3">
         <v>118800</v>
       </c>
-      <c r="AF24" s="3">
+      <c r="AG24" s="3">
         <v>163600</v>
       </c>
-      <c r="AG24" s="3">
+      <c r="AH24" s="3">
         <v>30300</v>
       </c>
-      <c r="AH24" s="3">
+      <c r="AI24" s="3">
         <v>80000</v>
       </c>
     </row>
-    <row r="25" spans="3:34" x14ac:dyDescent="0.2">
+    <row r="25" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C25" s="1" t="s">
         <v>20</v>
       </c>
@@ -2356,8 +2405,11 @@
       <c r="AH25" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="26" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI25" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="26" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C26" s="1" t="s">
         <v>21</v>
       </c>
@@ -2365,97 +2417,100 @@
         <v>5</v>
       </c>
       <c r="E26" s="3">
-        <v>69300</v>
+        <v>629200</v>
       </c>
       <c r="F26" s="3">
-        <v>670200</v>
+        <v>71200</v>
       </c>
       <c r="G26" s="3">
-        <v>487000</v>
+        <v>688600</v>
       </c>
       <c r="H26" s="3">
-        <v>691000</v>
+        <v>500400</v>
       </c>
       <c r="I26" s="3">
-        <v>387800</v>
+        <v>710000</v>
       </c>
       <c r="J26" s="3">
+        <v>398500</v>
+      </c>
+      <c r="K26" s="3">
         <v>681400</v>
       </c>
-      <c r="K26" s="3">
+      <c r="L26" s="3">
         <v>750000</v>
       </c>
-      <c r="L26" s="3">
+      <c r="M26" s="3">
         <v>671800</v>
       </c>
-      <c r="M26" s="3">
+      <c r="N26" s="3">
         <v>334300</v>
       </c>
-      <c r="N26" s="3">
+      <c r="O26" s="3">
         <v>618300</v>
       </c>
-      <c r="O26" s="3">
+      <c r="P26" s="3">
         <v>613800</v>
       </c>
-      <c r="P26" s="3">
+      <c r="Q26" s="3">
         <v>532000</v>
       </c>
-      <c r="Q26" s="3">
+      <c r="R26" s="3">
         <v>162400</v>
       </c>
-      <c r="R26" s="3">
+      <c r="S26" s="3">
         <v>401700</v>
       </c>
-      <c r="S26" s="3">
+      <c r="T26" s="3">
         <v>166500</v>
       </c>
-      <c r="T26" s="3">
+      <c r="U26" s="3">
         <v>451800</v>
       </c>
-      <c r="U26" s="3">
+      <c r="V26" s="3">
         <v>196800</v>
       </c>
-      <c r="V26" s="3">
+      <c r="W26" s="3">
         <v>454000</v>
       </c>
-      <c r="W26" s="3">
+      <c r="X26" s="3">
         <v>578500</v>
       </c>
-      <c r="X26" s="3">
+      <c r="Y26" s="3">
         <v>559200</v>
       </c>
-      <c r="Y26" s="3">
+      <c r="Z26" s="3">
         <v>109900</v>
       </c>
-      <c r="Z26" s="3">
+      <c r="AA26" s="3">
         <v>489700</v>
       </c>
-      <c r="AA26" s="3">
+      <c r="AB26" s="3">
         <v>606300</v>
       </c>
-      <c r="AB26" s="3">
+      <c r="AC26" s="3">
         <v>499400</v>
       </c>
-      <c r="AC26" s="3">
+      <c r="AD26" s="3">
         <v>121100</v>
       </c>
-      <c r="AD26" s="3">
+      <c r="AE26" s="3">
         <v>249400</v>
       </c>
-      <c r="AE26" s="3">
+      <c r="AF26" s="3">
         <v>410300</v>
       </c>
-      <c r="AF26" s="3">
+      <c r="AG26" s="3">
         <v>565600</v>
       </c>
-      <c r="AG26" s="3">
+      <c r="AH26" s="3">
         <v>144300</v>
       </c>
-      <c r="AH26" s="3">
+      <c r="AI26" s="3">
         <v>323500</v>
       </c>
     </row>
-    <row r="27" spans="3:34" x14ac:dyDescent="0.2">
+    <row r="27" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C27" s="1" t="s">
         <v>22</v>
       </c>
@@ -2463,97 +2518,100 @@
         <v>5</v>
       </c>
       <c r="E27" s="3">
-        <v>24000</v>
+        <v>591600</v>
       </c>
       <c r="F27" s="3">
-        <v>632600</v>
+        <v>24600</v>
       </c>
       <c r="G27" s="3">
-        <v>432500</v>
+        <v>649900</v>
       </c>
       <c r="H27" s="3">
-        <v>644800</v>
+        <v>444300</v>
       </c>
       <c r="I27" s="3">
-        <v>329800</v>
+        <v>662500</v>
       </c>
       <c r="J27" s="3">
+        <v>338800</v>
+      </c>
+      <c r="K27" s="3">
         <v>640600</v>
       </c>
-      <c r="K27" s="3">
+      <c r="L27" s="3">
         <v>684400</v>
       </c>
-      <c r="L27" s="3">
+      <c r="M27" s="3">
         <v>631400</v>
       </c>
-      <c r="M27" s="3">
+      <c r="N27" s="3">
         <v>279500</v>
       </c>
-      <c r="N27" s="3">
+      <c r="O27" s="3">
         <v>570700</v>
       </c>
-      <c r="O27" s="3">
+      <c r="P27" s="3">
         <v>552600</v>
       </c>
-      <c r="P27" s="3">
+      <c r="Q27" s="3">
         <v>482000</v>
       </c>
-      <c r="Q27" s="3">
+      <c r="R27" s="3">
         <v>112600</v>
       </c>
-      <c r="R27" s="3">
+      <c r="S27" s="3">
         <v>358800</v>
       </c>
-      <c r="S27" s="3">
+      <c r="T27" s="3">
         <v>100500</v>
       </c>
-      <c r="T27" s="3">
+      <c r="U27" s="3">
         <v>412900</v>
       </c>
-      <c r="U27" s="3">
+      <c r="V27" s="3">
         <v>174900</v>
       </c>
-      <c r="V27" s="3">
+      <c r="W27" s="3">
         <v>410100</v>
       </c>
-      <c r="W27" s="3">
+      <c r="X27" s="3">
         <v>537700</v>
       </c>
-      <c r="X27" s="3">
+      <c r="Y27" s="3">
         <v>517500</v>
       </c>
-      <c r="Y27" s="3">
+      <c r="Z27" s="3">
         <v>76800</v>
       </c>
-      <c r="Z27" s="3">
+      <c r="AA27" s="3">
         <v>453900</v>
       </c>
-      <c r="AA27" s="3">
+      <c r="AB27" s="3">
         <v>569900</v>
       </c>
-      <c r="AB27" s="3">
+      <c r="AC27" s="3">
         <v>463600</v>
       </c>
-      <c r="AC27" s="3">
+      <c r="AD27" s="3">
         <v>84900</v>
       </c>
-      <c r="AD27" s="3">
+      <c r="AE27" s="3">
         <v>212100</v>
       </c>
-      <c r="AE27" s="3">
+      <c r="AF27" s="3">
         <v>369000</v>
       </c>
-      <c r="AF27" s="3">
+      <c r="AG27" s="3">
         <v>517600</v>
       </c>
-      <c r="AG27" s="3">
+      <c r="AH27" s="3">
         <v>88500</v>
       </c>
-      <c r="AH27" s="3">
+      <c r="AI27" s="3">
         <v>275700</v>
       </c>
     </row>
-    <row r="28" spans="3:34" x14ac:dyDescent="0.2">
+    <row r="28" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C28" s="1" t="s">
         <v>23</v>
       </c>
@@ -2650,8 +2708,11 @@
       <c r="AH28" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="29" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI28" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="29" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C29" s="1" t="s">
         <v>24</v>
       </c>
@@ -2748,8 +2809,11 @@
       <c r="AH29" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="30" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI29" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="30" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C30" s="1" t="s">
         <v>25</v>
       </c>
@@ -2846,8 +2910,11 @@
       <c r="AH30" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="31" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI30" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="31" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C31" s="1" t="s">
         <v>26</v>
       </c>
@@ -2944,8 +3011,11 @@
       <c r="AH31" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="32" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI31" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="32" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C32" s="1" t="s">
         <v>27</v>
       </c>
@@ -2953,97 +3023,100 @@
         <v>5</v>
       </c>
       <c r="E32" s="3">
-        <v>879000</v>
+        <v>515800</v>
       </c>
       <c r="F32" s="3">
-        <v>496000</v>
+        <v>903100</v>
       </c>
       <c r="G32" s="3">
-        <v>554600</v>
+        <v>509600</v>
       </c>
       <c r="H32" s="3">
-        <v>501500</v>
+        <v>569800</v>
       </c>
       <c r="I32" s="3">
-        <v>990200</v>
+        <v>515200</v>
       </c>
       <c r="J32" s="3">
+        <v>1017300</v>
+      </c>
+      <c r="K32" s="3">
         <v>606600</v>
       </c>
-      <c r="K32" s="3">
+      <c r="L32" s="3">
         <v>375600</v>
       </c>
-      <c r="L32" s="3">
+      <c r="M32" s="3">
         <v>505900</v>
       </c>
-      <c r="M32" s="3">
+      <c r="N32" s="3">
         <v>806400</v>
       </c>
-      <c r="N32" s="3">
+      <c r="O32" s="3">
         <v>394200</v>
       </c>
-      <c r="O32" s="3">
+      <c r="P32" s="3">
         <v>406900</v>
       </c>
-      <c r="P32" s="3">
+      <c r="Q32" s="3">
         <v>399500</v>
       </c>
-      <c r="Q32" s="3">
+      <c r="R32" s="3">
         <v>784600</v>
       </c>
-      <c r="R32" s="3">
+      <c r="S32" s="3">
         <v>508200</v>
       </c>
-      <c r="S32" s="3">
+      <c r="T32" s="3">
         <v>674600</v>
       </c>
-      <c r="T32" s="3">
+      <c r="U32" s="3">
         <v>492400</v>
       </c>
-      <c r="U32" s="3">
+      <c r="V32" s="3">
         <v>920900</v>
       </c>
-      <c r="V32" s="3">
+      <c r="W32" s="3">
         <v>527400</v>
       </c>
-      <c r="W32" s="3">
+      <c r="X32" s="3">
         <v>447200</v>
       </c>
-      <c r="X32" s="3">
+      <c r="Y32" s="3">
         <v>519600</v>
       </c>
-      <c r="Y32" s="3">
+      <c r="Z32" s="3">
         <v>847700</v>
       </c>
-      <c r="Z32" s="3">
+      <c r="AA32" s="3">
         <v>418500</v>
       </c>
-      <c r="AA32" s="3">
+      <c r="AB32" s="3">
         <v>401200</v>
       </c>
-      <c r="AB32" s="3">
+      <c r="AC32" s="3">
         <v>355800</v>
       </c>
-      <c r="AC32" s="3">
+      <c r="AD32" s="3">
         <v>756300</v>
       </c>
-      <c r="AD32" s="3">
+      <c r="AE32" s="3">
         <v>671500</v>
       </c>
-      <c r="AE32" s="3">
+      <c r="AF32" s="3">
         <v>417500</v>
       </c>
-      <c r="AF32" s="3">
+      <c r="AG32" s="3">
         <v>274500</v>
       </c>
-      <c r="AG32" s="3">
+      <c r="AH32" s="3">
         <v>821100</v>
       </c>
-      <c r="AH32" s="3">
+      <c r="AI32" s="3">
         <v>531000</v>
       </c>
     </row>
-    <row r="33" spans="2:34" x14ac:dyDescent="0.2">
+    <row r="33" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C33" s="1" t="s">
         <v>28</v>
       </c>
@@ -3051,97 +3124,100 @@
         <v>5</v>
       </c>
       <c r="E33" s="3">
-        <v>24000</v>
+        <v>591600</v>
       </c>
       <c r="F33" s="3">
-        <v>632600</v>
+        <v>24600</v>
       </c>
       <c r="G33" s="3">
-        <v>432500</v>
+        <v>649900</v>
       </c>
       <c r="H33" s="3">
-        <v>644800</v>
+        <v>444300</v>
       </c>
       <c r="I33" s="3">
-        <v>329800</v>
+        <v>662500</v>
       </c>
       <c r="J33" s="3">
+        <v>338800</v>
+      </c>
+      <c r="K33" s="3">
         <v>640600</v>
       </c>
-      <c r="K33" s="3">
+      <c r="L33" s="3">
         <v>684400</v>
       </c>
-      <c r="L33" s="3">
+      <c r="M33" s="3">
         <v>631400</v>
       </c>
-      <c r="M33" s="3">
+      <c r="N33" s="3">
         <v>279500</v>
       </c>
-      <c r="N33" s="3">
+      <c r="O33" s="3">
         <v>570700</v>
       </c>
-      <c r="O33" s="3">
+      <c r="P33" s="3">
         <v>552600</v>
       </c>
-      <c r="P33" s="3">
+      <c r="Q33" s="3">
         <v>482000</v>
       </c>
-      <c r="Q33" s="3">
+      <c r="R33" s="3">
         <v>112600</v>
       </c>
-      <c r="R33" s="3">
+      <c r="S33" s="3">
         <v>358800</v>
       </c>
-      <c r="S33" s="3">
+      <c r="T33" s="3">
         <v>100500</v>
       </c>
-      <c r="T33" s="3">
+      <c r="U33" s="3">
         <v>412900</v>
       </c>
-      <c r="U33" s="3">
+      <c r="V33" s="3">
         <v>174900</v>
       </c>
-      <c r="V33" s="3">
+      <c r="W33" s="3">
         <v>410100</v>
       </c>
-      <c r="W33" s="3">
+      <c r="X33" s="3">
         <v>537700</v>
       </c>
-      <c r="X33" s="3">
+      <c r="Y33" s="3">
         <v>517500</v>
       </c>
-      <c r="Y33" s="3">
+      <c r="Z33" s="3">
         <v>76800</v>
       </c>
-      <c r="Z33" s="3">
+      <c r="AA33" s="3">
         <v>453900</v>
       </c>
-      <c r="AA33" s="3">
+      <c r="AB33" s="3">
         <v>569900</v>
       </c>
-      <c r="AB33" s="3">
+      <c r="AC33" s="3">
         <v>463600</v>
       </c>
-      <c r="AC33" s="3">
+      <c r="AD33" s="3">
         <v>84900</v>
       </c>
-      <c r="AD33" s="3">
+      <c r="AE33" s="3">
         <v>212100</v>
       </c>
-      <c r="AE33" s="3">
+      <c r="AF33" s="3">
         <v>369000</v>
       </c>
-      <c r="AF33" s="3">
+      <c r="AG33" s="3">
         <v>517600</v>
       </c>
-      <c r="AG33" s="3">
+      <c r="AH33" s="3">
         <v>88500</v>
       </c>
-      <c r="AH33" s="3">
+      <c r="AI33" s="3">
         <v>275700</v>
       </c>
     </row>
-    <row r="34" spans="2:34" x14ac:dyDescent="0.2">
+    <row r="34" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C34" s="1" t="s">
         <v>29</v>
       </c>
@@ -3238,8 +3314,11 @@
       <c r="AH34" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="35" spans="2:34" x14ac:dyDescent="0.2">
+      <c r="AI34" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="35" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C35" s="1" t="s">
         <v>30</v>
       </c>
@@ -3247,200 +3326,206 @@
         <v>5</v>
       </c>
       <c r="E35" s="3">
-        <v>24000</v>
+        <v>591600</v>
       </c>
       <c r="F35" s="3">
-        <v>632600</v>
+        <v>24600</v>
       </c>
       <c r="G35" s="3">
-        <v>432500</v>
+        <v>649900</v>
       </c>
       <c r="H35" s="3">
-        <v>644800</v>
+        <v>444300</v>
       </c>
       <c r="I35" s="3">
-        <v>329800</v>
+        <v>662500</v>
       </c>
       <c r="J35" s="3">
+        <v>338800</v>
+      </c>
+      <c r="K35" s="3">
         <v>640600</v>
       </c>
-      <c r="K35" s="3">
+      <c r="L35" s="3">
         <v>684400</v>
       </c>
-      <c r="L35" s="3">
+      <c r="M35" s="3">
         <v>631400</v>
       </c>
-      <c r="M35" s="3">
+      <c r="N35" s="3">
         <v>279500</v>
       </c>
-      <c r="N35" s="3">
+      <c r="O35" s="3">
         <v>570700</v>
       </c>
-      <c r="O35" s="3">
+      <c r="P35" s="3">
         <v>552600</v>
       </c>
-      <c r="P35" s="3">
+      <c r="Q35" s="3">
         <v>482000</v>
       </c>
-      <c r="Q35" s="3">
+      <c r="R35" s="3">
         <v>112600</v>
       </c>
-      <c r="R35" s="3">
+      <c r="S35" s="3">
         <v>358800</v>
       </c>
-      <c r="S35" s="3">
+      <c r="T35" s="3">
         <v>100500</v>
       </c>
-      <c r="T35" s="3">
+      <c r="U35" s="3">
         <v>412900</v>
       </c>
-      <c r="U35" s="3">
+      <c r="V35" s="3">
         <v>174900</v>
       </c>
-      <c r="V35" s="3">
+      <c r="W35" s="3">
         <v>410100</v>
       </c>
-      <c r="W35" s="3">
+      <c r="X35" s="3">
         <v>537700</v>
       </c>
-      <c r="X35" s="3">
+      <c r="Y35" s="3">
         <v>517500</v>
       </c>
-      <c r="Y35" s="3">
+      <c r="Z35" s="3">
         <v>76800</v>
       </c>
-      <c r="Z35" s="3">
+      <c r="AA35" s="3">
         <v>453900</v>
       </c>
-      <c r="AA35" s="3">
+      <c r="AB35" s="3">
         <v>569900</v>
       </c>
-      <c r="AB35" s="3">
+      <c r="AC35" s="3">
         <v>463600</v>
       </c>
-      <c r="AC35" s="3">
+      <c r="AD35" s="3">
         <v>84900</v>
       </c>
-      <c r="AD35" s="3">
+      <c r="AE35" s="3">
         <v>212100</v>
       </c>
-      <c r="AE35" s="3">
+      <c r="AF35" s="3">
         <v>369000</v>
       </c>
-      <c r="AF35" s="3">
+      <c r="AG35" s="3">
         <v>517600</v>
       </c>
-      <c r="AG35" s="3">
+      <c r="AH35" s="3">
         <v>88500</v>
       </c>
-      <c r="AH35" s="3">
+      <c r="AI35" s="3">
         <v>275700</v>
       </c>
     </row>
-    <row r="37" spans="2:34" x14ac:dyDescent="0.2">
+    <row r="37" spans="2:35" x14ac:dyDescent="0.2">
       <c r="B37" s="1" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="38" spans="2:34" x14ac:dyDescent="0.2">
+    <row r="38" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C38" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D38" s="2">
+        <v>45473</v>
+      </c>
+      <c r="E38" s="2">
         <v>45382</v>
       </c>
-      <c r="E38" s="2">
+      <c r="F38" s="2">
         <v>45291</v>
       </c>
-      <c r="F38" s="2">
+      <c r="G38" s="2">
         <v>45199</v>
       </c>
-      <c r="G38" s="2">
+      <c r="H38" s="2">
         <v>45107</v>
       </c>
-      <c r="H38" s="2">
+      <c r="I38" s="2">
         <v>45016</v>
       </c>
-      <c r="I38" s="2">
+      <c r="J38" s="2">
         <v>44926</v>
       </c>
-      <c r="J38" s="2">
+      <c r="K38" s="2">
         <v>44834</v>
       </c>
-      <c r="K38" s="2">
+      <c r="L38" s="2">
         <v>44742</v>
       </c>
-      <c r="L38" s="2">
+      <c r="M38" s="2">
         <v>44651</v>
       </c>
-      <c r="M38" s="2">
+      <c r="N38" s="2">
         <v>44561</v>
       </c>
-      <c r="N38" s="2">
+      <c r="O38" s="2">
         <v>44469</v>
       </c>
-      <c r="O38" s="2">
+      <c r="P38" s="2">
         <v>44377</v>
       </c>
-      <c r="P38" s="2">
+      <c r="Q38" s="2">
         <v>44286</v>
       </c>
-      <c r="Q38" s="2">
+      <c r="R38" s="2">
         <v>44196</v>
       </c>
-      <c r="R38" s="2">
+      <c r="S38" s="2">
         <v>44104</v>
       </c>
-      <c r="S38" s="2">
+      <c r="T38" s="2">
         <v>44012</v>
       </c>
-      <c r="T38" s="2">
+      <c r="U38" s="2">
         <v>43921</v>
       </c>
-      <c r="U38" s="2">
+      <c r="V38" s="2">
         <v>43830</v>
       </c>
-      <c r="V38" s="2">
+      <c r="W38" s="2">
         <v>43738</v>
       </c>
-      <c r="W38" s="2">
+      <c r="X38" s="2">
         <v>43646</v>
       </c>
-      <c r="X38" s="2">
+      <c r="Y38" s="2">
         <v>43555</v>
       </c>
-      <c r="Y38" s="2">
+      <c r="Z38" s="2">
         <v>43465</v>
       </c>
-      <c r="Z38" s="2">
+      <c r="AA38" s="2">
         <v>43373</v>
       </c>
-      <c r="AA38" s="2">
+      <c r="AB38" s="2">
         <v>43281</v>
       </c>
-      <c r="AB38" s="2">
+      <c r="AC38" s="2">
         <v>43190</v>
       </c>
-      <c r="AC38" s="2">
+      <c r="AD38" s="2">
         <v>43100</v>
       </c>
-      <c r="AD38" s="2">
+      <c r="AE38" s="2">
         <v>43008</v>
       </c>
-      <c r="AE38" s="2">
+      <c r="AF38" s="2">
         <v>42916</v>
       </c>
-      <c r="AF38" s="2">
+      <c r="AG38" s="2">
         <v>42825</v>
       </c>
-      <c r="AG38" s="2">
+      <c r="AH38" s="2">
         <v>42735</v>
       </c>
-      <c r="AH38" s="2">
+      <c r="AI38" s="2">
         <v>42643</v>
       </c>
     </row>
-    <row r="39" spans="2:34" x14ac:dyDescent="0.2">
+    <row r="39" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C39" s="1" t="s">
         <v>32</v>
       </c>
@@ -3475,8 +3560,9 @@
       <c r="AF39" s="3"/>
       <c r="AG39" s="3"/>
       <c r="AH39" s="3"/>
-    </row>
-    <row r="40" spans="2:34" x14ac:dyDescent="0.2">
+      <c r="AI39" s="3"/>
+    </row>
+    <row r="40" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C40" s="1" t="s">
         <v>33</v>
       </c>
@@ -3511,204 +3597,211 @@
       <c r="AF40" s="3"/>
       <c r="AG40" s="3"/>
       <c r="AH40" s="3"/>
-    </row>
-    <row r="41" spans="2:34" x14ac:dyDescent="0.2">
+      <c r="AI40" s="3"/>
+    </row>
+    <row r="41" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C41" s="1" t="s">
         <v>34</v>
       </c>
       <c r="D41" s="3">
-        <v>23124000</v>
+        <v>19032100</v>
       </c>
       <c r="E41" s="3">
-        <v>22212800</v>
+        <v>23757500</v>
       </c>
       <c r="F41" s="3">
-        <v>18766400</v>
+        <v>22821400</v>
       </c>
       <c r="G41" s="3">
-        <v>15619500</v>
+        <v>19280500</v>
       </c>
       <c r="H41" s="3">
-        <v>22485700</v>
+        <v>16047400</v>
       </c>
       <c r="I41" s="3">
-        <v>24914300</v>
+        <v>23101800</v>
       </c>
       <c r="J41" s="3">
+        <v>25596900</v>
+      </c>
+      <c r="K41" s="3">
         <v>6507700</v>
       </c>
-      <c r="K41" s="3">
+      <c r="L41" s="3">
         <v>7377100</v>
       </c>
-      <c r="L41" s="3">
+      <c r="M41" s="3">
         <v>9785500</v>
       </c>
-      <c r="M41" s="3">
+      <c r="N41" s="3">
         <v>5555400</v>
       </c>
-      <c r="N41" s="3">
+      <c r="O41" s="3">
         <v>7893500</v>
       </c>
-      <c r="O41" s="3">
+      <c r="P41" s="3">
         <v>7303900</v>
       </c>
-      <c r="P41" s="3">
+      <c r="Q41" s="3">
         <v>7996900</v>
       </c>
-      <c r="Q41" s="3">
+      <c r="R41" s="3">
         <v>6985700</v>
       </c>
-      <c r="R41" s="3">
+      <c r="S41" s="3">
         <v>6452400</v>
       </c>
-      <c r="S41" s="3">
+      <c r="T41" s="3">
         <v>6934700</v>
       </c>
-      <c r="T41" s="3">
+      <c r="U41" s="3">
         <v>7810800</v>
       </c>
-      <c r="U41" s="3">
+      <c r="V41" s="3">
         <v>5327800</v>
       </c>
-      <c r="V41" s="3">
+      <c r="W41" s="3">
         <v>7069900</v>
       </c>
-      <c r="W41" s="3">
+      <c r="X41" s="3">
         <v>5777500</v>
       </c>
-      <c r="X41" s="3">
+      <c r="Y41" s="3">
         <v>4361000</v>
       </c>
-      <c r="Y41" s="3">
+      <c r="Z41" s="3">
         <v>5329900</v>
       </c>
-      <c r="Z41" s="3">
+      <c r="AA41" s="3">
         <v>4608100</v>
       </c>
-      <c r="AA41" s="3">
+      <c r="AB41" s="3">
         <v>4589200</v>
       </c>
-      <c r="AB41" s="3">
+      <c r="AC41" s="3">
         <v>4387400</v>
       </c>
-      <c r="AC41" s="3">
+      <c r="AD41" s="3">
         <v>5323900</v>
       </c>
-      <c r="AD41" s="3">
+      <c r="AE41" s="3">
         <v>5337600</v>
       </c>
-      <c r="AE41" s="3">
+      <c r="AF41" s="3">
         <v>5780800</v>
       </c>
-      <c r="AF41" s="3">
+      <c r="AG41" s="3">
         <v>6495200</v>
       </c>
-      <c r="AG41" s="3">
+      <c r="AH41" s="3">
         <v>6385500</v>
       </c>
-      <c r="AH41" s="3">
+      <c r="AI41" s="3">
         <v>7024600</v>
       </c>
     </row>
-    <row r="42" spans="2:34" x14ac:dyDescent="0.2">
+    <row r="42" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C42" s="1" t="s">
         <v>35</v>
       </c>
       <c r="D42" s="3">
-        <v>17164500</v>
+        <v>17617400</v>
       </c>
       <c r="E42" s="3">
-        <v>42070300</v>
+        <v>41332400</v>
       </c>
       <c r="F42" s="3">
-        <v>39219900</v>
+        <v>43222900</v>
       </c>
       <c r="G42" s="3">
-        <v>45997000</v>
+        <v>40294500</v>
       </c>
       <c r="H42" s="3">
-        <v>37482400</v>
+        <v>47257200</v>
       </c>
       <c r="I42" s="3">
-        <v>39988600</v>
+        <v>38509300</v>
       </c>
       <c r="J42" s="3">
+        <v>41084100</v>
+      </c>
+      <c r="K42" s="3">
         <v>48087900</v>
       </c>
-      <c r="K42" s="3">
+      <c r="L42" s="3">
         <v>44907700</v>
       </c>
-      <c r="L42" s="3">
+      <c r="M42" s="3">
         <v>44616700</v>
       </c>
-      <c r="M42" s="3">
+      <c r="N42" s="3">
         <v>44083500</v>
       </c>
-      <c r="N42" s="3">
+      <c r="O42" s="3">
         <v>38326100</v>
       </c>
-      <c r="O42" s="3">
+      <c r="P42" s="3">
         <v>33800600</v>
       </c>
-      <c r="P42" s="3">
+      <c r="Q42" s="3">
         <v>32013900</v>
       </c>
-      <c r="Q42" s="3">
+      <c r="R42" s="3">
         <v>39170300</v>
       </c>
-      <c r="R42" s="3">
+      <c r="S42" s="3">
         <v>33273800</v>
       </c>
-      <c r="S42" s="3">
+      <c r="T42" s="3">
         <v>36396600</v>
       </c>
-      <c r="T42" s="3">
+      <c r="U42" s="3">
         <v>38606200</v>
       </c>
-      <c r="U42" s="3">
+      <c r="V42" s="3">
         <v>37680800</v>
       </c>
-      <c r="V42" s="3">
+      <c r="W42" s="3">
         <v>39232200</v>
       </c>
-      <c r="W42" s="3">
+      <c r="X42" s="3">
         <v>36892000</v>
       </c>
-      <c r="X42" s="3">
+      <c r="Y42" s="3">
         <v>30905300</v>
       </c>
-      <c r="Y42" s="3">
+      <c r="Z42" s="3">
         <v>29776700</v>
       </c>
-      <c r="Z42" s="3">
+      <c r="AA42" s="3">
         <v>20883600</v>
       </c>
-      <c r="AA42" s="3">
+      <c r="AB42" s="3">
         <v>22286700</v>
       </c>
-      <c r="AB42" s="3">
+      <c r="AC42" s="3">
         <v>21840100</v>
       </c>
-      <c r="AC42" s="3">
+      <c r="AD42" s="3">
         <v>20932300</v>
       </c>
-      <c r="AD42" s="3">
+      <c r="AE42" s="3">
         <v>12488600</v>
       </c>
-      <c r="AE42" s="3">
+      <c r="AF42" s="3">
         <v>14955900</v>
       </c>
-      <c r="AF42" s="3">
+      <c r="AG42" s="3">
         <v>13350900</v>
       </c>
-      <c r="AG42" s="3">
+      <c r="AH42" s="3">
         <v>14204100</v>
       </c>
-      <c r="AH42" s="3">
+      <c r="AI42" s="3">
         <v>16154100</v>
       </c>
     </row>
-    <row r="43" spans="2:34" x14ac:dyDescent="0.2">
+    <row r="43" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C43" s="1" t="s">
         <v>36</v>
       </c>
@@ -3805,8 +3898,11 @@
       <c r="AH43" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="44" spans="2:34" x14ac:dyDescent="0.2">
+      <c r="AI43" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="44" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C44" s="1" t="s">
         <v>37</v>
       </c>
@@ -3903,8 +3999,11 @@
       <c r="AH44" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="45" spans="2:34" x14ac:dyDescent="0.2">
+      <c r="AI44" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="45" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C45" s="1" t="s">
         <v>38</v>
       </c>
@@ -4001,8 +4100,11 @@
       <c r="AH45" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="46" spans="2:34" x14ac:dyDescent="0.2">
+      <c r="AI45" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="46" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C46" s="1" t="s">
         <v>39</v>
       </c>
@@ -4099,302 +4201,314 @@
       <c r="AH46" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="47" spans="2:34" x14ac:dyDescent="0.2">
+      <c r="AI46" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="47" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C47" s="1" t="s">
         <v>40</v>
       </c>
       <c r="D47" s="3">
-        <v>1451300</v>
+        <v>1424500</v>
       </c>
       <c r="E47" s="3">
-        <v>1310600</v>
+        <v>1491000</v>
       </c>
       <c r="F47" s="3">
-        <v>1282400</v>
+        <v>1346500</v>
       </c>
       <c r="G47" s="3">
-        <v>1183800</v>
+        <v>1317600</v>
       </c>
       <c r="H47" s="3">
-        <v>1082600</v>
+        <v>1216300</v>
       </c>
       <c r="I47" s="3">
-        <v>953100</v>
+        <v>1112300</v>
       </c>
       <c r="J47" s="3">
+        <v>979200</v>
+      </c>
+      <c r="K47" s="3">
         <v>976800</v>
       </c>
-      <c r="K47" s="3">
+      <c r="L47" s="3">
         <v>1035000</v>
       </c>
-      <c r="L47" s="3">
+      <c r="M47" s="3">
         <v>1011300</v>
       </c>
-      <c r="M47" s="3">
+      <c r="N47" s="3">
         <v>1001400</v>
       </c>
-      <c r="N47" s="3">
+      <c r="O47" s="3">
         <v>896000</v>
       </c>
-      <c r="O47" s="3">
+      <c r="P47" s="3">
         <v>881500</v>
       </c>
-      <c r="P47" s="3">
+      <c r="Q47" s="3">
         <v>775800</v>
       </c>
-      <c r="Q47" s="3">
+      <c r="R47" s="3">
         <v>735000</v>
       </c>
-      <c r="R47" s="3">
+      <c r="S47" s="3">
         <v>829200</v>
       </c>
-      <c r="S47" s="3">
+      <c r="T47" s="3">
         <v>714700</v>
       </c>
-      <c r="T47" s="3">
+      <c r="U47" s="3">
         <v>674300</v>
       </c>
-      <c r="U47" s="3">
+      <c r="V47" s="3">
         <v>685400</v>
       </c>
-      <c r="V47" s="3">
+      <c r="W47" s="3">
         <v>322100</v>
       </c>
-      <c r="W47" s="3">
+      <c r="X47" s="3">
         <v>311500</v>
       </c>
-      <c r="X47" s="3">
+      <c r="Y47" s="3">
         <v>316200</v>
       </c>
-      <c r="Y47" s="3">
+      <c r="Z47" s="3">
         <v>303600</v>
       </c>
-      <c r="Z47" s="3">
+      <c r="AA47" s="3">
         <v>276700</v>
       </c>
-      <c r="AA47" s="3">
+      <c r="AB47" s="3">
         <v>346900</v>
       </c>
-      <c r="AB47" s="3">
+      <c r="AC47" s="3">
         <v>348200</v>
       </c>
-      <c r="AC47" s="3">
+      <c r="AD47" s="3">
         <v>367000</v>
       </c>
-      <c r="AD47" s="3">
+      <c r="AE47" s="3">
         <v>490900</v>
       </c>
-      <c r="AE47" s="3">
+      <c r="AF47" s="3">
         <v>326300</v>
       </c>
-      <c r="AF47" s="3">
+      <c r="AG47" s="3">
         <v>351100</v>
       </c>
-      <c r="AG47" s="3">
+      <c r="AH47" s="3">
         <v>395100</v>
       </c>
-      <c r="AH47" s="3">
+      <c r="AI47" s="3">
         <v>377600</v>
       </c>
     </row>
-    <row r="48" spans="2:34" x14ac:dyDescent="0.2">
+    <row r="48" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C48" s="1" t="s">
         <v>41</v>
       </c>
       <c r="D48" s="3">
-        <v>2668700</v>
+        <v>2851500</v>
       </c>
       <c r="E48" s="3">
-        <v>2664200</v>
+        <v>2741900</v>
       </c>
       <c r="F48" s="3">
-        <v>2637100</v>
+        <v>2737100</v>
       </c>
       <c r="G48" s="3">
-        <v>2633500</v>
+        <v>2709300</v>
       </c>
       <c r="H48" s="3">
-        <v>2656000</v>
+        <v>2705700</v>
       </c>
       <c r="I48" s="3">
-        <v>2577400</v>
+        <v>2728700</v>
       </c>
       <c r="J48" s="3">
+        <v>2648000</v>
+      </c>
+      <c r="K48" s="3">
         <v>2590300</v>
       </c>
-      <c r="K48" s="3">
+      <c r="L48" s="3">
         <v>2689200</v>
       </c>
-      <c r="L48" s="3">
+      <c r="M48" s="3">
         <v>2729900</v>
       </c>
-      <c r="M48" s="3">
+      <c r="N48" s="3">
         <v>2673200</v>
       </c>
-      <c r="N48" s="3">
+      <c r="O48" s="3">
         <v>2701000</v>
       </c>
-      <c r="O48" s="3">
+      <c r="P48" s="3">
         <v>2682600</v>
       </c>
-      <c r="P48" s="3">
+      <c r="Q48" s="3">
         <v>2700600</v>
       </c>
-      <c r="Q48" s="3">
+      <c r="R48" s="3">
         <v>2719200</v>
       </c>
-      <c r="R48" s="3">
+      <c r="S48" s="3">
         <v>2764300</v>
       </c>
-      <c r="S48" s="3">
+      <c r="T48" s="3">
         <v>2790300</v>
       </c>
-      <c r="T48" s="3">
+      <c r="U48" s="3">
         <v>2961700</v>
       </c>
-      <c r="U48" s="3">
+      <c r="V48" s="3">
         <v>3098200</v>
       </c>
-      <c r="V48" s="3">
+      <c r="W48" s="3">
         <v>3089800</v>
       </c>
-      <c r="W48" s="3">
+      <c r="X48" s="3">
         <v>3058200</v>
       </c>
-      <c r="X48" s="3">
+      <c r="Y48" s="3">
         <v>3080600</v>
       </c>
-      <c r="Y48" s="3">
+      <c r="Z48" s="3">
         <v>2368100</v>
       </c>
-      <c r="Z48" s="3">
+      <c r="AA48" s="3">
         <v>2284800</v>
       </c>
-      <c r="AA48" s="3">
+      <c r="AB48" s="3">
         <v>2378800</v>
       </c>
-      <c r="AB48" s="3">
+      <c r="AC48" s="3">
         <v>2384000</v>
       </c>
-      <c r="AC48" s="3">
+      <c r="AD48" s="3">
         <v>2507000</v>
       </c>
-      <c r="AD48" s="3">
+      <c r="AE48" s="3">
         <v>2509800</v>
       </c>
-      <c r="AE48" s="3">
+      <c r="AF48" s="3">
         <v>2480800</v>
       </c>
-      <c r="AF48" s="3">
+      <c r="AG48" s="3">
         <v>2470200</v>
       </c>
-      <c r="AG48" s="3">
+      <c r="AH48" s="3">
         <v>2534900</v>
       </c>
-      <c r="AH48" s="3">
+      <c r="AI48" s="3">
         <v>2525400</v>
       </c>
     </row>
-    <row r="49" spans="3:34" x14ac:dyDescent="0.2">
+    <row r="49" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C49" s="1" t="s">
         <v>42</v>
       </c>
       <c r="D49" s="3">
-        <v>729900</v>
+        <v>769000</v>
       </c>
       <c r="E49" s="3">
-        <v>727700</v>
+        <v>749900</v>
       </c>
       <c r="F49" s="3">
-        <v>718800</v>
+        <v>747600</v>
       </c>
       <c r="G49" s="3">
-        <v>722300</v>
+        <v>738500</v>
       </c>
       <c r="H49" s="3">
-        <v>701000</v>
+        <v>742100</v>
       </c>
       <c r="I49" s="3">
-        <v>619900</v>
+        <v>720200</v>
       </c>
       <c r="J49" s="3">
+        <v>636800</v>
+      </c>
+      <c r="K49" s="3">
         <v>639200</v>
       </c>
-      <c r="K49" s="3">
+      <c r="L49" s="3">
         <v>596500</v>
       </c>
-      <c r="L49" s="3">
+      <c r="M49" s="3">
         <v>608700</v>
       </c>
-      <c r="M49" s="3">
+      <c r="N49" s="3">
         <v>589000</v>
       </c>
-      <c r="N49" s="3">
+      <c r="O49" s="3">
         <v>586400</v>
       </c>
-      <c r="O49" s="3">
+      <c r="P49" s="3">
         <v>581700</v>
       </c>
-      <c r="P49" s="3">
+      <c r="Q49" s="3">
         <v>582600</v>
       </c>
-      <c r="Q49" s="3">
+      <c r="R49" s="3">
         <v>586100</v>
       </c>
-      <c r="R49" s="3">
+      <c r="S49" s="3">
         <v>615800</v>
       </c>
-      <c r="S49" s="3">
+      <c r="T49" s="3">
         <v>631700</v>
       </c>
-      <c r="T49" s="3">
+      <c r="U49" s="3">
         <v>668000</v>
       </c>
-      <c r="U49" s="3">
+      <c r="V49" s="3">
         <v>717500</v>
       </c>
-      <c r="V49" s="3">
+      <c r="W49" s="3">
         <v>590200</v>
       </c>
-      <c r="W49" s="3">
+      <c r="X49" s="3">
         <v>565800</v>
       </c>
-      <c r="X49" s="3">
+      <c r="Y49" s="3">
         <v>588900</v>
       </c>
-      <c r="Y49" s="3">
+      <c r="Z49" s="3">
         <v>493300</v>
       </c>
-      <c r="Z49" s="3">
+      <c r="AA49" s="3">
         <v>502400</v>
       </c>
-      <c r="AA49" s="3">
+      <c r="AB49" s="3">
         <v>549000</v>
       </c>
-      <c r="AB49" s="3">
+      <c r="AC49" s="3">
         <v>452700</v>
       </c>
-      <c r="AC49" s="3">
+      <c r="AD49" s="3">
         <v>456400</v>
       </c>
-      <c r="AD49" s="3">
+      <c r="AE49" s="3">
         <v>461900</v>
       </c>
-      <c r="AE49" s="3">
+      <c r="AF49" s="3">
         <v>446100</v>
       </c>
-      <c r="AF49" s="3">
+      <c r="AG49" s="3">
         <v>415100</v>
       </c>
-      <c r="AG49" s="3">
+      <c r="AH49" s="3">
         <v>435400</v>
       </c>
-      <c r="AH49" s="3">
+      <c r="AI49" s="3">
         <v>376700</v>
       </c>
     </row>
-    <row r="50" spans="3:34" x14ac:dyDescent="0.2">
+    <row r="50" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C50" s="1" t="s">
         <v>43</v>
       </c>
@@ -4491,8 +4605,11 @@
       <c r="AH50" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="51" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI50" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="51" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C51" s="1" t="s">
         <v>44</v>
       </c>
@@ -4589,106 +4706,112 @@
       <c r="AH51" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="52" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI51" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="52" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C52" s="1" t="s">
         <v>45</v>
       </c>
       <c r="D52" s="3">
-        <v>211800</v>
+        <v>147600</v>
       </c>
       <c r="E52" s="3">
-        <v>258400</v>
+        <v>217600</v>
       </c>
       <c r="F52" s="3">
-        <v>304400</v>
+        <v>265500</v>
       </c>
       <c r="G52" s="3">
-        <v>289200</v>
+        <v>312800</v>
       </c>
       <c r="H52" s="3">
-        <v>150700</v>
+        <v>297100</v>
       </c>
       <c r="I52" s="3">
-        <v>322900</v>
+        <v>154800</v>
       </c>
       <c r="J52" s="3">
+        <v>331800</v>
+      </c>
+      <c r="K52" s="3">
         <v>284500</v>
       </c>
-      <c r="K52" s="3">
+      <c r="L52" s="3">
         <v>166400</v>
       </c>
-      <c r="L52" s="3">
+      <c r="M52" s="3">
         <v>58400</v>
       </c>
-      <c r="M52" s="3">
+      <c r="N52" s="3">
         <v>59100</v>
       </c>
-      <c r="N52" s="3">
+      <c r="O52" s="3">
         <v>41100</v>
       </c>
-      <c r="O52" s="3">
+      <c r="P52" s="3">
         <v>56000</v>
       </c>
-      <c r="P52" s="3">
+      <c r="Q52" s="3">
         <v>73700</v>
       </c>
-      <c r="Q52" s="3">
+      <c r="R52" s="3">
         <v>82700</v>
       </c>
-      <c r="R52" s="3">
+      <c r="S52" s="3">
         <v>74500</v>
       </c>
-      <c r="S52" s="3">
+      <c r="T52" s="3">
         <v>37800</v>
       </c>
-      <c r="T52" s="3">
+      <c r="U52" s="3">
         <v>38200</v>
       </c>
-      <c r="U52" s="3">
+      <c r="V52" s="3">
         <v>44800</v>
       </c>
-      <c r="V52" s="3">
+      <c r="W52" s="3">
         <v>82300</v>
       </c>
-      <c r="W52" s="3">
+      <c r="X52" s="3">
         <v>69500</v>
       </c>
-      <c r="X52" s="3">
+      <c r="Y52" s="3">
         <v>68200</v>
       </c>
-      <c r="Y52" s="3">
+      <c r="Z52" s="3">
         <v>120400</v>
       </c>
-      <c r="Z52" s="3">
+      <c r="AA52" s="3">
         <v>36800</v>
       </c>
-      <c r="AA52" s="3">
+      <c r="AB52" s="3">
         <v>91100</v>
       </c>
-      <c r="AB52" s="3">
+      <c r="AC52" s="3">
         <v>177600</v>
       </c>
-      <c r="AC52" s="3">
+      <c r="AD52" s="3">
         <v>289300</v>
       </c>
-      <c r="AD52" s="3">
+      <c r="AE52" s="3">
         <v>234800</v>
       </c>
-      <c r="AE52" s="3">
+      <c r="AF52" s="3">
         <v>221100</v>
       </c>
-      <c r="AF52" s="3">
+      <c r="AG52" s="3">
         <v>262700</v>
       </c>
-      <c r="AG52" s="3">
+      <c r="AH52" s="3">
         <v>274800</v>
       </c>
-      <c r="AH52" s="3">
+      <c r="AI52" s="3">
         <v>143800</v>
       </c>
     </row>
-    <row r="53" spans="3:34" x14ac:dyDescent="0.2">
+    <row r="53" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C53" s="1" t="s">
         <v>46</v>
       </c>
@@ -4785,106 +4908,112 @@
       <c r="AH53" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="54" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI53" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="54" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C54" s="1" t="s">
         <v>47</v>
       </c>
       <c r="D54" s="3">
-        <v>368480200</v>
+        <v>381585900</v>
       </c>
       <c r="E54" s="3">
-        <v>363543600</v>
+        <v>378575500</v>
       </c>
       <c r="F54" s="3">
-        <v>354719400</v>
+        <v>373503700</v>
       </c>
       <c r="G54" s="3">
-        <v>352525500</v>
+        <v>364437800</v>
       </c>
       <c r="H54" s="3">
-        <v>348997900</v>
+        <v>362183700</v>
       </c>
       <c r="I54" s="3">
-        <v>350746300</v>
+        <v>358559400</v>
       </c>
       <c r="J54" s="3">
+        <v>360355800</v>
+      </c>
+      <c r="K54" s="3">
         <v>366510300</v>
       </c>
-      <c r="K54" s="3">
+      <c r="L54" s="3">
         <v>368558700</v>
       </c>
-      <c r="L54" s="3">
+      <c r="M54" s="3">
         <v>358592300</v>
       </c>
-      <c r="M54" s="3">
+      <c r="N54" s="3">
         <v>335387900</v>
       </c>
-      <c r="N54" s="3">
+      <c r="O54" s="3">
         <v>328638700</v>
       </c>
-      <c r="O54" s="3">
+      <c r="P54" s="3">
         <v>315953000</v>
       </c>
-      <c r="P54" s="3">
+      <c r="Q54" s="3">
         <v>307917200</v>
       </c>
-      <c r="Q54" s="3">
+      <c r="R54" s="3">
         <v>295320000</v>
       </c>
-      <c r="R54" s="3">
+      <c r="S54" s="3">
         <v>293246000</v>
       </c>
-      <c r="S54" s="3">
+      <c r="T54" s="3">
         <v>292659600</v>
       </c>
-      <c r="T54" s="3">
+      <c r="U54" s="3">
         <v>306353500</v>
       </c>
-      <c r="U54" s="3">
+      <c r="V54" s="3">
         <v>307683600</v>
       </c>
-      <c r="V54" s="3">
+      <c r="W54" s="3">
         <v>314996600</v>
       </c>
-      <c r="W54" s="3">
+      <c r="X54" s="3">
         <v>316273500</v>
       </c>
-      <c r="X54" s="3">
+      <c r="Y54" s="3">
         <v>314085600</v>
       </c>
-      <c r="Y54" s="3">
+      <c r="Z54" s="3">
         <v>285975600</v>
       </c>
-      <c r="Z54" s="3">
+      <c r="AA54" s="3">
         <v>267139300</v>
       </c>
-      <c r="AA54" s="3">
+      <c r="AB54" s="3">
         <v>274311500</v>
       </c>
-      <c r="AB54" s="3">
+      <c r="AC54" s="3">
         <v>273668600</v>
       </c>
-      <c r="AC54" s="3">
+      <c r="AD54" s="3">
         <v>278340000</v>
       </c>
-      <c r="AD54" s="3">
+      <c r="AE54" s="3">
         <v>279730100</v>
       </c>
-      <c r="AE54" s="3">
+      <c r="AF54" s="3">
         <v>278137400</v>
       </c>
-      <c r="AF54" s="3">
+      <c r="AG54" s="3">
         <v>273600800</v>
       </c>
-      <c r="AG54" s="3">
+      <c r="AH54" s="3">
         <v>279614500</v>
       </c>
-      <c r="AH54" s="3">
+      <c r="AI54" s="3">
         <v>281548700</v>
       </c>
     </row>
-    <row r="55" spans="3:34" x14ac:dyDescent="0.2">
+    <row r="55" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C55" s="1" t="s">
         <v>48</v>
       </c>
@@ -4919,8 +5048,9 @@
       <c r="AF55" s="3"/>
       <c r="AG55" s="3"/>
       <c r="AH55" s="3"/>
-    </row>
-    <row r="56" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI55" s="3"/>
+    </row>
+    <row r="56" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C56" s="1" t="s">
         <v>49</v>
       </c>
@@ -4955,8 +5085,9 @@
       <c r="AF56" s="3"/>
       <c r="AG56" s="3"/>
       <c r="AH56" s="3"/>
-    </row>
-    <row r="57" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI56" s="3"/>
+    </row>
+    <row r="57" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C57" s="1" t="s">
         <v>50</v>
       </c>
@@ -4964,97 +5095,100 @@
         <v>5</v>
       </c>
       <c r="E57" s="3">
-        <v>9097800</v>
+        <v>13774400</v>
       </c>
       <c r="F57" s="3">
-        <v>13922400</v>
+        <v>9347000</v>
       </c>
       <c r="G57" s="3">
-        <v>14189900</v>
+        <v>14303900</v>
       </c>
       <c r="H57" s="3">
-        <v>13315100</v>
+        <v>14578600</v>
       </c>
       <c r="I57" s="3">
-        <v>8363000</v>
+        <v>13679900</v>
       </c>
       <c r="J57" s="3">
+        <v>8592200</v>
+      </c>
+      <c r="K57" s="3">
         <v>12736100</v>
       </c>
-      <c r="K57" s="3">
+      <c r="L57" s="3">
         <v>12538100</v>
       </c>
-      <c r="L57" s="3">
+      <c r="M57" s="3">
         <v>11104000</v>
       </c>
-      <c r="M57" s="3">
+      <c r="N57" s="3">
         <v>10844700</v>
       </c>
-      <c r="N57" s="3">
+      <c r="O57" s="3">
         <v>7957500</v>
       </c>
-      <c r="O57" s="3">
+      <c r="P57" s="3">
         <v>9468900</v>
       </c>
-      <c r="P57" s="3">
+      <c r="Q57" s="3">
         <v>7995800</v>
       </c>
-      <c r="Q57" s="3">
+      <c r="R57" s="3">
         <v>3698600</v>
       </c>
-      <c r="R57" s="3">
+      <c r="S57" s="3">
         <v>7530800</v>
       </c>
-      <c r="S57" s="3">
+      <c r="T57" s="3">
         <v>8467000</v>
       </c>
-      <c r="T57" s="3">
+      <c r="U57" s="3">
         <v>9538600</v>
       </c>
-      <c r="U57" s="3">
+      <c r="V57" s="3">
         <v>7264700</v>
       </c>
-      <c r="V57" s="3">
+      <c r="W57" s="3">
         <v>13339700</v>
       </c>
-      <c r="W57" s="3">
+      <c r="X57" s="3">
         <v>15138200</v>
       </c>
-      <c r="X57" s="3">
+      <c r="Y57" s="3">
         <v>14778600</v>
       </c>
-      <c r="Y57" s="3">
+      <c r="Z57" s="3">
         <v>10988500</v>
       </c>
-      <c r="Z57" s="3">
+      <c r="AA57" s="3">
         <v>12068900</v>
       </c>
-      <c r="AA57" s="3">
+      <c r="AB57" s="3">
         <v>11638400</v>
       </c>
-      <c r="AB57" s="3">
+      <c r="AC57" s="3">
         <v>12317300</v>
       </c>
-      <c r="AC57" s="3">
+      <c r="AD57" s="3">
         <v>5801500</v>
       </c>
-      <c r="AD57" s="3">
+      <c r="AE57" s="3">
         <v>13814400</v>
       </c>
-      <c r="AE57" s="3">
+      <c r="AF57" s="3">
         <v>14756900</v>
       </c>
-      <c r="AF57" s="3">
+      <c r="AG57" s="3">
         <v>10823000</v>
       </c>
-      <c r="AG57" s="3">
+      <c r="AH57" s="3">
         <v>13329400</v>
       </c>
-      <c r="AH57" s="3">
+      <c r="AI57" s="3">
         <v>15356600</v>
       </c>
     </row>
-    <row r="58" spans="3:34" x14ac:dyDescent="0.2">
+    <row r="58" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C58" s="1" t="s">
         <v>51</v>
       </c>
@@ -5151,106 +5285,112 @@
       <c r="AH58" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="59" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI58" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="59" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C59" s="1" t="s">
         <v>52</v>
       </c>
       <c r="D59" s="3">
-        <v>56000</v>
+        <v>109400</v>
       </c>
       <c r="E59" s="3">
-        <v>3243400</v>
+        <v>3293300</v>
       </c>
       <c r="F59" s="3">
-        <v>3380200</v>
+        <v>3332200</v>
       </c>
       <c r="G59" s="3">
-        <v>2994300</v>
+        <v>3472800</v>
       </c>
       <c r="H59" s="3">
-        <v>3172500</v>
+        <v>3076300</v>
       </c>
       <c r="I59" s="3">
-        <v>2965900</v>
+        <v>3259400</v>
       </c>
       <c r="J59" s="3">
+        <v>3047200</v>
+      </c>
+      <c r="K59" s="3">
         <v>2229700</v>
       </c>
-      <c r="K59" s="3">
+      <c r="L59" s="3">
         <v>1968300</v>
       </c>
-      <c r="L59" s="3">
+      <c r="M59" s="3">
         <v>2093100</v>
       </c>
-      <c r="M59" s="3">
+      <c r="N59" s="3">
         <v>1991300</v>
       </c>
-      <c r="N59" s="3">
+      <c r="O59" s="3">
         <v>1538600</v>
       </c>
-      <c r="O59" s="3">
+      <c r="P59" s="3">
         <v>1446500</v>
       </c>
-      <c r="P59" s="3">
+      <c r="Q59" s="3">
         <v>1600800</v>
       </c>
-      <c r="Q59" s="3">
+      <c r="R59" s="3">
         <v>1790900</v>
       </c>
-      <c r="R59" s="3">
+      <c r="S59" s="3">
         <v>1521700</v>
       </c>
-      <c r="S59" s="3">
+      <c r="T59" s="3">
         <v>1545300</v>
       </c>
-      <c r="T59" s="3">
+      <c r="U59" s="3">
         <v>1892000</v>
       </c>
-      <c r="U59" s="3">
+      <c r="V59" s="3">
         <v>2294100</v>
       </c>
-      <c r="V59" s="3">
+      <c r="W59" s="3">
         <v>2199800</v>
       </c>
-      <c r="W59" s="3">
+      <c r="X59" s="3">
         <v>2064700</v>
       </c>
-      <c r="X59" s="3">
+      <c r="Y59" s="3">
         <v>2149400</v>
       </c>
-      <c r="Y59" s="3">
+      <c r="Z59" s="3">
         <v>1989900</v>
       </c>
-      <c r="Z59" s="3">
+      <c r="AA59" s="3">
         <v>1798500</v>
       </c>
-      <c r="AA59" s="3">
+      <c r="AB59" s="3">
         <v>1649500</v>
       </c>
-      <c r="AB59" s="3">
+      <c r="AC59" s="3">
         <v>1642100</v>
       </c>
-      <c r="AC59" s="3">
+      <c r="AD59" s="3">
         <v>2008600</v>
       </c>
-      <c r="AD59" s="3">
+      <c r="AE59" s="3">
         <v>2057400</v>
       </c>
-      <c r="AE59" s="3">
+      <c r="AF59" s="3">
         <v>1681400</v>
       </c>
-      <c r="AF59" s="3">
+      <c r="AG59" s="3">
         <v>1880000</v>
       </c>
-      <c r="AG59" s="3">
+      <c r="AH59" s="3">
         <v>2004400</v>
       </c>
-      <c r="AH59" s="3">
+      <c r="AI59" s="3">
         <v>1813400</v>
       </c>
     </row>
-    <row r="60" spans="3:34" x14ac:dyDescent="0.2">
+    <row r="60" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C60" s="1" t="s">
         <v>53</v>
       </c>
@@ -5347,204 +5487,213 @@
       <c r="AH60" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="61" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI60" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="61" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C61" s="1" t="s">
         <v>54</v>
       </c>
       <c r="D61" s="3">
-        <v>52456500</v>
+        <v>54313100</v>
       </c>
       <c r="E61" s="3">
-        <v>51332300</v>
+        <v>52340200</v>
       </c>
       <c r="F61" s="3">
-        <v>51747200</v>
+        <v>52738700</v>
       </c>
       <c r="G61" s="3">
-        <v>51956700</v>
+        <v>53164900</v>
       </c>
       <c r="H61" s="3">
-        <v>51851700</v>
+        <v>53380200</v>
       </c>
       <c r="I61" s="3">
-        <v>51265600</v>
+        <v>53272300</v>
       </c>
       <c r="J61" s="3">
+        <v>52670100</v>
+      </c>
+      <c r="K61" s="3">
         <v>58817800</v>
       </c>
-      <c r="K61" s="3">
+      <c r="L61" s="3">
         <v>58413400</v>
       </c>
-      <c r="L61" s="3">
+      <c r="M61" s="3">
         <v>54512100</v>
       </c>
-      <c r="M61" s="3">
+      <c r="N61" s="3">
         <v>51506600</v>
       </c>
-      <c r="N61" s="3">
+      <c r="O61" s="3">
         <v>49335300</v>
       </c>
-      <c r="O61" s="3">
+      <c r="P61" s="3">
         <v>46999300</v>
       </c>
-      <c r="P61" s="3">
+      <c r="Q61" s="3">
         <v>43329900</v>
       </c>
-      <c r="Q61" s="3">
+      <c r="R61" s="3">
         <v>42586400</v>
       </c>
-      <c r="R61" s="3">
+      <c r="S61" s="3">
         <v>38230600</v>
       </c>
-      <c r="S61" s="3">
+      <c r="T61" s="3">
         <v>39214800</v>
       </c>
-      <c r="T61" s="3">
+      <c r="U61" s="3">
         <v>43080800</v>
       </c>
-      <c r="U61" s="3">
+      <c r="V61" s="3">
         <v>42129500</v>
       </c>
-      <c r="V61" s="3">
+      <c r="W61" s="3">
         <v>44185000</v>
       </c>
-      <c r="W61" s="3">
+      <c r="X61" s="3">
         <v>43142100</v>
       </c>
-      <c r="X61" s="3">
+      <c r="Y61" s="3">
         <v>40307800</v>
       </c>
-      <c r="Y61" s="3">
+      <c r="Z61" s="3">
         <v>36868700</v>
       </c>
-      <c r="Z61" s="3">
+      <c r="AA61" s="3">
         <v>34955700</v>
       </c>
-      <c r="AA61" s="3">
+      <c r="AB61" s="3">
         <v>35115500</v>
       </c>
-      <c r="AB61" s="3">
+      <c r="AC61" s="3">
         <v>34009900</v>
       </c>
-      <c r="AC61" s="3">
+      <c r="AD61" s="3">
         <v>36941800</v>
       </c>
-      <c r="AD61" s="3">
+      <c r="AE61" s="3">
         <v>37408900</v>
       </c>
-      <c r="AE61" s="3">
+      <c r="AF61" s="3">
         <v>35000000</v>
       </c>
-      <c r="AF61" s="3">
+      <c r="AG61" s="3">
         <v>33280700</v>
       </c>
-      <c r="AG61" s="3">
+      <c r="AH61" s="3">
         <v>34538700</v>
       </c>
-      <c r="AH61" s="3">
+      <c r="AI61" s="3">
         <v>33926000</v>
       </c>
     </row>
-    <row r="62" spans="3:34" x14ac:dyDescent="0.2">
+    <row r="62" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C62" s="1" t="s">
         <v>55</v>
       </c>
       <c r="D62" s="3">
-        <v>843300</v>
+        <v>969600</v>
       </c>
       <c r="E62" s="3">
-        <v>936800</v>
+        <v>866400</v>
       </c>
       <c r="F62" s="3">
-        <v>798500</v>
+        <v>962500</v>
       </c>
       <c r="G62" s="3">
-        <v>759100</v>
+        <v>820400</v>
       </c>
       <c r="H62" s="3">
-        <v>573600</v>
+        <v>779900</v>
       </c>
       <c r="I62" s="3">
-        <v>447400</v>
+        <v>589300</v>
       </c>
       <c r="J62" s="3">
+        <v>459600</v>
+      </c>
+      <c r="K62" s="3">
         <v>438000</v>
       </c>
-      <c r="K62" s="3">
+      <c r="L62" s="3">
         <v>469900</v>
       </c>
-      <c r="L62" s="3">
+      <c r="M62" s="3">
         <v>523500</v>
       </c>
-      <c r="M62" s="3">
+      <c r="N62" s="3">
         <v>608300</v>
       </c>
-      <c r="N62" s="3">
+      <c r="O62" s="3">
         <v>663300</v>
       </c>
-      <c r="O62" s="3">
+      <c r="P62" s="3">
         <v>620300</v>
       </c>
-      <c r="P62" s="3">
+      <c r="Q62" s="3">
         <v>542300</v>
       </c>
-      <c r="Q62" s="3">
+      <c r="R62" s="3">
         <v>528500</v>
       </c>
-      <c r="R62" s="3">
+      <c r="S62" s="3">
         <v>720700</v>
       </c>
-      <c r="S62" s="3">
+      <c r="T62" s="3">
         <v>691400</v>
       </c>
-      <c r="T62" s="3">
+      <c r="U62" s="3">
         <v>680000</v>
       </c>
-      <c r="U62" s="3">
+      <c r="V62" s="3">
         <v>570200</v>
       </c>
-      <c r="V62" s="3">
+      <c r="W62" s="3">
         <v>714600</v>
       </c>
-      <c r="W62" s="3">
+      <c r="X62" s="3">
         <v>648100</v>
       </c>
-      <c r="X62" s="3">
+      <c r="Y62" s="3">
         <v>618700</v>
       </c>
-      <c r="Y62" s="3">
+      <c r="Z62" s="3">
         <v>520300</v>
       </c>
-      <c r="Z62" s="3">
+      <c r="AA62" s="3">
         <v>418500</v>
       </c>
-      <c r="AA62" s="3">
+      <c r="AB62" s="3">
         <v>420800</v>
       </c>
-      <c r="AB62" s="3">
+      <c r="AC62" s="3">
         <v>527700</v>
       </c>
-      <c r="AC62" s="3">
+      <c r="AD62" s="3">
         <v>419200</v>
       </c>
-      <c r="AD62" s="3">
+      <c r="AE62" s="3">
         <v>395900</v>
       </c>
-      <c r="AE62" s="3">
+      <c r="AF62" s="3">
         <v>382900</v>
       </c>
-      <c r="AF62" s="3">
+      <c r="AG62" s="3">
         <v>400700</v>
       </c>
-      <c r="AG62" s="3">
+      <c r="AH62" s="3">
         <v>463600</v>
       </c>
-      <c r="AH62" s="3">
+      <c r="AI62" s="3">
         <v>459900</v>
       </c>
     </row>
-    <row r="63" spans="3:34" x14ac:dyDescent="0.2">
+    <row r="63" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C63" s="1" t="s">
         <v>56</v>
       </c>
@@ -5641,8 +5790,11 @@
       <c r="AH63" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="64" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI63" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="64" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C64" s="1" t="s">
         <v>20</v>
       </c>
@@ -5739,8 +5891,11 @@
       <c r="AH64" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="65" spans="2:34" x14ac:dyDescent="0.2">
+      <c r="AI64" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="65" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C65" s="1" t="s">
         <v>57</v>
       </c>
@@ -5837,106 +5992,112 @@
       <c r="AH65" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="66" spans="2:34" x14ac:dyDescent="0.2">
+      <c r="AI65" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="66" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C66" s="1" t="s">
         <v>58</v>
       </c>
       <c r="D66" s="3">
-        <v>344956800</v>
+        <v>356485900</v>
       </c>
       <c r="E66" s="3">
-        <v>340426800</v>
+        <v>354407700</v>
       </c>
       <c r="F66" s="3">
-        <v>331662200</v>
+        <v>349753500</v>
       </c>
       <c r="G66" s="3">
-        <v>330446900</v>
+        <v>340748800</v>
       </c>
       <c r="H66" s="3">
-        <v>327346300</v>
+        <v>339500200</v>
       </c>
       <c r="I66" s="3">
-        <v>329750100</v>
+        <v>336314700</v>
       </c>
       <c r="J66" s="3">
+        <v>338784400</v>
+      </c>
+      <c r="K66" s="3">
         <v>345885900</v>
       </c>
-      <c r="K66" s="3">
+      <c r="L66" s="3">
         <v>348018900</v>
       </c>
-      <c r="L66" s="3">
+      <c r="M66" s="3">
         <v>338354200</v>
       </c>
-      <c r="M66" s="3">
+      <c r="N66" s="3">
         <v>316006400</v>
       </c>
-      <c r="N66" s="3">
+      <c r="O66" s="3">
         <v>309651700</v>
       </c>
-      <c r="O66" s="3">
+      <c r="P66" s="3">
         <v>297533600</v>
       </c>
-      <c r="P66" s="3">
+      <c r="Q66" s="3">
         <v>290517700</v>
       </c>
-      <c r="Q66" s="3">
+      <c r="R66" s="3">
         <v>278260300</v>
       </c>
-      <c r="R66" s="3">
+      <c r="S66" s="3">
         <v>275726000</v>
       </c>
-      <c r="S66" s="3">
+      <c r="T66" s="3">
         <v>275487700</v>
       </c>
-      <c r="T66" s="3">
+      <c r="U66" s="3">
         <v>288675900</v>
       </c>
-      <c r="U66" s="3">
+      <c r="V66" s="3">
         <v>289399800</v>
       </c>
-      <c r="V66" s="3">
+      <c r="W66" s="3">
         <v>297278600</v>
       </c>
-      <c r="W66" s="3">
+      <c r="X66" s="3">
         <v>299163500</v>
       </c>
-      <c r="X66" s="3">
+      <c r="Y66" s="3">
         <v>296968200</v>
       </c>
-      <c r="Y66" s="3">
+      <c r="Z66" s="3">
         <v>267714100</v>
       </c>
-      <c r="Z66" s="3">
+      <c r="AA66" s="3">
         <v>249559900</v>
       </c>
-      <c r="AA66" s="3">
+      <c r="AB66" s="3">
         <v>256847800</v>
       </c>
-      <c r="AB66" s="3">
+      <c r="AC66" s="3">
         <v>256582900</v>
       </c>
-      <c r="AC66" s="3">
+      <c r="AD66" s="3">
         <v>260418000</v>
       </c>
-      <c r="AD66" s="3">
+      <c r="AE66" s="3">
         <v>261733600</v>
       </c>
-      <c r="AE66" s="3">
+      <c r="AF66" s="3">
         <v>260311800</v>
       </c>
-      <c r="AF66" s="3">
+      <c r="AG66" s="3">
         <v>255640700</v>
       </c>
-      <c r="AG66" s="3">
+      <c r="AH66" s="3">
         <v>261266900</v>
       </c>
-      <c r="AH66" s="3">
+      <c r="AI66" s="3">
         <v>263136400</v>
       </c>
     </row>
-    <row r="67" spans="2:34" x14ac:dyDescent="0.2">
+    <row r="67" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C67" s="1" t="s">
         <v>59</v>
       </c>
@@ -5971,8 +6132,9 @@
       <c r="AF67" s="3"/>
       <c r="AG67" s="3"/>
       <c r="AH67" s="3"/>
-    </row>
-    <row r="68" spans="2:34" x14ac:dyDescent="0.2">
+      <c r="AI67" s="3"/>
+    </row>
+    <row r="68" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C68" s="1" t="s">
         <v>60</v>
       </c>
@@ -6069,8 +6231,11 @@
       <c r="AH68" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="69" spans="2:34" x14ac:dyDescent="0.2">
+      <c r="AI68" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="69" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C69" s="1" t="s">
         <v>61</v>
       </c>
@@ -6167,8 +6332,11 @@
       <c r="AH69" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="70" spans="2:34" x14ac:dyDescent="0.2">
+      <c r="AI69" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="70" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C70" s="1" t="s">
         <v>62</v>
       </c>
@@ -6265,8 +6433,11 @@
       <c r="AH70" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="71" spans="2:34" x14ac:dyDescent="0.2">
+      <c r="AI70" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="71" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C71" s="1" t="s">
         <v>63</v>
       </c>
@@ -6363,106 +6534,112 @@
       <c r="AH71" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="72" spans="2:34" x14ac:dyDescent="0.2">
+      <c r="AI71" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="72" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C72" s="1" t="s">
         <v>64</v>
       </c>
       <c r="D72" s="3">
-        <v>18364800</v>
+        <v>19437000</v>
       </c>
       <c r="E72" s="3">
-        <v>18240100</v>
+        <v>18868000</v>
       </c>
       <c r="F72" s="3">
-        <v>18387100</v>
+        <v>18739900</v>
       </c>
       <c r="G72" s="3">
-        <v>17850100</v>
+        <v>18890800</v>
       </c>
       <c r="H72" s="3">
-        <v>17417600</v>
+        <v>18339100</v>
       </c>
       <c r="I72" s="3">
-        <v>17337600</v>
+        <v>17894800</v>
       </c>
       <c r="J72" s="3">
+        <v>17812600</v>
+      </c>
+      <c r="K72" s="3">
         <v>17007700</v>
       </c>
-      <c r="K72" s="3">
+      <c r="L72" s="3">
         <v>17130600</v>
       </c>
-      <c r="L72" s="3">
+      <c r="M72" s="3">
         <v>16662400</v>
       </c>
-      <c r="M72" s="3">
+      <c r="N72" s="3">
         <v>16044400</v>
       </c>
-      <c r="N72" s="3">
+      <c r="O72" s="3">
         <v>15764300</v>
       </c>
-      <c r="O72" s="3">
+      <c r="P72" s="3">
         <v>15298800</v>
       </c>
-      <c r="P72" s="3">
+      <c r="Q72" s="3">
         <v>14524300</v>
       </c>
-      <c r="Q72" s="3">
+      <c r="R72" s="3">
         <v>14258500</v>
       </c>
-      <c r="R72" s="3">
+      <c r="S72" s="3">
         <v>14719300</v>
       </c>
-      <c r="S72" s="3">
+      <c r="T72" s="3">
         <v>14362200</v>
       </c>
-      <c r="T72" s="3">
+      <c r="U72" s="3">
         <v>15002800</v>
       </c>
-      <c r="U72" s="3">
+      <c r="V72" s="3">
         <v>15745800</v>
       </c>
-      <c r="V72" s="3">
+      <c r="W72" s="3">
         <v>15573800</v>
       </c>
-      <c r="W72" s="3">
+      <c r="X72" s="3">
         <v>15698600</v>
       </c>
-      <c r="X72" s="3">
+      <c r="Y72" s="3">
         <v>15678000</v>
       </c>
-      <c r="Y72" s="3">
+      <c r="Z72" s="3">
         <v>14384700</v>
       </c>
-      <c r="Z72" s="3">
+      <c r="AA72" s="3">
         <v>13795900</v>
       </c>
-      <c r="AA72" s="3">
+      <c r="AB72" s="3">
         <v>13837700</v>
       </c>
-      <c r="AB72" s="3">
+      <c r="AC72" s="3">
         <v>13273900</v>
       </c>
-      <c r="AC72" s="3">
+      <c r="AD72" s="3">
         <v>13745600</v>
       </c>
-      <c r="AD72" s="3">
+      <c r="AE72" s="3">
         <v>13660700</v>
       </c>
-      <c r="AE72" s="3">
+      <c r="AF72" s="3">
         <v>13507800</v>
       </c>
-      <c r="AF72" s="3">
+      <c r="AG72" s="3">
         <v>13138800</v>
       </c>
-      <c r="AG72" s="3">
+      <c r="AH72" s="3">
         <v>13150400</v>
       </c>
-      <c r="AH72" s="3">
+      <c r="AI72" s="3">
         <v>13062800</v>
       </c>
     </row>
-    <row r="73" spans="2:34" x14ac:dyDescent="0.2">
+    <row r="73" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C73" s="1" t="s">
         <v>65</v>
       </c>
@@ -6559,8 +6736,11 @@
       <c r="AH73" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="74" spans="2:34" x14ac:dyDescent="0.2">
+      <c r="AI73" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="74" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C74" s="1" t="s">
         <v>66</v>
       </c>
@@ -6657,8 +6837,11 @@
       <c r="AH74" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="75" spans="2:34" x14ac:dyDescent="0.2">
+      <c r="AI74" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="75" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C75" s="1" t="s">
         <v>67</v>
       </c>
@@ -6755,106 +6938,112 @@
       <c r="AH75" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="76" spans="2:34" x14ac:dyDescent="0.2">
+      <c r="AI75" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="76" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C76" s="1" t="s">
         <v>68</v>
       </c>
       <c r="D76" s="3">
-        <v>23523400</v>
+        <v>25099900</v>
       </c>
       <c r="E76" s="3">
-        <v>23116800</v>
+        <v>24167800</v>
       </c>
       <c r="F76" s="3">
-        <v>23057200</v>
+        <v>23750200</v>
       </c>
       <c r="G76" s="3">
-        <v>22078600</v>
+        <v>23688900</v>
       </c>
       <c r="H76" s="3">
-        <v>21651600</v>
+        <v>22683500</v>
       </c>
       <c r="I76" s="3">
-        <v>20996200</v>
+        <v>22244800</v>
       </c>
       <c r="J76" s="3">
+        <v>21571400</v>
+      </c>
+      <c r="K76" s="3">
         <v>20624400</v>
       </c>
-      <c r="K76" s="3">
+      <c r="L76" s="3">
         <v>20539800</v>
       </c>
-      <c r="L76" s="3">
+      <c r="M76" s="3">
         <v>20238100</v>
       </c>
-      <c r="M76" s="3">
+      <c r="N76" s="3">
         <v>19381500</v>
       </c>
-      <c r="N76" s="3">
+      <c r="O76" s="3">
         <v>18987000</v>
       </c>
-      <c r="O76" s="3">
+      <c r="P76" s="3">
         <v>18419400</v>
       </c>
-      <c r="P76" s="3">
+      <c r="Q76" s="3">
         <v>17399500</v>
       </c>
-      <c r="Q76" s="3">
+      <c r="R76" s="3">
         <v>17059700</v>
       </c>
-      <c r="R76" s="3">
+      <c r="S76" s="3">
         <v>17519900</v>
       </c>
-      <c r="S76" s="3">
+      <c r="T76" s="3">
         <v>17171900</v>
       </c>
-      <c r="T76" s="3">
+      <c r="U76" s="3">
         <v>17677500</v>
       </c>
-      <c r="U76" s="3">
+      <c r="V76" s="3">
         <v>18283800</v>
       </c>
-      <c r="V76" s="3">
+      <c r="W76" s="3">
         <v>17718000</v>
       </c>
-      <c r="W76" s="3">
+      <c r="X76" s="3">
         <v>17110000</v>
       </c>
-      <c r="X76" s="3">
+      <c r="Y76" s="3">
         <v>17117400</v>
       </c>
-      <c r="Y76" s="3">
+      <c r="Z76" s="3">
         <v>18261500</v>
       </c>
-      <c r="Z76" s="3">
+      <c r="AA76" s="3">
         <v>17579400</v>
       </c>
-      <c r="AA76" s="3">
+      <c r="AB76" s="3">
         <v>17463800</v>
       </c>
-      <c r="AB76" s="3">
+      <c r="AC76" s="3">
         <v>17085700</v>
       </c>
-      <c r="AC76" s="3">
+      <c r="AD76" s="3">
         <v>17922000</v>
       </c>
-      <c r="AD76" s="3">
+      <c r="AE76" s="3">
         <v>17996500</v>
       </c>
-      <c r="AE76" s="3">
+      <c r="AF76" s="3">
         <v>17825600</v>
       </c>
-      <c r="AF76" s="3">
+      <c r="AG76" s="3">
         <v>17960100</v>
       </c>
-      <c r="AG76" s="3">
+      <c r="AH76" s="3">
         <v>18347500</v>
       </c>
-      <c r="AH76" s="3">
+      <c r="AI76" s="3">
         <v>18412300</v>
       </c>
     </row>
-    <row r="77" spans="2:34" x14ac:dyDescent="0.2">
+    <row r="77" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C77" s="1" t="s">
         <v>69</v>
       </c>
@@ -6951,111 +7140,117 @@
       <c r="AH77" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="79" spans="2:34" x14ac:dyDescent="0.2">
+      <c r="AI77" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="79" spans="2:35" x14ac:dyDescent="0.2">
       <c r="B79" s="1" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="80" spans="2:34" x14ac:dyDescent="0.2">
+    <row r="80" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C80" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D80" s="2">
+        <v>45473</v>
+      </c>
+      <c r="E80" s="2">
         <v>45382</v>
       </c>
-      <c r="E80" s="2">
+      <c r="F80" s="2">
         <v>45291</v>
       </c>
-      <c r="F80" s="2">
+      <c r="G80" s="2">
         <v>45199</v>
       </c>
-      <c r="G80" s="2">
+      <c r="H80" s="2">
         <v>45107</v>
       </c>
-      <c r="H80" s="2">
+      <c r="I80" s="2">
         <v>45016</v>
       </c>
-      <c r="I80" s="2">
+      <c r="J80" s="2">
         <v>44926</v>
       </c>
-      <c r="J80" s="2">
+      <c r="K80" s="2">
         <v>44834</v>
       </c>
-      <c r="K80" s="2">
+      <c r="L80" s="2">
         <v>44742</v>
       </c>
-      <c r="L80" s="2">
+      <c r="M80" s="2">
         <v>44651</v>
       </c>
-      <c r="M80" s="2">
+      <c r="N80" s="2">
         <v>44561</v>
       </c>
-      <c r="N80" s="2">
+      <c r="O80" s="2">
         <v>44469</v>
       </c>
-      <c r="O80" s="2">
+      <c r="P80" s="2">
         <v>44377</v>
       </c>
-      <c r="P80" s="2">
+      <c r="Q80" s="2">
         <v>44286</v>
       </c>
-      <c r="Q80" s="2">
+      <c r="R80" s="2">
         <v>44196</v>
       </c>
-      <c r="R80" s="2">
+      <c r="S80" s="2">
         <v>44104</v>
       </c>
-      <c r="S80" s="2">
+      <c r="T80" s="2">
         <v>44012</v>
       </c>
-      <c r="T80" s="2">
+      <c r="U80" s="2">
         <v>43921</v>
       </c>
-      <c r="U80" s="2">
+      <c r="V80" s="2">
         <v>43830</v>
       </c>
-      <c r="V80" s="2">
+      <c r="W80" s="2">
         <v>43738</v>
       </c>
-      <c r="W80" s="2">
+      <c r="X80" s="2">
         <v>43646</v>
       </c>
-      <c r="X80" s="2">
+      <c r="Y80" s="2">
         <v>43555</v>
       </c>
-      <c r="Y80" s="2">
+      <c r="Z80" s="2">
         <v>43465</v>
       </c>
-      <c r="Z80" s="2">
+      <c r="AA80" s="2">
         <v>43373</v>
       </c>
-      <c r="AA80" s="2">
+      <c r="AB80" s="2">
         <v>43281</v>
       </c>
-      <c r="AB80" s="2">
+      <c r="AC80" s="2">
         <v>43190</v>
       </c>
-      <c r="AC80" s="2">
+      <c r="AD80" s="2">
         <v>43100</v>
       </c>
-      <c r="AD80" s="2">
+      <c r="AE80" s="2">
         <v>43008</v>
       </c>
-      <c r="AE80" s="2">
+      <c r="AF80" s="2">
         <v>42916</v>
       </c>
-      <c r="AF80" s="2">
+      <c r="AG80" s="2">
         <v>42825</v>
       </c>
-      <c r="AG80" s="2">
+      <c r="AH80" s="2">
         <v>42735</v>
       </c>
-      <c r="AH80" s="2">
+      <c r="AI80" s="2">
         <v>42643</v>
       </c>
     </row>
-    <row r="81" spans="3:34" x14ac:dyDescent="0.2">
+    <row r="81" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C81" s="1" t="s">
         <v>28</v>
       </c>
@@ -7063,97 +7258,100 @@
         <v>5</v>
       </c>
       <c r="E81" s="3">
-        <v>24000</v>
+        <v>591600</v>
       </c>
       <c r="F81" s="3">
-        <v>632600</v>
+        <v>24600</v>
       </c>
       <c r="G81" s="3">
-        <v>432500</v>
+        <v>649900</v>
       </c>
       <c r="H81" s="3">
-        <v>644800</v>
+        <v>444300</v>
       </c>
       <c r="I81" s="3">
-        <v>329800</v>
+        <v>662500</v>
       </c>
       <c r="J81" s="3">
+        <v>338800</v>
+      </c>
+      <c r="K81" s="3">
         <v>640600</v>
       </c>
-      <c r="K81" s="3">
+      <c r="L81" s="3">
         <v>684400</v>
       </c>
-      <c r="L81" s="3">
+      <c r="M81" s="3">
         <v>631400</v>
       </c>
-      <c r="M81" s="3">
+      <c r="N81" s="3">
         <v>279500</v>
       </c>
-      <c r="N81" s="3">
+      <c r="O81" s="3">
         <v>570700</v>
       </c>
-      <c r="O81" s="3">
+      <c r="P81" s="3">
         <v>552600</v>
       </c>
-      <c r="P81" s="3">
+      <c r="Q81" s="3">
         <v>482000</v>
       </c>
-      <c r="Q81" s="3">
+      <c r="R81" s="3">
         <v>112600</v>
       </c>
-      <c r="R81" s="3">
+      <c r="S81" s="3">
         <v>358800</v>
       </c>
-      <c r="S81" s="3">
+      <c r="T81" s="3">
         <v>100500</v>
       </c>
-      <c r="T81" s="3">
+      <c r="U81" s="3">
         <v>412900</v>
       </c>
-      <c r="U81" s="3">
+      <c r="V81" s="3">
         <v>174900</v>
       </c>
-      <c r="V81" s="3">
+      <c r="W81" s="3">
         <v>410100</v>
       </c>
-      <c r="W81" s="3">
+      <c r="X81" s="3">
         <v>537700</v>
       </c>
-      <c r="X81" s="3">
+      <c r="Y81" s="3">
         <v>517500</v>
       </c>
-      <c r="Y81" s="3">
+      <c r="Z81" s="3">
         <v>76800</v>
       </c>
-      <c r="Z81" s="3">
+      <c r="AA81" s="3">
         <v>453900</v>
       </c>
-      <c r="AA81" s="3">
+      <c r="AB81" s="3">
         <v>569900</v>
       </c>
-      <c r="AB81" s="3">
+      <c r="AC81" s="3">
         <v>463600</v>
       </c>
-      <c r="AC81" s="3">
+      <c r="AD81" s="3">
         <v>84900</v>
       </c>
-      <c r="AD81" s="3">
+      <c r="AE81" s="3">
         <v>212100</v>
       </c>
-      <c r="AE81" s="3">
+      <c r="AF81" s="3">
         <v>369000</v>
       </c>
-      <c r="AF81" s="3">
+      <c r="AG81" s="3">
         <v>517600</v>
       </c>
-      <c r="AG81" s="3">
+      <c r="AH81" s="3">
         <v>88500</v>
       </c>
-      <c r="AH81" s="3">
+      <c r="AI81" s="3">
         <v>275700</v>
       </c>
     </row>
-    <row r="82" spans="3:34" x14ac:dyDescent="0.2">
+    <row r="82" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C82" s="1" t="s">
         <v>71</v>
       </c>
@@ -7188,106 +7386,110 @@
       <c r="AF82" s="3"/>
       <c r="AG82" s="3"/>
       <c r="AH82" s="3"/>
-    </row>
-    <row r="83" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI82" s="3"/>
+    </row>
+    <row r="83" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C83" s="1" t="s">
         <v>72</v>
       </c>
       <c r="D83" s="3">
-        <v>201500</v>
+        <v>216100</v>
       </c>
       <c r="E83" s="3">
-        <v>192600</v>
+        <v>207000</v>
       </c>
       <c r="F83" s="3">
-        <v>175400</v>
+        <v>197900</v>
       </c>
       <c r="G83" s="3">
-        <v>177400</v>
+        <v>180200</v>
       </c>
       <c r="H83" s="3">
-        <v>179600</v>
+        <v>182300</v>
       </c>
       <c r="I83" s="3">
-        <v>180300</v>
+        <v>184500</v>
       </c>
       <c r="J83" s="3">
+        <v>185200</v>
+      </c>
+      <c r="K83" s="3">
         <v>169700</v>
       </c>
-      <c r="K83" s="3">
+      <c r="L83" s="3">
         <v>175600</v>
       </c>
-      <c r="L83" s="3">
+      <c r="M83" s="3">
         <v>168600</v>
       </c>
-      <c r="M83" s="3">
+      <c r="N83" s="3">
         <v>155900</v>
       </c>
-      <c r="N83" s="3">
+      <c r="O83" s="3">
         <v>149200</v>
       </c>
-      <c r="O83" s="3">
+      <c r="P83" s="3">
         <v>184500</v>
       </c>
-      <c r="P83" s="3">
+      <c r="Q83" s="3">
         <v>102900</v>
       </c>
-      <c r="Q83" s="3">
+      <c r="R83" s="3">
         <v>101300</v>
       </c>
-      <c r="R83" s="3">
+      <c r="S83" s="3">
         <v>101500</v>
       </c>
-      <c r="S83" s="3">
+      <c r="T83" s="3">
         <v>98700</v>
       </c>
-      <c r="T83" s="3">
+      <c r="U83" s="3">
         <v>112300</v>
       </c>
-      <c r="U83" s="3">
+      <c r="V83" s="3">
         <v>120400</v>
       </c>
-      <c r="V83" s="3">
+      <c r="W83" s="3">
         <v>116900</v>
       </c>
-      <c r="W83" s="3">
+      <c r="X83" s="3">
         <v>108900</v>
       </c>
-      <c r="X83" s="3">
+      <c r="Y83" s="3">
         <v>93600</v>
       </c>
-      <c r="Y83" s="3">
+      <c r="Z83" s="3">
         <v>61600</v>
       </c>
-      <c r="Z83" s="3">
+      <c r="AA83" s="3">
         <v>58600</v>
       </c>
-      <c r="AA83" s="3">
+      <c r="AB83" s="3">
         <v>56000</v>
       </c>
-      <c r="AB83" s="3">
+      <c r="AC83" s="3">
         <v>50600</v>
       </c>
-      <c r="AC83" s="3">
+      <c r="AD83" s="3">
         <v>49900</v>
       </c>
-      <c r="AD83" s="3">
+      <c r="AE83" s="3">
         <v>50800</v>
       </c>
-      <c r="AE83" s="3">
+      <c r="AF83" s="3">
         <v>51600</v>
       </c>
-      <c r="AF83" s="3">
+      <c r="AG83" s="3">
         <v>55200</v>
       </c>
-      <c r="AG83" s="3">
+      <c r="AH83" s="3">
         <v>54800</v>
       </c>
-      <c r="AH83" s="3">
+      <c r="AI83" s="3">
         <v>53700</v>
       </c>
     </row>
-    <row r="84" spans="3:34" x14ac:dyDescent="0.2">
+    <row r="84" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C84" s="1" t="s">
         <v>73</v>
       </c>
@@ -7384,8 +7586,11 @@
       <c r="AH84" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="85" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI84" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="85" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C85" s="1" t="s">
         <v>74</v>
       </c>
@@ -7482,8 +7687,11 @@
       <c r="AH85" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="86" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI85" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="86" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C86" s="1" t="s">
         <v>75</v>
       </c>
@@ -7580,8 +7788,11 @@
       <c r="AH86" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="87" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI86" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="87" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C87" s="1" t="s">
         <v>76</v>
       </c>
@@ -7678,8 +7889,11 @@
       <c r="AH87" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="88" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI87" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="88" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C88" s="1" t="s">
         <v>77</v>
       </c>
@@ -7776,106 +7990,112 @@
       <c r="AH88" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="89" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI88" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="89" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C89" s="1" t="s">
         <v>78</v>
       </c>
       <c r="D89" s="3">
-        <v>-161100</v>
+        <v>-3559500</v>
       </c>
       <c r="E89" s="3">
-        <v>4619100</v>
+        <v>-165600</v>
       </c>
       <c r="F89" s="3">
-        <v>4521300</v>
+        <v>4745600</v>
       </c>
       <c r="G89" s="3">
-        <v>-5436700</v>
+        <v>4645200</v>
       </c>
       <c r="H89" s="3">
-        <v>-2519600</v>
+        <v>-5585700</v>
       </c>
       <c r="I89" s="3">
-        <v>11691600</v>
+        <v>-2588600</v>
       </c>
       <c r="J89" s="3">
+        <v>12011900</v>
+      </c>
+      <c r="K89" s="3">
         <v>-3350300</v>
       </c>
-      <c r="K89" s="3">
+      <c r="L89" s="3">
         <v>-2130300</v>
       </c>
-      <c r="L89" s="3">
+      <c r="M89" s="3">
         <v>7700600</v>
       </c>
-      <c r="M89" s="3">
+      <c r="N89" s="3">
         <v>4027400</v>
       </c>
-      <c r="N89" s="3">
+      <c r="O89" s="3">
         <v>2586700</v>
       </c>
-      <c r="O89" s="3">
+      <c r="P89" s="3">
         <v>-4607300</v>
       </c>
-      <c r="P89" s="3">
+      <c r="Q89" s="3">
         <v>831700</v>
       </c>
-      <c r="Q89" s="3">
+      <c r="R89" s="3">
         <v>1545900</v>
       </c>
-      <c r="R89" s="3">
+      <c r="S89" s="3">
         <v>-766500</v>
       </c>
-      <c r="S89" s="3">
+      <c r="T89" s="3">
         <v>2718500</v>
       </c>
-      <c r="T89" s="3">
+      <c r="U89" s="3">
         <v>-824700</v>
       </c>
-      <c r="U89" s="3">
+      <c r="V89" s="3">
         <v>-153300</v>
       </c>
-      <c r="V89" s="3">
+      <c r="W89" s="3">
         <v>-428600</v>
       </c>
-      <c r="W89" s="3">
+      <c r="X89" s="3">
         <v>3501700</v>
       </c>
-      <c r="X89" s="3">
+      <c r="Y89" s="3">
         <v>-1296100</v>
       </c>
-      <c r="Y89" s="3">
+      <c r="Z89" s="3">
         <v>5231600</v>
       </c>
-      <c r="Z89" s="3">
+      <c r="AA89" s="3">
         <v>908000</v>
       </c>
-      <c r="AA89" s="3">
+      <c r="AB89" s="3">
         <v>643600</v>
       </c>
-      <c r="AB89" s="3">
+      <c r="AC89" s="3">
         <v>877700</v>
       </c>
-      <c r="AC89" s="3">
+      <c r="AD89" s="3">
         <v>-506300</v>
       </c>
-      <c r="AD89" s="3">
+      <c r="AE89" s="3">
         <v>-2456000</v>
       </c>
-      <c r="AE89" s="3">
+      <c r="AF89" s="3">
         <v>-340700</v>
       </c>
-      <c r="AF89" s="3">
+      <c r="AG89" s="3">
         <v>1561500</v>
       </c>
-      <c r="AG89" s="3">
+      <c r="AH89" s="3">
         <v>108800</v>
       </c>
-      <c r="AH89" s="3">
+      <c r="AI89" s="3">
         <v>3807600</v>
       </c>
     </row>
-    <row r="90" spans="3:34" x14ac:dyDescent="0.2">
+    <row r="90" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C90" s="1" t="s">
         <v>79</v>
       </c>
@@ -7910,106 +8130,110 @@
       <c r="AF90" s="3"/>
       <c r="AG90" s="3"/>
       <c r="AH90" s="3"/>
-    </row>
-    <row r="91" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI90" s="3"/>
+    </row>
+    <row r="91" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C91" s="1" t="s">
         <v>80</v>
       </c>
       <c r="D91" s="3">
+        <v>-121377000</v>
+      </c>
+      <c r="E91" s="3">
         <v>-77550000</v>
       </c>
-      <c r="E91" s="3">
+      <c r="F91" s="3">
         <v>-161762000</v>
       </c>
-      <c r="F91" s="3">
+      <c r="G91" s="3">
         <v>-68486000</v>
       </c>
-      <c r="G91" s="3">
+      <c r="H91" s="3">
         <v>-103704000</v>
       </c>
-      <c r="H91" s="3">
+      <c r="I91" s="3">
         <v>-59247000</v>
       </c>
-      <c r="I91" s="3">
+      <c r="J91" s="3">
         <v>-113722000</v>
       </c>
-      <c r="J91" s="3">
+      <c r="K91" s="3">
         <v>-77226000</v>
       </c>
-      <c r="K91" s="3">
+      <c r="L91" s="3">
         <v>-104059000</v>
       </c>
-      <c r="L91" s="3">
+      <c r="M91" s="3">
         <v>-52618000</v>
       </c>
-      <c r="M91" s="3">
+      <c r="N91" s="3">
         <v>-74615000</v>
       </c>
-      <c r="N91" s="3">
+      <c r="O91" s="3">
         <v>-81614000</v>
       </c>
-      <c r="O91" s="3">
+      <c r="P91" s="3">
         <v>-15900</v>
       </c>
-      <c r="P91" s="3">
+      <c r="Q91" s="3">
         <v>-14300</v>
       </c>
-      <c r="Q91" s="3">
+      <c r="R91" s="3">
         <v>-43600</v>
       </c>
-      <c r="R91" s="3">
+      <c r="S91" s="3">
         <v>-25600</v>
       </c>
-      <c r="S91" s="3">
+      <c r="T91" s="3">
         <v>-24800</v>
       </c>
-      <c r="T91" s="3">
+      <c r="U91" s="3">
         <v>-20300</v>
       </c>
-      <c r="U91" s="3">
+      <c r="V91" s="3">
         <v>-190900</v>
       </c>
-      <c r="V91" s="3">
+      <c r="W91" s="3">
         <v>-91000</v>
       </c>
-      <c r="W91" s="3">
+      <c r="X91" s="3">
         <v>-55400</v>
       </c>
-      <c r="X91" s="3">
+      <c r="Y91" s="3">
         <v>-31700</v>
       </c>
-      <c r="Y91" s="3">
+      <c r="Z91" s="3">
         <v>-43000</v>
       </c>
-      <c r="Z91" s="3">
+      <c r="AA91" s="3">
         <v>-20100</v>
       </c>
-      <c r="AA91" s="3">
+      <c r="AB91" s="3">
         <v>-18000</v>
       </c>
-      <c r="AB91" s="3">
+      <c r="AC91" s="3">
         <v>-17800</v>
       </c>
-      <c r="AC91" s="3">
+      <c r="AD91" s="3">
         <v>-25100</v>
       </c>
-      <c r="AD91" s="3">
+      <c r="AE91" s="3">
         <v>-57300</v>
       </c>
-      <c r="AE91" s="3">
+      <c r="AF91" s="3">
         <v>-37900</v>
       </c>
-      <c r="AF91" s="3">
+      <c r="AG91" s="3">
         <v>-22400</v>
       </c>
-      <c r="AG91" s="3">
+      <c r="AH91" s="3">
         <v>-111600</v>
       </c>
-      <c r="AH91" s="3">
+      <c r="AI91" s="3">
         <v>-90400</v>
       </c>
     </row>
-    <row r="92" spans="3:34" x14ac:dyDescent="0.2">
+    <row r="92" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C92" s="1" t="s">
         <v>81</v>
       </c>
@@ -8106,8 +8330,11 @@
       <c r="AH92" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="93" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI92" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="93" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C93" s="1" t="s">
         <v>82</v>
       </c>
@@ -8204,106 +8431,112 @@
       <c r="AH93" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="94" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI93" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="94" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C94" s="1" t="s">
         <v>83</v>
       </c>
       <c r="D94" s="3">
-        <v>1806200</v>
+        <v>-1129000</v>
       </c>
       <c r="E94" s="3">
-        <v>-592000</v>
+        <v>1855700</v>
       </c>
       <c r="F94" s="3">
-        <v>-1088400</v>
+        <v>-608200</v>
       </c>
       <c r="G94" s="3">
-        <v>-251500</v>
+        <v>-1118200</v>
       </c>
       <c r="H94" s="3">
-        <v>286300</v>
+        <v>-258400</v>
       </c>
       <c r="I94" s="3">
-        <v>-2832800</v>
+        <v>294200</v>
       </c>
       <c r="J94" s="3">
+        <v>-2910400</v>
+      </c>
+      <c r="K94" s="3">
         <v>-2354900</v>
       </c>
-      <c r="K94" s="3">
+      <c r="L94" s="3">
         <v>2353800</v>
       </c>
-      <c r="L94" s="3">
+      <c r="M94" s="3">
         <v>-2278800</v>
       </c>
-      <c r="M94" s="3">
+      <c r="N94" s="3">
         <v>-4489600</v>
       </c>
-      <c r="N94" s="3">
+      <c r="O94" s="3">
         <v>-3902300</v>
       </c>
-      <c r="O94" s="3">
+      <c r="P94" s="3">
         <v>1124900</v>
       </c>
-      <c r="P94" s="3">
+      <c r="Q94" s="3">
         <v>-723400</v>
       </c>
-      <c r="Q94" s="3">
+      <c r="R94" s="3">
         <v>-365200</v>
       </c>
-      <c r="R94" s="3">
+      <c r="S94" s="3">
         <v>-124500</v>
       </c>
-      <c r="S94" s="3">
+      <c r="T94" s="3">
         <v>-446100</v>
       </c>
-      <c r="T94" s="3">
+      <c r="U94" s="3">
         <v>-179800</v>
       </c>
-      <c r="U94" s="3">
+      <c r="V94" s="3">
         <v>-962200</v>
       </c>
-      <c r="V94" s="3">
+      <c r="W94" s="3">
         <v>-913600</v>
       </c>
-      <c r="W94" s="3">
+      <c r="X94" s="3">
         <v>-5520900</v>
       </c>
-      <c r="X94" s="3">
+      <c r="Y94" s="3">
         <v>-97900</v>
       </c>
-      <c r="Y94" s="3">
+      <c r="Z94" s="3">
         <v>-5105000</v>
       </c>
-      <c r="Z94" s="3">
+      <c r="AA94" s="3">
         <v>-2452600</v>
       </c>
-      <c r="AA94" s="3">
+      <c r="AB94" s="3">
         <v>-1063800</v>
       </c>
-      <c r="AB94" s="3">
+      <c r="AC94" s="3">
         <v>-587600</v>
       </c>
-      <c r="AC94" s="3">
+      <c r="AD94" s="3">
         <v>1277600</v>
       </c>
-      <c r="AD94" s="3">
+      <c r="AE94" s="3">
         <v>-195600</v>
       </c>
-      <c r="AE94" s="3">
+      <c r="AF94" s="3">
         <v>183200</v>
       </c>
-      <c r="AF94" s="3">
+      <c r="AG94" s="3">
         <v>392500</v>
       </c>
-      <c r="AG94" s="3">
+      <c r="AH94" s="3">
         <v>-2371700</v>
       </c>
-      <c r="AH94" s="3">
+      <c r="AI94" s="3">
         <v>694800</v>
       </c>
     </row>
-    <row r="95" spans="3:34" x14ac:dyDescent="0.2">
+    <row r="95" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C95" s="1" t="s">
         <v>84</v>
       </c>
@@ -8338,8 +8571,9 @@
       <c r="AF95" s="3"/>
       <c r="AG95" s="3"/>
       <c r="AH95" s="3"/>
-    </row>
-    <row r="96" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI95" s="3"/>
+    </row>
+    <row r="96" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C96" s="1" t="s">
         <v>85</v>
       </c>
@@ -8347,13 +8581,13 @@
         <v>0</v>
       </c>
       <c r="E96" s="3">
-        <v>-98200</v>
+        <v>0</v>
       </c>
       <c r="F96" s="3">
-        <v>-95400</v>
+        <v>-100900</v>
       </c>
       <c r="G96" s="3">
-        <v>0</v>
+        <v>-98000</v>
       </c>
       <c r="H96" s="3">
         <v>0</v>
@@ -8362,11 +8596,11 @@
         <v>0</v>
       </c>
       <c r="J96" s="3">
+        <v>0</v>
+      </c>
+      <c r="K96" s="3">
         <v>-79700</v>
       </c>
-      <c r="K96" s="3">
-        <v>0</v>
-      </c>
       <c r="L96" s="3">
         <v>0</v>
       </c>
@@ -8374,11 +8608,11 @@
         <v>0</v>
       </c>
       <c r="N96" s="3">
+        <v>0</v>
+      </c>
+      <c r="O96" s="3">
         <v>-81300</v>
       </c>
-      <c r="O96" s="3">
-        <v>0</v>
-      </c>
       <c r="P96" s="3">
         <v>0</v>
       </c>
@@ -8422,22 +8656,25 @@
         <v>0</v>
       </c>
       <c r="AD96" s="3">
+        <v>0</v>
+      </c>
+      <c r="AE96" s="3">
         <v>-59200</v>
       </c>
-      <c r="AE96" s="3">
+      <c r="AF96" s="3">
         <v>-237000</v>
       </c>
-      <c r="AF96" s="3">
-        <v>0</v>
-      </c>
       <c r="AG96" s="3">
+        <v>0</v>
+      </c>
+      <c r="AH96" s="3">
         <v>-38100</v>
       </c>
-      <c r="AH96" s="3">
+      <c r="AI96" s="3">
         <v>-22800</v>
       </c>
     </row>
-    <row r="97" spans="3:34" x14ac:dyDescent="0.2">
+    <row r="97" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C97" s="1" t="s">
         <v>86</v>
       </c>
@@ -8534,8 +8771,11 @@
       <c r="AH97" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="98" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI97" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="98" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C98" s="1" t="s">
         <v>87</v>
       </c>
@@ -8632,8 +8872,11 @@
       <c r="AH98" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="99" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI98" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="99" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C99" s="1" t="s">
         <v>88</v>
       </c>
@@ -8730,298 +8973,310 @@
       <c r="AH99" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="100" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI99" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="100" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C100" s="1" t="s">
         <v>89</v>
       </c>
       <c r="D100" s="3">
-        <v>-897200</v>
+        <v>-397200</v>
       </c>
       <c r="E100" s="3">
-        <v>-452100</v>
+        <v>-921800</v>
       </c>
       <c r="F100" s="3">
-        <v>-392700</v>
+        <v>-464400</v>
       </c>
       <c r="G100" s="3">
-        <v>-997300</v>
+        <v>-403400</v>
       </c>
       <c r="H100" s="3">
-        <v>-245900</v>
+        <v>-1024600</v>
       </c>
       <c r="I100" s="3">
-        <v>-5010000</v>
+        <v>-252600</v>
       </c>
       <c r="J100" s="3">
+        <v>-5147300</v>
+      </c>
+      <c r="K100" s="3">
         <v>1697300</v>
       </c>
-      <c r="K100" s="3">
+      <c r="L100" s="3">
         <v>3000400</v>
       </c>
-      <c r="L100" s="3">
+      <c r="M100" s="3">
         <v>1932700</v>
       </c>
-      <c r="M100" s="3">
+      <c r="N100" s="3">
         <v>2031800</v>
       </c>
-      <c r="N100" s="3">
+      <c r="O100" s="3">
         <v>1404600</v>
       </c>
-      <c r="O100" s="3">
+      <c r="P100" s="3">
         <v>2911000</v>
       </c>
-      <c r="P100" s="3">
+      <c r="Q100" s="3">
         <v>453200</v>
       </c>
-      <c r="Q100" s="3">
+      <c r="R100" s="3">
         <v>261800</v>
       </c>
-      <c r="R100" s="3">
+      <c r="S100" s="3">
         <v>553800</v>
       </c>
-      <c r="S100" s="3">
+      <c r="T100" s="3">
         <v>-2356000</v>
       </c>
-      <c r="T100" s="3">
+      <c r="U100" s="3">
         <v>3526800</v>
       </c>
-      <c r="U100" s="3">
+      <c r="V100" s="3">
         <v>-950700</v>
       </c>
-      <c r="V100" s="3">
+      <c r="W100" s="3">
         <v>3000500</v>
       </c>
-      <c r="W100" s="3">
+      <c r="X100" s="3">
         <v>3588600</v>
       </c>
-      <c r="X100" s="3">
+      <c r="Y100" s="3">
         <v>-289800</v>
       </c>
-      <c r="Y100" s="3">
+      <c r="Z100" s="3">
         <v>491400</v>
       </c>
-      <c r="Z100" s="3">
+      <c r="AA100" s="3">
         <v>1689200</v>
       </c>
-      <c r="AA100" s="3">
+      <c r="AB100" s="3">
         <v>354700</v>
       </c>
-      <c r="AB100" s="3">
+      <c r="AC100" s="3">
         <v>-1323700</v>
       </c>
-      <c r="AC100" s="3">
+      <c r="AD100" s="3">
         <v>-309500</v>
       </c>
-      <c r="AD100" s="3">
+      <c r="AE100" s="3">
         <v>2140800</v>
       </c>
-      <c r="AE100" s="3">
+      <c r="AF100" s="3">
         <v>-384900</v>
       </c>
-      <c r="AF100" s="3">
+      <c r="AG100" s="3">
         <v>-1500100</v>
       </c>
-      <c r="AG100" s="3">
+      <c r="AH100" s="3">
         <v>1503800</v>
       </c>
-      <c r="AH100" s="3">
+      <c r="AI100" s="3">
         <v>-1778900</v>
       </c>
     </row>
-    <row r="101" spans="3:34" x14ac:dyDescent="0.2">
+    <row r="101" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C101" s="1" t="s">
         <v>90</v>
       </c>
       <c r="D101" s="3">
-        <v>257800</v>
+        <v>238700</v>
       </c>
       <c r="E101" s="3">
-        <v>-169700</v>
+        <v>264800</v>
       </c>
       <c r="F101" s="3">
-        <v>26800</v>
+        <v>-174400</v>
       </c>
       <c r="G101" s="3">
-        <v>-101100</v>
+        <v>27500</v>
       </c>
       <c r="H101" s="3">
-        <v>119800</v>
+        <v>-103800</v>
       </c>
       <c r="I101" s="3">
-        <v>-1439700</v>
+        <v>123000</v>
       </c>
       <c r="J101" s="3">
+        <v>-1479100</v>
+      </c>
+      <c r="K101" s="3">
         <v>638600</v>
       </c>
-      <c r="K101" s="3">
+      <c r="L101" s="3">
         <v>657000</v>
       </c>
-      <c r="L101" s="3">
+      <c r="M101" s="3">
         <v>203100</v>
       </c>
-      <c r="M101" s="3">
+      <c r="N101" s="3">
         <v>68900</v>
       </c>
-      <c r="N101" s="3">
+      <c r="O101" s="3">
         <v>409500</v>
       </c>
-      <c r="O101" s="3">
+      <c r="P101" s="3">
         <v>18100</v>
       </c>
-      <c r="P101" s="3">
+      <c r="Q101" s="3">
         <v>295500</v>
       </c>
-      <c r="Q101" s="3">
+      <c r="R101" s="3">
         <v>-571700</v>
       </c>
-      <c r="R101" s="3">
+      <c r="S101" s="3">
         <v>-142900</v>
       </c>
-      <c r="S101" s="3">
+      <c r="T101" s="3">
         <v>-159900</v>
       </c>
-      <c r="T101" s="3">
+      <c r="U101" s="3">
         <v>200400</v>
       </c>
-      <c r="U101" s="3">
+      <c r="V101" s="3">
         <v>369400</v>
       </c>
-      <c r="V101" s="3">
+      <c r="W101" s="3">
         <v>-340600</v>
       </c>
-      <c r="W101" s="3">
+      <c r="X101" s="3">
         <v>51200</v>
       </c>
-      <c r="X101" s="3">
+      <c r="Y101" s="3">
         <v>90500</v>
       </c>
-      <c r="Y101" s="3">
+      <c r="Z101" s="3">
         <v>6400</v>
       </c>
-      <c r="Z101" s="3">
+      <c r="AA101" s="3">
         <v>-76600</v>
       </c>
-      <c r="AA101" s="3">
+      <c r="AB101" s="3">
         <v>218900</v>
       </c>
-      <c r="AB101" s="3">
+      <c r="AC101" s="3">
         <v>50500</v>
       </c>
-      <c r="AC101" s="3">
+      <c r="AD101" s="3">
         <v>-377500</v>
       </c>
-      <c r="AD101" s="3">
+      <c r="AE101" s="3">
         <v>14000</v>
       </c>
-      <c r="AE101" s="3">
+      <c r="AF101" s="3">
         <v>8400</v>
       </c>
-      <c r="AF101" s="3">
+      <c r="AG101" s="3">
         <v>-108300</v>
       </c>
-      <c r="AG101" s="3">
+      <c r="AH101" s="3">
         <v>138000</v>
       </c>
-      <c r="AH101" s="3">
+      <c r="AI101" s="3">
         <v>-105900</v>
       </c>
     </row>
-    <row r="102" spans="3:34" x14ac:dyDescent="0.2">
+    <row r="102" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C102" s="1" t="s">
         <v>91</v>
       </c>
       <c r="D102" s="3">
-        <v>1005700</v>
+        <v>-4847000</v>
       </c>
       <c r="E102" s="3">
-        <v>3405300</v>
+        <v>1033200</v>
       </c>
       <c r="F102" s="3">
-        <v>3067100</v>
+        <v>3498600</v>
       </c>
       <c r="G102" s="3">
-        <v>-6786600</v>
+        <v>3151100</v>
       </c>
       <c r="H102" s="3">
-        <v>-2359400</v>
+        <v>-6972500</v>
       </c>
       <c r="I102" s="3">
-        <v>2409100</v>
+        <v>-2424100</v>
       </c>
       <c r="J102" s="3">
+        <v>2475100</v>
+      </c>
+      <c r="K102" s="3">
         <v>-3369400</v>
       </c>
-      <c r="K102" s="3">
+      <c r="L102" s="3">
         <v>3880900</v>
       </c>
-      <c r="L102" s="3">
+      <c r="M102" s="3">
         <v>7557600</v>
       </c>
-      <c r="M102" s="3">
+      <c r="N102" s="3">
         <v>1638600</v>
       </c>
-      <c r="N102" s="3">
+      <c r="O102" s="3">
         <v>498500</v>
       </c>
-      <c r="O102" s="3">
+      <c r="P102" s="3">
         <v>-553300</v>
       </c>
-      <c r="P102" s="3">
+      <c r="Q102" s="3">
         <v>857000</v>
       </c>
-      <c r="Q102" s="3">
+      <c r="R102" s="3">
         <v>870800</v>
       </c>
-      <c r="R102" s="3">
+      <c r="S102" s="3">
         <v>-480000</v>
       </c>
-      <c r="S102" s="3">
+      <c r="T102" s="3">
         <v>-243500</v>
       </c>
-      <c r="T102" s="3">
+      <c r="U102" s="3">
         <v>2722600</v>
       </c>
-      <c r="U102" s="3">
+      <c r="V102" s="3">
         <v>-1696800</v>
       </c>
-      <c r="V102" s="3">
+      <c r="W102" s="3">
         <v>1317700</v>
       </c>
-      <c r="W102" s="3">
+      <c r="X102" s="3">
         <v>1620600</v>
       </c>
-      <c r="X102" s="3">
+      <c r="Y102" s="3">
         <v>-1593300</v>
       </c>
-      <c r="Y102" s="3">
+      <c r="Z102" s="3">
         <v>624400</v>
       </c>
-      <c r="Z102" s="3">
+      <c r="AA102" s="3">
         <v>68000</v>
       </c>
-      <c r="AA102" s="3">
+      <c r="AB102" s="3">
         <v>153400</v>
       </c>
-      <c r="AB102" s="3">
+      <c r="AC102" s="3">
         <v>-983000</v>
       </c>
-      <c r="AC102" s="3">
+      <c r="AD102" s="3">
         <v>84300</v>
       </c>
-      <c r="AD102" s="3">
+      <c r="AE102" s="3">
         <v>-496900</v>
       </c>
-      <c r="AE102" s="3">
+      <c r="AF102" s="3">
         <v>-534100</v>
       </c>
-      <c r="AF102" s="3">
+      <c r="AG102" s="3">
         <v>345600</v>
       </c>
-      <c r="AG102" s="3">
+      <c r="AH102" s="3">
         <v>-621200</v>
       </c>
-      <c r="AH102" s="3">
+      <c r="AI102" s="3">
         <v>2617600</v>
       </c>
     </row>

--- a/AAII_Financials/Quarterly/WF_QTR_FIN.xlsx
+++ b/AAII_Financials/Quarterly/WF_QTR_FIN.xlsx
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="203" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="194" uniqueCount="92">
   <si>
     <t>WF</t>
   </si>
@@ -656,261 +656,262 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet2"/>
-  <dimension ref="A5:AI102"/>
+  <dimension ref="A5:AJ102"/>
   <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="5" style="1" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="26.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="69.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="17" style="1" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="16" style="1" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="17" style="1" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="16" style="1" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="17" style="1" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="16" style="1" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="17" style="1" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="16" style="1" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="17" style="1" bestFit="1" customWidth="1"/>
-    <col min="13" max="35" width="16" style="1" bestFit="1" customWidth="1"/>
-    <col min="36" max="16384" width="9.140625" style="1"/>
+    <col min="4" max="10" width="16" style="1" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="17" style="1" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="16" style="1" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="17" style="1" bestFit="1" customWidth="1"/>
+    <col min="14" max="36" width="16" style="1" bestFit="1" customWidth="1"/>
+    <col min="37" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
-    <row r="5" spans="1:35" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:36" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:35" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:36" x14ac:dyDescent="0.2">
       <c r="B6" s="1" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:35" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:36" x14ac:dyDescent="0.2">
       <c r="C7" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D7" s="2">
+        <v>45565</v>
+      </c>
+      <c r="E7" s="2">
         <v>45473</v>
       </c>
-      <c r="E7" s="2">
+      <c r="F7" s="2">
         <v>45382</v>
       </c>
-      <c r="F7" s="2">
+      <c r="G7" s="2">
         <v>45291</v>
       </c>
-      <c r="G7" s="2">
+      <c r="H7" s="2">
         <v>45199</v>
       </c>
-      <c r="H7" s="2">
+      <c r="I7" s="2">
         <v>45107</v>
       </c>
-      <c r="I7" s="2">
+      <c r="J7" s="2">
         <v>45016</v>
       </c>
-      <c r="J7" s="2">
+      <c r="K7" s="2">
         <v>44926</v>
       </c>
-      <c r="K7" s="2">
+      <c r="L7" s="2">
         <v>44834</v>
       </c>
-      <c r="L7" s="2">
+      <c r="M7" s="2">
         <v>44742</v>
       </c>
-      <c r="M7" s="2">
+      <c r="N7" s="2">
         <v>44651</v>
       </c>
-      <c r="N7" s="2">
+      <c r="O7" s="2">
         <v>44561</v>
       </c>
-      <c r="O7" s="2">
+      <c r="P7" s="2">
         <v>44469</v>
       </c>
-      <c r="P7" s="2">
+      <c r="Q7" s="2">
         <v>44377</v>
       </c>
-      <c r="Q7" s="2">
+      <c r="R7" s="2">
         <v>44286</v>
       </c>
-      <c r="R7" s="2">
+      <c r="S7" s="2">
         <v>44196</v>
       </c>
-      <c r="S7" s="2">
+      <c r="T7" s="2">
         <v>44104</v>
       </c>
-      <c r="T7" s="2">
+      <c r="U7" s="2">
         <v>44012</v>
       </c>
-      <c r="U7" s="2">
+      <c r="V7" s="2">
         <v>43921</v>
       </c>
-      <c r="V7" s="2">
+      <c r="W7" s="2">
         <v>43830</v>
       </c>
-      <c r="W7" s="2">
+      <c r="X7" s="2">
         <v>43738</v>
       </c>
-      <c r="X7" s="2">
+      <c r="Y7" s="2">
         <v>43646</v>
       </c>
-      <c r="Y7" s="2">
+      <c r="Z7" s="2">
         <v>43555</v>
       </c>
-      <c r="Z7" s="2">
+      <c r="AA7" s="2">
         <v>43465</v>
       </c>
-      <c r="AA7" s="2">
+      <c r="AB7" s="2">
         <v>43373</v>
       </c>
-      <c r="AB7" s="2">
+      <c r="AC7" s="2">
         <v>43281</v>
       </c>
-      <c r="AC7" s="2">
+      <c r="AD7" s="2">
         <v>43190</v>
       </c>
-      <c r="AD7" s="2">
+      <c r="AE7" s="2">
         <v>43100</v>
       </c>
-      <c r="AE7" s="2">
+      <c r="AF7" s="2">
         <v>43008</v>
       </c>
-      <c r="AF7" s="2">
+      <c r="AG7" s="2">
         <v>42916</v>
       </c>
-      <c r="AG7" s="2">
+      <c r="AH7" s="2">
         <v>42825</v>
       </c>
-      <c r="AH7" s="2">
+      <c r="AI7" s="2">
         <v>42735</v>
       </c>
-      <c r="AI7" s="2">
+      <c r="AJ7" s="2">
         <v>42643</v>
       </c>
     </row>
-    <row r="8" spans="1:35" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:36" x14ac:dyDescent="0.2">
       <c r="C8" s="1" t="s">
         <v>3</v>
       </c>
-      <c r="D8" s="3" t="s">
-        <v>5</v>
+      <c r="D8" s="3">
+        <v>1797600</v>
       </c>
       <c r="E8" s="3">
-        <v>4102100</v>
+        <v>2144400</v>
       </c>
       <c r="F8" s="3">
-        <v>4068300</v>
+        <v>2219900</v>
       </c>
       <c r="G8" s="3">
-        <v>3929500</v>
+        <v>1187700</v>
       </c>
       <c r="H8" s="3">
-        <v>3786600</v>
+        <v>2101400</v>
       </c>
       <c r="I8" s="3">
-        <v>3696900</v>
+        <v>1748600</v>
       </c>
       <c r="J8" s="3">
+        <v>2091700</v>
+      </c>
+      <c r="K8" s="3">
         <v>3462200</v>
       </c>
-      <c r="K8" s="3">
+      <c r="L8" s="3">
         <v>2792200</v>
       </c>
-      <c r="L8" s="3">
+      <c r="M8" s="3">
         <v>2487200</v>
       </c>
-      <c r="M8" s="3">
+      <c r="N8" s="3">
         <v>2264400</v>
       </c>
-      <c r="N8" s="3">
+      <c r="O8" s="3">
         <v>2026000</v>
       </c>
-      <c r="O8" s="3">
+      <c r="P8" s="3">
         <v>1862200</v>
       </c>
-      <c r="P8" s="3">
+      <c r="Q8" s="3">
         <v>1787500</v>
       </c>
-      <c r="Q8" s="3">
+      <c r="R8" s="3">
         <v>1722100</v>
       </c>
-      <c r="R8" s="3">
+      <c r="S8" s="3">
         <v>1728200</v>
       </c>
-      <c r="S8" s="3">
+      <c r="T8" s="3">
         <v>1749800</v>
       </c>
-      <c r="T8" s="3">
+      <c r="U8" s="3">
         <v>1857400</v>
       </c>
-      <c r="U8" s="3">
+      <c r="V8" s="3">
         <v>2028100</v>
       </c>
-      <c r="V8" s="3">
+      <c r="W8" s="3">
         <v>2216400</v>
       </c>
-      <c r="W8" s="3">
+      <c r="X8" s="3">
         <v>2287800</v>
       </c>
-      <c r="X8" s="3">
+      <c r="Y8" s="3">
         <v>2353100</v>
       </c>
-      <c r="Y8" s="3">
+      <c r="Z8" s="3">
         <v>2369400</v>
       </c>
-      <c r="Z8" s="3">
+      <c r="AA8" s="3">
         <v>2154000</v>
       </c>
-      <c r="AA8" s="3">
+      <c r="AB8" s="3">
         <v>2006200</v>
       </c>
-      <c r="AB8" s="3">
+      <c r="AC8" s="3">
         <v>1989700</v>
       </c>
-      <c r="AC8" s="3">
+      <c r="AD8" s="3">
         <v>1910800</v>
       </c>
-      <c r="AD8" s="3">
+      <c r="AE8" s="3">
         <v>1912500</v>
       </c>
-      <c r="AE8" s="3">
+      <c r="AF8" s="3">
         <v>1925300</v>
       </c>
-      <c r="AF8" s="3">
+      <c r="AG8" s="3">
         <v>1853100</v>
       </c>
-      <c r="AG8" s="3">
+      <c r="AH8" s="3">
         <v>1833700</v>
       </c>
-      <c r="AH8" s="3">
+      <c r="AI8" s="3">
         <v>1898800</v>
       </c>
-      <c r="AI8" s="3">
+      <c r="AJ8" s="3">
         <v>1898000</v>
       </c>
     </row>
-    <row r="9" spans="1:35" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:36" x14ac:dyDescent="0.2">
       <c r="C9" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="D9" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="E9" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="F9" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="G9" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="H9" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="I9" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="J9" s="3" t="s">
-        <v>5</v>
+      <c r="D9" s="3">
+        <v>7600</v>
+      </c>
+      <c r="E9" s="3">
+        <v>7000</v>
+      </c>
+      <c r="F9" s="3">
+        <v>7100</v>
+      </c>
+      <c r="G9" s="3">
+        <v>9400</v>
+      </c>
+      <c r="H9" s="3">
+        <v>6800</v>
+      </c>
+      <c r="I9" s="3">
+        <v>6800</v>
+      </c>
+      <c r="J9" s="3">
+        <v>7100</v>
       </c>
       <c r="K9" s="3" t="s">
         <v>5</v>
@@ -987,31 +988,34 @@
       <c r="AI9" s="3" t="s">
         <v>5</v>
       </c>
+      <c r="AJ9" s="3" t="s">
+        <v>5</v>
+      </c>
     </row>
-    <row r="10" spans="1:35" x14ac:dyDescent="0.2">
+    <row r="10" spans="1:36" x14ac:dyDescent="0.2">
       <c r="C10" s="1" t="s">
         <v>6</v>
       </c>
-      <c r="D10" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="E10" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="F10" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="G10" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="H10" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="I10" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="J10" s="3" t="s">
-        <v>5</v>
+      <c r="D10" s="3">
+        <v>1790000</v>
+      </c>
+      <c r="E10" s="3">
+        <v>2137400</v>
+      </c>
+      <c r="F10" s="3">
+        <v>2212800</v>
+      </c>
+      <c r="G10" s="3">
+        <v>1178300</v>
+      </c>
+      <c r="H10" s="3">
+        <v>2094600</v>
+      </c>
+      <c r="I10" s="3">
+        <v>1741800</v>
+      </c>
+      <c r="J10" s="3">
+        <v>2084600</v>
       </c>
       <c r="K10" s="3" t="s">
         <v>5</v>
@@ -1088,8 +1092,11 @@
       <c r="AI10" s="3" t="s">
         <v>5</v>
       </c>
+      <c r="AJ10" s="3" t="s">
+        <v>5</v>
+      </c>
     </row>
-    <row r="11" spans="1:35" x14ac:dyDescent="0.2">
+    <row r="11" spans="1:36" x14ac:dyDescent="0.2">
       <c r="C11" s="1" t="s">
         <v>7</v>
       </c>
@@ -1125,8 +1132,9 @@
       <c r="AG11" s="3"/>
       <c r="AH11" s="3"/>
       <c r="AI11" s="3"/>
+      <c r="AJ11" s="3"/>
     </row>
-    <row r="12" spans="1:35" x14ac:dyDescent="0.2">
+    <row r="12" spans="1:36" x14ac:dyDescent="0.2">
       <c r="C12" s="1" t="s">
         <v>8</v>
       </c>
@@ -1226,8 +1234,11 @@
       <c r="AI12" s="3" t="s">
         <v>5</v>
       </c>
+      <c r="AJ12" s="3" t="s">
+        <v>5</v>
+      </c>
     </row>
-    <row r="13" spans="1:35" x14ac:dyDescent="0.2">
+    <row r="13" spans="1:36" x14ac:dyDescent="0.2">
       <c r="C13" s="1" t="s">
         <v>9</v>
       </c>
@@ -1327,8 +1338,11 @@
       <c r="AI13" s="3">
         <v>0</v>
       </c>
+      <c r="AJ13" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="14" spans="1:35" x14ac:dyDescent="0.2">
+    <row r="14" spans="1:36" x14ac:dyDescent="0.2">
       <c r="C14" s="1" t="s">
         <v>10</v>
       </c>
@@ -1336,22 +1350,22 @@
         <v>0</v>
       </c>
       <c r="E14" s="3">
-        <v>0</v>
+        <v>4600</v>
       </c>
       <c r="F14" s="3">
-        <v>0</v>
+        <v>12300</v>
       </c>
       <c r="G14" s="3">
-        <v>0</v>
+        <v>-1700</v>
       </c>
       <c r="H14" s="3">
         <v>0</v>
       </c>
       <c r="I14" s="3">
-        <v>0</v>
+        <v>-200</v>
       </c>
       <c r="J14" s="3">
-        <v>0</v>
+        <v>42300</v>
       </c>
       <c r="K14" s="3">
         <v>0</v>
@@ -1428,109 +1442,115 @@
       <c r="AI14" s="3">
         <v>0</v>
       </c>
+      <c r="AJ14" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="15" spans="1:35" x14ac:dyDescent="0.2">
+    <row r="15" spans="1:36" x14ac:dyDescent="0.2">
       <c r="C15" s="1" t="s">
         <v>11</v>
       </c>
       <c r="D15" s="3">
-        <v>-103500</v>
+        <v>164900</v>
       </c>
       <c r="E15" s="3">
-        <v>-100200</v>
+        <v>149400</v>
       </c>
       <c r="F15" s="3">
-        <v>-98700</v>
+        <v>148900</v>
       </c>
       <c r="G15" s="3">
-        <v>-88300</v>
+        <v>144200</v>
       </c>
       <c r="H15" s="3">
-        <v>-94800</v>
+        <v>130600</v>
       </c>
       <c r="I15" s="3">
+        <v>130000</v>
+      </c>
+      <c r="J15" s="3">
+        <v>130100</v>
+      </c>
+      <c r="K15" s="3">
+        <v>-101500</v>
+      </c>
+      <c r="L15" s="3">
+        <v>-92100</v>
+      </c>
+      <c r="M15" s="3">
+        <v>-100700</v>
+      </c>
+      <c r="N15" s="3">
+        <v>-101400</v>
+      </c>
+      <c r="O15" s="3">
+        <v>-98200</v>
+      </c>
+      <c r="P15" s="3">
+        <v>-97600</v>
+      </c>
+      <c r="Q15" s="3">
+        <v>-97400</v>
+      </c>
+      <c r="R15" s="3">
+        <v>-100600</v>
+      </c>
+      <c r="S15" s="3">
+        <v>-99400</v>
+      </c>
+      <c r="T15" s="3">
         <v>-99600</v>
       </c>
-      <c r="J15" s="3">
-        <v>-101500</v>
-      </c>
-      <c r="K15" s="3">
-        <v>-92100</v>
-      </c>
-      <c r="L15" s="3">
-        <v>-100700</v>
-      </c>
-      <c r="M15" s="3">
-        <v>-101400</v>
-      </c>
-      <c r="N15" s="3">
-        <v>-98200</v>
-      </c>
-      <c r="O15" s="3">
-        <v>-97600</v>
-      </c>
-      <c r="P15" s="3">
-        <v>-97400</v>
-      </c>
-      <c r="Q15" s="3">
-        <v>-100600</v>
-      </c>
-      <c r="R15" s="3">
-        <v>-99400</v>
-      </c>
-      <c r="S15" s="3">
-        <v>-99600</v>
-      </c>
-      <c r="T15" s="3">
+      <c r="U15" s="3">
         <v>-96100</v>
       </c>
-      <c r="U15" s="3">
+      <c r="V15" s="3">
         <v>-109500</v>
       </c>
-      <c r="V15" s="3">
+      <c r="W15" s="3">
         <v>-115200</v>
       </c>
-      <c r="W15" s="3">
+      <c r="X15" s="3">
         <v>-112100</v>
       </c>
-      <c r="X15" s="3">
+      <c r="Y15" s="3">
         <v>-104100</v>
       </c>
-      <c r="Y15" s="3">
+      <c r="Z15" s="3">
         <v>-88900</v>
       </c>
-      <c r="Z15" s="3">
+      <c r="AA15" s="3">
         <v>-50500</v>
       </c>
-      <c r="AA15" s="3">
+      <c r="AB15" s="3">
         <v>-47800</v>
       </c>
-      <c r="AB15" s="3">
+      <c r="AC15" s="3">
         <v>-44700</v>
       </c>
-      <c r="AC15" s="3">
+      <c r="AD15" s="3">
         <v>-40700</v>
       </c>
-      <c r="AD15" s="3">
+      <c r="AE15" s="3">
         <v>-39500</v>
       </c>
-      <c r="AE15" s="3">
+      <c r="AF15" s="3">
         <v>-40300</v>
       </c>
-      <c r="AF15" s="3">
+      <c r="AG15" s="3">
         <v>-40800</v>
       </c>
-      <c r="AG15" s="3">
+      <c r="AH15" s="3">
         <v>-44500</v>
       </c>
-      <c r="AH15" s="3">
+      <c r="AI15" s="3">
         <v>-54800</v>
       </c>
-      <c r="AI15" s="3">
+      <c r="AJ15" s="3">
         <v>-53700</v>
       </c>
     </row>
-    <row r="16" spans="1:35" x14ac:dyDescent="0.2">
+    <row r="16" spans="1:36" x14ac:dyDescent="0.2">
       <c r="D16" s="3"/>
       <c r="E16" s="3"/>
       <c r="F16" s="3"/>
@@ -1563,210 +1583,217 @@
       <c r="AG16" s="3"/>
       <c r="AH16" s="3"/>
       <c r="AI16" s="3"/>
+      <c r="AJ16" s="3"/>
     </row>
-    <row r="17" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="17" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C17" s="1" t="s">
         <v>12</v>
       </c>
-      <c r="D17" s="3" t="s">
-        <v>5</v>
+      <c r="D17" s="3">
+        <v>887900</v>
       </c>
       <c r="E17" s="3">
-        <v>2728400</v>
+        <v>1233600</v>
       </c>
       <c r="F17" s="3">
-        <v>3073600</v>
+        <v>1363800</v>
       </c>
       <c r="G17" s="3">
-        <v>2484800</v>
+        <v>1160500</v>
       </c>
       <c r="H17" s="3">
-        <v>2558100</v>
+        <v>1189600</v>
       </c>
       <c r="I17" s="3">
-        <v>2228900</v>
+        <v>1049500</v>
       </c>
       <c r="J17" s="3">
+        <v>1131700</v>
+      </c>
+      <c r="K17" s="3">
         <v>1897900</v>
       </c>
-      <c r="K17" s="3">
+      <c r="L17" s="3">
         <v>1245200</v>
       </c>
-      <c r="L17" s="3">
+      <c r="M17" s="3">
         <v>1121400</v>
       </c>
-      <c r="M17" s="3">
+      <c r="N17" s="3">
         <v>861300</v>
       </c>
-      <c r="N17" s="3">
+      <c r="O17" s="3">
         <v>772200</v>
       </c>
-      <c r="O17" s="3">
+      <c r="P17" s="3">
         <v>616800</v>
       </c>
-      <c r="P17" s="3">
+      <c r="Q17" s="3">
         <v>573600</v>
       </c>
-      <c r="Q17" s="3">
+      <c r="R17" s="3">
         <v>625700</v>
       </c>
-      <c r="R17" s="3">
+      <c r="S17" s="3">
         <v>727900</v>
       </c>
-      <c r="S17" s="3">
+      <c r="T17" s="3">
         <v>721100</v>
       </c>
-      <c r="T17" s="3">
+      <c r="U17" s="3">
         <v>966200</v>
       </c>
-      <c r="U17" s="3">
+      <c r="V17" s="3">
         <v>926000</v>
       </c>
-      <c r="V17" s="3">
+      <c r="W17" s="3">
         <v>1019500</v>
       </c>
-      <c r="W17" s="3">
+      <c r="X17" s="3">
         <v>1190700</v>
       </c>
-      <c r="X17" s="3">
+      <c r="Y17" s="3">
         <v>1111900</v>
       </c>
-      <c r="Y17" s="3">
+      <c r="Z17" s="3">
         <v>1098300</v>
       </c>
-      <c r="Z17" s="3">
+      <c r="AA17" s="3">
         <v>1157200</v>
       </c>
-      <c r="AA17" s="3">
+      <c r="AB17" s="3">
         <v>918800</v>
       </c>
-      <c r="AB17" s="3">
+      <c r="AC17" s="3">
         <v>752200</v>
       </c>
-      <c r="AC17" s="3">
+      <c r="AD17" s="3">
         <v>877900</v>
       </c>
-      <c r="AD17" s="3">
+      <c r="AE17" s="3">
         <v>1026000</v>
       </c>
-      <c r="AE17" s="3">
+      <c r="AF17" s="3">
         <v>926800</v>
       </c>
-      <c r="AF17" s="3">
+      <c r="AG17" s="3">
         <v>906500</v>
       </c>
-      <c r="AG17" s="3">
+      <c r="AH17" s="3">
         <v>830000</v>
       </c>
-      <c r="AH17" s="3">
+      <c r="AI17" s="3">
         <v>903100</v>
       </c>
-      <c r="AI17" s="3">
+      <c r="AJ17" s="3">
         <v>963600</v>
       </c>
     </row>
-    <row r="18" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="18" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C18" s="1" t="s">
         <v>13</v>
       </c>
-      <c r="D18" s="3" t="s">
-        <v>5</v>
+      <c r="D18" s="3">
+        <v>909700</v>
       </c>
       <c r="E18" s="3">
-        <v>1373800</v>
+        <v>910800</v>
       </c>
       <c r="F18" s="3">
-        <v>994700</v>
+        <v>856000</v>
       </c>
       <c r="G18" s="3">
-        <v>1444600</v>
+        <v>27200</v>
       </c>
       <c r="H18" s="3">
-        <v>1228400</v>
+        <v>911700</v>
       </c>
       <c r="I18" s="3">
-        <v>1467900</v>
+        <v>699100</v>
       </c>
       <c r="J18" s="3">
+        <v>960100</v>
+      </c>
+      <c r="K18" s="3">
         <v>1564300</v>
       </c>
-      <c r="K18" s="3">
+      <c r="L18" s="3">
         <v>1547000</v>
       </c>
-      <c r="L18" s="3">
+      <c r="M18" s="3">
         <v>1365800</v>
       </c>
-      <c r="M18" s="3">
+      <c r="N18" s="3">
         <v>1403000</v>
       </c>
-      <c r="N18" s="3">
+      <c r="O18" s="3">
         <v>1253800</v>
       </c>
-      <c r="O18" s="3">
+      <c r="P18" s="3">
         <v>1245400</v>
       </c>
-      <c r="P18" s="3">
+      <c r="Q18" s="3">
         <v>1213900</v>
       </c>
-      <c r="Q18" s="3">
+      <c r="R18" s="3">
         <v>1096400</v>
       </c>
-      <c r="R18" s="3">
+      <c r="S18" s="3">
         <v>1000300</v>
       </c>
-      <c r="S18" s="3">
+      <c r="T18" s="3">
         <v>1028700</v>
       </c>
-      <c r="T18" s="3">
+      <c r="U18" s="3">
         <v>891200</v>
       </c>
-      <c r="U18" s="3">
+      <c r="V18" s="3">
         <v>1102100</v>
       </c>
-      <c r="V18" s="3">
+      <c r="W18" s="3">
         <v>1196900</v>
       </c>
-      <c r="W18" s="3">
+      <c r="X18" s="3">
         <v>1097100</v>
       </c>
-      <c r="X18" s="3">
+      <c r="Y18" s="3">
         <v>1241200</v>
       </c>
-      <c r="Y18" s="3">
+      <c r="Z18" s="3">
         <v>1271100</v>
       </c>
-      <c r="Z18" s="3">
+      <c r="AA18" s="3">
         <v>996800</v>
       </c>
-      <c r="AA18" s="3">
+      <c r="AB18" s="3">
         <v>1087400</v>
       </c>
-      <c r="AB18" s="3">
+      <c r="AC18" s="3">
         <v>1237400</v>
       </c>
-      <c r="AC18" s="3">
+      <c r="AD18" s="3">
         <v>1032900</v>
       </c>
-      <c r="AD18" s="3">
+      <c r="AE18" s="3">
         <v>886500</v>
       </c>
-      <c r="AE18" s="3">
+      <c r="AF18" s="3">
         <v>998500</v>
       </c>
-      <c r="AF18" s="3">
+      <c r="AG18" s="3">
         <v>946600</v>
       </c>
-      <c r="AG18" s="3">
+      <c r="AH18" s="3">
         <v>1003700</v>
       </c>
-      <c r="AH18" s="3">
+      <c r="AI18" s="3">
         <v>995700</v>
       </c>
-      <c r="AI18" s="3">
+      <c r="AJ18" s="3">
         <v>934400</v>
       </c>
     </row>
-    <row r="19" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="19" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C19" s="1" t="s">
         <v>14</v>
       </c>
@@ -1802,233 +1829,240 @@
       <c r="AG19" s="3"/>
       <c r="AH19" s="3"/>
       <c r="AI19" s="3"/>
+      <c r="AJ19" s="3"/>
     </row>
-    <row r="20" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="20" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C20" s="1" t="s">
         <v>15</v>
       </c>
-      <c r="D20" s="3" t="s">
-        <v>5</v>
+      <c r="D20" s="3">
+        <v>-4400</v>
       </c>
       <c r="E20" s="3">
-        <v>-515800</v>
+        <v>1400</v>
       </c>
       <c r="F20" s="3">
-        <v>-903100</v>
+        <v>-7500</v>
       </c>
       <c r="G20" s="3">
-        <v>-509600</v>
+        <v>-65300</v>
       </c>
       <c r="H20" s="3">
-        <v>-569800</v>
+        <v>-14500</v>
       </c>
       <c r="I20" s="3">
-        <v>-515200</v>
+        <v>32600</v>
       </c>
       <c r="J20" s="3">
+        <v>-56500</v>
+      </c>
+      <c r="K20" s="3">
         <v>-1017300</v>
       </c>
-      <c r="K20" s="3">
+      <c r="L20" s="3">
         <v>-606600</v>
       </c>
-      <c r="L20" s="3">
+      <c r="M20" s="3">
         <v>-375600</v>
       </c>
-      <c r="M20" s="3">
+      <c r="N20" s="3">
         <v>-505900</v>
       </c>
-      <c r="N20" s="3">
+      <c r="O20" s="3">
         <v>-806400</v>
       </c>
-      <c r="O20" s="3">
+      <c r="P20" s="3">
         <v>-394200</v>
       </c>
-      <c r="P20" s="3">
+      <c r="Q20" s="3">
         <v>-406900</v>
       </c>
-      <c r="Q20" s="3">
+      <c r="R20" s="3">
         <v>-399500</v>
       </c>
-      <c r="R20" s="3">
+      <c r="S20" s="3">
         <v>-784600</v>
       </c>
-      <c r="S20" s="3">
+      <c r="T20" s="3">
         <v>-508200</v>
       </c>
-      <c r="T20" s="3">
+      <c r="U20" s="3">
         <v>-674600</v>
       </c>
-      <c r="U20" s="3">
+      <c r="V20" s="3">
         <v>-492400</v>
       </c>
-      <c r="V20" s="3">
+      <c r="W20" s="3">
         <v>-920900</v>
       </c>
-      <c r="W20" s="3">
+      <c r="X20" s="3">
         <v>-527400</v>
       </c>
-      <c r="X20" s="3">
+      <c r="Y20" s="3">
         <v>-447200</v>
       </c>
-      <c r="Y20" s="3">
+      <c r="Z20" s="3">
         <v>-519600</v>
       </c>
-      <c r="Z20" s="3">
+      <c r="AA20" s="3">
         <v>-847700</v>
       </c>
-      <c r="AA20" s="3">
+      <c r="AB20" s="3">
         <v>-418500</v>
       </c>
-      <c r="AB20" s="3">
+      <c r="AC20" s="3">
         <v>-401200</v>
       </c>
-      <c r="AC20" s="3">
+      <c r="AD20" s="3">
         <v>-355800</v>
       </c>
-      <c r="AD20" s="3">
+      <c r="AE20" s="3">
         <v>-756300</v>
       </c>
-      <c r="AE20" s="3">
+      <c r="AF20" s="3">
         <v>-671500</v>
       </c>
-      <c r="AF20" s="3">
+      <c r="AG20" s="3">
         <v>-417500</v>
       </c>
-      <c r="AG20" s="3">
+      <c r="AH20" s="3">
         <v>-274500</v>
       </c>
-      <c r="AH20" s="3">
+      <c r="AI20" s="3">
         <v>-821100</v>
       </c>
-      <c r="AI20" s="3">
+      <c r="AJ20" s="3">
         <v>-531000</v>
       </c>
     </row>
-    <row r="21" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="21" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C21" s="1" t="s">
         <v>16</v>
       </c>
-      <c r="D21" s="3" t="s">
-        <v>5</v>
+      <c r="D21" s="3">
+        <v>1079100</v>
       </c>
       <c r="E21" s="3">
-        <v>1065000</v>
+        <v>1058900</v>
       </c>
       <c r="F21" s="3">
-        <v>289500</v>
+        <v>1012400</v>
       </c>
       <c r="G21" s="3">
-        <v>1115300</v>
+        <v>236700</v>
       </c>
       <c r="H21" s="3">
-        <v>840900</v>
+        <v>1056800</v>
       </c>
       <c r="I21" s="3">
-        <v>1137200</v>
+        <v>796500</v>
       </c>
       <c r="J21" s="3">
+        <v>1146700</v>
+      </c>
+      <c r="K21" s="3">
         <v>732200</v>
       </c>
-      <c r="K21" s="3">
+      <c r="L21" s="3">
         <v>1110000</v>
       </c>
-      <c r="L21" s="3">
+      <c r="M21" s="3">
         <v>1165700</v>
       </c>
-      <c r="M21" s="3">
+      <c r="N21" s="3">
         <v>1065700</v>
       </c>
-      <c r="N21" s="3">
+      <c r="O21" s="3">
         <v>603300</v>
       </c>
-      <c r="O21" s="3">
+      <c r="P21" s="3">
         <v>1000500</v>
       </c>
-      <c r="P21" s="3">
+      <c r="Q21" s="3">
         <v>991500</v>
       </c>
-      <c r="Q21" s="3">
+      <c r="R21" s="3">
         <v>799800</v>
       </c>
-      <c r="R21" s="3">
+      <c r="S21" s="3">
         <v>316900</v>
       </c>
-      <c r="S21" s="3">
+      <c r="T21" s="3">
         <v>622000</v>
       </c>
-      <c r="T21" s="3">
+      <c r="U21" s="3">
         <v>315300</v>
       </c>
-      <c r="U21" s="3">
+      <c r="V21" s="3">
         <v>721900</v>
       </c>
-      <c r="V21" s="3">
+      <c r="W21" s="3">
         <v>396300</v>
       </c>
-      <c r="W21" s="3">
+      <c r="X21" s="3">
         <v>686600</v>
       </c>
-      <c r="X21" s="3">
+      <c r="Y21" s="3">
         <v>902900</v>
       </c>
-      <c r="Y21" s="3">
+      <c r="Z21" s="3">
         <v>845100</v>
       </c>
-      <c r="Z21" s="3">
+      <c r="AA21" s="3">
         <v>210800</v>
       </c>
-      <c r="AA21" s="3">
+      <c r="AB21" s="3">
         <v>727400</v>
       </c>
-      <c r="AB21" s="3">
+      <c r="AC21" s="3">
         <v>892200</v>
       </c>
-      <c r="AC21" s="3">
+      <c r="AD21" s="3">
         <v>727700</v>
       </c>
-      <c r="AD21" s="3">
+      <c r="AE21" s="3">
         <v>180100</v>
       </c>
-      <c r="AE21" s="3">
+      <c r="AF21" s="3">
         <v>377800</v>
       </c>
-      <c r="AF21" s="3">
+      <c r="AG21" s="3">
         <v>580800</v>
       </c>
-      <c r="AG21" s="3">
+      <c r="AH21" s="3">
         <v>784400</v>
       </c>
-      <c r="AH21" s="3">
+      <c r="AI21" s="3">
         <v>229400</v>
       </c>
-      <c r="AI21" s="3">
+      <c r="AJ21" s="3">
         <v>457200</v>
       </c>
     </row>
-    <row r="22" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="22" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C22" s="1" t="s">
         <v>17</v>
       </c>
-      <c r="D22" s="3">
-        <v>0</v>
-      </c>
-      <c r="E22" s="3">
-        <v>0</v>
-      </c>
-      <c r="F22" s="3">
-        <v>0</v>
-      </c>
-      <c r="G22" s="3">
-        <v>0</v>
-      </c>
-      <c r="H22" s="3">
-        <v>0</v>
-      </c>
-      <c r="I22" s="3">
-        <v>0</v>
-      </c>
-      <c r="J22" s="3">
-        <v>0</v>
+      <c r="D22" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="E22" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="F22" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="G22" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="H22" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="I22" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="J22" s="3" t="s">
+        <v>5</v>
       </c>
       <c r="K22" s="3">
         <v>0</v>
@@ -2105,210 +2139,219 @@
       <c r="AI22" s="3">
         <v>0</v>
       </c>
+      <c r="AJ22" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="23" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="23" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C23" s="1" t="s">
         <v>18</v>
       </c>
       <c r="D23" s="3">
-        <v>935200</v>
+        <v>914200</v>
       </c>
       <c r="E23" s="3">
-        <v>858000</v>
+        <v>904900</v>
       </c>
       <c r="F23" s="3">
-        <v>91600</v>
+        <v>851200</v>
       </c>
       <c r="G23" s="3">
-        <v>935100</v>
+        <v>94200</v>
       </c>
       <c r="H23" s="3">
-        <v>658700</v>
+        <v>926200</v>
       </c>
       <c r="I23" s="3">
-        <v>952700</v>
+        <v>666800</v>
       </c>
       <c r="J23" s="3">
+        <v>974300</v>
+      </c>
+      <c r="K23" s="3">
         <v>546900</v>
       </c>
-      <c r="K23" s="3">
+      <c r="L23" s="3">
         <v>940400</v>
       </c>
-      <c r="L23" s="3">
+      <c r="M23" s="3">
         <v>990200</v>
       </c>
-      <c r="M23" s="3">
+      <c r="N23" s="3">
         <v>897100</v>
       </c>
-      <c r="N23" s="3">
+      <c r="O23" s="3">
         <v>447400</v>
       </c>
-      <c r="O23" s="3">
+      <c r="P23" s="3">
         <v>851200</v>
       </c>
-      <c r="P23" s="3">
+      <c r="Q23" s="3">
         <v>807000</v>
       </c>
-      <c r="Q23" s="3">
+      <c r="R23" s="3">
         <v>696900</v>
       </c>
-      <c r="R23" s="3">
+      <c r="S23" s="3">
         <v>215700</v>
       </c>
-      <c r="S23" s="3">
+      <c r="T23" s="3">
         <v>520500</v>
       </c>
-      <c r="T23" s="3">
+      <c r="U23" s="3">
         <v>216600</v>
       </c>
-      <c r="U23" s="3">
+      <c r="V23" s="3">
         <v>609600</v>
       </c>
-      <c r="V23" s="3">
+      <c r="W23" s="3">
         <v>276000</v>
       </c>
-      <c r="W23" s="3">
+      <c r="X23" s="3">
         <v>569700</v>
       </c>
-      <c r="X23" s="3">
+      <c r="Y23" s="3">
         <v>794000</v>
       </c>
-      <c r="Y23" s="3">
+      <c r="Z23" s="3">
         <v>751500</v>
       </c>
-      <c r="Z23" s="3">
+      <c r="AA23" s="3">
         <v>149100</v>
       </c>
-      <c r="AA23" s="3">
+      <c r="AB23" s="3">
         <v>668900</v>
       </c>
-      <c r="AB23" s="3">
+      <c r="AC23" s="3">
         <v>836200</v>
       </c>
-      <c r="AC23" s="3">
+      <c r="AD23" s="3">
         <v>677100</v>
       </c>
-      <c r="AD23" s="3">
+      <c r="AE23" s="3">
         <v>130200</v>
       </c>
-      <c r="AE23" s="3">
+      <c r="AF23" s="3">
         <v>327000</v>
       </c>
-      <c r="AF23" s="3">
+      <c r="AG23" s="3">
         <v>529200</v>
       </c>
-      <c r="AG23" s="3">
+      <c r="AH23" s="3">
         <v>729200</v>
       </c>
-      <c r="AH23" s="3">
+      <c r="AI23" s="3">
         <v>174600</v>
       </c>
-      <c r="AI23" s="3">
+      <c r="AJ23" s="3">
         <v>403400</v>
       </c>
     </row>
-    <row r="24" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="24" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C24" s="1" t="s">
         <v>19</v>
       </c>
       <c r="D24" s="3">
-        <v>214000</v>
+        <v>216000</v>
       </c>
       <c r="E24" s="3">
-        <v>228800</v>
+        <v>207100</v>
       </c>
       <c r="F24" s="3">
-        <v>20400</v>
+        <v>227000</v>
       </c>
       <c r="G24" s="3">
-        <v>246500</v>
+        <v>21000</v>
       </c>
       <c r="H24" s="3">
-        <v>158300</v>
+        <v>244100</v>
       </c>
       <c r="I24" s="3">
-        <v>242800</v>
+        <v>160200</v>
       </c>
       <c r="J24" s="3">
+        <v>248300</v>
+      </c>
+      <c r="K24" s="3">
         <v>148500</v>
       </c>
-      <c r="K24" s="3">
+      <c r="L24" s="3">
         <v>259000</v>
       </c>
-      <c r="L24" s="3">
+      <c r="M24" s="3">
         <v>240200</v>
       </c>
-      <c r="M24" s="3">
+      <c r="N24" s="3">
         <v>225300</v>
       </c>
-      <c r="N24" s="3">
+      <c r="O24" s="3">
         <v>113100</v>
       </c>
-      <c r="O24" s="3">
+      <c r="P24" s="3">
         <v>232900</v>
       </c>
-      <c r="P24" s="3">
+      <c r="Q24" s="3">
         <v>193200</v>
       </c>
-      <c r="Q24" s="3">
+      <c r="R24" s="3">
         <v>164900</v>
       </c>
-      <c r="R24" s="3">
+      <c r="S24" s="3">
         <v>53200</v>
       </c>
-      <c r="S24" s="3">
+      <c r="T24" s="3">
         <v>118800</v>
       </c>
-      <c r="T24" s="3">
+      <c r="U24" s="3">
         <v>50000</v>
       </c>
-      <c r="U24" s="3">
+      <c r="V24" s="3">
         <v>157800</v>
       </c>
-      <c r="V24" s="3">
+      <c r="W24" s="3">
         <v>79200</v>
       </c>
-      <c r="W24" s="3">
+      <c r="X24" s="3">
         <v>115700</v>
       </c>
-      <c r="X24" s="3">
+      <c r="Y24" s="3">
         <v>215500</v>
       </c>
-      <c r="Y24" s="3">
+      <c r="Z24" s="3">
         <v>192300</v>
       </c>
-      <c r="Z24" s="3">
+      <c r="AA24" s="3">
         <v>39300</v>
       </c>
-      <c r="AA24" s="3">
+      <c r="AB24" s="3">
         <v>179200</v>
       </c>
-      <c r="AB24" s="3">
+      <c r="AC24" s="3">
         <v>229900</v>
       </c>
-      <c r="AC24" s="3">
+      <c r="AD24" s="3">
         <v>177700</v>
       </c>
-      <c r="AD24" s="3">
+      <c r="AE24" s="3">
         <v>9000</v>
       </c>
-      <c r="AE24" s="3">
+      <c r="AF24" s="3">
         <v>77600</v>
       </c>
-      <c r="AF24" s="3">
+      <c r="AG24" s="3">
         <v>118800</v>
       </c>
-      <c r="AG24" s="3">
+      <c r="AH24" s="3">
         <v>163600</v>
       </c>
-      <c r="AH24" s="3">
+      <c r="AI24" s="3">
         <v>30300</v>
       </c>
-      <c r="AI24" s="3">
+      <c r="AJ24" s="3">
         <v>80000</v>
       </c>
     </row>
-    <row r="25" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="25" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C25" s="1" t="s">
         <v>20</v>
       </c>
@@ -2408,210 +2451,219 @@
       <c r="AI25" s="3">
         <v>0</v>
       </c>
+      <c r="AJ25" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="26" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="26" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C26" s="1" t="s">
         <v>21</v>
       </c>
-      <c r="D26" s="3" t="s">
-        <v>5</v>
+      <c r="D26" s="3">
+        <v>698200</v>
       </c>
       <c r="E26" s="3">
-        <v>629200</v>
+        <v>697800</v>
       </c>
       <c r="F26" s="3">
-        <v>71200</v>
+        <v>624200</v>
       </c>
       <c r="G26" s="3">
-        <v>688600</v>
+        <v>73200</v>
       </c>
       <c r="H26" s="3">
-        <v>500400</v>
+        <v>682000</v>
       </c>
       <c r="I26" s="3">
-        <v>710000</v>
+        <v>506600</v>
       </c>
       <c r="J26" s="3">
+        <v>726000</v>
+      </c>
+      <c r="K26" s="3">
         <v>398500</v>
       </c>
-      <c r="K26" s="3">
+      <c r="L26" s="3">
         <v>681400</v>
       </c>
-      <c r="L26" s="3">
+      <c r="M26" s="3">
         <v>750000</v>
       </c>
-      <c r="M26" s="3">
+      <c r="N26" s="3">
         <v>671800</v>
       </c>
-      <c r="N26" s="3">
+      <c r="O26" s="3">
         <v>334300</v>
       </c>
-      <c r="O26" s="3">
+      <c r="P26" s="3">
         <v>618300</v>
       </c>
-      <c r="P26" s="3">
+      <c r="Q26" s="3">
         <v>613800</v>
       </c>
-      <c r="Q26" s="3">
+      <c r="R26" s="3">
         <v>532000</v>
       </c>
-      <c r="R26" s="3">
+      <c r="S26" s="3">
         <v>162400</v>
       </c>
-      <c r="S26" s="3">
+      <c r="T26" s="3">
         <v>401700</v>
       </c>
-      <c r="T26" s="3">
+      <c r="U26" s="3">
         <v>166500</v>
       </c>
-      <c r="U26" s="3">
+      <c r="V26" s="3">
         <v>451800</v>
       </c>
-      <c r="V26" s="3">
+      <c r="W26" s="3">
         <v>196800</v>
       </c>
-      <c r="W26" s="3">
+      <c r="X26" s="3">
         <v>454000</v>
       </c>
-      <c r="X26" s="3">
+      <c r="Y26" s="3">
         <v>578500</v>
       </c>
-      <c r="Y26" s="3">
+      <c r="Z26" s="3">
         <v>559200</v>
       </c>
-      <c r="Z26" s="3">
+      <c r="AA26" s="3">
         <v>109900</v>
       </c>
-      <c r="AA26" s="3">
+      <c r="AB26" s="3">
         <v>489700</v>
       </c>
-      <c r="AB26" s="3">
+      <c r="AC26" s="3">
         <v>606300</v>
       </c>
-      <c r="AC26" s="3">
+      <c r="AD26" s="3">
         <v>499400</v>
       </c>
-      <c r="AD26" s="3">
+      <c r="AE26" s="3">
         <v>121100</v>
       </c>
-      <c r="AE26" s="3">
+      <c r="AF26" s="3">
         <v>249400</v>
       </c>
-      <c r="AF26" s="3">
+      <c r="AG26" s="3">
         <v>410300</v>
       </c>
-      <c r="AG26" s="3">
+      <c r="AH26" s="3">
         <v>565600</v>
       </c>
-      <c r="AH26" s="3">
+      <c r="AI26" s="3">
         <v>144300</v>
       </c>
-      <c r="AI26" s="3">
+      <c r="AJ26" s="3">
         <v>323500</v>
       </c>
     </row>
-    <row r="27" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="27" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C27" s="1" t="s">
         <v>22</v>
       </c>
-      <c r="D27" s="3" t="s">
-        <v>5</v>
+      <c r="D27" s="3">
+        <v>655100</v>
       </c>
       <c r="E27" s="3">
-        <v>591600</v>
+        <v>647100</v>
       </c>
       <c r="F27" s="3">
-        <v>24600</v>
+        <v>586900</v>
       </c>
       <c r="G27" s="3">
-        <v>649900</v>
+        <v>25300</v>
       </c>
       <c r="H27" s="3">
-        <v>444300</v>
+        <v>643700</v>
       </c>
       <c r="I27" s="3">
-        <v>662500</v>
+        <v>449800</v>
       </c>
       <c r="J27" s="3">
+        <v>677400</v>
+      </c>
+      <c r="K27" s="3">
         <v>338800</v>
       </c>
-      <c r="K27" s="3">
+      <c r="L27" s="3">
         <v>640600</v>
       </c>
-      <c r="L27" s="3">
+      <c r="M27" s="3">
         <v>684400</v>
       </c>
-      <c r="M27" s="3">
+      <c r="N27" s="3">
         <v>631400</v>
       </c>
-      <c r="N27" s="3">
+      <c r="O27" s="3">
         <v>279500</v>
       </c>
-      <c r="O27" s="3">
+      <c r="P27" s="3">
         <v>570700</v>
       </c>
-      <c r="P27" s="3">
+      <c r="Q27" s="3">
         <v>552600</v>
       </c>
-      <c r="Q27" s="3">
+      <c r="R27" s="3">
         <v>482000</v>
       </c>
-      <c r="R27" s="3">
+      <c r="S27" s="3">
         <v>112600</v>
       </c>
-      <c r="S27" s="3">
+      <c r="T27" s="3">
         <v>358800</v>
       </c>
-      <c r="T27" s="3">
+      <c r="U27" s="3">
         <v>100500</v>
       </c>
-      <c r="U27" s="3">
+      <c r="V27" s="3">
         <v>412900</v>
       </c>
-      <c r="V27" s="3">
+      <c r="W27" s="3">
         <v>174900</v>
       </c>
-      <c r="W27" s="3">
+      <c r="X27" s="3">
         <v>410100</v>
       </c>
-      <c r="X27" s="3">
+      <c r="Y27" s="3">
         <v>537700</v>
       </c>
-      <c r="Y27" s="3">
+      <c r="Z27" s="3">
         <v>517500</v>
       </c>
-      <c r="Z27" s="3">
+      <c r="AA27" s="3">
         <v>76800</v>
       </c>
-      <c r="AA27" s="3">
+      <c r="AB27" s="3">
         <v>453900</v>
       </c>
-      <c r="AB27" s="3">
+      <c r="AC27" s="3">
         <v>569900</v>
       </c>
-      <c r="AC27" s="3">
+      <c r="AD27" s="3">
         <v>463600</v>
       </c>
-      <c r="AD27" s="3">
+      <c r="AE27" s="3">
         <v>84900</v>
       </c>
-      <c r="AE27" s="3">
+      <c r="AF27" s="3">
         <v>212100</v>
       </c>
-      <c r="AF27" s="3">
+      <c r="AG27" s="3">
         <v>369000</v>
       </c>
-      <c r="AG27" s="3">
+      <c r="AH27" s="3">
         <v>517600</v>
       </c>
-      <c r="AH27" s="3">
+      <c r="AI27" s="3">
         <v>88500</v>
       </c>
-      <c r="AI27" s="3">
+      <c r="AJ27" s="3">
         <v>275700</v>
       </c>
     </row>
-    <row r="28" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="28" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C28" s="1" t="s">
         <v>23</v>
       </c>
@@ -2711,8 +2763,11 @@
       <c r="AI28" s="3">
         <v>0</v>
       </c>
+      <c r="AJ28" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="29" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="29" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C29" s="1" t="s">
         <v>24</v>
       </c>
@@ -2812,8 +2867,11 @@
       <c r="AI29" s="3">
         <v>0</v>
       </c>
+      <c r="AJ29" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="30" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="30" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C30" s="1" t="s">
         <v>25</v>
       </c>
@@ -2913,8 +2971,11 @@
       <c r="AI30" s="3">
         <v>0</v>
       </c>
+      <c r="AJ30" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="31" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="31" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C31" s="1" t="s">
         <v>26</v>
       </c>
@@ -3014,210 +3075,219 @@
       <c r="AI31" s="3">
         <v>0</v>
       </c>
+      <c r="AJ31" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="32" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="32" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C32" s="1" t="s">
         <v>27</v>
       </c>
-      <c r="D32" s="3" t="s">
-        <v>5</v>
+      <c r="D32" s="3">
+        <v>4400</v>
       </c>
       <c r="E32" s="3">
-        <v>515800</v>
+        <v>-1400</v>
       </c>
       <c r="F32" s="3">
-        <v>903100</v>
+        <v>7500</v>
       </c>
       <c r="G32" s="3">
-        <v>509600</v>
+        <v>65300</v>
       </c>
       <c r="H32" s="3">
-        <v>569800</v>
+        <v>14500</v>
       </c>
       <c r="I32" s="3">
-        <v>515200</v>
+        <v>-32600</v>
       </c>
       <c r="J32" s="3">
+        <v>56500</v>
+      </c>
+      <c r="K32" s="3">
         <v>1017300</v>
       </c>
-      <c r="K32" s="3">
+      <c r="L32" s="3">
         <v>606600</v>
       </c>
-      <c r="L32" s="3">
+      <c r="M32" s="3">
         <v>375600</v>
       </c>
-      <c r="M32" s="3">
+      <c r="N32" s="3">
         <v>505900</v>
       </c>
-      <c r="N32" s="3">
+      <c r="O32" s="3">
         <v>806400</v>
       </c>
-      <c r="O32" s="3">
+      <c r="P32" s="3">
         <v>394200</v>
       </c>
-      <c r="P32" s="3">
+      <c r="Q32" s="3">
         <v>406900</v>
       </c>
-      <c r="Q32" s="3">
+      <c r="R32" s="3">
         <v>399500</v>
       </c>
-      <c r="R32" s="3">
+      <c r="S32" s="3">
         <v>784600</v>
       </c>
-      <c r="S32" s="3">
+      <c r="T32" s="3">
         <v>508200</v>
       </c>
-      <c r="T32" s="3">
+      <c r="U32" s="3">
         <v>674600</v>
       </c>
-      <c r="U32" s="3">
+      <c r="V32" s="3">
         <v>492400</v>
       </c>
-      <c r="V32" s="3">
+      <c r="W32" s="3">
         <v>920900</v>
       </c>
-      <c r="W32" s="3">
+      <c r="X32" s="3">
         <v>527400</v>
       </c>
-      <c r="X32" s="3">
+      <c r="Y32" s="3">
         <v>447200</v>
       </c>
-      <c r="Y32" s="3">
+      <c r="Z32" s="3">
         <v>519600</v>
       </c>
-      <c r="Z32" s="3">
+      <c r="AA32" s="3">
         <v>847700</v>
       </c>
-      <c r="AA32" s="3">
+      <c r="AB32" s="3">
         <v>418500</v>
       </c>
-      <c r="AB32" s="3">
+      <c r="AC32" s="3">
         <v>401200</v>
       </c>
-      <c r="AC32" s="3">
+      <c r="AD32" s="3">
         <v>355800</v>
       </c>
-      <c r="AD32" s="3">
+      <c r="AE32" s="3">
         <v>756300</v>
       </c>
-      <c r="AE32" s="3">
+      <c r="AF32" s="3">
         <v>671500</v>
       </c>
-      <c r="AF32" s="3">
+      <c r="AG32" s="3">
         <v>417500</v>
       </c>
-      <c r="AG32" s="3">
+      <c r="AH32" s="3">
         <v>274500</v>
       </c>
-      <c r="AH32" s="3">
+      <c r="AI32" s="3">
         <v>821100</v>
       </c>
-      <c r="AI32" s="3">
+      <c r="AJ32" s="3">
         <v>531000</v>
       </c>
     </row>
-    <row r="33" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="33" spans="2:36" x14ac:dyDescent="0.2">
       <c r="C33" s="1" t="s">
         <v>28</v>
       </c>
-      <c r="D33" s="3" t="s">
-        <v>5</v>
+      <c r="D33" s="3">
+        <v>688600</v>
       </c>
       <c r="E33" s="3">
-        <v>591600</v>
+        <v>676000</v>
       </c>
       <c r="F33" s="3">
-        <v>24600</v>
+        <v>613100</v>
       </c>
       <c r="G33" s="3">
-        <v>649900</v>
+        <v>52500</v>
       </c>
       <c r="H33" s="3">
-        <v>444300</v>
+        <v>668000</v>
       </c>
       <c r="I33" s="3">
-        <v>662500</v>
+        <v>474700</v>
       </c>
       <c r="J33" s="3">
+        <v>700700</v>
+      </c>
+      <c r="K33" s="3">
         <v>338800</v>
       </c>
-      <c r="K33" s="3">
+      <c r="L33" s="3">
         <v>640600</v>
       </c>
-      <c r="L33" s="3">
+      <c r="M33" s="3">
         <v>684400</v>
       </c>
-      <c r="M33" s="3">
+      <c r="N33" s="3">
         <v>631400</v>
       </c>
-      <c r="N33" s="3">
+      <c r="O33" s="3">
         <v>279500</v>
       </c>
-      <c r="O33" s="3">
+      <c r="P33" s="3">
         <v>570700</v>
       </c>
-      <c r="P33" s="3">
+      <c r="Q33" s="3">
         <v>552600</v>
       </c>
-      <c r="Q33" s="3">
+      <c r="R33" s="3">
         <v>482000</v>
       </c>
-      <c r="R33" s="3">
+      <c r="S33" s="3">
         <v>112600</v>
       </c>
-      <c r="S33" s="3">
+      <c r="T33" s="3">
         <v>358800</v>
       </c>
-      <c r="T33" s="3">
+      <c r="U33" s="3">
         <v>100500</v>
       </c>
-      <c r="U33" s="3">
+      <c r="V33" s="3">
         <v>412900</v>
       </c>
-      <c r="V33" s="3">
+      <c r="W33" s="3">
         <v>174900</v>
       </c>
-      <c r="W33" s="3">
+      <c r="X33" s="3">
         <v>410100</v>
       </c>
-      <c r="X33" s="3">
+      <c r="Y33" s="3">
         <v>537700</v>
       </c>
-      <c r="Y33" s="3">
+      <c r="Z33" s="3">
         <v>517500</v>
       </c>
-      <c r="Z33" s="3">
+      <c r="AA33" s="3">
         <v>76800</v>
       </c>
-      <c r="AA33" s="3">
+      <c r="AB33" s="3">
         <v>453900</v>
       </c>
-      <c r="AB33" s="3">
+      <c r="AC33" s="3">
         <v>569900</v>
       </c>
-      <c r="AC33" s="3">
+      <c r="AD33" s="3">
         <v>463600</v>
       </c>
-      <c r="AD33" s="3">
+      <c r="AE33" s="3">
         <v>84900</v>
       </c>
-      <c r="AE33" s="3">
+      <c r="AF33" s="3">
         <v>212100</v>
       </c>
-      <c r="AF33" s="3">
+      <c r="AG33" s="3">
         <v>369000</v>
       </c>
-      <c r="AG33" s="3">
+      <c r="AH33" s="3">
         <v>517600</v>
       </c>
-      <c r="AH33" s="3">
+      <c r="AI33" s="3">
         <v>88500</v>
       </c>
-      <c r="AI33" s="3">
+      <c r="AJ33" s="3">
         <v>275700</v>
       </c>
     </row>
-    <row r="34" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="34" spans="2:36" x14ac:dyDescent="0.2">
       <c r="C34" s="1" t="s">
         <v>29</v>
       </c>
@@ -3317,215 +3387,224 @@
       <c r="AI34" s="3">
         <v>0</v>
       </c>
+      <c r="AJ34" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="35" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="35" spans="2:36" x14ac:dyDescent="0.2">
       <c r="C35" s="1" t="s">
         <v>30</v>
       </c>
-      <c r="D35" s="3" t="s">
-        <v>5</v>
+      <c r="D35" s="3">
+        <v>688600</v>
       </c>
       <c r="E35" s="3">
-        <v>591600</v>
+        <v>676000</v>
       </c>
       <c r="F35" s="3">
-        <v>24600</v>
+        <v>613100</v>
       </c>
       <c r="G35" s="3">
-        <v>649900</v>
+        <v>52500</v>
       </c>
       <c r="H35" s="3">
-        <v>444300</v>
+        <v>668000</v>
       </c>
       <c r="I35" s="3">
-        <v>662500</v>
+        <v>474700</v>
       </c>
       <c r="J35" s="3">
+        <v>700700</v>
+      </c>
+      <c r="K35" s="3">
         <v>338800</v>
       </c>
-      <c r="K35" s="3">
+      <c r="L35" s="3">
         <v>640600</v>
       </c>
-      <c r="L35" s="3">
+      <c r="M35" s="3">
         <v>684400</v>
       </c>
-      <c r="M35" s="3">
+      <c r="N35" s="3">
         <v>631400</v>
       </c>
-      <c r="N35" s="3">
+      <c r="O35" s="3">
         <v>279500</v>
       </c>
-      <c r="O35" s="3">
+      <c r="P35" s="3">
         <v>570700</v>
       </c>
-      <c r="P35" s="3">
+      <c r="Q35" s="3">
         <v>552600</v>
       </c>
-      <c r="Q35" s="3">
+      <c r="R35" s="3">
         <v>482000</v>
       </c>
-      <c r="R35" s="3">
+      <c r="S35" s="3">
         <v>112600</v>
       </c>
-      <c r="S35" s="3">
+      <c r="T35" s="3">
         <v>358800</v>
       </c>
-      <c r="T35" s="3">
+      <c r="U35" s="3">
         <v>100500</v>
       </c>
-      <c r="U35" s="3">
+      <c r="V35" s="3">
         <v>412900</v>
       </c>
-      <c r="V35" s="3">
+      <c r="W35" s="3">
         <v>174900</v>
       </c>
-      <c r="W35" s="3">
+      <c r="X35" s="3">
         <v>410100</v>
       </c>
-      <c r="X35" s="3">
+      <c r="Y35" s="3">
         <v>537700</v>
       </c>
-      <c r="Y35" s="3">
+      <c r="Z35" s="3">
         <v>517500</v>
       </c>
-      <c r="Z35" s="3">
+      <c r="AA35" s="3">
         <v>76800</v>
       </c>
-      <c r="AA35" s="3">
+      <c r="AB35" s="3">
         <v>453900</v>
       </c>
-      <c r="AB35" s="3">
+      <c r="AC35" s="3">
         <v>569900</v>
       </c>
-      <c r="AC35" s="3">
+      <c r="AD35" s="3">
         <v>463600</v>
       </c>
-      <c r="AD35" s="3">
+      <c r="AE35" s="3">
         <v>84900</v>
       </c>
-      <c r="AE35" s="3">
+      <c r="AF35" s="3">
         <v>212100</v>
       </c>
-      <c r="AF35" s="3">
+      <c r="AG35" s="3">
         <v>369000</v>
       </c>
-      <c r="AG35" s="3">
+      <c r="AH35" s="3">
         <v>517600</v>
       </c>
-      <c r="AH35" s="3">
+      <c r="AI35" s="3">
         <v>88500</v>
       </c>
-      <c r="AI35" s="3">
+      <c r="AJ35" s="3">
         <v>275700</v>
       </c>
     </row>
-    <row r="37" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="37" spans="2:36" x14ac:dyDescent="0.2">
       <c r="B37" s="1" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="38" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="38" spans="2:36" x14ac:dyDescent="0.2">
       <c r="C38" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D38" s="2">
+        <v>45565</v>
+      </c>
+      <c r="E38" s="2">
         <v>45473</v>
       </c>
-      <c r="E38" s="2">
+      <c r="F38" s="2">
         <v>45382</v>
       </c>
-      <c r="F38" s="2">
+      <c r="G38" s="2">
         <v>45291</v>
       </c>
-      <c r="G38" s="2">
+      <c r="H38" s="2">
         <v>45199</v>
       </c>
-      <c r="H38" s="2">
+      <c r="I38" s="2">
         <v>45107</v>
       </c>
-      <c r="I38" s="2">
+      <c r="J38" s="2">
         <v>45016</v>
       </c>
-      <c r="J38" s="2">
+      <c r="K38" s="2">
         <v>44926</v>
       </c>
-      <c r="K38" s="2">
+      <c r="L38" s="2">
         <v>44834</v>
       </c>
-      <c r="L38" s="2">
+      <c r="M38" s="2">
         <v>44742</v>
       </c>
-      <c r="M38" s="2">
+      <c r="N38" s="2">
         <v>44651</v>
       </c>
-      <c r="N38" s="2">
+      <c r="O38" s="2">
         <v>44561</v>
       </c>
-      <c r="O38" s="2">
+      <c r="P38" s="2">
         <v>44469</v>
       </c>
-      <c r="P38" s="2">
+      <c r="Q38" s="2">
         <v>44377</v>
       </c>
-      <c r="Q38" s="2">
+      <c r="R38" s="2">
         <v>44286</v>
       </c>
-      <c r="R38" s="2">
+      <c r="S38" s="2">
         <v>44196</v>
       </c>
-      <c r="S38" s="2">
+      <c r="T38" s="2">
         <v>44104</v>
       </c>
-      <c r="T38" s="2">
+      <c r="U38" s="2">
         <v>44012</v>
       </c>
-      <c r="U38" s="2">
+      <c r="V38" s="2">
         <v>43921</v>
       </c>
-      <c r="V38" s="2">
+      <c r="W38" s="2">
         <v>43830</v>
       </c>
-      <c r="W38" s="2">
+      <c r="X38" s="2">
         <v>43738</v>
       </c>
-      <c r="X38" s="2">
+      <c r="Y38" s="2">
         <v>43646</v>
       </c>
-      <c r="Y38" s="2">
+      <c r="Z38" s="2">
         <v>43555</v>
       </c>
-      <c r="Z38" s="2">
+      <c r="AA38" s="2">
         <v>43465</v>
       </c>
-      <c r="AA38" s="2">
+      <c r="AB38" s="2">
         <v>43373</v>
       </c>
-      <c r="AB38" s="2">
+      <c r="AC38" s="2">
         <v>43281</v>
       </c>
-      <c r="AC38" s="2">
+      <c r="AD38" s="2">
         <v>43190</v>
       </c>
-      <c r="AD38" s="2">
+      <c r="AE38" s="2">
         <v>43100</v>
       </c>
-      <c r="AE38" s="2">
+      <c r="AF38" s="2">
         <v>43008</v>
       </c>
-      <c r="AF38" s="2">
+      <c r="AG38" s="2">
         <v>42916</v>
       </c>
-      <c r="AG38" s="2">
+      <c r="AH38" s="2">
         <v>42825</v>
       </c>
-      <c r="AH38" s="2">
+      <c r="AI38" s="2">
         <v>42735</v>
       </c>
-      <c r="AI38" s="2">
+      <c r="AJ38" s="2">
         <v>42643</v>
       </c>
     </row>
-    <row r="39" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="39" spans="2:36" x14ac:dyDescent="0.2">
       <c r="C39" s="1" t="s">
         <v>32</v>
       </c>
@@ -3561,8 +3640,9 @@
       <c r="AG39" s="3"/>
       <c r="AH39" s="3"/>
       <c r="AI39" s="3"/>
+      <c r="AJ39" s="3"/>
     </row>
-    <row r="40" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="40" spans="2:36" x14ac:dyDescent="0.2">
       <c r="C40" s="1" t="s">
         <v>33</v>
       </c>
@@ -3598,233 +3678,240 @@
       <c r="AG40" s="3"/>
       <c r="AH40" s="3"/>
       <c r="AI40" s="3"/>
+      <c r="AJ40" s="3"/>
     </row>
-    <row r="41" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="41" spans="2:36" x14ac:dyDescent="0.2">
       <c r="C41" s="1" t="s">
         <v>34</v>
       </c>
       <c r="D41" s="3">
-        <v>19032100</v>
+        <v>13834100</v>
       </c>
       <c r="E41" s="3">
-        <v>23757500</v>
+        <v>8534800</v>
       </c>
       <c r="F41" s="3">
-        <v>22821400</v>
+        <v>13129900</v>
       </c>
       <c r="G41" s="3">
-        <v>19280500</v>
+        <v>12476200</v>
       </c>
       <c r="H41" s="3">
-        <v>16047400</v>
+        <v>7157900</v>
       </c>
       <c r="I41" s="3">
-        <v>23101800</v>
+        <v>9809900</v>
       </c>
       <c r="J41" s="3">
+        <v>10234100</v>
+      </c>
+      <c r="K41" s="3">
         <v>25596900</v>
       </c>
-      <c r="K41" s="3">
+      <c r="L41" s="3">
         <v>6507700</v>
       </c>
-      <c r="L41" s="3">
+      <c r="M41" s="3">
         <v>7377100</v>
       </c>
-      <c r="M41" s="3">
+      <c r="N41" s="3">
         <v>9785500</v>
       </c>
-      <c r="N41" s="3">
+      <c r="O41" s="3">
         <v>5555400</v>
       </c>
-      <c r="O41" s="3">
+      <c r="P41" s="3">
         <v>7893500</v>
       </c>
-      <c r="P41" s="3">
+      <c r="Q41" s="3">
         <v>7303900</v>
       </c>
-      <c r="Q41" s="3">
+      <c r="R41" s="3">
         <v>7996900</v>
       </c>
-      <c r="R41" s="3">
+      <c r="S41" s="3">
         <v>6985700</v>
       </c>
-      <c r="S41" s="3">
+      <c r="T41" s="3">
         <v>6452400</v>
       </c>
-      <c r="T41" s="3">
+      <c r="U41" s="3">
         <v>6934700</v>
       </c>
-      <c r="U41" s="3">
+      <c r="V41" s="3">
         <v>7810800</v>
       </c>
-      <c r="V41" s="3">
+      <c r="W41" s="3">
         <v>5327800</v>
       </c>
-      <c r="W41" s="3">
+      <c r="X41" s="3">
         <v>7069900</v>
       </c>
-      <c r="X41" s="3">
+      <c r="Y41" s="3">
         <v>5777500</v>
       </c>
-      <c r="Y41" s="3">
+      <c r="Z41" s="3">
         <v>4361000</v>
       </c>
-      <c r="Z41" s="3">
+      <c r="AA41" s="3">
         <v>5329900</v>
       </c>
-      <c r="AA41" s="3">
+      <c r="AB41" s="3">
         <v>4608100</v>
       </c>
-      <c r="AB41" s="3">
+      <c r="AC41" s="3">
         <v>4589200</v>
       </c>
-      <c r="AC41" s="3">
+      <c r="AD41" s="3">
         <v>4387400</v>
       </c>
-      <c r="AD41" s="3">
+      <c r="AE41" s="3">
         <v>5323900</v>
       </c>
-      <c r="AE41" s="3">
+      <c r="AF41" s="3">
         <v>5337600</v>
       </c>
-      <c r="AF41" s="3">
+      <c r="AG41" s="3">
         <v>5780800</v>
       </c>
-      <c r="AG41" s="3">
+      <c r="AH41" s="3">
         <v>6495200</v>
       </c>
-      <c r="AH41" s="3">
+      <c r="AI41" s="3">
         <v>6385500</v>
       </c>
-      <c r="AI41" s="3">
+      <c r="AJ41" s="3">
         <v>7024600</v>
       </c>
     </row>
-    <row r="42" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="42" spans="2:36" x14ac:dyDescent="0.2">
       <c r="C42" s="1" t="s">
         <v>35</v>
       </c>
       <c r="D42" s="3">
-        <v>17617400</v>
+        <v>29370000</v>
       </c>
       <c r="E42" s="3">
-        <v>41332400</v>
+        <v>19283100</v>
       </c>
       <c r="F42" s="3">
-        <v>43222900</v>
+        <v>18486700</v>
       </c>
       <c r="G42" s="3">
-        <v>40294500</v>
+        <v>18215800</v>
       </c>
       <c r="H42" s="3">
-        <v>47257200</v>
+        <v>17492100</v>
       </c>
       <c r="I42" s="3">
-        <v>38509300</v>
+        <v>25108400</v>
       </c>
       <c r="J42" s="3">
+        <v>17703400</v>
+      </c>
+      <c r="K42" s="3">
         <v>41084100</v>
       </c>
-      <c r="K42" s="3">
+      <c r="L42" s="3">
         <v>48087900</v>
       </c>
-      <c r="L42" s="3">
+      <c r="M42" s="3">
         <v>44907700</v>
       </c>
-      <c r="M42" s="3">
+      <c r="N42" s="3">
         <v>44616700</v>
       </c>
-      <c r="N42" s="3">
+      <c r="O42" s="3">
         <v>44083500</v>
       </c>
-      <c r="O42" s="3">
+      <c r="P42" s="3">
         <v>38326100</v>
       </c>
-      <c r="P42" s="3">
+      <c r="Q42" s="3">
         <v>33800600</v>
       </c>
-      <c r="Q42" s="3">
+      <c r="R42" s="3">
         <v>32013900</v>
       </c>
-      <c r="R42" s="3">
+      <c r="S42" s="3">
         <v>39170300</v>
       </c>
-      <c r="S42" s="3">
+      <c r="T42" s="3">
         <v>33273800</v>
       </c>
-      <c r="T42" s="3">
+      <c r="U42" s="3">
         <v>36396600</v>
       </c>
-      <c r="U42" s="3">
+      <c r="V42" s="3">
         <v>38606200</v>
       </c>
-      <c r="V42" s="3">
+      <c r="W42" s="3">
         <v>37680800</v>
       </c>
-      <c r="W42" s="3">
+      <c r="X42" s="3">
         <v>39232200</v>
       </c>
-      <c r="X42" s="3">
+      <c r="Y42" s="3">
         <v>36892000</v>
       </c>
-      <c r="Y42" s="3">
+      <c r="Z42" s="3">
         <v>30905300</v>
       </c>
-      <c r="Z42" s="3">
+      <c r="AA42" s="3">
         <v>29776700</v>
       </c>
-      <c r="AA42" s="3">
+      <c r="AB42" s="3">
         <v>20883600</v>
       </c>
-      <c r="AB42" s="3">
+      <c r="AC42" s="3">
         <v>22286700</v>
       </c>
-      <c r="AC42" s="3">
+      <c r="AD42" s="3">
         <v>21840100</v>
       </c>
-      <c r="AD42" s="3">
+      <c r="AE42" s="3">
         <v>20932300</v>
       </c>
-      <c r="AE42" s="3">
+      <c r="AF42" s="3">
         <v>12488600</v>
       </c>
-      <c r="AF42" s="3">
+      <c r="AG42" s="3">
         <v>14955900</v>
       </c>
-      <c r="AG42" s="3">
+      <c r="AH42" s="3">
         <v>13350900</v>
       </c>
-      <c r="AH42" s="3">
+      <c r="AI42" s="3">
         <v>14204100</v>
       </c>
-      <c r="AI42" s="3">
+      <c r="AJ42" s="3">
         <v>16154100</v>
       </c>
     </row>
-    <row r="43" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="43" spans="2:36" x14ac:dyDescent="0.2">
       <c r="C43" s="1" t="s">
         <v>36</v>
       </c>
       <c r="D43" s="3">
-        <v>0</v>
+        <v>13077600</v>
       </c>
       <c r="E43" s="3">
-        <v>0</v>
+        <v>9540700</v>
       </c>
       <c r="F43" s="3">
-        <v>0</v>
+        <v>10078300</v>
       </c>
       <c r="G43" s="3">
-        <v>0</v>
+        <v>8598900</v>
       </c>
       <c r="H43" s="3">
-        <v>0</v>
+        <v>9843900</v>
       </c>
       <c r="I43" s="3">
-        <v>0</v>
+        <v>11594400</v>
       </c>
       <c r="J43" s="3">
-        <v>0</v>
+        <v>10468300</v>
       </c>
       <c r="K43" s="3">
         <v>0</v>
@@ -3901,31 +3988,34 @@
       <c r="AI43" s="3">
         <v>0</v>
       </c>
+      <c r="AJ43" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="44" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="44" spans="2:36" x14ac:dyDescent="0.2">
       <c r="C44" s="1" t="s">
         <v>37</v>
       </c>
-      <c r="D44" s="3">
-        <v>0</v>
-      </c>
-      <c r="E44" s="3">
-        <v>0</v>
-      </c>
-      <c r="F44" s="3">
-        <v>0</v>
-      </c>
-      <c r="G44" s="3">
-        <v>0</v>
-      </c>
-      <c r="H44" s="3">
-        <v>0</v>
-      </c>
-      <c r="I44" s="3">
-        <v>0</v>
-      </c>
-      <c r="J44" s="3">
-        <v>0</v>
+      <c r="D44" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="E44" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="F44" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="G44" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="H44" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="I44" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="J44" s="3" t="s">
+        <v>5</v>
       </c>
       <c r="K44" s="3">
         <v>0</v>
@@ -4002,31 +4092,34 @@
       <c r="AI44" s="3">
         <v>0</v>
       </c>
+      <c r="AJ44" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="45" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="45" spans="2:36" x14ac:dyDescent="0.2">
       <c r="C45" s="1" t="s">
         <v>38</v>
       </c>
       <c r="D45" s="3">
-        <v>0</v>
+        <v>2191600</v>
       </c>
       <c r="E45" s="3">
-        <v>0</v>
+        <v>2546100</v>
       </c>
       <c r="F45" s="3">
-        <v>0</v>
+        <v>2248400</v>
       </c>
       <c r="G45" s="3">
-        <v>0</v>
+        <v>3229200</v>
       </c>
       <c r="H45" s="3">
-        <v>0</v>
+        <v>2254000</v>
       </c>
       <c r="I45" s="3">
-        <v>0</v>
+        <v>2036900</v>
       </c>
       <c r="J45" s="3">
-        <v>0</v>
+        <v>1992400</v>
       </c>
       <c r="K45" s="3">
         <v>0</v>
@@ -4103,31 +4196,34 @@
       <c r="AI45" s="3">
         <v>0</v>
       </c>
+      <c r="AJ45" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="46" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="46" spans="2:36" x14ac:dyDescent="0.2">
       <c r="C46" s="1" t="s">
         <v>39</v>
       </c>
       <c r="D46" s="3">
-        <v>0</v>
+        <v>70438600</v>
       </c>
       <c r="E46" s="3">
-        <v>0</v>
+        <v>50125600</v>
       </c>
       <c r="F46" s="3">
-        <v>0</v>
+        <v>54875900</v>
       </c>
       <c r="G46" s="3">
-        <v>0</v>
+        <v>53874000</v>
       </c>
       <c r="H46" s="3">
-        <v>0</v>
+        <v>49079800</v>
       </c>
       <c r="I46" s="3">
-        <v>0</v>
+        <v>55527700</v>
       </c>
       <c r="J46" s="3">
-        <v>0</v>
+        <v>55109700</v>
       </c>
       <c r="K46" s="3">
         <v>0</v>
@@ -4204,311 +4300,323 @@
       <c r="AI46" s="3">
         <v>0</v>
       </c>
+      <c r="AJ46" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="47" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="47" spans="2:36" x14ac:dyDescent="0.2">
       <c r="C47" s="1" t="s">
         <v>40</v>
       </c>
       <c r="D47" s="3">
-        <v>1424500</v>
+        <v>43909700</v>
       </c>
       <c r="E47" s="3">
-        <v>1491000</v>
+        <v>45684200</v>
       </c>
       <c r="F47" s="3">
-        <v>1346500</v>
+        <v>45083200</v>
       </c>
       <c r="G47" s="3">
-        <v>1317600</v>
+        <v>33116700</v>
       </c>
       <c r="H47" s="3">
-        <v>1216300</v>
+        <v>46697400</v>
       </c>
       <c r="I47" s="3">
-        <v>1112300</v>
+        <v>47231400</v>
       </c>
       <c r="J47" s="3">
+        <v>47653400</v>
+      </c>
+      <c r="K47" s="3">
         <v>979200</v>
       </c>
-      <c r="K47" s="3">
+      <c r="L47" s="3">
         <v>976800</v>
       </c>
-      <c r="L47" s="3">
+      <c r="M47" s="3">
         <v>1035000</v>
       </c>
-      <c r="M47" s="3">
+      <c r="N47" s="3">
         <v>1011300</v>
       </c>
-      <c r="N47" s="3">
+      <c r="O47" s="3">
         <v>1001400</v>
       </c>
-      <c r="O47" s="3">
+      <c r="P47" s="3">
         <v>896000</v>
       </c>
-      <c r="P47" s="3">
+      <c r="Q47" s="3">
         <v>881500</v>
       </c>
-      <c r="Q47" s="3">
+      <c r="R47" s="3">
         <v>775800</v>
       </c>
-      <c r="R47" s="3">
+      <c r="S47" s="3">
         <v>735000</v>
       </c>
-      <c r="S47" s="3">
+      <c r="T47" s="3">
         <v>829200</v>
       </c>
-      <c r="T47" s="3">
+      <c r="U47" s="3">
         <v>714700</v>
       </c>
-      <c r="U47" s="3">
+      <c r="V47" s="3">
         <v>674300</v>
       </c>
-      <c r="V47" s="3">
+      <c r="W47" s="3">
         <v>685400</v>
       </c>
-      <c r="W47" s="3">
+      <c r="X47" s="3">
         <v>322100</v>
       </c>
-      <c r="X47" s="3">
+      <c r="Y47" s="3">
         <v>311500</v>
       </c>
-      <c r="Y47" s="3">
+      <c r="Z47" s="3">
         <v>316200</v>
       </c>
-      <c r="Z47" s="3">
+      <c r="AA47" s="3">
         <v>303600</v>
       </c>
-      <c r="AA47" s="3">
+      <c r="AB47" s="3">
         <v>276700</v>
       </c>
-      <c r="AB47" s="3">
+      <c r="AC47" s="3">
         <v>346900</v>
       </c>
-      <c r="AC47" s="3">
+      <c r="AD47" s="3">
         <v>348200</v>
       </c>
-      <c r="AD47" s="3">
+      <c r="AE47" s="3">
         <v>367000</v>
       </c>
-      <c r="AE47" s="3">
+      <c r="AF47" s="3">
         <v>490900</v>
       </c>
-      <c r="AF47" s="3">
+      <c r="AG47" s="3">
         <v>326300</v>
       </c>
-      <c r="AG47" s="3">
+      <c r="AH47" s="3">
         <v>351100</v>
       </c>
-      <c r="AH47" s="3">
+      <c r="AI47" s="3">
         <v>395100</v>
       </c>
-      <c r="AI47" s="3">
+      <c r="AJ47" s="3">
         <v>377600</v>
       </c>
     </row>
-    <row r="48" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="48" spans="2:36" x14ac:dyDescent="0.2">
       <c r="C48" s="1" t="s">
         <v>41</v>
       </c>
       <c r="D48" s="3">
-        <v>2851500</v>
+        <v>5522800</v>
       </c>
       <c r="E48" s="3">
-        <v>2741900</v>
+        <v>5103100</v>
       </c>
       <c r="F48" s="3">
-        <v>2737100</v>
+        <v>4908300</v>
       </c>
       <c r="G48" s="3">
-        <v>2709300</v>
+        <v>4983700</v>
       </c>
       <c r="H48" s="3">
-        <v>2705700</v>
+        <v>4486300</v>
       </c>
       <c r="I48" s="3">
-        <v>2728700</v>
+        <v>4434900</v>
       </c>
       <c r="J48" s="3">
+        <v>4401200</v>
+      </c>
+      <c r="K48" s="3">
         <v>2648000</v>
       </c>
-      <c r="K48" s="3">
+      <c r="L48" s="3">
         <v>2590300</v>
       </c>
-      <c r="L48" s="3">
+      <c r="M48" s="3">
         <v>2689200</v>
       </c>
-      <c r="M48" s="3">
+      <c r="N48" s="3">
         <v>2729900</v>
       </c>
-      <c r="N48" s="3">
+      <c r="O48" s="3">
         <v>2673200</v>
       </c>
-      <c r="O48" s="3">
+      <c r="P48" s="3">
         <v>2701000</v>
       </c>
-      <c r="P48" s="3">
+      <c r="Q48" s="3">
         <v>2682600</v>
       </c>
-      <c r="Q48" s="3">
+      <c r="R48" s="3">
         <v>2700600</v>
       </c>
-      <c r="R48" s="3">
+      <c r="S48" s="3">
         <v>2719200</v>
       </c>
-      <c r="S48" s="3">
+      <c r="T48" s="3">
         <v>2764300</v>
       </c>
-      <c r="T48" s="3">
+      <c r="U48" s="3">
         <v>2790300</v>
       </c>
-      <c r="U48" s="3">
+      <c r="V48" s="3">
         <v>2961700</v>
       </c>
-      <c r="V48" s="3">
+      <c r="W48" s="3">
         <v>3098200</v>
       </c>
-      <c r="W48" s="3">
+      <c r="X48" s="3">
         <v>3089800</v>
       </c>
-      <c r="X48" s="3">
+      <c r="Y48" s="3">
         <v>3058200</v>
       </c>
-      <c r="Y48" s="3">
+      <c r="Z48" s="3">
         <v>3080600</v>
       </c>
-      <c r="Z48" s="3">
+      <c r="AA48" s="3">
         <v>2368100</v>
       </c>
-      <c r="AA48" s="3">
+      <c r="AB48" s="3">
         <v>2284800</v>
       </c>
-      <c r="AB48" s="3">
+      <c r="AC48" s="3">
         <v>2378800</v>
       </c>
-      <c r="AC48" s="3">
+      <c r="AD48" s="3">
         <v>2384000</v>
       </c>
-      <c r="AD48" s="3">
+      <c r="AE48" s="3">
         <v>2507000</v>
       </c>
-      <c r="AE48" s="3">
+      <c r="AF48" s="3">
         <v>2509800</v>
       </c>
-      <c r="AF48" s="3">
+      <c r="AG48" s="3">
         <v>2480800</v>
       </c>
-      <c r="AG48" s="3">
+      <c r="AH48" s="3">
         <v>2470200</v>
       </c>
-      <c r="AH48" s="3">
+      <c r="AI48" s="3">
         <v>2534900</v>
       </c>
-      <c r="AI48" s="3">
+      <c r="AJ48" s="3">
         <v>2525400</v>
       </c>
     </row>
-    <row r="49" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="49" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C49" s="1" t="s">
         <v>42</v>
       </c>
       <c r="D49" s="3">
-        <v>769000</v>
+        <v>621800</v>
       </c>
       <c r="E49" s="3">
-        <v>749900</v>
+        <v>557800</v>
       </c>
       <c r="F49" s="3">
-        <v>747600</v>
+        <v>562600</v>
       </c>
       <c r="G49" s="3">
-        <v>738500</v>
+        <v>582000</v>
       </c>
       <c r="H49" s="3">
-        <v>742100</v>
+        <v>568100</v>
       </c>
       <c r="I49" s="3">
-        <v>720200</v>
+        <v>586300</v>
       </c>
       <c r="J49" s="3">
+        <v>573300</v>
+      </c>
+      <c r="K49" s="3">
         <v>636800</v>
       </c>
-      <c r="K49" s="3">
+      <c r="L49" s="3">
         <v>639200</v>
       </c>
-      <c r="L49" s="3">
+      <c r="M49" s="3">
         <v>596500</v>
       </c>
-      <c r="M49" s="3">
+      <c r="N49" s="3">
         <v>608700</v>
       </c>
-      <c r="N49" s="3">
+      <c r="O49" s="3">
         <v>589000</v>
       </c>
-      <c r="O49" s="3">
+      <c r="P49" s="3">
         <v>586400</v>
       </c>
-      <c r="P49" s="3">
+      <c r="Q49" s="3">
         <v>581700</v>
       </c>
-      <c r="Q49" s="3">
+      <c r="R49" s="3">
         <v>582600</v>
       </c>
-      <c r="R49" s="3">
+      <c r="S49" s="3">
         <v>586100</v>
       </c>
-      <c r="S49" s="3">
+      <c r="T49" s="3">
         <v>615800</v>
       </c>
-      <c r="T49" s="3">
+      <c r="U49" s="3">
         <v>631700</v>
       </c>
-      <c r="U49" s="3">
+      <c r="V49" s="3">
         <v>668000</v>
       </c>
-      <c r="V49" s="3">
+      <c r="W49" s="3">
         <v>717500</v>
       </c>
-      <c r="W49" s="3">
+      <c r="X49" s="3">
         <v>590200</v>
       </c>
-      <c r="X49" s="3">
+      <c r="Y49" s="3">
         <v>565800</v>
       </c>
-      <c r="Y49" s="3">
+      <c r="Z49" s="3">
         <v>588900</v>
       </c>
-      <c r="Z49" s="3">
+      <c r="AA49" s="3">
         <v>493300</v>
       </c>
-      <c r="AA49" s="3">
+      <c r="AB49" s="3">
         <v>502400</v>
       </c>
-      <c r="AB49" s="3">
+      <c r="AC49" s="3">
         <v>549000</v>
       </c>
-      <c r="AC49" s="3">
+      <c r="AD49" s="3">
         <v>452700</v>
       </c>
-      <c r="AD49" s="3">
+      <c r="AE49" s="3">
         <v>456400</v>
       </c>
-      <c r="AE49" s="3">
+      <c r="AF49" s="3">
         <v>461900</v>
       </c>
-      <c r="AF49" s="3">
+      <c r="AG49" s="3">
         <v>446100</v>
       </c>
-      <c r="AG49" s="3">
+      <c r="AH49" s="3">
         <v>415100</v>
       </c>
-      <c r="AH49" s="3">
+      <c r="AI49" s="3">
         <v>435400</v>
       </c>
-      <c r="AI49" s="3">
+      <c r="AJ49" s="3">
         <v>376700</v>
       </c>
     </row>
-    <row r="50" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="50" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C50" s="1" t="s">
         <v>43</v>
       </c>
@@ -4608,8 +4716,11 @@
       <c r="AI50" s="3">
         <v>0</v>
       </c>
+      <c r="AJ50" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="51" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="51" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C51" s="1" t="s">
         <v>44</v>
       </c>
@@ -4709,109 +4820,115 @@
       <c r="AI51" s="3">
         <v>0</v>
       </c>
+      <c r="AJ51" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="52" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="52" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C52" s="1" t="s">
         <v>45</v>
       </c>
       <c r="D52" s="3">
-        <v>147600</v>
+        <v>1117800</v>
       </c>
       <c r="E52" s="3">
-        <v>217600</v>
+        <v>1097200</v>
       </c>
       <c r="F52" s="3">
-        <v>265500</v>
+        <v>1375500</v>
       </c>
       <c r="G52" s="3">
-        <v>312800</v>
+        <v>17293300</v>
       </c>
       <c r="H52" s="3">
-        <v>297100</v>
+        <v>1488400</v>
       </c>
       <c r="I52" s="3">
-        <v>154800</v>
+        <v>1186200</v>
       </c>
       <c r="J52" s="3">
+        <v>1174600</v>
+      </c>
+      <c r="K52" s="3">
         <v>331800</v>
       </c>
-      <c r="K52" s="3">
+      <c r="L52" s="3">
         <v>284500</v>
       </c>
-      <c r="L52" s="3">
+      <c r="M52" s="3">
         <v>166400</v>
       </c>
-      <c r="M52" s="3">
+      <c r="N52" s="3">
         <v>58400</v>
       </c>
-      <c r="N52" s="3">
+      <c r="O52" s="3">
         <v>59100</v>
       </c>
-      <c r="O52" s="3">
+      <c r="P52" s="3">
         <v>41100</v>
       </c>
-      <c r="P52" s="3">
+      <c r="Q52" s="3">
         <v>56000</v>
       </c>
-      <c r="Q52" s="3">
+      <c r="R52" s="3">
         <v>73700</v>
       </c>
-      <c r="R52" s="3">
+      <c r="S52" s="3">
         <v>82700</v>
       </c>
-      <c r="S52" s="3">
+      <c r="T52" s="3">
         <v>74500</v>
       </c>
-      <c r="T52" s="3">
+      <c r="U52" s="3">
         <v>37800</v>
       </c>
-      <c r="U52" s="3">
+      <c r="V52" s="3">
         <v>38200</v>
       </c>
-      <c r="V52" s="3">
+      <c r="W52" s="3">
         <v>44800</v>
       </c>
-      <c r="W52" s="3">
+      <c r="X52" s="3">
         <v>82300</v>
       </c>
-      <c r="X52" s="3">
+      <c r="Y52" s="3">
         <v>69500</v>
       </c>
-      <c r="Y52" s="3">
+      <c r="Z52" s="3">
         <v>68200</v>
       </c>
-      <c r="Z52" s="3">
+      <c r="AA52" s="3">
         <v>120400</v>
       </c>
-      <c r="AA52" s="3">
+      <c r="AB52" s="3">
         <v>36800</v>
       </c>
-      <c r="AB52" s="3">
+      <c r="AC52" s="3">
         <v>91100</v>
       </c>
-      <c r="AC52" s="3">
+      <c r="AD52" s="3">
         <v>177600</v>
       </c>
-      <c r="AD52" s="3">
+      <c r="AE52" s="3">
         <v>289300</v>
       </c>
-      <c r="AE52" s="3">
+      <c r="AF52" s="3">
         <v>234800</v>
       </c>
-      <c r="AF52" s="3">
+      <c r="AG52" s="3">
         <v>221100</v>
       </c>
-      <c r="AG52" s="3">
+      <c r="AH52" s="3">
         <v>262700</v>
       </c>
-      <c r="AH52" s="3">
+      <c r="AI52" s="3">
         <v>274800</v>
       </c>
-      <c r="AI52" s="3">
+      <c r="AJ52" s="3">
         <v>143800</v>
       </c>
     </row>
-    <row r="53" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="53" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C53" s="1" t="s">
         <v>46</v>
       </c>
@@ -4911,109 +5028,115 @@
       <c r="AI53" s="3">
         <v>0</v>
       </c>
+      <c r="AJ53" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="54" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="54" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C54" s="1" t="s">
         <v>47</v>
       </c>
       <c r="D54" s="3">
-        <v>381585900</v>
+        <v>413964600</v>
       </c>
       <c r="E54" s="3">
-        <v>378575500</v>
+        <v>369217100</v>
       </c>
       <c r="F54" s="3">
-        <v>373503700</v>
+        <v>375587700</v>
       </c>
       <c r="G54" s="3">
-        <v>364437800</v>
+        <v>384037900</v>
       </c>
       <c r="H54" s="3">
-        <v>362183700</v>
+        <v>360962600</v>
       </c>
       <c r="I54" s="3">
-        <v>358559400</v>
+        <v>366653200</v>
       </c>
       <c r="J54" s="3">
+        <v>366661700</v>
+      </c>
+      <c r="K54" s="3">
         <v>360355800</v>
       </c>
-      <c r="K54" s="3">
+      <c r="L54" s="3">
         <v>366510300</v>
       </c>
-      <c r="L54" s="3">
+      <c r="M54" s="3">
         <v>368558700</v>
       </c>
-      <c r="M54" s="3">
+      <c r="N54" s="3">
         <v>358592300</v>
       </c>
-      <c r="N54" s="3">
+      <c r="O54" s="3">
         <v>335387900</v>
       </c>
-      <c r="O54" s="3">
+      <c r="P54" s="3">
         <v>328638700</v>
       </c>
-      <c r="P54" s="3">
+      <c r="Q54" s="3">
         <v>315953000</v>
       </c>
-      <c r="Q54" s="3">
+      <c r="R54" s="3">
         <v>307917200</v>
       </c>
-      <c r="R54" s="3">
+      <c r="S54" s="3">
         <v>295320000</v>
       </c>
-      <c r="S54" s="3">
+      <c r="T54" s="3">
         <v>293246000</v>
       </c>
-      <c r="T54" s="3">
+      <c r="U54" s="3">
         <v>292659600</v>
       </c>
-      <c r="U54" s="3">
+      <c r="V54" s="3">
         <v>306353500</v>
       </c>
-      <c r="V54" s="3">
+      <c r="W54" s="3">
         <v>307683600</v>
       </c>
-      <c r="W54" s="3">
+      <c r="X54" s="3">
         <v>314996600</v>
       </c>
-      <c r="X54" s="3">
+      <c r="Y54" s="3">
         <v>316273500</v>
       </c>
-      <c r="Y54" s="3">
+      <c r="Z54" s="3">
         <v>314085600</v>
       </c>
-      <c r="Z54" s="3">
+      <c r="AA54" s="3">
         <v>285975600</v>
       </c>
-      <c r="AA54" s="3">
+      <c r="AB54" s="3">
         <v>267139300</v>
       </c>
-      <c r="AB54" s="3">
+      <c r="AC54" s="3">
         <v>274311500</v>
       </c>
-      <c r="AC54" s="3">
+      <c r="AD54" s="3">
         <v>273668600</v>
       </c>
-      <c r="AD54" s="3">
+      <c r="AE54" s="3">
         <v>278340000</v>
       </c>
-      <c r="AE54" s="3">
+      <c r="AF54" s="3">
         <v>279730100</v>
       </c>
-      <c r="AF54" s="3">
+      <c r="AG54" s="3">
         <v>278137400</v>
       </c>
-      <c r="AG54" s="3">
+      <c r="AH54" s="3">
         <v>273600800</v>
       </c>
-      <c r="AH54" s="3">
+      <c r="AI54" s="3">
         <v>279614500</v>
       </c>
-      <c r="AI54" s="3">
+      <c r="AJ54" s="3">
         <v>281548700</v>
       </c>
     </row>
-    <row r="55" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="55" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C55" s="1" t="s">
         <v>48</v>
       </c>
@@ -5049,8 +5172,9 @@
       <c r="AG55" s="3"/>
       <c r="AH55" s="3"/>
       <c r="AI55" s="3"/>
+      <c r="AJ55" s="3"/>
     </row>
-    <row r="56" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="56" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C56" s="1" t="s">
         <v>49</v>
       </c>
@@ -5086,132 +5210,136 @@
       <c r="AG56" s="3"/>
       <c r="AH56" s="3"/>
       <c r="AI56" s="3"/>
+      <c r="AJ56" s="3"/>
     </row>
-    <row r="57" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="57" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C57" s="1" t="s">
         <v>50</v>
       </c>
-      <c r="D57" s="3" t="s">
-        <v>5</v>
+      <c r="D57" s="3">
+        <v>303683400</v>
       </c>
       <c r="E57" s="3">
-        <v>13774400</v>
+        <v>269353200</v>
       </c>
       <c r="F57" s="3">
-        <v>9347000</v>
+        <v>273669100</v>
       </c>
       <c r="G57" s="3">
-        <v>14303900</v>
+        <v>283746600</v>
       </c>
       <c r="H57" s="3">
-        <v>14578600</v>
+        <v>257925300</v>
       </c>
       <c r="I57" s="3">
-        <v>13679900</v>
+        <v>263215600</v>
       </c>
       <c r="J57" s="3">
+        <v>259046400</v>
+      </c>
+      <c r="K57" s="3">
         <v>8592200</v>
       </c>
-      <c r="K57" s="3">
+      <c r="L57" s="3">
         <v>12736100</v>
       </c>
-      <c r="L57" s="3">
+      <c r="M57" s="3">
         <v>12538100</v>
       </c>
-      <c r="M57" s="3">
+      <c r="N57" s="3">
         <v>11104000</v>
       </c>
-      <c r="N57" s="3">
+      <c r="O57" s="3">
         <v>10844700</v>
       </c>
-      <c r="O57" s="3">
+      <c r="P57" s="3">
         <v>7957500</v>
       </c>
-      <c r="P57" s="3">
+      <c r="Q57" s="3">
         <v>9468900</v>
       </c>
-      <c r="Q57" s="3">
+      <c r="R57" s="3">
         <v>7995800</v>
       </c>
-      <c r="R57" s="3">
+      <c r="S57" s="3">
         <v>3698600</v>
       </c>
-      <c r="S57" s="3">
+      <c r="T57" s="3">
         <v>7530800</v>
       </c>
-      <c r="T57" s="3">
+      <c r="U57" s="3">
         <v>8467000</v>
       </c>
-      <c r="U57" s="3">
+      <c r="V57" s="3">
         <v>9538600</v>
       </c>
-      <c r="V57" s="3">
+      <c r="W57" s="3">
         <v>7264700</v>
       </c>
-      <c r="W57" s="3">
+      <c r="X57" s="3">
         <v>13339700</v>
       </c>
-      <c r="X57" s="3">
+      <c r="Y57" s="3">
         <v>15138200</v>
       </c>
-      <c r="Y57" s="3">
+      <c r="Z57" s="3">
         <v>14778600</v>
       </c>
-      <c r="Z57" s="3">
+      <c r="AA57" s="3">
         <v>10988500</v>
       </c>
-      <c r="AA57" s="3">
+      <c r="AB57" s="3">
         <v>12068900</v>
       </c>
-      <c r="AB57" s="3">
+      <c r="AC57" s="3">
         <v>11638400</v>
       </c>
-      <c r="AC57" s="3">
+      <c r="AD57" s="3">
         <v>12317300</v>
       </c>
-      <c r="AD57" s="3">
+      <c r="AE57" s="3">
         <v>5801500</v>
       </c>
-      <c r="AE57" s="3">
+      <c r="AF57" s="3">
         <v>13814400</v>
       </c>
-      <c r="AF57" s="3">
+      <c r="AG57" s="3">
         <v>14756900</v>
       </c>
-      <c r="AG57" s="3">
+      <c r="AH57" s="3">
         <v>10823000</v>
       </c>
-      <c r="AH57" s="3">
+      <c r="AI57" s="3">
         <v>13329400</v>
       </c>
-      <c r="AI57" s="3">
+      <c r="AJ57" s="3">
         <v>15356600</v>
       </c>
     </row>
-    <row r="58" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="58" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C58" s="1" t="s">
         <v>51</v>
       </c>
       <c r="D58" s="3">
-        <v>0</v>
+        <v>10388900</v>
       </c>
       <c r="E58" s="3">
-        <v>0</v>
+        <v>10701400</v>
       </c>
       <c r="F58" s="3">
-        <v>0</v>
+        <v>11337600</v>
       </c>
       <c r="G58" s="3">
-        <v>0</v>
+        <v>9863100</v>
       </c>
       <c r="H58" s="3">
-        <v>0</v>
+        <v>11103300</v>
       </c>
       <c r="I58" s="3">
-        <v>0</v>
+        <v>10559700</v>
       </c>
       <c r="J58" s="3">
-        <v>0</v>
+        <v>10550500</v>
       </c>
       <c r="K58" s="3">
         <v>0</v>
@@ -5288,132 +5416,138 @@
       <c r="AI58" s="3">
         <v>0</v>
       </c>
+      <c r="AJ58" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="59" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="59" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C59" s="1" t="s">
         <v>52</v>
       </c>
       <c r="D59" s="3">
-        <v>109400</v>
+        <v>917100</v>
       </c>
       <c r="E59" s="3">
-        <v>3293300</v>
+        <v>585700</v>
       </c>
       <c r="F59" s="3">
-        <v>3332200</v>
+        <v>748600</v>
       </c>
       <c r="G59" s="3">
-        <v>3472800</v>
+        <v>795100</v>
       </c>
       <c r="H59" s="3">
-        <v>3076300</v>
+        <v>581800</v>
       </c>
       <c r="I59" s="3">
-        <v>3259400</v>
+        <v>593500</v>
       </c>
       <c r="J59" s="3">
+        <v>1203800</v>
+      </c>
+      <c r="K59" s="3">
         <v>3047200</v>
       </c>
-      <c r="K59" s="3">
+      <c r="L59" s="3">
         <v>2229700</v>
       </c>
-      <c r="L59" s="3">
+      <c r="M59" s="3">
         <v>1968300</v>
       </c>
-      <c r="M59" s="3">
+      <c r="N59" s="3">
         <v>2093100</v>
       </c>
-      <c r="N59" s="3">
+      <c r="O59" s="3">
         <v>1991300</v>
       </c>
-      <c r="O59" s="3">
+      <c r="P59" s="3">
         <v>1538600</v>
       </c>
-      <c r="P59" s="3">
+      <c r="Q59" s="3">
         <v>1446500</v>
       </c>
-      <c r="Q59" s="3">
+      <c r="R59" s="3">
         <v>1600800</v>
       </c>
-      <c r="R59" s="3">
+      <c r="S59" s="3">
         <v>1790900</v>
       </c>
-      <c r="S59" s="3">
+      <c r="T59" s="3">
         <v>1521700</v>
       </c>
-      <c r="T59" s="3">
+      <c r="U59" s="3">
         <v>1545300</v>
       </c>
-      <c r="U59" s="3">
+      <c r="V59" s="3">
         <v>1892000</v>
       </c>
-      <c r="V59" s="3">
+      <c r="W59" s="3">
         <v>2294100</v>
       </c>
-      <c r="W59" s="3">
+      <c r="X59" s="3">
         <v>2199800</v>
       </c>
-      <c r="X59" s="3">
+      <c r="Y59" s="3">
         <v>2064700</v>
       </c>
-      <c r="Y59" s="3">
+      <c r="Z59" s="3">
         <v>2149400</v>
       </c>
-      <c r="Z59" s="3">
+      <c r="AA59" s="3">
         <v>1989900</v>
       </c>
-      <c r="AA59" s="3">
+      <c r="AB59" s="3">
         <v>1798500</v>
       </c>
-      <c r="AB59" s="3">
+      <c r="AC59" s="3">
         <v>1649500</v>
       </c>
-      <c r="AC59" s="3">
+      <c r="AD59" s="3">
         <v>1642100</v>
       </c>
-      <c r="AD59" s="3">
+      <c r="AE59" s="3">
         <v>2008600</v>
       </c>
-      <c r="AE59" s="3">
+      <c r="AF59" s="3">
         <v>2057400</v>
       </c>
-      <c r="AF59" s="3">
+      <c r="AG59" s="3">
         <v>1681400</v>
       </c>
-      <c r="AG59" s="3">
+      <c r="AH59" s="3">
         <v>1880000</v>
       </c>
-      <c r="AH59" s="3">
+      <c r="AI59" s="3">
         <v>2004400</v>
       </c>
-      <c r="AI59" s="3">
+      <c r="AJ59" s="3">
         <v>1813400</v>
       </c>
     </row>
-    <row r="60" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="60" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C60" s="1" t="s">
         <v>53</v>
       </c>
       <c r="D60" s="3">
-        <v>0</v>
+        <v>318811800</v>
       </c>
       <c r="E60" s="3">
-        <v>0</v>
+        <v>283969800</v>
       </c>
       <c r="F60" s="3">
-        <v>0</v>
+        <v>288965400</v>
       </c>
       <c r="G60" s="3">
-        <v>0</v>
+        <v>297751000</v>
       </c>
       <c r="H60" s="3">
-        <v>0</v>
+        <v>272946300</v>
       </c>
       <c r="I60" s="3">
-        <v>0</v>
+        <v>277365200</v>
       </c>
       <c r="J60" s="3">
-        <v>0</v>
+        <v>273486900</v>
       </c>
       <c r="K60" s="3">
         <v>0</v>
@@ -5490,210 +5624,219 @@
       <c r="AI60" s="3">
         <v>0</v>
       </c>
+      <c r="AJ60" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="61" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="61" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C61" s="1" t="s">
         <v>54</v>
       </c>
       <c r="D61" s="3">
-        <v>54313100</v>
+        <v>57884900</v>
       </c>
       <c r="E61" s="3">
-        <v>52340200</v>
+        <v>51737100</v>
       </c>
       <c r="F61" s="3">
-        <v>52738700</v>
+        <v>52671400</v>
       </c>
       <c r="G61" s="3">
-        <v>53164900</v>
+        <v>54929200</v>
       </c>
       <c r="H61" s="3">
-        <v>53380200</v>
+        <v>53360000</v>
       </c>
       <c r="I61" s="3">
-        <v>53272300</v>
+        <v>54858600</v>
       </c>
       <c r="J61" s="3">
+        <v>55629400</v>
+      </c>
+      <c r="K61" s="3">
         <v>52670100</v>
       </c>
-      <c r="K61" s="3">
+      <c r="L61" s="3">
         <v>58817800</v>
       </c>
-      <c r="L61" s="3">
+      <c r="M61" s="3">
         <v>58413400</v>
       </c>
-      <c r="M61" s="3">
+      <c r="N61" s="3">
         <v>54512100</v>
       </c>
-      <c r="N61" s="3">
+      <c r="O61" s="3">
         <v>51506600</v>
       </c>
-      <c r="O61" s="3">
+      <c r="P61" s="3">
         <v>49335300</v>
       </c>
-      <c r="P61" s="3">
+      <c r="Q61" s="3">
         <v>46999300</v>
       </c>
-      <c r="Q61" s="3">
+      <c r="R61" s="3">
         <v>43329900</v>
       </c>
-      <c r="R61" s="3">
+      <c r="S61" s="3">
         <v>42586400</v>
       </c>
-      <c r="S61" s="3">
+      <c r="T61" s="3">
         <v>38230600</v>
       </c>
-      <c r="T61" s="3">
+      <c r="U61" s="3">
         <v>39214800</v>
       </c>
-      <c r="U61" s="3">
+      <c r="V61" s="3">
         <v>43080800</v>
       </c>
-      <c r="V61" s="3">
+      <c r="W61" s="3">
         <v>42129500</v>
       </c>
-      <c r="W61" s="3">
+      <c r="X61" s="3">
         <v>44185000</v>
       </c>
-      <c r="X61" s="3">
+      <c r="Y61" s="3">
         <v>43142100</v>
       </c>
-      <c r="Y61" s="3">
+      <c r="Z61" s="3">
         <v>40307800</v>
       </c>
-      <c r="Z61" s="3">
+      <c r="AA61" s="3">
         <v>36868700</v>
       </c>
-      <c r="AA61" s="3">
+      <c r="AB61" s="3">
         <v>34955700</v>
       </c>
-      <c r="AB61" s="3">
+      <c r="AC61" s="3">
         <v>35115500</v>
       </c>
-      <c r="AC61" s="3">
+      <c r="AD61" s="3">
         <v>34009900</v>
       </c>
-      <c r="AD61" s="3">
+      <c r="AE61" s="3">
         <v>36941800</v>
       </c>
-      <c r="AE61" s="3">
+      <c r="AF61" s="3">
         <v>37408900</v>
       </c>
-      <c r="AF61" s="3">
+      <c r="AG61" s="3">
         <v>35000000</v>
       </c>
-      <c r="AG61" s="3">
+      <c r="AH61" s="3">
         <v>33280700</v>
       </c>
-      <c r="AH61" s="3">
+      <c r="AI61" s="3">
         <v>34538700</v>
       </c>
-      <c r="AI61" s="3">
+      <c r="AJ61" s="3">
         <v>33926000</v>
       </c>
     </row>
-    <row r="62" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="62" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C62" s="1" t="s">
         <v>55</v>
       </c>
       <c r="D62" s="3">
-        <v>969600</v>
+        <v>8065900</v>
       </c>
       <c r="E62" s="3">
-        <v>866400</v>
+        <v>6973100</v>
       </c>
       <c r="F62" s="3">
-        <v>962500</v>
+        <v>7766400</v>
       </c>
       <c r="G62" s="3">
-        <v>820400</v>
+        <v>4724200</v>
       </c>
       <c r="H62" s="3">
-        <v>779900</v>
+        <v>8885900</v>
       </c>
       <c r="I62" s="3">
-        <v>589300</v>
+        <v>8657200</v>
       </c>
       <c r="J62" s="3">
+        <v>11788800</v>
+      </c>
+      <c r="K62" s="3">
         <v>459600</v>
       </c>
-      <c r="K62" s="3">
+      <c r="L62" s="3">
         <v>438000</v>
       </c>
-      <c r="L62" s="3">
+      <c r="M62" s="3">
         <v>469900</v>
       </c>
-      <c r="M62" s="3">
+      <c r="N62" s="3">
         <v>523500</v>
       </c>
-      <c r="N62" s="3">
+      <c r="O62" s="3">
         <v>608300</v>
       </c>
-      <c r="O62" s="3">
+      <c r="P62" s="3">
         <v>663300</v>
       </c>
-      <c r="P62" s="3">
+      <c r="Q62" s="3">
         <v>620300</v>
       </c>
-      <c r="Q62" s="3">
+      <c r="R62" s="3">
         <v>542300</v>
       </c>
-      <c r="R62" s="3">
+      <c r="S62" s="3">
         <v>528500</v>
       </c>
-      <c r="S62" s="3">
+      <c r="T62" s="3">
         <v>720700</v>
       </c>
-      <c r="T62" s="3">
+      <c r="U62" s="3">
         <v>691400</v>
       </c>
-      <c r="U62" s="3">
+      <c r="V62" s="3">
         <v>680000</v>
       </c>
-      <c r="V62" s="3">
+      <c r="W62" s="3">
         <v>570200</v>
       </c>
-      <c r="W62" s="3">
+      <c r="X62" s="3">
         <v>714600</v>
       </c>
-      <c r="X62" s="3">
+      <c r="Y62" s="3">
         <v>648100</v>
       </c>
-      <c r="Y62" s="3">
+      <c r="Z62" s="3">
         <v>618700</v>
       </c>
-      <c r="Z62" s="3">
+      <c r="AA62" s="3">
         <v>520300</v>
       </c>
-      <c r="AA62" s="3">
+      <c r="AB62" s="3">
         <v>418500</v>
       </c>
-      <c r="AB62" s="3">
+      <c r="AC62" s="3">
         <v>420800</v>
       </c>
-      <c r="AC62" s="3">
+      <c r="AD62" s="3">
         <v>527700</v>
       </c>
-      <c r="AD62" s="3">
+      <c r="AE62" s="3">
         <v>419200</v>
       </c>
-      <c r="AE62" s="3">
+      <c r="AF62" s="3">
         <v>395900</v>
       </c>
-      <c r="AF62" s="3">
+      <c r="AG62" s="3">
         <v>382900</v>
       </c>
-      <c r="AG62" s="3">
+      <c r="AH62" s="3">
         <v>400700</v>
       </c>
-      <c r="AH62" s="3">
+      <c r="AI62" s="3">
         <v>463600</v>
       </c>
-      <c r="AI62" s="3">
+      <c r="AJ62" s="3">
         <v>459900</v>
       </c>
     </row>
-    <row r="63" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="63" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C63" s="1" t="s">
         <v>56</v>
       </c>
@@ -5793,8 +5936,11 @@
       <c r="AI63" s="3">
         <v>0</v>
       </c>
+      <c r="AJ63" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="64" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="64" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C64" s="1" t="s">
         <v>20</v>
       </c>
@@ -5894,8 +6040,11 @@
       <c r="AI64" s="3">
         <v>0</v>
       </c>
+      <c r="AJ64" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="65" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="65" spans="2:36" x14ac:dyDescent="0.2">
       <c r="C65" s="1" t="s">
         <v>57</v>
       </c>
@@ -5995,109 +6144,115 @@
       <c r="AI65" s="3">
         <v>0</v>
       </c>
+      <c r="AJ65" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="66" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="66" spans="2:36" x14ac:dyDescent="0.2">
       <c r="C66" s="1" t="s">
         <v>58</v>
       </c>
       <c r="D66" s="3">
-        <v>356485900</v>
+        <v>386400900</v>
       </c>
       <c r="E66" s="3">
-        <v>354407700</v>
+        <v>343710800</v>
       </c>
       <c r="F66" s="3">
-        <v>349753500</v>
+        <v>350345300</v>
       </c>
       <c r="G66" s="3">
-        <v>340748800</v>
+        <v>358283300</v>
       </c>
       <c r="H66" s="3">
-        <v>339500200</v>
+        <v>336284100</v>
       </c>
       <c r="I66" s="3">
-        <v>336314700</v>
+        <v>341832200</v>
       </c>
       <c r="J66" s="3">
+        <v>341656500</v>
+      </c>
+      <c r="K66" s="3">
         <v>338784400</v>
       </c>
-      <c r="K66" s="3">
+      <c r="L66" s="3">
         <v>345885900</v>
       </c>
-      <c r="L66" s="3">
+      <c r="M66" s="3">
         <v>348018900</v>
       </c>
-      <c r="M66" s="3">
+      <c r="N66" s="3">
         <v>338354200</v>
       </c>
-      <c r="N66" s="3">
+      <c r="O66" s="3">
         <v>316006400</v>
       </c>
-      <c r="O66" s="3">
+      <c r="P66" s="3">
         <v>309651700</v>
       </c>
-      <c r="P66" s="3">
+      <c r="Q66" s="3">
         <v>297533600</v>
       </c>
-      <c r="Q66" s="3">
+      <c r="R66" s="3">
         <v>290517700</v>
       </c>
-      <c r="R66" s="3">
+      <c r="S66" s="3">
         <v>278260300</v>
       </c>
-      <c r="S66" s="3">
+      <c r="T66" s="3">
         <v>275726000</v>
       </c>
-      <c r="T66" s="3">
+      <c r="U66" s="3">
         <v>275487700</v>
       </c>
-      <c r="U66" s="3">
+      <c r="V66" s="3">
         <v>288675900</v>
       </c>
-      <c r="V66" s="3">
+      <c r="W66" s="3">
         <v>289399800</v>
       </c>
-      <c r="W66" s="3">
+      <c r="X66" s="3">
         <v>297278600</v>
       </c>
-      <c r="X66" s="3">
+      <c r="Y66" s="3">
         <v>299163500</v>
       </c>
-      <c r="Y66" s="3">
+      <c r="Z66" s="3">
         <v>296968200</v>
       </c>
-      <c r="Z66" s="3">
+      <c r="AA66" s="3">
         <v>267714100</v>
       </c>
-      <c r="AA66" s="3">
+      <c r="AB66" s="3">
         <v>249559900</v>
       </c>
-      <c r="AB66" s="3">
+      <c r="AC66" s="3">
         <v>256847800</v>
       </c>
-      <c r="AC66" s="3">
+      <c r="AD66" s="3">
         <v>256582900</v>
       </c>
-      <c r="AD66" s="3">
+      <c r="AE66" s="3">
         <v>260418000</v>
       </c>
-      <c r="AE66" s="3">
+      <c r="AF66" s="3">
         <v>261733600</v>
       </c>
-      <c r="AF66" s="3">
+      <c r="AG66" s="3">
         <v>260311800</v>
       </c>
-      <c r="AG66" s="3">
+      <c r="AH66" s="3">
         <v>255640700</v>
       </c>
-      <c r="AH66" s="3">
+      <c r="AI66" s="3">
         <v>261266900</v>
       </c>
-      <c r="AI66" s="3">
+      <c r="AJ66" s="3">
         <v>263136400</v>
       </c>
     </row>
-    <row r="67" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="67" spans="2:36" x14ac:dyDescent="0.2">
       <c r="C67" s="1" t="s">
         <v>59</v>
       </c>
@@ -6133,8 +6288,9 @@
       <c r="AG67" s="3"/>
       <c r="AH67" s="3"/>
       <c r="AI67" s="3"/>
+      <c r="AJ67" s="3"/>
     </row>
-    <row r="68" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="68" spans="2:36" x14ac:dyDescent="0.2">
       <c r="C68" s="1" t="s">
         <v>60</v>
       </c>
@@ -6234,8 +6390,11 @@
       <c r="AI68" s="3">
         <v>0</v>
       </c>
+      <c r="AJ68" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="69" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="69" spans="2:36" x14ac:dyDescent="0.2">
       <c r="C69" s="1" t="s">
         <v>61</v>
       </c>
@@ -6335,8 +6494,11 @@
       <c r="AI69" s="3">
         <v>0</v>
       </c>
+      <c r="AJ69" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="70" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="70" spans="2:36" x14ac:dyDescent="0.2">
       <c r="C70" s="1" t="s">
         <v>62</v>
       </c>
@@ -6436,8 +6598,11 @@
       <c r="AI70" s="3">
         <v>0</v>
       </c>
+      <c r="AJ70" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="71" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="71" spans="2:36" x14ac:dyDescent="0.2">
       <c r="C71" s="1" t="s">
         <v>63</v>
       </c>
@@ -6537,109 +6702,115 @@
       <c r="AI71" s="3">
         <v>0</v>
       </c>
+      <c r="AJ71" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="72" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="72" spans="2:36" x14ac:dyDescent="0.2">
       <c r="C72" s="1" t="s">
         <v>64</v>
       </c>
       <c r="D72" s="3">
-        <v>19437000</v>
+        <v>20282200</v>
       </c>
       <c r="E72" s="3">
-        <v>18868000</v>
+        <v>18807000</v>
       </c>
       <c r="F72" s="3">
-        <v>18739900</v>
+        <v>18719000</v>
       </c>
       <c r="G72" s="3">
-        <v>18890800</v>
+        <v>19268400</v>
       </c>
       <c r="H72" s="3">
-        <v>18339100</v>
+        <v>18710700</v>
       </c>
       <c r="I72" s="3">
-        <v>17894800</v>
+        <v>18565400</v>
       </c>
       <c r="J72" s="3">
+        <v>18299100</v>
+      </c>
+      <c r="K72" s="3">
         <v>17812600</v>
       </c>
-      <c r="K72" s="3">
+      <c r="L72" s="3">
         <v>17007700</v>
       </c>
-      <c r="L72" s="3">
+      <c r="M72" s="3">
         <v>17130600</v>
       </c>
-      <c r="M72" s="3">
+      <c r="N72" s="3">
         <v>16662400</v>
       </c>
-      <c r="N72" s="3">
+      <c r="O72" s="3">
         <v>16044400</v>
       </c>
-      <c r="O72" s="3">
+      <c r="P72" s="3">
         <v>15764300</v>
       </c>
-      <c r="P72" s="3">
+      <c r="Q72" s="3">
         <v>15298800</v>
       </c>
-      <c r="Q72" s="3">
+      <c r="R72" s="3">
         <v>14524300</v>
       </c>
-      <c r="R72" s="3">
+      <c r="S72" s="3">
         <v>14258500</v>
       </c>
-      <c r="S72" s="3">
+      <c r="T72" s="3">
         <v>14719300</v>
       </c>
-      <c r="T72" s="3">
+      <c r="U72" s="3">
         <v>14362200</v>
       </c>
-      <c r="U72" s="3">
+      <c r="V72" s="3">
         <v>15002800</v>
       </c>
-      <c r="V72" s="3">
+      <c r="W72" s="3">
         <v>15745800</v>
       </c>
-      <c r="W72" s="3">
+      <c r="X72" s="3">
         <v>15573800</v>
       </c>
-      <c r="X72" s="3">
+      <c r="Y72" s="3">
         <v>15698600</v>
       </c>
-      <c r="Y72" s="3">
+      <c r="Z72" s="3">
         <v>15678000</v>
       </c>
-      <c r="Z72" s="3">
+      <c r="AA72" s="3">
         <v>14384700</v>
       </c>
-      <c r="AA72" s="3">
+      <c r="AB72" s="3">
         <v>13795900</v>
       </c>
-      <c r="AB72" s="3">
+      <c r="AC72" s="3">
         <v>13837700</v>
       </c>
-      <c r="AC72" s="3">
+      <c r="AD72" s="3">
         <v>13273900</v>
       </c>
-      <c r="AD72" s="3">
+      <c r="AE72" s="3">
         <v>13745600</v>
       </c>
-      <c r="AE72" s="3">
+      <c r="AF72" s="3">
         <v>13660700</v>
       </c>
-      <c r="AF72" s="3">
+      <c r="AG72" s="3">
         <v>13507800</v>
       </c>
-      <c r="AG72" s="3">
+      <c r="AH72" s="3">
         <v>13138800</v>
       </c>
-      <c r="AH72" s="3">
+      <c r="AI72" s="3">
         <v>13150400</v>
       </c>
-      <c r="AI72" s="3">
+      <c r="AJ72" s="3">
         <v>13062800</v>
       </c>
     </row>
-    <row r="73" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="73" spans="2:36" x14ac:dyDescent="0.2">
       <c r="C73" s="1" t="s">
         <v>65</v>
       </c>
@@ -6739,8 +6910,11 @@
       <c r="AI73" s="3">
         <v>0</v>
       </c>
+      <c r="AJ73" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="74" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="74" spans="2:36" x14ac:dyDescent="0.2">
       <c r="C74" s="1" t="s">
         <v>66</v>
       </c>
@@ -6840,8 +7014,11 @@
       <c r="AI74" s="3">
         <v>0</v>
       </c>
+      <c r="AJ74" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="75" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="75" spans="2:36" x14ac:dyDescent="0.2">
       <c r="C75" s="1" t="s">
         <v>67</v>
       </c>
@@ -6941,109 +7118,115 @@
       <c r="AI75" s="3">
         <v>0</v>
       </c>
+      <c r="AJ75" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="76" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="76" spans="2:36" x14ac:dyDescent="0.2">
       <c r="C76" s="1" t="s">
         <v>68</v>
       </c>
       <c r="D76" s="3">
-        <v>25099900</v>
+        <v>25698700</v>
       </c>
       <c r="E76" s="3">
-        <v>24167800</v>
+        <v>24286300</v>
       </c>
       <c r="F76" s="3">
-        <v>23750200</v>
+        <v>23977100</v>
       </c>
       <c r="G76" s="3">
-        <v>23688900</v>
+        <v>24420000</v>
       </c>
       <c r="H76" s="3">
-        <v>22683500</v>
+        <v>23463000</v>
       </c>
       <c r="I76" s="3">
-        <v>22244800</v>
+        <v>22963400</v>
       </c>
       <c r="J76" s="3">
+        <v>22747400</v>
+      </c>
+      <c r="K76" s="3">
         <v>21571400</v>
       </c>
-      <c r="K76" s="3">
+      <c r="L76" s="3">
         <v>20624400</v>
       </c>
-      <c r="L76" s="3">
+      <c r="M76" s="3">
         <v>20539800</v>
       </c>
-      <c r="M76" s="3">
+      <c r="N76" s="3">
         <v>20238100</v>
       </c>
-      <c r="N76" s="3">
+      <c r="O76" s="3">
         <v>19381500</v>
       </c>
-      <c r="O76" s="3">
+      <c r="P76" s="3">
         <v>18987000</v>
       </c>
-      <c r="P76" s="3">
+      <c r="Q76" s="3">
         <v>18419400</v>
       </c>
-      <c r="Q76" s="3">
+      <c r="R76" s="3">
         <v>17399500</v>
       </c>
-      <c r="R76" s="3">
+      <c r="S76" s="3">
         <v>17059700</v>
       </c>
-      <c r="S76" s="3">
+      <c r="T76" s="3">
         <v>17519900</v>
       </c>
-      <c r="T76" s="3">
+      <c r="U76" s="3">
         <v>17171900</v>
       </c>
-      <c r="U76" s="3">
+      <c r="V76" s="3">
         <v>17677500</v>
       </c>
-      <c r="V76" s="3">
+      <c r="W76" s="3">
         <v>18283800</v>
       </c>
-      <c r="W76" s="3">
+      <c r="X76" s="3">
         <v>17718000</v>
       </c>
-      <c r="X76" s="3">
+      <c r="Y76" s="3">
         <v>17110000</v>
       </c>
-      <c r="Y76" s="3">
+      <c r="Z76" s="3">
         <v>17117400</v>
       </c>
-      <c r="Z76" s="3">
+      <c r="AA76" s="3">
         <v>18261500</v>
       </c>
-      <c r="AA76" s="3">
+      <c r="AB76" s="3">
         <v>17579400</v>
       </c>
-      <c r="AB76" s="3">
+      <c r="AC76" s="3">
         <v>17463800</v>
       </c>
-      <c r="AC76" s="3">
+      <c r="AD76" s="3">
         <v>17085700</v>
       </c>
-      <c r="AD76" s="3">
+      <c r="AE76" s="3">
         <v>17922000</v>
       </c>
-      <c r="AE76" s="3">
+      <c r="AF76" s="3">
         <v>17996500</v>
       </c>
-      <c r="AF76" s="3">
+      <c r="AG76" s="3">
         <v>17825600</v>
       </c>
-      <c r="AG76" s="3">
+      <c r="AH76" s="3">
         <v>17960100</v>
       </c>
-      <c r="AH76" s="3">
+      <c r="AI76" s="3">
         <v>18347500</v>
       </c>
-      <c r="AI76" s="3">
+      <c r="AJ76" s="3">
         <v>18412300</v>
       </c>
     </row>
-    <row r="77" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="77" spans="2:36" x14ac:dyDescent="0.2">
       <c r="C77" s="1" t="s">
         <v>69</v>
       </c>
@@ -7143,215 +7326,224 @@
       <c r="AI77" s="3">
         <v>0</v>
       </c>
+      <c r="AJ77" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="79" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="79" spans="2:36" x14ac:dyDescent="0.2">
       <c r="B79" s="1" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="80" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="80" spans="2:36" x14ac:dyDescent="0.2">
       <c r="C80" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D80" s="2">
+        <v>45565</v>
+      </c>
+      <c r="E80" s="2">
         <v>45473</v>
       </c>
-      <c r="E80" s="2">
+      <c r="F80" s="2">
         <v>45382</v>
       </c>
-      <c r="F80" s="2">
+      <c r="G80" s="2">
         <v>45291</v>
       </c>
-      <c r="G80" s="2">
+      <c r="H80" s="2">
         <v>45199</v>
       </c>
-      <c r="H80" s="2">
+      <c r="I80" s="2">
         <v>45107</v>
       </c>
-      <c r="I80" s="2">
+      <c r="J80" s="2">
         <v>45016</v>
       </c>
-      <c r="J80" s="2">
+      <c r="K80" s="2">
         <v>44926</v>
       </c>
-      <c r="K80" s="2">
+      <c r="L80" s="2">
         <v>44834</v>
       </c>
-      <c r="L80" s="2">
+      <c r="M80" s="2">
         <v>44742</v>
       </c>
-      <c r="M80" s="2">
+      <c r="N80" s="2">
         <v>44651</v>
       </c>
-      <c r="N80" s="2">
+      <c r="O80" s="2">
         <v>44561</v>
       </c>
-      <c r="O80" s="2">
+      <c r="P80" s="2">
         <v>44469</v>
       </c>
-      <c r="P80" s="2">
+      <c r="Q80" s="2">
         <v>44377</v>
       </c>
-      <c r="Q80" s="2">
+      <c r="R80" s="2">
         <v>44286</v>
       </c>
-      <c r="R80" s="2">
+      <c r="S80" s="2">
         <v>44196</v>
       </c>
-      <c r="S80" s="2">
+      <c r="T80" s="2">
         <v>44104</v>
       </c>
-      <c r="T80" s="2">
+      <c r="U80" s="2">
         <v>44012</v>
       </c>
-      <c r="U80" s="2">
+      <c r="V80" s="2">
         <v>43921</v>
       </c>
-      <c r="V80" s="2">
+      <c r="W80" s="2">
         <v>43830</v>
       </c>
-      <c r="W80" s="2">
+      <c r="X80" s="2">
         <v>43738</v>
       </c>
-      <c r="X80" s="2">
+      <c r="Y80" s="2">
         <v>43646</v>
       </c>
-      <c r="Y80" s="2">
+      <c r="Z80" s="2">
         <v>43555</v>
       </c>
-      <c r="Z80" s="2">
+      <c r="AA80" s="2">
         <v>43465</v>
       </c>
-      <c r="AA80" s="2">
+      <c r="AB80" s="2">
         <v>43373</v>
       </c>
-      <c r="AB80" s="2">
+      <c r="AC80" s="2">
         <v>43281</v>
       </c>
-      <c r="AC80" s="2">
+      <c r="AD80" s="2">
         <v>43190</v>
       </c>
-      <c r="AD80" s="2">
+      <c r="AE80" s="2">
         <v>43100</v>
       </c>
-      <c r="AE80" s="2">
+      <c r="AF80" s="2">
         <v>43008</v>
       </c>
-      <c r="AF80" s="2">
+      <c r="AG80" s="2">
         <v>42916</v>
       </c>
-      <c r="AG80" s="2">
+      <c r="AH80" s="2">
         <v>42825</v>
       </c>
-      <c r="AH80" s="2">
+      <c r="AI80" s="2">
         <v>42735</v>
       </c>
-      <c r="AI80" s="2">
+      <c r="AJ80" s="2">
         <v>42643</v>
       </c>
     </row>
-    <row r="81" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="81" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C81" s="1" t="s">
         <v>28</v>
       </c>
-      <c r="D81" s="3" t="s">
-        <v>5</v>
+      <c r="D81" s="3">
+        <v>688600</v>
       </c>
       <c r="E81" s="3">
-        <v>591600</v>
+        <v>676000</v>
       </c>
       <c r="F81" s="3">
-        <v>24600</v>
+        <v>613100</v>
       </c>
       <c r="G81" s="3">
-        <v>649900</v>
+        <v>52500</v>
       </c>
       <c r="H81" s="3">
-        <v>444300</v>
+        <v>668000</v>
       </c>
       <c r="I81" s="3">
-        <v>662500</v>
+        <v>474700</v>
       </c>
       <c r="J81" s="3">
+        <v>700700</v>
+      </c>
+      <c r="K81" s="3">
         <v>338800</v>
       </c>
-      <c r="K81" s="3">
+      <c r="L81" s="3">
         <v>640600</v>
       </c>
-      <c r="L81" s="3">
+      <c r="M81" s="3">
         <v>684400</v>
       </c>
-      <c r="M81" s="3">
+      <c r="N81" s="3">
         <v>631400</v>
       </c>
-      <c r="N81" s="3">
+      <c r="O81" s="3">
         <v>279500</v>
       </c>
-      <c r="O81" s="3">
+      <c r="P81" s="3">
         <v>570700</v>
       </c>
-      <c r="P81" s="3">
+      <c r="Q81" s="3">
         <v>552600</v>
       </c>
-      <c r="Q81" s="3">
+      <c r="R81" s="3">
         <v>482000</v>
       </c>
-      <c r="R81" s="3">
+      <c r="S81" s="3">
         <v>112600</v>
       </c>
-      <c r="S81" s="3">
+      <c r="T81" s="3">
         <v>358800</v>
       </c>
-      <c r="T81" s="3">
+      <c r="U81" s="3">
         <v>100500</v>
       </c>
-      <c r="U81" s="3">
+      <c r="V81" s="3">
         <v>412900</v>
       </c>
-      <c r="V81" s="3">
+      <c r="W81" s="3">
         <v>174900</v>
       </c>
-      <c r="W81" s="3">
+      <c r="X81" s="3">
         <v>410100</v>
       </c>
-      <c r="X81" s="3">
+      <c r="Y81" s="3">
         <v>537700</v>
       </c>
-      <c r="Y81" s="3">
+      <c r="Z81" s="3">
         <v>517500</v>
       </c>
-      <c r="Z81" s="3">
+      <c r="AA81" s="3">
         <v>76800</v>
       </c>
-      <c r="AA81" s="3">
+      <c r="AB81" s="3">
         <v>453900</v>
       </c>
-      <c r="AB81" s="3">
+      <c r="AC81" s="3">
         <v>569900</v>
       </c>
-      <c r="AC81" s="3">
+      <c r="AD81" s="3">
         <v>463600</v>
       </c>
-      <c r="AD81" s="3">
+      <c r="AE81" s="3">
         <v>84900</v>
       </c>
-      <c r="AE81" s="3">
+      <c r="AF81" s="3">
         <v>212100</v>
       </c>
-      <c r="AF81" s="3">
+      <c r="AG81" s="3">
         <v>369000</v>
       </c>
-      <c r="AG81" s="3">
+      <c r="AH81" s="3">
         <v>517600</v>
       </c>
-      <c r="AH81" s="3">
+      <c r="AI81" s="3">
         <v>88500</v>
       </c>
-      <c r="AI81" s="3">
+      <c r="AJ81" s="3">
         <v>275700</v>
       </c>
     </row>
-    <row r="82" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="82" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C82" s="1" t="s">
         <v>71</v>
       </c>
@@ -7387,109 +7579,113 @@
       <c r="AG82" s="3"/>
       <c r="AH82" s="3"/>
       <c r="AI82" s="3"/>
+      <c r="AJ82" s="3"/>
     </row>
-    <row r="83" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="83" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C83" s="1" t="s">
         <v>72</v>
       </c>
       <c r="D83" s="3">
-        <v>216100</v>
+        <v>150800</v>
       </c>
       <c r="E83" s="3">
-        <v>207000</v>
+        <v>153800</v>
       </c>
       <c r="F83" s="3">
-        <v>197900</v>
+        <v>154400</v>
       </c>
       <c r="G83" s="3">
-        <v>180200</v>
+        <v>162700</v>
       </c>
       <c r="H83" s="3">
-        <v>182300</v>
+        <v>133200</v>
       </c>
       <c r="I83" s="3">
+        <v>147300</v>
+      </c>
+      <c r="J83" s="3">
+        <v>148000</v>
+      </c>
+      <c r="K83" s="3">
+        <v>185200</v>
+      </c>
+      <c r="L83" s="3">
+        <v>169700</v>
+      </c>
+      <c r="M83" s="3">
+        <v>175600</v>
+      </c>
+      <c r="N83" s="3">
+        <v>168600</v>
+      </c>
+      <c r="O83" s="3">
+        <v>155900</v>
+      </c>
+      <c r="P83" s="3">
+        <v>149200</v>
+      </c>
+      <c r="Q83" s="3">
         <v>184500</v>
       </c>
-      <c r="J83" s="3">
-        <v>185200</v>
-      </c>
-      <c r="K83" s="3">
-        <v>169700</v>
-      </c>
-      <c r="L83" s="3">
-        <v>175600</v>
-      </c>
-      <c r="M83" s="3">
-        <v>168600</v>
-      </c>
-      <c r="N83" s="3">
-        <v>155900</v>
-      </c>
-      <c r="O83" s="3">
-        <v>149200</v>
-      </c>
-      <c r="P83" s="3">
-        <v>184500</v>
-      </c>
-      <c r="Q83" s="3">
+      <c r="R83" s="3">
         <v>102900</v>
       </c>
-      <c r="R83" s="3">
+      <c r="S83" s="3">
         <v>101300</v>
       </c>
-      <c r="S83" s="3">
+      <c r="T83" s="3">
         <v>101500</v>
       </c>
-      <c r="T83" s="3">
+      <c r="U83" s="3">
         <v>98700</v>
       </c>
-      <c r="U83" s="3">
+      <c r="V83" s="3">
         <v>112300</v>
       </c>
-      <c r="V83" s="3">
+      <c r="W83" s="3">
         <v>120400</v>
       </c>
-      <c r="W83" s="3">
+      <c r="X83" s="3">
         <v>116900</v>
       </c>
-      <c r="X83" s="3">
+      <c r="Y83" s="3">
         <v>108900</v>
       </c>
-      <c r="Y83" s="3">
+      <c r="Z83" s="3">
         <v>93600</v>
       </c>
-      <c r="Z83" s="3">
+      <c r="AA83" s="3">
         <v>61600</v>
       </c>
-      <c r="AA83" s="3">
+      <c r="AB83" s="3">
         <v>58600</v>
       </c>
-      <c r="AB83" s="3">
+      <c r="AC83" s="3">
         <v>56000</v>
       </c>
-      <c r="AC83" s="3">
+      <c r="AD83" s="3">
         <v>50600</v>
       </c>
-      <c r="AD83" s="3">
+      <c r="AE83" s="3">
         <v>49900</v>
       </c>
-      <c r="AE83" s="3">
+      <c r="AF83" s="3">
         <v>50800</v>
       </c>
-      <c r="AF83" s="3">
+      <c r="AG83" s="3">
         <v>51600</v>
       </c>
-      <c r="AG83" s="3">
+      <c r="AH83" s="3">
         <v>55200</v>
       </c>
-      <c r="AH83" s="3">
+      <c r="AI83" s="3">
         <v>54800</v>
       </c>
-      <c r="AI83" s="3">
+      <c r="AJ83" s="3">
         <v>53700</v>
       </c>
     </row>
-    <row r="84" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="84" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C84" s="1" t="s">
         <v>73</v>
       </c>
@@ -7589,8 +7785,11 @@
       <c r="AI84" s="3">
         <v>0</v>
       </c>
+      <c r="AJ84" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="85" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="85" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C85" s="1" t="s">
         <v>74</v>
       </c>
@@ -7690,8 +7889,11 @@
       <c r="AI85" s="3">
         <v>0</v>
       </c>
+      <c r="AJ85" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="86" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="86" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C86" s="1" t="s">
         <v>75</v>
       </c>
@@ -7791,8 +7993,11 @@
       <c r="AI86" s="3">
         <v>0</v>
       </c>
+      <c r="AJ86" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="87" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="87" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C87" s="1" t="s">
         <v>76</v>
       </c>
@@ -7892,8 +8097,11 @@
       <c r="AI87" s="3">
         <v>0</v>
       </c>
+      <c r="AJ87" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="88" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="88" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C88" s="1" t="s">
         <v>77</v>
       </c>
@@ -7993,109 +8201,115 @@
       <c r="AI88" s="3">
         <v>0</v>
       </c>
+      <c r="AJ88" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="89" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="89" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C89" s="1" t="s">
         <v>78</v>
       </c>
       <c r="D89" s="3">
-        <v>-3559500</v>
+        <v>-21513100</v>
       </c>
       <c r="E89" s="3">
-        <v>-165600</v>
+        <v>-5708900</v>
       </c>
       <c r="F89" s="3">
-        <v>4745600</v>
+        <v>3028800</v>
       </c>
       <c r="G89" s="3">
-        <v>4645200</v>
+        <v>-13351300</v>
       </c>
       <c r="H89" s="3">
-        <v>-5585700</v>
+        <v>3754000</v>
       </c>
       <c r="I89" s="3">
-        <v>-2588600</v>
+        <v>-11714900</v>
       </c>
       <c r="J89" s="3">
+        <v>10840700</v>
+      </c>
+      <c r="K89" s="3">
         <v>12011900</v>
       </c>
-      <c r="K89" s="3">
+      <c r="L89" s="3">
         <v>-3350300</v>
       </c>
-      <c r="L89" s="3">
+      <c r="M89" s="3">
         <v>-2130300</v>
       </c>
-      <c r="M89" s="3">
+      <c r="N89" s="3">
         <v>7700600</v>
       </c>
-      <c r="N89" s="3">
+      <c r="O89" s="3">
         <v>4027400</v>
       </c>
-      <c r="O89" s="3">
+      <c r="P89" s="3">
         <v>2586700</v>
       </c>
-      <c r="P89" s="3">
+      <c r="Q89" s="3">
         <v>-4607300</v>
       </c>
-      <c r="Q89" s="3">
+      <c r="R89" s="3">
         <v>831700</v>
       </c>
-      <c r="R89" s="3">
+      <c r="S89" s="3">
         <v>1545900</v>
       </c>
-      <c r="S89" s="3">
+      <c r="T89" s="3">
         <v>-766500</v>
       </c>
-      <c r="T89" s="3">
+      <c r="U89" s="3">
         <v>2718500</v>
       </c>
-      <c r="U89" s="3">
+      <c r="V89" s="3">
         <v>-824700</v>
       </c>
-      <c r="V89" s="3">
+      <c r="W89" s="3">
         <v>-153300</v>
       </c>
-      <c r="W89" s="3">
+      <c r="X89" s="3">
         <v>-428600</v>
       </c>
-      <c r="X89" s="3">
+      <c r="Y89" s="3">
         <v>3501700</v>
       </c>
-      <c r="Y89" s="3">
+      <c r="Z89" s="3">
         <v>-1296100</v>
       </c>
-      <c r="Z89" s="3">
+      <c r="AA89" s="3">
         <v>5231600</v>
       </c>
-      <c r="AA89" s="3">
+      <c r="AB89" s="3">
         <v>908000</v>
       </c>
-      <c r="AB89" s="3">
+      <c r="AC89" s="3">
         <v>643600</v>
       </c>
-      <c r="AC89" s="3">
+      <c r="AD89" s="3">
         <v>877700</v>
       </c>
-      <c r="AD89" s="3">
+      <c r="AE89" s="3">
         <v>-506300</v>
       </c>
-      <c r="AE89" s="3">
+      <c r="AF89" s="3">
         <v>-2456000</v>
       </c>
-      <c r="AF89" s="3">
+      <c r="AG89" s="3">
         <v>-340700</v>
       </c>
-      <c r="AG89" s="3">
+      <c r="AH89" s="3">
         <v>1561500</v>
       </c>
-      <c r="AH89" s="3">
+      <c r="AI89" s="3">
         <v>108800</v>
       </c>
-      <c r="AI89" s="3">
+      <c r="AJ89" s="3">
         <v>3807600</v>
       </c>
     </row>
-    <row r="90" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="90" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C90" s="1" t="s">
         <v>79</v>
       </c>
@@ -8131,109 +8345,113 @@
       <c r="AG90" s="3"/>
       <c r="AH90" s="3"/>
       <c r="AI90" s="3"/>
+      <c r="AJ90" s="3"/>
     </row>
-    <row r="91" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="91" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C91" s="1" t="s">
         <v>80</v>
       </c>
       <c r="D91" s="3">
-        <v>-121377000</v>
+        <v>-62500</v>
       </c>
       <c r="E91" s="3">
-        <v>-77550000</v>
+        <v>-40100</v>
       </c>
       <c r="F91" s="3">
-        <v>-161762000</v>
+        <v>-27400</v>
       </c>
       <c r="G91" s="3">
-        <v>-68486000</v>
+        <v>-61300</v>
       </c>
       <c r="H91" s="3">
-        <v>-103704000</v>
+        <v>-23300</v>
       </c>
       <c r="I91" s="3">
-        <v>-59247000</v>
+        <v>-23900</v>
       </c>
       <c r="J91" s="3">
+        <v>-17100</v>
+      </c>
+      <c r="K91" s="3">
         <v>-113722000</v>
       </c>
-      <c r="K91" s="3">
+      <c r="L91" s="3">
         <v>-77226000</v>
       </c>
-      <c r="L91" s="3">
+      <c r="M91" s="3">
         <v>-104059000</v>
       </c>
-      <c r="M91" s="3">
+      <c r="N91" s="3">
         <v>-52618000</v>
       </c>
-      <c r="N91" s="3">
+      <c r="O91" s="3">
         <v>-74615000</v>
       </c>
-      <c r="O91" s="3">
+      <c r="P91" s="3">
         <v>-81614000</v>
       </c>
-      <c r="P91" s="3">
+      <c r="Q91" s="3">
         <v>-15900</v>
       </c>
-      <c r="Q91" s="3">
+      <c r="R91" s="3">
         <v>-14300</v>
       </c>
-      <c r="R91" s="3">
+      <c r="S91" s="3">
         <v>-43600</v>
       </c>
-      <c r="S91" s="3">
+      <c r="T91" s="3">
         <v>-25600</v>
       </c>
-      <c r="T91" s="3">
+      <c r="U91" s="3">
         <v>-24800</v>
       </c>
-      <c r="U91" s="3">
+      <c r="V91" s="3">
         <v>-20300</v>
       </c>
-      <c r="V91" s="3">
+      <c r="W91" s="3">
         <v>-190900</v>
       </c>
-      <c r="W91" s="3">
+      <c r="X91" s="3">
         <v>-91000</v>
       </c>
-      <c r="X91" s="3">
+      <c r="Y91" s="3">
         <v>-55400</v>
       </c>
-      <c r="Y91" s="3">
+      <c r="Z91" s="3">
         <v>-31700</v>
       </c>
-      <c r="Z91" s="3">
+      <c r="AA91" s="3">
         <v>-43000</v>
       </c>
-      <c r="AA91" s="3">
+      <c r="AB91" s="3">
         <v>-20100</v>
       </c>
-      <c r="AB91" s="3">
+      <c r="AC91" s="3">
         <v>-18000</v>
       </c>
-      <c r="AC91" s="3">
+      <c r="AD91" s="3">
         <v>-17800</v>
       </c>
-      <c r="AD91" s="3">
+      <c r="AE91" s="3">
         <v>-25100</v>
       </c>
-      <c r="AE91" s="3">
+      <c r="AF91" s="3">
         <v>-57300</v>
       </c>
-      <c r="AF91" s="3">
+      <c r="AG91" s="3">
         <v>-37900</v>
       </c>
-      <c r="AG91" s="3">
+      <c r="AH91" s="3">
         <v>-22400</v>
       </c>
-      <c r="AH91" s="3">
+      <c r="AI91" s="3">
         <v>-111600</v>
       </c>
-      <c r="AI91" s="3">
+      <c r="AJ91" s="3">
         <v>-90400</v>
       </c>
     </row>
-    <row r="92" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="92" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C92" s="1" t="s">
         <v>81</v>
       </c>
@@ -8333,8 +8551,11 @@
       <c r="AI92" s="3">
         <v>0</v>
       </c>
+      <c r="AJ92" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="93" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="93" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C93" s="1" t="s">
         <v>82</v>
       </c>
@@ -8434,109 +8655,115 @@
       <c r="AI93" s="3">
         <v>0</v>
       </c>
+      <c r="AJ93" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="94" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="94" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C94" s="1" t="s">
         <v>83</v>
       </c>
       <c r="D94" s="3">
-        <v>-1129000</v>
+        <v>3642700</v>
       </c>
       <c r="E94" s="3">
-        <v>1855700</v>
+        <v>-1092400</v>
       </c>
       <c r="F94" s="3">
-        <v>-608200</v>
+        <v>1841100</v>
       </c>
       <c r="G94" s="3">
-        <v>-1118200</v>
+        <v>-625400</v>
       </c>
       <c r="H94" s="3">
-        <v>-258400</v>
+        <v>-1107500</v>
       </c>
       <c r="I94" s="3">
-        <v>294200</v>
+        <v>-261600</v>
       </c>
       <c r="J94" s="3">
+        <v>300800</v>
+      </c>
+      <c r="K94" s="3">
         <v>-2910400</v>
       </c>
-      <c r="K94" s="3">
+      <c r="L94" s="3">
         <v>-2354900</v>
       </c>
-      <c r="L94" s="3">
+      <c r="M94" s="3">
         <v>2353800</v>
       </c>
-      <c r="M94" s="3">
+      <c r="N94" s="3">
         <v>-2278800</v>
       </c>
-      <c r="N94" s="3">
+      <c r="O94" s="3">
         <v>-4489600</v>
       </c>
-      <c r="O94" s="3">
+      <c r="P94" s="3">
         <v>-3902300</v>
       </c>
-      <c r="P94" s="3">
+      <c r="Q94" s="3">
         <v>1124900</v>
       </c>
-      <c r="Q94" s="3">
+      <c r="R94" s="3">
         <v>-723400</v>
       </c>
-      <c r="R94" s="3">
+      <c r="S94" s="3">
         <v>-365200</v>
       </c>
-      <c r="S94" s="3">
+      <c r="T94" s="3">
         <v>-124500</v>
       </c>
-      <c r="T94" s="3">
+      <c r="U94" s="3">
         <v>-446100</v>
       </c>
-      <c r="U94" s="3">
+      <c r="V94" s="3">
         <v>-179800</v>
       </c>
-      <c r="V94" s="3">
+      <c r="W94" s="3">
         <v>-962200</v>
       </c>
-      <c r="W94" s="3">
+      <c r="X94" s="3">
         <v>-913600</v>
       </c>
-      <c r="X94" s="3">
+      <c r="Y94" s="3">
         <v>-5520900</v>
       </c>
-      <c r="Y94" s="3">
+      <c r="Z94" s="3">
         <v>-97900</v>
       </c>
-      <c r="Z94" s="3">
+      <c r="AA94" s="3">
         <v>-5105000</v>
       </c>
-      <c r="AA94" s="3">
+      <c r="AB94" s="3">
         <v>-2452600</v>
       </c>
-      <c r="AB94" s="3">
+      <c r="AC94" s="3">
         <v>-1063800</v>
       </c>
-      <c r="AC94" s="3">
+      <c r="AD94" s="3">
         <v>-587600</v>
       </c>
-      <c r="AD94" s="3">
+      <c r="AE94" s="3">
         <v>1277600</v>
       </c>
-      <c r="AE94" s="3">
+      <c r="AF94" s="3">
         <v>-195600</v>
       </c>
-      <c r="AF94" s="3">
+      <c r="AG94" s="3">
         <v>183200</v>
       </c>
-      <c r="AG94" s="3">
+      <c r="AH94" s="3">
         <v>392500</v>
       </c>
-      <c r="AH94" s="3">
+      <c r="AI94" s="3">
         <v>-2371700</v>
       </c>
-      <c r="AI94" s="3">
+      <c r="AJ94" s="3">
         <v>694800</v>
       </c>
     </row>
-    <row r="95" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="95" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C95" s="1" t="s">
         <v>84</v>
       </c>
@@ -8572,38 +8799,39 @@
       <c r="AG95" s="3"/>
       <c r="AH95" s="3"/>
       <c r="AI95" s="3"/>
+      <c r="AJ95" s="3"/>
     </row>
-    <row r="96" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="96" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C96" s="1" t="s">
         <v>85</v>
       </c>
       <c r="D96" s="3">
-        <v>0</v>
+        <v>134900</v>
       </c>
       <c r="E96" s="3">
-        <v>0</v>
+        <v>473000</v>
       </c>
       <c r="F96" s="3">
-        <v>-100900</v>
+        <v>26200</v>
       </c>
       <c r="G96" s="3">
-        <v>-98000</v>
+        <v>151100</v>
       </c>
       <c r="H96" s="3">
-        <v>0</v>
+        <v>102000</v>
       </c>
       <c r="I96" s="3">
-        <v>0</v>
+        <v>566300</v>
       </c>
       <c r="J96" s="3">
-        <v>0</v>
+        <v>23300</v>
       </c>
       <c r="K96" s="3">
+        <v>0</v>
+      </c>
+      <c r="L96" s="3">
         <v>-79700</v>
       </c>
-      <c r="L96" s="3">
-        <v>0</v>
-      </c>
       <c r="M96" s="3">
         <v>0</v>
       </c>
@@ -8611,11 +8839,11 @@
         <v>0</v>
       </c>
       <c r="O96" s="3">
+        <v>0</v>
+      </c>
+      <c r="P96" s="3">
         <v>-81300</v>
       </c>
-      <c r="P96" s="3">
-        <v>0</v>
-      </c>
       <c r="Q96" s="3">
         <v>0</v>
       </c>
@@ -8659,22 +8887,25 @@
         <v>0</v>
       </c>
       <c r="AE96" s="3">
+        <v>0</v>
+      </c>
+      <c r="AF96" s="3">
         <v>-59200</v>
       </c>
-      <c r="AF96" s="3">
+      <c r="AG96" s="3">
         <v>-237000</v>
       </c>
-      <c r="AG96" s="3">
-        <v>0</v>
-      </c>
       <c r="AH96" s="3">
+        <v>0</v>
+      </c>
+      <c r="AI96" s="3">
         <v>-38100</v>
       </c>
-      <c r="AI96" s="3">
+      <c r="AJ96" s="3">
         <v>-22800</v>
       </c>
     </row>
-    <row r="97" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="97" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C97" s="1" t="s">
         <v>86</v>
       </c>
@@ -8774,8 +9005,11 @@
       <c r="AI97" s="3">
         <v>0</v>
       </c>
+      <c r="AJ97" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="98" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="98" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C98" s="1" t="s">
         <v>87</v>
       </c>
@@ -8875,8 +9109,11 @@
       <c r="AI98" s="3">
         <v>0</v>
       </c>
+      <c r="AJ98" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="99" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="99" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C99" s="1" t="s">
         <v>88</v>
       </c>
@@ -8976,307 +9213,319 @@
       <c r="AI99" s="3">
         <v>0</v>
       </c>
+      <c r="AJ99" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="100" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="100" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C100" s="1" t="s">
         <v>89</v>
       </c>
       <c r="D100" s="3">
-        <v>-397200</v>
+        <v>24357600</v>
       </c>
       <c r="E100" s="3">
-        <v>-921800</v>
+        <v>1880400</v>
       </c>
       <c r="F100" s="3">
-        <v>-464400</v>
+        <v>-4107500</v>
       </c>
       <c r="G100" s="3">
-        <v>-403400</v>
+        <v>17753300</v>
       </c>
       <c r="H100" s="3">
-        <v>-1024600</v>
+        <v>447300</v>
       </c>
       <c r="I100" s="3">
-        <v>-252600</v>
+        <v>5022900</v>
       </c>
       <c r="J100" s="3">
+        <v>-13746200</v>
+      </c>
+      <c r="K100" s="3">
         <v>-5147300</v>
       </c>
-      <c r="K100" s="3">
+      <c r="L100" s="3">
         <v>1697300</v>
       </c>
-      <c r="L100" s="3">
+      <c r="M100" s="3">
         <v>3000400</v>
       </c>
-      <c r="M100" s="3">
+      <c r="N100" s="3">
         <v>1932700</v>
       </c>
-      <c r="N100" s="3">
+      <c r="O100" s="3">
         <v>2031800</v>
       </c>
-      <c r="O100" s="3">
+      <c r="P100" s="3">
         <v>1404600</v>
       </c>
-      <c r="P100" s="3">
+      <c r="Q100" s="3">
         <v>2911000</v>
       </c>
-      <c r="Q100" s="3">
+      <c r="R100" s="3">
         <v>453200</v>
       </c>
-      <c r="R100" s="3">
+      <c r="S100" s="3">
         <v>261800</v>
       </c>
-      <c r="S100" s="3">
+      <c r="T100" s="3">
         <v>553800</v>
       </c>
-      <c r="T100" s="3">
+      <c r="U100" s="3">
         <v>-2356000</v>
       </c>
-      <c r="U100" s="3">
+      <c r="V100" s="3">
         <v>3526800</v>
       </c>
-      <c r="V100" s="3">
+      <c r="W100" s="3">
         <v>-950700</v>
       </c>
-      <c r="W100" s="3">
+      <c r="X100" s="3">
         <v>3000500</v>
       </c>
-      <c r="X100" s="3">
+      <c r="Y100" s="3">
         <v>3588600</v>
       </c>
-      <c r="Y100" s="3">
+      <c r="Z100" s="3">
         <v>-289800</v>
       </c>
-      <c r="Z100" s="3">
+      <c r="AA100" s="3">
         <v>491400</v>
       </c>
-      <c r="AA100" s="3">
+      <c r="AB100" s="3">
         <v>1689200</v>
       </c>
-      <c r="AB100" s="3">
+      <c r="AC100" s="3">
         <v>354700</v>
       </c>
-      <c r="AC100" s="3">
+      <c r="AD100" s="3">
         <v>-1323700</v>
       </c>
-      <c r="AD100" s="3">
+      <c r="AE100" s="3">
         <v>-309500</v>
       </c>
-      <c r="AE100" s="3">
+      <c r="AF100" s="3">
         <v>2140800</v>
       </c>
-      <c r="AF100" s="3">
+      <c r="AG100" s="3">
         <v>-384900</v>
       </c>
-      <c r="AG100" s="3">
+      <c r="AH100" s="3">
         <v>-1500100</v>
       </c>
-      <c r="AH100" s="3">
+      <c r="AI100" s="3">
         <v>1503800</v>
       </c>
-      <c r="AI100" s="3">
+      <c r="AJ100" s="3">
         <v>-1778900</v>
       </c>
     </row>
-    <row r="101" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="101" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C101" s="1" t="s">
         <v>90</v>
       </c>
       <c r="D101" s="3">
-        <v>238700</v>
+        <v>27300</v>
       </c>
       <c r="E101" s="3">
-        <v>264800</v>
+        <v>-105100</v>
       </c>
       <c r="F101" s="3">
-        <v>-174400</v>
+        <v>125800</v>
       </c>
       <c r="G101" s="3">
-        <v>27500</v>
+        <v>-1568200</v>
       </c>
       <c r="H101" s="3">
-        <v>-103800</v>
+        <v>609200</v>
       </c>
       <c r="I101" s="3">
-        <v>123000</v>
+        <v>667200</v>
       </c>
       <c r="J101" s="3">
+        <v>217100</v>
+      </c>
+      <c r="K101" s="3">
         <v>-1479100</v>
       </c>
-      <c r="K101" s="3">
+      <c r="L101" s="3">
         <v>638600</v>
       </c>
-      <c r="L101" s="3">
+      <c r="M101" s="3">
         <v>657000</v>
       </c>
-      <c r="M101" s="3">
+      <c r="N101" s="3">
         <v>203100</v>
       </c>
-      <c r="N101" s="3">
+      <c r="O101" s="3">
         <v>68900</v>
       </c>
-      <c r="O101" s="3">
+      <c r="P101" s="3">
         <v>409500</v>
       </c>
-      <c r="P101" s="3">
+      <c r="Q101" s="3">
         <v>18100</v>
       </c>
-      <c r="Q101" s="3">
+      <c r="R101" s="3">
         <v>295500</v>
       </c>
-      <c r="R101" s="3">
+      <c r="S101" s="3">
         <v>-571700</v>
       </c>
-      <c r="S101" s="3">
+      <c r="T101" s="3">
         <v>-142900</v>
       </c>
-      <c r="T101" s="3">
+      <c r="U101" s="3">
         <v>-159900</v>
       </c>
-      <c r="U101" s="3">
+      <c r="V101" s="3">
         <v>200400</v>
       </c>
-      <c r="V101" s="3">
+      <c r="W101" s="3">
         <v>369400</v>
       </c>
-      <c r="W101" s="3">
+      <c r="X101" s="3">
         <v>-340600</v>
       </c>
-      <c r="X101" s="3">
+      <c r="Y101" s="3">
         <v>51200</v>
       </c>
-      <c r="Y101" s="3">
+      <c r="Z101" s="3">
         <v>90500</v>
       </c>
-      <c r="Z101" s="3">
+      <c r="AA101" s="3">
         <v>6400</v>
       </c>
-      <c r="AA101" s="3">
+      <c r="AB101" s="3">
         <v>-76600</v>
       </c>
-      <c r="AB101" s="3">
+      <c r="AC101" s="3">
         <v>218900</v>
       </c>
-      <c r="AC101" s="3">
+      <c r="AD101" s="3">
         <v>50500</v>
       </c>
-      <c r="AD101" s="3">
+      <c r="AE101" s="3">
         <v>-377500</v>
       </c>
-      <c r="AE101" s="3">
+      <c r="AF101" s="3">
         <v>14000</v>
       </c>
-      <c r="AF101" s="3">
+      <c r="AG101" s="3">
         <v>8400</v>
       </c>
-      <c r="AG101" s="3">
+      <c r="AH101" s="3">
         <v>-108300</v>
       </c>
-      <c r="AH101" s="3">
+      <c r="AI101" s="3">
         <v>138000</v>
       </c>
-      <c r="AI101" s="3">
+      <c r="AJ101" s="3">
         <v>-105900</v>
       </c>
     </row>
-    <row r="102" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="102" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C102" s="1" t="s">
         <v>91</v>
       </c>
       <c r="D102" s="3">
-        <v>-4847000</v>
+        <v>6101900</v>
       </c>
       <c r="E102" s="3">
-        <v>1033200</v>
+        <v>-4689900</v>
       </c>
       <c r="F102" s="3">
-        <v>3498600</v>
+        <v>1025100</v>
       </c>
       <c r="G102" s="3">
-        <v>3151100</v>
+        <v>3597300</v>
       </c>
       <c r="H102" s="3">
-        <v>-6972500</v>
+        <v>3121100</v>
       </c>
       <c r="I102" s="3">
-        <v>-2424100</v>
+        <v>-7058600</v>
       </c>
       <c r="J102" s="3">
+        <v>-2478800</v>
+      </c>
+      <c r="K102" s="3">
         <v>2475100</v>
       </c>
-      <c r="K102" s="3">
+      <c r="L102" s="3">
         <v>-3369400</v>
       </c>
-      <c r="L102" s="3">
+      <c r="M102" s="3">
         <v>3880900</v>
       </c>
-      <c r="M102" s="3">
+      <c r="N102" s="3">
         <v>7557600</v>
       </c>
-      <c r="N102" s="3">
+      <c r="O102" s="3">
         <v>1638600</v>
       </c>
-      <c r="O102" s="3">
+      <c r="P102" s="3">
         <v>498500</v>
       </c>
-      <c r="P102" s="3">
+      <c r="Q102" s="3">
         <v>-553300</v>
       </c>
-      <c r="Q102" s="3">
+      <c r="R102" s="3">
         <v>857000</v>
       </c>
-      <c r="R102" s="3">
+      <c r="S102" s="3">
         <v>870800</v>
       </c>
-      <c r="S102" s="3">
+      <c r="T102" s="3">
         <v>-480000</v>
       </c>
-      <c r="T102" s="3">
+      <c r="U102" s="3">
         <v>-243500</v>
       </c>
-      <c r="U102" s="3">
+      <c r="V102" s="3">
         <v>2722600</v>
       </c>
-      <c r="V102" s="3">
+      <c r="W102" s="3">
         <v>-1696800</v>
       </c>
-      <c r="W102" s="3">
+      <c r="X102" s="3">
         <v>1317700</v>
       </c>
-      <c r="X102" s="3">
+      <c r="Y102" s="3">
         <v>1620600</v>
       </c>
-      <c r="Y102" s="3">
+      <c r="Z102" s="3">
         <v>-1593300</v>
       </c>
-      <c r="Z102" s="3">
+      <c r="AA102" s="3">
         <v>624400</v>
       </c>
-      <c r="AA102" s="3">
+      <c r="AB102" s="3">
         <v>68000</v>
       </c>
-      <c r="AB102" s="3">
+      <c r="AC102" s="3">
         <v>153400</v>
       </c>
-      <c r="AC102" s="3">
+      <c r="AD102" s="3">
         <v>-983000</v>
       </c>
-      <c r="AD102" s="3">
+      <c r="AE102" s="3">
         <v>84300</v>
       </c>
-      <c r="AE102" s="3">
+      <c r="AF102" s="3">
         <v>-496900</v>
       </c>
-      <c r="AF102" s="3">
+      <c r="AG102" s="3">
         <v>-534100</v>
       </c>
-      <c r="AG102" s="3">
+      <c r="AH102" s="3">
         <v>345600</v>
       </c>
-      <c r="AH102" s="3">
+      <c r="AI102" s="3">
         <v>-621200</v>
       </c>
-      <c r="AI102" s="3">
+      <c r="AJ102" s="3">
         <v>2617600</v>
       </c>
     </row>

--- a/AAII_Financials/Quarterly/WF_QTR_FIN.xlsx
+++ b/AAII_Financials/Quarterly/WF_QTR_FIN.xlsx
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="194" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="197" uniqueCount="92">
   <si>
     <t>WF</t>
   </si>
@@ -656,266 +656,272 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet2"/>
-  <dimension ref="A5:AJ102"/>
+  <dimension ref="A5:AK102"/>
   <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="5" style="1" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="26.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="69.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="10" width="16" style="1" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="17" style="1" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="16" style="1" bestFit="1" customWidth="1"/>
-    <col min="13" max="13" width="17" style="1" bestFit="1" customWidth="1"/>
-    <col min="14" max="36" width="16" style="1" bestFit="1" customWidth="1"/>
-    <col min="37" max="16384" width="9.140625" style="1"/>
+    <col min="4" max="11" width="16" style="1" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="17" style="1" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="16" style="1" bestFit="1" customWidth="1"/>
+    <col min="14" max="14" width="17" style="1" bestFit="1" customWidth="1"/>
+    <col min="15" max="37" width="16" style="1" bestFit="1" customWidth="1"/>
+    <col min="38" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
-    <row r="5" spans="1:36" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:37" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:36" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:37" x14ac:dyDescent="0.2">
       <c r="B6" s="1" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:36" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:37" x14ac:dyDescent="0.2">
       <c r="C7" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D7" s="2">
+        <v>45657</v>
+      </c>
+      <c r="E7" s="2">
         <v>45565</v>
       </c>
-      <c r="E7" s="2">
+      <c r="F7" s="2">
         <v>45473</v>
       </c>
-      <c r="F7" s="2">
+      <c r="G7" s="2">
         <v>45382</v>
       </c>
-      <c r="G7" s="2">
+      <c r="H7" s="2">
         <v>45291</v>
       </c>
-      <c r="H7" s="2">
+      <c r="I7" s="2">
         <v>45199</v>
       </c>
-      <c r="I7" s="2">
+      <c r="J7" s="2">
         <v>45107</v>
       </c>
-      <c r="J7" s="2">
+      <c r="K7" s="2">
         <v>45016</v>
       </c>
-      <c r="K7" s="2">
+      <c r="L7" s="2">
         <v>44926</v>
       </c>
-      <c r="L7" s="2">
+      <c r="M7" s="2">
         <v>44834</v>
       </c>
-      <c r="M7" s="2">
+      <c r="N7" s="2">
         <v>44742</v>
       </c>
-      <c r="N7" s="2">
+      <c r="O7" s="2">
         <v>44651</v>
       </c>
-      <c r="O7" s="2">
+      <c r="P7" s="2">
         <v>44561</v>
       </c>
-      <c r="P7" s="2">
+      <c r="Q7" s="2">
         <v>44469</v>
       </c>
-      <c r="Q7" s="2">
+      <c r="R7" s="2">
         <v>44377</v>
       </c>
-      <c r="R7" s="2">
+      <c r="S7" s="2">
         <v>44286</v>
       </c>
-      <c r="S7" s="2">
+      <c r="T7" s="2">
         <v>44196</v>
       </c>
-      <c r="T7" s="2">
+      <c r="U7" s="2">
         <v>44104</v>
       </c>
-      <c r="U7" s="2">
+      <c r="V7" s="2">
         <v>44012</v>
       </c>
-      <c r="V7" s="2">
+      <c r="W7" s="2">
         <v>43921</v>
       </c>
-      <c r="W7" s="2">
+      <c r="X7" s="2">
         <v>43830</v>
       </c>
-      <c r="X7" s="2">
+      <c r="Y7" s="2">
         <v>43738</v>
       </c>
-      <c r="Y7" s="2">
+      <c r="Z7" s="2">
         <v>43646</v>
       </c>
-      <c r="Z7" s="2">
+      <c r="AA7" s="2">
         <v>43555</v>
       </c>
-      <c r="AA7" s="2">
+      <c r="AB7" s="2">
         <v>43465</v>
       </c>
-      <c r="AB7" s="2">
+      <c r="AC7" s="2">
         <v>43373</v>
       </c>
-      <c r="AC7" s="2">
+      <c r="AD7" s="2">
         <v>43281</v>
       </c>
-      <c r="AD7" s="2">
+      <c r="AE7" s="2">
         <v>43190</v>
       </c>
-      <c r="AE7" s="2">
+      <c r="AF7" s="2">
         <v>43100</v>
       </c>
-      <c r="AF7" s="2">
+      <c r="AG7" s="2">
         <v>43008</v>
       </c>
-      <c r="AG7" s="2">
+      <c r="AH7" s="2">
         <v>42916</v>
       </c>
-      <c r="AH7" s="2">
+      <c r="AI7" s="2">
         <v>42825</v>
       </c>
-      <c r="AI7" s="2">
+      <c r="AJ7" s="2">
         <v>42735</v>
       </c>
-      <c r="AJ7" s="2">
+      <c r="AK7" s="2">
         <v>42643</v>
       </c>
     </row>
-    <row r="8" spans="1:36" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:37" x14ac:dyDescent="0.2">
       <c r="C8" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D8" s="3">
+        <v>2144100</v>
+      </c>
+      <c r="E8" s="3">
         <v>1797600</v>
       </c>
-      <c r="E8" s="3">
+      <c r="F8" s="3">
         <v>2144400</v>
       </c>
-      <c r="F8" s="3">
+      <c r="G8" s="3">
         <v>2219900</v>
       </c>
-      <c r="G8" s="3">
-        <v>1187700</v>
-      </c>
       <c r="H8" s="3">
+        <v>1264600</v>
+      </c>
+      <c r="I8" s="3">
         <v>2101400</v>
       </c>
-      <c r="I8" s="3">
+      <c r="J8" s="3">
         <v>1748600</v>
       </c>
-      <c r="J8" s="3">
+      <c r="K8" s="3">
         <v>2091700</v>
       </c>
-      <c r="K8" s="3">
+      <c r="L8" s="3">
         <v>3462200</v>
       </c>
-      <c r="L8" s="3">
+      <c r="M8" s="3">
         <v>2792200</v>
       </c>
-      <c r="M8" s="3">
+      <c r="N8" s="3">
         <v>2487200</v>
       </c>
-      <c r="N8" s="3">
+      <c r="O8" s="3">
         <v>2264400</v>
       </c>
-      <c r="O8" s="3">
+      <c r="P8" s="3">
         <v>2026000</v>
       </c>
-      <c r="P8" s="3">
+      <c r="Q8" s="3">
         <v>1862200</v>
       </c>
-      <c r="Q8" s="3">
+      <c r="R8" s="3">
         <v>1787500</v>
       </c>
-      <c r="R8" s="3">
+      <c r="S8" s="3">
         <v>1722100</v>
       </c>
-      <c r="S8" s="3">
+      <c r="T8" s="3">
         <v>1728200</v>
       </c>
-      <c r="T8" s="3">
+      <c r="U8" s="3">
         <v>1749800</v>
       </c>
-      <c r="U8" s="3">
+      <c r="V8" s="3">
         <v>1857400</v>
       </c>
-      <c r="V8" s="3">
+      <c r="W8" s="3">
         <v>2028100</v>
       </c>
-      <c r="W8" s="3">
+      <c r="X8" s="3">
         <v>2216400</v>
       </c>
-      <c r="X8" s="3">
+      <c r="Y8" s="3">
         <v>2287800</v>
       </c>
-      <c r="Y8" s="3">
+      <c r="Z8" s="3">
         <v>2353100</v>
       </c>
-      <c r="Z8" s="3">
+      <c r="AA8" s="3">
         <v>2369400</v>
       </c>
-      <c r="AA8" s="3">
+      <c r="AB8" s="3">
         <v>2154000</v>
       </c>
-      <c r="AB8" s="3">
+      <c r="AC8" s="3">
         <v>2006200</v>
       </c>
-      <c r="AC8" s="3">
+      <c r="AD8" s="3">
         <v>1989700</v>
       </c>
-      <c r="AD8" s="3">
+      <c r="AE8" s="3">
         <v>1910800</v>
       </c>
-      <c r="AE8" s="3">
+      <c r="AF8" s="3">
         <v>1912500</v>
       </c>
-      <c r="AF8" s="3">
+      <c r="AG8" s="3">
         <v>1925300</v>
       </c>
-      <c r="AG8" s="3">
+      <c r="AH8" s="3">
         <v>1853100</v>
       </c>
-      <c r="AH8" s="3">
+      <c r="AI8" s="3">
         <v>1833700</v>
       </c>
-      <c r="AI8" s="3">
+      <c r="AJ8" s="3">
         <v>1898800</v>
       </c>
-      <c r="AJ8" s="3">
+      <c r="AK8" s="3">
         <v>1898000</v>
       </c>
     </row>
-    <row r="9" spans="1:36" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:37" x14ac:dyDescent="0.2">
       <c r="C9" s="1" t="s">
         <v>4</v>
       </c>
       <c r="D9" s="3">
+        <v>7000</v>
+      </c>
+      <c r="E9" s="3">
         <v>7600</v>
       </c>
-      <c r="E9" s="3">
+      <c r="F9" s="3">
         <v>7000</v>
       </c>
-      <c r="F9" s="3">
+      <c r="G9" s="3">
         <v>7100</v>
       </c>
-      <c r="G9" s="3">
+      <c r="H9" s="3">
         <v>9400</v>
-      </c>
-      <c r="H9" s="3">
-        <v>6800</v>
       </c>
       <c r="I9" s="3">
         <v>6800</v>
       </c>
       <c r="J9" s="3">
+        <v>6800</v>
+      </c>
+      <c r="K9" s="3">
         <v>7100</v>
       </c>
-      <c r="K9" s="3" t="s">
-        <v>5</v>
-      </c>
       <c r="L9" s="3" t="s">
         <v>5</v>
       </c>
@@ -991,35 +997,38 @@
       <c r="AJ9" s="3" t="s">
         <v>5</v>
       </c>
+      <c r="AK9" s="3" t="s">
+        <v>5</v>
+      </c>
     </row>
-    <row r="10" spans="1:36" x14ac:dyDescent="0.2">
+    <row r="10" spans="1:37" x14ac:dyDescent="0.2">
       <c r="C10" s="1" t="s">
         <v>6</v>
       </c>
       <c r="D10" s="3">
+        <v>2137100</v>
+      </c>
+      <c r="E10" s="3">
         <v>1790000</v>
       </c>
-      <c r="E10" s="3">
+      <c r="F10" s="3">
         <v>2137400</v>
       </c>
-      <c r="F10" s="3">
+      <c r="G10" s="3">
         <v>2212800</v>
       </c>
-      <c r="G10" s="3">
-        <v>1178300</v>
-      </c>
       <c r="H10" s="3">
+        <v>1255200</v>
+      </c>
+      <c r="I10" s="3">
         <v>2094600</v>
       </c>
-      <c r="I10" s="3">
+      <c r="J10" s="3">
         <v>1741800</v>
       </c>
-      <c r="J10" s="3">
+      <c r="K10" s="3">
         <v>2084600</v>
       </c>
-      <c r="K10" s="3" t="s">
-        <v>5</v>
-      </c>
       <c r="L10" s="3" t="s">
         <v>5</v>
       </c>
@@ -1095,8 +1104,11 @@
       <c r="AJ10" s="3" t="s">
         <v>5</v>
       </c>
+      <c r="AK10" s="3" t="s">
+        <v>5</v>
+      </c>
     </row>
-    <row r="11" spans="1:36" x14ac:dyDescent="0.2">
+    <row r="11" spans="1:37" x14ac:dyDescent="0.2">
       <c r="C11" s="1" t="s">
         <v>7</v>
       </c>
@@ -1133,8 +1145,9 @@
       <c r="AH11" s="3"/>
       <c r="AI11" s="3"/>
       <c r="AJ11" s="3"/>
+      <c r="AK11" s="3"/>
     </row>
-    <row r="12" spans="1:36" x14ac:dyDescent="0.2">
+    <row r="12" spans="1:37" x14ac:dyDescent="0.2">
       <c r="C12" s="1" t="s">
         <v>8</v>
       </c>
@@ -1237,8 +1250,11 @@
       <c r="AJ12" s="3" t="s">
         <v>5</v>
       </c>
+      <c r="AK12" s="3" t="s">
+        <v>5</v>
+      </c>
     </row>
-    <row r="13" spans="1:36" x14ac:dyDescent="0.2">
+    <row r="13" spans="1:37" x14ac:dyDescent="0.2">
       <c r="C13" s="1" t="s">
         <v>9</v>
       </c>
@@ -1341,35 +1357,38 @@
       <c r="AJ13" s="3">
         <v>0</v>
       </c>
+      <c r="AK13" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="14" spans="1:36" x14ac:dyDescent="0.2">
+    <row r="14" spans="1:37" x14ac:dyDescent="0.2">
       <c r="C14" s="1" t="s">
         <v>10</v>
       </c>
       <c r="D14" s="3">
-        <v>0</v>
+        <v>6200</v>
       </c>
       <c r="E14" s="3">
+        <v>0</v>
+      </c>
+      <c r="F14" s="3">
         <v>4600</v>
       </c>
-      <c r="F14" s="3">
+      <c r="G14" s="3">
         <v>12300</v>
       </c>
-      <c r="G14" s="3">
+      <c r="H14" s="3">
         <v>-1700</v>
       </c>
-      <c r="H14" s="3">
-        <v>0</v>
-      </c>
       <c r="I14" s="3">
+        <v>0</v>
+      </c>
+      <c r="J14" s="3">
         <v>-200</v>
       </c>
-      <c r="J14" s="3">
+      <c r="K14" s="3">
         <v>42300</v>
       </c>
-      <c r="K14" s="3">
-        <v>0</v>
-      </c>
       <c r="L14" s="3">
         <v>0</v>
       </c>
@@ -1445,112 +1464,118 @@
       <c r="AJ14" s="3">
         <v>0</v>
       </c>
+      <c r="AK14" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="15" spans="1:36" x14ac:dyDescent="0.2">
+    <row r="15" spans="1:37" x14ac:dyDescent="0.2">
       <c r="C15" s="1" t="s">
         <v>11</v>
       </c>
       <c r="D15" s="3">
+        <v>150600</v>
+      </c>
+      <c r="E15" s="3">
         <v>164900</v>
       </c>
-      <c r="E15" s="3">
+      <c r="F15" s="3">
         <v>149400</v>
       </c>
-      <c r="F15" s="3">
+      <c r="G15" s="3">
         <v>148900</v>
       </c>
-      <c r="G15" s="3">
+      <c r="H15" s="3">
         <v>144200</v>
       </c>
-      <c r="H15" s="3">
+      <c r="I15" s="3">
         <v>130600</v>
       </c>
-      <c r="I15" s="3">
+      <c r="J15" s="3">
         <v>130000</v>
       </c>
-      <c r="J15" s="3">
+      <c r="K15" s="3">
         <v>130100</v>
       </c>
-      <c r="K15" s="3">
+      <c r="L15" s="3">
         <v>-101500</v>
       </c>
-      <c r="L15" s="3">
+      <c r="M15" s="3">
         <v>-92100</v>
       </c>
-      <c r="M15" s="3">
+      <c r="N15" s="3">
         <v>-100700</v>
       </c>
-      <c r="N15" s="3">
+      <c r="O15" s="3">
         <v>-101400</v>
       </c>
-      <c r="O15" s="3">
+      <c r="P15" s="3">
         <v>-98200</v>
       </c>
-      <c r="P15" s="3">
+      <c r="Q15" s="3">
         <v>-97600</v>
       </c>
-      <c r="Q15" s="3">
+      <c r="R15" s="3">
         <v>-97400</v>
       </c>
-      <c r="R15" s="3">
+      <c r="S15" s="3">
         <v>-100600</v>
       </c>
-      <c r="S15" s="3">
+      <c r="T15" s="3">
         <v>-99400</v>
       </c>
-      <c r="T15" s="3">
+      <c r="U15" s="3">
         <v>-99600</v>
       </c>
-      <c r="U15" s="3">
+      <c r="V15" s="3">
         <v>-96100</v>
       </c>
-      <c r="V15" s="3">
+      <c r="W15" s="3">
         <v>-109500</v>
       </c>
-      <c r="W15" s="3">
+      <c r="X15" s="3">
         <v>-115200</v>
       </c>
-      <c r="X15" s="3">
+      <c r="Y15" s="3">
         <v>-112100</v>
       </c>
-      <c r="Y15" s="3">
+      <c r="Z15" s="3">
         <v>-104100</v>
       </c>
-      <c r="Z15" s="3">
+      <c r="AA15" s="3">
         <v>-88900</v>
       </c>
-      <c r="AA15" s="3">
+      <c r="AB15" s="3">
         <v>-50500</v>
       </c>
-      <c r="AB15" s="3">
+      <c r="AC15" s="3">
         <v>-47800</v>
       </c>
-      <c r="AC15" s="3">
+      <c r="AD15" s="3">
         <v>-44700</v>
       </c>
-      <c r="AD15" s="3">
+      <c r="AE15" s="3">
         <v>-40700</v>
       </c>
-      <c r="AE15" s="3">
+      <c r="AF15" s="3">
         <v>-39500</v>
       </c>
-      <c r="AF15" s="3">
+      <c r="AG15" s="3">
         <v>-40300</v>
       </c>
-      <c r="AG15" s="3">
+      <c r="AH15" s="3">
         <v>-40800</v>
       </c>
-      <c r="AH15" s="3">
+      <c r="AI15" s="3">
         <v>-44500</v>
       </c>
-      <c r="AI15" s="3">
+      <c r="AJ15" s="3">
         <v>-54800</v>
       </c>
-      <c r="AJ15" s="3">
+      <c r="AK15" s="3">
         <v>-53700</v>
       </c>
     </row>
-    <row r="16" spans="1:36" x14ac:dyDescent="0.2">
+    <row r="16" spans="1:37" x14ac:dyDescent="0.2">
       <c r="D16" s="3"/>
       <c r="E16" s="3"/>
       <c r="F16" s="3"/>
@@ -1584,216 +1609,223 @@
       <c r="AH16" s="3"/>
       <c r="AI16" s="3"/>
       <c r="AJ16" s="3"/>
+      <c r="AK16" s="3"/>
     </row>
-    <row r="17" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="17" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C17" s="1" t="s">
         <v>12</v>
       </c>
       <c r="D17" s="3">
+        <v>1684700</v>
+      </c>
+      <c r="E17" s="3">
         <v>887900</v>
       </c>
-      <c r="E17" s="3">
+      <c r="F17" s="3">
         <v>1233600</v>
       </c>
-      <c r="F17" s="3">
+      <c r="G17" s="3">
         <v>1363800</v>
       </c>
-      <c r="G17" s="3">
+      <c r="H17" s="3">
         <v>1160500</v>
       </c>
-      <c r="H17" s="3">
+      <c r="I17" s="3">
         <v>1189600</v>
       </c>
-      <c r="I17" s="3">
+      <c r="J17" s="3">
         <v>1049500</v>
       </c>
-      <c r="J17" s="3">
+      <c r="K17" s="3">
         <v>1131700</v>
       </c>
-      <c r="K17" s="3">
+      <c r="L17" s="3">
         <v>1897900</v>
       </c>
-      <c r="L17" s="3">
+      <c r="M17" s="3">
         <v>1245200</v>
       </c>
-      <c r="M17" s="3">
+      <c r="N17" s="3">
         <v>1121400</v>
       </c>
-      <c r="N17" s="3">
+      <c r="O17" s="3">
         <v>861300</v>
       </c>
-      <c r="O17" s="3">
+      <c r="P17" s="3">
         <v>772200</v>
       </c>
-      <c r="P17" s="3">
+      <c r="Q17" s="3">
         <v>616800</v>
       </c>
-      <c r="Q17" s="3">
+      <c r="R17" s="3">
         <v>573600</v>
       </c>
-      <c r="R17" s="3">
+      <c r="S17" s="3">
         <v>625700</v>
       </c>
-      <c r="S17" s="3">
+      <c r="T17" s="3">
         <v>727900</v>
       </c>
-      <c r="T17" s="3">
+      <c r="U17" s="3">
         <v>721100</v>
       </c>
-      <c r="U17" s="3">
+      <c r="V17" s="3">
         <v>966200</v>
       </c>
-      <c r="V17" s="3">
+      <c r="W17" s="3">
         <v>926000</v>
       </c>
-      <c r="W17" s="3">
+      <c r="X17" s="3">
         <v>1019500</v>
       </c>
-      <c r="X17" s="3">
+      <c r="Y17" s="3">
         <v>1190700</v>
       </c>
-      <c r="Y17" s="3">
+      <c r="Z17" s="3">
         <v>1111900</v>
       </c>
-      <c r="Z17" s="3">
+      <c r="AA17" s="3">
         <v>1098300</v>
       </c>
-      <c r="AA17" s="3">
+      <c r="AB17" s="3">
         <v>1157200</v>
       </c>
-      <c r="AB17" s="3">
+      <c r="AC17" s="3">
         <v>918800</v>
       </c>
-      <c r="AC17" s="3">
+      <c r="AD17" s="3">
         <v>752200</v>
       </c>
-      <c r="AD17" s="3">
+      <c r="AE17" s="3">
         <v>877900</v>
       </c>
-      <c r="AE17" s="3">
+      <c r="AF17" s="3">
         <v>1026000</v>
       </c>
-      <c r="AF17" s="3">
+      <c r="AG17" s="3">
         <v>926800</v>
       </c>
-      <c r="AG17" s="3">
+      <c r="AH17" s="3">
         <v>906500</v>
       </c>
-      <c r="AH17" s="3">
+      <c r="AI17" s="3">
         <v>830000</v>
       </c>
-      <c r="AI17" s="3">
+      <c r="AJ17" s="3">
         <v>903100</v>
       </c>
-      <c r="AJ17" s="3">
+      <c r="AK17" s="3">
         <v>963600</v>
       </c>
     </row>
-    <row r="18" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="18" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C18" s="1" t="s">
         <v>13</v>
       </c>
       <c r="D18" s="3">
+        <v>459500</v>
+      </c>
+      <c r="E18" s="3">
         <v>909700</v>
       </c>
-      <c r="E18" s="3">
+      <c r="F18" s="3">
         <v>910800</v>
       </c>
-      <c r="F18" s="3">
+      <c r="G18" s="3">
         <v>856000</v>
       </c>
-      <c r="G18" s="3">
-        <v>27200</v>
-      </c>
       <c r="H18" s="3">
+        <v>104100</v>
+      </c>
+      <c r="I18" s="3">
         <v>911700</v>
       </c>
-      <c r="I18" s="3">
+      <c r="J18" s="3">
         <v>699100</v>
       </c>
-      <c r="J18" s="3">
+      <c r="K18" s="3">
         <v>960100</v>
       </c>
-      <c r="K18" s="3">
+      <c r="L18" s="3">
         <v>1564300</v>
       </c>
-      <c r="L18" s="3">
+      <c r="M18" s="3">
         <v>1547000</v>
       </c>
-      <c r="M18" s="3">
+      <c r="N18" s="3">
         <v>1365800</v>
       </c>
-      <c r="N18" s="3">
+      <c r="O18" s="3">
         <v>1403000</v>
       </c>
-      <c r="O18" s="3">
+      <c r="P18" s="3">
         <v>1253800</v>
       </c>
-      <c r="P18" s="3">
+      <c r="Q18" s="3">
         <v>1245400</v>
       </c>
-      <c r="Q18" s="3">
+      <c r="R18" s="3">
         <v>1213900</v>
       </c>
-      <c r="R18" s="3">
+      <c r="S18" s="3">
         <v>1096400</v>
       </c>
-      <c r="S18" s="3">
+      <c r="T18" s="3">
         <v>1000300</v>
       </c>
-      <c r="T18" s="3">
+      <c r="U18" s="3">
         <v>1028700</v>
       </c>
-      <c r="U18" s="3">
+      <c r="V18" s="3">
         <v>891200</v>
       </c>
-      <c r="V18" s="3">
+      <c r="W18" s="3">
         <v>1102100</v>
       </c>
-      <c r="W18" s="3">
+      <c r="X18" s="3">
         <v>1196900</v>
       </c>
-      <c r="X18" s="3">
+      <c r="Y18" s="3">
         <v>1097100</v>
       </c>
-      <c r="Y18" s="3">
+      <c r="Z18" s="3">
         <v>1241200</v>
       </c>
-      <c r="Z18" s="3">
+      <c r="AA18" s="3">
         <v>1271100</v>
       </c>
-      <c r="AA18" s="3">
+      <c r="AB18" s="3">
         <v>996800</v>
       </c>
-      <c r="AB18" s="3">
+      <c r="AC18" s="3">
         <v>1087400</v>
       </c>
-      <c r="AC18" s="3">
+      <c r="AD18" s="3">
         <v>1237400</v>
       </c>
-      <c r="AD18" s="3">
+      <c r="AE18" s="3">
         <v>1032900</v>
       </c>
-      <c r="AE18" s="3">
+      <c r="AF18" s="3">
         <v>886500</v>
       </c>
-      <c r="AF18" s="3">
+      <c r="AG18" s="3">
         <v>998500</v>
       </c>
-      <c r="AG18" s="3">
+      <c r="AH18" s="3">
         <v>946600</v>
       </c>
-      <c r="AH18" s="3">
+      <c r="AI18" s="3">
         <v>1003700</v>
       </c>
-      <c r="AI18" s="3">
+      <c r="AJ18" s="3">
         <v>995700</v>
       </c>
-      <c r="AJ18" s="3">
+      <c r="AK18" s="3">
         <v>934400</v>
       </c>
     </row>
-    <row r="19" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="19" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C19" s="1" t="s">
         <v>14</v>
       </c>
@@ -1830,216 +1862,223 @@
       <c r="AH19" s="3"/>
       <c r="AI19" s="3"/>
       <c r="AJ19" s="3"/>
+      <c r="AK19" s="3"/>
     </row>
-    <row r="20" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="20" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C20" s="1" t="s">
         <v>15</v>
       </c>
       <c r="D20" s="3">
+        <v>26000</v>
+      </c>
+      <c r="E20" s="3">
         <v>-4400</v>
       </c>
-      <c r="E20" s="3">
+      <c r="F20" s="3">
         <v>1400</v>
       </c>
-      <c r="F20" s="3">
+      <c r="G20" s="3">
         <v>-7500</v>
       </c>
-      <c r="G20" s="3">
-        <v>-65300</v>
-      </c>
       <c r="H20" s="3">
+        <v>11600</v>
+      </c>
+      <c r="I20" s="3">
         <v>-14500</v>
       </c>
-      <c r="I20" s="3">
+      <c r="J20" s="3">
         <v>32600</v>
       </c>
-      <c r="J20" s="3">
+      <c r="K20" s="3">
         <v>-56500</v>
       </c>
-      <c r="K20" s="3">
+      <c r="L20" s="3">
         <v>-1017300</v>
       </c>
-      <c r="L20" s="3">
+      <c r="M20" s="3">
         <v>-606600</v>
       </c>
-      <c r="M20" s="3">
+      <c r="N20" s="3">
         <v>-375600</v>
       </c>
-      <c r="N20" s="3">
+      <c r="O20" s="3">
         <v>-505900</v>
       </c>
-      <c r="O20" s="3">
+      <c r="P20" s="3">
         <v>-806400</v>
       </c>
-      <c r="P20" s="3">
+      <c r="Q20" s="3">
         <v>-394200</v>
       </c>
-      <c r="Q20" s="3">
+      <c r="R20" s="3">
         <v>-406900</v>
       </c>
-      <c r="R20" s="3">
+      <c r="S20" s="3">
         <v>-399500</v>
       </c>
-      <c r="S20" s="3">
+      <c r="T20" s="3">
         <v>-784600</v>
       </c>
-      <c r="T20" s="3">
+      <c r="U20" s="3">
         <v>-508200</v>
       </c>
-      <c r="U20" s="3">
+      <c r="V20" s="3">
         <v>-674600</v>
       </c>
-      <c r="V20" s="3">
+      <c r="W20" s="3">
         <v>-492400</v>
       </c>
-      <c r="W20" s="3">
+      <c r="X20" s="3">
         <v>-920900</v>
       </c>
-      <c r="X20" s="3">
+      <c r="Y20" s="3">
         <v>-527400</v>
       </c>
-      <c r="Y20" s="3">
+      <c r="Z20" s="3">
         <v>-447200</v>
       </c>
-      <c r="Z20" s="3">
+      <c r="AA20" s="3">
         <v>-519600</v>
       </c>
-      <c r="AA20" s="3">
+      <c r="AB20" s="3">
         <v>-847700</v>
       </c>
-      <c r="AB20" s="3">
+      <c r="AC20" s="3">
         <v>-418500</v>
       </c>
-      <c r="AC20" s="3">
+      <c r="AD20" s="3">
         <v>-401200</v>
       </c>
-      <c r="AD20" s="3">
+      <c r="AE20" s="3">
         <v>-355800</v>
       </c>
-      <c r="AE20" s="3">
+      <c r="AF20" s="3">
         <v>-756300</v>
       </c>
-      <c r="AF20" s="3">
+      <c r="AG20" s="3">
         <v>-671500</v>
       </c>
-      <c r="AG20" s="3">
+      <c r="AH20" s="3">
         <v>-417500</v>
       </c>
-      <c r="AH20" s="3">
+      <c r="AI20" s="3">
         <v>-274500</v>
       </c>
-      <c r="AI20" s="3">
+      <c r="AJ20" s="3">
         <v>-821100</v>
       </c>
-      <c r="AJ20" s="3">
+      <c r="AK20" s="3">
         <v>-531000</v>
       </c>
     </row>
-    <row r="21" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="21" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C21" s="1" t="s">
         <v>16</v>
       </c>
       <c r="D21" s="3">
+        <v>584100</v>
+      </c>
+      <c r="E21" s="3">
         <v>1079100</v>
       </c>
-      <c r="E21" s="3">
+      <c r="F21" s="3">
         <v>1058900</v>
       </c>
-      <c r="F21" s="3">
+      <c r="G21" s="3">
         <v>1012400</v>
       </c>
-      <c r="G21" s="3">
+      <c r="H21" s="3">
         <v>236700</v>
       </c>
-      <c r="H21" s="3">
+      <c r="I21" s="3">
         <v>1056800</v>
       </c>
-      <c r="I21" s="3">
+      <c r="J21" s="3">
         <v>796500</v>
       </c>
-      <c r="J21" s="3">
+      <c r="K21" s="3">
         <v>1146700</v>
       </c>
-      <c r="K21" s="3">
+      <c r="L21" s="3">
         <v>732200</v>
       </c>
-      <c r="L21" s="3">
+      <c r="M21" s="3">
         <v>1110000</v>
       </c>
-      <c r="M21" s="3">
+      <c r="N21" s="3">
         <v>1165700</v>
       </c>
-      <c r="N21" s="3">
+      <c r="O21" s="3">
         <v>1065700</v>
       </c>
-      <c r="O21" s="3">
+      <c r="P21" s="3">
         <v>603300</v>
       </c>
-      <c r="P21" s="3">
+      <c r="Q21" s="3">
         <v>1000500</v>
       </c>
-      <c r="Q21" s="3">
+      <c r="R21" s="3">
         <v>991500</v>
       </c>
-      <c r="R21" s="3">
+      <c r="S21" s="3">
         <v>799800</v>
       </c>
-      <c r="S21" s="3">
+      <c r="T21" s="3">
         <v>316900</v>
       </c>
-      <c r="T21" s="3">
+      <c r="U21" s="3">
         <v>622000</v>
       </c>
-      <c r="U21" s="3">
+      <c r="V21" s="3">
         <v>315300</v>
       </c>
-      <c r="V21" s="3">
+      <c r="W21" s="3">
         <v>721900</v>
       </c>
-      <c r="W21" s="3">
+      <c r="X21" s="3">
         <v>396300</v>
       </c>
-      <c r="X21" s="3">
+      <c r="Y21" s="3">
         <v>686600</v>
       </c>
-      <c r="Y21" s="3">
+      <c r="Z21" s="3">
         <v>902900</v>
       </c>
-      <c r="Z21" s="3">
+      <c r="AA21" s="3">
         <v>845100</v>
       </c>
-      <c r="AA21" s="3">
+      <c r="AB21" s="3">
         <v>210800</v>
       </c>
-      <c r="AB21" s="3">
+      <c r="AC21" s="3">
         <v>727400</v>
       </c>
-      <c r="AC21" s="3">
+      <c r="AD21" s="3">
         <v>892200</v>
       </c>
-      <c r="AD21" s="3">
+      <c r="AE21" s="3">
         <v>727700</v>
       </c>
-      <c r="AE21" s="3">
+      <c r="AF21" s="3">
         <v>180100</v>
       </c>
-      <c r="AF21" s="3">
+      <c r="AG21" s="3">
         <v>377800</v>
       </c>
-      <c r="AG21" s="3">
+      <c r="AH21" s="3">
         <v>580800</v>
       </c>
-      <c r="AH21" s="3">
+      <c r="AI21" s="3">
         <v>784400</v>
       </c>
-      <c r="AI21" s="3">
+      <c r="AJ21" s="3">
         <v>229400</v>
       </c>
-      <c r="AJ21" s="3">
+      <c r="AK21" s="3">
         <v>457200</v>
       </c>
     </row>
-    <row r="22" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="22" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C22" s="1" t="s">
         <v>17</v>
       </c>
@@ -2064,8 +2103,8 @@
       <c r="J22" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="K22" s="3">
-        <v>0</v>
+      <c r="K22" s="3" t="s">
+        <v>5</v>
       </c>
       <c r="L22" s="3">
         <v>0</v>
@@ -2142,216 +2181,225 @@
       <c r="AJ22" s="3">
         <v>0</v>
       </c>
+      <c r="AK22" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="23" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="23" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C23" s="1" t="s">
         <v>18</v>
       </c>
       <c r="D23" s="3">
+        <v>427300</v>
+      </c>
+      <c r="E23" s="3">
         <v>914200</v>
       </c>
-      <c r="E23" s="3">
+      <c r="F23" s="3">
         <v>904900</v>
       </c>
-      <c r="F23" s="3">
+      <c r="G23" s="3">
         <v>851200</v>
       </c>
-      <c r="G23" s="3">
+      <c r="H23" s="3">
         <v>94200</v>
       </c>
-      <c r="H23" s="3">
+      <c r="I23" s="3">
         <v>926200</v>
       </c>
-      <c r="I23" s="3">
+      <c r="J23" s="3">
         <v>666800</v>
       </c>
-      <c r="J23" s="3">
+      <c r="K23" s="3">
         <v>974300</v>
       </c>
-      <c r="K23" s="3">
+      <c r="L23" s="3">
         <v>546900</v>
       </c>
-      <c r="L23" s="3">
+      <c r="M23" s="3">
         <v>940400</v>
       </c>
-      <c r="M23" s="3">
+      <c r="N23" s="3">
         <v>990200</v>
       </c>
-      <c r="N23" s="3">
+      <c r="O23" s="3">
         <v>897100</v>
       </c>
-      <c r="O23" s="3">
+      <c r="P23" s="3">
         <v>447400</v>
       </c>
-      <c r="P23" s="3">
+      <c r="Q23" s="3">
         <v>851200</v>
       </c>
-      <c r="Q23" s="3">
+      <c r="R23" s="3">
         <v>807000</v>
       </c>
-      <c r="R23" s="3">
+      <c r="S23" s="3">
         <v>696900</v>
       </c>
-      <c r="S23" s="3">
+      <c r="T23" s="3">
         <v>215700</v>
       </c>
-      <c r="T23" s="3">
+      <c r="U23" s="3">
         <v>520500</v>
       </c>
-      <c r="U23" s="3">
+      <c r="V23" s="3">
         <v>216600</v>
       </c>
-      <c r="V23" s="3">
+      <c r="W23" s="3">
         <v>609600</v>
       </c>
-      <c r="W23" s="3">
+      <c r="X23" s="3">
         <v>276000</v>
       </c>
-      <c r="X23" s="3">
+      <c r="Y23" s="3">
         <v>569700</v>
       </c>
-      <c r="Y23" s="3">
+      <c r="Z23" s="3">
         <v>794000</v>
       </c>
-      <c r="Z23" s="3">
+      <c r="AA23" s="3">
         <v>751500</v>
       </c>
-      <c r="AA23" s="3">
+      <c r="AB23" s="3">
         <v>149100</v>
       </c>
-      <c r="AB23" s="3">
+      <c r="AC23" s="3">
         <v>668900</v>
       </c>
-      <c r="AC23" s="3">
+      <c r="AD23" s="3">
         <v>836200</v>
       </c>
-      <c r="AD23" s="3">
+      <c r="AE23" s="3">
         <v>677100</v>
       </c>
-      <c r="AE23" s="3">
+      <c r="AF23" s="3">
         <v>130200</v>
       </c>
-      <c r="AF23" s="3">
+      <c r="AG23" s="3">
         <v>327000</v>
       </c>
-      <c r="AG23" s="3">
+      <c r="AH23" s="3">
         <v>529200</v>
       </c>
-      <c r="AH23" s="3">
+      <c r="AI23" s="3">
         <v>729200</v>
       </c>
-      <c r="AI23" s="3">
+      <c r="AJ23" s="3">
         <v>174600</v>
       </c>
-      <c r="AJ23" s="3">
+      <c r="AK23" s="3">
         <v>403400</v>
       </c>
     </row>
-    <row r="24" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="24" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C24" s="1" t="s">
         <v>19</v>
       </c>
       <c r="D24" s="3">
+        <v>120000</v>
+      </c>
+      <c r="E24" s="3">
         <v>216000</v>
       </c>
-      <c r="E24" s="3">
+      <c r="F24" s="3">
         <v>207100</v>
       </c>
-      <c r="F24" s="3">
+      <c r="G24" s="3">
         <v>227000</v>
       </c>
-      <c r="G24" s="3">
+      <c r="H24" s="3">
         <v>21000</v>
       </c>
-      <c r="H24" s="3">
+      <c r="I24" s="3">
         <v>244100</v>
       </c>
-      <c r="I24" s="3">
+      <c r="J24" s="3">
         <v>160200</v>
       </c>
-      <c r="J24" s="3">
+      <c r="K24" s="3">
         <v>248300</v>
       </c>
-      <c r="K24" s="3">
+      <c r="L24" s="3">
         <v>148500</v>
       </c>
-      <c r="L24" s="3">
+      <c r="M24" s="3">
         <v>259000</v>
       </c>
-      <c r="M24" s="3">
+      <c r="N24" s="3">
         <v>240200</v>
       </c>
-      <c r="N24" s="3">
+      <c r="O24" s="3">
         <v>225300</v>
       </c>
-      <c r="O24" s="3">
+      <c r="P24" s="3">
         <v>113100</v>
       </c>
-      <c r="P24" s="3">
+      <c r="Q24" s="3">
         <v>232900</v>
       </c>
-      <c r="Q24" s="3">
+      <c r="R24" s="3">
         <v>193200</v>
       </c>
-      <c r="R24" s="3">
+      <c r="S24" s="3">
         <v>164900</v>
       </c>
-      <c r="S24" s="3">
+      <c r="T24" s="3">
         <v>53200</v>
       </c>
-      <c r="T24" s="3">
+      <c r="U24" s="3">
         <v>118800</v>
       </c>
-      <c r="U24" s="3">
+      <c r="V24" s="3">
         <v>50000</v>
       </c>
-      <c r="V24" s="3">
+      <c r="W24" s="3">
         <v>157800</v>
       </c>
-      <c r="W24" s="3">
+      <c r="X24" s="3">
         <v>79200</v>
       </c>
-      <c r="X24" s="3">
+      <c r="Y24" s="3">
         <v>115700</v>
       </c>
-      <c r="Y24" s="3">
+      <c r="Z24" s="3">
         <v>215500</v>
       </c>
-      <c r="Z24" s="3">
+      <c r="AA24" s="3">
         <v>192300</v>
       </c>
-      <c r="AA24" s="3">
+      <c r="AB24" s="3">
         <v>39300</v>
       </c>
-      <c r="AB24" s="3">
+      <c r="AC24" s="3">
         <v>179200</v>
       </c>
-      <c r="AC24" s="3">
+      <c r="AD24" s="3">
         <v>229900</v>
       </c>
-      <c r="AD24" s="3">
+      <c r="AE24" s="3">
         <v>177700</v>
       </c>
-      <c r="AE24" s="3">
+      <c r="AF24" s="3">
         <v>9000</v>
       </c>
-      <c r="AF24" s="3">
+      <c r="AG24" s="3">
         <v>77600</v>
       </c>
-      <c r="AG24" s="3">
+      <c r="AH24" s="3">
         <v>118800</v>
       </c>
-      <c r="AH24" s="3">
+      <c r="AI24" s="3">
         <v>163600</v>
       </c>
-      <c r="AI24" s="3">
+      <c r="AJ24" s="3">
         <v>30300</v>
       </c>
-      <c r="AJ24" s="3">
+      <c r="AK24" s="3">
         <v>80000</v>
       </c>
     </row>
-    <row r="25" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="25" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C25" s="1" t="s">
         <v>20</v>
       </c>
@@ -2454,216 +2502,225 @@
       <c r="AJ25" s="3">
         <v>0</v>
       </c>
+      <c r="AK25" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="26" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="26" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C26" s="1" t="s">
         <v>21</v>
       </c>
       <c r="D26" s="3">
+        <v>307400</v>
+      </c>
+      <c r="E26" s="3">
         <v>698200</v>
       </c>
-      <c r="E26" s="3">
+      <c r="F26" s="3">
         <v>697800</v>
       </c>
-      <c r="F26" s="3">
+      <c r="G26" s="3">
         <v>624200</v>
       </c>
-      <c r="G26" s="3">
+      <c r="H26" s="3">
         <v>73200</v>
       </c>
-      <c r="H26" s="3">
+      <c r="I26" s="3">
         <v>682000</v>
       </c>
-      <c r="I26" s="3">
+      <c r="J26" s="3">
         <v>506600</v>
       </c>
-      <c r="J26" s="3">
+      <c r="K26" s="3">
         <v>726000</v>
       </c>
-      <c r="K26" s="3">
+      <c r="L26" s="3">
         <v>398500</v>
       </c>
-      <c r="L26" s="3">
+      <c r="M26" s="3">
         <v>681400</v>
       </c>
-      <c r="M26" s="3">
+      <c r="N26" s="3">
         <v>750000</v>
       </c>
-      <c r="N26" s="3">
+      <c r="O26" s="3">
         <v>671800</v>
       </c>
-      <c r="O26" s="3">
+      <c r="P26" s="3">
         <v>334300</v>
       </c>
-      <c r="P26" s="3">
+      <c r="Q26" s="3">
         <v>618300</v>
       </c>
-      <c r="Q26" s="3">
+      <c r="R26" s="3">
         <v>613800</v>
       </c>
-      <c r="R26" s="3">
+      <c r="S26" s="3">
         <v>532000</v>
       </c>
-      <c r="S26" s="3">
+      <c r="T26" s="3">
         <v>162400</v>
       </c>
-      <c r="T26" s="3">
+      <c r="U26" s="3">
         <v>401700</v>
       </c>
-      <c r="U26" s="3">
+      <c r="V26" s="3">
         <v>166500</v>
       </c>
-      <c r="V26" s="3">
+      <c r="W26" s="3">
         <v>451800</v>
       </c>
-      <c r="W26" s="3">
+      <c r="X26" s="3">
         <v>196800</v>
       </c>
-      <c r="X26" s="3">
+      <c r="Y26" s="3">
         <v>454000</v>
       </c>
-      <c r="Y26" s="3">
+      <c r="Z26" s="3">
         <v>578500</v>
       </c>
-      <c r="Z26" s="3">
+      <c r="AA26" s="3">
         <v>559200</v>
       </c>
-      <c r="AA26" s="3">
+      <c r="AB26" s="3">
         <v>109900</v>
       </c>
-      <c r="AB26" s="3">
+      <c r="AC26" s="3">
         <v>489700</v>
       </c>
-      <c r="AC26" s="3">
+      <c r="AD26" s="3">
         <v>606300</v>
       </c>
-      <c r="AD26" s="3">
+      <c r="AE26" s="3">
         <v>499400</v>
       </c>
-      <c r="AE26" s="3">
+      <c r="AF26" s="3">
         <v>121100</v>
       </c>
-      <c r="AF26" s="3">
+      <c r="AG26" s="3">
         <v>249400</v>
       </c>
-      <c r="AG26" s="3">
+      <c r="AH26" s="3">
         <v>410300</v>
       </c>
-      <c r="AH26" s="3">
+      <c r="AI26" s="3">
         <v>565600</v>
       </c>
-      <c r="AI26" s="3">
+      <c r="AJ26" s="3">
         <v>144300</v>
       </c>
-      <c r="AJ26" s="3">
+      <c r="AK26" s="3">
         <v>323500</v>
       </c>
     </row>
-    <row r="27" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="27" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C27" s="1" t="s">
         <v>22</v>
       </c>
       <c r="D27" s="3">
+        <v>261600</v>
+      </c>
+      <c r="E27" s="3">
         <v>655100</v>
       </c>
-      <c r="E27" s="3">
+      <c r="F27" s="3">
         <v>647100</v>
       </c>
-      <c r="F27" s="3">
+      <c r="G27" s="3">
         <v>586900</v>
       </c>
-      <c r="G27" s="3">
+      <c r="H27" s="3">
         <v>25300</v>
       </c>
-      <c r="H27" s="3">
+      <c r="I27" s="3">
         <v>643700</v>
       </c>
-      <c r="I27" s="3">
+      <c r="J27" s="3">
         <v>449800</v>
       </c>
-      <c r="J27" s="3">
+      <c r="K27" s="3">
         <v>677400</v>
       </c>
-      <c r="K27" s="3">
+      <c r="L27" s="3">
         <v>338800</v>
       </c>
-      <c r="L27" s="3">
+      <c r="M27" s="3">
         <v>640600</v>
       </c>
-      <c r="M27" s="3">
+      <c r="N27" s="3">
         <v>684400</v>
       </c>
-      <c r="N27" s="3">
+      <c r="O27" s="3">
         <v>631400</v>
       </c>
-      <c r="O27" s="3">
+      <c r="P27" s="3">
         <v>279500</v>
       </c>
-      <c r="P27" s="3">
+      <c r="Q27" s="3">
         <v>570700</v>
       </c>
-      <c r="Q27" s="3">
+      <c r="R27" s="3">
         <v>552600</v>
       </c>
-      <c r="R27" s="3">
+      <c r="S27" s="3">
         <v>482000</v>
       </c>
-      <c r="S27" s="3">
+      <c r="T27" s="3">
         <v>112600</v>
       </c>
-      <c r="T27" s="3">
+      <c r="U27" s="3">
         <v>358800</v>
       </c>
-      <c r="U27" s="3">
+      <c r="V27" s="3">
         <v>100500</v>
       </c>
-      <c r="V27" s="3">
+      <c r="W27" s="3">
         <v>412900</v>
       </c>
-      <c r="W27" s="3">
+      <c r="X27" s="3">
         <v>174900</v>
       </c>
-      <c r="X27" s="3">
+      <c r="Y27" s="3">
         <v>410100</v>
       </c>
-      <c r="Y27" s="3">
+      <c r="Z27" s="3">
         <v>537700</v>
       </c>
-      <c r="Z27" s="3">
+      <c r="AA27" s="3">
         <v>517500</v>
       </c>
-      <c r="AA27" s="3">
+      <c r="AB27" s="3">
         <v>76800</v>
       </c>
-      <c r="AB27" s="3">
+      <c r="AC27" s="3">
         <v>453900</v>
       </c>
-      <c r="AC27" s="3">
+      <c r="AD27" s="3">
         <v>569900</v>
       </c>
-      <c r="AD27" s="3">
+      <c r="AE27" s="3">
         <v>463600</v>
       </c>
-      <c r="AE27" s="3">
+      <c r="AF27" s="3">
         <v>84900</v>
       </c>
-      <c r="AF27" s="3">
+      <c r="AG27" s="3">
         <v>212100</v>
       </c>
-      <c r="AG27" s="3">
+      <c r="AH27" s="3">
         <v>369000</v>
       </c>
-      <c r="AH27" s="3">
+      <c r="AI27" s="3">
         <v>517600</v>
       </c>
-      <c r="AI27" s="3">
+      <c r="AJ27" s="3">
         <v>88500</v>
       </c>
-      <c r="AJ27" s="3">
+      <c r="AK27" s="3">
         <v>275700</v>
       </c>
     </row>
-    <row r="28" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="28" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C28" s="1" t="s">
         <v>23</v>
       </c>
@@ -2766,8 +2823,11 @@
       <c r="AJ28" s="3">
         <v>0</v>
       </c>
+      <c r="AK28" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="29" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="29" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C29" s="1" t="s">
         <v>24</v>
       </c>
@@ -2870,8 +2930,11 @@
       <c r="AJ29" s="3">
         <v>0</v>
       </c>
+      <c r="AK29" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="30" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="30" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C30" s="1" t="s">
         <v>25</v>
       </c>
@@ -2974,8 +3037,11 @@
       <c r="AJ30" s="3">
         <v>0</v>
       </c>
+      <c r="AK30" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="31" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="31" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C31" s="1" t="s">
         <v>26</v>
       </c>
@@ -3078,216 +3144,225 @@
       <c r="AJ31" s="3">
         <v>0</v>
       </c>
+      <c r="AK31" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="32" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="32" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C32" s="1" t="s">
         <v>27</v>
       </c>
       <c r="D32" s="3">
+        <v>-26000</v>
+      </c>
+      <c r="E32" s="3">
         <v>4400</v>
       </c>
-      <c r="E32" s="3">
+      <c r="F32" s="3">
         <v>-1400</v>
       </c>
-      <c r="F32" s="3">
+      <c r="G32" s="3">
         <v>7500</v>
       </c>
-      <c r="G32" s="3">
-        <v>65300</v>
-      </c>
       <c r="H32" s="3">
+        <v>-11600</v>
+      </c>
+      <c r="I32" s="3">
         <v>14500</v>
       </c>
-      <c r="I32" s="3">
+      <c r="J32" s="3">
         <v>-32600</v>
       </c>
-      <c r="J32" s="3">
+      <c r="K32" s="3">
         <v>56500</v>
       </c>
-      <c r="K32" s="3">
+      <c r="L32" s="3">
         <v>1017300</v>
       </c>
-      <c r="L32" s="3">
+      <c r="M32" s="3">
         <v>606600</v>
       </c>
-      <c r="M32" s="3">
+      <c r="N32" s="3">
         <v>375600</v>
       </c>
-      <c r="N32" s="3">
+      <c r="O32" s="3">
         <v>505900</v>
       </c>
-      <c r="O32" s="3">
+      <c r="P32" s="3">
         <v>806400</v>
       </c>
-      <c r="P32" s="3">
+      <c r="Q32" s="3">
         <v>394200</v>
       </c>
-      <c r="Q32" s="3">
+      <c r="R32" s="3">
         <v>406900</v>
       </c>
-      <c r="R32" s="3">
+      <c r="S32" s="3">
         <v>399500</v>
       </c>
-      <c r="S32" s="3">
+      <c r="T32" s="3">
         <v>784600</v>
       </c>
-      <c r="T32" s="3">
+      <c r="U32" s="3">
         <v>508200</v>
       </c>
-      <c r="U32" s="3">
+      <c r="V32" s="3">
         <v>674600</v>
       </c>
-      <c r="V32" s="3">
+      <c r="W32" s="3">
         <v>492400</v>
       </c>
-      <c r="W32" s="3">
+      <c r="X32" s="3">
         <v>920900</v>
       </c>
-      <c r="X32" s="3">
+      <c r="Y32" s="3">
         <v>527400</v>
       </c>
-      <c r="Y32" s="3">
+      <c r="Z32" s="3">
         <v>447200</v>
       </c>
-      <c r="Z32" s="3">
+      <c r="AA32" s="3">
         <v>519600</v>
       </c>
-      <c r="AA32" s="3">
+      <c r="AB32" s="3">
         <v>847700</v>
       </c>
-      <c r="AB32" s="3">
+      <c r="AC32" s="3">
         <v>418500</v>
       </c>
-      <c r="AC32" s="3">
+      <c r="AD32" s="3">
         <v>401200</v>
       </c>
-      <c r="AD32" s="3">
+      <c r="AE32" s="3">
         <v>355800</v>
       </c>
-      <c r="AE32" s="3">
+      <c r="AF32" s="3">
         <v>756300</v>
       </c>
-      <c r="AF32" s="3">
+      <c r="AG32" s="3">
         <v>671500</v>
       </c>
-      <c r="AG32" s="3">
+      <c r="AH32" s="3">
         <v>417500</v>
       </c>
-      <c r="AH32" s="3">
+      <c r="AI32" s="3">
         <v>274500</v>
       </c>
-      <c r="AI32" s="3">
+      <c r="AJ32" s="3">
         <v>821100</v>
       </c>
-      <c r="AJ32" s="3">
+      <c r="AK32" s="3">
         <v>531000</v>
       </c>
     </row>
-    <row r="33" spans="2:36" x14ac:dyDescent="0.2">
+    <row r="33" spans="2:37" x14ac:dyDescent="0.2">
       <c r="C33" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D33" s="3">
+        <v>288500</v>
+      </c>
+      <c r="E33" s="3">
         <v>688600</v>
       </c>
-      <c r="E33" s="3">
+      <c r="F33" s="3">
         <v>676000</v>
       </c>
-      <c r="F33" s="3">
+      <c r="G33" s="3">
         <v>613100</v>
       </c>
-      <c r="G33" s="3">
+      <c r="H33" s="3">
         <v>52500</v>
       </c>
-      <c r="H33" s="3">
+      <c r="I33" s="3">
         <v>668000</v>
       </c>
-      <c r="I33" s="3">
+      <c r="J33" s="3">
         <v>474700</v>
       </c>
-      <c r="J33" s="3">
+      <c r="K33" s="3">
         <v>700700</v>
       </c>
-      <c r="K33" s="3">
+      <c r="L33" s="3">
         <v>338800</v>
       </c>
-      <c r="L33" s="3">
+      <c r="M33" s="3">
         <v>640600</v>
       </c>
-      <c r="M33" s="3">
+      <c r="N33" s="3">
         <v>684400</v>
       </c>
-      <c r="N33" s="3">
+      <c r="O33" s="3">
         <v>631400</v>
       </c>
-      <c r="O33" s="3">
+      <c r="P33" s="3">
         <v>279500</v>
       </c>
-      <c r="P33" s="3">
+      <c r="Q33" s="3">
         <v>570700</v>
       </c>
-      <c r="Q33" s="3">
+      <c r="R33" s="3">
         <v>552600</v>
       </c>
-      <c r="R33" s="3">
+      <c r="S33" s="3">
         <v>482000</v>
       </c>
-      <c r="S33" s="3">
+      <c r="T33" s="3">
         <v>112600</v>
       </c>
-      <c r="T33" s="3">
+      <c r="U33" s="3">
         <v>358800</v>
       </c>
-      <c r="U33" s="3">
+      <c r="V33" s="3">
         <v>100500</v>
       </c>
-      <c r="V33" s="3">
+      <c r="W33" s="3">
         <v>412900</v>
       </c>
-      <c r="W33" s="3">
+      <c r="X33" s="3">
         <v>174900</v>
       </c>
-      <c r="X33" s="3">
+      <c r="Y33" s="3">
         <v>410100</v>
       </c>
-      <c r="Y33" s="3">
+      <c r="Z33" s="3">
         <v>537700</v>
       </c>
-      <c r="Z33" s="3">
+      <c r="AA33" s="3">
         <v>517500</v>
       </c>
-      <c r="AA33" s="3">
+      <c r="AB33" s="3">
         <v>76800</v>
       </c>
-      <c r="AB33" s="3">
+      <c r="AC33" s="3">
         <v>453900</v>
       </c>
-      <c r="AC33" s="3">
+      <c r="AD33" s="3">
         <v>569900</v>
       </c>
-      <c r="AD33" s="3">
+      <c r="AE33" s="3">
         <v>463600</v>
       </c>
-      <c r="AE33" s="3">
+      <c r="AF33" s="3">
         <v>84900</v>
       </c>
-      <c r="AF33" s="3">
+      <c r="AG33" s="3">
         <v>212100</v>
       </c>
-      <c r="AG33" s="3">
+      <c r="AH33" s="3">
         <v>369000</v>
       </c>
-      <c r="AH33" s="3">
+      <c r="AI33" s="3">
         <v>517600</v>
       </c>
-      <c r="AI33" s="3">
+      <c r="AJ33" s="3">
         <v>88500</v>
       </c>
-      <c r="AJ33" s="3">
+      <c r="AK33" s="3">
         <v>275700</v>
       </c>
     </row>
-    <row r="34" spans="2:36" x14ac:dyDescent="0.2">
+    <row r="34" spans="2:37" x14ac:dyDescent="0.2">
       <c r="C34" s="1" t="s">
         <v>29</v>
       </c>
@@ -3390,221 +3465,230 @@
       <c r="AJ34" s="3">
         <v>0</v>
       </c>
+      <c r="AK34" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="35" spans="2:36" x14ac:dyDescent="0.2">
+    <row r="35" spans="2:37" x14ac:dyDescent="0.2">
       <c r="C35" s="1" t="s">
         <v>30</v>
       </c>
       <c r="D35" s="3">
+        <v>288500</v>
+      </c>
+      <c r="E35" s="3">
         <v>688600</v>
       </c>
-      <c r="E35" s="3">
+      <c r="F35" s="3">
         <v>676000</v>
       </c>
-      <c r="F35" s="3">
+      <c r="G35" s="3">
         <v>613100</v>
       </c>
-      <c r="G35" s="3">
+      <c r="H35" s="3">
         <v>52500</v>
       </c>
-      <c r="H35" s="3">
+      <c r="I35" s="3">
         <v>668000</v>
       </c>
-      <c r="I35" s="3">
+      <c r="J35" s="3">
         <v>474700</v>
       </c>
-      <c r="J35" s="3">
+      <c r="K35" s="3">
         <v>700700</v>
       </c>
-      <c r="K35" s="3">
+      <c r="L35" s="3">
         <v>338800</v>
       </c>
-      <c r="L35" s="3">
+      <c r="M35" s="3">
         <v>640600</v>
       </c>
-      <c r="M35" s="3">
+      <c r="N35" s="3">
         <v>684400</v>
       </c>
-      <c r="N35" s="3">
+      <c r="O35" s="3">
         <v>631400</v>
       </c>
-      <c r="O35" s="3">
+      <c r="P35" s="3">
         <v>279500</v>
       </c>
-      <c r="P35" s="3">
+      <c r="Q35" s="3">
         <v>570700</v>
       </c>
-      <c r="Q35" s="3">
+      <c r="R35" s="3">
         <v>552600</v>
       </c>
-      <c r="R35" s="3">
+      <c r="S35" s="3">
         <v>482000</v>
       </c>
-      <c r="S35" s="3">
+      <c r="T35" s="3">
         <v>112600</v>
       </c>
-      <c r="T35" s="3">
+      <c r="U35" s="3">
         <v>358800</v>
       </c>
-      <c r="U35" s="3">
+      <c r="V35" s="3">
         <v>100500</v>
       </c>
-      <c r="V35" s="3">
+      <c r="W35" s="3">
         <v>412900</v>
       </c>
-      <c r="W35" s="3">
+      <c r="X35" s="3">
         <v>174900</v>
       </c>
-      <c r="X35" s="3">
+      <c r="Y35" s="3">
         <v>410100</v>
       </c>
-      <c r="Y35" s="3">
+      <c r="Z35" s="3">
         <v>537700</v>
       </c>
-      <c r="Z35" s="3">
+      <c r="AA35" s="3">
         <v>517500</v>
       </c>
-      <c r="AA35" s="3">
+      <c r="AB35" s="3">
         <v>76800</v>
       </c>
-      <c r="AB35" s="3">
+      <c r="AC35" s="3">
         <v>453900</v>
       </c>
-      <c r="AC35" s="3">
+      <c r="AD35" s="3">
         <v>569900</v>
       </c>
-      <c r="AD35" s="3">
+      <c r="AE35" s="3">
         <v>463600</v>
       </c>
-      <c r="AE35" s="3">
+      <c r="AF35" s="3">
         <v>84900</v>
       </c>
-      <c r="AF35" s="3">
+      <c r="AG35" s="3">
         <v>212100</v>
       </c>
-      <c r="AG35" s="3">
+      <c r="AH35" s="3">
         <v>369000</v>
       </c>
-      <c r="AH35" s="3">
+      <c r="AI35" s="3">
         <v>517600</v>
       </c>
-      <c r="AI35" s="3">
+      <c r="AJ35" s="3">
         <v>88500</v>
       </c>
-      <c r="AJ35" s="3">
+      <c r="AK35" s="3">
         <v>275700</v>
       </c>
     </row>
-    <row r="37" spans="2:36" x14ac:dyDescent="0.2">
+    <row r="37" spans="2:37" x14ac:dyDescent="0.2">
       <c r="B37" s="1" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="38" spans="2:36" x14ac:dyDescent="0.2">
+    <row r="38" spans="2:37" x14ac:dyDescent="0.2">
       <c r="C38" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D38" s="2">
+        <v>45657</v>
+      </c>
+      <c r="E38" s="2">
         <v>45565</v>
       </c>
-      <c r="E38" s="2">
+      <c r="F38" s="2">
         <v>45473</v>
       </c>
-      <c r="F38" s="2">
+      <c r="G38" s="2">
         <v>45382</v>
       </c>
-      <c r="G38" s="2">
+      <c r="H38" s="2">
         <v>45291</v>
       </c>
-      <c r="H38" s="2">
+      <c r="I38" s="2">
         <v>45199</v>
       </c>
-      <c r="I38" s="2">
+      <c r="J38" s="2">
         <v>45107</v>
       </c>
-      <c r="J38" s="2">
+      <c r="K38" s="2">
         <v>45016</v>
       </c>
-      <c r="K38" s="2">
+      <c r="L38" s="2">
         <v>44926</v>
       </c>
-      <c r="L38" s="2">
+      <c r="M38" s="2">
         <v>44834</v>
       </c>
-      <c r="M38" s="2">
+      <c r="N38" s="2">
         <v>44742</v>
       </c>
-      <c r="N38" s="2">
+      <c r="O38" s="2">
         <v>44651</v>
       </c>
-      <c r="O38" s="2">
+      <c r="P38" s="2">
         <v>44561</v>
       </c>
-      <c r="P38" s="2">
+      <c r="Q38" s="2">
         <v>44469</v>
       </c>
-      <c r="Q38" s="2">
+      <c r="R38" s="2">
         <v>44377</v>
       </c>
-      <c r="R38" s="2">
+      <c r="S38" s="2">
         <v>44286</v>
       </c>
-      <c r="S38" s="2">
+      <c r="T38" s="2">
         <v>44196</v>
       </c>
-      <c r="T38" s="2">
+      <c r="U38" s="2">
         <v>44104</v>
       </c>
-      <c r="U38" s="2">
+      <c r="V38" s="2">
         <v>44012</v>
       </c>
-      <c r="V38" s="2">
+      <c r="W38" s="2">
         <v>43921</v>
       </c>
-      <c r="W38" s="2">
+      <c r="X38" s="2">
         <v>43830</v>
       </c>
-      <c r="X38" s="2">
+      <c r="Y38" s="2">
         <v>43738</v>
       </c>
-      <c r="Y38" s="2">
+      <c r="Z38" s="2">
         <v>43646</v>
       </c>
-      <c r="Z38" s="2">
+      <c r="AA38" s="2">
         <v>43555</v>
       </c>
-      <c r="AA38" s="2">
+      <c r="AB38" s="2">
         <v>43465</v>
       </c>
-      <c r="AB38" s="2">
+      <c r="AC38" s="2">
         <v>43373</v>
       </c>
-      <c r="AC38" s="2">
+      <c r="AD38" s="2">
         <v>43281</v>
       </c>
-      <c r="AD38" s="2">
+      <c r="AE38" s="2">
         <v>43190</v>
       </c>
-      <c r="AE38" s="2">
+      <c r="AF38" s="2">
         <v>43100</v>
       </c>
-      <c r="AF38" s="2">
+      <c r="AG38" s="2">
         <v>43008</v>
       </c>
-      <c r="AG38" s="2">
+      <c r="AH38" s="2">
         <v>42916</v>
       </c>
-      <c r="AH38" s="2">
+      <c r="AI38" s="2">
         <v>42825</v>
       </c>
-      <c r="AI38" s="2">
+      <c r="AJ38" s="2">
         <v>42735</v>
       </c>
-      <c r="AJ38" s="2">
+      <c r="AK38" s="2">
         <v>42643</v>
       </c>
     </row>
-    <row r="39" spans="2:36" x14ac:dyDescent="0.2">
+    <row r="39" spans="2:37" x14ac:dyDescent="0.2">
       <c r="C39" s="1" t="s">
         <v>32</v>
       </c>
@@ -3641,8 +3725,9 @@
       <c r="AH39" s="3"/>
       <c r="AI39" s="3"/>
       <c r="AJ39" s="3"/>
+      <c r="AK39" s="3"/>
     </row>
-    <row r="40" spans="2:36" x14ac:dyDescent="0.2">
+    <row r="40" spans="2:37" x14ac:dyDescent="0.2">
       <c r="C40" s="1" t="s">
         <v>33</v>
       </c>
@@ -3679,243 +3764,250 @@
       <c r="AH40" s="3"/>
       <c r="AI40" s="3"/>
       <c r="AJ40" s="3"/>
+      <c r="AK40" s="3"/>
     </row>
-    <row r="41" spans="2:36" x14ac:dyDescent="0.2">
+    <row r="41" spans="2:37" x14ac:dyDescent="0.2">
       <c r="C41" s="1" t="s">
         <v>34</v>
       </c>
       <c r="D41" s="3">
+        <v>9892700</v>
+      </c>
+      <c r="E41" s="3">
         <v>13834100</v>
       </c>
-      <c r="E41" s="3">
+      <c r="F41" s="3">
         <v>8534800</v>
       </c>
-      <c r="F41" s="3">
+      <c r="G41" s="3">
         <v>13129900</v>
       </c>
-      <c r="G41" s="3">
+      <c r="H41" s="3">
         <v>12476200</v>
       </c>
-      <c r="H41" s="3">
+      <c r="I41" s="3">
         <v>7157900</v>
       </c>
-      <c r="I41" s="3">
+      <c r="J41" s="3">
         <v>9809900</v>
       </c>
-      <c r="J41" s="3">
+      <c r="K41" s="3">
         <v>10234100</v>
       </c>
-      <c r="K41" s="3">
+      <c r="L41" s="3">
         <v>25596900</v>
       </c>
-      <c r="L41" s="3">
+      <c r="M41" s="3">
         <v>6507700</v>
       </c>
-      <c r="M41" s="3">
+      <c r="N41" s="3">
         <v>7377100</v>
       </c>
-      <c r="N41" s="3">
+      <c r="O41" s="3">
         <v>9785500</v>
       </c>
-      <c r="O41" s="3">
+      <c r="P41" s="3">
         <v>5555400</v>
       </c>
-      <c r="P41" s="3">
+      <c r="Q41" s="3">
         <v>7893500</v>
       </c>
-      <c r="Q41" s="3">
+      <c r="R41" s="3">
         <v>7303900</v>
       </c>
-      <c r="R41" s="3">
+      <c r="S41" s="3">
         <v>7996900</v>
       </c>
-      <c r="S41" s="3">
+      <c r="T41" s="3">
         <v>6985700</v>
       </c>
-      <c r="T41" s="3">
+      <c r="U41" s="3">
         <v>6452400</v>
       </c>
-      <c r="U41" s="3">
+      <c r="V41" s="3">
         <v>6934700</v>
       </c>
-      <c r="V41" s="3">
+      <c r="W41" s="3">
         <v>7810800</v>
       </c>
-      <c r="W41" s="3">
+      <c r="X41" s="3">
         <v>5327800</v>
       </c>
-      <c r="X41" s="3">
+      <c r="Y41" s="3">
         <v>7069900</v>
       </c>
-      <c r="Y41" s="3">
+      <c r="Z41" s="3">
         <v>5777500</v>
       </c>
-      <c r="Z41" s="3">
+      <c r="AA41" s="3">
         <v>4361000</v>
       </c>
-      <c r="AA41" s="3">
+      <c r="AB41" s="3">
         <v>5329900</v>
       </c>
-      <c r="AB41" s="3">
+      <c r="AC41" s="3">
         <v>4608100</v>
       </c>
-      <c r="AC41" s="3">
+      <c r="AD41" s="3">
         <v>4589200</v>
       </c>
-      <c r="AD41" s="3">
+      <c r="AE41" s="3">
         <v>4387400</v>
       </c>
-      <c r="AE41" s="3">
+      <c r="AF41" s="3">
         <v>5323900</v>
       </c>
-      <c r="AF41" s="3">
+      <c r="AG41" s="3">
         <v>5337600</v>
       </c>
-      <c r="AG41" s="3">
+      <c r="AH41" s="3">
         <v>5780800</v>
       </c>
-      <c r="AH41" s="3">
+      <c r="AI41" s="3">
         <v>6495200</v>
       </c>
-      <c r="AI41" s="3">
+      <c r="AJ41" s="3">
         <v>6385500</v>
       </c>
-      <c r="AJ41" s="3">
+      <c r="AK41" s="3">
         <v>7024600</v>
       </c>
     </row>
-    <row r="42" spans="2:36" x14ac:dyDescent="0.2">
+    <row r="42" spans="2:37" x14ac:dyDescent="0.2">
       <c r="C42" s="1" t="s">
         <v>35</v>
       </c>
       <c r="D42" s="3">
+        <v>22818100</v>
+      </c>
+      <c r="E42" s="3">
         <v>29370000</v>
       </c>
-      <c r="E42" s="3">
+      <c r="F42" s="3">
         <v>19283100</v>
       </c>
-      <c r="F42" s="3">
+      <c r="G42" s="3">
         <v>18486700</v>
       </c>
-      <c r="G42" s="3">
+      <c r="H42" s="3">
         <v>18215800</v>
       </c>
-      <c r="H42" s="3">
+      <c r="I42" s="3">
         <v>17492100</v>
       </c>
-      <c r="I42" s="3">
+      <c r="J42" s="3">
         <v>25108400</v>
       </c>
-      <c r="J42" s="3">
+      <c r="K42" s="3">
         <v>17703400</v>
       </c>
-      <c r="K42" s="3">
+      <c r="L42" s="3">
         <v>41084100</v>
       </c>
-      <c r="L42" s="3">
+      <c r="M42" s="3">
         <v>48087900</v>
       </c>
-      <c r="M42" s="3">
+      <c r="N42" s="3">
         <v>44907700</v>
       </c>
-      <c r="N42" s="3">
+      <c r="O42" s="3">
         <v>44616700</v>
       </c>
-      <c r="O42" s="3">
+      <c r="P42" s="3">
         <v>44083500</v>
       </c>
-      <c r="P42" s="3">
+      <c r="Q42" s="3">
         <v>38326100</v>
       </c>
-      <c r="Q42" s="3">
+      <c r="R42" s="3">
         <v>33800600</v>
       </c>
-      <c r="R42" s="3">
+      <c r="S42" s="3">
         <v>32013900</v>
       </c>
-      <c r="S42" s="3">
+      <c r="T42" s="3">
         <v>39170300</v>
       </c>
-      <c r="T42" s="3">
+      <c r="U42" s="3">
         <v>33273800</v>
       </c>
-      <c r="U42" s="3">
+      <c r="V42" s="3">
         <v>36396600</v>
       </c>
-      <c r="V42" s="3">
+      <c r="W42" s="3">
         <v>38606200</v>
       </c>
-      <c r="W42" s="3">
+      <c r="X42" s="3">
         <v>37680800</v>
       </c>
-      <c r="X42" s="3">
+      <c r="Y42" s="3">
         <v>39232200</v>
       </c>
-      <c r="Y42" s="3">
+      <c r="Z42" s="3">
         <v>36892000</v>
       </c>
-      <c r="Z42" s="3">
+      <c r="AA42" s="3">
         <v>30905300</v>
       </c>
-      <c r="AA42" s="3">
+      <c r="AB42" s="3">
         <v>29776700</v>
       </c>
-      <c r="AB42" s="3">
+      <c r="AC42" s="3">
         <v>20883600</v>
       </c>
-      <c r="AC42" s="3">
+      <c r="AD42" s="3">
         <v>22286700</v>
       </c>
-      <c r="AD42" s="3">
+      <c r="AE42" s="3">
         <v>21840100</v>
       </c>
-      <c r="AE42" s="3">
+      <c r="AF42" s="3">
         <v>20932300</v>
       </c>
-      <c r="AF42" s="3">
+      <c r="AG42" s="3">
         <v>12488600</v>
       </c>
-      <c r="AG42" s="3">
+      <c r="AH42" s="3">
         <v>14955900</v>
       </c>
-      <c r="AH42" s="3">
+      <c r="AI42" s="3">
         <v>13350900</v>
       </c>
-      <c r="AI42" s="3">
+      <c r="AJ42" s="3">
         <v>14204100</v>
       </c>
-      <c r="AJ42" s="3">
+      <c r="AK42" s="3">
         <v>16154100</v>
       </c>
     </row>
-    <row r="43" spans="2:36" x14ac:dyDescent="0.2">
+    <row r="43" spans="2:37" x14ac:dyDescent="0.2">
       <c r="C43" s="1" t="s">
         <v>36</v>
       </c>
       <c r="D43" s="3">
+        <v>6099900</v>
+      </c>
+      <c r="E43" s="3">
         <v>13077600</v>
       </c>
-      <c r="E43" s="3">
+      <c r="F43" s="3">
         <v>9540700</v>
       </c>
-      <c r="F43" s="3">
+      <c r="G43" s="3">
         <v>10078300</v>
       </c>
-      <c r="G43" s="3">
+      <c r="H43" s="3">
         <v>8598900</v>
       </c>
-      <c r="H43" s="3">
+      <c r="I43" s="3">
         <v>9843900</v>
       </c>
-      <c r="I43" s="3">
+      <c r="J43" s="3">
         <v>11594400</v>
       </c>
-      <c r="J43" s="3">
+      <c r="K43" s="3">
         <v>10468300</v>
       </c>
-      <c r="K43" s="3">
-        <v>0</v>
-      </c>
       <c r="L43" s="3">
         <v>0</v>
       </c>
@@ -3991,8 +4083,11 @@
       <c r="AJ43" s="3">
         <v>0</v>
       </c>
+      <c r="AK43" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="44" spans="2:36" x14ac:dyDescent="0.2">
+    <row r="44" spans="2:37" x14ac:dyDescent="0.2">
       <c r="C44" s="1" t="s">
         <v>37</v>
       </c>
@@ -4017,8 +4112,8 @@
       <c r="J44" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="K44" s="3">
-        <v>0</v>
+      <c r="K44" s="3" t="s">
+        <v>5</v>
       </c>
       <c r="L44" s="3">
         <v>0</v>
@@ -4095,35 +4190,38 @@
       <c r="AJ44" s="3">
         <v>0</v>
       </c>
+      <c r="AK44" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="45" spans="2:36" x14ac:dyDescent="0.2">
+    <row r="45" spans="2:37" x14ac:dyDescent="0.2">
       <c r="C45" s="1" t="s">
         <v>38</v>
       </c>
       <c r="D45" s="3">
+        <v>3417100</v>
+      </c>
+      <c r="E45" s="3">
         <v>2191600</v>
       </c>
-      <c r="E45" s="3">
+      <c r="F45" s="3">
         <v>2546100</v>
       </c>
-      <c r="F45" s="3">
+      <c r="G45" s="3">
         <v>2248400</v>
       </c>
-      <c r="G45" s="3">
+      <c r="H45" s="3">
         <v>3229200</v>
       </c>
-      <c r="H45" s="3">
+      <c r="I45" s="3">
         <v>2254000</v>
       </c>
-      <c r="I45" s="3">
+      <c r="J45" s="3">
         <v>2036900</v>
       </c>
-      <c r="J45" s="3">
+      <c r="K45" s="3">
         <v>1992400</v>
       </c>
-      <c r="K45" s="3">
-        <v>0</v>
-      </c>
       <c r="L45" s="3">
         <v>0</v>
       </c>
@@ -4199,35 +4297,38 @@
       <c r="AJ45" s="3">
         <v>0</v>
       </c>
+      <c r="AK45" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="46" spans="2:36" x14ac:dyDescent="0.2">
+    <row r="46" spans="2:37" x14ac:dyDescent="0.2">
       <c r="C46" s="1" t="s">
         <v>39</v>
       </c>
       <c r="D46" s="3">
+        <v>51046100</v>
+      </c>
+      <c r="E46" s="3">
         <v>70438600</v>
       </c>
-      <c r="E46" s="3">
+      <c r="F46" s="3">
         <v>50125600</v>
       </c>
-      <c r="F46" s="3">
+      <c r="G46" s="3">
         <v>54875900</v>
       </c>
-      <c r="G46" s="3">
+      <c r="H46" s="3">
         <v>53874000</v>
       </c>
-      <c r="H46" s="3">
+      <c r="I46" s="3">
         <v>49079800</v>
       </c>
-      <c r="I46" s="3">
+      <c r="J46" s="3">
         <v>55527700</v>
       </c>
-      <c r="J46" s="3">
+      <c r="K46" s="3">
         <v>55109700</v>
       </c>
-      <c r="K46" s="3">
-        <v>0</v>
-      </c>
       <c r="L46" s="3">
         <v>0</v>
       </c>
@@ -4303,320 +4404,332 @@
       <c r="AJ46" s="3">
         <v>0</v>
       </c>
+      <c r="AK46" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="47" spans="2:36" x14ac:dyDescent="0.2">
+    <row r="47" spans="2:37" x14ac:dyDescent="0.2">
       <c r="C47" s="1" t="s">
         <v>40</v>
       </c>
       <c r="D47" s="3">
+        <v>29734600</v>
+      </c>
+      <c r="E47" s="3">
         <v>43909700</v>
       </c>
-      <c r="E47" s="3">
+      <c r="F47" s="3">
         <v>45684200</v>
       </c>
-      <c r="F47" s="3">
+      <c r="G47" s="3">
         <v>45083200</v>
       </c>
-      <c r="G47" s="3">
-        <v>33116700</v>
-      </c>
       <c r="H47" s="3">
+        <v>33573300</v>
+      </c>
+      <c r="I47" s="3">
         <v>46697400</v>
       </c>
-      <c r="I47" s="3">
+      <c r="J47" s="3">
         <v>47231400</v>
       </c>
-      <c r="J47" s="3">
+      <c r="K47" s="3">
         <v>47653400</v>
       </c>
-      <c r="K47" s="3">
+      <c r="L47" s="3">
         <v>979200</v>
       </c>
-      <c r="L47" s="3">
+      <c r="M47" s="3">
         <v>976800</v>
       </c>
-      <c r="M47" s="3">
+      <c r="N47" s="3">
         <v>1035000</v>
       </c>
-      <c r="N47" s="3">
+      <c r="O47" s="3">
         <v>1011300</v>
       </c>
-      <c r="O47" s="3">
+      <c r="P47" s="3">
         <v>1001400</v>
       </c>
-      <c r="P47" s="3">
+      <c r="Q47" s="3">
         <v>896000</v>
       </c>
-      <c r="Q47" s="3">
+      <c r="R47" s="3">
         <v>881500</v>
       </c>
-      <c r="R47" s="3">
+      <c r="S47" s="3">
         <v>775800</v>
       </c>
-      <c r="S47" s="3">
+      <c r="T47" s="3">
         <v>735000</v>
       </c>
-      <c r="T47" s="3">
+      <c r="U47" s="3">
         <v>829200</v>
       </c>
-      <c r="U47" s="3">
+      <c r="V47" s="3">
         <v>714700</v>
       </c>
-      <c r="V47" s="3">
+      <c r="W47" s="3">
         <v>674300</v>
       </c>
-      <c r="W47" s="3">
+      <c r="X47" s="3">
         <v>685400</v>
       </c>
-      <c r="X47" s="3">
+      <c r="Y47" s="3">
         <v>322100</v>
       </c>
-      <c r="Y47" s="3">
+      <c r="Z47" s="3">
         <v>311500</v>
       </c>
-      <c r="Z47" s="3">
+      <c r="AA47" s="3">
         <v>316200</v>
       </c>
-      <c r="AA47" s="3">
+      <c r="AB47" s="3">
         <v>303600</v>
       </c>
-      <c r="AB47" s="3">
+      <c r="AC47" s="3">
         <v>276700</v>
       </c>
-      <c r="AC47" s="3">
+      <c r="AD47" s="3">
         <v>346900</v>
       </c>
-      <c r="AD47" s="3">
+      <c r="AE47" s="3">
         <v>348200</v>
       </c>
-      <c r="AE47" s="3">
+      <c r="AF47" s="3">
         <v>367000</v>
       </c>
-      <c r="AF47" s="3">
+      <c r="AG47" s="3">
         <v>490900</v>
       </c>
-      <c r="AG47" s="3">
+      <c r="AH47" s="3">
         <v>326300</v>
       </c>
-      <c r="AH47" s="3">
+      <c r="AI47" s="3">
         <v>351100</v>
       </c>
-      <c r="AI47" s="3">
+      <c r="AJ47" s="3">
         <v>395100</v>
       </c>
-      <c r="AJ47" s="3">
+      <c r="AK47" s="3">
         <v>377600</v>
       </c>
     </row>
-    <row r="48" spans="2:36" x14ac:dyDescent="0.2">
+    <row r="48" spans="2:37" x14ac:dyDescent="0.2">
       <c r="C48" s="1" t="s">
         <v>41</v>
       </c>
       <c r="D48" s="3">
+        <v>4937200</v>
+      </c>
+      <c r="E48" s="3">
         <v>5522800</v>
       </c>
-      <c r="E48" s="3">
+      <c r="F48" s="3">
         <v>5103100</v>
       </c>
-      <c r="F48" s="3">
+      <c r="G48" s="3">
         <v>4908300</v>
       </c>
-      <c r="G48" s="3">
+      <c r="H48" s="3">
         <v>4983700</v>
       </c>
-      <c r="H48" s="3">
+      <c r="I48" s="3">
         <v>4486300</v>
       </c>
-      <c r="I48" s="3">
+      <c r="J48" s="3">
         <v>4434900</v>
       </c>
-      <c r="J48" s="3">
+      <c r="K48" s="3">
         <v>4401200</v>
       </c>
-      <c r="K48" s="3">
+      <c r="L48" s="3">
         <v>2648000</v>
       </c>
-      <c r="L48" s="3">
+      <c r="M48" s="3">
         <v>2590300</v>
       </c>
-      <c r="M48" s="3">
+      <c r="N48" s="3">
         <v>2689200</v>
       </c>
-      <c r="N48" s="3">
+      <c r="O48" s="3">
         <v>2729900</v>
       </c>
-      <c r="O48" s="3">
+      <c r="P48" s="3">
         <v>2673200</v>
       </c>
-      <c r="P48" s="3">
+      <c r="Q48" s="3">
         <v>2701000</v>
       </c>
-      <c r="Q48" s="3">
+      <c r="R48" s="3">
         <v>2682600</v>
       </c>
-      <c r="R48" s="3">
+      <c r="S48" s="3">
         <v>2700600</v>
       </c>
-      <c r="S48" s="3">
+      <c r="T48" s="3">
         <v>2719200</v>
       </c>
-      <c r="T48" s="3">
+      <c r="U48" s="3">
         <v>2764300</v>
       </c>
-      <c r="U48" s="3">
+      <c r="V48" s="3">
         <v>2790300</v>
       </c>
-      <c r="V48" s="3">
+      <c r="W48" s="3">
         <v>2961700</v>
       </c>
-      <c r="W48" s="3">
+      <c r="X48" s="3">
         <v>3098200</v>
       </c>
-      <c r="X48" s="3">
+      <c r="Y48" s="3">
         <v>3089800</v>
       </c>
-      <c r="Y48" s="3">
+      <c r="Z48" s="3">
         <v>3058200</v>
       </c>
-      <c r="Z48" s="3">
+      <c r="AA48" s="3">
         <v>3080600</v>
       </c>
-      <c r="AA48" s="3">
+      <c r="AB48" s="3">
         <v>2368100</v>
       </c>
-      <c r="AB48" s="3">
+      <c r="AC48" s="3">
         <v>2284800</v>
       </c>
-      <c r="AC48" s="3">
+      <c r="AD48" s="3">
         <v>2378800</v>
       </c>
-      <c r="AD48" s="3">
+      <c r="AE48" s="3">
         <v>2384000</v>
       </c>
-      <c r="AE48" s="3">
+      <c r="AF48" s="3">
         <v>2507000</v>
       </c>
-      <c r="AF48" s="3">
+      <c r="AG48" s="3">
         <v>2509800</v>
       </c>
-      <c r="AG48" s="3">
+      <c r="AH48" s="3">
         <v>2480800</v>
       </c>
-      <c r="AH48" s="3">
+      <c r="AI48" s="3">
         <v>2470200</v>
       </c>
-      <c r="AI48" s="3">
+      <c r="AJ48" s="3">
         <v>2534900</v>
       </c>
-      <c r="AJ48" s="3">
+      <c r="AK48" s="3">
         <v>2525400</v>
       </c>
     </row>
-    <row r="49" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="49" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C49" s="1" t="s">
         <v>42</v>
       </c>
       <c r="D49" s="3">
+        <v>552200</v>
+      </c>
+      <c r="E49" s="3">
         <v>621800</v>
       </c>
-      <c r="E49" s="3">
+      <c r="F49" s="3">
         <v>557800</v>
       </c>
-      <c r="F49" s="3">
+      <c r="G49" s="3">
         <v>562600</v>
       </c>
-      <c r="G49" s="3">
+      <c r="H49" s="3">
         <v>582000</v>
       </c>
-      <c r="H49" s="3">
+      <c r="I49" s="3">
         <v>568100</v>
       </c>
-      <c r="I49" s="3">
+      <c r="J49" s="3">
         <v>586300</v>
       </c>
-      <c r="J49" s="3">
+      <c r="K49" s="3">
         <v>573300</v>
       </c>
-      <c r="K49" s="3">
+      <c r="L49" s="3">
         <v>636800</v>
       </c>
-      <c r="L49" s="3">
+      <c r="M49" s="3">
         <v>639200</v>
       </c>
-      <c r="M49" s="3">
+      <c r="N49" s="3">
         <v>596500</v>
       </c>
-      <c r="N49" s="3">
+      <c r="O49" s="3">
         <v>608700</v>
       </c>
-      <c r="O49" s="3">
+      <c r="P49" s="3">
         <v>589000</v>
       </c>
-      <c r="P49" s="3">
+      <c r="Q49" s="3">
         <v>586400</v>
       </c>
-      <c r="Q49" s="3">
+      <c r="R49" s="3">
         <v>581700</v>
       </c>
-      <c r="R49" s="3">
+      <c r="S49" s="3">
         <v>582600</v>
       </c>
-      <c r="S49" s="3">
+      <c r="T49" s="3">
         <v>586100</v>
       </c>
-      <c r="T49" s="3">
+      <c r="U49" s="3">
         <v>615800</v>
       </c>
-      <c r="U49" s="3">
+      <c r="V49" s="3">
         <v>631700</v>
       </c>
-      <c r="V49" s="3">
+      <c r="W49" s="3">
         <v>668000</v>
       </c>
-      <c r="W49" s="3">
+      <c r="X49" s="3">
         <v>717500</v>
       </c>
-      <c r="X49" s="3">
+      <c r="Y49" s="3">
         <v>590200</v>
       </c>
-      <c r="Y49" s="3">
+      <c r="Z49" s="3">
         <v>565800</v>
       </c>
-      <c r="Z49" s="3">
+      <c r="AA49" s="3">
         <v>588900</v>
       </c>
-      <c r="AA49" s="3">
+      <c r="AB49" s="3">
         <v>493300</v>
       </c>
-      <c r="AB49" s="3">
+      <c r="AC49" s="3">
         <v>502400</v>
       </c>
-      <c r="AC49" s="3">
+      <c r="AD49" s="3">
         <v>549000</v>
       </c>
-      <c r="AD49" s="3">
+      <c r="AE49" s="3">
         <v>452700</v>
       </c>
-      <c r="AE49" s="3">
+      <c r="AF49" s="3">
         <v>456400</v>
       </c>
-      <c r="AF49" s="3">
+      <c r="AG49" s="3">
         <v>461900</v>
       </c>
-      <c r="AG49" s="3">
+      <c r="AH49" s="3">
         <v>446100</v>
       </c>
-      <c r="AH49" s="3">
+      <c r="AI49" s="3">
         <v>415100</v>
       </c>
-      <c r="AI49" s="3">
+      <c r="AJ49" s="3">
         <v>435400</v>
       </c>
-      <c r="AJ49" s="3">
+      <c r="AK49" s="3">
         <v>376700</v>
       </c>
     </row>
-    <row r="50" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="50" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C50" s="1" t="s">
         <v>43</v>
       </c>
@@ -4719,8 +4832,11 @@
       <c r="AJ50" s="3">
         <v>0</v>
       </c>
+      <c r="AK50" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="51" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="51" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C51" s="1" t="s">
         <v>44</v>
       </c>
@@ -4823,112 +4939,118 @@
       <c r="AJ51" s="3">
         <v>0</v>
       </c>
+      <c r="AK51" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="52" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="52" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C52" s="1" t="s">
         <v>45</v>
       </c>
       <c r="D52" s="3">
+        <v>15193100</v>
+      </c>
+      <c r="E52" s="3">
         <v>1117800</v>
       </c>
-      <c r="E52" s="3">
+      <c r="F52" s="3">
         <v>1097200</v>
       </c>
-      <c r="F52" s="3">
+      <c r="G52" s="3">
         <v>1375500</v>
       </c>
-      <c r="G52" s="3">
-        <v>17293300</v>
-      </c>
       <c r="H52" s="3">
+        <v>16836600</v>
+      </c>
+      <c r="I52" s="3">
         <v>1488400</v>
       </c>
-      <c r="I52" s="3">
+      <c r="J52" s="3">
         <v>1186200</v>
       </c>
-      <c r="J52" s="3">
+      <c r="K52" s="3">
         <v>1174600</v>
       </c>
-      <c r="K52" s="3">
+      <c r="L52" s="3">
         <v>331800</v>
       </c>
-      <c r="L52" s="3">
+      <c r="M52" s="3">
         <v>284500</v>
       </c>
-      <c r="M52" s="3">
+      <c r="N52" s="3">
         <v>166400</v>
       </c>
-      <c r="N52" s="3">
+      <c r="O52" s="3">
         <v>58400</v>
       </c>
-      <c r="O52" s="3">
+      <c r="P52" s="3">
         <v>59100</v>
       </c>
-      <c r="P52" s="3">
+      <c r="Q52" s="3">
         <v>41100</v>
       </c>
-      <c r="Q52" s="3">
+      <c r="R52" s="3">
         <v>56000</v>
       </c>
-      <c r="R52" s="3">
+      <c r="S52" s="3">
         <v>73700</v>
       </c>
-      <c r="S52" s="3">
+      <c r="T52" s="3">
         <v>82700</v>
       </c>
-      <c r="T52" s="3">
+      <c r="U52" s="3">
         <v>74500</v>
       </c>
-      <c r="U52" s="3">
+      <c r="V52" s="3">
         <v>37800</v>
       </c>
-      <c r="V52" s="3">
+      <c r="W52" s="3">
         <v>38200</v>
       </c>
-      <c r="W52" s="3">
+      <c r="X52" s="3">
         <v>44800</v>
       </c>
-      <c r="X52" s="3">
+      <c r="Y52" s="3">
         <v>82300</v>
       </c>
-      <c r="Y52" s="3">
+      <c r="Z52" s="3">
         <v>69500</v>
       </c>
-      <c r="Z52" s="3">
+      <c r="AA52" s="3">
         <v>68200</v>
       </c>
-      <c r="AA52" s="3">
+      <c r="AB52" s="3">
         <v>120400</v>
       </c>
-      <c r="AB52" s="3">
+      <c r="AC52" s="3">
         <v>36800</v>
       </c>
-      <c r="AC52" s="3">
+      <c r="AD52" s="3">
         <v>91100</v>
       </c>
-      <c r="AD52" s="3">
+      <c r="AE52" s="3">
         <v>177600</v>
       </c>
-      <c r="AE52" s="3">
+      <c r="AF52" s="3">
         <v>289300</v>
       </c>
-      <c r="AF52" s="3">
+      <c r="AG52" s="3">
         <v>234800</v>
       </c>
-      <c r="AG52" s="3">
+      <c r="AH52" s="3">
         <v>221100</v>
       </c>
-      <c r="AH52" s="3">
+      <c r="AI52" s="3">
         <v>262700</v>
       </c>
-      <c r="AI52" s="3">
+      <c r="AJ52" s="3">
         <v>274800</v>
       </c>
-      <c r="AJ52" s="3">
+      <c r="AK52" s="3">
         <v>143800</v>
       </c>
     </row>
-    <row r="53" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="53" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C53" s="1" t="s">
         <v>46</v>
       </c>
@@ -5031,112 +5153,118 @@
       <c r="AJ53" s="3">
         <v>0</v>
       </c>
+      <c r="AK53" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="54" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="54" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C54" s="1" t="s">
         <v>47</v>
       </c>
       <c r="D54" s="3">
+        <v>355900000</v>
+      </c>
+      <c r="E54" s="3">
         <v>413964600</v>
       </c>
-      <c r="E54" s="3">
+      <c r="F54" s="3">
         <v>369217100</v>
       </c>
-      <c r="F54" s="3">
+      <c r="G54" s="3">
         <v>375587700</v>
       </c>
-      <c r="G54" s="3">
+      <c r="H54" s="3">
         <v>384037900</v>
       </c>
-      <c r="H54" s="3">
+      <c r="I54" s="3">
         <v>360962600</v>
       </c>
-      <c r="I54" s="3">
+      <c r="J54" s="3">
         <v>366653200</v>
       </c>
-      <c r="J54" s="3">
+      <c r="K54" s="3">
         <v>366661700</v>
       </c>
-      <c r="K54" s="3">
+      <c r="L54" s="3">
         <v>360355800</v>
       </c>
-      <c r="L54" s="3">
+      <c r="M54" s="3">
         <v>366510300</v>
       </c>
-      <c r="M54" s="3">
+      <c r="N54" s="3">
         <v>368558700</v>
       </c>
-      <c r="N54" s="3">
+      <c r="O54" s="3">
         <v>358592300</v>
       </c>
-      <c r="O54" s="3">
+      <c r="P54" s="3">
         <v>335387900</v>
       </c>
-      <c r="P54" s="3">
+      <c r="Q54" s="3">
         <v>328638700</v>
       </c>
-      <c r="Q54" s="3">
+      <c r="R54" s="3">
         <v>315953000</v>
       </c>
-      <c r="R54" s="3">
+      <c r="S54" s="3">
         <v>307917200</v>
       </c>
-      <c r="S54" s="3">
+      <c r="T54" s="3">
         <v>295320000</v>
       </c>
-      <c r="T54" s="3">
+      <c r="U54" s="3">
         <v>293246000</v>
       </c>
-      <c r="U54" s="3">
+      <c r="V54" s="3">
         <v>292659600</v>
       </c>
-      <c r="V54" s="3">
+      <c r="W54" s="3">
         <v>306353500</v>
       </c>
-      <c r="W54" s="3">
+      <c r="X54" s="3">
         <v>307683600</v>
       </c>
-      <c r="X54" s="3">
+      <c r="Y54" s="3">
         <v>314996600</v>
       </c>
-      <c r="Y54" s="3">
+      <c r="Z54" s="3">
         <v>316273500</v>
       </c>
-      <c r="Z54" s="3">
+      <c r="AA54" s="3">
         <v>314085600</v>
       </c>
-      <c r="AA54" s="3">
+      <c r="AB54" s="3">
         <v>285975600</v>
       </c>
-      <c r="AB54" s="3">
+      <c r="AC54" s="3">
         <v>267139300</v>
       </c>
-      <c r="AC54" s="3">
+      <c r="AD54" s="3">
         <v>274311500</v>
       </c>
-      <c r="AD54" s="3">
+      <c r="AE54" s="3">
         <v>273668600</v>
       </c>
-      <c r="AE54" s="3">
+      <c r="AF54" s="3">
         <v>278340000</v>
       </c>
-      <c r="AF54" s="3">
+      <c r="AG54" s="3">
         <v>279730100</v>
       </c>
-      <c r="AG54" s="3">
+      <c r="AH54" s="3">
         <v>278137400</v>
       </c>
-      <c r="AH54" s="3">
+      <c r="AI54" s="3">
         <v>273600800</v>
       </c>
-      <c r="AI54" s="3">
+      <c r="AJ54" s="3">
         <v>279614500</v>
       </c>
-      <c r="AJ54" s="3">
+      <c r="AK54" s="3">
         <v>281548700</v>
       </c>
     </row>
-    <row r="55" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="55" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C55" s="1" t="s">
         <v>48</v>
       </c>
@@ -5173,8 +5301,9 @@
       <c r="AH55" s="3"/>
       <c r="AI55" s="3"/>
       <c r="AJ55" s="3"/>
+      <c r="AK55" s="3"/>
     </row>
-    <row r="56" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="56" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C56" s="1" t="s">
         <v>49</v>
       </c>
@@ -5211,139 +5340,143 @@
       <c r="AH56" s="3"/>
       <c r="AI56" s="3"/>
       <c r="AJ56" s="3"/>
+      <c r="AK56" s="3"/>
     </row>
-    <row r="57" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="57" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C57" s="1" t="s">
         <v>50</v>
       </c>
       <c r="D57" s="3">
+        <v>253583100</v>
+      </c>
+      <c r="E57" s="3">
         <v>303683400</v>
       </c>
-      <c r="E57" s="3">
+      <c r="F57" s="3">
         <v>269353200</v>
       </c>
-      <c r="F57" s="3">
+      <c r="G57" s="3">
         <v>273669100</v>
       </c>
-      <c r="G57" s="3">
+      <c r="H57" s="3">
         <v>283746600</v>
       </c>
-      <c r="H57" s="3">
+      <c r="I57" s="3">
         <v>257925300</v>
       </c>
-      <c r="I57" s="3">
+      <c r="J57" s="3">
         <v>263215600</v>
       </c>
-      <c r="J57" s="3">
+      <c r="K57" s="3">
         <v>259046400</v>
       </c>
-      <c r="K57" s="3">
+      <c r="L57" s="3">
         <v>8592200</v>
       </c>
-      <c r="L57" s="3">
+      <c r="M57" s="3">
         <v>12736100</v>
       </c>
-      <c r="M57" s="3">
+      <c r="N57" s="3">
         <v>12538100</v>
       </c>
-      <c r="N57" s="3">
+      <c r="O57" s="3">
         <v>11104000</v>
       </c>
-      <c r="O57" s="3">
+      <c r="P57" s="3">
         <v>10844700</v>
       </c>
-      <c r="P57" s="3">
+      <c r="Q57" s="3">
         <v>7957500</v>
       </c>
-      <c r="Q57" s="3">
+      <c r="R57" s="3">
         <v>9468900</v>
       </c>
-      <c r="R57" s="3">
+      <c r="S57" s="3">
         <v>7995800</v>
       </c>
-      <c r="S57" s="3">
+      <c r="T57" s="3">
         <v>3698600</v>
       </c>
-      <c r="T57" s="3">
+      <c r="U57" s="3">
         <v>7530800</v>
       </c>
-      <c r="U57" s="3">
+      <c r="V57" s="3">
         <v>8467000</v>
       </c>
-      <c r="V57" s="3">
+      <c r="W57" s="3">
         <v>9538600</v>
       </c>
-      <c r="W57" s="3">
+      <c r="X57" s="3">
         <v>7264700</v>
       </c>
-      <c r="X57" s="3">
+      <c r="Y57" s="3">
         <v>13339700</v>
       </c>
-      <c r="Y57" s="3">
+      <c r="Z57" s="3">
         <v>15138200</v>
       </c>
-      <c r="Z57" s="3">
+      <c r="AA57" s="3">
         <v>14778600</v>
       </c>
-      <c r="AA57" s="3">
+      <c r="AB57" s="3">
         <v>10988500</v>
       </c>
-      <c r="AB57" s="3">
+      <c r="AC57" s="3">
         <v>12068900</v>
       </c>
-      <c r="AC57" s="3">
+      <c r="AD57" s="3">
         <v>11638400</v>
       </c>
-      <c r="AD57" s="3">
+      <c r="AE57" s="3">
         <v>12317300</v>
       </c>
-      <c r="AE57" s="3">
+      <c r="AF57" s="3">
         <v>5801500</v>
       </c>
-      <c r="AF57" s="3">
+      <c r="AG57" s="3">
         <v>13814400</v>
       </c>
-      <c r="AG57" s="3">
+      <c r="AH57" s="3">
         <v>14756900</v>
       </c>
-      <c r="AH57" s="3">
+      <c r="AI57" s="3">
         <v>10823000</v>
       </c>
-      <c r="AI57" s="3">
+      <c r="AJ57" s="3">
         <v>13329400</v>
       </c>
-      <c r="AJ57" s="3">
+      <c r="AK57" s="3">
         <v>15356600</v>
       </c>
     </row>
-    <row r="58" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="58" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C58" s="1" t="s">
         <v>51</v>
       </c>
       <c r="D58" s="3">
+        <v>12014400</v>
+      </c>
+      <c r="E58" s="3">
         <v>10388900</v>
       </c>
-      <c r="E58" s="3">
+      <c r="F58" s="3">
         <v>10701400</v>
       </c>
-      <c r="F58" s="3">
+      <c r="G58" s="3">
         <v>11337600</v>
       </c>
-      <c r="G58" s="3">
+      <c r="H58" s="3">
         <v>9863100</v>
       </c>
-      <c r="H58" s="3">
+      <c r="I58" s="3">
         <v>11103300</v>
       </c>
-      <c r="I58" s="3">
+      <c r="J58" s="3">
         <v>10559700</v>
       </c>
-      <c r="J58" s="3">
+      <c r="K58" s="3">
         <v>10550500</v>
       </c>
-      <c r="K58" s="3">
-        <v>0</v>
-      </c>
       <c r="L58" s="3">
         <v>0</v>
       </c>
@@ -5419,139 +5552,145 @@
       <c r="AJ58" s="3">
         <v>0</v>
       </c>
+      <c r="AK58" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="59" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="59" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C59" s="1" t="s">
         <v>52</v>
       </c>
       <c r="D59" s="3">
+        <v>747300</v>
+      </c>
+      <c r="E59" s="3">
         <v>917100</v>
       </c>
-      <c r="E59" s="3">
+      <c r="F59" s="3">
         <v>585700</v>
       </c>
-      <c r="F59" s="3">
+      <c r="G59" s="3">
         <v>748600</v>
       </c>
-      <c r="G59" s="3">
+      <c r="H59" s="3">
         <v>795100</v>
       </c>
-      <c r="H59" s="3">
+      <c r="I59" s="3">
         <v>581800</v>
       </c>
-      <c r="I59" s="3">
+      <c r="J59" s="3">
         <v>593500</v>
       </c>
-      <c r="J59" s="3">
+      <c r="K59" s="3">
         <v>1203800</v>
       </c>
-      <c r="K59" s="3">
+      <c r="L59" s="3">
         <v>3047200</v>
       </c>
-      <c r="L59" s="3">
+      <c r="M59" s="3">
         <v>2229700</v>
       </c>
-      <c r="M59" s="3">
+      <c r="N59" s="3">
         <v>1968300</v>
       </c>
-      <c r="N59" s="3">
+      <c r="O59" s="3">
         <v>2093100</v>
       </c>
-      <c r="O59" s="3">
+      <c r="P59" s="3">
         <v>1991300</v>
       </c>
-      <c r="P59" s="3">
+      <c r="Q59" s="3">
         <v>1538600</v>
       </c>
-      <c r="Q59" s="3">
+      <c r="R59" s="3">
         <v>1446500</v>
       </c>
-      <c r="R59" s="3">
+      <c r="S59" s="3">
         <v>1600800</v>
       </c>
-      <c r="S59" s="3">
+      <c r="T59" s="3">
         <v>1790900</v>
       </c>
-      <c r="T59" s="3">
+      <c r="U59" s="3">
         <v>1521700</v>
       </c>
-      <c r="U59" s="3">
+      <c r="V59" s="3">
         <v>1545300</v>
       </c>
-      <c r="V59" s="3">
+      <c r="W59" s="3">
         <v>1892000</v>
       </c>
-      <c r="W59" s="3">
+      <c r="X59" s="3">
         <v>2294100</v>
       </c>
-      <c r="X59" s="3">
+      <c r="Y59" s="3">
         <v>2199800</v>
       </c>
-      <c r="Y59" s="3">
+      <c r="Z59" s="3">
         <v>2064700</v>
       </c>
-      <c r="Z59" s="3">
+      <c r="AA59" s="3">
         <v>2149400</v>
       </c>
-      <c r="AA59" s="3">
+      <c r="AB59" s="3">
         <v>1989900</v>
       </c>
-      <c r="AB59" s="3">
+      <c r="AC59" s="3">
         <v>1798500</v>
       </c>
-      <c r="AC59" s="3">
+      <c r="AD59" s="3">
         <v>1649500</v>
       </c>
-      <c r="AD59" s="3">
+      <c r="AE59" s="3">
         <v>1642100</v>
       </c>
-      <c r="AE59" s="3">
+      <c r="AF59" s="3">
         <v>2008600</v>
       </c>
-      <c r="AF59" s="3">
+      <c r="AG59" s="3">
         <v>2057400</v>
       </c>
-      <c r="AG59" s="3">
+      <c r="AH59" s="3">
         <v>1681400</v>
       </c>
-      <c r="AH59" s="3">
+      <c r="AI59" s="3">
         <v>1880000</v>
       </c>
-      <c r="AI59" s="3">
+      <c r="AJ59" s="3">
         <v>2004400</v>
       </c>
-      <c r="AJ59" s="3">
+      <c r="AK59" s="3">
         <v>1813400</v>
       </c>
     </row>
-    <row r="60" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="60" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C60" s="1" t="s">
         <v>53</v>
       </c>
       <c r="D60" s="3">
+        <v>269522700</v>
+      </c>
+      <c r="E60" s="3">
         <v>318811800</v>
       </c>
-      <c r="E60" s="3">
+      <c r="F60" s="3">
         <v>283969800</v>
       </c>
-      <c r="F60" s="3">
+      <c r="G60" s="3">
         <v>288965400</v>
       </c>
-      <c r="G60" s="3">
+      <c r="H60" s="3">
         <v>297751000</v>
       </c>
-      <c r="H60" s="3">
+      <c r="I60" s="3">
         <v>272946300</v>
       </c>
-      <c r="I60" s="3">
+      <c r="J60" s="3">
         <v>277365200</v>
       </c>
-      <c r="J60" s="3">
+      <c r="K60" s="3">
         <v>273486900</v>
       </c>
-      <c r="K60" s="3">
-        <v>0</v>
-      </c>
       <c r="L60" s="3">
         <v>0</v>
       </c>
@@ -5627,216 +5766,225 @@
       <c r="AJ60" s="3">
         <v>0</v>
       </c>
+      <c r="AK60" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="61" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="61" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C61" s="1" t="s">
         <v>54</v>
       </c>
       <c r="D61" s="3">
+        <v>52292900</v>
+      </c>
+      <c r="E61" s="3">
         <v>57884900</v>
       </c>
-      <c r="E61" s="3">
+      <c r="F61" s="3">
         <v>51737100</v>
       </c>
-      <c r="F61" s="3">
+      <c r="G61" s="3">
         <v>52671400</v>
       </c>
-      <c r="G61" s="3">
+      <c r="H61" s="3">
         <v>54929200</v>
       </c>
-      <c r="H61" s="3">
+      <c r="I61" s="3">
         <v>53360000</v>
       </c>
-      <c r="I61" s="3">
+      <c r="J61" s="3">
         <v>54858600</v>
       </c>
-      <c r="J61" s="3">
+      <c r="K61" s="3">
         <v>55629400</v>
       </c>
-      <c r="K61" s="3">
+      <c r="L61" s="3">
         <v>52670100</v>
       </c>
-      <c r="L61" s="3">
+      <c r="M61" s="3">
         <v>58817800</v>
       </c>
-      <c r="M61" s="3">
+      <c r="N61" s="3">
         <v>58413400</v>
       </c>
-      <c r="N61" s="3">
+      <c r="O61" s="3">
         <v>54512100</v>
       </c>
-      <c r="O61" s="3">
+      <c r="P61" s="3">
         <v>51506600</v>
       </c>
-      <c r="P61" s="3">
+      <c r="Q61" s="3">
         <v>49335300</v>
       </c>
-      <c r="Q61" s="3">
+      <c r="R61" s="3">
         <v>46999300</v>
       </c>
-      <c r="R61" s="3">
+      <c r="S61" s="3">
         <v>43329900</v>
       </c>
-      <c r="S61" s="3">
+      <c r="T61" s="3">
         <v>42586400</v>
       </c>
-      <c r="T61" s="3">
+      <c r="U61" s="3">
         <v>38230600</v>
       </c>
-      <c r="U61" s="3">
+      <c r="V61" s="3">
         <v>39214800</v>
       </c>
-      <c r="V61" s="3">
+      <c r="W61" s="3">
         <v>43080800</v>
       </c>
-      <c r="W61" s="3">
+      <c r="X61" s="3">
         <v>42129500</v>
       </c>
-      <c r="X61" s="3">
+      <c r="Y61" s="3">
         <v>44185000</v>
       </c>
-      <c r="Y61" s="3">
+      <c r="Z61" s="3">
         <v>43142100</v>
       </c>
-      <c r="Z61" s="3">
+      <c r="AA61" s="3">
         <v>40307800</v>
       </c>
-      <c r="AA61" s="3">
+      <c r="AB61" s="3">
         <v>36868700</v>
       </c>
-      <c r="AB61" s="3">
+      <c r="AC61" s="3">
         <v>34955700</v>
       </c>
-      <c r="AC61" s="3">
+      <c r="AD61" s="3">
         <v>35115500</v>
       </c>
-      <c r="AD61" s="3">
+      <c r="AE61" s="3">
         <v>34009900</v>
       </c>
-      <c r="AE61" s="3">
+      <c r="AF61" s="3">
         <v>36941800</v>
       </c>
-      <c r="AF61" s="3">
+      <c r="AG61" s="3">
         <v>37408900</v>
       </c>
-      <c r="AG61" s="3">
+      <c r="AH61" s="3">
         <v>35000000</v>
       </c>
-      <c r="AH61" s="3">
+      <c r="AI61" s="3">
         <v>33280700</v>
       </c>
-      <c r="AI61" s="3">
+      <c r="AJ61" s="3">
         <v>34538700</v>
       </c>
-      <c r="AJ61" s="3">
+      <c r="AK61" s="3">
         <v>33926000</v>
       </c>
     </row>
-    <row r="62" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="62" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C62" s="1" t="s">
         <v>55</v>
       </c>
       <c r="D62" s="3">
+        <v>8428000</v>
+      </c>
+      <c r="E62" s="3">
         <v>8065900</v>
       </c>
-      <c r="E62" s="3">
+      <c r="F62" s="3">
         <v>6973100</v>
       </c>
-      <c r="F62" s="3">
+      <c r="G62" s="3">
         <v>7766400</v>
       </c>
-      <c r="G62" s="3">
+      <c r="H62" s="3">
         <v>4724200</v>
       </c>
-      <c r="H62" s="3">
+      <c r="I62" s="3">
         <v>8885900</v>
       </c>
-      <c r="I62" s="3">
+      <c r="J62" s="3">
         <v>8657200</v>
       </c>
-      <c r="J62" s="3">
+      <c r="K62" s="3">
         <v>11788800</v>
       </c>
-      <c r="K62" s="3">
+      <c r="L62" s="3">
         <v>459600</v>
       </c>
-      <c r="L62" s="3">
+      <c r="M62" s="3">
         <v>438000</v>
       </c>
-      <c r="M62" s="3">
+      <c r="N62" s="3">
         <v>469900</v>
       </c>
-      <c r="N62" s="3">
+      <c r="O62" s="3">
         <v>523500</v>
       </c>
-      <c r="O62" s="3">
+      <c r="P62" s="3">
         <v>608300</v>
       </c>
-      <c r="P62" s="3">
+      <c r="Q62" s="3">
         <v>663300</v>
       </c>
-      <c r="Q62" s="3">
+      <c r="R62" s="3">
         <v>620300</v>
       </c>
-      <c r="R62" s="3">
+      <c r="S62" s="3">
         <v>542300</v>
       </c>
-      <c r="S62" s="3">
+      <c r="T62" s="3">
         <v>528500</v>
       </c>
-      <c r="T62" s="3">
+      <c r="U62" s="3">
         <v>720700</v>
       </c>
-      <c r="U62" s="3">
+      <c r="V62" s="3">
         <v>691400</v>
       </c>
-      <c r="V62" s="3">
+      <c r="W62" s="3">
         <v>680000</v>
       </c>
-      <c r="W62" s="3">
+      <c r="X62" s="3">
         <v>570200</v>
       </c>
-      <c r="X62" s="3">
+      <c r="Y62" s="3">
         <v>714600</v>
       </c>
-      <c r="Y62" s="3">
+      <c r="Z62" s="3">
         <v>648100</v>
       </c>
-      <c r="Z62" s="3">
+      <c r="AA62" s="3">
         <v>618700</v>
       </c>
-      <c r="AA62" s="3">
+      <c r="AB62" s="3">
         <v>520300</v>
       </c>
-      <c r="AB62" s="3">
+      <c r="AC62" s="3">
         <v>418500</v>
       </c>
-      <c r="AC62" s="3">
+      <c r="AD62" s="3">
         <v>420800</v>
       </c>
-      <c r="AD62" s="3">
+      <c r="AE62" s="3">
         <v>527700</v>
       </c>
-      <c r="AE62" s="3">
+      <c r="AF62" s="3">
         <v>419200</v>
       </c>
-      <c r="AF62" s="3">
+      <c r="AG62" s="3">
         <v>395900</v>
       </c>
-      <c r="AG62" s="3">
+      <c r="AH62" s="3">
         <v>382900</v>
       </c>
-      <c r="AH62" s="3">
+      <c r="AI62" s="3">
         <v>400700</v>
       </c>
-      <c r="AI62" s="3">
+      <c r="AJ62" s="3">
         <v>463600</v>
       </c>
-      <c r="AJ62" s="3">
+      <c r="AK62" s="3">
         <v>459900</v>
       </c>
     </row>
-    <row r="63" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="63" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C63" s="1" t="s">
         <v>56</v>
       </c>
@@ -5939,8 +6087,11 @@
       <c r="AJ63" s="3">
         <v>0</v>
       </c>
+      <c r="AK63" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="64" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="64" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C64" s="1" t="s">
         <v>20</v>
       </c>
@@ -6043,8 +6194,11 @@
       <c r="AJ64" s="3">
         <v>0</v>
       </c>
+      <c r="AK64" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="65" spans="2:36" x14ac:dyDescent="0.2">
+    <row r="65" spans="2:37" x14ac:dyDescent="0.2">
       <c r="C65" s="1" t="s">
         <v>57</v>
       </c>
@@ -6147,112 +6301,118 @@
       <c r="AJ65" s="3">
         <v>0</v>
       </c>
+      <c r="AK65" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="66" spans="2:36" x14ac:dyDescent="0.2">
+    <row r="66" spans="2:37" x14ac:dyDescent="0.2">
       <c r="C66" s="1" t="s">
         <v>58</v>
       </c>
       <c r="D66" s="3">
+        <v>331601300</v>
+      </c>
+      <c r="E66" s="3">
         <v>386400900</v>
       </c>
-      <c r="E66" s="3">
+      <c r="F66" s="3">
         <v>343710800</v>
       </c>
-      <c r="F66" s="3">
+      <c r="G66" s="3">
         <v>350345300</v>
       </c>
-      <c r="G66" s="3">
+      <c r="H66" s="3">
         <v>358283300</v>
       </c>
-      <c r="H66" s="3">
+      <c r="I66" s="3">
         <v>336284100</v>
       </c>
-      <c r="I66" s="3">
+      <c r="J66" s="3">
         <v>341832200</v>
       </c>
-      <c r="J66" s="3">
+      <c r="K66" s="3">
         <v>341656500</v>
       </c>
-      <c r="K66" s="3">
+      <c r="L66" s="3">
         <v>338784400</v>
       </c>
-      <c r="L66" s="3">
+      <c r="M66" s="3">
         <v>345885900</v>
       </c>
-      <c r="M66" s="3">
+      <c r="N66" s="3">
         <v>348018900</v>
       </c>
-      <c r="N66" s="3">
+      <c r="O66" s="3">
         <v>338354200</v>
       </c>
-      <c r="O66" s="3">
+      <c r="P66" s="3">
         <v>316006400</v>
       </c>
-      <c r="P66" s="3">
+      <c r="Q66" s="3">
         <v>309651700</v>
       </c>
-      <c r="Q66" s="3">
+      <c r="R66" s="3">
         <v>297533600</v>
       </c>
-      <c r="R66" s="3">
+      <c r="S66" s="3">
         <v>290517700</v>
       </c>
-      <c r="S66" s="3">
+      <c r="T66" s="3">
         <v>278260300</v>
       </c>
-      <c r="T66" s="3">
+      <c r="U66" s="3">
         <v>275726000</v>
       </c>
-      <c r="U66" s="3">
+      <c r="V66" s="3">
         <v>275487700</v>
       </c>
-      <c r="V66" s="3">
+      <c r="W66" s="3">
         <v>288675900</v>
       </c>
-      <c r="W66" s="3">
+      <c r="X66" s="3">
         <v>289399800</v>
       </c>
-      <c r="X66" s="3">
+      <c r="Y66" s="3">
         <v>297278600</v>
       </c>
-      <c r="Y66" s="3">
+      <c r="Z66" s="3">
         <v>299163500</v>
       </c>
-      <c r="Z66" s="3">
+      <c r="AA66" s="3">
         <v>296968200</v>
       </c>
-      <c r="AA66" s="3">
+      <c r="AB66" s="3">
         <v>267714100</v>
       </c>
-      <c r="AB66" s="3">
+      <c r="AC66" s="3">
         <v>249559900</v>
       </c>
-      <c r="AC66" s="3">
+      <c r="AD66" s="3">
         <v>256847800</v>
       </c>
-      <c r="AD66" s="3">
+      <c r="AE66" s="3">
         <v>256582900</v>
       </c>
-      <c r="AE66" s="3">
+      <c r="AF66" s="3">
         <v>260418000</v>
       </c>
-      <c r="AF66" s="3">
+      <c r="AG66" s="3">
         <v>261733600</v>
       </c>
-      <c r="AG66" s="3">
+      <c r="AH66" s="3">
         <v>260311800</v>
       </c>
-      <c r="AH66" s="3">
+      <c r="AI66" s="3">
         <v>255640700</v>
       </c>
-      <c r="AI66" s="3">
+      <c r="AJ66" s="3">
         <v>261266900</v>
       </c>
-      <c r="AJ66" s="3">
+      <c r="AK66" s="3">
         <v>263136400</v>
       </c>
     </row>
-    <row r="67" spans="2:36" x14ac:dyDescent="0.2">
+    <row r="67" spans="2:37" x14ac:dyDescent="0.2">
       <c r="C67" s="1" t="s">
         <v>59</v>
       </c>
@@ -6289,8 +6449,9 @@
       <c r="AH67" s="3"/>
       <c r="AI67" s="3"/>
       <c r="AJ67" s="3"/>
+      <c r="AK67" s="3"/>
     </row>
-    <row r="68" spans="2:36" x14ac:dyDescent="0.2">
+    <row r="68" spans="2:37" x14ac:dyDescent="0.2">
       <c r="C68" s="1" t="s">
         <v>60</v>
       </c>
@@ -6393,8 +6554,11 @@
       <c r="AJ68" s="3">
         <v>0</v>
       </c>
+      <c r="AK68" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="69" spans="2:36" x14ac:dyDescent="0.2">
+    <row r="69" spans="2:37" x14ac:dyDescent="0.2">
       <c r="C69" s="1" t="s">
         <v>61</v>
       </c>
@@ -6497,8 +6661,11 @@
       <c r="AJ69" s="3">
         <v>0</v>
       </c>
+      <c r="AK69" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="70" spans="2:36" x14ac:dyDescent="0.2">
+    <row r="70" spans="2:37" x14ac:dyDescent="0.2">
       <c r="C70" s="1" t="s">
         <v>62</v>
       </c>
@@ -6601,8 +6768,11 @@
       <c r="AJ70" s="3">
         <v>0</v>
       </c>
+      <c r="AK70" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="71" spans="2:36" x14ac:dyDescent="0.2">
+    <row r="71" spans="2:37" x14ac:dyDescent="0.2">
       <c r="C71" s="1" t="s">
         <v>63</v>
       </c>
@@ -6705,112 +6875,118 @@
       <c r="AJ71" s="3">
         <v>0</v>
       </c>
+      <c r="AK71" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="72" spans="2:36" x14ac:dyDescent="0.2">
+    <row r="72" spans="2:37" x14ac:dyDescent="0.2">
       <c r="C72" s="1" t="s">
         <v>64</v>
       </c>
       <c r="D72" s="3">
+        <v>18243700</v>
+      </c>
+      <c r="E72" s="3">
         <v>20282200</v>
       </c>
-      <c r="E72" s="3">
+      <c r="F72" s="3">
         <v>18807000</v>
       </c>
-      <c r="F72" s="3">
+      <c r="G72" s="3">
         <v>18719000</v>
       </c>
-      <c r="G72" s="3">
+      <c r="H72" s="3">
         <v>19268400</v>
       </c>
-      <c r="H72" s="3">
+      <c r="I72" s="3">
         <v>18710700</v>
       </c>
-      <c r="I72" s="3">
+      <c r="J72" s="3">
         <v>18565400</v>
       </c>
-      <c r="J72" s="3">
+      <c r="K72" s="3">
         <v>18299100</v>
       </c>
-      <c r="K72" s="3">
+      <c r="L72" s="3">
         <v>17812600</v>
       </c>
-      <c r="L72" s="3">
+      <c r="M72" s="3">
         <v>17007700</v>
       </c>
-      <c r="M72" s="3">
+      <c r="N72" s="3">
         <v>17130600</v>
       </c>
-      <c r="N72" s="3">
+      <c r="O72" s="3">
         <v>16662400</v>
       </c>
-      <c r="O72" s="3">
+      <c r="P72" s="3">
         <v>16044400</v>
       </c>
-      <c r="P72" s="3">
+      <c r="Q72" s="3">
         <v>15764300</v>
       </c>
-      <c r="Q72" s="3">
+      <c r="R72" s="3">
         <v>15298800</v>
       </c>
-      <c r="R72" s="3">
+      <c r="S72" s="3">
         <v>14524300</v>
       </c>
-      <c r="S72" s="3">
+      <c r="T72" s="3">
         <v>14258500</v>
       </c>
-      <c r="T72" s="3">
+      <c r="U72" s="3">
         <v>14719300</v>
       </c>
-      <c r="U72" s="3">
+      <c r="V72" s="3">
         <v>14362200</v>
       </c>
-      <c r="V72" s="3">
+      <c r="W72" s="3">
         <v>15002800</v>
       </c>
-      <c r="W72" s="3">
+      <c r="X72" s="3">
         <v>15745800</v>
       </c>
-      <c r="X72" s="3">
+      <c r="Y72" s="3">
         <v>15573800</v>
       </c>
-      <c r="Y72" s="3">
+      <c r="Z72" s="3">
         <v>15698600</v>
       </c>
-      <c r="Z72" s="3">
+      <c r="AA72" s="3">
         <v>15678000</v>
       </c>
-      <c r="AA72" s="3">
+      <c r="AB72" s="3">
         <v>14384700</v>
       </c>
-      <c r="AB72" s="3">
+      <c r="AC72" s="3">
         <v>13795900</v>
       </c>
-      <c r="AC72" s="3">
+      <c r="AD72" s="3">
         <v>13837700</v>
       </c>
-      <c r="AD72" s="3">
+      <c r="AE72" s="3">
         <v>13273900</v>
       </c>
-      <c r="AE72" s="3">
+      <c r="AF72" s="3">
         <v>13745600</v>
       </c>
-      <c r="AF72" s="3">
+      <c r="AG72" s="3">
         <v>13660700</v>
       </c>
-      <c r="AG72" s="3">
+      <c r="AH72" s="3">
         <v>13507800</v>
       </c>
-      <c r="AH72" s="3">
+      <c r="AI72" s="3">
         <v>13138800</v>
       </c>
-      <c r="AI72" s="3">
+      <c r="AJ72" s="3">
         <v>13150400</v>
       </c>
-      <c r="AJ72" s="3">
+      <c r="AK72" s="3">
         <v>13062800</v>
       </c>
     </row>
-    <row r="73" spans="2:36" x14ac:dyDescent="0.2">
+    <row r="73" spans="2:37" x14ac:dyDescent="0.2">
       <c r="C73" s="1" t="s">
         <v>65</v>
       </c>
@@ -6913,8 +7089,11 @@
       <c r="AJ73" s="3">
         <v>0</v>
       </c>
+      <c r="AK73" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="74" spans="2:36" x14ac:dyDescent="0.2">
+    <row r="74" spans="2:37" x14ac:dyDescent="0.2">
       <c r="C74" s="1" t="s">
         <v>66</v>
       </c>
@@ -7017,8 +7196,11 @@
       <c r="AJ74" s="3">
         <v>0</v>
       </c>
+      <c r="AK74" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="75" spans="2:36" x14ac:dyDescent="0.2">
+    <row r="75" spans="2:37" x14ac:dyDescent="0.2">
       <c r="C75" s="1" t="s">
         <v>67</v>
       </c>
@@ -7121,112 +7303,118 @@
       <c r="AJ75" s="3">
         <v>0</v>
       </c>
+      <c r="AK75" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="76" spans="2:36" x14ac:dyDescent="0.2">
+    <row r="76" spans="2:37" x14ac:dyDescent="0.2">
       <c r="C76" s="1" t="s">
         <v>68</v>
       </c>
       <c r="D76" s="3">
+        <v>23081300</v>
+      </c>
+      <c r="E76" s="3">
         <v>25698700</v>
       </c>
-      <c r="E76" s="3">
+      <c r="F76" s="3">
         <v>24286300</v>
       </c>
-      <c r="F76" s="3">
+      <c r="G76" s="3">
         <v>23977100</v>
       </c>
-      <c r="G76" s="3">
+      <c r="H76" s="3">
         <v>24420000</v>
       </c>
-      <c r="H76" s="3">
+      <c r="I76" s="3">
         <v>23463000</v>
       </c>
-      <c r="I76" s="3">
+      <c r="J76" s="3">
         <v>22963400</v>
       </c>
-      <c r="J76" s="3">
+      <c r="K76" s="3">
         <v>22747400</v>
       </c>
-      <c r="K76" s="3">
+      <c r="L76" s="3">
         <v>21571400</v>
       </c>
-      <c r="L76" s="3">
+      <c r="M76" s="3">
         <v>20624400</v>
       </c>
-      <c r="M76" s="3">
+      <c r="N76" s="3">
         <v>20539800</v>
       </c>
-      <c r="N76" s="3">
+      <c r="O76" s="3">
         <v>20238100</v>
       </c>
-      <c r="O76" s="3">
+      <c r="P76" s="3">
         <v>19381500</v>
       </c>
-      <c r="P76" s="3">
+      <c r="Q76" s="3">
         <v>18987000</v>
       </c>
-      <c r="Q76" s="3">
+      <c r="R76" s="3">
         <v>18419400</v>
       </c>
-      <c r="R76" s="3">
+      <c r="S76" s="3">
         <v>17399500</v>
       </c>
-      <c r="S76" s="3">
+      <c r="T76" s="3">
         <v>17059700</v>
       </c>
-      <c r="T76" s="3">
+      <c r="U76" s="3">
         <v>17519900</v>
       </c>
-      <c r="U76" s="3">
+      <c r="V76" s="3">
         <v>17171900</v>
       </c>
-      <c r="V76" s="3">
+      <c r="W76" s="3">
         <v>17677500</v>
       </c>
-      <c r="W76" s="3">
+      <c r="X76" s="3">
         <v>18283800</v>
       </c>
-      <c r="X76" s="3">
+      <c r="Y76" s="3">
         <v>17718000</v>
       </c>
-      <c r="Y76" s="3">
+      <c r="Z76" s="3">
         <v>17110000</v>
       </c>
-      <c r="Z76" s="3">
+      <c r="AA76" s="3">
         <v>17117400</v>
       </c>
-      <c r="AA76" s="3">
+      <c r="AB76" s="3">
         <v>18261500</v>
       </c>
-      <c r="AB76" s="3">
+      <c r="AC76" s="3">
         <v>17579400</v>
       </c>
-      <c r="AC76" s="3">
+      <c r="AD76" s="3">
         <v>17463800</v>
       </c>
-      <c r="AD76" s="3">
+      <c r="AE76" s="3">
         <v>17085700</v>
       </c>
-      <c r="AE76" s="3">
+      <c r="AF76" s="3">
         <v>17922000</v>
       </c>
-      <c r="AF76" s="3">
+      <c r="AG76" s="3">
         <v>17996500</v>
       </c>
-      <c r="AG76" s="3">
+      <c r="AH76" s="3">
         <v>17825600</v>
       </c>
-      <c r="AH76" s="3">
+      <c r="AI76" s="3">
         <v>17960100</v>
       </c>
-      <c r="AI76" s="3">
+      <c r="AJ76" s="3">
         <v>18347500</v>
       </c>
-      <c r="AJ76" s="3">
+      <c r="AK76" s="3">
         <v>18412300</v>
       </c>
     </row>
-    <row r="77" spans="2:36" x14ac:dyDescent="0.2">
+    <row r="77" spans="2:37" x14ac:dyDescent="0.2">
       <c r="C77" s="1" t="s">
         <v>69</v>
       </c>
@@ -7329,221 +7517,230 @@
       <c r="AJ77" s="3">
         <v>0</v>
       </c>
+      <c r="AK77" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="79" spans="2:36" x14ac:dyDescent="0.2">
+    <row r="79" spans="2:37" x14ac:dyDescent="0.2">
       <c r="B79" s="1" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="80" spans="2:36" x14ac:dyDescent="0.2">
+    <row r="80" spans="2:37" x14ac:dyDescent="0.2">
       <c r="C80" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D80" s="2">
+        <v>45657</v>
+      </c>
+      <c r="E80" s="2">
         <v>45565</v>
       </c>
-      <c r="E80" s="2">
+      <c r="F80" s="2">
         <v>45473</v>
       </c>
-      <c r="F80" s="2">
+      <c r="G80" s="2">
         <v>45382</v>
       </c>
-      <c r="G80" s="2">
+      <c r="H80" s="2">
         <v>45291</v>
       </c>
-      <c r="H80" s="2">
+      <c r="I80" s="2">
         <v>45199</v>
       </c>
-      <c r="I80" s="2">
+      <c r="J80" s="2">
         <v>45107</v>
       </c>
-      <c r="J80" s="2">
+      <c r="K80" s="2">
         <v>45016</v>
       </c>
-      <c r="K80" s="2">
+      <c r="L80" s="2">
         <v>44926</v>
       </c>
-      <c r="L80" s="2">
+      <c r="M80" s="2">
         <v>44834</v>
       </c>
-      <c r="M80" s="2">
+      <c r="N80" s="2">
         <v>44742</v>
       </c>
-      <c r="N80" s="2">
+      <c r="O80" s="2">
         <v>44651</v>
       </c>
-      <c r="O80" s="2">
+      <c r="P80" s="2">
         <v>44561</v>
       </c>
-      <c r="P80" s="2">
+      <c r="Q80" s="2">
         <v>44469</v>
       </c>
-      <c r="Q80" s="2">
+      <c r="R80" s="2">
         <v>44377</v>
       </c>
-      <c r="R80" s="2">
+      <c r="S80" s="2">
         <v>44286</v>
       </c>
-      <c r="S80" s="2">
+      <c r="T80" s="2">
         <v>44196</v>
       </c>
-      <c r="T80" s="2">
+      <c r="U80" s="2">
         <v>44104</v>
       </c>
-      <c r="U80" s="2">
+      <c r="V80" s="2">
         <v>44012</v>
       </c>
-      <c r="V80" s="2">
+      <c r="W80" s="2">
         <v>43921</v>
       </c>
-      <c r="W80" s="2">
+      <c r="X80" s="2">
         <v>43830</v>
       </c>
-      <c r="X80" s="2">
+      <c r="Y80" s="2">
         <v>43738</v>
       </c>
-      <c r="Y80" s="2">
+      <c r="Z80" s="2">
         <v>43646</v>
       </c>
-      <c r="Z80" s="2">
+      <c r="AA80" s="2">
         <v>43555</v>
       </c>
-      <c r="AA80" s="2">
+      <c r="AB80" s="2">
         <v>43465</v>
       </c>
-      <c r="AB80" s="2">
+      <c r="AC80" s="2">
         <v>43373</v>
       </c>
-      <c r="AC80" s="2">
+      <c r="AD80" s="2">
         <v>43281</v>
       </c>
-      <c r="AD80" s="2">
+      <c r="AE80" s="2">
         <v>43190</v>
       </c>
-      <c r="AE80" s="2">
+      <c r="AF80" s="2">
         <v>43100</v>
       </c>
-      <c r="AF80" s="2">
+      <c r="AG80" s="2">
         <v>43008</v>
       </c>
-      <c r="AG80" s="2">
+      <c r="AH80" s="2">
         <v>42916</v>
       </c>
-      <c r="AH80" s="2">
+      <c r="AI80" s="2">
         <v>42825</v>
       </c>
-      <c r="AI80" s="2">
+      <c r="AJ80" s="2">
         <v>42735</v>
       </c>
-      <c r="AJ80" s="2">
+      <c r="AK80" s="2">
         <v>42643</v>
       </c>
     </row>
-    <row r="81" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="81" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C81" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D81" s="3">
+        <v>288500</v>
+      </c>
+      <c r="E81" s="3">
         <v>688600</v>
       </c>
-      <c r="E81" s="3">
+      <c r="F81" s="3">
         <v>676000</v>
       </c>
-      <c r="F81" s="3">
+      <c r="G81" s="3">
         <v>613100</v>
       </c>
-      <c r="G81" s="3">
+      <c r="H81" s="3">
         <v>52500</v>
       </c>
-      <c r="H81" s="3">
+      <c r="I81" s="3">
         <v>668000</v>
       </c>
-      <c r="I81" s="3">
+      <c r="J81" s="3">
         <v>474700</v>
       </c>
-      <c r="J81" s="3">
+      <c r="K81" s="3">
         <v>700700</v>
       </c>
-      <c r="K81" s="3">
+      <c r="L81" s="3">
         <v>338800</v>
       </c>
-      <c r="L81" s="3">
+      <c r="M81" s="3">
         <v>640600</v>
       </c>
-      <c r="M81" s="3">
+      <c r="N81" s="3">
         <v>684400</v>
       </c>
-      <c r="N81" s="3">
+      <c r="O81" s="3">
         <v>631400</v>
       </c>
-      <c r="O81" s="3">
+      <c r="P81" s="3">
         <v>279500</v>
       </c>
-      <c r="P81" s="3">
+      <c r="Q81" s="3">
         <v>570700</v>
       </c>
-      <c r="Q81" s="3">
+      <c r="R81" s="3">
         <v>552600</v>
       </c>
-      <c r="R81" s="3">
+      <c r="S81" s="3">
         <v>482000</v>
       </c>
-      <c r="S81" s="3">
+      <c r="T81" s="3">
         <v>112600</v>
       </c>
-      <c r="T81" s="3">
+      <c r="U81" s="3">
         <v>358800</v>
       </c>
-      <c r="U81" s="3">
+      <c r="V81" s="3">
         <v>100500</v>
       </c>
-      <c r="V81" s="3">
+      <c r="W81" s="3">
         <v>412900</v>
       </c>
-      <c r="W81" s="3">
+      <c r="X81" s="3">
         <v>174900</v>
       </c>
-      <c r="X81" s="3">
+      <c r="Y81" s="3">
         <v>410100</v>
       </c>
-      <c r="Y81" s="3">
+      <c r="Z81" s="3">
         <v>537700</v>
       </c>
-      <c r="Z81" s="3">
+      <c r="AA81" s="3">
         <v>517500</v>
       </c>
-      <c r="AA81" s="3">
+      <c r="AB81" s="3">
         <v>76800</v>
       </c>
-      <c r="AB81" s="3">
+      <c r="AC81" s="3">
         <v>453900</v>
       </c>
-      <c r="AC81" s="3">
+      <c r="AD81" s="3">
         <v>569900</v>
       </c>
-      <c r="AD81" s="3">
+      <c r="AE81" s="3">
         <v>463600</v>
       </c>
-      <c r="AE81" s="3">
+      <c r="AF81" s="3">
         <v>84900</v>
       </c>
-      <c r="AF81" s="3">
+      <c r="AG81" s="3">
         <v>212100</v>
       </c>
-      <c r="AG81" s="3">
+      <c r="AH81" s="3">
         <v>369000</v>
       </c>
-      <c r="AH81" s="3">
+      <c r="AI81" s="3">
         <v>517600</v>
       </c>
-      <c r="AI81" s="3">
+      <c r="AJ81" s="3">
         <v>88500</v>
       </c>
-      <c r="AJ81" s="3">
+      <c r="AK81" s="3">
         <v>275700</v>
       </c>
     </row>
-    <row r="82" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="82" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C82" s="1" t="s">
         <v>71</v>
       </c>
@@ -7580,112 +7777,116 @@
       <c r="AH82" s="3"/>
       <c r="AI82" s="3"/>
       <c r="AJ82" s="3"/>
+      <c r="AK82" s="3"/>
     </row>
-    <row r="83" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="83" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C83" s="1" t="s">
         <v>72</v>
       </c>
       <c r="D83" s="3">
+        <v>173700</v>
+      </c>
+      <c r="E83" s="3">
         <v>150800</v>
       </c>
-      <c r="E83" s="3">
+      <c r="F83" s="3">
         <v>153800</v>
       </c>
-      <c r="F83" s="3">
+      <c r="G83" s="3">
         <v>154400</v>
       </c>
-      <c r="G83" s="3">
+      <c r="H83" s="3">
         <v>162700</v>
       </c>
-      <c r="H83" s="3">
+      <c r="I83" s="3">
         <v>133200</v>
       </c>
-      <c r="I83" s="3">
+      <c r="J83" s="3">
         <v>147300</v>
       </c>
-      <c r="J83" s="3">
+      <c r="K83" s="3">
         <v>148000</v>
       </c>
-      <c r="K83" s="3">
+      <c r="L83" s="3">
         <v>185200</v>
       </c>
-      <c r="L83" s="3">
+      <c r="M83" s="3">
         <v>169700</v>
       </c>
-      <c r="M83" s="3">
+      <c r="N83" s="3">
         <v>175600</v>
       </c>
-      <c r="N83" s="3">
+      <c r="O83" s="3">
         <v>168600</v>
       </c>
-      <c r="O83" s="3">
+      <c r="P83" s="3">
         <v>155900</v>
       </c>
-      <c r="P83" s="3">
+      <c r="Q83" s="3">
         <v>149200</v>
       </c>
-      <c r="Q83" s="3">
+      <c r="R83" s="3">
         <v>184500</v>
       </c>
-      <c r="R83" s="3">
+      <c r="S83" s="3">
         <v>102900</v>
       </c>
-      <c r="S83" s="3">
+      <c r="T83" s="3">
         <v>101300</v>
       </c>
-      <c r="T83" s="3">
+      <c r="U83" s="3">
         <v>101500</v>
       </c>
-      <c r="U83" s="3">
+      <c r="V83" s="3">
         <v>98700</v>
       </c>
-      <c r="V83" s="3">
+      <c r="W83" s="3">
         <v>112300</v>
       </c>
-      <c r="W83" s="3">
+      <c r="X83" s="3">
         <v>120400</v>
       </c>
-      <c r="X83" s="3">
+      <c r="Y83" s="3">
         <v>116900</v>
       </c>
-      <c r="Y83" s="3">
+      <c r="Z83" s="3">
         <v>108900</v>
       </c>
-      <c r="Z83" s="3">
+      <c r="AA83" s="3">
         <v>93600</v>
       </c>
-      <c r="AA83" s="3">
+      <c r="AB83" s="3">
         <v>61600</v>
       </c>
-      <c r="AB83" s="3">
+      <c r="AC83" s="3">
         <v>58600</v>
       </c>
-      <c r="AC83" s="3">
+      <c r="AD83" s="3">
         <v>56000</v>
       </c>
-      <c r="AD83" s="3">
+      <c r="AE83" s="3">
         <v>50600</v>
       </c>
-      <c r="AE83" s="3">
+      <c r="AF83" s="3">
         <v>49900</v>
       </c>
-      <c r="AF83" s="3">
+      <c r="AG83" s="3">
         <v>50800</v>
       </c>
-      <c r="AG83" s="3">
+      <c r="AH83" s="3">
         <v>51600</v>
       </c>
-      <c r="AH83" s="3">
+      <c r="AI83" s="3">
         <v>55200</v>
       </c>
-      <c r="AI83" s="3">
+      <c r="AJ83" s="3">
         <v>54800</v>
       </c>
-      <c r="AJ83" s="3">
+      <c r="AK83" s="3">
         <v>53700</v>
       </c>
     </row>
-    <row r="84" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="84" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C84" s="1" t="s">
         <v>73</v>
       </c>
@@ -7788,8 +7989,11 @@
       <c r="AJ84" s="3">
         <v>0</v>
       </c>
+      <c r="AK84" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="85" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="85" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C85" s="1" t="s">
         <v>74</v>
       </c>
@@ -7892,8 +8096,11 @@
       <c r="AJ85" s="3">
         <v>0</v>
       </c>
+      <c r="AK85" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="86" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="86" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C86" s="1" t="s">
         <v>75</v>
       </c>
@@ -7996,8 +8203,11 @@
       <c r="AJ86" s="3">
         <v>0</v>
       </c>
+      <c r="AK86" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="87" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="87" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C87" s="1" t="s">
         <v>76</v>
       </c>
@@ -8100,8 +8310,11 @@
       <c r="AJ87" s="3">
         <v>0</v>
       </c>
+      <c r="AK87" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="88" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="88" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C88" s="1" t="s">
         <v>77</v>
       </c>
@@ -8204,112 +8417,118 @@
       <c r="AJ88" s="3">
         <v>0</v>
       </c>
+      <c r="AK88" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="89" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="89" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C89" s="1" t="s">
         <v>78</v>
       </c>
       <c r="D89" s="3">
+        <v>15238500</v>
+      </c>
+      <c r="E89" s="3">
         <v>-21513100</v>
       </c>
-      <c r="E89" s="3">
+      <c r="F89" s="3">
         <v>-5708900</v>
       </c>
-      <c r="F89" s="3">
+      <c r="G89" s="3">
         <v>3028800</v>
       </c>
-      <c r="G89" s="3">
+      <c r="H89" s="3">
         <v>-13351300</v>
       </c>
-      <c r="H89" s="3">
+      <c r="I89" s="3">
         <v>3754000</v>
       </c>
-      <c r="I89" s="3">
+      <c r="J89" s="3">
         <v>-11714900</v>
       </c>
-      <c r="J89" s="3">
+      <c r="K89" s="3">
         <v>10840700</v>
       </c>
-      <c r="K89" s="3">
+      <c r="L89" s="3">
         <v>12011900</v>
       </c>
-      <c r="L89" s="3">
+      <c r="M89" s="3">
         <v>-3350300</v>
       </c>
-      <c r="M89" s="3">
+      <c r="N89" s="3">
         <v>-2130300</v>
       </c>
-      <c r="N89" s="3">
+      <c r="O89" s="3">
         <v>7700600</v>
       </c>
-      <c r="O89" s="3">
+      <c r="P89" s="3">
         <v>4027400</v>
       </c>
-      <c r="P89" s="3">
+      <c r="Q89" s="3">
         <v>2586700</v>
       </c>
-      <c r="Q89" s="3">
+      <c r="R89" s="3">
         <v>-4607300</v>
       </c>
-      <c r="R89" s="3">
+      <c r="S89" s="3">
         <v>831700</v>
       </c>
-      <c r="S89" s="3">
+      <c r="T89" s="3">
         <v>1545900</v>
       </c>
-      <c r="T89" s="3">
+      <c r="U89" s="3">
         <v>-766500</v>
       </c>
-      <c r="U89" s="3">
+      <c r="V89" s="3">
         <v>2718500</v>
       </c>
-      <c r="V89" s="3">
+      <c r="W89" s="3">
         <v>-824700</v>
       </c>
-      <c r="W89" s="3">
+      <c r="X89" s="3">
         <v>-153300</v>
       </c>
-      <c r="X89" s="3">
+      <c r="Y89" s="3">
         <v>-428600</v>
       </c>
-      <c r="Y89" s="3">
+      <c r="Z89" s="3">
         <v>3501700</v>
       </c>
-      <c r="Z89" s="3">
+      <c r="AA89" s="3">
         <v>-1296100</v>
       </c>
-      <c r="AA89" s="3">
+      <c r="AB89" s="3">
         <v>5231600</v>
       </c>
-      <c r="AB89" s="3">
+      <c r="AC89" s="3">
         <v>908000</v>
       </c>
-      <c r="AC89" s="3">
+      <c r="AD89" s="3">
         <v>643600</v>
       </c>
-      <c r="AD89" s="3">
+      <c r="AE89" s="3">
         <v>877700</v>
       </c>
-      <c r="AE89" s="3">
+      <c r="AF89" s="3">
         <v>-506300</v>
       </c>
-      <c r="AF89" s="3">
+      <c r="AG89" s="3">
         <v>-2456000</v>
       </c>
-      <c r="AG89" s="3">
+      <c r="AH89" s="3">
         <v>-340700</v>
       </c>
-      <c r="AH89" s="3">
+      <c r="AI89" s="3">
         <v>1561500</v>
       </c>
-      <c r="AI89" s="3">
+      <c r="AJ89" s="3">
         <v>108800</v>
       </c>
-      <c r="AJ89" s="3">
+      <c r="AK89" s="3">
         <v>3807600</v>
       </c>
     </row>
-    <row r="90" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="90" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C90" s="1" t="s">
         <v>79</v>
       </c>
@@ -8346,112 +8565,116 @@
       <c r="AH90" s="3"/>
       <c r="AI90" s="3"/>
       <c r="AJ90" s="3"/>
+      <c r="AK90" s="3"/>
     </row>
-    <row r="91" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="91" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C91" s="1" t="s">
         <v>80</v>
       </c>
       <c r="D91" s="3">
+        <v>-32300</v>
+      </c>
+      <c r="E91" s="3">
         <v>-62500</v>
       </c>
-      <c r="E91" s="3">
+      <c r="F91" s="3">
         <v>-40100</v>
       </c>
-      <c r="F91" s="3">
+      <c r="G91" s="3">
         <v>-27400</v>
       </c>
-      <c r="G91" s="3">
+      <c r="H91" s="3">
         <v>-61300</v>
       </c>
-      <c r="H91" s="3">
+      <c r="I91" s="3">
         <v>-23300</v>
       </c>
-      <c r="I91" s="3">
+      <c r="J91" s="3">
         <v>-23900</v>
       </c>
-      <c r="J91" s="3">
+      <c r="K91" s="3">
         <v>-17100</v>
       </c>
-      <c r="K91" s="3">
+      <c r="L91" s="3">
         <v>-113722000</v>
       </c>
-      <c r="L91" s="3">
+      <c r="M91" s="3">
         <v>-77226000</v>
       </c>
-      <c r="M91" s="3">
+      <c r="N91" s="3">
         <v>-104059000</v>
       </c>
-      <c r="N91" s="3">
+      <c r="O91" s="3">
         <v>-52618000</v>
       </c>
-      <c r="O91" s="3">
+      <c r="P91" s="3">
         <v>-74615000</v>
       </c>
-      <c r="P91" s="3">
+      <c r="Q91" s="3">
         <v>-81614000</v>
       </c>
-      <c r="Q91" s="3">
+      <c r="R91" s="3">
         <v>-15900</v>
       </c>
-      <c r="R91" s="3">
+      <c r="S91" s="3">
         <v>-14300</v>
       </c>
-      <c r="S91" s="3">
+      <c r="T91" s="3">
         <v>-43600</v>
       </c>
-      <c r="T91" s="3">
+      <c r="U91" s="3">
         <v>-25600</v>
       </c>
-      <c r="U91" s="3">
+      <c r="V91" s="3">
         <v>-24800</v>
       </c>
-      <c r="V91" s="3">
+      <c r="W91" s="3">
         <v>-20300</v>
       </c>
-      <c r="W91" s="3">
+      <c r="X91" s="3">
         <v>-190900</v>
       </c>
-      <c r="X91" s="3">
+      <c r="Y91" s="3">
         <v>-91000</v>
       </c>
-      <c r="Y91" s="3">
+      <c r="Z91" s="3">
         <v>-55400</v>
       </c>
-      <c r="Z91" s="3">
+      <c r="AA91" s="3">
         <v>-31700</v>
       </c>
-      <c r="AA91" s="3">
+      <c r="AB91" s="3">
         <v>-43000</v>
       </c>
-      <c r="AB91" s="3">
+      <c r="AC91" s="3">
         <v>-20100</v>
       </c>
-      <c r="AC91" s="3">
+      <c r="AD91" s="3">
         <v>-18000</v>
       </c>
-      <c r="AD91" s="3">
+      <c r="AE91" s="3">
         <v>-17800</v>
       </c>
-      <c r="AE91" s="3">
+      <c r="AF91" s="3">
         <v>-25100</v>
       </c>
-      <c r="AF91" s="3">
+      <c r="AG91" s="3">
         <v>-57300</v>
       </c>
-      <c r="AG91" s="3">
+      <c r="AH91" s="3">
         <v>-37900</v>
       </c>
-      <c r="AH91" s="3">
+      <c r="AI91" s="3">
         <v>-22400</v>
       </c>
-      <c r="AI91" s="3">
+      <c r="AJ91" s="3">
         <v>-111600</v>
       </c>
-      <c r="AJ91" s="3">
+      <c r="AK91" s="3">
         <v>-90400</v>
       </c>
     </row>
-    <row r="92" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="92" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C92" s="1" t="s">
         <v>81</v>
       </c>
@@ -8554,8 +8777,11 @@
       <c r="AJ92" s="3">
         <v>0</v>
       </c>
+      <c r="AK92" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="93" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="93" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C93" s="1" t="s">
         <v>82</v>
       </c>
@@ -8658,112 +8884,118 @@
       <c r="AJ93" s="3">
         <v>0</v>
       </c>
+      <c r="AK93" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="94" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="94" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C94" s="1" t="s">
         <v>83</v>
       </c>
       <c r="D94" s="3">
+        <v>-3917800</v>
+      </c>
+      <c r="E94" s="3">
         <v>3642700</v>
       </c>
-      <c r="E94" s="3">
+      <c r="F94" s="3">
         <v>-1092400</v>
       </c>
-      <c r="F94" s="3">
+      <c r="G94" s="3">
         <v>1841100</v>
       </c>
-      <c r="G94" s="3">
+      <c r="H94" s="3">
         <v>-625400</v>
       </c>
-      <c r="H94" s="3">
+      <c r="I94" s="3">
         <v>-1107500</v>
       </c>
-      <c r="I94" s="3">
+      <c r="J94" s="3">
         <v>-261600</v>
       </c>
-      <c r="J94" s="3">
+      <c r="K94" s="3">
         <v>300800</v>
       </c>
-      <c r="K94" s="3">
+      <c r="L94" s="3">
         <v>-2910400</v>
       </c>
-      <c r="L94" s="3">
+      <c r="M94" s="3">
         <v>-2354900</v>
       </c>
-      <c r="M94" s="3">
+      <c r="N94" s="3">
         <v>2353800</v>
       </c>
-      <c r="N94" s="3">
+      <c r="O94" s="3">
         <v>-2278800</v>
       </c>
-      <c r="O94" s="3">
+      <c r="P94" s="3">
         <v>-4489600</v>
       </c>
-      <c r="P94" s="3">
+      <c r="Q94" s="3">
         <v>-3902300</v>
       </c>
-      <c r="Q94" s="3">
+      <c r="R94" s="3">
         <v>1124900</v>
       </c>
-      <c r="R94" s="3">
+      <c r="S94" s="3">
         <v>-723400</v>
       </c>
-      <c r="S94" s="3">
+      <c r="T94" s="3">
         <v>-365200</v>
       </c>
-      <c r="T94" s="3">
+      <c r="U94" s="3">
         <v>-124500</v>
       </c>
-      <c r="U94" s="3">
+      <c r="V94" s="3">
         <v>-446100</v>
       </c>
-      <c r="V94" s="3">
+      <c r="W94" s="3">
         <v>-179800</v>
       </c>
-      <c r="W94" s="3">
+      <c r="X94" s="3">
         <v>-962200</v>
       </c>
-      <c r="X94" s="3">
+      <c r="Y94" s="3">
         <v>-913600</v>
       </c>
-      <c r="Y94" s="3">
+      <c r="Z94" s="3">
         <v>-5520900</v>
       </c>
-      <c r="Z94" s="3">
+      <c r="AA94" s="3">
         <v>-97900</v>
       </c>
-      <c r="AA94" s="3">
+      <c r="AB94" s="3">
         <v>-5105000</v>
       </c>
-      <c r="AB94" s="3">
+      <c r="AC94" s="3">
         <v>-2452600</v>
       </c>
-      <c r="AC94" s="3">
+      <c r="AD94" s="3">
         <v>-1063800</v>
       </c>
-      <c r="AD94" s="3">
+      <c r="AE94" s="3">
         <v>-587600</v>
       </c>
-      <c r="AE94" s="3">
+      <c r="AF94" s="3">
         <v>1277600</v>
       </c>
-      <c r="AF94" s="3">
+      <c r="AG94" s="3">
         <v>-195600</v>
       </c>
-      <c r="AG94" s="3">
+      <c r="AH94" s="3">
         <v>183200</v>
       </c>
-      <c r="AH94" s="3">
+      <c r="AI94" s="3">
         <v>392500</v>
       </c>
-      <c r="AI94" s="3">
+      <c r="AJ94" s="3">
         <v>-2371700</v>
       </c>
-      <c r="AJ94" s="3">
+      <c r="AK94" s="3">
         <v>694800</v>
       </c>
     </row>
-    <row r="95" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="95" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C95" s="1" t="s">
         <v>84</v>
       </c>
@@ -8800,41 +9032,42 @@
       <c r="AH95" s="3"/>
       <c r="AI95" s="3"/>
       <c r="AJ95" s="3"/>
+      <c r="AK95" s="3"/>
     </row>
-    <row r="96" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="96" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C96" s="1" t="s">
         <v>85</v>
       </c>
       <c r="D96" s="3">
+        <v>117000</v>
+      </c>
+      <c r="E96" s="3">
         <v>134900</v>
       </c>
-      <c r="E96" s="3">
+      <c r="F96" s="3">
         <v>473000</v>
       </c>
-      <c r="F96" s="3">
+      <c r="G96" s="3">
         <v>26200</v>
       </c>
-      <c r="G96" s="3">
+      <c r="H96" s="3">
         <v>151100</v>
       </c>
-      <c r="H96" s="3">
+      <c r="I96" s="3">
         <v>102000</v>
       </c>
-      <c r="I96" s="3">
+      <c r="J96" s="3">
         <v>566300</v>
       </c>
-      <c r="J96" s="3">
+      <c r="K96" s="3">
         <v>23300</v>
       </c>
-      <c r="K96" s="3">
-        <v>0</v>
-      </c>
       <c r="L96" s="3">
+        <v>0</v>
+      </c>
+      <c r="M96" s="3">
         <v>-79700</v>
       </c>
-      <c r="M96" s="3">
-        <v>0</v>
-      </c>
       <c r="N96" s="3">
         <v>0</v>
       </c>
@@ -8842,11 +9075,11 @@
         <v>0</v>
       </c>
       <c r="P96" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q96" s="3">
         <v>-81300</v>
       </c>
-      <c r="Q96" s="3">
-        <v>0</v>
-      </c>
       <c r="R96" s="3">
         <v>0</v>
       </c>
@@ -8890,22 +9123,25 @@
         <v>0</v>
       </c>
       <c r="AF96" s="3">
+        <v>0</v>
+      </c>
+      <c r="AG96" s="3">
         <v>-59200</v>
       </c>
-      <c r="AG96" s="3">
+      <c r="AH96" s="3">
         <v>-237000</v>
       </c>
-      <c r="AH96" s="3">
-        <v>0</v>
-      </c>
       <c r="AI96" s="3">
+        <v>0</v>
+      </c>
+      <c r="AJ96" s="3">
         <v>-38100</v>
       </c>
-      <c r="AJ96" s="3">
+      <c r="AK96" s="3">
         <v>-22800</v>
       </c>
     </row>
-    <row r="97" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="97" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C97" s="1" t="s">
         <v>86</v>
       </c>
@@ -9008,8 +9244,11 @@
       <c r="AJ97" s="3">
         <v>0</v>
       </c>
+      <c r="AK97" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="98" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="98" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C98" s="1" t="s">
         <v>87</v>
       </c>
@@ -9112,8 +9351,11 @@
       <c r="AJ98" s="3">
         <v>0</v>
       </c>
+      <c r="AK98" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="99" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="99" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C99" s="1" t="s">
         <v>88</v>
       </c>
@@ -9216,316 +9458,328 @@
       <c r="AJ99" s="3">
         <v>0</v>
       </c>
+      <c r="AK99" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="100" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="100" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C100" s="1" t="s">
         <v>89</v>
       </c>
       <c r="D100" s="3">
+        <v>-16521000</v>
+      </c>
+      <c r="E100" s="3">
         <v>24357600</v>
       </c>
-      <c r="E100" s="3">
+      <c r="F100" s="3">
         <v>1880400</v>
       </c>
-      <c r="F100" s="3">
+      <c r="G100" s="3">
         <v>-4107500</v>
       </c>
-      <c r="G100" s="3">
+      <c r="H100" s="3">
         <v>17753300</v>
       </c>
-      <c r="H100" s="3">
+      <c r="I100" s="3">
         <v>447300</v>
       </c>
-      <c r="I100" s="3">
+      <c r="J100" s="3">
         <v>5022900</v>
       </c>
-      <c r="J100" s="3">
+      <c r="K100" s="3">
         <v>-13746200</v>
       </c>
-      <c r="K100" s="3">
+      <c r="L100" s="3">
         <v>-5147300</v>
       </c>
-      <c r="L100" s="3">
+      <c r="M100" s="3">
         <v>1697300</v>
       </c>
-      <c r="M100" s="3">
+      <c r="N100" s="3">
         <v>3000400</v>
       </c>
-      <c r="N100" s="3">
+      <c r="O100" s="3">
         <v>1932700</v>
       </c>
-      <c r="O100" s="3">
+      <c r="P100" s="3">
         <v>2031800</v>
       </c>
-      <c r="P100" s="3">
+      <c r="Q100" s="3">
         <v>1404600</v>
       </c>
-      <c r="Q100" s="3">
+      <c r="R100" s="3">
         <v>2911000</v>
       </c>
-      <c r="R100" s="3">
+      <c r="S100" s="3">
         <v>453200</v>
       </c>
-      <c r="S100" s="3">
+      <c r="T100" s="3">
         <v>261800</v>
       </c>
-      <c r="T100" s="3">
+      <c r="U100" s="3">
         <v>553800</v>
       </c>
-      <c r="U100" s="3">
+      <c r="V100" s="3">
         <v>-2356000</v>
       </c>
-      <c r="V100" s="3">
+      <c r="W100" s="3">
         <v>3526800</v>
       </c>
-      <c r="W100" s="3">
+      <c r="X100" s="3">
         <v>-950700</v>
       </c>
-      <c r="X100" s="3">
+      <c r="Y100" s="3">
         <v>3000500</v>
       </c>
-      <c r="Y100" s="3">
+      <c r="Z100" s="3">
         <v>3588600</v>
       </c>
-      <c r="Z100" s="3">
+      <c r="AA100" s="3">
         <v>-289800</v>
       </c>
-      <c r="AA100" s="3">
+      <c r="AB100" s="3">
         <v>491400</v>
       </c>
-      <c r="AB100" s="3">
+      <c r="AC100" s="3">
         <v>1689200</v>
       </c>
-      <c r="AC100" s="3">
+      <c r="AD100" s="3">
         <v>354700</v>
       </c>
-      <c r="AD100" s="3">
+      <c r="AE100" s="3">
         <v>-1323700</v>
       </c>
-      <c r="AE100" s="3">
+      <c r="AF100" s="3">
         <v>-309500</v>
       </c>
-      <c r="AF100" s="3">
+      <c r="AG100" s="3">
         <v>2140800</v>
       </c>
-      <c r="AG100" s="3">
+      <c r="AH100" s="3">
         <v>-384900</v>
       </c>
-      <c r="AH100" s="3">
+      <c r="AI100" s="3">
         <v>-1500100</v>
       </c>
-      <c r="AI100" s="3">
+      <c r="AJ100" s="3">
         <v>1503800</v>
       </c>
-      <c r="AJ100" s="3">
+      <c r="AK100" s="3">
         <v>-1778900</v>
       </c>
     </row>
-    <row r="101" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="101" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C101" s="1" t="s">
         <v>90</v>
       </c>
       <c r="D101" s="3">
+        <v>-179300</v>
+      </c>
+      <c r="E101" s="3">
         <v>27300</v>
       </c>
-      <c r="E101" s="3">
+      <c r="F101" s="3">
         <v>-105100</v>
       </c>
-      <c r="F101" s="3">
+      <c r="G101" s="3">
         <v>125800</v>
       </c>
-      <c r="G101" s="3">
+      <c r="H101" s="3">
         <v>-1568200</v>
       </c>
-      <c r="H101" s="3">
+      <c r="I101" s="3">
         <v>609200</v>
       </c>
-      <c r="I101" s="3">
+      <c r="J101" s="3">
         <v>667200</v>
       </c>
-      <c r="J101" s="3">
+      <c r="K101" s="3">
         <v>217100</v>
       </c>
-      <c r="K101" s="3">
+      <c r="L101" s="3">
         <v>-1479100</v>
       </c>
-      <c r="L101" s="3">
+      <c r="M101" s="3">
         <v>638600</v>
       </c>
-      <c r="M101" s="3">
+      <c r="N101" s="3">
         <v>657000</v>
       </c>
-      <c r="N101" s="3">
+      <c r="O101" s="3">
         <v>203100</v>
       </c>
-      <c r="O101" s="3">
+      <c r="P101" s="3">
         <v>68900</v>
       </c>
-      <c r="P101" s="3">
+      <c r="Q101" s="3">
         <v>409500</v>
       </c>
-      <c r="Q101" s="3">
+      <c r="R101" s="3">
         <v>18100</v>
       </c>
-      <c r="R101" s="3">
+      <c r="S101" s="3">
         <v>295500</v>
       </c>
-      <c r="S101" s="3">
+      <c r="T101" s="3">
         <v>-571700</v>
       </c>
-      <c r="T101" s="3">
+      <c r="U101" s="3">
         <v>-142900</v>
       </c>
-      <c r="U101" s="3">
+      <c r="V101" s="3">
         <v>-159900</v>
       </c>
-      <c r="V101" s="3">
+      <c r="W101" s="3">
         <v>200400</v>
       </c>
-      <c r="W101" s="3">
+      <c r="X101" s="3">
         <v>369400</v>
       </c>
-      <c r="X101" s="3">
+      <c r="Y101" s="3">
         <v>-340600</v>
       </c>
-      <c r="Y101" s="3">
+      <c r="Z101" s="3">
         <v>51200</v>
       </c>
-      <c r="Z101" s="3">
+      <c r="AA101" s="3">
         <v>90500</v>
       </c>
-      <c r="AA101" s="3">
+      <c r="AB101" s="3">
         <v>6400</v>
       </c>
-      <c r="AB101" s="3">
+      <c r="AC101" s="3">
         <v>-76600</v>
       </c>
-      <c r="AC101" s="3">
+      <c r="AD101" s="3">
         <v>218900</v>
       </c>
-      <c r="AD101" s="3">
+      <c r="AE101" s="3">
         <v>50500</v>
       </c>
-      <c r="AE101" s="3">
+      <c r="AF101" s="3">
         <v>-377500</v>
       </c>
-      <c r="AF101" s="3">
+      <c r="AG101" s="3">
         <v>14000</v>
       </c>
-      <c r="AG101" s="3">
+      <c r="AH101" s="3">
         <v>8400</v>
       </c>
-      <c r="AH101" s="3">
+      <c r="AI101" s="3">
         <v>-108300</v>
       </c>
-      <c r="AI101" s="3">
+      <c r="AJ101" s="3">
         <v>138000</v>
       </c>
-      <c r="AJ101" s="3">
+      <c r="AK101" s="3">
         <v>-105900</v>
       </c>
     </row>
-    <row r="102" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="102" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C102" s="1" t="s">
         <v>91</v>
       </c>
       <c r="D102" s="3">
+        <v>-4200200</v>
+      </c>
+      <c r="E102" s="3">
         <v>6101900</v>
       </c>
-      <c r="E102" s="3">
+      <c r="F102" s="3">
         <v>-4689900</v>
       </c>
-      <c r="F102" s="3">
+      <c r="G102" s="3">
         <v>1025100</v>
       </c>
-      <c r="G102" s="3">
+      <c r="H102" s="3">
         <v>3597300</v>
       </c>
-      <c r="H102" s="3">
+      <c r="I102" s="3">
         <v>3121100</v>
       </c>
-      <c r="I102" s="3">
+      <c r="J102" s="3">
         <v>-7058600</v>
       </c>
-      <c r="J102" s="3">
+      <c r="K102" s="3">
         <v>-2478800</v>
       </c>
-      <c r="K102" s="3">
+      <c r="L102" s="3">
         <v>2475100</v>
       </c>
-      <c r="L102" s="3">
+      <c r="M102" s="3">
         <v>-3369400</v>
       </c>
-      <c r="M102" s="3">
+      <c r="N102" s="3">
         <v>3880900</v>
       </c>
-      <c r="N102" s="3">
+      <c r="O102" s="3">
         <v>7557600</v>
       </c>
-      <c r="O102" s="3">
+      <c r="P102" s="3">
         <v>1638600</v>
       </c>
-      <c r="P102" s="3">
+      <c r="Q102" s="3">
         <v>498500</v>
       </c>
-      <c r="Q102" s="3">
+      <c r="R102" s="3">
         <v>-553300</v>
       </c>
-      <c r="R102" s="3">
+      <c r="S102" s="3">
         <v>857000</v>
       </c>
-      <c r="S102" s="3">
+      <c r="T102" s="3">
         <v>870800</v>
       </c>
-      <c r="T102" s="3">
+      <c r="U102" s="3">
         <v>-480000</v>
       </c>
-      <c r="U102" s="3">
+      <c r="V102" s="3">
         <v>-243500</v>
       </c>
-      <c r="V102" s="3">
+      <c r="W102" s="3">
         <v>2722600</v>
       </c>
-      <c r="W102" s="3">
+      <c r="X102" s="3">
         <v>-1696800</v>
       </c>
-      <c r="X102" s="3">
+      <c r="Y102" s="3">
         <v>1317700</v>
       </c>
-      <c r="Y102" s="3">
+      <c r="Z102" s="3">
         <v>1620600</v>
       </c>
-      <c r="Z102" s="3">
+      <c r="AA102" s="3">
         <v>-1593300</v>
       </c>
-      <c r="AA102" s="3">
+      <c r="AB102" s="3">
         <v>624400</v>
       </c>
-      <c r="AB102" s="3">
+      <c r="AC102" s="3">
         <v>68000</v>
       </c>
-      <c r="AC102" s="3">
+      <c r="AD102" s="3">
         <v>153400</v>
       </c>
-      <c r="AD102" s="3">
+      <c r="AE102" s="3">
         <v>-983000</v>
       </c>
-      <c r="AE102" s="3">
+      <c r="AF102" s="3">
         <v>84300</v>
       </c>
-      <c r="AF102" s="3">
+      <c r="AG102" s="3">
         <v>-496900</v>
       </c>
-      <c r="AG102" s="3">
+      <c r="AH102" s="3">
         <v>-534100</v>
       </c>
-      <c r="AH102" s="3">
+      <c r="AI102" s="3">
         <v>345600</v>
       </c>
-      <c r="AI102" s="3">
+      <c r="AJ102" s="3">
         <v>-621200</v>
       </c>
-      <c r="AJ102" s="3">
+      <c r="AK102" s="3">
         <v>2617600</v>
       </c>
     </row>

--- a/AAII_Financials/Quarterly/WF_QTR_FIN.xlsx
+++ b/AAII_Financials/Quarterly/WF_QTR_FIN.xlsx
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="197" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="200" uniqueCount="92">
   <si>
     <t>WF</t>
   </si>
@@ -656,275 +656,281 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet2"/>
-  <dimension ref="A5:AK102"/>
+  <dimension ref="A5:AL102"/>
   <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="5" style="1" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="26.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="69.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="11" width="16" style="1" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="17" style="1" bestFit="1" customWidth="1"/>
-    <col min="13" max="13" width="16" style="1" bestFit="1" customWidth="1"/>
-    <col min="14" max="14" width="17" style="1" bestFit="1" customWidth="1"/>
-    <col min="15" max="37" width="16" style="1" bestFit="1" customWidth="1"/>
-    <col min="38" max="16384" width="9.140625" style="1"/>
+    <col min="4" max="12" width="16" style="1" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="17" style="1" bestFit="1" customWidth="1"/>
+    <col min="14" max="14" width="16" style="1" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="17" style="1" bestFit="1" customWidth="1"/>
+    <col min="16" max="38" width="16" style="1" bestFit="1" customWidth="1"/>
+    <col min="39" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
-    <row r="5" spans="1:37" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:38" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:37" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:38" x14ac:dyDescent="0.2">
       <c r="B6" s="1" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:37" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:38" x14ac:dyDescent="0.2">
       <c r="C7" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D7" s="2">
+        <v>45747</v>
+      </c>
+      <c r="E7" s="2">
         <v>45657</v>
       </c>
-      <c r="E7" s="2">
+      <c r="F7" s="2">
         <v>45565</v>
       </c>
-      <c r="F7" s="2">
+      <c r="G7" s="2">
         <v>45473</v>
       </c>
-      <c r="G7" s="2">
+      <c r="H7" s="2">
         <v>45382</v>
       </c>
-      <c r="H7" s="2">
+      <c r="I7" s="2">
         <v>45291</v>
       </c>
-      <c r="I7" s="2">
+      <c r="J7" s="2">
         <v>45199</v>
       </c>
-      <c r="J7" s="2">
+      <c r="K7" s="2">
         <v>45107</v>
       </c>
-      <c r="K7" s="2">
+      <c r="L7" s="2">
         <v>45016</v>
       </c>
-      <c r="L7" s="2">
+      <c r="M7" s="2">
         <v>44926</v>
       </c>
-      <c r="M7" s="2">
+      <c r="N7" s="2">
         <v>44834</v>
       </c>
-      <c r="N7" s="2">
+      <c r="O7" s="2">
         <v>44742</v>
       </c>
-      <c r="O7" s="2">
+      <c r="P7" s="2">
         <v>44651</v>
       </c>
-      <c r="P7" s="2">
+      <c r="Q7" s="2">
         <v>44561</v>
       </c>
-      <c r="Q7" s="2">
+      <c r="R7" s="2">
         <v>44469</v>
       </c>
-      <c r="R7" s="2">
+      <c r="S7" s="2">
         <v>44377</v>
       </c>
-      <c r="S7" s="2">
+      <c r="T7" s="2">
         <v>44286</v>
       </c>
-      <c r="T7" s="2">
+      <c r="U7" s="2">
         <v>44196</v>
       </c>
-      <c r="U7" s="2">
+      <c r="V7" s="2">
         <v>44104</v>
       </c>
-      <c r="V7" s="2">
+      <c r="W7" s="2">
         <v>44012</v>
       </c>
-      <c r="W7" s="2">
+      <c r="X7" s="2">
         <v>43921</v>
       </c>
-      <c r="X7" s="2">
+      <c r="Y7" s="2">
         <v>43830</v>
       </c>
-      <c r="Y7" s="2">
+      <c r="Z7" s="2">
         <v>43738</v>
       </c>
-      <c r="Z7" s="2">
+      <c r="AA7" s="2">
         <v>43646</v>
       </c>
-      <c r="AA7" s="2">
+      <c r="AB7" s="2">
         <v>43555</v>
       </c>
-      <c r="AB7" s="2">
+      <c r="AC7" s="2">
         <v>43465</v>
       </c>
-      <c r="AC7" s="2">
+      <c r="AD7" s="2">
         <v>43373</v>
       </c>
-      <c r="AD7" s="2">
+      <c r="AE7" s="2">
         <v>43281</v>
       </c>
-      <c r="AE7" s="2">
+      <c r="AF7" s="2">
         <v>43190</v>
       </c>
-      <c r="AF7" s="2">
+      <c r="AG7" s="2">
         <v>43100</v>
       </c>
-      <c r="AG7" s="2">
+      <c r="AH7" s="2">
         <v>43008</v>
       </c>
-      <c r="AH7" s="2">
+      <c r="AI7" s="2">
         <v>42916</v>
       </c>
-      <c r="AI7" s="2">
+      <c r="AJ7" s="2">
         <v>42825</v>
       </c>
-      <c r="AJ7" s="2">
+      <c r="AK7" s="2">
         <v>42735</v>
       </c>
-      <c r="AK7" s="2">
+      <c r="AL7" s="2">
         <v>42643</v>
       </c>
     </row>
-    <row r="8" spans="1:37" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:38" x14ac:dyDescent="0.2">
       <c r="C8" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D8" s="3">
+        <v>1801500</v>
+      </c>
+      <c r="E8" s="3">
         <v>2144100</v>
       </c>
-      <c r="E8" s="3">
+      <c r="F8" s="3">
         <v>1797600</v>
       </c>
-      <c r="F8" s="3">
+      <c r="G8" s="3">
         <v>2144400</v>
       </c>
-      <c r="G8" s="3">
+      <c r="H8" s="3">
         <v>2219900</v>
       </c>
-      <c r="H8" s="3">
+      <c r="I8" s="3">
         <v>1264600</v>
       </c>
-      <c r="I8" s="3">
+      <c r="J8" s="3">
         <v>2101400</v>
       </c>
-      <c r="J8" s="3">
+      <c r="K8" s="3">
         <v>1748600</v>
       </c>
-      <c r="K8" s="3">
+      <c r="L8" s="3">
         <v>2091700</v>
       </c>
-      <c r="L8" s="3">
+      <c r="M8" s="3">
         <v>3462200</v>
       </c>
-      <c r="M8" s="3">
+      <c r="N8" s="3">
         <v>2792200</v>
       </c>
-      <c r="N8" s="3">
+      <c r="O8" s="3">
         <v>2487200</v>
       </c>
-      <c r="O8" s="3">
+      <c r="P8" s="3">
         <v>2264400</v>
       </c>
-      <c r="P8" s="3">
+      <c r="Q8" s="3">
         <v>2026000</v>
       </c>
-      <c r="Q8" s="3">
+      <c r="R8" s="3">
         <v>1862200</v>
       </c>
-      <c r="R8" s="3">
+      <c r="S8" s="3">
         <v>1787500</v>
       </c>
-      <c r="S8" s="3">
+      <c r="T8" s="3">
         <v>1722100</v>
       </c>
-      <c r="T8" s="3">
+      <c r="U8" s="3">
         <v>1728200</v>
       </c>
-      <c r="U8" s="3">
+      <c r="V8" s="3">
         <v>1749800</v>
       </c>
-      <c r="V8" s="3">
+      <c r="W8" s="3">
         <v>1857400</v>
       </c>
-      <c r="W8" s="3">
+      <c r="X8" s="3">
         <v>2028100</v>
       </c>
-      <c r="X8" s="3">
+      <c r="Y8" s="3">
         <v>2216400</v>
       </c>
-      <c r="Y8" s="3">
+      <c r="Z8" s="3">
         <v>2287800</v>
       </c>
-      <c r="Z8" s="3">
+      <c r="AA8" s="3">
         <v>2353100</v>
       </c>
-      <c r="AA8" s="3">
+      <c r="AB8" s="3">
         <v>2369400</v>
       </c>
-      <c r="AB8" s="3">
+      <c r="AC8" s="3">
         <v>2154000</v>
       </c>
-      <c r="AC8" s="3">
+      <c r="AD8" s="3">
         <v>2006200</v>
       </c>
-      <c r="AD8" s="3">
+      <c r="AE8" s="3">
         <v>1989700</v>
       </c>
-      <c r="AE8" s="3">
+      <c r="AF8" s="3">
         <v>1910800</v>
       </c>
-      <c r="AF8" s="3">
+      <c r="AG8" s="3">
         <v>1912500</v>
       </c>
-      <c r="AG8" s="3">
+      <c r="AH8" s="3">
         <v>1925300</v>
       </c>
-      <c r="AH8" s="3">
+      <c r="AI8" s="3">
         <v>1853100</v>
       </c>
-      <c r="AI8" s="3">
+      <c r="AJ8" s="3">
         <v>1833700</v>
       </c>
-      <c r="AJ8" s="3">
+      <c r="AK8" s="3">
         <v>1898800</v>
       </c>
-      <c r="AK8" s="3">
+      <c r="AL8" s="3">
         <v>1898000</v>
       </c>
     </row>
-    <row r="9" spans="1:37" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:38" x14ac:dyDescent="0.2">
       <c r="C9" s="1" t="s">
         <v>4</v>
       </c>
       <c r="D9" s="3">
+        <v>5900</v>
+      </c>
+      <c r="E9" s="3">
         <v>7000</v>
       </c>
-      <c r="E9" s="3">
+      <c r="F9" s="3">
         <v>7600</v>
       </c>
-      <c r="F9" s="3">
+      <c r="G9" s="3">
         <v>7000</v>
       </c>
-      <c r="G9" s="3">
+      <c r="H9" s="3">
         <v>7100</v>
       </c>
-      <c r="H9" s="3">
+      <c r="I9" s="3">
         <v>9400</v>
-      </c>
-      <c r="I9" s="3">
-        <v>6800</v>
       </c>
       <c r="J9" s="3">
         <v>6800</v>
       </c>
       <c r="K9" s="3">
+        <v>6800</v>
+      </c>
+      <c r="L9" s="3">
         <v>7100</v>
       </c>
-      <c r="L9" s="3" t="s">
-        <v>5</v>
-      </c>
       <c r="M9" s="3" t="s">
         <v>5</v>
       </c>
@@ -1000,38 +1006,41 @@
       <c r="AK9" s="3" t="s">
         <v>5</v>
       </c>
+      <c r="AL9" s="3" t="s">
+        <v>5</v>
+      </c>
     </row>
-    <row r="10" spans="1:37" x14ac:dyDescent="0.2">
+    <row r="10" spans="1:38" x14ac:dyDescent="0.2">
       <c r="C10" s="1" t="s">
         <v>6</v>
       </c>
       <c r="D10" s="3">
+        <v>1795600</v>
+      </c>
+      <c r="E10" s="3">
         <v>2137100</v>
       </c>
-      <c r="E10" s="3">
+      <c r="F10" s="3">
         <v>1790000</v>
       </c>
-      <c r="F10" s="3">
+      <c r="G10" s="3">
         <v>2137400</v>
       </c>
-      <c r="G10" s="3">
+      <c r="H10" s="3">
         <v>2212800</v>
       </c>
-      <c r="H10" s="3">
+      <c r="I10" s="3">
         <v>1255200</v>
       </c>
-      <c r="I10" s="3">
+      <c r="J10" s="3">
         <v>2094600</v>
       </c>
-      <c r="J10" s="3">
+      <c r="K10" s="3">
         <v>1741800</v>
       </c>
-      <c r="K10" s="3">
+      <c r="L10" s="3">
         <v>2084600</v>
       </c>
-      <c r="L10" s="3" t="s">
-        <v>5</v>
-      </c>
       <c r="M10" s="3" t="s">
         <v>5</v>
       </c>
@@ -1107,8 +1116,11 @@
       <c r="AK10" s="3" t="s">
         <v>5</v>
       </c>
+      <c r="AL10" s="3" t="s">
+        <v>5</v>
+      </c>
     </row>
-    <row r="11" spans="1:37" x14ac:dyDescent="0.2">
+    <row r="11" spans="1:38" x14ac:dyDescent="0.2">
       <c r="C11" s="1" t="s">
         <v>7</v>
       </c>
@@ -1146,8 +1158,9 @@
       <c r="AI11" s="3"/>
       <c r="AJ11" s="3"/>
       <c r="AK11" s="3"/>
+      <c r="AL11" s="3"/>
     </row>
-    <row r="12" spans="1:37" x14ac:dyDescent="0.2">
+    <row r="12" spans="1:38" x14ac:dyDescent="0.2">
       <c r="C12" s="1" t="s">
         <v>8</v>
       </c>
@@ -1253,8 +1266,11 @@
       <c r="AK12" s="3" t="s">
         <v>5</v>
       </c>
+      <c r="AL12" s="3" t="s">
+        <v>5</v>
+      </c>
     </row>
-    <row r="13" spans="1:37" x14ac:dyDescent="0.2">
+    <row r="13" spans="1:38" x14ac:dyDescent="0.2">
       <c r="C13" s="1" t="s">
         <v>9</v>
       </c>
@@ -1360,38 +1376,41 @@
       <c r="AK13" s="3">
         <v>0</v>
       </c>
+      <c r="AL13" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="14" spans="1:37" x14ac:dyDescent="0.2">
+    <row r="14" spans="1:38" x14ac:dyDescent="0.2">
       <c r="C14" s="1" t="s">
         <v>10</v>
       </c>
       <c r="D14" s="3">
+        <v>200</v>
+      </c>
+      <c r="E14" s="3">
         <v>6200</v>
       </c>
-      <c r="E14" s="3">
-        <v>0</v>
-      </c>
       <c r="F14" s="3">
+        <v>0</v>
+      </c>
+      <c r="G14" s="3">
         <v>4600</v>
       </c>
-      <c r="G14" s="3">
-        <v>12300</v>
-      </c>
       <c r="H14" s="3">
+        <v>8400</v>
+      </c>
+      <c r="I14" s="3">
         <v>-1700</v>
       </c>
-      <c r="I14" s="3">
-        <v>0</v>
-      </c>
       <c r="J14" s="3">
+        <v>0</v>
+      </c>
+      <c r="K14" s="3">
         <v>-200</v>
       </c>
-      <c r="K14" s="3">
+      <c r="L14" s="3">
         <v>42300</v>
       </c>
-      <c r="L14" s="3">
-        <v>0</v>
-      </c>
       <c r="M14" s="3">
         <v>0</v>
       </c>
@@ -1467,115 +1486,121 @@
       <c r="AK14" s="3">
         <v>0</v>
       </c>
+      <c r="AL14" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="15" spans="1:37" x14ac:dyDescent="0.2">
+    <row r="15" spans="1:38" x14ac:dyDescent="0.2">
       <c r="C15" s="1" t="s">
         <v>11</v>
       </c>
       <c r="D15" s="3">
+        <v>210100</v>
+      </c>
+      <c r="E15" s="3">
         <v>150600</v>
       </c>
-      <c r="E15" s="3">
+      <c r="F15" s="3">
         <v>164900</v>
       </c>
-      <c r="F15" s="3">
+      <c r="G15" s="3">
         <v>149400</v>
       </c>
-      <c r="G15" s="3">
-        <v>148900</v>
-      </c>
       <c r="H15" s="3">
+        <v>205400</v>
+      </c>
+      <c r="I15" s="3">
         <v>144200</v>
       </c>
-      <c r="I15" s="3">
+      <c r="J15" s="3">
         <v>130600</v>
       </c>
-      <c r="J15" s="3">
+      <c r="K15" s="3">
         <v>130000</v>
       </c>
-      <c r="K15" s="3">
+      <c r="L15" s="3">
         <v>130100</v>
       </c>
-      <c r="L15" s="3">
+      <c r="M15" s="3">
         <v>-101500</v>
       </c>
-      <c r="M15" s="3">
+      <c r="N15" s="3">
         <v>-92100</v>
       </c>
-      <c r="N15" s="3">
+      <c r="O15" s="3">
         <v>-100700</v>
       </c>
-      <c r="O15" s="3">
+      <c r="P15" s="3">
         <v>-101400</v>
       </c>
-      <c r="P15" s="3">
+      <c r="Q15" s="3">
         <v>-98200</v>
       </c>
-      <c r="Q15" s="3">
+      <c r="R15" s="3">
         <v>-97600</v>
       </c>
-      <c r="R15" s="3">
+      <c r="S15" s="3">
         <v>-97400</v>
       </c>
-      <c r="S15" s="3">
+      <c r="T15" s="3">
         <v>-100600</v>
       </c>
-      <c r="T15" s="3">
+      <c r="U15" s="3">
         <v>-99400</v>
       </c>
-      <c r="U15" s="3">
+      <c r="V15" s="3">
         <v>-99600</v>
       </c>
-      <c r="V15" s="3">
+      <c r="W15" s="3">
         <v>-96100</v>
       </c>
-      <c r="W15" s="3">
+      <c r="X15" s="3">
         <v>-109500</v>
       </c>
-      <c r="X15" s="3">
+      <c r="Y15" s="3">
         <v>-115200</v>
       </c>
-      <c r="Y15" s="3">
+      <c r="Z15" s="3">
         <v>-112100</v>
       </c>
-      <c r="Z15" s="3">
+      <c r="AA15" s="3">
         <v>-104100</v>
       </c>
-      <c r="AA15" s="3">
+      <c r="AB15" s="3">
         <v>-88900</v>
       </c>
-      <c r="AB15" s="3">
+      <c r="AC15" s="3">
         <v>-50500</v>
       </c>
-      <c r="AC15" s="3">
+      <c r="AD15" s="3">
         <v>-47800</v>
       </c>
-      <c r="AD15" s="3">
+      <c r="AE15" s="3">
         <v>-44700</v>
       </c>
-      <c r="AE15" s="3">
+      <c r="AF15" s="3">
         <v>-40700</v>
       </c>
-      <c r="AF15" s="3">
+      <c r="AG15" s="3">
         <v>-39500</v>
       </c>
-      <c r="AG15" s="3">
+      <c r="AH15" s="3">
         <v>-40300</v>
       </c>
-      <c r="AH15" s="3">
+      <c r="AI15" s="3">
         <v>-40800</v>
       </c>
-      <c r="AI15" s="3">
+      <c r="AJ15" s="3">
         <v>-44500</v>
       </c>
-      <c r="AJ15" s="3">
+      <c r="AK15" s="3">
         <v>-54800</v>
       </c>
-      <c r="AK15" s="3">
+      <c r="AL15" s="3">
         <v>-53700</v>
       </c>
     </row>
-    <row r="16" spans="1:37" x14ac:dyDescent="0.2">
+    <row r="16" spans="1:38" x14ac:dyDescent="0.2">
       <c r="D16" s="3"/>
       <c r="E16" s="3"/>
       <c r="F16" s="3"/>
@@ -1610,222 +1635,229 @@
       <c r="AI16" s="3"/>
       <c r="AJ16" s="3"/>
       <c r="AK16" s="3"/>
+      <c r="AL16" s="3"/>
     </row>
-    <row r="17" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="17" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C17" s="1" t="s">
         <v>12</v>
       </c>
       <c r="D17" s="3">
+        <v>1211300</v>
+      </c>
+      <c r="E17" s="3">
         <v>1684700</v>
       </c>
-      <c r="E17" s="3">
+      <c r="F17" s="3">
         <v>887900</v>
       </c>
-      <c r="F17" s="3">
+      <c r="G17" s="3">
         <v>1233600</v>
       </c>
-      <c r="G17" s="3">
+      <c r="H17" s="3">
         <v>1363800</v>
       </c>
-      <c r="H17" s="3">
+      <c r="I17" s="3">
         <v>1160500</v>
       </c>
-      <c r="I17" s="3">
+      <c r="J17" s="3">
         <v>1189600</v>
       </c>
-      <c r="J17" s="3">
+      <c r="K17" s="3">
         <v>1049500</v>
       </c>
-      <c r="K17" s="3">
+      <c r="L17" s="3">
         <v>1131700</v>
       </c>
-      <c r="L17" s="3">
+      <c r="M17" s="3">
         <v>1897900</v>
       </c>
-      <c r="M17" s="3">
+      <c r="N17" s="3">
         <v>1245200</v>
       </c>
-      <c r="N17" s="3">
+      <c r="O17" s="3">
         <v>1121400</v>
       </c>
-      <c r="O17" s="3">
+      <c r="P17" s="3">
         <v>861300</v>
       </c>
-      <c r="P17" s="3">
+      <c r="Q17" s="3">
         <v>772200</v>
       </c>
-      <c r="Q17" s="3">
+      <c r="R17" s="3">
         <v>616800</v>
       </c>
-      <c r="R17" s="3">
+      <c r="S17" s="3">
         <v>573600</v>
       </c>
-      <c r="S17" s="3">
+      <c r="T17" s="3">
         <v>625700</v>
       </c>
-      <c r="T17" s="3">
+      <c r="U17" s="3">
         <v>727900</v>
       </c>
-      <c r="U17" s="3">
+      <c r="V17" s="3">
         <v>721100</v>
       </c>
-      <c r="V17" s="3">
+      <c r="W17" s="3">
         <v>966200</v>
       </c>
-      <c r="W17" s="3">
+      <c r="X17" s="3">
         <v>926000</v>
       </c>
-      <c r="X17" s="3">
+      <c r="Y17" s="3">
         <v>1019500</v>
       </c>
-      <c r="Y17" s="3">
+      <c r="Z17" s="3">
         <v>1190700</v>
       </c>
-      <c r="Z17" s="3">
+      <c r="AA17" s="3">
         <v>1111900</v>
       </c>
-      <c r="AA17" s="3">
+      <c r="AB17" s="3">
         <v>1098300</v>
       </c>
-      <c r="AB17" s="3">
+      <c r="AC17" s="3">
         <v>1157200</v>
       </c>
-      <c r="AC17" s="3">
+      <c r="AD17" s="3">
         <v>918800</v>
       </c>
-      <c r="AD17" s="3">
+      <c r="AE17" s="3">
         <v>752200</v>
       </c>
-      <c r="AE17" s="3">
+      <c r="AF17" s="3">
         <v>877900</v>
       </c>
-      <c r="AF17" s="3">
+      <c r="AG17" s="3">
         <v>1026000</v>
       </c>
-      <c r="AG17" s="3">
+      <c r="AH17" s="3">
         <v>926800</v>
       </c>
-      <c r="AH17" s="3">
+      <c r="AI17" s="3">
         <v>906500</v>
       </c>
-      <c r="AI17" s="3">
+      <c r="AJ17" s="3">
         <v>830000</v>
       </c>
-      <c r="AJ17" s="3">
+      <c r="AK17" s="3">
         <v>903100</v>
       </c>
-      <c r="AK17" s="3">
+      <c r="AL17" s="3">
         <v>963600</v>
       </c>
     </row>
-    <row r="18" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="18" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C18" s="1" t="s">
         <v>13</v>
       </c>
       <c r="D18" s="3">
+        <v>590100</v>
+      </c>
+      <c r="E18" s="3">
         <v>459500</v>
       </c>
-      <c r="E18" s="3">
+      <c r="F18" s="3">
         <v>909700</v>
       </c>
-      <c r="F18" s="3">
+      <c r="G18" s="3">
         <v>910800</v>
       </c>
-      <c r="G18" s="3">
+      <c r="H18" s="3">
         <v>856000</v>
       </c>
-      <c r="H18" s="3">
+      <c r="I18" s="3">
         <v>104100</v>
       </c>
-      <c r="I18" s="3">
+      <c r="J18" s="3">
         <v>911700</v>
       </c>
-      <c r="J18" s="3">
+      <c r="K18" s="3">
         <v>699100</v>
       </c>
-      <c r="K18" s="3">
+      <c r="L18" s="3">
         <v>960100</v>
       </c>
-      <c r="L18" s="3">
+      <c r="M18" s="3">
         <v>1564300</v>
       </c>
-      <c r="M18" s="3">
+      <c r="N18" s="3">
         <v>1547000</v>
       </c>
-      <c r="N18" s="3">
+      <c r="O18" s="3">
         <v>1365800</v>
       </c>
-      <c r="O18" s="3">
+      <c r="P18" s="3">
         <v>1403000</v>
       </c>
-      <c r="P18" s="3">
+      <c r="Q18" s="3">
         <v>1253800</v>
       </c>
-      <c r="Q18" s="3">
+      <c r="R18" s="3">
         <v>1245400</v>
       </c>
-      <c r="R18" s="3">
+      <c r="S18" s="3">
         <v>1213900</v>
       </c>
-      <c r="S18" s="3">
+      <c r="T18" s="3">
         <v>1096400</v>
       </c>
-      <c r="T18" s="3">
+      <c r="U18" s="3">
         <v>1000300</v>
       </c>
-      <c r="U18" s="3">
+      <c r="V18" s="3">
         <v>1028700</v>
       </c>
-      <c r="V18" s="3">
+      <c r="W18" s="3">
         <v>891200</v>
       </c>
-      <c r="W18" s="3">
+      <c r="X18" s="3">
         <v>1102100</v>
       </c>
-      <c r="X18" s="3">
+      <c r="Y18" s="3">
         <v>1196900</v>
       </c>
-      <c r="Y18" s="3">
+      <c r="Z18" s="3">
         <v>1097100</v>
       </c>
-      <c r="Z18" s="3">
+      <c r="AA18" s="3">
         <v>1241200</v>
       </c>
-      <c r="AA18" s="3">
+      <c r="AB18" s="3">
         <v>1271100</v>
       </c>
-      <c r="AB18" s="3">
+      <c r="AC18" s="3">
         <v>996800</v>
       </c>
-      <c r="AC18" s="3">
+      <c r="AD18" s="3">
         <v>1087400</v>
       </c>
-      <c r="AD18" s="3">
+      <c r="AE18" s="3">
         <v>1237400</v>
       </c>
-      <c r="AE18" s="3">
+      <c r="AF18" s="3">
         <v>1032900</v>
       </c>
-      <c r="AF18" s="3">
+      <c r="AG18" s="3">
         <v>886500</v>
       </c>
-      <c r="AG18" s="3">
+      <c r="AH18" s="3">
         <v>998500</v>
       </c>
-      <c r="AH18" s="3">
+      <c r="AI18" s="3">
         <v>946600</v>
       </c>
-      <c r="AI18" s="3">
+      <c r="AJ18" s="3">
         <v>1003700</v>
       </c>
-      <c r="AJ18" s="3">
+      <c r="AK18" s="3">
         <v>995700</v>
       </c>
-      <c r="AK18" s="3">
+      <c r="AL18" s="3">
         <v>934400</v>
       </c>
     </row>
-    <row r="19" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="19" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C19" s="1" t="s">
         <v>14</v>
       </c>
@@ -1863,222 +1895,229 @@
       <c r="AI19" s="3"/>
       <c r="AJ19" s="3"/>
       <c r="AK19" s="3"/>
+      <c r="AL19" s="3"/>
     </row>
-    <row r="20" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="20" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C20" s="1" t="s">
         <v>15</v>
       </c>
       <c r="D20" s="3">
+        <v>2800</v>
+      </c>
+      <c r="E20" s="3">
         <v>26000</v>
       </c>
-      <c r="E20" s="3">
+      <c r="F20" s="3">
         <v>-4400</v>
       </c>
-      <c r="F20" s="3">
+      <c r="G20" s="3">
         <v>1400</v>
       </c>
-      <c r="G20" s="3">
-        <v>-7500</v>
-      </c>
       <c r="H20" s="3">
+        <v>-3500</v>
+      </c>
+      <c r="I20" s="3">
         <v>11600</v>
       </c>
-      <c r="I20" s="3">
+      <c r="J20" s="3">
         <v>-14500</v>
       </c>
-      <c r="J20" s="3">
+      <c r="K20" s="3">
         <v>32600</v>
       </c>
-      <c r="K20" s="3">
+      <c r="L20" s="3">
         <v>-56500</v>
       </c>
-      <c r="L20" s="3">
+      <c r="M20" s="3">
         <v>-1017300</v>
       </c>
-      <c r="M20" s="3">
+      <c r="N20" s="3">
         <v>-606600</v>
       </c>
-      <c r="N20" s="3">
+      <c r="O20" s="3">
         <v>-375600</v>
       </c>
-      <c r="O20" s="3">
+      <c r="P20" s="3">
         <v>-505900</v>
       </c>
-      <c r="P20" s="3">
+      <c r="Q20" s="3">
         <v>-806400</v>
       </c>
-      <c r="Q20" s="3">
+      <c r="R20" s="3">
         <v>-394200</v>
       </c>
-      <c r="R20" s="3">
+      <c r="S20" s="3">
         <v>-406900</v>
       </c>
-      <c r="S20" s="3">
+      <c r="T20" s="3">
         <v>-399500</v>
       </c>
-      <c r="T20" s="3">
+      <c r="U20" s="3">
         <v>-784600</v>
       </c>
-      <c r="U20" s="3">
+      <c r="V20" s="3">
         <v>-508200</v>
       </c>
-      <c r="V20" s="3">
+      <c r="W20" s="3">
         <v>-674600</v>
       </c>
-      <c r="W20" s="3">
+      <c r="X20" s="3">
         <v>-492400</v>
       </c>
-      <c r="X20" s="3">
+      <c r="Y20" s="3">
         <v>-920900</v>
       </c>
-      <c r="Y20" s="3">
+      <c r="Z20" s="3">
         <v>-527400</v>
       </c>
-      <c r="Z20" s="3">
+      <c r="AA20" s="3">
         <v>-447200</v>
       </c>
-      <c r="AA20" s="3">
+      <c r="AB20" s="3">
         <v>-519600</v>
       </c>
-      <c r="AB20" s="3">
+      <c r="AC20" s="3">
         <v>-847700</v>
       </c>
-      <c r="AC20" s="3">
+      <c r="AD20" s="3">
         <v>-418500</v>
       </c>
-      <c r="AD20" s="3">
+      <c r="AE20" s="3">
         <v>-401200</v>
       </c>
-      <c r="AE20" s="3">
+      <c r="AF20" s="3">
         <v>-355800</v>
       </c>
-      <c r="AF20" s="3">
+      <c r="AG20" s="3">
         <v>-756300</v>
       </c>
-      <c r="AG20" s="3">
+      <c r="AH20" s="3">
         <v>-671500</v>
       </c>
-      <c r="AH20" s="3">
+      <c r="AI20" s="3">
         <v>-417500</v>
       </c>
-      <c r="AI20" s="3">
+      <c r="AJ20" s="3">
         <v>-274500</v>
       </c>
-      <c r="AJ20" s="3">
+      <c r="AK20" s="3">
         <v>-821100</v>
       </c>
-      <c r="AK20" s="3">
+      <c r="AL20" s="3">
         <v>-531000</v>
       </c>
     </row>
-    <row r="21" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="21" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C21" s="1" t="s">
         <v>16</v>
       </c>
       <c r="D21" s="3">
+        <v>797400</v>
+      </c>
+      <c r="E21" s="3">
         <v>584100</v>
       </c>
-      <c r="E21" s="3">
+      <c r="F21" s="3">
         <v>1079100</v>
       </c>
-      <c r="F21" s="3">
+      <c r="G21" s="3">
         <v>1058900</v>
       </c>
-      <c r="G21" s="3">
-        <v>1012400</v>
-      </c>
       <c r="H21" s="3">
+        <v>1064900</v>
+      </c>
+      <c r="I21" s="3">
         <v>236700</v>
       </c>
-      <c r="I21" s="3">
+      <c r="J21" s="3">
         <v>1056800</v>
       </c>
-      <c r="J21" s="3">
+      <c r="K21" s="3">
         <v>796500</v>
       </c>
-      <c r="K21" s="3">
+      <c r="L21" s="3">
         <v>1146700</v>
       </c>
-      <c r="L21" s="3">
+      <c r="M21" s="3">
         <v>732200</v>
       </c>
-      <c r="M21" s="3">
+      <c r="N21" s="3">
         <v>1110000</v>
       </c>
-      <c r="N21" s="3">
+      <c r="O21" s="3">
         <v>1165700</v>
       </c>
-      <c r="O21" s="3">
+      <c r="P21" s="3">
         <v>1065700</v>
       </c>
-      <c r="P21" s="3">
+      <c r="Q21" s="3">
         <v>603300</v>
       </c>
-      <c r="Q21" s="3">
+      <c r="R21" s="3">
         <v>1000500</v>
       </c>
-      <c r="R21" s="3">
+      <c r="S21" s="3">
         <v>991500</v>
       </c>
-      <c r="S21" s="3">
+      <c r="T21" s="3">
         <v>799800</v>
       </c>
-      <c r="T21" s="3">
+      <c r="U21" s="3">
         <v>316900</v>
       </c>
-      <c r="U21" s="3">
+      <c r="V21" s="3">
         <v>622000</v>
       </c>
-      <c r="V21" s="3">
+      <c r="W21" s="3">
         <v>315300</v>
       </c>
-      <c r="W21" s="3">
+      <c r="X21" s="3">
         <v>721900</v>
       </c>
-      <c r="X21" s="3">
+      <c r="Y21" s="3">
         <v>396300</v>
       </c>
-      <c r="Y21" s="3">
+      <c r="Z21" s="3">
         <v>686600</v>
       </c>
-      <c r="Z21" s="3">
+      <c r="AA21" s="3">
         <v>902900</v>
       </c>
-      <c r="AA21" s="3">
+      <c r="AB21" s="3">
         <v>845100</v>
       </c>
-      <c r="AB21" s="3">
+      <c r="AC21" s="3">
         <v>210800</v>
       </c>
-      <c r="AC21" s="3">
+      <c r="AD21" s="3">
         <v>727400</v>
       </c>
-      <c r="AD21" s="3">
+      <c r="AE21" s="3">
         <v>892200</v>
       </c>
-      <c r="AE21" s="3">
+      <c r="AF21" s="3">
         <v>727700</v>
       </c>
-      <c r="AF21" s="3">
+      <c r="AG21" s="3">
         <v>180100</v>
       </c>
-      <c r="AG21" s="3">
+      <c r="AH21" s="3">
         <v>377800</v>
       </c>
-      <c r="AH21" s="3">
+      <c r="AI21" s="3">
         <v>580800</v>
       </c>
-      <c r="AI21" s="3">
+      <c r="AJ21" s="3">
         <v>784400</v>
       </c>
-      <c r="AJ21" s="3">
+      <c r="AK21" s="3">
         <v>229400</v>
       </c>
-      <c r="AK21" s="3">
+      <c r="AL21" s="3">
         <v>457200</v>
       </c>
     </row>
-    <row r="22" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="22" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C22" s="1" t="s">
         <v>17</v>
       </c>
@@ -2106,8 +2145,8 @@
       <c r="K22" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="L22" s="3">
-        <v>0</v>
+      <c r="L22" s="3" t="s">
+        <v>5</v>
       </c>
       <c r="M22" s="3">
         <v>0</v>
@@ -2184,222 +2223,231 @@
       <c r="AK22" s="3">
         <v>0</v>
       </c>
+      <c r="AL22" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="23" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="23" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C23" s="1" t="s">
         <v>18</v>
       </c>
       <c r="D23" s="3">
+        <v>587100</v>
+      </c>
+      <c r="E23" s="3">
         <v>427300</v>
       </c>
-      <c r="E23" s="3">
+      <c r="F23" s="3">
         <v>914200</v>
       </c>
-      <c r="F23" s="3">
+      <c r="G23" s="3">
         <v>904900</v>
       </c>
-      <c r="G23" s="3">
+      <c r="H23" s="3">
         <v>851200</v>
       </c>
-      <c r="H23" s="3">
+      <c r="I23" s="3">
         <v>94200</v>
       </c>
-      <c r="I23" s="3">
+      <c r="J23" s="3">
         <v>926200</v>
       </c>
-      <c r="J23" s="3">
+      <c r="K23" s="3">
         <v>666800</v>
       </c>
-      <c r="K23" s="3">
+      <c r="L23" s="3">
         <v>974300</v>
       </c>
-      <c r="L23" s="3">
+      <c r="M23" s="3">
         <v>546900</v>
       </c>
-      <c r="M23" s="3">
+      <c r="N23" s="3">
         <v>940400</v>
       </c>
-      <c r="N23" s="3">
+      <c r="O23" s="3">
         <v>990200</v>
       </c>
-      <c r="O23" s="3">
+      <c r="P23" s="3">
         <v>897100</v>
       </c>
-      <c r="P23" s="3">
+      <c r="Q23" s="3">
         <v>447400</v>
       </c>
-      <c r="Q23" s="3">
+      <c r="R23" s="3">
         <v>851200</v>
       </c>
-      <c r="R23" s="3">
+      <c r="S23" s="3">
         <v>807000</v>
       </c>
-      <c r="S23" s="3">
+      <c r="T23" s="3">
         <v>696900</v>
       </c>
-      <c r="T23" s="3">
+      <c r="U23" s="3">
         <v>215700</v>
       </c>
-      <c r="U23" s="3">
+      <c r="V23" s="3">
         <v>520500</v>
       </c>
-      <c r="V23" s="3">
+      <c r="W23" s="3">
         <v>216600</v>
       </c>
-      <c r="W23" s="3">
+      <c r="X23" s="3">
         <v>609600</v>
       </c>
-      <c r="X23" s="3">
+      <c r="Y23" s="3">
         <v>276000</v>
       </c>
-      <c r="Y23" s="3">
+      <c r="Z23" s="3">
         <v>569700</v>
       </c>
-      <c r="Z23" s="3">
+      <c r="AA23" s="3">
         <v>794000</v>
       </c>
-      <c r="AA23" s="3">
+      <c r="AB23" s="3">
         <v>751500</v>
       </c>
-      <c r="AB23" s="3">
+      <c r="AC23" s="3">
         <v>149100</v>
       </c>
-      <c r="AC23" s="3">
+      <c r="AD23" s="3">
         <v>668900</v>
       </c>
-      <c r="AD23" s="3">
+      <c r="AE23" s="3">
         <v>836200</v>
       </c>
-      <c r="AE23" s="3">
+      <c r="AF23" s="3">
         <v>677100</v>
       </c>
-      <c r="AF23" s="3">
+      <c r="AG23" s="3">
         <v>130200</v>
       </c>
-      <c r="AG23" s="3">
+      <c r="AH23" s="3">
         <v>327000</v>
       </c>
-      <c r="AH23" s="3">
+      <c r="AI23" s="3">
         <v>529200</v>
       </c>
-      <c r="AI23" s="3">
+      <c r="AJ23" s="3">
         <v>729200</v>
       </c>
-      <c r="AJ23" s="3">
+      <c r="AK23" s="3">
         <v>174600</v>
       </c>
-      <c r="AK23" s="3">
+      <c r="AL23" s="3">
         <v>403400</v>
       </c>
     </row>
-    <row r="24" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="24" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C24" s="1" t="s">
         <v>19</v>
       </c>
       <c r="D24" s="3">
+        <v>142600</v>
+      </c>
+      <c r="E24" s="3">
         <v>120000</v>
       </c>
-      <c r="E24" s="3">
+      <c r="F24" s="3">
         <v>216000</v>
       </c>
-      <c r="F24" s="3">
+      <c r="G24" s="3">
         <v>207100</v>
       </c>
-      <c r="G24" s="3">
+      <c r="H24" s="3">
         <v>227000</v>
       </c>
-      <c r="H24" s="3">
+      <c r="I24" s="3">
         <v>21000</v>
       </c>
-      <c r="I24" s="3">
+      <c r="J24" s="3">
         <v>244100</v>
       </c>
-      <c r="J24" s="3">
+      <c r="K24" s="3">
         <v>160200</v>
       </c>
-      <c r="K24" s="3">
+      <c r="L24" s="3">
         <v>248300</v>
       </c>
-      <c r="L24" s="3">
+      <c r="M24" s="3">
         <v>148500</v>
       </c>
-      <c r="M24" s="3">
+      <c r="N24" s="3">
         <v>259000</v>
       </c>
-      <c r="N24" s="3">
+      <c r="O24" s="3">
         <v>240200</v>
       </c>
-      <c r="O24" s="3">
+      <c r="P24" s="3">
         <v>225300</v>
       </c>
-      <c r="P24" s="3">
+      <c r="Q24" s="3">
         <v>113100</v>
       </c>
-      <c r="Q24" s="3">
+      <c r="R24" s="3">
         <v>232900</v>
       </c>
-      <c r="R24" s="3">
+      <c r="S24" s="3">
         <v>193200</v>
       </c>
-      <c r="S24" s="3">
+      <c r="T24" s="3">
         <v>164900</v>
       </c>
-      <c r="T24" s="3">
+      <c r="U24" s="3">
         <v>53200</v>
       </c>
-      <c r="U24" s="3">
+      <c r="V24" s="3">
         <v>118800</v>
       </c>
-      <c r="V24" s="3">
+      <c r="W24" s="3">
         <v>50000</v>
       </c>
-      <c r="W24" s="3">
+      <c r="X24" s="3">
         <v>157800</v>
       </c>
-      <c r="X24" s="3">
+      <c r="Y24" s="3">
         <v>79200</v>
       </c>
-      <c r="Y24" s="3">
+      <c r="Z24" s="3">
         <v>115700</v>
       </c>
-      <c r="Z24" s="3">
+      <c r="AA24" s="3">
         <v>215500</v>
       </c>
-      <c r="AA24" s="3">
+      <c r="AB24" s="3">
         <v>192300</v>
       </c>
-      <c r="AB24" s="3">
+      <c r="AC24" s="3">
         <v>39300</v>
       </c>
-      <c r="AC24" s="3">
+      <c r="AD24" s="3">
         <v>179200</v>
       </c>
-      <c r="AD24" s="3">
+      <c r="AE24" s="3">
         <v>229900</v>
       </c>
-      <c r="AE24" s="3">
+      <c r="AF24" s="3">
         <v>177700</v>
       </c>
-      <c r="AF24" s="3">
+      <c r="AG24" s="3">
         <v>9000</v>
       </c>
-      <c r="AG24" s="3">
+      <c r="AH24" s="3">
         <v>77600</v>
       </c>
-      <c r="AH24" s="3">
+      <c r="AI24" s="3">
         <v>118800</v>
       </c>
-      <c r="AI24" s="3">
+      <c r="AJ24" s="3">
         <v>163600</v>
       </c>
-      <c r="AJ24" s="3">
+      <c r="AK24" s="3">
         <v>30300</v>
       </c>
-      <c r="AK24" s="3">
+      <c r="AL24" s="3">
         <v>80000</v>
       </c>
     </row>
-    <row r="25" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="25" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C25" s="1" t="s">
         <v>20</v>
       </c>
@@ -2505,222 +2553,231 @@
       <c r="AK25" s="3">
         <v>0</v>
       </c>
+      <c r="AL25" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="26" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="26" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C26" s="1" t="s">
         <v>21</v>
       </c>
       <c r="D26" s="3">
+        <v>444500</v>
+      </c>
+      <c r="E26" s="3">
         <v>307400</v>
       </c>
-      <c r="E26" s="3">
+      <c r="F26" s="3">
         <v>698200</v>
       </c>
-      <c r="F26" s="3">
+      <c r="G26" s="3">
         <v>697800</v>
       </c>
-      <c r="G26" s="3">
+      <c r="H26" s="3">
         <v>624200</v>
       </c>
-      <c r="H26" s="3">
+      <c r="I26" s="3">
         <v>73200</v>
       </c>
-      <c r="I26" s="3">
+      <c r="J26" s="3">
         <v>682000</v>
       </c>
-      <c r="J26" s="3">
+      <c r="K26" s="3">
         <v>506600</v>
       </c>
-      <c r="K26" s="3">
+      <c r="L26" s="3">
         <v>726000</v>
       </c>
-      <c r="L26" s="3">
+      <c r="M26" s="3">
         <v>398500</v>
       </c>
-      <c r="M26" s="3">
+      <c r="N26" s="3">
         <v>681400</v>
       </c>
-      <c r="N26" s="3">
+      <c r="O26" s="3">
         <v>750000</v>
       </c>
-      <c r="O26" s="3">
+      <c r="P26" s="3">
         <v>671800</v>
       </c>
-      <c r="P26" s="3">
+      <c r="Q26" s="3">
         <v>334300</v>
       </c>
-      <c r="Q26" s="3">
+      <c r="R26" s="3">
         <v>618300</v>
       </c>
-      <c r="R26" s="3">
+      <c r="S26" s="3">
         <v>613800</v>
       </c>
-      <c r="S26" s="3">
+      <c r="T26" s="3">
         <v>532000</v>
       </c>
-      <c r="T26" s="3">
+      <c r="U26" s="3">
         <v>162400</v>
       </c>
-      <c r="U26" s="3">
+      <c r="V26" s="3">
         <v>401700</v>
       </c>
-      <c r="V26" s="3">
+      <c r="W26" s="3">
         <v>166500</v>
       </c>
-      <c r="W26" s="3">
+      <c r="X26" s="3">
         <v>451800</v>
       </c>
-      <c r="X26" s="3">
+      <c r="Y26" s="3">
         <v>196800</v>
       </c>
-      <c r="Y26" s="3">
+      <c r="Z26" s="3">
         <v>454000</v>
       </c>
-      <c r="Z26" s="3">
+      <c r="AA26" s="3">
         <v>578500</v>
       </c>
-      <c r="AA26" s="3">
+      <c r="AB26" s="3">
         <v>559200</v>
       </c>
-      <c r="AB26" s="3">
+      <c r="AC26" s="3">
         <v>109900</v>
       </c>
-      <c r="AC26" s="3">
+      <c r="AD26" s="3">
         <v>489700</v>
       </c>
-      <c r="AD26" s="3">
+      <c r="AE26" s="3">
         <v>606300</v>
       </c>
-      <c r="AE26" s="3">
+      <c r="AF26" s="3">
         <v>499400</v>
       </c>
-      <c r="AF26" s="3">
+      <c r="AG26" s="3">
         <v>121100</v>
       </c>
-      <c r="AG26" s="3">
+      <c r="AH26" s="3">
         <v>249400</v>
       </c>
-      <c r="AH26" s="3">
+      <c r="AI26" s="3">
         <v>410300</v>
       </c>
-      <c r="AI26" s="3">
+      <c r="AJ26" s="3">
         <v>565600</v>
       </c>
-      <c r="AJ26" s="3">
+      <c r="AK26" s="3">
         <v>144300</v>
       </c>
-      <c r="AK26" s="3">
+      <c r="AL26" s="3">
         <v>323500</v>
       </c>
     </row>
-    <row r="27" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="27" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C27" s="1" t="s">
         <v>22</v>
       </c>
       <c r="D27" s="3">
+        <v>391900</v>
+      </c>
+      <c r="E27" s="3">
         <v>261600</v>
       </c>
-      <c r="E27" s="3">
+      <c r="F27" s="3">
         <v>655100</v>
       </c>
-      <c r="F27" s="3">
+      <c r="G27" s="3">
         <v>647100</v>
       </c>
-      <c r="G27" s="3">
+      <c r="H27" s="3">
         <v>586900</v>
       </c>
-      <c r="H27" s="3">
+      <c r="I27" s="3">
         <v>25300</v>
       </c>
-      <c r="I27" s="3">
+      <c r="J27" s="3">
         <v>643700</v>
       </c>
-      <c r="J27" s="3">
+      <c r="K27" s="3">
         <v>449800</v>
       </c>
-      <c r="K27" s="3">
+      <c r="L27" s="3">
         <v>677400</v>
       </c>
-      <c r="L27" s="3">
+      <c r="M27" s="3">
         <v>338800</v>
       </c>
-      <c r="M27" s="3">
+      <c r="N27" s="3">
         <v>640600</v>
       </c>
-      <c r="N27" s="3">
+      <c r="O27" s="3">
         <v>684400</v>
       </c>
-      <c r="O27" s="3">
+      <c r="P27" s="3">
         <v>631400</v>
       </c>
-      <c r="P27" s="3">
+      <c r="Q27" s="3">
         <v>279500</v>
       </c>
-      <c r="Q27" s="3">
+      <c r="R27" s="3">
         <v>570700</v>
       </c>
-      <c r="R27" s="3">
+      <c r="S27" s="3">
         <v>552600</v>
       </c>
-      <c r="S27" s="3">
+      <c r="T27" s="3">
         <v>482000</v>
       </c>
-      <c r="T27" s="3">
+      <c r="U27" s="3">
         <v>112600</v>
       </c>
-      <c r="U27" s="3">
+      <c r="V27" s="3">
         <v>358800</v>
       </c>
-      <c r="V27" s="3">
+      <c r="W27" s="3">
         <v>100500</v>
       </c>
-      <c r="W27" s="3">
+      <c r="X27" s="3">
         <v>412900</v>
       </c>
-      <c r="X27" s="3">
+      <c r="Y27" s="3">
         <v>174900</v>
       </c>
-      <c r="Y27" s="3">
+      <c r="Z27" s="3">
         <v>410100</v>
       </c>
-      <c r="Z27" s="3">
+      <c r="AA27" s="3">
         <v>537700</v>
       </c>
-      <c r="AA27" s="3">
+      <c r="AB27" s="3">
         <v>517500</v>
       </c>
-      <c r="AB27" s="3">
+      <c r="AC27" s="3">
         <v>76800</v>
       </c>
-      <c r="AC27" s="3">
+      <c r="AD27" s="3">
         <v>453900</v>
       </c>
-      <c r="AD27" s="3">
+      <c r="AE27" s="3">
         <v>569900</v>
       </c>
-      <c r="AE27" s="3">
+      <c r="AF27" s="3">
         <v>463600</v>
       </c>
-      <c r="AF27" s="3">
+      <c r="AG27" s="3">
         <v>84900</v>
       </c>
-      <c r="AG27" s="3">
+      <c r="AH27" s="3">
         <v>212100</v>
       </c>
-      <c r="AH27" s="3">
+      <c r="AI27" s="3">
         <v>369000</v>
       </c>
-      <c r="AI27" s="3">
+      <c r="AJ27" s="3">
         <v>517600</v>
       </c>
-      <c r="AJ27" s="3">
+      <c r="AK27" s="3">
         <v>88500</v>
       </c>
-      <c r="AK27" s="3">
+      <c r="AL27" s="3">
         <v>275700</v>
       </c>
     </row>
-    <row r="28" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="28" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C28" s="1" t="s">
         <v>23</v>
       </c>
@@ -2826,8 +2883,11 @@
       <c r="AK28" s="3">
         <v>0</v>
       </c>
+      <c r="AL28" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="29" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="29" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C29" s="1" t="s">
         <v>24</v>
       </c>
@@ -2933,8 +2993,11 @@
       <c r="AK29" s="3">
         <v>0</v>
       </c>
+      <c r="AL29" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="30" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="30" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C30" s="1" t="s">
         <v>25</v>
       </c>
@@ -3040,8 +3103,11 @@
       <c r="AK30" s="3">
         <v>0</v>
       </c>
+      <c r="AL30" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="31" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="31" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C31" s="1" t="s">
         <v>26</v>
       </c>
@@ -3147,222 +3213,231 @@
       <c r="AK31" s="3">
         <v>0</v>
       </c>
+      <c r="AL31" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="32" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="32" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C32" s="1" t="s">
         <v>27</v>
       </c>
       <c r="D32" s="3">
+        <v>-2800</v>
+      </c>
+      <c r="E32" s="3">
         <v>-26000</v>
       </c>
-      <c r="E32" s="3">
+      <c r="F32" s="3">
         <v>4400</v>
       </c>
-      <c r="F32" s="3">
+      <c r="G32" s="3">
         <v>-1400</v>
       </c>
-      <c r="G32" s="3">
-        <v>7500</v>
-      </c>
       <c r="H32" s="3">
+        <v>3500</v>
+      </c>
+      <c r="I32" s="3">
         <v>-11600</v>
       </c>
-      <c r="I32" s="3">
+      <c r="J32" s="3">
         <v>14500</v>
       </c>
-      <c r="J32" s="3">
+      <c r="K32" s="3">
         <v>-32600</v>
       </c>
-      <c r="K32" s="3">
+      <c r="L32" s="3">
         <v>56500</v>
       </c>
-      <c r="L32" s="3">
+      <c r="M32" s="3">
         <v>1017300</v>
       </c>
-      <c r="M32" s="3">
+      <c r="N32" s="3">
         <v>606600</v>
       </c>
-      <c r="N32" s="3">
+      <c r="O32" s="3">
         <v>375600</v>
       </c>
-      <c r="O32" s="3">
+      <c r="P32" s="3">
         <v>505900</v>
       </c>
-      <c r="P32" s="3">
+      <c r="Q32" s="3">
         <v>806400</v>
       </c>
-      <c r="Q32" s="3">
+      <c r="R32" s="3">
         <v>394200</v>
       </c>
-      <c r="R32" s="3">
+      <c r="S32" s="3">
         <v>406900</v>
       </c>
-      <c r="S32" s="3">
+      <c r="T32" s="3">
         <v>399500</v>
       </c>
-      <c r="T32" s="3">
+      <c r="U32" s="3">
         <v>784600</v>
       </c>
-      <c r="U32" s="3">
+      <c r="V32" s="3">
         <v>508200</v>
       </c>
-      <c r="V32" s="3">
+      <c r="W32" s="3">
         <v>674600</v>
       </c>
-      <c r="W32" s="3">
+      <c r="X32" s="3">
         <v>492400</v>
       </c>
-      <c r="X32" s="3">
+      <c r="Y32" s="3">
         <v>920900</v>
       </c>
-      <c r="Y32" s="3">
+      <c r="Z32" s="3">
         <v>527400</v>
       </c>
-      <c r="Z32" s="3">
+      <c r="AA32" s="3">
         <v>447200</v>
       </c>
-      <c r="AA32" s="3">
+      <c r="AB32" s="3">
         <v>519600</v>
       </c>
-      <c r="AB32" s="3">
+      <c r="AC32" s="3">
         <v>847700</v>
       </c>
-      <c r="AC32" s="3">
+      <c r="AD32" s="3">
         <v>418500</v>
       </c>
-      <c r="AD32" s="3">
+      <c r="AE32" s="3">
         <v>401200</v>
       </c>
-      <c r="AE32" s="3">
+      <c r="AF32" s="3">
         <v>355800</v>
       </c>
-      <c r="AF32" s="3">
+      <c r="AG32" s="3">
         <v>756300</v>
       </c>
-      <c r="AG32" s="3">
+      <c r="AH32" s="3">
         <v>671500</v>
       </c>
-      <c r="AH32" s="3">
+      <c r="AI32" s="3">
         <v>417500</v>
       </c>
-      <c r="AI32" s="3">
+      <c r="AJ32" s="3">
         <v>274500</v>
       </c>
-      <c r="AJ32" s="3">
+      <c r="AK32" s="3">
         <v>821100</v>
       </c>
-      <c r="AK32" s="3">
+      <c r="AL32" s="3">
         <v>531000</v>
       </c>
     </row>
-    <row r="33" spans="2:37" x14ac:dyDescent="0.2">
+    <row r="33" spans="2:38" x14ac:dyDescent="0.2">
       <c r="C33" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D33" s="3">
+        <v>418800</v>
+      </c>
+      <c r="E33" s="3">
         <v>288500</v>
       </c>
-      <c r="E33" s="3">
+      <c r="F33" s="3">
         <v>688600</v>
       </c>
-      <c r="F33" s="3">
+      <c r="G33" s="3">
         <v>676000</v>
       </c>
-      <c r="G33" s="3">
+      <c r="H33" s="3">
         <v>613100</v>
       </c>
-      <c r="H33" s="3">
+      <c r="I33" s="3">
         <v>52500</v>
       </c>
-      <c r="I33" s="3">
+      <c r="J33" s="3">
         <v>668000</v>
       </c>
-      <c r="J33" s="3">
+      <c r="K33" s="3">
         <v>474700</v>
       </c>
-      <c r="K33" s="3">
+      <c r="L33" s="3">
         <v>700700</v>
       </c>
-      <c r="L33" s="3">
+      <c r="M33" s="3">
         <v>338800</v>
       </c>
-      <c r="M33" s="3">
+      <c r="N33" s="3">
         <v>640600</v>
       </c>
-      <c r="N33" s="3">
+      <c r="O33" s="3">
         <v>684400</v>
       </c>
-      <c r="O33" s="3">
+      <c r="P33" s="3">
         <v>631400</v>
       </c>
-      <c r="P33" s="3">
+      <c r="Q33" s="3">
         <v>279500</v>
       </c>
-      <c r="Q33" s="3">
+      <c r="R33" s="3">
         <v>570700</v>
       </c>
-      <c r="R33" s="3">
+      <c r="S33" s="3">
         <v>552600</v>
       </c>
-      <c r="S33" s="3">
+      <c r="T33" s="3">
         <v>482000</v>
       </c>
-      <c r="T33" s="3">
+      <c r="U33" s="3">
         <v>112600</v>
       </c>
-      <c r="U33" s="3">
+      <c r="V33" s="3">
         <v>358800</v>
       </c>
-      <c r="V33" s="3">
+      <c r="W33" s="3">
         <v>100500</v>
       </c>
-      <c r="W33" s="3">
+      <c r="X33" s="3">
         <v>412900</v>
       </c>
-      <c r="X33" s="3">
+      <c r="Y33" s="3">
         <v>174900</v>
       </c>
-      <c r="Y33" s="3">
+      <c r="Z33" s="3">
         <v>410100</v>
       </c>
-      <c r="Z33" s="3">
+      <c r="AA33" s="3">
         <v>537700</v>
       </c>
-      <c r="AA33" s="3">
+      <c r="AB33" s="3">
         <v>517500</v>
       </c>
-      <c r="AB33" s="3">
+      <c r="AC33" s="3">
         <v>76800</v>
       </c>
-      <c r="AC33" s="3">
+      <c r="AD33" s="3">
         <v>453900</v>
       </c>
-      <c r="AD33" s="3">
+      <c r="AE33" s="3">
         <v>569900</v>
       </c>
-      <c r="AE33" s="3">
+      <c r="AF33" s="3">
         <v>463600</v>
       </c>
-      <c r="AF33" s="3">
+      <c r="AG33" s="3">
         <v>84900</v>
       </c>
-      <c r="AG33" s="3">
+      <c r="AH33" s="3">
         <v>212100</v>
       </c>
-      <c r="AH33" s="3">
+      <c r="AI33" s="3">
         <v>369000</v>
       </c>
-      <c r="AI33" s="3">
+      <c r="AJ33" s="3">
         <v>517600</v>
       </c>
-      <c r="AJ33" s="3">
+      <c r="AK33" s="3">
         <v>88500</v>
       </c>
-      <c r="AK33" s="3">
+      <c r="AL33" s="3">
         <v>275700</v>
       </c>
     </row>
-    <row r="34" spans="2:37" x14ac:dyDescent="0.2">
+    <row r="34" spans="2:38" x14ac:dyDescent="0.2">
       <c r="C34" s="1" t="s">
         <v>29</v>
       </c>
@@ -3468,227 +3543,236 @@
       <c r="AK34" s="3">
         <v>0</v>
       </c>
+      <c r="AL34" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="35" spans="2:37" x14ac:dyDescent="0.2">
+    <row r="35" spans="2:38" x14ac:dyDescent="0.2">
       <c r="C35" s="1" t="s">
         <v>30</v>
       </c>
       <c r="D35" s="3">
+        <v>418800</v>
+      </c>
+      <c r="E35" s="3">
         <v>288500</v>
       </c>
-      <c r="E35" s="3">
+      <c r="F35" s="3">
         <v>688600</v>
       </c>
-      <c r="F35" s="3">
+      <c r="G35" s="3">
         <v>676000</v>
       </c>
-      <c r="G35" s="3">
+      <c r="H35" s="3">
         <v>613100</v>
       </c>
-      <c r="H35" s="3">
+      <c r="I35" s="3">
         <v>52500</v>
       </c>
-      <c r="I35" s="3">
+      <c r="J35" s="3">
         <v>668000</v>
       </c>
-      <c r="J35" s="3">
+      <c r="K35" s="3">
         <v>474700</v>
       </c>
-      <c r="K35" s="3">
+      <c r="L35" s="3">
         <v>700700</v>
       </c>
-      <c r="L35" s="3">
+      <c r="M35" s="3">
         <v>338800</v>
       </c>
-      <c r="M35" s="3">
+      <c r="N35" s="3">
         <v>640600</v>
       </c>
-      <c r="N35" s="3">
+      <c r="O35" s="3">
         <v>684400</v>
       </c>
-      <c r="O35" s="3">
+      <c r="P35" s="3">
         <v>631400</v>
       </c>
-      <c r="P35" s="3">
+      <c r="Q35" s="3">
         <v>279500</v>
       </c>
-      <c r="Q35" s="3">
+      <c r="R35" s="3">
         <v>570700</v>
       </c>
-      <c r="R35" s="3">
+      <c r="S35" s="3">
         <v>552600</v>
       </c>
-      <c r="S35" s="3">
+      <c r="T35" s="3">
         <v>482000</v>
       </c>
-      <c r="T35" s="3">
+      <c r="U35" s="3">
         <v>112600</v>
       </c>
-      <c r="U35" s="3">
+      <c r="V35" s="3">
         <v>358800</v>
       </c>
-      <c r="V35" s="3">
+      <c r="W35" s="3">
         <v>100500</v>
       </c>
-      <c r="W35" s="3">
+      <c r="X35" s="3">
         <v>412900</v>
       </c>
-      <c r="X35" s="3">
+      <c r="Y35" s="3">
         <v>174900</v>
       </c>
-      <c r="Y35" s="3">
+      <c r="Z35" s="3">
         <v>410100</v>
       </c>
-      <c r="Z35" s="3">
+      <c r="AA35" s="3">
         <v>537700</v>
       </c>
-      <c r="AA35" s="3">
+      <c r="AB35" s="3">
         <v>517500</v>
       </c>
-      <c r="AB35" s="3">
+      <c r="AC35" s="3">
         <v>76800</v>
       </c>
-      <c r="AC35" s="3">
+      <c r="AD35" s="3">
         <v>453900</v>
       </c>
-      <c r="AD35" s="3">
+      <c r="AE35" s="3">
         <v>569900</v>
       </c>
-      <c r="AE35" s="3">
+      <c r="AF35" s="3">
         <v>463600</v>
       </c>
-      <c r="AF35" s="3">
+      <c r="AG35" s="3">
         <v>84900</v>
       </c>
-      <c r="AG35" s="3">
+      <c r="AH35" s="3">
         <v>212100</v>
       </c>
-      <c r="AH35" s="3">
+      <c r="AI35" s="3">
         <v>369000</v>
       </c>
-      <c r="AI35" s="3">
+      <c r="AJ35" s="3">
         <v>517600</v>
       </c>
-      <c r="AJ35" s="3">
+      <c r="AK35" s="3">
         <v>88500</v>
       </c>
-      <c r="AK35" s="3">
+      <c r="AL35" s="3">
         <v>275700</v>
       </c>
     </row>
-    <row r="37" spans="2:37" x14ac:dyDescent="0.2">
+    <row r="37" spans="2:38" x14ac:dyDescent="0.2">
       <c r="B37" s="1" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="38" spans="2:37" x14ac:dyDescent="0.2">
+    <row r="38" spans="2:38" x14ac:dyDescent="0.2">
       <c r="C38" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D38" s="2">
+        <v>45747</v>
+      </c>
+      <c r="E38" s="2">
         <v>45657</v>
       </c>
-      <c r="E38" s="2">
+      <c r="F38" s="2">
         <v>45565</v>
       </c>
-      <c r="F38" s="2">
+      <c r="G38" s="2">
         <v>45473</v>
       </c>
-      <c r="G38" s="2">
+      <c r="H38" s="2">
         <v>45382</v>
       </c>
-      <c r="H38" s="2">
+      <c r="I38" s="2">
         <v>45291</v>
       </c>
-      <c r="I38" s="2">
+      <c r="J38" s="2">
         <v>45199</v>
       </c>
-      <c r="J38" s="2">
+      <c r="K38" s="2">
         <v>45107</v>
       </c>
-      <c r="K38" s="2">
+      <c r="L38" s="2">
         <v>45016</v>
       </c>
-      <c r="L38" s="2">
+      <c r="M38" s="2">
         <v>44926</v>
       </c>
-      <c r="M38" s="2">
+      <c r="N38" s="2">
         <v>44834</v>
       </c>
-      <c r="N38" s="2">
+      <c r="O38" s="2">
         <v>44742</v>
       </c>
-      <c r="O38" s="2">
+      <c r="P38" s="2">
         <v>44651</v>
       </c>
-      <c r="P38" s="2">
+      <c r="Q38" s="2">
         <v>44561</v>
       </c>
-      <c r="Q38" s="2">
+      <c r="R38" s="2">
         <v>44469</v>
       </c>
-      <c r="R38" s="2">
+      <c r="S38" s="2">
         <v>44377</v>
       </c>
-      <c r="S38" s="2">
+      <c r="T38" s="2">
         <v>44286</v>
       </c>
-      <c r="T38" s="2">
+      <c r="U38" s="2">
         <v>44196</v>
       </c>
-      <c r="U38" s="2">
+      <c r="V38" s="2">
         <v>44104</v>
       </c>
-      <c r="V38" s="2">
+      <c r="W38" s="2">
         <v>44012</v>
       </c>
-      <c r="W38" s="2">
+      <c r="X38" s="2">
         <v>43921</v>
       </c>
-      <c r="X38" s="2">
+      <c r="Y38" s="2">
         <v>43830</v>
       </c>
-      <c r="Y38" s="2">
+      <c r="Z38" s="2">
         <v>43738</v>
       </c>
-      <c r="Z38" s="2">
+      <c r="AA38" s="2">
         <v>43646</v>
       </c>
-      <c r="AA38" s="2">
+      <c r="AB38" s="2">
         <v>43555</v>
       </c>
-      <c r="AB38" s="2">
+      <c r="AC38" s="2">
         <v>43465</v>
       </c>
-      <c r="AC38" s="2">
+      <c r="AD38" s="2">
         <v>43373</v>
       </c>
-      <c r="AD38" s="2">
+      <c r="AE38" s="2">
         <v>43281</v>
       </c>
-      <c r="AE38" s="2">
+      <c r="AF38" s="2">
         <v>43190</v>
       </c>
-      <c r="AF38" s="2">
+      <c r="AG38" s="2">
         <v>43100</v>
       </c>
-      <c r="AG38" s="2">
+      <c r="AH38" s="2">
         <v>43008</v>
       </c>
-      <c r="AH38" s="2">
+      <c r="AI38" s="2">
         <v>42916</v>
       </c>
-      <c r="AI38" s="2">
+      <c r="AJ38" s="2">
         <v>42825</v>
       </c>
-      <c r="AJ38" s="2">
+      <c r="AK38" s="2">
         <v>42735</v>
       </c>
-      <c r="AK38" s="2">
+      <c r="AL38" s="2">
         <v>42643</v>
       </c>
     </row>
-    <row r="39" spans="2:37" x14ac:dyDescent="0.2">
+    <row r="39" spans="2:38" x14ac:dyDescent="0.2">
       <c r="C39" s="1" t="s">
         <v>32</v>
       </c>
@@ -3726,8 +3810,9 @@
       <c r="AI39" s="3"/>
       <c r="AJ39" s="3"/>
       <c r="AK39" s="3"/>
+      <c r="AL39" s="3"/>
     </row>
-    <row r="40" spans="2:37" x14ac:dyDescent="0.2">
+    <row r="40" spans="2:38" x14ac:dyDescent="0.2">
       <c r="C40" s="1" t="s">
         <v>33</v>
       </c>
@@ -3765,252 +3850,259 @@
       <c r="AI40" s="3"/>
       <c r="AJ40" s="3"/>
       <c r="AK40" s="3"/>
+      <c r="AL40" s="3"/>
     </row>
-    <row r="41" spans="2:37" x14ac:dyDescent="0.2">
+    <row r="41" spans="2:38" x14ac:dyDescent="0.2">
       <c r="C41" s="1" t="s">
         <v>34</v>
       </c>
       <c r="D41" s="3">
+        <v>9800400</v>
+      </c>
+      <c r="E41" s="3">
         <v>9892700</v>
       </c>
-      <c r="E41" s="3">
+      <c r="F41" s="3">
         <v>13834100</v>
       </c>
-      <c r="F41" s="3">
+      <c r="G41" s="3">
         <v>8534800</v>
       </c>
-      <c r="G41" s="3">
+      <c r="H41" s="3">
         <v>13129900</v>
       </c>
-      <c r="H41" s="3">
+      <c r="I41" s="3">
         <v>12476200</v>
       </c>
-      <c r="I41" s="3">
+      <c r="J41" s="3">
         <v>7157900</v>
       </c>
-      <c r="J41" s="3">
+      <c r="K41" s="3">
         <v>9809900</v>
       </c>
-      <c r="K41" s="3">
+      <c r="L41" s="3">
         <v>10234100</v>
       </c>
-      <c r="L41" s="3">
+      <c r="M41" s="3">
         <v>25596900</v>
       </c>
-      <c r="M41" s="3">
+      <c r="N41" s="3">
         <v>6507700</v>
       </c>
-      <c r="N41" s="3">
+      <c r="O41" s="3">
         <v>7377100</v>
       </c>
-      <c r="O41" s="3">
+      <c r="P41" s="3">
         <v>9785500</v>
       </c>
-      <c r="P41" s="3">
+      <c r="Q41" s="3">
         <v>5555400</v>
       </c>
-      <c r="Q41" s="3">
+      <c r="R41" s="3">
         <v>7893500</v>
       </c>
-      <c r="R41" s="3">
+      <c r="S41" s="3">
         <v>7303900</v>
       </c>
-      <c r="S41" s="3">
+      <c r="T41" s="3">
         <v>7996900</v>
       </c>
-      <c r="T41" s="3">
+      <c r="U41" s="3">
         <v>6985700</v>
       </c>
-      <c r="U41" s="3">
+      <c r="V41" s="3">
         <v>6452400</v>
       </c>
-      <c r="V41" s="3">
+      <c r="W41" s="3">
         <v>6934700</v>
       </c>
-      <c r="W41" s="3">
+      <c r="X41" s="3">
         <v>7810800</v>
       </c>
-      <c r="X41" s="3">
+      <c r="Y41" s="3">
         <v>5327800</v>
       </c>
-      <c r="Y41" s="3">
+      <c r="Z41" s="3">
         <v>7069900</v>
       </c>
-      <c r="Z41" s="3">
+      <c r="AA41" s="3">
         <v>5777500</v>
       </c>
-      <c r="AA41" s="3">
+      <c r="AB41" s="3">
         <v>4361000</v>
       </c>
-      <c r="AB41" s="3">
+      <c r="AC41" s="3">
         <v>5329900</v>
       </c>
-      <c r="AC41" s="3">
+      <c r="AD41" s="3">
         <v>4608100</v>
       </c>
-      <c r="AD41" s="3">
+      <c r="AE41" s="3">
         <v>4589200</v>
       </c>
-      <c r="AE41" s="3">
+      <c r="AF41" s="3">
         <v>4387400</v>
       </c>
-      <c r="AF41" s="3">
+      <c r="AG41" s="3">
         <v>5323900</v>
       </c>
-      <c r="AG41" s="3">
+      <c r="AH41" s="3">
         <v>5337600</v>
       </c>
-      <c r="AH41" s="3">
+      <c r="AI41" s="3">
         <v>5780800</v>
       </c>
-      <c r="AI41" s="3">
+      <c r="AJ41" s="3">
         <v>6495200</v>
       </c>
-      <c r="AJ41" s="3">
+      <c r="AK41" s="3">
         <v>6385500</v>
       </c>
-      <c r="AK41" s="3">
+      <c r="AL41" s="3">
         <v>7024600</v>
       </c>
     </row>
-    <row r="42" spans="2:37" x14ac:dyDescent="0.2">
+    <row r="42" spans="2:38" x14ac:dyDescent="0.2">
       <c r="C42" s="1" t="s">
         <v>35</v>
       </c>
       <c r="D42" s="3">
+        <v>27028100</v>
+      </c>
+      <c r="E42" s="3">
         <v>22818100</v>
       </c>
-      <c r="E42" s="3">
+      <c r="F42" s="3">
         <v>29370000</v>
       </c>
-      <c r="F42" s="3">
+      <c r="G42" s="3">
         <v>19283100</v>
       </c>
-      <c r="G42" s="3">
+      <c r="H42" s="3">
         <v>18486700</v>
       </c>
-      <c r="H42" s="3">
+      <c r="I42" s="3">
         <v>18215800</v>
       </c>
-      <c r="I42" s="3">
+      <c r="J42" s="3">
         <v>17492100</v>
       </c>
-      <c r="J42" s="3">
+      <c r="K42" s="3">
         <v>25108400</v>
       </c>
-      <c r="K42" s="3">
+      <c r="L42" s="3">
         <v>17703400</v>
       </c>
-      <c r="L42" s="3">
+      <c r="M42" s="3">
         <v>41084100</v>
       </c>
-      <c r="M42" s="3">
+      <c r="N42" s="3">
         <v>48087900</v>
       </c>
-      <c r="N42" s="3">
+      <c r="O42" s="3">
         <v>44907700</v>
       </c>
-      <c r="O42" s="3">
+      <c r="P42" s="3">
         <v>44616700</v>
       </c>
-      <c r="P42" s="3">
+      <c r="Q42" s="3">
         <v>44083500</v>
       </c>
-      <c r="Q42" s="3">
+      <c r="R42" s="3">
         <v>38326100</v>
       </c>
-      <c r="R42" s="3">
+      <c r="S42" s="3">
         <v>33800600</v>
       </c>
-      <c r="S42" s="3">
+      <c r="T42" s="3">
         <v>32013900</v>
       </c>
-      <c r="T42" s="3">
+      <c r="U42" s="3">
         <v>39170300</v>
       </c>
-      <c r="U42" s="3">
+      <c r="V42" s="3">
         <v>33273800</v>
       </c>
-      <c r="V42" s="3">
+      <c r="W42" s="3">
         <v>36396600</v>
       </c>
-      <c r="W42" s="3">
+      <c r="X42" s="3">
         <v>38606200</v>
       </c>
-      <c r="X42" s="3">
+      <c r="Y42" s="3">
         <v>37680800</v>
       </c>
-      <c r="Y42" s="3">
+      <c r="Z42" s="3">
         <v>39232200</v>
       </c>
-      <c r="Z42" s="3">
+      <c r="AA42" s="3">
         <v>36892000</v>
       </c>
-      <c r="AA42" s="3">
+      <c r="AB42" s="3">
         <v>30905300</v>
       </c>
-      <c r="AB42" s="3">
+      <c r="AC42" s="3">
         <v>29776700</v>
       </c>
-      <c r="AC42" s="3">
+      <c r="AD42" s="3">
         <v>20883600</v>
       </c>
-      <c r="AD42" s="3">
+      <c r="AE42" s="3">
         <v>22286700</v>
       </c>
-      <c r="AE42" s="3">
+      <c r="AF42" s="3">
         <v>21840100</v>
       </c>
-      <c r="AF42" s="3">
+      <c r="AG42" s="3">
         <v>20932300</v>
       </c>
-      <c r="AG42" s="3">
+      <c r="AH42" s="3">
         <v>12488600</v>
       </c>
-      <c r="AH42" s="3">
+      <c r="AI42" s="3">
         <v>14955900</v>
       </c>
-      <c r="AI42" s="3">
+      <c r="AJ42" s="3">
         <v>13350900</v>
       </c>
-      <c r="AJ42" s="3">
+      <c r="AK42" s="3">
         <v>14204100</v>
       </c>
-      <c r="AK42" s="3">
+      <c r="AL42" s="3">
         <v>16154100</v>
       </c>
     </row>
-    <row r="43" spans="2:37" x14ac:dyDescent="0.2">
+    <row r="43" spans="2:38" x14ac:dyDescent="0.2">
       <c r="C43" s="1" t="s">
         <v>36</v>
       </c>
       <c r="D43" s="3">
+        <v>12353800</v>
+      </c>
+      <c r="E43" s="3">
         <v>6099900</v>
       </c>
-      <c r="E43" s="3">
+      <c r="F43" s="3">
         <v>13077600</v>
       </c>
-      <c r="F43" s="3">
+      <c r="G43" s="3">
         <v>9540700</v>
       </c>
-      <c r="G43" s="3">
+      <c r="H43" s="3">
         <v>10078300</v>
       </c>
-      <c r="H43" s="3">
+      <c r="I43" s="3">
         <v>8598900</v>
       </c>
-      <c r="I43" s="3">
+      <c r="J43" s="3">
         <v>9843900</v>
       </c>
-      <c r="J43" s="3">
+      <c r="K43" s="3">
         <v>11594400</v>
       </c>
-      <c r="K43" s="3">
+      <c r="L43" s="3">
         <v>10468300</v>
       </c>
-      <c r="L43" s="3">
-        <v>0</v>
-      </c>
       <c r="M43" s="3">
         <v>0</v>
       </c>
@@ -4086,8 +4178,11 @@
       <c r="AK43" s="3">
         <v>0</v>
       </c>
+      <c r="AL43" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="44" spans="2:37" x14ac:dyDescent="0.2">
+    <row r="44" spans="2:38" x14ac:dyDescent="0.2">
       <c r="C44" s="1" t="s">
         <v>37</v>
       </c>
@@ -4115,8 +4210,8 @@
       <c r="K44" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="L44" s="3">
-        <v>0</v>
+      <c r="L44" s="3" t="s">
+        <v>5</v>
       </c>
       <c r="M44" s="3">
         <v>0</v>
@@ -4193,38 +4288,41 @@
       <c r="AK44" s="3">
         <v>0</v>
       </c>
+      <c r="AL44" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="45" spans="2:37" x14ac:dyDescent="0.2">
+    <row r="45" spans="2:38" x14ac:dyDescent="0.2">
       <c r="C45" s="1" t="s">
         <v>38</v>
       </c>
       <c r="D45" s="3">
+        <v>1943300</v>
+      </c>
+      <c r="E45" s="3">
         <v>3417100</v>
       </c>
-      <c r="E45" s="3">
+      <c r="F45" s="3">
         <v>2191600</v>
       </c>
-      <c r="F45" s="3">
+      <c r="G45" s="3">
         <v>2546100</v>
       </c>
-      <c r="G45" s="3">
+      <c r="H45" s="3">
         <v>2248400</v>
       </c>
-      <c r="H45" s="3">
+      <c r="I45" s="3">
         <v>3229200</v>
       </c>
-      <c r="I45" s="3">
+      <c r="J45" s="3">
         <v>2254000</v>
       </c>
-      <c r="J45" s="3">
+      <c r="K45" s="3">
         <v>2036900</v>
       </c>
-      <c r="K45" s="3">
+      <c r="L45" s="3">
         <v>1992400</v>
       </c>
-      <c r="L45" s="3">
-        <v>0</v>
-      </c>
       <c r="M45" s="3">
         <v>0</v>
       </c>
@@ -4300,38 +4398,41 @@
       <c r="AK45" s="3">
         <v>0</v>
       </c>
+      <c r="AL45" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="46" spans="2:37" x14ac:dyDescent="0.2">
+    <row r="46" spans="2:38" x14ac:dyDescent="0.2">
       <c r="C46" s="1" t="s">
         <v>39</v>
       </c>
       <c r="D46" s="3">
+        <v>58995800</v>
+      </c>
+      <c r="E46" s="3">
         <v>51046100</v>
       </c>
-      <c r="E46" s="3">
+      <c r="F46" s="3">
         <v>70438600</v>
       </c>
-      <c r="F46" s="3">
+      <c r="G46" s="3">
         <v>50125600</v>
       </c>
-      <c r="G46" s="3">
+      <c r="H46" s="3">
         <v>54875900</v>
       </c>
-      <c r="H46" s="3">
+      <c r="I46" s="3">
         <v>53874000</v>
       </c>
-      <c r="I46" s="3">
+      <c r="J46" s="3">
         <v>49079800</v>
       </c>
-      <c r="J46" s="3">
+      <c r="K46" s="3">
         <v>55527700</v>
       </c>
-      <c r="K46" s="3">
+      <c r="L46" s="3">
         <v>55109700</v>
       </c>
-      <c r="L46" s="3">
-        <v>0</v>
-      </c>
       <c r="M46" s="3">
         <v>0</v>
       </c>
@@ -4407,329 +4508,341 @@
       <c r="AK46" s="3">
         <v>0</v>
       </c>
+      <c r="AL46" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="47" spans="2:37" x14ac:dyDescent="0.2">
+    <row r="47" spans="2:38" x14ac:dyDescent="0.2">
       <c r="C47" s="1" t="s">
         <v>40</v>
       </c>
       <c r="D47" s="3">
+        <v>43339500</v>
+      </c>
+      <c r="E47" s="3">
         <v>29734600</v>
       </c>
-      <c r="E47" s="3">
+      <c r="F47" s="3">
         <v>43909700</v>
       </c>
-      <c r="F47" s="3">
+      <c r="G47" s="3">
         <v>45684200</v>
       </c>
-      <c r="G47" s="3">
+      <c r="H47" s="3">
         <v>45083200</v>
       </c>
-      <c r="H47" s="3">
+      <c r="I47" s="3">
         <v>33573300</v>
       </c>
-      <c r="I47" s="3">
+      <c r="J47" s="3">
         <v>46697400</v>
       </c>
-      <c r="J47" s="3">
+      <c r="K47" s="3">
         <v>47231400</v>
       </c>
-      <c r="K47" s="3">
+      <c r="L47" s="3">
         <v>47653400</v>
       </c>
-      <c r="L47" s="3">
+      <c r="M47" s="3">
         <v>979200</v>
       </c>
-      <c r="M47" s="3">
+      <c r="N47" s="3">
         <v>976800</v>
       </c>
-      <c r="N47" s="3">
+      <c r="O47" s="3">
         <v>1035000</v>
       </c>
-      <c r="O47" s="3">
+      <c r="P47" s="3">
         <v>1011300</v>
       </c>
-      <c r="P47" s="3">
+      <c r="Q47" s="3">
         <v>1001400</v>
       </c>
-      <c r="Q47" s="3">
+      <c r="R47" s="3">
         <v>896000</v>
       </c>
-      <c r="R47" s="3">
+      <c r="S47" s="3">
         <v>881500</v>
       </c>
-      <c r="S47" s="3">
+      <c r="T47" s="3">
         <v>775800</v>
       </c>
-      <c r="T47" s="3">
+      <c r="U47" s="3">
         <v>735000</v>
       </c>
-      <c r="U47" s="3">
+      <c r="V47" s="3">
         <v>829200</v>
       </c>
-      <c r="V47" s="3">
+      <c r="W47" s="3">
         <v>714700</v>
       </c>
-      <c r="W47" s="3">
+      <c r="X47" s="3">
         <v>674300</v>
       </c>
-      <c r="X47" s="3">
+      <c r="Y47" s="3">
         <v>685400</v>
       </c>
-      <c r="Y47" s="3">
+      <c r="Z47" s="3">
         <v>322100</v>
       </c>
-      <c r="Z47" s="3">
+      <c r="AA47" s="3">
         <v>311500</v>
       </c>
-      <c r="AA47" s="3">
+      <c r="AB47" s="3">
         <v>316200</v>
       </c>
-      <c r="AB47" s="3">
+      <c r="AC47" s="3">
         <v>303600</v>
       </c>
-      <c r="AC47" s="3">
+      <c r="AD47" s="3">
         <v>276700</v>
       </c>
-      <c r="AD47" s="3">
+      <c r="AE47" s="3">
         <v>346900</v>
       </c>
-      <c r="AE47" s="3">
+      <c r="AF47" s="3">
         <v>348200</v>
       </c>
-      <c r="AF47" s="3">
+      <c r="AG47" s="3">
         <v>367000</v>
       </c>
-      <c r="AG47" s="3">
+      <c r="AH47" s="3">
         <v>490900</v>
       </c>
-      <c r="AH47" s="3">
+      <c r="AI47" s="3">
         <v>326300</v>
       </c>
-      <c r="AI47" s="3">
+      <c r="AJ47" s="3">
         <v>351100</v>
       </c>
-      <c r="AJ47" s="3">
+      <c r="AK47" s="3">
         <v>395100</v>
       </c>
-      <c r="AK47" s="3">
+      <c r="AL47" s="3">
         <v>377600</v>
       </c>
     </row>
-    <row r="48" spans="2:37" x14ac:dyDescent="0.2">
+    <row r="48" spans="2:38" x14ac:dyDescent="0.2">
       <c r="C48" s="1" t="s">
         <v>41</v>
       </c>
       <c r="D48" s="3">
+        <v>4933500</v>
+      </c>
+      <c r="E48" s="3">
         <v>4937200</v>
       </c>
-      <c r="E48" s="3">
+      <c r="F48" s="3">
         <v>5522800</v>
       </c>
-      <c r="F48" s="3">
+      <c r="G48" s="3">
         <v>5103100</v>
       </c>
-      <c r="G48" s="3">
+      <c r="H48" s="3">
         <v>4908300</v>
       </c>
-      <c r="H48" s="3">
+      <c r="I48" s="3">
         <v>4983700</v>
       </c>
-      <c r="I48" s="3">
+      <c r="J48" s="3">
         <v>4486300</v>
       </c>
-      <c r="J48" s="3">
+      <c r="K48" s="3">
         <v>4434900</v>
       </c>
-      <c r="K48" s="3">
+      <c r="L48" s="3">
         <v>4401200</v>
       </c>
-      <c r="L48" s="3">
+      <c r="M48" s="3">
         <v>2648000</v>
       </c>
-      <c r="M48" s="3">
+      <c r="N48" s="3">
         <v>2590300</v>
       </c>
-      <c r="N48" s="3">
+      <c r="O48" s="3">
         <v>2689200</v>
       </c>
-      <c r="O48" s="3">
+      <c r="P48" s="3">
         <v>2729900</v>
       </c>
-      <c r="P48" s="3">
+      <c r="Q48" s="3">
         <v>2673200</v>
       </c>
-      <c r="Q48" s="3">
+      <c r="R48" s="3">
         <v>2701000</v>
       </c>
-      <c r="R48" s="3">
+      <c r="S48" s="3">
         <v>2682600</v>
       </c>
-      <c r="S48" s="3">
+      <c r="T48" s="3">
         <v>2700600</v>
       </c>
-      <c r="T48" s="3">
+      <c r="U48" s="3">
         <v>2719200</v>
       </c>
-      <c r="U48" s="3">
+      <c r="V48" s="3">
         <v>2764300</v>
       </c>
-      <c r="V48" s="3">
+      <c r="W48" s="3">
         <v>2790300</v>
       </c>
-      <c r="W48" s="3">
+      <c r="X48" s="3">
         <v>2961700</v>
       </c>
-      <c r="X48" s="3">
+      <c r="Y48" s="3">
         <v>3098200</v>
       </c>
-      <c r="Y48" s="3">
+      <c r="Z48" s="3">
         <v>3089800</v>
       </c>
-      <c r="Z48" s="3">
+      <c r="AA48" s="3">
         <v>3058200</v>
       </c>
-      <c r="AA48" s="3">
+      <c r="AB48" s="3">
         <v>3080600</v>
       </c>
-      <c r="AB48" s="3">
+      <c r="AC48" s="3">
         <v>2368100</v>
       </c>
-      <c r="AC48" s="3">
+      <c r="AD48" s="3">
         <v>2284800</v>
       </c>
-      <c r="AD48" s="3">
+      <c r="AE48" s="3">
         <v>2378800</v>
       </c>
-      <c r="AE48" s="3">
+      <c r="AF48" s="3">
         <v>2384000</v>
       </c>
-      <c r="AF48" s="3">
+      <c r="AG48" s="3">
         <v>2507000</v>
       </c>
-      <c r="AG48" s="3">
+      <c r="AH48" s="3">
         <v>2509800</v>
       </c>
-      <c r="AH48" s="3">
+      <c r="AI48" s="3">
         <v>2480800</v>
       </c>
-      <c r="AI48" s="3">
+      <c r="AJ48" s="3">
         <v>2470200</v>
       </c>
-      <c r="AJ48" s="3">
+      <c r="AK48" s="3">
         <v>2534900</v>
       </c>
-      <c r="AK48" s="3">
+      <c r="AL48" s="3">
         <v>2525400</v>
       </c>
     </row>
-    <row r="49" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="49" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C49" s="1" t="s">
         <v>42</v>
       </c>
       <c r="D49" s="3">
+        <v>745500</v>
+      </c>
+      <c r="E49" s="3">
         <v>552200</v>
       </c>
-      <c r="E49" s="3">
+      <c r="F49" s="3">
         <v>621800</v>
       </c>
-      <c r="F49" s="3">
+      <c r="G49" s="3">
         <v>557800</v>
       </c>
-      <c r="G49" s="3">
+      <c r="H49" s="3">
         <v>562600</v>
       </c>
-      <c r="H49" s="3">
+      <c r="I49" s="3">
         <v>582000</v>
       </c>
-      <c r="I49" s="3">
+      <c r="J49" s="3">
         <v>568100</v>
       </c>
-      <c r="J49" s="3">
+      <c r="K49" s="3">
         <v>586300</v>
       </c>
-      <c r="K49" s="3">
+      <c r="L49" s="3">
         <v>573300</v>
       </c>
-      <c r="L49" s="3">
+      <c r="M49" s="3">
         <v>636800</v>
       </c>
-      <c r="M49" s="3">
+      <c r="N49" s="3">
         <v>639200</v>
       </c>
-      <c r="N49" s="3">
+      <c r="O49" s="3">
         <v>596500</v>
       </c>
-      <c r="O49" s="3">
+      <c r="P49" s="3">
         <v>608700</v>
       </c>
-      <c r="P49" s="3">
+      <c r="Q49" s="3">
         <v>589000</v>
       </c>
-      <c r="Q49" s="3">
+      <c r="R49" s="3">
         <v>586400</v>
       </c>
-      <c r="R49" s="3">
+      <c r="S49" s="3">
         <v>581700</v>
       </c>
-      <c r="S49" s="3">
+      <c r="T49" s="3">
         <v>582600</v>
       </c>
-      <c r="T49" s="3">
+      <c r="U49" s="3">
         <v>586100</v>
       </c>
-      <c r="U49" s="3">
+      <c r="V49" s="3">
         <v>615800</v>
       </c>
-      <c r="V49" s="3">
+      <c r="W49" s="3">
         <v>631700</v>
       </c>
-      <c r="W49" s="3">
+      <c r="X49" s="3">
         <v>668000</v>
       </c>
-      <c r="X49" s="3">
+      <c r="Y49" s="3">
         <v>717500</v>
       </c>
-      <c r="Y49" s="3">
+      <c r="Z49" s="3">
         <v>590200</v>
       </c>
-      <c r="Z49" s="3">
+      <c r="AA49" s="3">
         <v>565800</v>
       </c>
-      <c r="AA49" s="3">
+      <c r="AB49" s="3">
         <v>588900</v>
       </c>
-      <c r="AB49" s="3">
+      <c r="AC49" s="3">
         <v>493300</v>
       </c>
-      <c r="AC49" s="3">
+      <c r="AD49" s="3">
         <v>502400</v>
       </c>
-      <c r="AD49" s="3">
+      <c r="AE49" s="3">
         <v>549000</v>
       </c>
-      <c r="AE49" s="3">
+      <c r="AF49" s="3">
         <v>452700</v>
       </c>
-      <c r="AF49" s="3">
+      <c r="AG49" s="3">
         <v>456400</v>
       </c>
-      <c r="AG49" s="3">
+      <c r="AH49" s="3">
         <v>461900</v>
       </c>
-      <c r="AH49" s="3">
+      <c r="AI49" s="3">
         <v>446100</v>
       </c>
-      <c r="AI49" s="3">
+      <c r="AJ49" s="3">
         <v>415100</v>
       </c>
-      <c r="AJ49" s="3">
+      <c r="AK49" s="3">
         <v>435400</v>
       </c>
-      <c r="AK49" s="3">
+      <c r="AL49" s="3">
         <v>376700</v>
       </c>
     </row>
-    <row r="50" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="50" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C50" s="1" t="s">
         <v>43</v>
       </c>
@@ -4835,8 +4948,11 @@
       <c r="AK50" s="3">
         <v>0</v>
       </c>
+      <c r="AL50" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="51" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="51" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C51" s="1" t="s">
         <v>44</v>
       </c>
@@ -4942,115 +5058,121 @@
       <c r="AK51" s="3">
         <v>0</v>
       </c>
+      <c r="AL51" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="52" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="52" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C52" s="1" t="s">
         <v>45</v>
       </c>
       <c r="D52" s="3">
+        <v>1099500</v>
+      </c>
+      <c r="E52" s="3">
         <v>15193100</v>
       </c>
-      <c r="E52" s="3">
+      <c r="F52" s="3">
         <v>1117800</v>
       </c>
-      <c r="F52" s="3">
+      <c r="G52" s="3">
         <v>1097200</v>
       </c>
-      <c r="G52" s="3">
+      <c r="H52" s="3">
         <v>1375500</v>
       </c>
-      <c r="H52" s="3">
+      <c r="I52" s="3">
         <v>16836600</v>
       </c>
-      <c r="I52" s="3">
+      <c r="J52" s="3">
         <v>1488400</v>
       </c>
-      <c r="J52" s="3">
+      <c r="K52" s="3">
         <v>1186200</v>
       </c>
-      <c r="K52" s="3">
+      <c r="L52" s="3">
         <v>1174600</v>
       </c>
-      <c r="L52" s="3">
+      <c r="M52" s="3">
         <v>331800</v>
       </c>
-      <c r="M52" s="3">
+      <c r="N52" s="3">
         <v>284500</v>
       </c>
-      <c r="N52" s="3">
+      <c r="O52" s="3">
         <v>166400</v>
       </c>
-      <c r="O52" s="3">
+      <c r="P52" s="3">
         <v>58400</v>
       </c>
-      <c r="P52" s="3">
+      <c r="Q52" s="3">
         <v>59100</v>
       </c>
-      <c r="Q52" s="3">
+      <c r="R52" s="3">
         <v>41100</v>
       </c>
-      <c r="R52" s="3">
+      <c r="S52" s="3">
         <v>56000</v>
       </c>
-      <c r="S52" s="3">
+      <c r="T52" s="3">
         <v>73700</v>
       </c>
-      <c r="T52" s="3">
+      <c r="U52" s="3">
         <v>82700</v>
       </c>
-      <c r="U52" s="3">
+      <c r="V52" s="3">
         <v>74500</v>
       </c>
-      <c r="V52" s="3">
+      <c r="W52" s="3">
         <v>37800</v>
       </c>
-      <c r="W52" s="3">
+      <c r="X52" s="3">
         <v>38200</v>
       </c>
-      <c r="X52" s="3">
+      <c r="Y52" s="3">
         <v>44800</v>
       </c>
-      <c r="Y52" s="3">
+      <c r="Z52" s="3">
         <v>82300</v>
       </c>
-      <c r="Z52" s="3">
+      <c r="AA52" s="3">
         <v>69500</v>
       </c>
-      <c r="AA52" s="3">
+      <c r="AB52" s="3">
         <v>68200</v>
       </c>
-      <c r="AB52" s="3">
+      <c r="AC52" s="3">
         <v>120400</v>
       </c>
-      <c r="AC52" s="3">
+      <c r="AD52" s="3">
         <v>36800</v>
       </c>
-      <c r="AD52" s="3">
+      <c r="AE52" s="3">
         <v>91100</v>
       </c>
-      <c r="AE52" s="3">
+      <c r="AF52" s="3">
         <v>177600</v>
       </c>
-      <c r="AF52" s="3">
+      <c r="AG52" s="3">
         <v>289300</v>
       </c>
-      <c r="AG52" s="3">
+      <c r="AH52" s="3">
         <v>234800</v>
       </c>
-      <c r="AH52" s="3">
+      <c r="AI52" s="3">
         <v>221100</v>
       </c>
-      <c r="AI52" s="3">
+      <c r="AJ52" s="3">
         <v>262700</v>
       </c>
-      <c r="AJ52" s="3">
+      <c r="AK52" s="3">
         <v>274800</v>
       </c>
-      <c r="AK52" s="3">
+      <c r="AL52" s="3">
         <v>143800</v>
       </c>
     </row>
-    <row r="53" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="53" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C53" s="1" t="s">
         <v>46</v>
       </c>
@@ -5156,115 +5278,121 @@
       <c r="AK53" s="3">
         <v>0</v>
       </c>
+      <c r="AL53" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="54" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="54" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C54" s="1" t="s">
         <v>47</v>
       </c>
       <c r="D54" s="3">
+        <v>361721400</v>
+      </c>
+      <c r="E54" s="3">
         <v>355900000</v>
       </c>
-      <c r="E54" s="3">
+      <c r="F54" s="3">
         <v>413964600</v>
       </c>
-      <c r="F54" s="3">
+      <c r="G54" s="3">
         <v>369217100</v>
       </c>
-      <c r="G54" s="3">
+      <c r="H54" s="3">
         <v>375587700</v>
       </c>
-      <c r="H54" s="3">
+      <c r="I54" s="3">
         <v>384037900</v>
       </c>
-      <c r="I54" s="3">
+      <c r="J54" s="3">
         <v>360962600</v>
       </c>
-      <c r="J54" s="3">
+      <c r="K54" s="3">
         <v>366653200</v>
       </c>
-      <c r="K54" s="3">
+      <c r="L54" s="3">
         <v>366661700</v>
       </c>
-      <c r="L54" s="3">
+      <c r="M54" s="3">
         <v>360355800</v>
       </c>
-      <c r="M54" s="3">
+      <c r="N54" s="3">
         <v>366510300</v>
       </c>
-      <c r="N54" s="3">
+      <c r="O54" s="3">
         <v>368558700</v>
       </c>
-      <c r="O54" s="3">
+      <c r="P54" s="3">
         <v>358592300</v>
       </c>
-      <c r="P54" s="3">
+      <c r="Q54" s="3">
         <v>335387900</v>
       </c>
-      <c r="Q54" s="3">
+      <c r="R54" s="3">
         <v>328638700</v>
       </c>
-      <c r="R54" s="3">
+      <c r="S54" s="3">
         <v>315953000</v>
       </c>
-      <c r="S54" s="3">
+      <c r="T54" s="3">
         <v>307917200</v>
       </c>
-      <c r="T54" s="3">
+      <c r="U54" s="3">
         <v>295320000</v>
       </c>
-      <c r="U54" s="3">
+      <c r="V54" s="3">
         <v>293246000</v>
       </c>
-      <c r="V54" s="3">
+      <c r="W54" s="3">
         <v>292659600</v>
       </c>
-      <c r="W54" s="3">
+      <c r="X54" s="3">
         <v>306353500</v>
       </c>
-      <c r="X54" s="3">
+      <c r="Y54" s="3">
         <v>307683600</v>
       </c>
-      <c r="Y54" s="3">
+      <c r="Z54" s="3">
         <v>314996600</v>
       </c>
-      <c r="Z54" s="3">
+      <c r="AA54" s="3">
         <v>316273500</v>
       </c>
-      <c r="AA54" s="3">
+      <c r="AB54" s="3">
         <v>314085600</v>
       </c>
-      <c r="AB54" s="3">
+      <c r="AC54" s="3">
         <v>285975600</v>
       </c>
-      <c r="AC54" s="3">
+      <c r="AD54" s="3">
         <v>267139300</v>
       </c>
-      <c r="AD54" s="3">
+      <c r="AE54" s="3">
         <v>274311500</v>
       </c>
-      <c r="AE54" s="3">
+      <c r="AF54" s="3">
         <v>273668600</v>
       </c>
-      <c r="AF54" s="3">
+      <c r="AG54" s="3">
         <v>278340000</v>
       </c>
-      <c r="AG54" s="3">
+      <c r="AH54" s="3">
         <v>279730100</v>
       </c>
-      <c r="AH54" s="3">
+      <c r="AI54" s="3">
         <v>278137400</v>
       </c>
-      <c r="AI54" s="3">
+      <c r="AJ54" s="3">
         <v>273600800</v>
       </c>
-      <c r="AJ54" s="3">
+      <c r="AK54" s="3">
         <v>279614500</v>
       </c>
-      <c r="AK54" s="3">
+      <c r="AL54" s="3">
         <v>281548700</v>
       </c>
     </row>
-    <row r="55" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="55" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C55" s="1" t="s">
         <v>48</v>
       </c>
@@ -5302,8 +5430,9 @@
       <c r="AI55" s="3"/>
       <c r="AJ55" s="3"/>
       <c r="AK55" s="3"/>
+      <c r="AL55" s="3"/>
     </row>
-    <row r="56" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="56" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C56" s="1" t="s">
         <v>49</v>
       </c>
@@ -5341,145 +5470,149 @@
       <c r="AI56" s="3"/>
       <c r="AJ56" s="3"/>
       <c r="AK56" s="3"/>
+      <c r="AL56" s="3"/>
     </row>
-    <row r="57" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="57" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C57" s="1" t="s">
         <v>50</v>
       </c>
       <c r="D57" s="3">
+        <v>262183700</v>
+      </c>
+      <c r="E57" s="3">
         <v>253583100</v>
       </c>
-      <c r="E57" s="3">
+      <c r="F57" s="3">
         <v>303683400</v>
       </c>
-      <c r="F57" s="3">
+      <c r="G57" s="3">
         <v>269353200</v>
       </c>
-      <c r="G57" s="3">
+      <c r="H57" s="3">
         <v>273669100</v>
       </c>
-      <c r="H57" s="3">
+      <c r="I57" s="3">
         <v>283746600</v>
       </c>
-      <c r="I57" s="3">
+      <c r="J57" s="3">
         <v>257925300</v>
       </c>
-      <c r="J57" s="3">
+      <c r="K57" s="3">
         <v>263215600</v>
       </c>
-      <c r="K57" s="3">
+      <c r="L57" s="3">
         <v>259046400</v>
       </c>
-      <c r="L57" s="3">
+      <c r="M57" s="3">
         <v>8592200</v>
       </c>
-      <c r="M57" s="3">
+      <c r="N57" s="3">
         <v>12736100</v>
       </c>
-      <c r="N57" s="3">
+      <c r="O57" s="3">
         <v>12538100</v>
       </c>
-      <c r="O57" s="3">
+      <c r="P57" s="3">
         <v>11104000</v>
       </c>
-      <c r="P57" s="3">
+      <c r="Q57" s="3">
         <v>10844700</v>
       </c>
-      <c r="Q57" s="3">
+      <c r="R57" s="3">
         <v>7957500</v>
       </c>
-      <c r="R57" s="3">
+      <c r="S57" s="3">
         <v>9468900</v>
       </c>
-      <c r="S57" s="3">
+      <c r="T57" s="3">
         <v>7995800</v>
       </c>
-      <c r="T57" s="3">
+      <c r="U57" s="3">
         <v>3698600</v>
       </c>
-      <c r="U57" s="3">
+      <c r="V57" s="3">
         <v>7530800</v>
       </c>
-      <c r="V57" s="3">
+      <c r="W57" s="3">
         <v>8467000</v>
       </c>
-      <c r="W57" s="3">
+      <c r="X57" s="3">
         <v>9538600</v>
       </c>
-      <c r="X57" s="3">
+      <c r="Y57" s="3">
         <v>7264700</v>
       </c>
-      <c r="Y57" s="3">
+      <c r="Z57" s="3">
         <v>13339700</v>
       </c>
-      <c r="Z57" s="3">
+      <c r="AA57" s="3">
         <v>15138200</v>
       </c>
-      <c r="AA57" s="3">
+      <c r="AB57" s="3">
         <v>14778600</v>
       </c>
-      <c r="AB57" s="3">
+      <c r="AC57" s="3">
         <v>10988500</v>
       </c>
-      <c r="AC57" s="3">
+      <c r="AD57" s="3">
         <v>12068900</v>
       </c>
-      <c r="AD57" s="3">
+      <c r="AE57" s="3">
         <v>11638400</v>
       </c>
-      <c r="AE57" s="3">
+      <c r="AF57" s="3">
         <v>12317300</v>
       </c>
-      <c r="AF57" s="3">
+      <c r="AG57" s="3">
         <v>5801500</v>
       </c>
-      <c r="AG57" s="3">
+      <c r="AH57" s="3">
         <v>13814400</v>
       </c>
-      <c r="AH57" s="3">
+      <c r="AI57" s="3">
         <v>14756900</v>
       </c>
-      <c r="AI57" s="3">
+      <c r="AJ57" s="3">
         <v>10823000</v>
       </c>
-      <c r="AJ57" s="3">
+      <c r="AK57" s="3">
         <v>13329400</v>
       </c>
-      <c r="AK57" s="3">
+      <c r="AL57" s="3">
         <v>15356600</v>
       </c>
     </row>
-    <row r="58" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="58" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C58" s="1" t="s">
         <v>51</v>
       </c>
       <c r="D58" s="3">
+        <v>10611200</v>
+      </c>
+      <c r="E58" s="3">
         <v>12014400</v>
       </c>
-      <c r="E58" s="3">
+      <c r="F58" s="3">
         <v>10388900</v>
       </c>
-      <c r="F58" s="3">
+      <c r="G58" s="3">
         <v>10701400</v>
       </c>
-      <c r="G58" s="3">
+      <c r="H58" s="3">
         <v>11337600</v>
       </c>
-      <c r="H58" s="3">
+      <c r="I58" s="3">
         <v>9863100</v>
       </c>
-      <c r="I58" s="3">
+      <c r="J58" s="3">
         <v>11103300</v>
       </c>
-      <c r="J58" s="3">
+      <c r="K58" s="3">
         <v>10559700</v>
       </c>
-      <c r="K58" s="3">
+      <c r="L58" s="3">
         <v>10550500</v>
       </c>
-      <c r="L58" s="3">
-        <v>0</v>
-      </c>
       <c r="M58" s="3">
         <v>0</v>
       </c>
@@ -5555,145 +5688,151 @@
       <c r="AK58" s="3">
         <v>0</v>
       </c>
+      <c r="AL58" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="59" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="59" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C59" s="1" t="s">
         <v>52</v>
       </c>
       <c r="D59" s="3">
+        <v>825800</v>
+      </c>
+      <c r="E59" s="3">
         <v>747300</v>
       </c>
-      <c r="E59" s="3">
+      <c r="F59" s="3">
         <v>917100</v>
       </c>
-      <c r="F59" s="3">
+      <c r="G59" s="3">
         <v>585700</v>
       </c>
-      <c r="G59" s="3">
+      <c r="H59" s="3">
         <v>748600</v>
       </c>
-      <c r="H59" s="3">
+      <c r="I59" s="3">
         <v>795100</v>
       </c>
-      <c r="I59" s="3">
+      <c r="J59" s="3">
         <v>581800</v>
       </c>
-      <c r="J59" s="3">
+      <c r="K59" s="3">
         <v>593500</v>
       </c>
-      <c r="K59" s="3">
+      <c r="L59" s="3">
         <v>1203800</v>
       </c>
-      <c r="L59" s="3">
+      <c r="M59" s="3">
         <v>3047200</v>
       </c>
-      <c r="M59" s="3">
+      <c r="N59" s="3">
         <v>2229700</v>
       </c>
-      <c r="N59" s="3">
+      <c r="O59" s="3">
         <v>1968300</v>
       </c>
-      <c r="O59" s="3">
+      <c r="P59" s="3">
         <v>2093100</v>
       </c>
-      <c r="P59" s="3">
+      <c r="Q59" s="3">
         <v>1991300</v>
       </c>
-      <c r="Q59" s="3">
+      <c r="R59" s="3">
         <v>1538600</v>
       </c>
-      <c r="R59" s="3">
+      <c r="S59" s="3">
         <v>1446500</v>
       </c>
-      <c r="S59" s="3">
+      <c r="T59" s="3">
         <v>1600800</v>
       </c>
-      <c r="T59" s="3">
+      <c r="U59" s="3">
         <v>1790900</v>
       </c>
-      <c r="U59" s="3">
+      <c r="V59" s="3">
         <v>1521700</v>
       </c>
-      <c r="V59" s="3">
+      <c r="W59" s="3">
         <v>1545300</v>
       </c>
-      <c r="W59" s="3">
+      <c r="X59" s="3">
         <v>1892000</v>
       </c>
-      <c r="X59" s="3">
+      <c r="Y59" s="3">
         <v>2294100</v>
       </c>
-      <c r="Y59" s="3">
+      <c r="Z59" s="3">
         <v>2199800</v>
       </c>
-      <c r="Z59" s="3">
+      <c r="AA59" s="3">
         <v>2064700</v>
       </c>
-      <c r="AA59" s="3">
+      <c r="AB59" s="3">
         <v>2149400</v>
       </c>
-      <c r="AB59" s="3">
+      <c r="AC59" s="3">
         <v>1989900</v>
       </c>
-      <c r="AC59" s="3">
+      <c r="AD59" s="3">
         <v>1798500</v>
       </c>
-      <c r="AD59" s="3">
+      <c r="AE59" s="3">
         <v>1649500</v>
       </c>
-      <c r="AE59" s="3">
+      <c r="AF59" s="3">
         <v>1642100</v>
       </c>
-      <c r="AF59" s="3">
+      <c r="AG59" s="3">
         <v>2008600</v>
       </c>
-      <c r="AG59" s="3">
+      <c r="AH59" s="3">
         <v>2057400</v>
       </c>
-      <c r="AH59" s="3">
+      <c r="AI59" s="3">
         <v>1681400</v>
       </c>
-      <c r="AI59" s="3">
+      <c r="AJ59" s="3">
         <v>1880000</v>
       </c>
-      <c r="AJ59" s="3">
+      <c r="AK59" s="3">
         <v>2004400</v>
       </c>
-      <c r="AK59" s="3">
+      <c r="AL59" s="3">
         <v>1813400</v>
       </c>
     </row>
-    <row r="60" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="60" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C60" s="1" t="s">
         <v>53</v>
       </c>
       <c r="D60" s="3">
+        <v>276760100</v>
+      </c>
+      <c r="E60" s="3">
         <v>269522700</v>
       </c>
-      <c r="E60" s="3">
+      <c r="F60" s="3">
         <v>318811800</v>
       </c>
-      <c r="F60" s="3">
+      <c r="G60" s="3">
         <v>283969800</v>
       </c>
-      <c r="G60" s="3">
+      <c r="H60" s="3">
         <v>288965400</v>
       </c>
-      <c r="H60" s="3">
+      <c r="I60" s="3">
         <v>297751000</v>
       </c>
-      <c r="I60" s="3">
+      <c r="J60" s="3">
         <v>272946300</v>
       </c>
-      <c r="J60" s="3">
+      <c r="K60" s="3">
         <v>277365200</v>
       </c>
-      <c r="K60" s="3">
+      <c r="L60" s="3">
         <v>273486900</v>
       </c>
-      <c r="L60" s="3">
-        <v>0</v>
-      </c>
       <c r="M60" s="3">
         <v>0</v>
       </c>
@@ -5769,222 +5908,231 @@
       <c r="AK60" s="3">
         <v>0</v>
       </c>
+      <c r="AL60" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="61" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="61" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C61" s="1" t="s">
         <v>54</v>
       </c>
       <c r="D61" s="3">
+        <v>51786600</v>
+      </c>
+      <c r="E61" s="3">
         <v>52292900</v>
       </c>
-      <c r="E61" s="3">
+      <c r="F61" s="3">
         <v>57884900</v>
       </c>
-      <c r="F61" s="3">
+      <c r="G61" s="3">
         <v>51737100</v>
       </c>
-      <c r="G61" s="3">
+      <c r="H61" s="3">
         <v>52671400</v>
       </c>
-      <c r="H61" s="3">
+      <c r="I61" s="3">
         <v>54929200</v>
       </c>
-      <c r="I61" s="3">
+      <c r="J61" s="3">
         <v>53360000</v>
       </c>
-      <c r="J61" s="3">
+      <c r="K61" s="3">
         <v>54858600</v>
       </c>
-      <c r="K61" s="3">
+      <c r="L61" s="3">
         <v>55629400</v>
       </c>
-      <c r="L61" s="3">
+      <c r="M61" s="3">
         <v>52670100</v>
       </c>
-      <c r="M61" s="3">
+      <c r="N61" s="3">
         <v>58817800</v>
       </c>
-      <c r="N61" s="3">
+      <c r="O61" s="3">
         <v>58413400</v>
       </c>
-      <c r="O61" s="3">
+      <c r="P61" s="3">
         <v>54512100</v>
       </c>
-      <c r="P61" s="3">
+      <c r="Q61" s="3">
         <v>51506600</v>
       </c>
-      <c r="Q61" s="3">
+      <c r="R61" s="3">
         <v>49335300</v>
       </c>
-      <c r="R61" s="3">
+      <c r="S61" s="3">
         <v>46999300</v>
       </c>
-      <c r="S61" s="3">
+      <c r="T61" s="3">
         <v>43329900</v>
       </c>
-      <c r="T61" s="3">
+      <c r="U61" s="3">
         <v>42586400</v>
       </c>
-      <c r="U61" s="3">
+      <c r="V61" s="3">
         <v>38230600</v>
       </c>
-      <c r="V61" s="3">
+      <c r="W61" s="3">
         <v>39214800</v>
       </c>
-      <c r="W61" s="3">
+      <c r="X61" s="3">
         <v>43080800</v>
       </c>
-      <c r="X61" s="3">
+      <c r="Y61" s="3">
         <v>42129500</v>
       </c>
-      <c r="Y61" s="3">
+      <c r="Z61" s="3">
         <v>44185000</v>
       </c>
-      <c r="Z61" s="3">
+      <c r="AA61" s="3">
         <v>43142100</v>
       </c>
-      <c r="AA61" s="3">
+      <c r="AB61" s="3">
         <v>40307800</v>
       </c>
-      <c r="AB61" s="3">
+      <c r="AC61" s="3">
         <v>36868700</v>
       </c>
-      <c r="AC61" s="3">
+      <c r="AD61" s="3">
         <v>34955700</v>
       </c>
-      <c r="AD61" s="3">
+      <c r="AE61" s="3">
         <v>35115500</v>
       </c>
-      <c r="AE61" s="3">
+      <c r="AF61" s="3">
         <v>34009900</v>
       </c>
-      <c r="AF61" s="3">
+      <c r="AG61" s="3">
         <v>36941800</v>
       </c>
-      <c r="AG61" s="3">
+      <c r="AH61" s="3">
         <v>37408900</v>
       </c>
-      <c r="AH61" s="3">
+      <c r="AI61" s="3">
         <v>35000000</v>
       </c>
-      <c r="AI61" s="3">
+      <c r="AJ61" s="3">
         <v>33280700</v>
       </c>
-      <c r="AJ61" s="3">
+      <c r="AK61" s="3">
         <v>34538700</v>
       </c>
-      <c r="AK61" s="3">
+      <c r="AL61" s="3">
         <v>33926000</v>
       </c>
     </row>
-    <row r="62" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="62" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C62" s="1" t="s">
         <v>55</v>
       </c>
       <c r="D62" s="3">
+        <v>7918500</v>
+      </c>
+      <c r="E62" s="3">
         <v>8428000</v>
       </c>
-      <c r="E62" s="3">
+      <c r="F62" s="3">
         <v>8065900</v>
       </c>
-      <c r="F62" s="3">
+      <c r="G62" s="3">
         <v>6973100</v>
       </c>
-      <c r="G62" s="3">
+      <c r="H62" s="3">
         <v>7766400</v>
       </c>
-      <c r="H62" s="3">
+      <c r="I62" s="3">
         <v>4724200</v>
       </c>
-      <c r="I62" s="3">
+      <c r="J62" s="3">
         <v>8885900</v>
       </c>
-      <c r="J62" s="3">
+      <c r="K62" s="3">
         <v>8657200</v>
       </c>
-      <c r="K62" s="3">
+      <c r="L62" s="3">
         <v>11788800</v>
       </c>
-      <c r="L62" s="3">
+      <c r="M62" s="3">
         <v>459600</v>
       </c>
-      <c r="M62" s="3">
+      <c r="N62" s="3">
         <v>438000</v>
       </c>
-      <c r="N62" s="3">
+      <c r="O62" s="3">
         <v>469900</v>
       </c>
-      <c r="O62" s="3">
+      <c r="P62" s="3">
         <v>523500</v>
       </c>
-      <c r="P62" s="3">
+      <c r="Q62" s="3">
         <v>608300</v>
       </c>
-      <c r="Q62" s="3">
+      <c r="R62" s="3">
         <v>663300</v>
       </c>
-      <c r="R62" s="3">
+      <c r="S62" s="3">
         <v>620300</v>
       </c>
-      <c r="S62" s="3">
+      <c r="T62" s="3">
         <v>542300</v>
       </c>
-      <c r="T62" s="3">
+      <c r="U62" s="3">
         <v>528500</v>
       </c>
-      <c r="U62" s="3">
+      <c r="V62" s="3">
         <v>720700</v>
       </c>
-      <c r="V62" s="3">
+      <c r="W62" s="3">
         <v>691400</v>
       </c>
-      <c r="W62" s="3">
+      <c r="X62" s="3">
         <v>680000</v>
       </c>
-      <c r="X62" s="3">
+      <c r="Y62" s="3">
         <v>570200</v>
       </c>
-      <c r="Y62" s="3">
+      <c r="Z62" s="3">
         <v>714600</v>
       </c>
-      <c r="Z62" s="3">
+      <c r="AA62" s="3">
         <v>648100</v>
       </c>
-      <c r="AA62" s="3">
+      <c r="AB62" s="3">
         <v>618700</v>
       </c>
-      <c r="AB62" s="3">
+      <c r="AC62" s="3">
         <v>520300</v>
       </c>
-      <c r="AC62" s="3">
+      <c r="AD62" s="3">
         <v>418500</v>
       </c>
-      <c r="AD62" s="3">
+      <c r="AE62" s="3">
         <v>420800</v>
       </c>
-      <c r="AE62" s="3">
+      <c r="AF62" s="3">
         <v>527700</v>
       </c>
-      <c r="AF62" s="3">
+      <c r="AG62" s="3">
         <v>419200</v>
       </c>
-      <c r="AG62" s="3">
+      <c r="AH62" s="3">
         <v>395900</v>
       </c>
-      <c r="AH62" s="3">
+      <c r="AI62" s="3">
         <v>382900</v>
       </c>
-      <c r="AI62" s="3">
+      <c r="AJ62" s="3">
         <v>400700</v>
       </c>
-      <c r="AJ62" s="3">
+      <c r="AK62" s="3">
         <v>463600</v>
       </c>
-      <c r="AK62" s="3">
+      <c r="AL62" s="3">
         <v>459900</v>
       </c>
     </row>
-    <row r="63" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="63" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C63" s="1" t="s">
         <v>56</v>
       </c>
@@ -6090,8 +6238,11 @@
       <c r="AK63" s="3">
         <v>0</v>
       </c>
+      <c r="AL63" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="64" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="64" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C64" s="1" t="s">
         <v>20</v>
       </c>
@@ -6197,8 +6348,11 @@
       <c r="AK64" s="3">
         <v>0</v>
       </c>
+      <c r="AL64" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="65" spans="2:37" x14ac:dyDescent="0.2">
+    <row r="65" spans="2:38" x14ac:dyDescent="0.2">
       <c r="C65" s="1" t="s">
         <v>57</v>
       </c>
@@ -6304,115 +6458,121 @@
       <c r="AK65" s="3">
         <v>0</v>
       </c>
+      <c r="AL65" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="66" spans="2:37" x14ac:dyDescent="0.2">
+    <row r="66" spans="2:38" x14ac:dyDescent="0.2">
       <c r="C66" s="1" t="s">
         <v>58</v>
       </c>
       <c r="D66" s="3">
+        <v>337599900</v>
+      </c>
+      <c r="E66" s="3">
         <v>331601300</v>
       </c>
-      <c r="E66" s="3">
+      <c r="F66" s="3">
         <v>386400900</v>
       </c>
-      <c r="F66" s="3">
+      <c r="G66" s="3">
         <v>343710800</v>
       </c>
-      <c r="G66" s="3">
+      <c r="H66" s="3">
         <v>350345300</v>
       </c>
-      <c r="H66" s="3">
+      <c r="I66" s="3">
         <v>358283300</v>
       </c>
-      <c r="I66" s="3">
+      <c r="J66" s="3">
         <v>336284100</v>
       </c>
-      <c r="J66" s="3">
+      <c r="K66" s="3">
         <v>341832200</v>
       </c>
-      <c r="K66" s="3">
+      <c r="L66" s="3">
         <v>341656500</v>
       </c>
-      <c r="L66" s="3">
+      <c r="M66" s="3">
         <v>338784400</v>
       </c>
-      <c r="M66" s="3">
+      <c r="N66" s="3">
         <v>345885900</v>
       </c>
-      <c r="N66" s="3">
+      <c r="O66" s="3">
         <v>348018900</v>
       </c>
-      <c r="O66" s="3">
+      <c r="P66" s="3">
         <v>338354200</v>
       </c>
-      <c r="P66" s="3">
+      <c r="Q66" s="3">
         <v>316006400</v>
       </c>
-      <c r="Q66" s="3">
+      <c r="R66" s="3">
         <v>309651700</v>
       </c>
-      <c r="R66" s="3">
+      <c r="S66" s="3">
         <v>297533600</v>
       </c>
-      <c r="S66" s="3">
+      <c r="T66" s="3">
         <v>290517700</v>
       </c>
-      <c r="T66" s="3">
+      <c r="U66" s="3">
         <v>278260300</v>
       </c>
-      <c r="U66" s="3">
+      <c r="V66" s="3">
         <v>275726000</v>
       </c>
-      <c r="V66" s="3">
+      <c r="W66" s="3">
         <v>275487700</v>
       </c>
-      <c r="W66" s="3">
+      <c r="X66" s="3">
         <v>288675900</v>
       </c>
-      <c r="X66" s="3">
+      <c r="Y66" s="3">
         <v>289399800</v>
       </c>
-      <c r="Y66" s="3">
+      <c r="Z66" s="3">
         <v>297278600</v>
       </c>
-      <c r="Z66" s="3">
+      <c r="AA66" s="3">
         <v>299163500</v>
       </c>
-      <c r="AA66" s="3">
+      <c r="AB66" s="3">
         <v>296968200</v>
       </c>
-      <c r="AB66" s="3">
+      <c r="AC66" s="3">
         <v>267714100</v>
       </c>
-      <c r="AC66" s="3">
+      <c r="AD66" s="3">
         <v>249559900</v>
       </c>
-      <c r="AD66" s="3">
+      <c r="AE66" s="3">
         <v>256847800</v>
       </c>
-      <c r="AE66" s="3">
+      <c r="AF66" s="3">
         <v>256582900</v>
       </c>
-      <c r="AF66" s="3">
+      <c r="AG66" s="3">
         <v>260418000</v>
       </c>
-      <c r="AG66" s="3">
+      <c r="AH66" s="3">
         <v>261733600</v>
       </c>
-      <c r="AH66" s="3">
+      <c r="AI66" s="3">
         <v>260311800</v>
       </c>
-      <c r="AI66" s="3">
+      <c r="AJ66" s="3">
         <v>255640700</v>
       </c>
-      <c r="AJ66" s="3">
+      <c r="AK66" s="3">
         <v>261266900</v>
       </c>
-      <c r="AK66" s="3">
+      <c r="AL66" s="3">
         <v>263136400</v>
       </c>
     </row>
-    <row r="67" spans="2:37" x14ac:dyDescent="0.2">
+    <row r="67" spans="2:38" x14ac:dyDescent="0.2">
       <c r="C67" s="1" t="s">
         <v>59</v>
       </c>
@@ -6450,8 +6610,9 @@
       <c r="AI67" s="3"/>
       <c r="AJ67" s="3"/>
       <c r="AK67" s="3"/>
+      <c r="AL67" s="3"/>
     </row>
-    <row r="68" spans="2:37" x14ac:dyDescent="0.2">
+    <row r="68" spans="2:38" x14ac:dyDescent="0.2">
       <c r="C68" s="1" t="s">
         <v>60</v>
       </c>
@@ -6557,8 +6718,11 @@
       <c r="AK68" s="3">
         <v>0</v>
       </c>
+      <c r="AL68" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="69" spans="2:37" x14ac:dyDescent="0.2">
+    <row r="69" spans="2:38" x14ac:dyDescent="0.2">
       <c r="C69" s="1" t="s">
         <v>61</v>
       </c>
@@ -6664,8 +6828,11 @@
       <c r="AK69" s="3">
         <v>0</v>
       </c>
+      <c r="AL69" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="70" spans="2:37" x14ac:dyDescent="0.2">
+    <row r="70" spans="2:38" x14ac:dyDescent="0.2">
       <c r="C70" s="1" t="s">
         <v>62</v>
       </c>
@@ -6771,8 +6938,11 @@
       <c r="AK70" s="3">
         <v>0</v>
       </c>
+      <c r="AL70" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="71" spans="2:37" x14ac:dyDescent="0.2">
+    <row r="71" spans="2:38" x14ac:dyDescent="0.2">
       <c r="C71" s="1" t="s">
         <v>63</v>
       </c>
@@ -6878,115 +7048,121 @@
       <c r="AK71" s="3">
         <v>0</v>
       </c>
+      <c r="AL71" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="72" spans="2:37" x14ac:dyDescent="0.2">
+    <row r="72" spans="2:38" x14ac:dyDescent="0.2">
       <c r="C72" s="1" t="s">
         <v>64</v>
       </c>
       <c r="D72" s="3">
+        <v>18322200</v>
+      </c>
+      <c r="E72" s="3">
         <v>18243700</v>
       </c>
-      <c r="E72" s="3">
+      <c r="F72" s="3">
         <v>20282200</v>
       </c>
-      <c r="F72" s="3">
+      <c r="G72" s="3">
         <v>18807000</v>
       </c>
-      <c r="G72" s="3">
+      <c r="H72" s="3">
         <v>18719000</v>
       </c>
-      <c r="H72" s="3">
+      <c r="I72" s="3">
         <v>19268400</v>
       </c>
-      <c r="I72" s="3">
+      <c r="J72" s="3">
         <v>18710700</v>
       </c>
-      <c r="J72" s="3">
+      <c r="K72" s="3">
         <v>18565400</v>
       </c>
-      <c r="K72" s="3">
+      <c r="L72" s="3">
         <v>18299100</v>
       </c>
-      <c r="L72" s="3">
+      <c r="M72" s="3">
         <v>17812600</v>
       </c>
-      <c r="M72" s="3">
+      <c r="N72" s="3">
         <v>17007700</v>
       </c>
-      <c r="N72" s="3">
+      <c r="O72" s="3">
         <v>17130600</v>
       </c>
-      <c r="O72" s="3">
+      <c r="P72" s="3">
         <v>16662400</v>
       </c>
-      <c r="P72" s="3">
+      <c r="Q72" s="3">
         <v>16044400</v>
       </c>
-      <c r="Q72" s="3">
+      <c r="R72" s="3">
         <v>15764300</v>
       </c>
-      <c r="R72" s="3">
+      <c r="S72" s="3">
         <v>15298800</v>
       </c>
-      <c r="S72" s="3">
+      <c r="T72" s="3">
         <v>14524300</v>
       </c>
-      <c r="T72" s="3">
+      <c r="U72" s="3">
         <v>14258500</v>
       </c>
-      <c r="U72" s="3">
+      <c r="V72" s="3">
         <v>14719300</v>
       </c>
-      <c r="V72" s="3">
+      <c r="W72" s="3">
         <v>14362200</v>
       </c>
-      <c r="W72" s="3">
+      <c r="X72" s="3">
         <v>15002800</v>
       </c>
-      <c r="X72" s="3">
+      <c r="Y72" s="3">
         <v>15745800</v>
       </c>
-      <c r="Y72" s="3">
+      <c r="Z72" s="3">
         <v>15573800</v>
       </c>
-      <c r="Z72" s="3">
+      <c r="AA72" s="3">
         <v>15698600</v>
       </c>
-      <c r="AA72" s="3">
+      <c r="AB72" s="3">
         <v>15678000</v>
       </c>
-      <c r="AB72" s="3">
+      <c r="AC72" s="3">
         <v>14384700</v>
       </c>
-      <c r="AC72" s="3">
+      <c r="AD72" s="3">
         <v>13795900</v>
       </c>
-      <c r="AD72" s="3">
+      <c r="AE72" s="3">
         <v>13837700</v>
       </c>
-      <c r="AE72" s="3">
+      <c r="AF72" s="3">
         <v>13273900</v>
       </c>
-      <c r="AF72" s="3">
+      <c r="AG72" s="3">
         <v>13745600</v>
       </c>
-      <c r="AG72" s="3">
+      <c r="AH72" s="3">
         <v>13660700</v>
       </c>
-      <c r="AH72" s="3">
+      <c r="AI72" s="3">
         <v>13507800</v>
       </c>
-      <c r="AI72" s="3">
+      <c r="AJ72" s="3">
         <v>13138800</v>
       </c>
-      <c r="AJ72" s="3">
+      <c r="AK72" s="3">
         <v>13150400</v>
       </c>
-      <c r="AK72" s="3">
+      <c r="AL72" s="3">
         <v>13062800</v>
       </c>
     </row>
-    <row r="73" spans="2:37" x14ac:dyDescent="0.2">
+    <row r="73" spans="2:38" x14ac:dyDescent="0.2">
       <c r="C73" s="1" t="s">
         <v>65</v>
       </c>
@@ -7092,8 +7268,11 @@
       <c r="AK73" s="3">
         <v>0</v>
       </c>
+      <c r="AL73" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="74" spans="2:37" x14ac:dyDescent="0.2">
+    <row r="74" spans="2:38" x14ac:dyDescent="0.2">
       <c r="C74" s="1" t="s">
         <v>66</v>
       </c>
@@ -7199,8 +7378,11 @@
       <c r="AK74" s="3">
         <v>0</v>
       </c>
+      <c r="AL74" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="75" spans="2:37" x14ac:dyDescent="0.2">
+    <row r="75" spans="2:38" x14ac:dyDescent="0.2">
       <c r="C75" s="1" t="s">
         <v>67</v>
       </c>
@@ -7306,115 +7488,121 @@
       <c r="AK75" s="3">
         <v>0</v>
       </c>
+      <c r="AL75" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="76" spans="2:37" x14ac:dyDescent="0.2">
+    <row r="76" spans="2:38" x14ac:dyDescent="0.2">
       <c r="C76" s="1" t="s">
         <v>68</v>
       </c>
       <c r="D76" s="3">
+        <v>22902500</v>
+      </c>
+      <c r="E76" s="3">
         <v>23081300</v>
       </c>
-      <c r="E76" s="3">
+      <c r="F76" s="3">
         <v>25698700</v>
       </c>
-      <c r="F76" s="3">
+      <c r="G76" s="3">
         <v>24286300</v>
       </c>
-      <c r="G76" s="3">
+      <c r="H76" s="3">
         <v>23977100</v>
       </c>
-      <c r="H76" s="3">
+      <c r="I76" s="3">
         <v>24420000</v>
       </c>
-      <c r="I76" s="3">
+      <c r="J76" s="3">
         <v>23463000</v>
       </c>
-      <c r="J76" s="3">
+      <c r="K76" s="3">
         <v>22963400</v>
       </c>
-      <c r="K76" s="3">
+      <c r="L76" s="3">
         <v>22747400</v>
       </c>
-      <c r="L76" s="3">
+      <c r="M76" s="3">
         <v>21571400</v>
       </c>
-      <c r="M76" s="3">
+      <c r="N76" s="3">
         <v>20624400</v>
       </c>
-      <c r="N76" s="3">
+      <c r="O76" s="3">
         <v>20539800</v>
       </c>
-      <c r="O76" s="3">
+      <c r="P76" s="3">
         <v>20238100</v>
       </c>
-      <c r="P76" s="3">
+      <c r="Q76" s="3">
         <v>19381500</v>
       </c>
-      <c r="Q76" s="3">
+      <c r="R76" s="3">
         <v>18987000</v>
       </c>
-      <c r="R76" s="3">
+      <c r="S76" s="3">
         <v>18419400</v>
       </c>
-      <c r="S76" s="3">
+      <c r="T76" s="3">
         <v>17399500</v>
       </c>
-      <c r="T76" s="3">
+      <c r="U76" s="3">
         <v>17059700</v>
       </c>
-      <c r="U76" s="3">
+      <c r="V76" s="3">
         <v>17519900</v>
       </c>
-      <c r="V76" s="3">
+      <c r="W76" s="3">
         <v>17171900</v>
       </c>
-      <c r="W76" s="3">
+      <c r="X76" s="3">
         <v>17677500</v>
       </c>
-      <c r="X76" s="3">
+      <c r="Y76" s="3">
         <v>18283800</v>
       </c>
-      <c r="Y76" s="3">
+      <c r="Z76" s="3">
         <v>17718000</v>
       </c>
-      <c r="Z76" s="3">
+      <c r="AA76" s="3">
         <v>17110000</v>
       </c>
-      <c r="AA76" s="3">
+      <c r="AB76" s="3">
         <v>17117400</v>
       </c>
-      <c r="AB76" s="3">
+      <c r="AC76" s="3">
         <v>18261500</v>
       </c>
-      <c r="AC76" s="3">
+      <c r="AD76" s="3">
         <v>17579400</v>
       </c>
-      <c r="AD76" s="3">
+      <c r="AE76" s="3">
         <v>17463800</v>
       </c>
-      <c r="AE76" s="3">
+      <c r="AF76" s="3">
         <v>17085700</v>
       </c>
-      <c r="AF76" s="3">
+      <c r="AG76" s="3">
         <v>17922000</v>
       </c>
-      <c r="AG76" s="3">
+      <c r="AH76" s="3">
         <v>17996500</v>
       </c>
-      <c r="AH76" s="3">
+      <c r="AI76" s="3">
         <v>17825600</v>
       </c>
-      <c r="AI76" s="3">
+      <c r="AJ76" s="3">
         <v>17960100</v>
       </c>
-      <c r="AJ76" s="3">
+      <c r="AK76" s="3">
         <v>18347500</v>
       </c>
-      <c r="AK76" s="3">
+      <c r="AL76" s="3">
         <v>18412300</v>
       </c>
     </row>
-    <row r="77" spans="2:37" x14ac:dyDescent="0.2">
+    <row r="77" spans="2:38" x14ac:dyDescent="0.2">
       <c r="C77" s="1" t="s">
         <v>69</v>
       </c>
@@ -7520,227 +7708,236 @@
       <c r="AK77" s="3">
         <v>0</v>
       </c>
+      <c r="AL77" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="79" spans="2:37" x14ac:dyDescent="0.2">
+    <row r="79" spans="2:38" x14ac:dyDescent="0.2">
       <c r="B79" s="1" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="80" spans="2:37" x14ac:dyDescent="0.2">
+    <row r="80" spans="2:38" x14ac:dyDescent="0.2">
       <c r="C80" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D80" s="2">
+        <v>45747</v>
+      </c>
+      <c r="E80" s="2">
         <v>45657</v>
       </c>
-      <c r="E80" s="2">
+      <c r="F80" s="2">
         <v>45565</v>
       </c>
-      <c r="F80" s="2">
+      <c r="G80" s="2">
         <v>45473</v>
       </c>
-      <c r="G80" s="2">
+      <c r="H80" s="2">
         <v>45382</v>
       </c>
-      <c r="H80" s="2">
+      <c r="I80" s="2">
         <v>45291</v>
       </c>
-      <c r="I80" s="2">
+      <c r="J80" s="2">
         <v>45199</v>
       </c>
-      <c r="J80" s="2">
+      <c r="K80" s="2">
         <v>45107</v>
       </c>
-      <c r="K80" s="2">
+      <c r="L80" s="2">
         <v>45016</v>
       </c>
-      <c r="L80" s="2">
+      <c r="M80" s="2">
         <v>44926</v>
       </c>
-      <c r="M80" s="2">
+      <c r="N80" s="2">
         <v>44834</v>
       </c>
-      <c r="N80" s="2">
+      <c r="O80" s="2">
         <v>44742</v>
       </c>
-      <c r="O80" s="2">
+      <c r="P80" s="2">
         <v>44651</v>
       </c>
-      <c r="P80" s="2">
+      <c r="Q80" s="2">
         <v>44561</v>
       </c>
-      <c r="Q80" s="2">
+      <c r="R80" s="2">
         <v>44469</v>
       </c>
-      <c r="R80" s="2">
+      <c r="S80" s="2">
         <v>44377</v>
       </c>
-      <c r="S80" s="2">
+      <c r="T80" s="2">
         <v>44286</v>
       </c>
-      <c r="T80" s="2">
+      <c r="U80" s="2">
         <v>44196</v>
       </c>
-      <c r="U80" s="2">
+      <c r="V80" s="2">
         <v>44104</v>
       </c>
-      <c r="V80" s="2">
+      <c r="W80" s="2">
         <v>44012</v>
       </c>
-      <c r="W80" s="2">
+      <c r="X80" s="2">
         <v>43921</v>
       </c>
-      <c r="X80" s="2">
+      <c r="Y80" s="2">
         <v>43830</v>
       </c>
-      <c r="Y80" s="2">
+      <c r="Z80" s="2">
         <v>43738</v>
       </c>
-      <c r="Z80" s="2">
+      <c r="AA80" s="2">
         <v>43646</v>
       </c>
-      <c r="AA80" s="2">
+      <c r="AB80" s="2">
         <v>43555</v>
       </c>
-      <c r="AB80" s="2">
+      <c r="AC80" s="2">
         <v>43465</v>
       </c>
-      <c r="AC80" s="2">
+      <c r="AD80" s="2">
         <v>43373</v>
       </c>
-      <c r="AD80" s="2">
+      <c r="AE80" s="2">
         <v>43281</v>
       </c>
-      <c r="AE80" s="2">
+      <c r="AF80" s="2">
         <v>43190</v>
       </c>
-      <c r="AF80" s="2">
+      <c r="AG80" s="2">
         <v>43100</v>
       </c>
-      <c r="AG80" s="2">
+      <c r="AH80" s="2">
         <v>43008</v>
       </c>
-      <c r="AH80" s="2">
+      <c r="AI80" s="2">
         <v>42916</v>
       </c>
-      <c r="AI80" s="2">
+      <c r="AJ80" s="2">
         <v>42825</v>
       </c>
-      <c r="AJ80" s="2">
+      <c r="AK80" s="2">
         <v>42735</v>
       </c>
-      <c r="AK80" s="2">
+      <c r="AL80" s="2">
         <v>42643</v>
       </c>
     </row>
-    <row r="81" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="81" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C81" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D81" s="3">
+        <v>418800</v>
+      </c>
+      <c r="E81" s="3">
         <v>288500</v>
       </c>
-      <c r="E81" s="3">
+      <c r="F81" s="3">
         <v>688600</v>
       </c>
-      <c r="F81" s="3">
+      <c r="G81" s="3">
         <v>676000</v>
       </c>
-      <c r="G81" s="3">
+      <c r="H81" s="3">
         <v>613100</v>
       </c>
-      <c r="H81" s="3">
+      <c r="I81" s="3">
         <v>52500</v>
       </c>
-      <c r="I81" s="3">
+      <c r="J81" s="3">
         <v>668000</v>
       </c>
-      <c r="J81" s="3">
+      <c r="K81" s="3">
         <v>474700</v>
       </c>
-      <c r="K81" s="3">
+      <c r="L81" s="3">
         <v>700700</v>
       </c>
-      <c r="L81" s="3">
+      <c r="M81" s="3">
         <v>338800</v>
       </c>
-      <c r="M81" s="3">
+      <c r="N81" s="3">
         <v>640600</v>
       </c>
-      <c r="N81" s="3">
+      <c r="O81" s="3">
         <v>684400</v>
       </c>
-      <c r="O81" s="3">
+      <c r="P81" s="3">
         <v>631400</v>
       </c>
-      <c r="P81" s="3">
+      <c r="Q81" s="3">
         <v>279500</v>
       </c>
-      <c r="Q81" s="3">
+      <c r="R81" s="3">
         <v>570700</v>
       </c>
-      <c r="R81" s="3">
+      <c r="S81" s="3">
         <v>552600</v>
       </c>
-      <c r="S81" s="3">
+      <c r="T81" s="3">
         <v>482000</v>
       </c>
-      <c r="T81" s="3">
+      <c r="U81" s="3">
         <v>112600</v>
       </c>
-      <c r="U81" s="3">
+      <c r="V81" s="3">
         <v>358800</v>
       </c>
-      <c r="V81" s="3">
+      <c r="W81" s="3">
         <v>100500</v>
       </c>
-      <c r="W81" s="3">
+      <c r="X81" s="3">
         <v>412900</v>
       </c>
-      <c r="X81" s="3">
+      <c r="Y81" s="3">
         <v>174900</v>
       </c>
-      <c r="Y81" s="3">
+      <c r="Z81" s="3">
         <v>410100</v>
       </c>
-      <c r="Z81" s="3">
+      <c r="AA81" s="3">
         <v>537700</v>
       </c>
-      <c r="AA81" s="3">
+      <c r="AB81" s="3">
         <v>517500</v>
       </c>
-      <c r="AB81" s="3">
+      <c r="AC81" s="3">
         <v>76800</v>
       </c>
-      <c r="AC81" s="3">
+      <c r="AD81" s="3">
         <v>453900</v>
       </c>
-      <c r="AD81" s="3">
+      <c r="AE81" s="3">
         <v>569900</v>
       </c>
-      <c r="AE81" s="3">
+      <c r="AF81" s="3">
         <v>463600</v>
       </c>
-      <c r="AF81" s="3">
+      <c r="AG81" s="3">
         <v>84900</v>
       </c>
-      <c r="AG81" s="3">
+      <c r="AH81" s="3">
         <v>212100</v>
       </c>
-      <c r="AH81" s="3">
+      <c r="AI81" s="3">
         <v>369000</v>
       </c>
-      <c r="AI81" s="3">
+      <c r="AJ81" s="3">
         <v>517600</v>
       </c>
-      <c r="AJ81" s="3">
+      <c r="AK81" s="3">
         <v>88500</v>
       </c>
-      <c r="AK81" s="3">
+      <c r="AL81" s="3">
         <v>275700</v>
       </c>
     </row>
-    <row r="82" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="82" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C82" s="1" t="s">
         <v>71</v>
       </c>
@@ -7778,115 +7975,119 @@
       <c r="AI82" s="3"/>
       <c r="AJ82" s="3"/>
       <c r="AK82" s="3"/>
+      <c r="AL82" s="3"/>
     </row>
-    <row r="83" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="83" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C83" s="1" t="s">
         <v>72</v>
       </c>
       <c r="D83" s="3">
+        <v>200500</v>
+      </c>
+      <c r="E83" s="3">
         <v>173700</v>
       </c>
-      <c r="E83" s="3">
+      <c r="F83" s="3">
         <v>150800</v>
       </c>
-      <c r="F83" s="3">
+      <c r="G83" s="3">
         <v>153800</v>
       </c>
-      <c r="G83" s="3">
+      <c r="H83" s="3">
         <v>154400</v>
       </c>
-      <c r="H83" s="3">
+      <c r="I83" s="3">
         <v>162700</v>
       </c>
-      <c r="I83" s="3">
+      <c r="J83" s="3">
         <v>133200</v>
       </c>
-      <c r="J83" s="3">
+      <c r="K83" s="3">
         <v>147300</v>
       </c>
-      <c r="K83" s="3">
+      <c r="L83" s="3">
         <v>148000</v>
       </c>
-      <c r="L83" s="3">
+      <c r="M83" s="3">
         <v>185200</v>
       </c>
-      <c r="M83" s="3">
+      <c r="N83" s="3">
         <v>169700</v>
       </c>
-      <c r="N83" s="3">
+      <c r="O83" s="3">
         <v>175600</v>
       </c>
-      <c r="O83" s="3">
+      <c r="P83" s="3">
         <v>168600</v>
       </c>
-      <c r="P83" s="3">
+      <c r="Q83" s="3">
         <v>155900</v>
       </c>
-      <c r="Q83" s="3">
+      <c r="R83" s="3">
         <v>149200</v>
       </c>
-      <c r="R83" s="3">
+      <c r="S83" s="3">
         <v>184500</v>
       </c>
-      <c r="S83" s="3">
+      <c r="T83" s="3">
         <v>102900</v>
       </c>
-      <c r="T83" s="3">
+      <c r="U83" s="3">
         <v>101300</v>
       </c>
-      <c r="U83" s="3">
+      <c r="V83" s="3">
         <v>101500</v>
       </c>
-      <c r="V83" s="3">
+      <c r="W83" s="3">
         <v>98700</v>
       </c>
-      <c r="W83" s="3">
+      <c r="X83" s="3">
         <v>112300</v>
       </c>
-      <c r="X83" s="3">
+      <c r="Y83" s="3">
         <v>120400</v>
       </c>
-      <c r="Y83" s="3">
+      <c r="Z83" s="3">
         <v>116900</v>
       </c>
-      <c r="Z83" s="3">
+      <c r="AA83" s="3">
         <v>108900</v>
       </c>
-      <c r="AA83" s="3">
+      <c r="AB83" s="3">
         <v>93600</v>
       </c>
-      <c r="AB83" s="3">
+      <c r="AC83" s="3">
         <v>61600</v>
       </c>
-      <c r="AC83" s="3">
+      <c r="AD83" s="3">
         <v>58600</v>
       </c>
-      <c r="AD83" s="3">
+      <c r="AE83" s="3">
         <v>56000</v>
       </c>
-      <c r="AE83" s="3">
+      <c r="AF83" s="3">
         <v>50600</v>
       </c>
-      <c r="AF83" s="3">
+      <c r="AG83" s="3">
         <v>49900</v>
       </c>
-      <c r="AG83" s="3">
+      <c r="AH83" s="3">
         <v>50800</v>
       </c>
-      <c r="AH83" s="3">
+      <c r="AI83" s="3">
         <v>51600</v>
       </c>
-      <c r="AI83" s="3">
+      <c r="AJ83" s="3">
         <v>55200</v>
       </c>
-      <c r="AJ83" s="3">
+      <c r="AK83" s="3">
         <v>54800</v>
       </c>
-      <c r="AK83" s="3">
+      <c r="AL83" s="3">
         <v>53700</v>
       </c>
     </row>
-    <row r="84" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="84" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C84" s="1" t="s">
         <v>73</v>
       </c>
@@ -7992,8 +8193,11 @@
       <c r="AK84" s="3">
         <v>0</v>
       </c>
+      <c r="AL84" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="85" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="85" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C85" s="1" t="s">
         <v>74</v>
       </c>
@@ -8099,8 +8303,11 @@
       <c r="AK85" s="3">
         <v>0</v>
       </c>
+      <c r="AL85" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="86" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="86" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C86" s="1" t="s">
         <v>75</v>
       </c>
@@ -8206,8 +8413,11 @@
       <c r="AK86" s="3">
         <v>0</v>
       </c>
+      <c r="AL86" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="87" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="87" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C87" s="1" t="s">
         <v>76</v>
       </c>
@@ -8313,8 +8523,11 @@
       <c r="AK87" s="3">
         <v>0</v>
       </c>
+      <c r="AL87" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="88" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="88" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C88" s="1" t="s">
         <v>77</v>
       </c>
@@ -8420,115 +8633,121 @@
       <c r="AK88" s="3">
         <v>0</v>
       </c>
+      <c r="AL88" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="89" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="89" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C89" s="1" t="s">
         <v>78</v>
       </c>
       <c r="D89" s="3">
+        <v>-1359600</v>
+      </c>
+      <c r="E89" s="3">
         <v>15238500</v>
       </c>
-      <c r="E89" s="3">
+      <c r="F89" s="3">
         <v>-21513100</v>
       </c>
-      <c r="F89" s="3">
+      <c r="G89" s="3">
         <v>-5708900</v>
       </c>
-      <c r="G89" s="3">
+      <c r="H89" s="3">
         <v>3028800</v>
       </c>
-      <c r="H89" s="3">
+      <c r="I89" s="3">
         <v>-13351300</v>
       </c>
-      <c r="I89" s="3">
+      <c r="J89" s="3">
         <v>3754000</v>
       </c>
-      <c r="J89" s="3">
+      <c r="K89" s="3">
         <v>-11714900</v>
       </c>
-      <c r="K89" s="3">
+      <c r="L89" s="3">
         <v>10840700</v>
       </c>
-      <c r="L89" s="3">
+      <c r="M89" s="3">
         <v>12011900</v>
       </c>
-      <c r="M89" s="3">
+      <c r="N89" s="3">
         <v>-3350300</v>
       </c>
-      <c r="N89" s="3">
+      <c r="O89" s="3">
         <v>-2130300</v>
       </c>
-      <c r="O89" s="3">
+      <c r="P89" s="3">
         <v>7700600</v>
       </c>
-      <c r="P89" s="3">
+      <c r="Q89" s="3">
         <v>4027400</v>
       </c>
-      <c r="Q89" s="3">
+      <c r="R89" s="3">
         <v>2586700</v>
       </c>
-      <c r="R89" s="3">
+      <c r="S89" s="3">
         <v>-4607300</v>
       </c>
-      <c r="S89" s="3">
+      <c r="T89" s="3">
         <v>831700</v>
       </c>
-      <c r="T89" s="3">
+      <c r="U89" s="3">
         <v>1545900</v>
       </c>
-      <c r="U89" s="3">
+      <c r="V89" s="3">
         <v>-766500</v>
       </c>
-      <c r="V89" s="3">
+      <c r="W89" s="3">
         <v>2718500</v>
       </c>
-      <c r="W89" s="3">
+      <c r="X89" s="3">
         <v>-824700</v>
       </c>
-      <c r="X89" s="3">
+      <c r="Y89" s="3">
         <v>-153300</v>
       </c>
-      <c r="Y89" s="3">
+      <c r="Z89" s="3">
         <v>-428600</v>
       </c>
-      <c r="Z89" s="3">
+      <c r="AA89" s="3">
         <v>3501700</v>
       </c>
-      <c r="AA89" s="3">
+      <c r="AB89" s="3">
         <v>-1296100</v>
       </c>
-      <c r="AB89" s="3">
+      <c r="AC89" s="3">
         <v>5231600</v>
       </c>
-      <c r="AC89" s="3">
+      <c r="AD89" s="3">
         <v>908000</v>
       </c>
-      <c r="AD89" s="3">
+      <c r="AE89" s="3">
         <v>643600</v>
       </c>
-      <c r="AE89" s="3">
+      <c r="AF89" s="3">
         <v>877700</v>
       </c>
-      <c r="AF89" s="3">
+      <c r="AG89" s="3">
         <v>-506300</v>
       </c>
-      <c r="AG89" s="3">
+      <c r="AH89" s="3">
         <v>-2456000</v>
       </c>
-      <c r="AH89" s="3">
+      <c r="AI89" s="3">
         <v>-340700</v>
       </c>
-      <c r="AI89" s="3">
+      <c r="AJ89" s="3">
         <v>1561500</v>
       </c>
-      <c r="AJ89" s="3">
+      <c r="AK89" s="3">
         <v>108800</v>
       </c>
-      <c r="AK89" s="3">
+      <c r="AL89" s="3">
         <v>3807600</v>
       </c>
     </row>
-    <row r="90" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="90" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C90" s="1" t="s">
         <v>79</v>
       </c>
@@ -8566,115 +8785,119 @@
       <c r="AI90" s="3"/>
       <c r="AJ90" s="3"/>
       <c r="AK90" s="3"/>
+      <c r="AL90" s="3"/>
     </row>
-    <row r="91" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="91" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C91" s="1" t="s">
         <v>80</v>
       </c>
       <c r="D91" s="3">
+        <v>-14600</v>
+      </c>
+      <c r="E91" s="3">
         <v>-32300</v>
       </c>
-      <c r="E91" s="3">
+      <c r="F91" s="3">
         <v>-62500</v>
       </c>
-      <c r="F91" s="3">
+      <c r="G91" s="3">
         <v>-40100</v>
       </c>
-      <c r="G91" s="3">
+      <c r="H91" s="3">
         <v>-27400</v>
       </c>
-      <c r="H91" s="3">
+      <c r="I91" s="3">
         <v>-61300</v>
       </c>
-      <c r="I91" s="3">
+      <c r="J91" s="3">
         <v>-23300</v>
       </c>
-      <c r="J91" s="3">
+      <c r="K91" s="3">
         <v>-23900</v>
       </c>
-      <c r="K91" s="3">
+      <c r="L91" s="3">
         <v>-17100</v>
       </c>
-      <c r="L91" s="3">
+      <c r="M91" s="3">
         <v>-113722000</v>
       </c>
-      <c r="M91" s="3">
+      <c r="N91" s="3">
         <v>-77226000</v>
       </c>
-      <c r="N91" s="3">
+      <c r="O91" s="3">
         <v>-104059000</v>
       </c>
-      <c r="O91" s="3">
+      <c r="P91" s="3">
         <v>-52618000</v>
       </c>
-      <c r="P91" s="3">
+      <c r="Q91" s="3">
         <v>-74615000</v>
       </c>
-      <c r="Q91" s="3">
+      <c r="R91" s="3">
         <v>-81614000</v>
       </c>
-      <c r="R91" s="3">
+      <c r="S91" s="3">
         <v>-15900</v>
       </c>
-      <c r="S91" s="3">
+      <c r="T91" s="3">
         <v>-14300</v>
       </c>
-      <c r="T91" s="3">
+      <c r="U91" s="3">
         <v>-43600</v>
       </c>
-      <c r="U91" s="3">
+      <c r="V91" s="3">
         <v>-25600</v>
       </c>
-      <c r="V91" s="3">
+      <c r="W91" s="3">
         <v>-24800</v>
       </c>
-      <c r="W91" s="3">
+      <c r="X91" s="3">
         <v>-20300</v>
       </c>
-      <c r="X91" s="3">
+      <c r="Y91" s="3">
         <v>-190900</v>
       </c>
-      <c r="Y91" s="3">
+      <c r="Z91" s="3">
         <v>-91000</v>
       </c>
-      <c r="Z91" s="3">
+      <c r="AA91" s="3">
         <v>-55400</v>
       </c>
-      <c r="AA91" s="3">
+      <c r="AB91" s="3">
         <v>-31700</v>
       </c>
-      <c r="AB91" s="3">
+      <c r="AC91" s="3">
         <v>-43000</v>
       </c>
-      <c r="AC91" s="3">
+      <c r="AD91" s="3">
         <v>-20100</v>
       </c>
-      <c r="AD91" s="3">
+      <c r="AE91" s="3">
         <v>-18000</v>
       </c>
-      <c r="AE91" s="3">
+      <c r="AF91" s="3">
         <v>-17800</v>
       </c>
-      <c r="AF91" s="3">
+      <c r="AG91" s="3">
         <v>-25100</v>
       </c>
-      <c r="AG91" s="3">
+      <c r="AH91" s="3">
         <v>-57300</v>
       </c>
-      <c r="AH91" s="3">
+      <c r="AI91" s="3">
         <v>-37900</v>
       </c>
-      <c r="AI91" s="3">
+      <c r="AJ91" s="3">
         <v>-22400</v>
       </c>
-      <c r="AJ91" s="3">
+      <c r="AK91" s="3">
         <v>-111600</v>
       </c>
-      <c r="AK91" s="3">
+      <c r="AL91" s="3">
         <v>-90400</v>
       </c>
     </row>
-    <row r="92" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="92" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C92" s="1" t="s">
         <v>81</v>
       </c>
@@ -8780,8 +9003,11 @@
       <c r="AK92" s="3">
         <v>0</v>
       </c>
+      <c r="AL92" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="93" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="93" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C93" s="1" t="s">
         <v>82</v>
       </c>
@@ -8887,115 +9113,121 @@
       <c r="AK93" s="3">
         <v>0</v>
       </c>
+      <c r="AL93" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="94" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="94" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C94" s="1" t="s">
         <v>83</v>
       </c>
       <c r="D94" s="3">
+        <v>265900</v>
+      </c>
+      <c r="E94" s="3">
         <v>-3917800</v>
       </c>
-      <c r="E94" s="3">
+      <c r="F94" s="3">
         <v>3642700</v>
       </c>
-      <c r="F94" s="3">
+      <c r="G94" s="3">
         <v>-1092400</v>
       </c>
-      <c r="G94" s="3">
+      <c r="H94" s="3">
         <v>1841100</v>
       </c>
-      <c r="H94" s="3">
+      <c r="I94" s="3">
         <v>-625400</v>
       </c>
-      <c r="I94" s="3">
+      <c r="J94" s="3">
         <v>-1107500</v>
       </c>
-      <c r="J94" s="3">
+      <c r="K94" s="3">
         <v>-261600</v>
       </c>
-      <c r="K94" s="3">
+      <c r="L94" s="3">
         <v>300800</v>
       </c>
-      <c r="L94" s="3">
+      <c r="M94" s="3">
         <v>-2910400</v>
       </c>
-      <c r="M94" s="3">
+      <c r="N94" s="3">
         <v>-2354900</v>
       </c>
-      <c r="N94" s="3">
+      <c r="O94" s="3">
         <v>2353800</v>
       </c>
-      <c r="O94" s="3">
+      <c r="P94" s="3">
         <v>-2278800</v>
       </c>
-      <c r="P94" s="3">
+      <c r="Q94" s="3">
         <v>-4489600</v>
       </c>
-      <c r="Q94" s="3">
+      <c r="R94" s="3">
         <v>-3902300</v>
       </c>
-      <c r="R94" s="3">
+      <c r="S94" s="3">
         <v>1124900</v>
       </c>
-      <c r="S94" s="3">
+      <c r="T94" s="3">
         <v>-723400</v>
       </c>
-      <c r="T94" s="3">
+      <c r="U94" s="3">
         <v>-365200</v>
       </c>
-      <c r="U94" s="3">
+      <c r="V94" s="3">
         <v>-124500</v>
       </c>
-      <c r="V94" s="3">
+      <c r="W94" s="3">
         <v>-446100</v>
       </c>
-      <c r="W94" s="3">
+      <c r="X94" s="3">
         <v>-179800</v>
       </c>
-      <c r="X94" s="3">
+      <c r="Y94" s="3">
         <v>-962200</v>
       </c>
-      <c r="Y94" s="3">
+      <c r="Z94" s="3">
         <v>-913600</v>
       </c>
-      <c r="Z94" s="3">
+      <c r="AA94" s="3">
         <v>-5520900</v>
       </c>
-      <c r="AA94" s="3">
+      <c r="AB94" s="3">
         <v>-97900</v>
       </c>
-      <c r="AB94" s="3">
+      <c r="AC94" s="3">
         <v>-5105000</v>
       </c>
-      <c r="AC94" s="3">
+      <c r="AD94" s="3">
         <v>-2452600</v>
       </c>
-      <c r="AD94" s="3">
+      <c r="AE94" s="3">
         <v>-1063800</v>
       </c>
-      <c r="AE94" s="3">
+      <c r="AF94" s="3">
         <v>-587600</v>
       </c>
-      <c r="AF94" s="3">
+      <c r="AG94" s="3">
         <v>1277600</v>
       </c>
-      <c r="AG94" s="3">
+      <c r="AH94" s="3">
         <v>-195600</v>
       </c>
-      <c r="AH94" s="3">
+      <c r="AI94" s="3">
         <v>183200</v>
       </c>
-      <c r="AI94" s="3">
+      <c r="AJ94" s="3">
         <v>392500</v>
       </c>
-      <c r="AJ94" s="3">
+      <c r="AK94" s="3">
         <v>-2371700</v>
       </c>
-      <c r="AK94" s="3">
+      <c r="AL94" s="3">
         <v>694800</v>
       </c>
     </row>
-    <row r="95" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="95" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C95" s="1" t="s">
         <v>84</v>
       </c>
@@ -9033,44 +9265,45 @@
       <c r="AI95" s="3"/>
       <c r="AJ95" s="3"/>
       <c r="AK95" s="3"/>
+      <c r="AL95" s="3"/>
     </row>
-    <row r="96" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="96" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C96" s="1" t="s">
         <v>85</v>
       </c>
       <c r="D96" s="3">
+        <v>26800</v>
+      </c>
+      <c r="E96" s="3">
         <v>117000</v>
       </c>
-      <c r="E96" s="3">
+      <c r="F96" s="3">
         <v>134900</v>
       </c>
-      <c r="F96" s="3">
+      <c r="G96" s="3">
         <v>473000</v>
       </c>
-      <c r="G96" s="3">
+      <c r="H96" s="3">
         <v>26200</v>
       </c>
-      <c r="H96" s="3">
+      <c r="I96" s="3">
         <v>151100</v>
       </c>
-      <c r="I96" s="3">
+      <c r="J96" s="3">
         <v>102000</v>
       </c>
-      <c r="J96" s="3">
+      <c r="K96" s="3">
         <v>566300</v>
       </c>
-      <c r="K96" s="3">
+      <c r="L96" s="3">
         <v>23300</v>
       </c>
-      <c r="L96" s="3">
-        <v>0</v>
-      </c>
       <c r="M96" s="3">
+        <v>0</v>
+      </c>
+      <c r="N96" s="3">
         <v>-79700</v>
       </c>
-      <c r="N96" s="3">
-        <v>0</v>
-      </c>
       <c r="O96" s="3">
         <v>0</v>
       </c>
@@ -9078,11 +9311,11 @@
         <v>0</v>
       </c>
       <c r="Q96" s="3">
+        <v>0</v>
+      </c>
+      <c r="R96" s="3">
         <v>-81300</v>
       </c>
-      <c r="R96" s="3">
-        <v>0</v>
-      </c>
       <c r="S96" s="3">
         <v>0</v>
       </c>
@@ -9126,22 +9359,25 @@
         <v>0</v>
       </c>
       <c r="AG96" s="3">
+        <v>0</v>
+      </c>
+      <c r="AH96" s="3">
         <v>-59200</v>
       </c>
-      <c r="AH96" s="3">
+      <c r="AI96" s="3">
         <v>-237000</v>
       </c>
-      <c r="AI96" s="3">
-        <v>0</v>
-      </c>
       <c r="AJ96" s="3">
+        <v>0</v>
+      </c>
+      <c r="AK96" s="3">
         <v>-38100</v>
       </c>
-      <c r="AK96" s="3">
+      <c r="AL96" s="3">
         <v>-22800</v>
       </c>
     </row>
-    <row r="97" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="97" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C97" s="1" t="s">
         <v>86</v>
       </c>
@@ -9247,8 +9483,11 @@
       <c r="AK97" s="3">
         <v>0</v>
       </c>
+      <c r="AL97" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="98" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="98" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C98" s="1" t="s">
         <v>87</v>
       </c>
@@ -9354,8 +9593,11 @@
       <c r="AK98" s="3">
         <v>0</v>
       </c>
+      <c r="AL98" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="99" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="99" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C99" s="1" t="s">
         <v>88</v>
       </c>
@@ -9461,325 +9703,337 @@
       <c r="AK99" s="3">
         <v>0</v>
       </c>
+      <c r="AL99" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="100" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="100" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C100" s="1" t="s">
         <v>89</v>
       </c>
       <c r="D100" s="3">
+        <v>-68000</v>
+      </c>
+      <c r="E100" s="3">
         <v>-16521000</v>
       </c>
-      <c r="E100" s="3">
+      <c r="F100" s="3">
         <v>24357600</v>
       </c>
-      <c r="F100" s="3">
+      <c r="G100" s="3">
         <v>1880400</v>
       </c>
-      <c r="G100" s="3">
+      <c r="H100" s="3">
         <v>-4107500</v>
       </c>
-      <c r="H100" s="3">
+      <c r="I100" s="3">
         <v>17753300</v>
       </c>
-      <c r="I100" s="3">
+      <c r="J100" s="3">
         <v>447300</v>
       </c>
-      <c r="J100" s="3">
+      <c r="K100" s="3">
         <v>5022900</v>
       </c>
-      <c r="K100" s="3">
+      <c r="L100" s="3">
         <v>-13746200</v>
       </c>
-      <c r="L100" s="3">
+      <c r="M100" s="3">
         <v>-5147300</v>
       </c>
-      <c r="M100" s="3">
+      <c r="N100" s="3">
         <v>1697300</v>
       </c>
-      <c r="N100" s="3">
+      <c r="O100" s="3">
         <v>3000400</v>
       </c>
-      <c r="O100" s="3">
+      <c r="P100" s="3">
         <v>1932700</v>
       </c>
-      <c r="P100" s="3">
+      <c r="Q100" s="3">
         <v>2031800</v>
       </c>
-      <c r="Q100" s="3">
+      <c r="R100" s="3">
         <v>1404600</v>
       </c>
-      <c r="R100" s="3">
+      <c r="S100" s="3">
         <v>2911000</v>
       </c>
-      <c r="S100" s="3">
+      <c r="T100" s="3">
         <v>453200</v>
       </c>
-      <c r="T100" s="3">
+      <c r="U100" s="3">
         <v>261800</v>
       </c>
-      <c r="U100" s="3">
+      <c r="V100" s="3">
         <v>553800</v>
       </c>
-      <c r="V100" s="3">
+      <c r="W100" s="3">
         <v>-2356000</v>
       </c>
-      <c r="W100" s="3">
+      <c r="X100" s="3">
         <v>3526800</v>
       </c>
-      <c r="X100" s="3">
+      <c r="Y100" s="3">
         <v>-950700</v>
       </c>
-      <c r="Y100" s="3">
+      <c r="Z100" s="3">
         <v>3000500</v>
       </c>
-      <c r="Z100" s="3">
+      <c r="AA100" s="3">
         <v>3588600</v>
       </c>
-      <c r="AA100" s="3">
+      <c r="AB100" s="3">
         <v>-289800</v>
       </c>
-      <c r="AB100" s="3">
+      <c r="AC100" s="3">
         <v>491400</v>
       </c>
-      <c r="AC100" s="3">
+      <c r="AD100" s="3">
         <v>1689200</v>
       </c>
-      <c r="AD100" s="3">
+      <c r="AE100" s="3">
         <v>354700</v>
       </c>
-      <c r="AE100" s="3">
+      <c r="AF100" s="3">
         <v>-1323700</v>
       </c>
-      <c r="AF100" s="3">
+      <c r="AG100" s="3">
         <v>-309500</v>
       </c>
-      <c r="AG100" s="3">
+      <c r="AH100" s="3">
         <v>2140800</v>
       </c>
-      <c r="AH100" s="3">
+      <c r="AI100" s="3">
         <v>-384900</v>
       </c>
-      <c r="AI100" s="3">
+      <c r="AJ100" s="3">
         <v>-1500100</v>
       </c>
-      <c r="AJ100" s="3">
+      <c r="AK100" s="3">
         <v>1503800</v>
       </c>
-      <c r="AK100" s="3">
+      <c r="AL100" s="3">
         <v>-1778900</v>
       </c>
     </row>
-    <row r="101" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="101" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C101" s="1" t="s">
         <v>90</v>
       </c>
       <c r="D101" s="3">
+        <v>262700</v>
+      </c>
+      <c r="E101" s="3">
         <v>-179300</v>
       </c>
-      <c r="E101" s="3">
+      <c r="F101" s="3">
         <v>27300</v>
       </c>
-      <c r="F101" s="3">
+      <c r="G101" s="3">
         <v>-105100</v>
       </c>
-      <c r="G101" s="3">
+      <c r="H101" s="3">
         <v>125800</v>
       </c>
-      <c r="H101" s="3">
+      <c r="I101" s="3">
         <v>-1568200</v>
       </c>
-      <c r="I101" s="3">
+      <c r="J101" s="3">
         <v>609200</v>
       </c>
-      <c r="J101" s="3">
+      <c r="K101" s="3">
         <v>667200</v>
       </c>
-      <c r="K101" s="3">
+      <c r="L101" s="3">
         <v>217100</v>
       </c>
-      <c r="L101" s="3">
+      <c r="M101" s="3">
         <v>-1479100</v>
       </c>
-      <c r="M101" s="3">
+      <c r="N101" s="3">
         <v>638600</v>
       </c>
-      <c r="N101" s="3">
+      <c r="O101" s="3">
         <v>657000</v>
       </c>
-      <c r="O101" s="3">
+      <c r="P101" s="3">
         <v>203100</v>
       </c>
-      <c r="P101" s="3">
+      <c r="Q101" s="3">
         <v>68900</v>
       </c>
-      <c r="Q101" s="3">
+      <c r="R101" s="3">
         <v>409500</v>
       </c>
-      <c r="R101" s="3">
+      <c r="S101" s="3">
         <v>18100</v>
       </c>
-      <c r="S101" s="3">
+      <c r="T101" s="3">
         <v>295500</v>
       </c>
-      <c r="T101" s="3">
+      <c r="U101" s="3">
         <v>-571700</v>
       </c>
-      <c r="U101" s="3">
+      <c r="V101" s="3">
         <v>-142900</v>
       </c>
-      <c r="V101" s="3">
+      <c r="W101" s="3">
         <v>-159900</v>
       </c>
-      <c r="W101" s="3">
+      <c r="X101" s="3">
         <v>200400</v>
       </c>
-      <c r="X101" s="3">
+      <c r="Y101" s="3">
         <v>369400</v>
       </c>
-      <c r="Y101" s="3">
+      <c r="Z101" s="3">
         <v>-340600</v>
       </c>
-      <c r="Z101" s="3">
+      <c r="AA101" s="3">
         <v>51200</v>
       </c>
-      <c r="AA101" s="3">
+      <c r="AB101" s="3">
         <v>90500</v>
       </c>
-      <c r="AB101" s="3">
+      <c r="AC101" s="3">
         <v>6400</v>
       </c>
-      <c r="AC101" s="3">
+      <c r="AD101" s="3">
         <v>-76600</v>
       </c>
-      <c r="AD101" s="3">
+      <c r="AE101" s="3">
         <v>218900</v>
       </c>
-      <c r="AE101" s="3">
+      <c r="AF101" s="3">
         <v>50500</v>
       </c>
-      <c r="AF101" s="3">
+      <c r="AG101" s="3">
         <v>-377500</v>
       </c>
-      <c r="AG101" s="3">
+      <c r="AH101" s="3">
         <v>14000</v>
       </c>
-      <c r="AH101" s="3">
+      <c r="AI101" s="3">
         <v>8400</v>
       </c>
-      <c r="AI101" s="3">
+      <c r="AJ101" s="3">
         <v>-108300</v>
       </c>
-      <c r="AJ101" s="3">
+      <c r="AK101" s="3">
         <v>138000</v>
       </c>
-      <c r="AK101" s="3">
+      <c r="AL101" s="3">
         <v>-105900</v>
       </c>
     </row>
-    <row r="102" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="102" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C102" s="1" t="s">
         <v>91</v>
       </c>
       <c r="D102" s="3">
+        <v>-1136400</v>
+      </c>
+      <c r="E102" s="3">
         <v>-4200200</v>
       </c>
-      <c r="E102" s="3">
+      <c r="F102" s="3">
         <v>6101900</v>
       </c>
-      <c r="F102" s="3">
+      <c r="G102" s="3">
         <v>-4689900</v>
       </c>
-      <c r="G102" s="3">
+      <c r="H102" s="3">
         <v>1025100</v>
       </c>
-      <c r="H102" s="3">
+      <c r="I102" s="3">
         <v>3597300</v>
       </c>
-      <c r="I102" s="3">
+      <c r="J102" s="3">
         <v>3121100</v>
       </c>
-      <c r="J102" s="3">
+      <c r="K102" s="3">
         <v>-7058600</v>
       </c>
-      <c r="K102" s="3">
+      <c r="L102" s="3">
         <v>-2478800</v>
       </c>
-      <c r="L102" s="3">
+      <c r="M102" s="3">
         <v>2475100</v>
       </c>
-      <c r="M102" s="3">
+      <c r="N102" s="3">
         <v>-3369400</v>
       </c>
-      <c r="N102" s="3">
+      <c r="O102" s="3">
         <v>3880900</v>
       </c>
-      <c r="O102" s="3">
+      <c r="P102" s="3">
         <v>7557600</v>
       </c>
-      <c r="P102" s="3">
+      <c r="Q102" s="3">
         <v>1638600</v>
       </c>
-      <c r="Q102" s="3">
+      <c r="R102" s="3">
         <v>498500</v>
       </c>
-      <c r="R102" s="3">
+      <c r="S102" s="3">
         <v>-553300</v>
       </c>
-      <c r="S102" s="3">
+      <c r="T102" s="3">
         <v>857000</v>
       </c>
-      <c r="T102" s="3">
+      <c r="U102" s="3">
         <v>870800</v>
       </c>
-      <c r="U102" s="3">
+      <c r="V102" s="3">
         <v>-480000</v>
       </c>
-      <c r="V102" s="3">
+      <c r="W102" s="3">
         <v>-243500</v>
       </c>
-      <c r="W102" s="3">
+      <c r="X102" s="3">
         <v>2722600</v>
       </c>
-      <c r="X102" s="3">
+      <c r="Y102" s="3">
         <v>-1696800</v>
       </c>
-      <c r="Y102" s="3">
+      <c r="Z102" s="3">
         <v>1317700</v>
       </c>
-      <c r="Z102" s="3">
+      <c r="AA102" s="3">
         <v>1620600</v>
       </c>
-      <c r="AA102" s="3">
+      <c r="AB102" s="3">
         <v>-1593300</v>
       </c>
-      <c r="AB102" s="3">
+      <c r="AC102" s="3">
         <v>624400</v>
       </c>
-      <c r="AC102" s="3">
+      <c r="AD102" s="3">
         <v>68000</v>
       </c>
-      <c r="AD102" s="3">
+      <c r="AE102" s="3">
         <v>153400</v>
       </c>
-      <c r="AE102" s="3">
+      <c r="AF102" s="3">
         <v>-983000</v>
       </c>
-      <c r="AF102" s="3">
+      <c r="AG102" s="3">
         <v>84300</v>
       </c>
-      <c r="AG102" s="3">
+      <c r="AH102" s="3">
         <v>-496900</v>
       </c>
-      <c r="AH102" s="3">
+      <c r="AI102" s="3">
         <v>-534100</v>
       </c>
-      <c r="AI102" s="3">
+      <c r="AJ102" s="3">
         <v>345600</v>
       </c>
-      <c r="AJ102" s="3">
+      <c r="AK102" s="3">
         <v>-621200</v>
       </c>
-      <c r="AK102" s="3">
+      <c r="AL102" s="3">
         <v>2617600</v>
       </c>
     </row>

--- a/AAII_Financials/Quarterly/WF_QTR_FIN.xlsx
+++ b/AAII_Financials/Quarterly/WF_QTR_FIN.xlsx
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="200" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="203" uniqueCount="92">
   <si>
     <t>WF</t>
   </si>
@@ -656,284 +656,290 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet2"/>
-  <dimension ref="A5:AL102"/>
+  <dimension ref="A5:AM102"/>
   <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="5" style="1" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="26.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="69.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="12" width="16" style="1" bestFit="1" customWidth="1"/>
-    <col min="13" max="13" width="17" style="1" bestFit="1" customWidth="1"/>
-    <col min="14" max="14" width="16" style="1" bestFit="1" customWidth="1"/>
-    <col min="15" max="15" width="17" style="1" bestFit="1" customWidth="1"/>
-    <col min="16" max="38" width="16" style="1" bestFit="1" customWidth="1"/>
-    <col min="39" max="16384" width="9.140625" style="1"/>
+    <col min="4" max="13" width="16" style="1" bestFit="1" customWidth="1"/>
+    <col min="14" max="14" width="17" style="1" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="16" style="1" bestFit="1" customWidth="1"/>
+    <col min="16" max="16" width="17" style="1" bestFit="1" customWidth="1"/>
+    <col min="17" max="39" width="16" style="1" bestFit="1" customWidth="1"/>
+    <col min="40" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
-    <row r="5" spans="1:38" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:39" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:38" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:39" x14ac:dyDescent="0.2">
       <c r="B6" s="1" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:38" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:39" x14ac:dyDescent="0.2">
       <c r="C7" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D7" s="2">
+        <v>45838</v>
+      </c>
+      <c r="E7" s="2">
         <v>45747</v>
       </c>
-      <c r="E7" s="2">
+      <c r="F7" s="2">
         <v>45657</v>
       </c>
-      <c r="F7" s="2">
+      <c r="G7" s="2">
         <v>45565</v>
       </c>
-      <c r="G7" s="2">
+      <c r="H7" s="2">
         <v>45473</v>
       </c>
-      <c r="H7" s="2">
+      <c r="I7" s="2">
         <v>45382</v>
       </c>
-      <c r="I7" s="2">
+      <c r="J7" s="2">
         <v>45291</v>
       </c>
-      <c r="J7" s="2">
+      <c r="K7" s="2">
         <v>45199</v>
       </c>
-      <c r="K7" s="2">
+      <c r="L7" s="2">
         <v>45107</v>
       </c>
-      <c r="L7" s="2">
+      <c r="M7" s="2">
         <v>45016</v>
       </c>
-      <c r="M7" s="2">
+      <c r="N7" s="2">
         <v>44926</v>
       </c>
-      <c r="N7" s="2">
+      <c r="O7" s="2">
         <v>44834</v>
       </c>
-      <c r="O7" s="2">
+      <c r="P7" s="2">
         <v>44742</v>
       </c>
-      <c r="P7" s="2">
+      <c r="Q7" s="2">
         <v>44651</v>
       </c>
-      <c r="Q7" s="2">
+      <c r="R7" s="2">
         <v>44561</v>
       </c>
-      <c r="R7" s="2">
+      <c r="S7" s="2">
         <v>44469</v>
       </c>
-      <c r="S7" s="2">
+      <c r="T7" s="2">
         <v>44377</v>
       </c>
-      <c r="T7" s="2">
+      <c r="U7" s="2">
         <v>44286</v>
       </c>
-      <c r="U7" s="2">
+      <c r="V7" s="2">
         <v>44196</v>
       </c>
-      <c r="V7" s="2">
+      <c r="W7" s="2">
         <v>44104</v>
       </c>
-      <c r="W7" s="2">
+      <c r="X7" s="2">
         <v>44012</v>
       </c>
-      <c r="X7" s="2">
+      <c r="Y7" s="2">
         <v>43921</v>
       </c>
-      <c r="Y7" s="2">
+      <c r="Z7" s="2">
         <v>43830</v>
       </c>
-      <c r="Z7" s="2">
+      <c r="AA7" s="2">
         <v>43738</v>
       </c>
-      <c r="AA7" s="2">
+      <c r="AB7" s="2">
         <v>43646</v>
       </c>
-      <c r="AB7" s="2">
+      <c r="AC7" s="2">
         <v>43555</v>
       </c>
-      <c r="AC7" s="2">
+      <c r="AD7" s="2">
         <v>43465</v>
       </c>
-      <c r="AD7" s="2">
+      <c r="AE7" s="2">
         <v>43373</v>
       </c>
-      <c r="AE7" s="2">
+      <c r="AF7" s="2">
         <v>43281</v>
       </c>
-      <c r="AF7" s="2">
+      <c r="AG7" s="2">
         <v>43190</v>
       </c>
-      <c r="AG7" s="2">
+      <c r="AH7" s="2">
         <v>43100</v>
       </c>
-      <c r="AH7" s="2">
+      <c r="AI7" s="2">
         <v>43008</v>
       </c>
-      <c r="AI7" s="2">
+      <c r="AJ7" s="2">
         <v>42916</v>
       </c>
-      <c r="AJ7" s="2">
+      <c r="AK7" s="2">
         <v>42825</v>
       </c>
-      <c r="AK7" s="2">
+      <c r="AL7" s="2">
         <v>42735</v>
       </c>
-      <c r="AL7" s="2">
+      <c r="AM7" s="2">
         <v>42643</v>
       </c>
     </row>
-    <row r="8" spans="1:38" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:39" x14ac:dyDescent="0.2">
       <c r="C8" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D8" s="3">
+        <v>1566500</v>
+      </c>
+      <c r="E8" s="3">
         <v>1801500</v>
       </c>
-      <c r="E8" s="3">
+      <c r="F8" s="3">
         <v>2144100</v>
       </c>
-      <c r="F8" s="3">
+      <c r="G8" s="3">
         <v>1797600</v>
       </c>
-      <c r="G8" s="3">
+      <c r="H8" s="3">
         <v>2144400</v>
       </c>
-      <c r="H8" s="3">
+      <c r="I8" s="3">
         <v>2219900</v>
       </c>
-      <c r="I8" s="3">
+      <c r="J8" s="3">
         <v>1264600</v>
       </c>
-      <c r="J8" s="3">
+      <c r="K8" s="3">
         <v>2101400</v>
       </c>
-      <c r="K8" s="3">
+      <c r="L8" s="3">
         <v>1748600</v>
       </c>
-      <c r="L8" s="3">
+      <c r="M8" s="3">
         <v>2091700</v>
       </c>
-      <c r="M8" s="3">
+      <c r="N8" s="3">
         <v>3462200</v>
       </c>
-      <c r="N8" s="3">
+      <c r="O8" s="3">
         <v>2792200</v>
       </c>
-      <c r="O8" s="3">
+      <c r="P8" s="3">
         <v>2487200</v>
       </c>
-      <c r="P8" s="3">
+      <c r="Q8" s="3">
         <v>2264400</v>
       </c>
-      <c r="Q8" s="3">
+      <c r="R8" s="3">
         <v>2026000</v>
       </c>
-      <c r="R8" s="3">
+      <c r="S8" s="3">
         <v>1862200</v>
       </c>
-      <c r="S8" s="3">
+      <c r="T8" s="3">
         <v>1787500</v>
       </c>
-      <c r="T8" s="3">
+      <c r="U8" s="3">
         <v>1722100</v>
       </c>
-      <c r="U8" s="3">
+      <c r="V8" s="3">
         <v>1728200</v>
       </c>
-      <c r="V8" s="3">
+      <c r="W8" s="3">
         <v>1749800</v>
       </c>
-      <c r="W8" s="3">
+      <c r="X8" s="3">
         <v>1857400</v>
       </c>
-      <c r="X8" s="3">
+      <c r="Y8" s="3">
         <v>2028100</v>
       </c>
-      <c r="Y8" s="3">
+      <c r="Z8" s="3">
         <v>2216400</v>
       </c>
-      <c r="Z8" s="3">
+      <c r="AA8" s="3">
         <v>2287800</v>
       </c>
-      <c r="AA8" s="3">
+      <c r="AB8" s="3">
         <v>2353100</v>
       </c>
-      <c r="AB8" s="3">
+      <c r="AC8" s="3">
         <v>2369400</v>
       </c>
-      <c r="AC8" s="3">
+      <c r="AD8" s="3">
         <v>2154000</v>
       </c>
-      <c r="AD8" s="3">
+      <c r="AE8" s="3">
         <v>2006200</v>
       </c>
-      <c r="AE8" s="3">
+      <c r="AF8" s="3">
         <v>1989700</v>
       </c>
-      <c r="AF8" s="3">
+      <c r="AG8" s="3">
         <v>1910800</v>
       </c>
-      <c r="AG8" s="3">
+      <c r="AH8" s="3">
         <v>1912500</v>
       </c>
-      <c r="AH8" s="3">
+      <c r="AI8" s="3">
         <v>1925300</v>
       </c>
-      <c r="AI8" s="3">
+      <c r="AJ8" s="3">
         <v>1853100</v>
       </c>
-      <c r="AJ8" s="3">
+      <c r="AK8" s="3">
         <v>1833700</v>
       </c>
-      <c r="AK8" s="3">
+      <c r="AL8" s="3">
         <v>1898800</v>
       </c>
-      <c r="AL8" s="3">
+      <c r="AM8" s="3">
         <v>1898000</v>
       </c>
     </row>
-    <row r="9" spans="1:38" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:39" x14ac:dyDescent="0.2">
       <c r="C9" s="1" t="s">
         <v>4</v>
       </c>
       <c r="D9" s="3">
+        <v>6400</v>
+      </c>
+      <c r="E9" s="3">
         <v>5900</v>
       </c>
-      <c r="E9" s="3">
+      <c r="F9" s="3">
         <v>7000</v>
       </c>
-      <c r="F9" s="3">
+      <c r="G9" s="3">
         <v>7600</v>
       </c>
-      <c r="G9" s="3">
+      <c r="H9" s="3">
         <v>7000</v>
       </c>
-      <c r="H9" s="3">
+      <c r="I9" s="3">
         <v>7100</v>
       </c>
-      <c r="I9" s="3">
+      <c r="J9" s="3">
         <v>9400</v>
-      </c>
-      <c r="J9" s="3">
-        <v>6800</v>
       </c>
       <c r="K9" s="3">
         <v>6800</v>
       </c>
       <c r="L9" s="3">
+        <v>6800</v>
+      </c>
+      <c r="M9" s="3">
         <v>7100</v>
       </c>
-      <c r="M9" s="3" t="s">
-        <v>5</v>
-      </c>
       <c r="N9" s="3" t="s">
         <v>5</v>
       </c>
@@ -1009,41 +1015,44 @@
       <c r="AL9" s="3" t="s">
         <v>5</v>
       </c>
+      <c r="AM9" s="3" t="s">
+        <v>5</v>
+      </c>
     </row>
-    <row r="10" spans="1:38" x14ac:dyDescent="0.2">
+    <row r="10" spans="1:39" x14ac:dyDescent="0.2">
       <c r="C10" s="1" t="s">
         <v>6</v>
       </c>
       <c r="D10" s="3">
+        <v>1560100</v>
+      </c>
+      <c r="E10" s="3">
         <v>1795600</v>
       </c>
-      <c r="E10" s="3">
+      <c r="F10" s="3">
         <v>2137100</v>
       </c>
-      <c r="F10" s="3">
+      <c r="G10" s="3">
         <v>1790000</v>
       </c>
-      <c r="G10" s="3">
+      <c r="H10" s="3">
         <v>2137400</v>
       </c>
-      <c r="H10" s="3">
+      <c r="I10" s="3">
         <v>2212800</v>
       </c>
-      <c r="I10" s="3">
+      <c r="J10" s="3">
         <v>1255200</v>
       </c>
-      <c r="J10" s="3">
+      <c r="K10" s="3">
         <v>2094600</v>
       </c>
-      <c r="K10" s="3">
+      <c r="L10" s="3">
         <v>1741800</v>
       </c>
-      <c r="L10" s="3">
+      <c r="M10" s="3">
         <v>2084600</v>
       </c>
-      <c r="M10" s="3" t="s">
-        <v>5</v>
-      </c>
       <c r="N10" s="3" t="s">
         <v>5</v>
       </c>
@@ -1119,8 +1128,11 @@
       <c r="AL10" s="3" t="s">
         <v>5</v>
       </c>
+      <c r="AM10" s="3" t="s">
+        <v>5</v>
+      </c>
     </row>
-    <row r="11" spans="1:38" x14ac:dyDescent="0.2">
+    <row r="11" spans="1:39" x14ac:dyDescent="0.2">
       <c r="C11" s="1" t="s">
         <v>7</v>
       </c>
@@ -1159,8 +1171,9 @@
       <c r="AJ11" s="3"/>
       <c r="AK11" s="3"/>
       <c r="AL11" s="3"/>
+      <c r="AM11" s="3"/>
     </row>
-    <row r="12" spans="1:38" x14ac:dyDescent="0.2">
+    <row r="12" spans="1:39" x14ac:dyDescent="0.2">
       <c r="C12" s="1" t="s">
         <v>8</v>
       </c>
@@ -1269,8 +1282,11 @@
       <c r="AL12" s="3" t="s">
         <v>5</v>
       </c>
+      <c r="AM12" s="3" t="s">
+        <v>5</v>
+      </c>
     </row>
-    <row r="13" spans="1:38" x14ac:dyDescent="0.2">
+    <row r="13" spans="1:39" x14ac:dyDescent="0.2">
       <c r="C13" s="1" t="s">
         <v>9</v>
       </c>
@@ -1379,41 +1395,44 @@
       <c r="AL13" s="3">
         <v>0</v>
       </c>
+      <c r="AM13" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="14" spans="1:38" x14ac:dyDescent="0.2">
+    <row r="14" spans="1:39" x14ac:dyDescent="0.2">
       <c r="C14" s="1" t="s">
         <v>10</v>
       </c>
       <c r="D14" s="3">
-        <v>200</v>
+        <v>-600</v>
       </c>
       <c r="E14" s="3">
+        <v>800</v>
+      </c>
+      <c r="F14" s="3">
         <v>6200</v>
       </c>
-      <c r="F14" s="3">
-        <v>0</v>
-      </c>
       <c r="G14" s="3">
-        <v>4600</v>
+        <v>0</v>
       </c>
       <c r="H14" s="3">
-        <v>8400</v>
+        <v>100</v>
       </c>
       <c r="I14" s="3">
+        <v>12300</v>
+      </c>
+      <c r="J14" s="3">
         <v>-1700</v>
       </c>
-      <c r="J14" s="3">
-        <v>0</v>
-      </c>
       <c r="K14" s="3">
+        <v>0</v>
+      </c>
+      <c r="L14" s="3">
         <v>-200</v>
       </c>
-      <c r="L14" s="3">
+      <c r="M14" s="3">
         <v>42300</v>
       </c>
-      <c r="M14" s="3">
-        <v>0</v>
-      </c>
       <c r="N14" s="3">
         <v>0</v>
       </c>
@@ -1489,118 +1508,124 @@
       <c r="AL14" s="3">
         <v>0</v>
       </c>
+      <c r="AM14" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="15" spans="1:38" x14ac:dyDescent="0.2">
+    <row r="15" spans="1:39" x14ac:dyDescent="0.2">
       <c r="C15" s="1" t="s">
         <v>11</v>
       </c>
       <c r="D15" s="3">
+        <v>112700</v>
+      </c>
+      <c r="E15" s="3">
         <v>210100</v>
       </c>
-      <c r="E15" s="3">
+      <c r="F15" s="3">
         <v>150600</v>
       </c>
-      <c r="F15" s="3">
+      <c r="G15" s="3">
         <v>164900</v>
       </c>
-      <c r="G15" s="3">
-        <v>149400</v>
-      </c>
       <c r="H15" s="3">
+        <v>6300</v>
+      </c>
+      <c r="I15" s="3">
         <v>205400</v>
       </c>
-      <c r="I15" s="3">
+      <c r="J15" s="3">
         <v>144200</v>
       </c>
-      <c r="J15" s="3">
+      <c r="K15" s="3">
         <v>130600</v>
       </c>
-      <c r="K15" s="3">
+      <c r="L15" s="3">
         <v>130000</v>
       </c>
-      <c r="L15" s="3">
+      <c r="M15" s="3">
         <v>130100</v>
       </c>
-      <c r="M15" s="3">
+      <c r="N15" s="3">
         <v>-101500</v>
       </c>
-      <c r="N15" s="3">
+      <c r="O15" s="3">
         <v>-92100</v>
       </c>
-      <c r="O15" s="3">
+      <c r="P15" s="3">
         <v>-100700</v>
       </c>
-      <c r="P15" s="3">
+      <c r="Q15" s="3">
         <v>-101400</v>
       </c>
-      <c r="Q15" s="3">
+      <c r="R15" s="3">
         <v>-98200</v>
       </c>
-      <c r="R15" s="3">
+      <c r="S15" s="3">
         <v>-97600</v>
       </c>
-      <c r="S15" s="3">
+      <c r="T15" s="3">
         <v>-97400</v>
       </c>
-      <c r="T15" s="3">
+      <c r="U15" s="3">
         <v>-100600</v>
       </c>
-      <c r="U15" s="3">
+      <c r="V15" s="3">
         <v>-99400</v>
       </c>
-      <c r="V15" s="3">
+      <c r="W15" s="3">
         <v>-99600</v>
       </c>
-      <c r="W15" s="3">
+      <c r="X15" s="3">
         <v>-96100</v>
       </c>
-      <c r="X15" s="3">
+      <c r="Y15" s="3">
         <v>-109500</v>
       </c>
-      <c r="Y15" s="3">
+      <c r="Z15" s="3">
         <v>-115200</v>
       </c>
-      <c r="Z15" s="3">
+      <c r="AA15" s="3">
         <v>-112100</v>
       </c>
-      <c r="AA15" s="3">
+      <c r="AB15" s="3">
         <v>-104100</v>
       </c>
-      <c r="AB15" s="3">
+      <c r="AC15" s="3">
         <v>-88900</v>
       </c>
-      <c r="AC15" s="3">
+      <c r="AD15" s="3">
         <v>-50500</v>
       </c>
-      <c r="AD15" s="3">
+      <c r="AE15" s="3">
         <v>-47800</v>
       </c>
-      <c r="AE15" s="3">
+      <c r="AF15" s="3">
         <v>-44700</v>
       </c>
-      <c r="AF15" s="3">
+      <c r="AG15" s="3">
         <v>-40700</v>
       </c>
-      <c r="AG15" s="3">
+      <c r="AH15" s="3">
         <v>-39500</v>
       </c>
-      <c r="AH15" s="3">
+      <c r="AI15" s="3">
         <v>-40300</v>
       </c>
-      <c r="AI15" s="3">
+      <c r="AJ15" s="3">
         <v>-40800</v>
       </c>
-      <c r="AJ15" s="3">
+      <c r="AK15" s="3">
         <v>-44500</v>
       </c>
-      <c r="AK15" s="3">
+      <c r="AL15" s="3">
         <v>-54800</v>
       </c>
-      <c r="AL15" s="3">
+      <c r="AM15" s="3">
         <v>-53700</v>
       </c>
     </row>
-    <row r="16" spans="1:38" x14ac:dyDescent="0.2">
+    <row r="16" spans="1:39" x14ac:dyDescent="0.2">
       <c r="D16" s="3"/>
       <c r="E16" s="3"/>
       <c r="F16" s="3"/>
@@ -1636,228 +1661,235 @@
       <c r="AJ16" s="3"/>
       <c r="AK16" s="3"/>
       <c r="AL16" s="3"/>
+      <c r="AM16" s="3"/>
     </row>
-    <row r="17" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="17" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C17" s="1" t="s">
         <v>12</v>
       </c>
       <c r="D17" s="3">
+        <v>736000</v>
+      </c>
+      <c r="E17" s="3">
         <v>1211300</v>
       </c>
-      <c r="E17" s="3">
+      <c r="F17" s="3">
         <v>1684700</v>
       </c>
-      <c r="F17" s="3">
+      <c r="G17" s="3">
         <v>887900</v>
       </c>
-      <c r="G17" s="3">
+      <c r="H17" s="3">
         <v>1233600</v>
       </c>
-      <c r="H17" s="3">
+      <c r="I17" s="3">
         <v>1363800</v>
       </c>
-      <c r="I17" s="3">
+      <c r="J17" s="3">
         <v>1160500</v>
       </c>
-      <c r="J17" s="3">
+      <c r="K17" s="3">
         <v>1189600</v>
       </c>
-      <c r="K17" s="3">
+      <c r="L17" s="3">
         <v>1049500</v>
       </c>
-      <c r="L17" s="3">
+      <c r="M17" s="3">
         <v>1131700</v>
       </c>
-      <c r="M17" s="3">
+      <c r="N17" s="3">
         <v>1897900</v>
       </c>
-      <c r="N17" s="3">
+      <c r="O17" s="3">
         <v>1245200</v>
       </c>
-      <c r="O17" s="3">
+      <c r="P17" s="3">
         <v>1121400</v>
       </c>
-      <c r="P17" s="3">
+      <c r="Q17" s="3">
         <v>861300</v>
       </c>
-      <c r="Q17" s="3">
+      <c r="R17" s="3">
         <v>772200</v>
       </c>
-      <c r="R17" s="3">
+      <c r="S17" s="3">
         <v>616800</v>
       </c>
-      <c r="S17" s="3">
+      <c r="T17" s="3">
         <v>573600</v>
       </c>
-      <c r="T17" s="3">
+      <c r="U17" s="3">
         <v>625700</v>
       </c>
-      <c r="U17" s="3">
+      <c r="V17" s="3">
         <v>727900</v>
       </c>
-      <c r="V17" s="3">
+      <c r="W17" s="3">
         <v>721100</v>
       </c>
-      <c r="W17" s="3">
+      <c r="X17" s="3">
         <v>966200</v>
       </c>
-      <c r="X17" s="3">
+      <c r="Y17" s="3">
         <v>926000</v>
       </c>
-      <c r="Y17" s="3">
+      <c r="Z17" s="3">
         <v>1019500</v>
       </c>
-      <c r="Z17" s="3">
+      <c r="AA17" s="3">
         <v>1190700</v>
       </c>
-      <c r="AA17" s="3">
+      <c r="AB17" s="3">
         <v>1111900</v>
       </c>
-      <c r="AB17" s="3">
+      <c r="AC17" s="3">
         <v>1098300</v>
       </c>
-      <c r="AC17" s="3">
+      <c r="AD17" s="3">
         <v>1157200</v>
       </c>
-      <c r="AD17" s="3">
+      <c r="AE17" s="3">
         <v>918800</v>
       </c>
-      <c r="AE17" s="3">
+      <c r="AF17" s="3">
         <v>752200</v>
       </c>
-      <c r="AF17" s="3">
+      <c r="AG17" s="3">
         <v>877900</v>
       </c>
-      <c r="AG17" s="3">
+      <c r="AH17" s="3">
         <v>1026000</v>
       </c>
-      <c r="AH17" s="3">
+      <c r="AI17" s="3">
         <v>926800</v>
       </c>
-      <c r="AI17" s="3">
+      <c r="AJ17" s="3">
         <v>906500</v>
       </c>
-      <c r="AJ17" s="3">
+      <c r="AK17" s="3">
         <v>830000</v>
       </c>
-      <c r="AK17" s="3">
+      <c r="AL17" s="3">
         <v>903100</v>
       </c>
-      <c r="AL17" s="3">
+      <c r="AM17" s="3">
         <v>963600</v>
       </c>
     </row>
-    <row r="18" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="18" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C18" s="1" t="s">
         <v>13</v>
       </c>
       <c r="D18" s="3">
+        <v>830500</v>
+      </c>
+      <c r="E18" s="3">
         <v>590100</v>
       </c>
-      <c r="E18" s="3">
+      <c r="F18" s="3">
         <v>459500</v>
       </c>
-      <c r="F18" s="3">
+      <c r="G18" s="3">
         <v>909700</v>
       </c>
-      <c r="G18" s="3">
+      <c r="H18" s="3">
         <v>910800</v>
       </c>
-      <c r="H18" s="3">
+      <c r="I18" s="3">
         <v>856000</v>
       </c>
-      <c r="I18" s="3">
+      <c r="J18" s="3">
         <v>104100</v>
       </c>
-      <c r="J18" s="3">
+      <c r="K18" s="3">
         <v>911700</v>
       </c>
-      <c r="K18" s="3">
+      <c r="L18" s="3">
         <v>699100</v>
       </c>
-      <c r="L18" s="3">
+      <c r="M18" s="3">
         <v>960100</v>
       </c>
-      <c r="M18" s="3">
+      <c r="N18" s="3">
         <v>1564300</v>
       </c>
-      <c r="N18" s="3">
+      <c r="O18" s="3">
         <v>1547000</v>
       </c>
-      <c r="O18" s="3">
+      <c r="P18" s="3">
         <v>1365800</v>
       </c>
-      <c r="P18" s="3">
+      <c r="Q18" s="3">
         <v>1403000</v>
       </c>
-      <c r="Q18" s="3">
+      <c r="R18" s="3">
         <v>1253800</v>
       </c>
-      <c r="R18" s="3">
+      <c r="S18" s="3">
         <v>1245400</v>
       </c>
-      <c r="S18" s="3">
+      <c r="T18" s="3">
         <v>1213900</v>
       </c>
-      <c r="T18" s="3">
+      <c r="U18" s="3">
         <v>1096400</v>
       </c>
-      <c r="U18" s="3">
+      <c r="V18" s="3">
         <v>1000300</v>
       </c>
-      <c r="V18" s="3">
+      <c r="W18" s="3">
         <v>1028700</v>
       </c>
-      <c r="W18" s="3">
+      <c r="X18" s="3">
         <v>891200</v>
       </c>
-      <c r="X18" s="3">
+      <c r="Y18" s="3">
         <v>1102100</v>
       </c>
-      <c r="Y18" s="3">
+      <c r="Z18" s="3">
         <v>1196900</v>
       </c>
-      <c r="Z18" s="3">
+      <c r="AA18" s="3">
         <v>1097100</v>
       </c>
-      <c r="AA18" s="3">
+      <c r="AB18" s="3">
         <v>1241200</v>
       </c>
-      <c r="AB18" s="3">
+      <c r="AC18" s="3">
         <v>1271100</v>
       </c>
-      <c r="AC18" s="3">
+      <c r="AD18" s="3">
         <v>996800</v>
       </c>
-      <c r="AD18" s="3">
+      <c r="AE18" s="3">
         <v>1087400</v>
       </c>
-      <c r="AE18" s="3">
+      <c r="AF18" s="3">
         <v>1237400</v>
       </c>
-      <c r="AF18" s="3">
+      <c r="AG18" s="3">
         <v>1032900</v>
       </c>
-      <c r="AG18" s="3">
+      <c r="AH18" s="3">
         <v>886500</v>
       </c>
-      <c r="AH18" s="3">
+      <c r="AI18" s="3">
         <v>998500</v>
       </c>
-      <c r="AI18" s="3">
+      <c r="AJ18" s="3">
         <v>946600</v>
       </c>
-      <c r="AJ18" s="3">
+      <c r="AK18" s="3">
         <v>1003700</v>
       </c>
-      <c r="AK18" s="3">
+      <c r="AL18" s="3">
         <v>995700</v>
       </c>
-      <c r="AL18" s="3">
+      <c r="AM18" s="3">
         <v>934400</v>
       </c>
     </row>
-    <row r="19" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="19" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C19" s="1" t="s">
         <v>14</v>
       </c>
@@ -1896,228 +1928,235 @@
       <c r="AJ19" s="3"/>
       <c r="AK19" s="3"/>
       <c r="AL19" s="3"/>
+      <c r="AM19" s="3"/>
     </row>
-    <row r="20" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="20" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C20" s="1" t="s">
         <v>15</v>
       </c>
       <c r="D20" s="3">
-        <v>2800</v>
+        <v>-45600</v>
       </c>
       <c r="E20" s="3">
+        <v>2200</v>
+      </c>
+      <c r="F20" s="3">
         <v>26000</v>
       </c>
-      <c r="F20" s="3">
+      <c r="G20" s="3">
         <v>-4400</v>
       </c>
-      <c r="G20" s="3">
-        <v>1400</v>
-      </c>
       <c r="H20" s="3">
-        <v>-3500</v>
+        <v>5900</v>
       </c>
       <c r="I20" s="3">
+        <v>-7500</v>
+      </c>
+      <c r="J20" s="3">
         <v>11600</v>
       </c>
-      <c r="J20" s="3">
+      <c r="K20" s="3">
         <v>-14500</v>
       </c>
-      <c r="K20" s="3">
+      <c r="L20" s="3">
         <v>32600</v>
       </c>
-      <c r="L20" s="3">
+      <c r="M20" s="3">
         <v>-56500</v>
       </c>
-      <c r="M20" s="3">
+      <c r="N20" s="3">
         <v>-1017300</v>
       </c>
-      <c r="N20" s="3">
+      <c r="O20" s="3">
         <v>-606600</v>
       </c>
-      <c r="O20" s="3">
+      <c r="P20" s="3">
         <v>-375600</v>
       </c>
-      <c r="P20" s="3">
+      <c r="Q20" s="3">
         <v>-505900</v>
       </c>
-      <c r="Q20" s="3">
+      <c r="R20" s="3">
         <v>-806400</v>
       </c>
-      <c r="R20" s="3">
+      <c r="S20" s="3">
         <v>-394200</v>
       </c>
-      <c r="S20" s="3">
+      <c r="T20" s="3">
         <v>-406900</v>
       </c>
-      <c r="T20" s="3">
+      <c r="U20" s="3">
         <v>-399500</v>
       </c>
-      <c r="U20" s="3">
+      <c r="V20" s="3">
         <v>-784600</v>
       </c>
-      <c r="V20" s="3">
+      <c r="W20" s="3">
         <v>-508200</v>
       </c>
-      <c r="W20" s="3">
+      <c r="X20" s="3">
         <v>-674600</v>
       </c>
-      <c r="X20" s="3">
+      <c r="Y20" s="3">
         <v>-492400</v>
       </c>
-      <c r="Y20" s="3">
+      <c r="Z20" s="3">
         <v>-920900</v>
       </c>
-      <c r="Z20" s="3">
+      <c r="AA20" s="3">
         <v>-527400</v>
       </c>
-      <c r="AA20" s="3">
+      <c r="AB20" s="3">
         <v>-447200</v>
       </c>
-      <c r="AB20" s="3">
+      <c r="AC20" s="3">
         <v>-519600</v>
       </c>
-      <c r="AC20" s="3">
+      <c r="AD20" s="3">
         <v>-847700</v>
       </c>
-      <c r="AD20" s="3">
+      <c r="AE20" s="3">
         <v>-418500</v>
       </c>
-      <c r="AE20" s="3">
+      <c r="AF20" s="3">
         <v>-401200</v>
       </c>
-      <c r="AF20" s="3">
+      <c r="AG20" s="3">
         <v>-355800</v>
       </c>
-      <c r="AG20" s="3">
+      <c r="AH20" s="3">
         <v>-756300</v>
       </c>
-      <c r="AH20" s="3">
+      <c r="AI20" s="3">
         <v>-671500</v>
       </c>
-      <c r="AI20" s="3">
+      <c r="AJ20" s="3">
         <v>-417500</v>
       </c>
-      <c r="AJ20" s="3">
+      <c r="AK20" s="3">
         <v>-274500</v>
       </c>
-      <c r="AK20" s="3">
+      <c r="AL20" s="3">
         <v>-821100</v>
       </c>
-      <c r="AL20" s="3">
+      <c r="AM20" s="3">
         <v>-531000</v>
       </c>
     </row>
-    <row r="21" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="21" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C21" s="1" t="s">
         <v>16</v>
       </c>
       <c r="D21" s="3">
-        <v>797400</v>
+        <v>988800</v>
       </c>
       <c r="E21" s="3">
+        <v>798100</v>
+      </c>
+      <c r="F21" s="3">
         <v>584100</v>
       </c>
-      <c r="F21" s="3">
+      <c r="G21" s="3">
         <v>1079100</v>
       </c>
-      <c r="G21" s="3">
-        <v>1058900</v>
-      </c>
       <c r="H21" s="3">
-        <v>1064900</v>
+        <v>911300</v>
       </c>
       <c r="I21" s="3">
+        <v>1068900</v>
+      </c>
+      <c r="J21" s="3">
         <v>236700</v>
       </c>
-      <c r="J21" s="3">
+      <c r="K21" s="3">
         <v>1056800</v>
       </c>
-      <c r="K21" s="3">
+      <c r="L21" s="3">
         <v>796500</v>
       </c>
-      <c r="L21" s="3">
+      <c r="M21" s="3">
         <v>1146700</v>
       </c>
-      <c r="M21" s="3">
+      <c r="N21" s="3">
         <v>732200</v>
       </c>
-      <c r="N21" s="3">
+      <c r="O21" s="3">
         <v>1110000</v>
       </c>
-      <c r="O21" s="3">
+      <c r="P21" s="3">
         <v>1165700</v>
       </c>
-      <c r="P21" s="3">
+      <c r="Q21" s="3">
         <v>1065700</v>
       </c>
-      <c r="Q21" s="3">
+      <c r="R21" s="3">
         <v>603300</v>
       </c>
-      <c r="R21" s="3">
+      <c r="S21" s="3">
         <v>1000500</v>
       </c>
-      <c r="S21" s="3">
+      <c r="T21" s="3">
         <v>991500</v>
       </c>
-      <c r="T21" s="3">
+      <c r="U21" s="3">
         <v>799800</v>
       </c>
-      <c r="U21" s="3">
+      <c r="V21" s="3">
         <v>316900</v>
       </c>
-      <c r="V21" s="3">
+      <c r="W21" s="3">
         <v>622000</v>
       </c>
-      <c r="W21" s="3">
+      <c r="X21" s="3">
         <v>315300</v>
       </c>
-      <c r="X21" s="3">
+      <c r="Y21" s="3">
         <v>721900</v>
       </c>
-      <c r="Y21" s="3">
+      <c r="Z21" s="3">
         <v>396300</v>
       </c>
-      <c r="Z21" s="3">
+      <c r="AA21" s="3">
         <v>686600</v>
       </c>
-      <c r="AA21" s="3">
+      <c r="AB21" s="3">
         <v>902900</v>
       </c>
-      <c r="AB21" s="3">
+      <c r="AC21" s="3">
         <v>845100</v>
       </c>
-      <c r="AC21" s="3">
+      <c r="AD21" s="3">
         <v>210800</v>
       </c>
-      <c r="AD21" s="3">
+      <c r="AE21" s="3">
         <v>727400</v>
       </c>
-      <c r="AE21" s="3">
+      <c r="AF21" s="3">
         <v>892200</v>
       </c>
-      <c r="AF21" s="3">
+      <c r="AG21" s="3">
         <v>727700</v>
       </c>
-      <c r="AG21" s="3">
+      <c r="AH21" s="3">
         <v>180100</v>
       </c>
-      <c r="AH21" s="3">
+      <c r="AI21" s="3">
         <v>377800</v>
       </c>
-      <c r="AI21" s="3">
+      <c r="AJ21" s="3">
         <v>580800</v>
       </c>
-      <c r="AJ21" s="3">
+      <c r="AK21" s="3">
         <v>784400</v>
       </c>
-      <c r="AK21" s="3">
+      <c r="AL21" s="3">
         <v>229400</v>
       </c>
-      <c r="AL21" s="3">
+      <c r="AM21" s="3">
         <v>457200</v>
       </c>
     </row>
-    <row r="22" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="22" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C22" s="1" t="s">
         <v>17</v>
       </c>
@@ -2148,8 +2187,8 @@
       <c r="L22" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="M22" s="3">
-        <v>0</v>
+      <c r="M22" s="3" t="s">
+        <v>5</v>
       </c>
       <c r="N22" s="3">
         <v>0</v>
@@ -2226,228 +2265,237 @@
       <c r="AL22" s="3">
         <v>0</v>
       </c>
+      <c r="AM22" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="23" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="23" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C23" s="1" t="s">
         <v>18</v>
       </c>
       <c r="D23" s="3">
+        <v>876700</v>
+      </c>
+      <c r="E23" s="3">
         <v>587100</v>
       </c>
-      <c r="E23" s="3">
+      <c r="F23" s="3">
         <v>427300</v>
       </c>
-      <c r="F23" s="3">
+      <c r="G23" s="3">
         <v>914200</v>
       </c>
-      <c r="G23" s="3">
+      <c r="H23" s="3">
         <v>904900</v>
       </c>
-      <c r="H23" s="3">
+      <c r="I23" s="3">
         <v>851200</v>
       </c>
-      <c r="I23" s="3">
+      <c r="J23" s="3">
         <v>94200</v>
       </c>
-      <c r="J23" s="3">
+      <c r="K23" s="3">
         <v>926200</v>
       </c>
-      <c r="K23" s="3">
+      <c r="L23" s="3">
         <v>666800</v>
       </c>
-      <c r="L23" s="3">
+      <c r="M23" s="3">
         <v>974300</v>
       </c>
-      <c r="M23" s="3">
+      <c r="N23" s="3">
         <v>546900</v>
       </c>
-      <c r="N23" s="3">
+      <c r="O23" s="3">
         <v>940400</v>
       </c>
-      <c r="O23" s="3">
+      <c r="P23" s="3">
         <v>990200</v>
       </c>
-      <c r="P23" s="3">
+      <c r="Q23" s="3">
         <v>897100</v>
       </c>
-      <c r="Q23" s="3">
+      <c r="R23" s="3">
         <v>447400</v>
       </c>
-      <c r="R23" s="3">
+      <c r="S23" s="3">
         <v>851200</v>
       </c>
-      <c r="S23" s="3">
+      <c r="T23" s="3">
         <v>807000</v>
       </c>
-      <c r="T23" s="3">
+      <c r="U23" s="3">
         <v>696900</v>
       </c>
-      <c r="U23" s="3">
+      <c r="V23" s="3">
         <v>215700</v>
       </c>
-      <c r="V23" s="3">
+      <c r="W23" s="3">
         <v>520500</v>
       </c>
-      <c r="W23" s="3">
+      <c r="X23" s="3">
         <v>216600</v>
       </c>
-      <c r="X23" s="3">
+      <c r="Y23" s="3">
         <v>609600</v>
       </c>
-      <c r="Y23" s="3">
+      <c r="Z23" s="3">
         <v>276000</v>
       </c>
-      <c r="Z23" s="3">
+      <c r="AA23" s="3">
         <v>569700</v>
       </c>
-      <c r="AA23" s="3">
+      <c r="AB23" s="3">
         <v>794000</v>
       </c>
-      <c r="AB23" s="3">
+      <c r="AC23" s="3">
         <v>751500</v>
       </c>
-      <c r="AC23" s="3">
+      <c r="AD23" s="3">
         <v>149100</v>
       </c>
-      <c r="AD23" s="3">
+      <c r="AE23" s="3">
         <v>668900</v>
       </c>
-      <c r="AE23" s="3">
+      <c r="AF23" s="3">
         <v>836200</v>
       </c>
-      <c r="AF23" s="3">
+      <c r="AG23" s="3">
         <v>677100</v>
       </c>
-      <c r="AG23" s="3">
+      <c r="AH23" s="3">
         <v>130200</v>
       </c>
-      <c r="AH23" s="3">
+      <c r="AI23" s="3">
         <v>327000</v>
       </c>
-      <c r="AI23" s="3">
+      <c r="AJ23" s="3">
         <v>529200</v>
       </c>
-      <c r="AJ23" s="3">
+      <c r="AK23" s="3">
         <v>729200</v>
       </c>
-      <c r="AK23" s="3">
+      <c r="AL23" s="3">
         <v>174600</v>
       </c>
-      <c r="AL23" s="3">
+      <c r="AM23" s="3">
         <v>403400</v>
       </c>
     </row>
-    <row r="24" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="24" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C24" s="1" t="s">
         <v>19</v>
       </c>
       <c r="D24" s="3">
+        <v>182300</v>
+      </c>
+      <c r="E24" s="3">
         <v>142600</v>
       </c>
-      <c r="E24" s="3">
+      <c r="F24" s="3">
         <v>120000</v>
       </c>
-      <c r="F24" s="3">
+      <c r="G24" s="3">
         <v>216000</v>
       </c>
-      <c r="G24" s="3">
+      <c r="H24" s="3">
         <v>207100</v>
       </c>
-      <c r="H24" s="3">
+      <c r="I24" s="3">
         <v>227000</v>
       </c>
-      <c r="I24" s="3">
+      <c r="J24" s="3">
         <v>21000</v>
       </c>
-      <c r="J24" s="3">
+      <c r="K24" s="3">
         <v>244100</v>
       </c>
-      <c r="K24" s="3">
+      <c r="L24" s="3">
         <v>160200</v>
       </c>
-      <c r="L24" s="3">
+      <c r="M24" s="3">
         <v>248300</v>
       </c>
-      <c r="M24" s="3">
+      <c r="N24" s="3">
         <v>148500</v>
       </c>
-      <c r="N24" s="3">
+      <c r="O24" s="3">
         <v>259000</v>
       </c>
-      <c r="O24" s="3">
+      <c r="P24" s="3">
         <v>240200</v>
       </c>
-      <c r="P24" s="3">
+      <c r="Q24" s="3">
         <v>225300</v>
       </c>
-      <c r="Q24" s="3">
+      <c r="R24" s="3">
         <v>113100</v>
       </c>
-      <c r="R24" s="3">
+      <c r="S24" s="3">
         <v>232900</v>
       </c>
-      <c r="S24" s="3">
+      <c r="T24" s="3">
         <v>193200</v>
       </c>
-      <c r="T24" s="3">
+      <c r="U24" s="3">
         <v>164900</v>
       </c>
-      <c r="U24" s="3">
+      <c r="V24" s="3">
         <v>53200</v>
       </c>
-      <c r="V24" s="3">
+      <c r="W24" s="3">
         <v>118800</v>
       </c>
-      <c r="W24" s="3">
+      <c r="X24" s="3">
         <v>50000</v>
       </c>
-      <c r="X24" s="3">
+      <c r="Y24" s="3">
         <v>157800</v>
       </c>
-      <c r="Y24" s="3">
+      <c r="Z24" s="3">
         <v>79200</v>
       </c>
-      <c r="Z24" s="3">
+      <c r="AA24" s="3">
         <v>115700</v>
       </c>
-      <c r="AA24" s="3">
+      <c r="AB24" s="3">
         <v>215500</v>
       </c>
-      <c r="AB24" s="3">
+      <c r="AC24" s="3">
         <v>192300</v>
       </c>
-      <c r="AC24" s="3">
+      <c r="AD24" s="3">
         <v>39300</v>
       </c>
-      <c r="AD24" s="3">
+      <c r="AE24" s="3">
         <v>179200</v>
       </c>
-      <c r="AE24" s="3">
+      <c r="AF24" s="3">
         <v>229900</v>
       </c>
-      <c r="AF24" s="3">
+      <c r="AG24" s="3">
         <v>177700</v>
       </c>
-      <c r="AG24" s="3">
+      <c r="AH24" s="3">
         <v>9000</v>
       </c>
-      <c r="AH24" s="3">
+      <c r="AI24" s="3">
         <v>77600</v>
       </c>
-      <c r="AI24" s="3">
+      <c r="AJ24" s="3">
         <v>118800</v>
       </c>
-      <c r="AJ24" s="3">
+      <c r="AK24" s="3">
         <v>163600</v>
       </c>
-      <c r="AK24" s="3">
+      <c r="AL24" s="3">
         <v>30300</v>
       </c>
-      <c r="AL24" s="3">
+      <c r="AM24" s="3">
         <v>80000</v>
       </c>
     </row>
-    <row r="25" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="25" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C25" s="1" t="s">
         <v>20</v>
       </c>
@@ -2556,228 +2604,237 @@
       <c r="AL25" s="3">
         <v>0</v>
       </c>
+      <c r="AM25" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="26" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="26" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C26" s="1" t="s">
         <v>21</v>
       </c>
       <c r="D26" s="3">
+        <v>694400</v>
+      </c>
+      <c r="E26" s="3">
         <v>444500</v>
       </c>
-      <c r="E26" s="3">
+      <c r="F26" s="3">
         <v>307400</v>
       </c>
-      <c r="F26" s="3">
+      <c r="G26" s="3">
         <v>698200</v>
       </c>
-      <c r="G26" s="3">
+      <c r="H26" s="3">
         <v>697800</v>
       </c>
-      <c r="H26" s="3">
+      <c r="I26" s="3">
         <v>624200</v>
       </c>
-      <c r="I26" s="3">
+      <c r="J26" s="3">
         <v>73200</v>
       </c>
-      <c r="J26" s="3">
+      <c r="K26" s="3">
         <v>682000</v>
       </c>
-      <c r="K26" s="3">
+      <c r="L26" s="3">
         <v>506600</v>
       </c>
-      <c r="L26" s="3">
+      <c r="M26" s="3">
         <v>726000</v>
       </c>
-      <c r="M26" s="3">
+      <c r="N26" s="3">
         <v>398500</v>
       </c>
-      <c r="N26" s="3">
+      <c r="O26" s="3">
         <v>681400</v>
       </c>
-      <c r="O26" s="3">
+      <c r="P26" s="3">
         <v>750000</v>
       </c>
-      <c r="P26" s="3">
+      <c r="Q26" s="3">
         <v>671800</v>
       </c>
-      <c r="Q26" s="3">
+      <c r="R26" s="3">
         <v>334300</v>
       </c>
-      <c r="R26" s="3">
+      <c r="S26" s="3">
         <v>618300</v>
       </c>
-      <c r="S26" s="3">
+      <c r="T26" s="3">
         <v>613800</v>
       </c>
-      <c r="T26" s="3">
+      <c r="U26" s="3">
         <v>532000</v>
       </c>
-      <c r="U26" s="3">
+      <c r="V26" s="3">
         <v>162400</v>
       </c>
-      <c r="V26" s="3">
+      <c r="W26" s="3">
         <v>401700</v>
       </c>
-      <c r="W26" s="3">
+      <c r="X26" s="3">
         <v>166500</v>
       </c>
-      <c r="X26" s="3">
+      <c r="Y26" s="3">
         <v>451800</v>
       </c>
-      <c r="Y26" s="3">
+      <c r="Z26" s="3">
         <v>196800</v>
       </c>
-      <c r="Z26" s="3">
+      <c r="AA26" s="3">
         <v>454000</v>
       </c>
-      <c r="AA26" s="3">
+      <c r="AB26" s="3">
         <v>578500</v>
       </c>
-      <c r="AB26" s="3">
+      <c r="AC26" s="3">
         <v>559200</v>
       </c>
-      <c r="AC26" s="3">
+      <c r="AD26" s="3">
         <v>109900</v>
       </c>
-      <c r="AD26" s="3">
+      <c r="AE26" s="3">
         <v>489700</v>
       </c>
-      <c r="AE26" s="3">
+      <c r="AF26" s="3">
         <v>606300</v>
       </c>
-      <c r="AF26" s="3">
+      <c r="AG26" s="3">
         <v>499400</v>
       </c>
-      <c r="AG26" s="3">
+      <c r="AH26" s="3">
         <v>121100</v>
       </c>
-      <c r="AH26" s="3">
+      <c r="AI26" s="3">
         <v>249400</v>
       </c>
-      <c r="AI26" s="3">
+      <c r="AJ26" s="3">
         <v>410300</v>
       </c>
-      <c r="AJ26" s="3">
+      <c r="AK26" s="3">
         <v>565600</v>
       </c>
-      <c r="AK26" s="3">
+      <c r="AL26" s="3">
         <v>144300</v>
       </c>
-      <c r="AL26" s="3">
+      <c r="AM26" s="3">
         <v>323500</v>
       </c>
     </row>
-    <row r="27" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="27" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C27" s="1" t="s">
         <v>22</v>
       </c>
       <c r="D27" s="3">
+        <v>664400</v>
+      </c>
+      <c r="E27" s="3">
         <v>391900</v>
       </c>
-      <c r="E27" s="3">
+      <c r="F27" s="3">
         <v>261600</v>
       </c>
-      <c r="F27" s="3">
+      <c r="G27" s="3">
         <v>655100</v>
       </c>
-      <c r="G27" s="3">
+      <c r="H27" s="3">
         <v>647100</v>
       </c>
-      <c r="H27" s="3">
+      <c r="I27" s="3">
         <v>586900</v>
       </c>
-      <c r="I27" s="3">
+      <c r="J27" s="3">
         <v>25300</v>
       </c>
-      <c r="J27" s="3">
+      <c r="K27" s="3">
         <v>643700</v>
       </c>
-      <c r="K27" s="3">
+      <c r="L27" s="3">
         <v>449800</v>
       </c>
-      <c r="L27" s="3">
+      <c r="M27" s="3">
         <v>677400</v>
       </c>
-      <c r="M27" s="3">
+      <c r="N27" s="3">
         <v>338800</v>
       </c>
-      <c r="N27" s="3">
+      <c r="O27" s="3">
         <v>640600</v>
       </c>
-      <c r="O27" s="3">
+      <c r="P27" s="3">
         <v>684400</v>
       </c>
-      <c r="P27" s="3">
+      <c r="Q27" s="3">
         <v>631400</v>
       </c>
-      <c r="Q27" s="3">
+      <c r="R27" s="3">
         <v>279500</v>
       </c>
-      <c r="R27" s="3">
+      <c r="S27" s="3">
         <v>570700</v>
       </c>
-      <c r="S27" s="3">
+      <c r="T27" s="3">
         <v>552600</v>
       </c>
-      <c r="T27" s="3">
+      <c r="U27" s="3">
         <v>482000</v>
       </c>
-      <c r="U27" s="3">
+      <c r="V27" s="3">
         <v>112600</v>
       </c>
-      <c r="V27" s="3">
+      <c r="W27" s="3">
         <v>358800</v>
       </c>
-      <c r="W27" s="3">
+      <c r="X27" s="3">
         <v>100500</v>
       </c>
-      <c r="X27" s="3">
+      <c r="Y27" s="3">
         <v>412900</v>
       </c>
-      <c r="Y27" s="3">
+      <c r="Z27" s="3">
         <v>174900</v>
       </c>
-      <c r="Z27" s="3">
+      <c r="AA27" s="3">
         <v>410100</v>
       </c>
-      <c r="AA27" s="3">
+      <c r="AB27" s="3">
         <v>537700</v>
       </c>
-      <c r="AB27" s="3">
+      <c r="AC27" s="3">
         <v>517500</v>
       </c>
-      <c r="AC27" s="3">
+      <c r="AD27" s="3">
         <v>76800</v>
       </c>
-      <c r="AD27" s="3">
+      <c r="AE27" s="3">
         <v>453900</v>
       </c>
-      <c r="AE27" s="3">
+      <c r="AF27" s="3">
         <v>569900</v>
       </c>
-      <c r="AF27" s="3">
+      <c r="AG27" s="3">
         <v>463600</v>
       </c>
-      <c r="AG27" s="3">
+      <c r="AH27" s="3">
         <v>84900</v>
       </c>
-      <c r="AH27" s="3">
+      <c r="AI27" s="3">
         <v>212100</v>
       </c>
-      <c r="AI27" s="3">
+      <c r="AJ27" s="3">
         <v>369000</v>
       </c>
-      <c r="AJ27" s="3">
+      <c r="AK27" s="3">
         <v>517600</v>
       </c>
-      <c r="AK27" s="3">
+      <c r="AL27" s="3">
         <v>88500</v>
       </c>
-      <c r="AL27" s="3">
+      <c r="AM27" s="3">
         <v>275700</v>
       </c>
     </row>
-    <row r="28" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="28" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C28" s="1" t="s">
         <v>23</v>
       </c>
@@ -2886,8 +2943,11 @@
       <c r="AL28" s="3">
         <v>0</v>
       </c>
+      <c r="AM28" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="29" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="29" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C29" s="1" t="s">
         <v>24</v>
       </c>
@@ -2996,8 +3056,11 @@
       <c r="AL29" s="3">
         <v>0</v>
       </c>
+      <c r="AM29" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="30" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="30" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C30" s="1" t="s">
         <v>25</v>
       </c>
@@ -3106,8 +3169,11 @@
       <c r="AL30" s="3">
         <v>0</v>
       </c>
+      <c r="AM30" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="31" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="31" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C31" s="1" t="s">
         <v>26</v>
       </c>
@@ -3216,228 +3282,237 @@
       <c r="AL31" s="3">
         <v>0</v>
       </c>
+      <c r="AM31" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="32" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="32" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C32" s="1" t="s">
         <v>27</v>
       </c>
       <c r="D32" s="3">
-        <v>-2800</v>
+        <v>45600</v>
       </c>
       <c r="E32" s="3">
+        <v>-2200</v>
+      </c>
+      <c r="F32" s="3">
         <v>-26000</v>
       </c>
-      <c r="F32" s="3">
+      <c r="G32" s="3">
         <v>4400</v>
       </c>
-      <c r="G32" s="3">
-        <v>-1400</v>
-      </c>
       <c r="H32" s="3">
-        <v>3500</v>
+        <v>-5900</v>
       </c>
       <c r="I32" s="3">
+        <v>7500</v>
+      </c>
+      <c r="J32" s="3">
         <v>-11600</v>
       </c>
-      <c r="J32" s="3">
+      <c r="K32" s="3">
         <v>14500</v>
       </c>
-      <c r="K32" s="3">
+      <c r="L32" s="3">
         <v>-32600</v>
       </c>
-      <c r="L32" s="3">
+      <c r="M32" s="3">
         <v>56500</v>
       </c>
-      <c r="M32" s="3">
+      <c r="N32" s="3">
         <v>1017300</v>
       </c>
-      <c r="N32" s="3">
+      <c r="O32" s="3">
         <v>606600</v>
       </c>
-      <c r="O32" s="3">
+      <c r="P32" s="3">
         <v>375600</v>
       </c>
-      <c r="P32" s="3">
+      <c r="Q32" s="3">
         <v>505900</v>
       </c>
-      <c r="Q32" s="3">
+      <c r="R32" s="3">
         <v>806400</v>
       </c>
-      <c r="R32" s="3">
+      <c r="S32" s="3">
         <v>394200</v>
       </c>
-      <c r="S32" s="3">
+      <c r="T32" s="3">
         <v>406900</v>
       </c>
-      <c r="T32" s="3">
+      <c r="U32" s="3">
         <v>399500</v>
       </c>
-      <c r="U32" s="3">
+      <c r="V32" s="3">
         <v>784600</v>
       </c>
-      <c r="V32" s="3">
+      <c r="W32" s="3">
         <v>508200</v>
       </c>
-      <c r="W32" s="3">
+      <c r="X32" s="3">
         <v>674600</v>
       </c>
-      <c r="X32" s="3">
+      <c r="Y32" s="3">
         <v>492400</v>
       </c>
-      <c r="Y32" s="3">
+      <c r="Z32" s="3">
         <v>920900</v>
       </c>
-      <c r="Z32" s="3">
+      <c r="AA32" s="3">
         <v>527400</v>
       </c>
-      <c r="AA32" s="3">
+      <c r="AB32" s="3">
         <v>447200</v>
       </c>
-      <c r="AB32" s="3">
+      <c r="AC32" s="3">
         <v>519600</v>
       </c>
-      <c r="AC32" s="3">
+      <c r="AD32" s="3">
         <v>847700</v>
       </c>
-      <c r="AD32" s="3">
+      <c r="AE32" s="3">
         <v>418500</v>
       </c>
-      <c r="AE32" s="3">
+      <c r="AF32" s="3">
         <v>401200</v>
       </c>
-      <c r="AF32" s="3">
+      <c r="AG32" s="3">
         <v>355800</v>
       </c>
-      <c r="AG32" s="3">
+      <c r="AH32" s="3">
         <v>756300</v>
       </c>
-      <c r="AH32" s="3">
+      <c r="AI32" s="3">
         <v>671500</v>
       </c>
-      <c r="AI32" s="3">
+      <c r="AJ32" s="3">
         <v>417500</v>
       </c>
-      <c r="AJ32" s="3">
+      <c r="AK32" s="3">
         <v>274500</v>
       </c>
-      <c r="AK32" s="3">
+      <c r="AL32" s="3">
         <v>821100</v>
       </c>
-      <c r="AL32" s="3">
+      <c r="AM32" s="3">
         <v>531000</v>
       </c>
     </row>
-    <row r="33" spans="2:38" x14ac:dyDescent="0.2">
+    <row r="33" spans="2:39" x14ac:dyDescent="0.2">
       <c r="C33" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D33" s="3">
+        <v>691100</v>
+      </c>
+      <c r="E33" s="3">
         <v>418800</v>
       </c>
-      <c r="E33" s="3">
+      <c r="F33" s="3">
         <v>288500</v>
       </c>
-      <c r="F33" s="3">
+      <c r="G33" s="3">
         <v>688600</v>
       </c>
-      <c r="G33" s="3">
+      <c r="H33" s="3">
         <v>676000</v>
       </c>
-      <c r="H33" s="3">
+      <c r="I33" s="3">
         <v>613100</v>
       </c>
-      <c r="I33" s="3">
+      <c r="J33" s="3">
         <v>52500</v>
       </c>
-      <c r="J33" s="3">
+      <c r="K33" s="3">
         <v>668000</v>
       </c>
-      <c r="K33" s="3">
+      <c r="L33" s="3">
         <v>474700</v>
       </c>
-      <c r="L33" s="3">
+      <c r="M33" s="3">
         <v>700700</v>
       </c>
-      <c r="M33" s="3">
+      <c r="N33" s="3">
         <v>338800</v>
       </c>
-      <c r="N33" s="3">
+      <c r="O33" s="3">
         <v>640600</v>
       </c>
-      <c r="O33" s="3">
+      <c r="P33" s="3">
         <v>684400</v>
       </c>
-      <c r="P33" s="3">
+      <c r="Q33" s="3">
         <v>631400</v>
       </c>
-      <c r="Q33" s="3">
+      <c r="R33" s="3">
         <v>279500</v>
       </c>
-      <c r="R33" s="3">
+      <c r="S33" s="3">
         <v>570700</v>
       </c>
-      <c r="S33" s="3">
+      <c r="T33" s="3">
         <v>552600</v>
       </c>
-      <c r="T33" s="3">
+      <c r="U33" s="3">
         <v>482000</v>
       </c>
-      <c r="U33" s="3">
+      <c r="V33" s="3">
         <v>112600</v>
       </c>
-      <c r="V33" s="3">
+      <c r="W33" s="3">
         <v>358800</v>
       </c>
-      <c r="W33" s="3">
+      <c r="X33" s="3">
         <v>100500</v>
       </c>
-      <c r="X33" s="3">
+      <c r="Y33" s="3">
         <v>412900</v>
       </c>
-      <c r="Y33" s="3">
+      <c r="Z33" s="3">
         <v>174900</v>
       </c>
-      <c r="Z33" s="3">
+      <c r="AA33" s="3">
         <v>410100</v>
       </c>
-      <c r="AA33" s="3">
+      <c r="AB33" s="3">
         <v>537700</v>
       </c>
-      <c r="AB33" s="3">
+      <c r="AC33" s="3">
         <v>517500</v>
       </c>
-      <c r="AC33" s="3">
+      <c r="AD33" s="3">
         <v>76800</v>
       </c>
-      <c r="AD33" s="3">
+      <c r="AE33" s="3">
         <v>453900</v>
       </c>
-      <c r="AE33" s="3">
+      <c r="AF33" s="3">
         <v>569900</v>
       </c>
-      <c r="AF33" s="3">
+      <c r="AG33" s="3">
         <v>463600</v>
       </c>
-      <c r="AG33" s="3">
+      <c r="AH33" s="3">
         <v>84900</v>
       </c>
-      <c r="AH33" s="3">
+      <c r="AI33" s="3">
         <v>212100</v>
       </c>
-      <c r="AI33" s="3">
+      <c r="AJ33" s="3">
         <v>369000</v>
       </c>
-      <c r="AJ33" s="3">
+      <c r="AK33" s="3">
         <v>517600</v>
       </c>
-      <c r="AK33" s="3">
+      <c r="AL33" s="3">
         <v>88500</v>
       </c>
-      <c r="AL33" s="3">
+      <c r="AM33" s="3">
         <v>275700</v>
       </c>
     </row>
-    <row r="34" spans="2:38" x14ac:dyDescent="0.2">
+    <row r="34" spans="2:39" x14ac:dyDescent="0.2">
       <c r="C34" s="1" t="s">
         <v>29</v>
       </c>
@@ -3546,233 +3621,242 @@
       <c r="AL34" s="3">
         <v>0</v>
       </c>
+      <c r="AM34" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="35" spans="2:38" x14ac:dyDescent="0.2">
+    <row r="35" spans="2:39" x14ac:dyDescent="0.2">
       <c r="C35" s="1" t="s">
         <v>30</v>
       </c>
       <c r="D35" s="3">
+        <v>691100</v>
+      </c>
+      <c r="E35" s="3">
         <v>418800</v>
       </c>
-      <c r="E35" s="3">
+      <c r="F35" s="3">
         <v>288500</v>
       </c>
-      <c r="F35" s="3">
+      <c r="G35" s="3">
         <v>688600</v>
       </c>
-      <c r="G35" s="3">
+      <c r="H35" s="3">
         <v>676000</v>
       </c>
-      <c r="H35" s="3">
+      <c r="I35" s="3">
         <v>613100</v>
       </c>
-      <c r="I35" s="3">
+      <c r="J35" s="3">
         <v>52500</v>
       </c>
-      <c r="J35" s="3">
+      <c r="K35" s="3">
         <v>668000</v>
       </c>
-      <c r="K35" s="3">
+      <c r="L35" s="3">
         <v>474700</v>
       </c>
-      <c r="L35" s="3">
+      <c r="M35" s="3">
         <v>700700</v>
       </c>
-      <c r="M35" s="3">
+      <c r="N35" s="3">
         <v>338800</v>
       </c>
-      <c r="N35" s="3">
+      <c r="O35" s="3">
         <v>640600</v>
       </c>
-      <c r="O35" s="3">
+      <c r="P35" s="3">
         <v>684400</v>
       </c>
-      <c r="P35" s="3">
+      <c r="Q35" s="3">
         <v>631400</v>
       </c>
-      <c r="Q35" s="3">
+      <c r="R35" s="3">
         <v>279500</v>
       </c>
-      <c r="R35" s="3">
+      <c r="S35" s="3">
         <v>570700</v>
       </c>
-      <c r="S35" s="3">
+      <c r="T35" s="3">
         <v>552600</v>
       </c>
-      <c r="T35" s="3">
+      <c r="U35" s="3">
         <v>482000</v>
       </c>
-      <c r="U35" s="3">
+      <c r="V35" s="3">
         <v>112600</v>
       </c>
-      <c r="V35" s="3">
+      <c r="W35" s="3">
         <v>358800</v>
       </c>
-      <c r="W35" s="3">
+      <c r="X35" s="3">
         <v>100500</v>
       </c>
-      <c r="X35" s="3">
+      <c r="Y35" s="3">
         <v>412900</v>
       </c>
-      <c r="Y35" s="3">
+      <c r="Z35" s="3">
         <v>174900</v>
       </c>
-      <c r="Z35" s="3">
+      <c r="AA35" s="3">
         <v>410100</v>
       </c>
-      <c r="AA35" s="3">
+      <c r="AB35" s="3">
         <v>537700</v>
       </c>
-      <c r="AB35" s="3">
+      <c r="AC35" s="3">
         <v>517500</v>
       </c>
-      <c r="AC35" s="3">
+      <c r="AD35" s="3">
         <v>76800</v>
       </c>
-      <c r="AD35" s="3">
+      <c r="AE35" s="3">
         <v>453900</v>
       </c>
-      <c r="AE35" s="3">
+      <c r="AF35" s="3">
         <v>569900</v>
       </c>
-      <c r="AF35" s="3">
+      <c r="AG35" s="3">
         <v>463600</v>
       </c>
-      <c r="AG35" s="3">
+      <c r="AH35" s="3">
         <v>84900</v>
       </c>
-      <c r="AH35" s="3">
+      <c r="AI35" s="3">
         <v>212100</v>
       </c>
-      <c r="AI35" s="3">
+      <c r="AJ35" s="3">
         <v>369000</v>
       </c>
-      <c r="AJ35" s="3">
+      <c r="AK35" s="3">
         <v>517600</v>
       </c>
-      <c r="AK35" s="3">
+      <c r="AL35" s="3">
         <v>88500</v>
       </c>
-      <c r="AL35" s="3">
+      <c r="AM35" s="3">
         <v>275700</v>
       </c>
     </row>
-    <row r="37" spans="2:38" x14ac:dyDescent="0.2">
+    <row r="37" spans="2:39" x14ac:dyDescent="0.2">
       <c r="B37" s="1" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="38" spans="2:38" x14ac:dyDescent="0.2">
+    <row r="38" spans="2:39" x14ac:dyDescent="0.2">
       <c r="C38" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D38" s="2">
+        <v>45838</v>
+      </c>
+      <c r="E38" s="2">
         <v>45747</v>
       </c>
-      <c r="E38" s="2">
+      <c r="F38" s="2">
         <v>45657</v>
       </c>
-      <c r="F38" s="2">
+      <c r="G38" s="2">
         <v>45565</v>
       </c>
-      <c r="G38" s="2">
+      <c r="H38" s="2">
         <v>45473</v>
       </c>
-      <c r="H38" s="2">
+      <c r="I38" s="2">
         <v>45382</v>
       </c>
-      <c r="I38" s="2">
+      <c r="J38" s="2">
         <v>45291</v>
       </c>
-      <c r="J38" s="2">
+      <c r="K38" s="2">
         <v>45199</v>
       </c>
-      <c r="K38" s="2">
+      <c r="L38" s="2">
         <v>45107</v>
       </c>
-      <c r="L38" s="2">
+      <c r="M38" s="2">
         <v>45016</v>
       </c>
-      <c r="M38" s="2">
+      <c r="N38" s="2">
         <v>44926</v>
       </c>
-      <c r="N38" s="2">
+      <c r="O38" s="2">
         <v>44834</v>
       </c>
-      <c r="O38" s="2">
+      <c r="P38" s="2">
         <v>44742</v>
       </c>
-      <c r="P38" s="2">
+      <c r="Q38" s="2">
         <v>44651</v>
       </c>
-      <c r="Q38" s="2">
+      <c r="R38" s="2">
         <v>44561</v>
       </c>
-      <c r="R38" s="2">
+      <c r="S38" s="2">
         <v>44469</v>
       </c>
-      <c r="S38" s="2">
+      <c r="T38" s="2">
         <v>44377</v>
       </c>
-      <c r="T38" s="2">
+      <c r="U38" s="2">
         <v>44286</v>
       </c>
-      <c r="U38" s="2">
+      <c r="V38" s="2">
         <v>44196</v>
       </c>
-      <c r="V38" s="2">
+      <c r="W38" s="2">
         <v>44104</v>
       </c>
-      <c r="W38" s="2">
+      <c r="X38" s="2">
         <v>44012</v>
       </c>
-      <c r="X38" s="2">
+      <c r="Y38" s="2">
         <v>43921</v>
       </c>
-      <c r="Y38" s="2">
+      <c r="Z38" s="2">
         <v>43830</v>
       </c>
-      <c r="Z38" s="2">
+      <c r="AA38" s="2">
         <v>43738</v>
       </c>
-      <c r="AA38" s="2">
+      <c r="AB38" s="2">
         <v>43646</v>
       </c>
-      <c r="AB38" s="2">
+      <c r="AC38" s="2">
         <v>43555</v>
       </c>
-      <c r="AC38" s="2">
+      <c r="AD38" s="2">
         <v>43465</v>
       </c>
-      <c r="AD38" s="2">
+      <c r="AE38" s="2">
         <v>43373</v>
       </c>
-      <c r="AE38" s="2">
+      <c r="AF38" s="2">
         <v>43281</v>
       </c>
-      <c r="AF38" s="2">
+      <c r="AG38" s="2">
         <v>43190</v>
       </c>
-      <c r="AG38" s="2">
+      <c r="AH38" s="2">
         <v>43100</v>
       </c>
-      <c r="AH38" s="2">
+      <c r="AI38" s="2">
         <v>43008</v>
       </c>
-      <c r="AI38" s="2">
+      <c r="AJ38" s="2">
         <v>42916</v>
       </c>
-      <c r="AJ38" s="2">
+      <c r="AK38" s="2">
         <v>42825</v>
       </c>
-      <c r="AK38" s="2">
+      <c r="AL38" s="2">
         <v>42735</v>
       </c>
-      <c r="AL38" s="2">
+      <c r="AM38" s="2">
         <v>42643</v>
       </c>
     </row>
-    <row r="39" spans="2:38" x14ac:dyDescent="0.2">
+    <row r="39" spans="2:39" x14ac:dyDescent="0.2">
       <c r="C39" s="1" t="s">
         <v>32</v>
       </c>
@@ -3811,8 +3895,9 @@
       <c r="AJ39" s="3"/>
       <c r="AK39" s="3"/>
       <c r="AL39" s="3"/>
+      <c r="AM39" s="3"/>
     </row>
-    <row r="40" spans="2:38" x14ac:dyDescent="0.2">
+    <row r="40" spans="2:39" x14ac:dyDescent="0.2">
       <c r="C40" s="1" t="s">
         <v>33</v>
       </c>
@@ -3851,261 +3936,268 @@
       <c r="AJ40" s="3"/>
       <c r="AK40" s="3"/>
       <c r="AL40" s="3"/>
+      <c r="AM40" s="3"/>
     </row>
-    <row r="41" spans="2:38" x14ac:dyDescent="0.2">
+    <row r="41" spans="2:39" x14ac:dyDescent="0.2">
       <c r="C41" s="1" t="s">
         <v>34</v>
       </c>
       <c r="D41" s="3">
+        <v>9721700</v>
+      </c>
+      <c r="E41" s="3">
         <v>9800400</v>
       </c>
-      <c r="E41" s="3">
+      <c r="F41" s="3">
         <v>9892700</v>
       </c>
-      <c r="F41" s="3">
+      <c r="G41" s="3">
         <v>13834100</v>
       </c>
-      <c r="G41" s="3">
+      <c r="H41" s="3">
         <v>8534800</v>
       </c>
-      <c r="H41" s="3">
+      <c r="I41" s="3">
         <v>13129900</v>
       </c>
-      <c r="I41" s="3">
+      <c r="J41" s="3">
         <v>12476200</v>
       </c>
-      <c r="J41" s="3">
+      <c r="K41" s="3">
         <v>7157900</v>
       </c>
-      <c r="K41" s="3">
+      <c r="L41" s="3">
         <v>9809900</v>
       </c>
-      <c r="L41" s="3">
+      <c r="M41" s="3">
         <v>10234100</v>
       </c>
-      <c r="M41" s="3">
+      <c r="N41" s="3">
         <v>25596900</v>
       </c>
-      <c r="N41" s="3">
+      <c r="O41" s="3">
         <v>6507700</v>
       </c>
-      <c r="O41" s="3">
+      <c r="P41" s="3">
         <v>7377100</v>
       </c>
-      <c r="P41" s="3">
+      <c r="Q41" s="3">
         <v>9785500</v>
       </c>
-      <c r="Q41" s="3">
+      <c r="R41" s="3">
         <v>5555400</v>
       </c>
-      <c r="R41" s="3">
+      <c r="S41" s="3">
         <v>7893500</v>
       </c>
-      <c r="S41" s="3">
+      <c r="T41" s="3">
         <v>7303900</v>
       </c>
-      <c r="T41" s="3">
+      <c r="U41" s="3">
         <v>7996900</v>
       </c>
-      <c r="U41" s="3">
+      <c r="V41" s="3">
         <v>6985700</v>
       </c>
-      <c r="V41" s="3">
+      <c r="W41" s="3">
         <v>6452400</v>
       </c>
-      <c r="W41" s="3">
+      <c r="X41" s="3">
         <v>6934700</v>
       </c>
-      <c r="X41" s="3">
+      <c r="Y41" s="3">
         <v>7810800</v>
       </c>
-      <c r="Y41" s="3">
+      <c r="Z41" s="3">
         <v>5327800</v>
       </c>
-      <c r="Z41" s="3">
+      <c r="AA41" s="3">
         <v>7069900</v>
       </c>
-      <c r="AA41" s="3">
+      <c r="AB41" s="3">
         <v>5777500</v>
       </c>
-      <c r="AB41" s="3">
+      <c r="AC41" s="3">
         <v>4361000</v>
       </c>
-      <c r="AC41" s="3">
+      <c r="AD41" s="3">
         <v>5329900</v>
       </c>
-      <c r="AD41" s="3">
+      <c r="AE41" s="3">
         <v>4608100</v>
       </c>
-      <c r="AE41" s="3">
+      <c r="AF41" s="3">
         <v>4589200</v>
       </c>
-      <c r="AF41" s="3">
+      <c r="AG41" s="3">
         <v>4387400</v>
       </c>
-      <c r="AG41" s="3">
+      <c r="AH41" s="3">
         <v>5323900</v>
       </c>
-      <c r="AH41" s="3">
+      <c r="AI41" s="3">
         <v>5337600</v>
       </c>
-      <c r="AI41" s="3">
+      <c r="AJ41" s="3">
         <v>5780800</v>
       </c>
-      <c r="AJ41" s="3">
+      <c r="AK41" s="3">
         <v>6495200</v>
       </c>
-      <c r="AK41" s="3">
+      <c r="AL41" s="3">
         <v>6385500</v>
       </c>
-      <c r="AL41" s="3">
+      <c r="AM41" s="3">
         <v>7024600</v>
       </c>
     </row>
-    <row r="42" spans="2:38" x14ac:dyDescent="0.2">
+    <row r="42" spans="2:39" x14ac:dyDescent="0.2">
       <c r="C42" s="1" t="s">
         <v>35</v>
       </c>
       <c r="D42" s="3">
-        <v>27028100</v>
+        <v>29338000</v>
       </c>
       <c r="E42" s="3">
+        <v>26987000</v>
+      </c>
+      <c r="F42" s="3">
         <v>22818100</v>
       </c>
-      <c r="F42" s="3">
+      <c r="G42" s="3">
         <v>29370000</v>
       </c>
-      <c r="G42" s="3">
+      <c r="H42" s="3">
         <v>19283100</v>
       </c>
-      <c r="H42" s="3">
+      <c r="I42" s="3">
         <v>18486700</v>
       </c>
-      <c r="I42" s="3">
+      <c r="J42" s="3">
         <v>18215800</v>
       </c>
-      <c r="J42" s="3">
+      <c r="K42" s="3">
         <v>17492100</v>
       </c>
-      <c r="K42" s="3">
+      <c r="L42" s="3">
         <v>25108400</v>
       </c>
-      <c r="L42" s="3">
+      <c r="M42" s="3">
         <v>17703400</v>
       </c>
-      <c r="M42" s="3">
+      <c r="N42" s="3">
         <v>41084100</v>
       </c>
-      <c r="N42" s="3">
+      <c r="O42" s="3">
         <v>48087900</v>
       </c>
-      <c r="O42" s="3">
+      <c r="P42" s="3">
         <v>44907700</v>
       </c>
-      <c r="P42" s="3">
+      <c r="Q42" s="3">
         <v>44616700</v>
       </c>
-      <c r="Q42" s="3">
+      <c r="R42" s="3">
         <v>44083500</v>
       </c>
-      <c r="R42" s="3">
+      <c r="S42" s="3">
         <v>38326100</v>
       </c>
-      <c r="S42" s="3">
+      <c r="T42" s="3">
         <v>33800600</v>
       </c>
-      <c r="T42" s="3">
+      <c r="U42" s="3">
         <v>32013900</v>
       </c>
-      <c r="U42" s="3">
+      <c r="V42" s="3">
         <v>39170300</v>
       </c>
-      <c r="V42" s="3">
+      <c r="W42" s="3">
         <v>33273800</v>
       </c>
-      <c r="W42" s="3">
+      <c r="X42" s="3">
         <v>36396600</v>
       </c>
-      <c r="X42" s="3">
+      <c r="Y42" s="3">
         <v>38606200</v>
       </c>
-      <c r="Y42" s="3">
+      <c r="Z42" s="3">
         <v>37680800</v>
       </c>
-      <c r="Z42" s="3">
+      <c r="AA42" s="3">
         <v>39232200</v>
       </c>
-      <c r="AA42" s="3">
+      <c r="AB42" s="3">
         <v>36892000</v>
       </c>
-      <c r="AB42" s="3">
+      <c r="AC42" s="3">
         <v>30905300</v>
       </c>
-      <c r="AC42" s="3">
+      <c r="AD42" s="3">
         <v>29776700</v>
       </c>
-      <c r="AD42" s="3">
+      <c r="AE42" s="3">
         <v>20883600</v>
       </c>
-      <c r="AE42" s="3">
+      <c r="AF42" s="3">
         <v>22286700</v>
       </c>
-      <c r="AF42" s="3">
+      <c r="AG42" s="3">
         <v>21840100</v>
       </c>
-      <c r="AG42" s="3">
+      <c r="AH42" s="3">
         <v>20932300</v>
       </c>
-      <c r="AH42" s="3">
+      <c r="AI42" s="3">
         <v>12488600</v>
       </c>
-      <c r="AI42" s="3">
+      <c r="AJ42" s="3">
         <v>14955900</v>
       </c>
-      <c r="AJ42" s="3">
+      <c r="AK42" s="3">
         <v>13350900</v>
       </c>
-      <c r="AK42" s="3">
+      <c r="AL42" s="3">
         <v>14204100</v>
       </c>
-      <c r="AL42" s="3">
+      <c r="AM42" s="3">
         <v>16154100</v>
       </c>
     </row>
-    <row r="43" spans="2:38" x14ac:dyDescent="0.2">
+    <row r="43" spans="2:39" x14ac:dyDescent="0.2">
       <c r="C43" s="1" t="s">
         <v>36</v>
       </c>
       <c r="D43" s="3">
+        <v>15335100</v>
+      </c>
+      <c r="E43" s="3">
         <v>12353800</v>
       </c>
-      <c r="E43" s="3">
+      <c r="F43" s="3">
         <v>6099900</v>
       </c>
-      <c r="F43" s="3">
+      <c r="G43" s="3">
         <v>13077600</v>
       </c>
-      <c r="G43" s="3">
+      <c r="H43" s="3">
         <v>9540700</v>
       </c>
-      <c r="H43" s="3">
+      <c r="I43" s="3">
         <v>10078300</v>
       </c>
-      <c r="I43" s="3">
+      <c r="J43" s="3">
         <v>8598900</v>
       </c>
-      <c r="J43" s="3">
+      <c r="K43" s="3">
         <v>9843900</v>
       </c>
-      <c r="K43" s="3">
+      <c r="L43" s="3">
         <v>11594400</v>
       </c>
-      <c r="L43" s="3">
+      <c r="M43" s="3">
         <v>10468300</v>
       </c>
-      <c r="M43" s="3">
-        <v>0</v>
-      </c>
       <c r="N43" s="3">
         <v>0</v>
       </c>
@@ -4181,8 +4273,11 @@
       <c r="AL43" s="3">
         <v>0</v>
       </c>
+      <c r="AM43" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="44" spans="2:38" x14ac:dyDescent="0.2">
+    <row r="44" spans="2:39" x14ac:dyDescent="0.2">
       <c r="C44" s="1" t="s">
         <v>37</v>
       </c>
@@ -4213,8 +4308,8 @@
       <c r="L44" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="M44" s="3">
-        <v>0</v>
+      <c r="M44" s="3" t="s">
+        <v>5</v>
       </c>
       <c r="N44" s="3">
         <v>0</v>
@@ -4291,41 +4386,44 @@
       <c r="AL44" s="3">
         <v>0</v>
       </c>
+      <c r="AM44" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="45" spans="2:38" x14ac:dyDescent="0.2">
+    <row r="45" spans="2:39" x14ac:dyDescent="0.2">
       <c r="C45" s="1" t="s">
         <v>38</v>
       </c>
       <c r="D45" s="3">
-        <v>1943300</v>
+        <v>2304800</v>
       </c>
       <c r="E45" s="3">
+        <v>1984500</v>
+      </c>
+      <c r="F45" s="3">
         <v>3417100</v>
       </c>
-      <c r="F45" s="3">
+      <c r="G45" s="3">
         <v>2191600</v>
       </c>
-      <c r="G45" s="3">
+      <c r="H45" s="3">
         <v>2546100</v>
       </c>
-      <c r="H45" s="3">
+      <c r="I45" s="3">
         <v>2248400</v>
       </c>
-      <c r="I45" s="3">
+      <c r="J45" s="3">
         <v>3229200</v>
       </c>
-      <c r="J45" s="3">
+      <c r="K45" s="3">
         <v>2254000</v>
       </c>
-      <c r="K45" s="3">
+      <c r="L45" s="3">
         <v>2036900</v>
       </c>
-      <c r="L45" s="3">
+      <c r="M45" s="3">
         <v>1992400</v>
       </c>
-      <c r="M45" s="3">
-        <v>0</v>
-      </c>
       <c r="N45" s="3">
         <v>0</v>
       </c>
@@ -4401,41 +4499,44 @@
       <c r="AL45" s="3">
         <v>0</v>
       </c>
+      <c r="AM45" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="46" spans="2:38" x14ac:dyDescent="0.2">
+    <row r="46" spans="2:39" x14ac:dyDescent="0.2">
       <c r="C46" s="1" t="s">
         <v>39</v>
       </c>
       <c r="D46" s="3">
+        <v>69444800</v>
+      </c>
+      <c r="E46" s="3">
         <v>58995800</v>
       </c>
-      <c r="E46" s="3">
+      <c r="F46" s="3">
         <v>51046100</v>
       </c>
-      <c r="F46" s="3">
+      <c r="G46" s="3">
         <v>70438600</v>
       </c>
-      <c r="G46" s="3">
+      <c r="H46" s="3">
         <v>50125600</v>
       </c>
-      <c r="H46" s="3">
+      <c r="I46" s="3">
         <v>54875900</v>
       </c>
-      <c r="I46" s="3">
+      <c r="J46" s="3">
         <v>53874000</v>
       </c>
-      <c r="J46" s="3">
+      <c r="K46" s="3">
         <v>49079800</v>
       </c>
-      <c r="K46" s="3">
+      <c r="L46" s="3">
         <v>55527700</v>
       </c>
-      <c r="L46" s="3">
+      <c r="M46" s="3">
         <v>55109700</v>
       </c>
-      <c r="M46" s="3">
-        <v>0</v>
-      </c>
       <c r="N46" s="3">
         <v>0</v>
       </c>
@@ -4511,338 +4612,350 @@
       <c r="AL46" s="3">
         <v>0</v>
       </c>
+      <c r="AM46" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="47" spans="2:38" x14ac:dyDescent="0.2">
+    <row r="47" spans="2:39" x14ac:dyDescent="0.2">
       <c r="C47" s="1" t="s">
         <v>40</v>
       </c>
       <c r="D47" s="3">
+        <v>44237900</v>
+      </c>
+      <c r="E47" s="3">
         <v>43339500</v>
       </c>
-      <c r="E47" s="3">
+      <c r="F47" s="3">
         <v>29734600</v>
       </c>
-      <c r="F47" s="3">
+      <c r="G47" s="3">
         <v>43909700</v>
       </c>
-      <c r="G47" s="3">
+      <c r="H47" s="3">
         <v>45684200</v>
       </c>
-      <c r="H47" s="3">
+      <c r="I47" s="3">
         <v>45083200</v>
       </c>
-      <c r="I47" s="3">
+      <c r="J47" s="3">
         <v>33573300</v>
       </c>
-      <c r="J47" s="3">
+      <c r="K47" s="3">
         <v>46697400</v>
       </c>
-      <c r="K47" s="3">
+      <c r="L47" s="3">
         <v>47231400</v>
       </c>
-      <c r="L47" s="3">
+      <c r="M47" s="3">
         <v>47653400</v>
       </c>
-      <c r="M47" s="3">
+      <c r="N47" s="3">
         <v>979200</v>
       </c>
-      <c r="N47" s="3">
+      <c r="O47" s="3">
         <v>976800</v>
       </c>
-      <c r="O47" s="3">
+      <c r="P47" s="3">
         <v>1035000</v>
       </c>
-      <c r="P47" s="3">
+      <c r="Q47" s="3">
         <v>1011300</v>
       </c>
-      <c r="Q47" s="3">
+      <c r="R47" s="3">
         <v>1001400</v>
       </c>
-      <c r="R47" s="3">
+      <c r="S47" s="3">
         <v>896000</v>
       </c>
-      <c r="S47" s="3">
+      <c r="T47" s="3">
         <v>881500</v>
       </c>
-      <c r="T47" s="3">
+      <c r="U47" s="3">
         <v>775800</v>
       </c>
-      <c r="U47" s="3">
+      <c r="V47" s="3">
         <v>735000</v>
       </c>
-      <c r="V47" s="3">
+      <c r="W47" s="3">
         <v>829200</v>
       </c>
-      <c r="W47" s="3">
+      <c r="X47" s="3">
         <v>714700</v>
       </c>
-      <c r="X47" s="3">
+      <c r="Y47" s="3">
         <v>674300</v>
       </c>
-      <c r="Y47" s="3">
+      <c r="Z47" s="3">
         <v>685400</v>
       </c>
-      <c r="Z47" s="3">
+      <c r="AA47" s="3">
         <v>322100</v>
       </c>
-      <c r="AA47" s="3">
+      <c r="AB47" s="3">
         <v>311500</v>
       </c>
-      <c r="AB47" s="3">
+      <c r="AC47" s="3">
         <v>316200</v>
       </c>
-      <c r="AC47" s="3">
+      <c r="AD47" s="3">
         <v>303600</v>
       </c>
-      <c r="AD47" s="3">
+      <c r="AE47" s="3">
         <v>276700</v>
       </c>
-      <c r="AE47" s="3">
+      <c r="AF47" s="3">
         <v>346900</v>
       </c>
-      <c r="AF47" s="3">
+      <c r="AG47" s="3">
         <v>348200</v>
       </c>
-      <c r="AG47" s="3">
+      <c r="AH47" s="3">
         <v>367000</v>
       </c>
-      <c r="AH47" s="3">
+      <c r="AI47" s="3">
         <v>490900</v>
       </c>
-      <c r="AI47" s="3">
+      <c r="AJ47" s="3">
         <v>326300</v>
       </c>
-      <c r="AJ47" s="3">
+      <c r="AK47" s="3">
         <v>351100</v>
       </c>
-      <c r="AK47" s="3">
+      <c r="AL47" s="3">
         <v>395100</v>
       </c>
-      <c r="AL47" s="3">
+      <c r="AM47" s="3">
         <v>377600</v>
       </c>
     </row>
-    <row r="48" spans="2:38" x14ac:dyDescent="0.2">
+    <row r="48" spans="2:39" x14ac:dyDescent="0.2">
       <c r="C48" s="1" t="s">
         <v>41</v>
       </c>
       <c r="D48" s="3">
+        <v>5310400</v>
+      </c>
+      <c r="E48" s="3">
         <v>4933500</v>
       </c>
-      <c r="E48" s="3">
+      <c r="F48" s="3">
         <v>4937200</v>
       </c>
-      <c r="F48" s="3">
+      <c r="G48" s="3">
         <v>5522800</v>
       </c>
-      <c r="G48" s="3">
+      <c r="H48" s="3">
         <v>5103100</v>
       </c>
-      <c r="H48" s="3">
+      <c r="I48" s="3">
         <v>4908300</v>
       </c>
-      <c r="I48" s="3">
+      <c r="J48" s="3">
         <v>4983700</v>
       </c>
-      <c r="J48" s="3">
+      <c r="K48" s="3">
         <v>4486300</v>
       </c>
-      <c r="K48" s="3">
+      <c r="L48" s="3">
         <v>4434900</v>
       </c>
-      <c r="L48" s="3">
+      <c r="M48" s="3">
         <v>4401200</v>
       </c>
-      <c r="M48" s="3">
+      <c r="N48" s="3">
         <v>2648000</v>
       </c>
-      <c r="N48" s="3">
+      <c r="O48" s="3">
         <v>2590300</v>
       </c>
-      <c r="O48" s="3">
+      <c r="P48" s="3">
         <v>2689200</v>
       </c>
-      <c r="P48" s="3">
+      <c r="Q48" s="3">
         <v>2729900</v>
       </c>
-      <c r="Q48" s="3">
+      <c r="R48" s="3">
         <v>2673200</v>
       </c>
-      <c r="R48" s="3">
+      <c r="S48" s="3">
         <v>2701000</v>
       </c>
-      <c r="S48" s="3">
+      <c r="T48" s="3">
         <v>2682600</v>
       </c>
-      <c r="T48" s="3">
+      <c r="U48" s="3">
         <v>2700600</v>
       </c>
-      <c r="U48" s="3">
+      <c r="V48" s="3">
         <v>2719200</v>
       </c>
-      <c r="V48" s="3">
+      <c r="W48" s="3">
         <v>2764300</v>
       </c>
-      <c r="W48" s="3">
+      <c r="X48" s="3">
         <v>2790300</v>
       </c>
-      <c r="X48" s="3">
+      <c r="Y48" s="3">
         <v>2961700</v>
       </c>
-      <c r="Y48" s="3">
+      <c r="Z48" s="3">
         <v>3098200</v>
       </c>
-      <c r="Z48" s="3">
+      <c r="AA48" s="3">
         <v>3089800</v>
       </c>
-      <c r="AA48" s="3">
+      <c r="AB48" s="3">
         <v>3058200</v>
       </c>
-      <c r="AB48" s="3">
+      <c r="AC48" s="3">
         <v>3080600</v>
       </c>
-      <c r="AC48" s="3">
+      <c r="AD48" s="3">
         <v>2368100</v>
       </c>
-      <c r="AD48" s="3">
+      <c r="AE48" s="3">
         <v>2284800</v>
       </c>
-      <c r="AE48" s="3">
+      <c r="AF48" s="3">
         <v>2378800</v>
       </c>
-      <c r="AF48" s="3">
+      <c r="AG48" s="3">
         <v>2384000</v>
       </c>
-      <c r="AG48" s="3">
+      <c r="AH48" s="3">
         <v>2507000</v>
       </c>
-      <c r="AH48" s="3">
+      <c r="AI48" s="3">
         <v>2509800</v>
       </c>
-      <c r="AI48" s="3">
+      <c r="AJ48" s="3">
         <v>2480800</v>
       </c>
-      <c r="AJ48" s="3">
+      <c r="AK48" s="3">
         <v>2470200</v>
       </c>
-      <c r="AK48" s="3">
+      <c r="AL48" s="3">
         <v>2534900</v>
       </c>
-      <c r="AL48" s="3">
+      <c r="AM48" s="3">
         <v>2525400</v>
       </c>
     </row>
-    <row r="49" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="49" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C49" s="1" t="s">
         <v>42</v>
       </c>
       <c r="D49" s="3">
+        <v>788000</v>
+      </c>
+      <c r="E49" s="3">
         <v>745500</v>
       </c>
-      <c r="E49" s="3">
+      <c r="F49" s="3">
         <v>552200</v>
       </c>
-      <c r="F49" s="3">
+      <c r="G49" s="3">
         <v>621800</v>
       </c>
-      <c r="G49" s="3">
+      <c r="H49" s="3">
         <v>557800</v>
       </c>
-      <c r="H49" s="3">
+      <c r="I49" s="3">
         <v>562600</v>
       </c>
-      <c r="I49" s="3">
+      <c r="J49" s="3">
         <v>582000</v>
       </c>
-      <c r="J49" s="3">
+      <c r="K49" s="3">
         <v>568100</v>
       </c>
-      <c r="K49" s="3">
+      <c r="L49" s="3">
         <v>586300</v>
       </c>
-      <c r="L49" s="3">
+      <c r="M49" s="3">
         <v>573300</v>
       </c>
-      <c r="M49" s="3">
+      <c r="N49" s="3">
         <v>636800</v>
       </c>
-      <c r="N49" s="3">
+      <c r="O49" s="3">
         <v>639200</v>
       </c>
-      <c r="O49" s="3">
+      <c r="P49" s="3">
         <v>596500</v>
       </c>
-      <c r="P49" s="3">
+      <c r="Q49" s="3">
         <v>608700</v>
       </c>
-      <c r="Q49" s="3">
+      <c r="R49" s="3">
         <v>589000</v>
       </c>
-      <c r="R49" s="3">
+      <c r="S49" s="3">
         <v>586400</v>
       </c>
-      <c r="S49" s="3">
+      <c r="T49" s="3">
         <v>581700</v>
       </c>
-      <c r="T49" s="3">
+      <c r="U49" s="3">
         <v>582600</v>
       </c>
-      <c r="U49" s="3">
+      <c r="V49" s="3">
         <v>586100</v>
       </c>
-      <c r="V49" s="3">
+      <c r="W49" s="3">
         <v>615800</v>
       </c>
-      <c r="W49" s="3">
+      <c r="X49" s="3">
         <v>631700</v>
       </c>
-      <c r="X49" s="3">
+      <c r="Y49" s="3">
         <v>668000</v>
       </c>
-      <c r="Y49" s="3">
+      <c r="Z49" s="3">
         <v>717500</v>
       </c>
-      <c r="Z49" s="3">
+      <c r="AA49" s="3">
         <v>590200</v>
       </c>
-      <c r="AA49" s="3">
+      <c r="AB49" s="3">
         <v>565800</v>
       </c>
-      <c r="AB49" s="3">
+      <c r="AC49" s="3">
         <v>588900</v>
       </c>
-      <c r="AC49" s="3">
+      <c r="AD49" s="3">
         <v>493300</v>
       </c>
-      <c r="AD49" s="3">
+      <c r="AE49" s="3">
         <v>502400</v>
       </c>
-      <c r="AE49" s="3">
+      <c r="AF49" s="3">
         <v>549000</v>
       </c>
-      <c r="AF49" s="3">
+      <c r="AG49" s="3">
         <v>452700</v>
       </c>
-      <c r="AG49" s="3">
+      <c r="AH49" s="3">
         <v>456400</v>
       </c>
-      <c r="AH49" s="3">
+      <c r="AI49" s="3">
         <v>461900</v>
       </c>
-      <c r="AI49" s="3">
+      <c r="AJ49" s="3">
         <v>446100</v>
       </c>
-      <c r="AJ49" s="3">
+      <c r="AK49" s="3">
         <v>415100</v>
       </c>
-      <c r="AK49" s="3">
+      <c r="AL49" s="3">
         <v>435400</v>
       </c>
-      <c r="AL49" s="3">
+      <c r="AM49" s="3">
         <v>376700</v>
       </c>
     </row>
-    <row r="50" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="50" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C50" s="1" t="s">
         <v>43</v>
       </c>
@@ -4951,8 +5064,11 @@
       <c r="AL50" s="3">
         <v>0</v>
       </c>
+      <c r="AM50" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="51" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="51" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C51" s="1" t="s">
         <v>44</v>
       </c>
@@ -5061,118 +5177,124 @@
       <c r="AL51" s="3">
         <v>0</v>
       </c>
+      <c r="AM51" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="52" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="52" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C52" s="1" t="s">
         <v>45</v>
       </c>
       <c r="D52" s="3">
+        <v>1343400</v>
+      </c>
+      <c r="E52" s="3">
         <v>1099500</v>
       </c>
-      <c r="E52" s="3">
+      <c r="F52" s="3">
         <v>15193100</v>
       </c>
-      <c r="F52" s="3">
+      <c r="G52" s="3">
         <v>1117800</v>
       </c>
-      <c r="G52" s="3">
+      <c r="H52" s="3">
         <v>1097200</v>
       </c>
-      <c r="H52" s="3">
+      <c r="I52" s="3">
         <v>1375500</v>
       </c>
-      <c r="I52" s="3">
+      <c r="J52" s="3">
         <v>16836600</v>
       </c>
-      <c r="J52" s="3">
+      <c r="K52" s="3">
         <v>1488400</v>
       </c>
-      <c r="K52" s="3">
+      <c r="L52" s="3">
         <v>1186200</v>
       </c>
-      <c r="L52" s="3">
+      <c r="M52" s="3">
         <v>1174600</v>
       </c>
-      <c r="M52" s="3">
+      <c r="N52" s="3">
         <v>331800</v>
       </c>
-      <c r="N52" s="3">
+      <c r="O52" s="3">
         <v>284500</v>
       </c>
-      <c r="O52" s="3">
+      <c r="P52" s="3">
         <v>166400</v>
       </c>
-      <c r="P52" s="3">
+      <c r="Q52" s="3">
         <v>58400</v>
       </c>
-      <c r="Q52" s="3">
+      <c r="R52" s="3">
         <v>59100</v>
       </c>
-      <c r="R52" s="3">
+      <c r="S52" s="3">
         <v>41100</v>
       </c>
-      <c r="S52" s="3">
+      <c r="T52" s="3">
         <v>56000</v>
       </c>
-      <c r="T52" s="3">
+      <c r="U52" s="3">
         <v>73700</v>
       </c>
-      <c r="U52" s="3">
+      <c r="V52" s="3">
         <v>82700</v>
       </c>
-      <c r="V52" s="3">
+      <c r="W52" s="3">
         <v>74500</v>
       </c>
-      <c r="W52" s="3">
+      <c r="X52" s="3">
         <v>37800</v>
       </c>
-      <c r="X52" s="3">
+      <c r="Y52" s="3">
         <v>38200</v>
       </c>
-      <c r="Y52" s="3">
+      <c r="Z52" s="3">
         <v>44800</v>
       </c>
-      <c r="Z52" s="3">
+      <c r="AA52" s="3">
         <v>82300</v>
       </c>
-      <c r="AA52" s="3">
+      <c r="AB52" s="3">
         <v>69500</v>
       </c>
-      <c r="AB52" s="3">
+      <c r="AC52" s="3">
         <v>68200</v>
       </c>
-      <c r="AC52" s="3">
+      <c r="AD52" s="3">
         <v>120400</v>
       </c>
-      <c r="AD52" s="3">
+      <c r="AE52" s="3">
         <v>36800</v>
       </c>
-      <c r="AE52" s="3">
+      <c r="AF52" s="3">
         <v>91100</v>
       </c>
-      <c r="AF52" s="3">
+      <c r="AG52" s="3">
         <v>177600</v>
       </c>
-      <c r="AG52" s="3">
+      <c r="AH52" s="3">
         <v>289300</v>
       </c>
-      <c r="AH52" s="3">
+      <c r="AI52" s="3">
         <v>234800</v>
       </c>
-      <c r="AI52" s="3">
+      <c r="AJ52" s="3">
         <v>221100</v>
       </c>
-      <c r="AJ52" s="3">
+      <c r="AK52" s="3">
         <v>262700</v>
       </c>
-      <c r="AK52" s="3">
+      <c r="AL52" s="3">
         <v>274800</v>
       </c>
-      <c r="AL52" s="3">
+      <c r="AM52" s="3">
         <v>143800</v>
       </c>
     </row>
-    <row r="53" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="53" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C53" s="1" t="s">
         <v>46</v>
       </c>
@@ -5281,118 +5403,124 @@
       <c r="AL53" s="3">
         <v>0</v>
       </c>
+      <c r="AM53" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="54" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="54" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C54" s="1" t="s">
         <v>47</v>
       </c>
       <c r="D54" s="3">
+        <v>394651000</v>
+      </c>
+      <c r="E54" s="3">
         <v>361721400</v>
       </c>
-      <c r="E54" s="3">
+      <c r="F54" s="3">
         <v>355900000</v>
       </c>
-      <c r="F54" s="3">
+      <c r="G54" s="3">
         <v>413964600</v>
       </c>
-      <c r="G54" s="3">
+      <c r="H54" s="3">
         <v>369217100</v>
       </c>
-      <c r="H54" s="3">
+      <c r="I54" s="3">
         <v>375587700</v>
       </c>
-      <c r="I54" s="3">
+      <c r="J54" s="3">
         <v>384037900</v>
       </c>
-      <c r="J54" s="3">
+      <c r="K54" s="3">
         <v>360962600</v>
       </c>
-      <c r="K54" s="3">
+      <c r="L54" s="3">
         <v>366653200</v>
       </c>
-      <c r="L54" s="3">
+      <c r="M54" s="3">
         <v>366661700</v>
       </c>
-      <c r="M54" s="3">
+      <c r="N54" s="3">
         <v>360355800</v>
       </c>
-      <c r="N54" s="3">
+      <c r="O54" s="3">
         <v>366510300</v>
       </c>
-      <c r="O54" s="3">
+      <c r="P54" s="3">
         <v>368558700</v>
       </c>
-      <c r="P54" s="3">
+      <c r="Q54" s="3">
         <v>358592300</v>
       </c>
-      <c r="Q54" s="3">
+      <c r="R54" s="3">
         <v>335387900</v>
       </c>
-      <c r="R54" s="3">
+      <c r="S54" s="3">
         <v>328638700</v>
       </c>
-      <c r="S54" s="3">
+      <c r="T54" s="3">
         <v>315953000</v>
       </c>
-      <c r="T54" s="3">
+      <c r="U54" s="3">
         <v>307917200</v>
       </c>
-      <c r="U54" s="3">
+      <c r="V54" s="3">
         <v>295320000</v>
       </c>
-      <c r="V54" s="3">
+      <c r="W54" s="3">
         <v>293246000</v>
       </c>
-      <c r="W54" s="3">
+      <c r="X54" s="3">
         <v>292659600</v>
       </c>
-      <c r="X54" s="3">
+      <c r="Y54" s="3">
         <v>306353500</v>
       </c>
-      <c r="Y54" s="3">
+      <c r="Z54" s="3">
         <v>307683600</v>
       </c>
-      <c r="Z54" s="3">
+      <c r="AA54" s="3">
         <v>314996600</v>
       </c>
-      <c r="AA54" s="3">
+      <c r="AB54" s="3">
         <v>316273500</v>
       </c>
-      <c r="AB54" s="3">
+      <c r="AC54" s="3">
         <v>314085600</v>
       </c>
-      <c r="AC54" s="3">
+      <c r="AD54" s="3">
         <v>285975600</v>
       </c>
-      <c r="AD54" s="3">
+      <c r="AE54" s="3">
         <v>267139300</v>
       </c>
-      <c r="AE54" s="3">
+      <c r="AF54" s="3">
         <v>274311500</v>
       </c>
-      <c r="AF54" s="3">
+      <c r="AG54" s="3">
         <v>273668600</v>
       </c>
-      <c r="AG54" s="3">
+      <c r="AH54" s="3">
         <v>278340000</v>
       </c>
-      <c r="AH54" s="3">
+      <c r="AI54" s="3">
         <v>279730100</v>
       </c>
-      <c r="AI54" s="3">
+      <c r="AJ54" s="3">
         <v>278137400</v>
       </c>
-      <c r="AJ54" s="3">
+      <c r="AK54" s="3">
         <v>273600800</v>
       </c>
-      <c r="AK54" s="3">
+      <c r="AL54" s="3">
         <v>279614500</v>
       </c>
-      <c r="AL54" s="3">
+      <c r="AM54" s="3">
         <v>281548700</v>
       </c>
     </row>
-    <row r="55" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="55" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C55" s="1" t="s">
         <v>48</v>
       </c>
@@ -5431,8 +5559,9 @@
       <c r="AJ55" s="3"/>
       <c r="AK55" s="3"/>
       <c r="AL55" s="3"/>
+      <c r="AM55" s="3"/>
     </row>
-    <row r="56" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="56" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C56" s="1" t="s">
         <v>49</v>
       </c>
@@ -5471,151 +5600,155 @@
       <c r="AJ56" s="3"/>
       <c r="AK56" s="3"/>
       <c r="AL56" s="3"/>
+      <c r="AM56" s="3"/>
     </row>
-    <row r="57" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="57" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C57" s="1" t="s">
         <v>50</v>
       </c>
       <c r="D57" s="3">
+        <v>287825900</v>
+      </c>
+      <c r="E57" s="3">
         <v>262183700</v>
       </c>
-      <c r="E57" s="3">
+      <c r="F57" s="3">
         <v>253583100</v>
       </c>
-      <c r="F57" s="3">
+      <c r="G57" s="3">
         <v>303683400</v>
       </c>
-      <c r="G57" s="3">
+      <c r="H57" s="3">
         <v>269353200</v>
       </c>
-      <c r="H57" s="3">
+      <c r="I57" s="3">
         <v>273669100</v>
       </c>
-      <c r="I57" s="3">
+      <c r="J57" s="3">
         <v>283746600</v>
       </c>
-      <c r="J57" s="3">
+      <c r="K57" s="3">
         <v>257925300</v>
       </c>
-      <c r="K57" s="3">
+      <c r="L57" s="3">
         <v>263215600</v>
       </c>
-      <c r="L57" s="3">
+      <c r="M57" s="3">
         <v>259046400</v>
       </c>
-      <c r="M57" s="3">
+      <c r="N57" s="3">
         <v>8592200</v>
       </c>
-      <c r="N57" s="3">
+      <c r="O57" s="3">
         <v>12736100</v>
       </c>
-      <c r="O57" s="3">
+      <c r="P57" s="3">
         <v>12538100</v>
       </c>
-      <c r="P57" s="3">
+      <c r="Q57" s="3">
         <v>11104000</v>
       </c>
-      <c r="Q57" s="3">
+      <c r="R57" s="3">
         <v>10844700</v>
       </c>
-      <c r="R57" s="3">
+      <c r="S57" s="3">
         <v>7957500</v>
       </c>
-      <c r="S57" s="3">
+      <c r="T57" s="3">
         <v>9468900</v>
       </c>
-      <c r="T57" s="3">
+      <c r="U57" s="3">
         <v>7995800</v>
       </c>
-      <c r="U57" s="3">
+      <c r="V57" s="3">
         <v>3698600</v>
       </c>
-      <c r="V57" s="3">
+      <c r="W57" s="3">
         <v>7530800</v>
       </c>
-      <c r="W57" s="3">
+      <c r="X57" s="3">
         <v>8467000</v>
       </c>
-      <c r="X57" s="3">
+      <c r="Y57" s="3">
         <v>9538600</v>
       </c>
-      <c r="Y57" s="3">
+      <c r="Z57" s="3">
         <v>7264700</v>
       </c>
-      <c r="Z57" s="3">
+      <c r="AA57" s="3">
         <v>13339700</v>
       </c>
-      <c r="AA57" s="3">
+      <c r="AB57" s="3">
         <v>15138200</v>
       </c>
-      <c r="AB57" s="3">
+      <c r="AC57" s="3">
         <v>14778600</v>
       </c>
-      <c r="AC57" s="3">
+      <c r="AD57" s="3">
         <v>10988500</v>
       </c>
-      <c r="AD57" s="3">
+      <c r="AE57" s="3">
         <v>12068900</v>
       </c>
-      <c r="AE57" s="3">
+      <c r="AF57" s="3">
         <v>11638400</v>
       </c>
-      <c r="AF57" s="3">
+      <c r="AG57" s="3">
         <v>12317300</v>
       </c>
-      <c r="AG57" s="3">
+      <c r="AH57" s="3">
         <v>5801500</v>
       </c>
-      <c r="AH57" s="3">
+      <c r="AI57" s="3">
         <v>13814400</v>
       </c>
-      <c r="AI57" s="3">
+      <c r="AJ57" s="3">
         <v>14756900</v>
       </c>
-      <c r="AJ57" s="3">
+      <c r="AK57" s="3">
         <v>10823000</v>
       </c>
-      <c r="AK57" s="3">
+      <c r="AL57" s="3">
         <v>13329400</v>
       </c>
-      <c r="AL57" s="3">
+      <c r="AM57" s="3">
         <v>15356600</v>
       </c>
     </row>
-    <row r="58" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="58" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C58" s="1" t="s">
         <v>51</v>
       </c>
       <c r="D58" s="3">
+        <v>8966800</v>
+      </c>
+      <c r="E58" s="3">
         <v>10611200</v>
       </c>
-      <c r="E58" s="3">
+      <c r="F58" s="3">
         <v>12014400</v>
       </c>
-      <c r="F58" s="3">
+      <c r="G58" s="3">
         <v>10388900</v>
       </c>
-      <c r="G58" s="3">
+      <c r="H58" s="3">
         <v>10701400</v>
       </c>
-      <c r="H58" s="3">
+      <c r="I58" s="3">
         <v>11337600</v>
       </c>
-      <c r="I58" s="3">
+      <c r="J58" s="3">
         <v>9863100</v>
       </c>
-      <c r="J58" s="3">
+      <c r="K58" s="3">
         <v>11103300</v>
       </c>
-      <c r="K58" s="3">
+      <c r="L58" s="3">
         <v>10559700</v>
       </c>
-      <c r="L58" s="3">
+      <c r="M58" s="3">
         <v>10550500</v>
       </c>
-      <c r="M58" s="3">
-        <v>0</v>
-      </c>
       <c r="N58" s="3">
         <v>0</v>
       </c>
@@ -5691,151 +5824,157 @@
       <c r="AL58" s="3">
         <v>0</v>
       </c>
+      <c r="AM58" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="59" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="59" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C59" s="1" t="s">
         <v>52</v>
       </c>
       <c r="D59" s="3">
+        <v>1084300</v>
+      </c>
+      <c r="E59" s="3">
         <v>825800</v>
       </c>
-      <c r="E59" s="3">
+      <c r="F59" s="3">
         <v>747300</v>
       </c>
-      <c r="F59" s="3">
+      <c r="G59" s="3">
         <v>917100</v>
       </c>
-      <c r="G59" s="3">
+      <c r="H59" s="3">
         <v>585700</v>
       </c>
-      <c r="H59" s="3">
+      <c r="I59" s="3">
         <v>748600</v>
       </c>
-      <c r="I59" s="3">
+      <c r="J59" s="3">
         <v>795100</v>
       </c>
-      <c r="J59" s="3">
+      <c r="K59" s="3">
         <v>581800</v>
       </c>
-      <c r="K59" s="3">
+      <c r="L59" s="3">
         <v>593500</v>
       </c>
-      <c r="L59" s="3">
+      <c r="M59" s="3">
         <v>1203800</v>
       </c>
-      <c r="M59" s="3">
+      <c r="N59" s="3">
         <v>3047200</v>
       </c>
-      <c r="N59" s="3">
+      <c r="O59" s="3">
         <v>2229700</v>
       </c>
-      <c r="O59" s="3">
+      <c r="P59" s="3">
         <v>1968300</v>
       </c>
-      <c r="P59" s="3">
+      <c r="Q59" s="3">
         <v>2093100</v>
       </c>
-      <c r="Q59" s="3">
+      <c r="R59" s="3">
         <v>1991300</v>
       </c>
-      <c r="R59" s="3">
+      <c r="S59" s="3">
         <v>1538600</v>
       </c>
-      <c r="S59" s="3">
+      <c r="T59" s="3">
         <v>1446500</v>
       </c>
-      <c r="T59" s="3">
+      <c r="U59" s="3">
         <v>1600800</v>
       </c>
-      <c r="U59" s="3">
+      <c r="V59" s="3">
         <v>1790900</v>
       </c>
-      <c r="V59" s="3">
+      <c r="W59" s="3">
         <v>1521700</v>
       </c>
-      <c r="W59" s="3">
+      <c r="X59" s="3">
         <v>1545300</v>
       </c>
-      <c r="X59" s="3">
+      <c r="Y59" s="3">
         <v>1892000</v>
       </c>
-      <c r="Y59" s="3">
+      <c r="Z59" s="3">
         <v>2294100</v>
       </c>
-      <c r="Z59" s="3">
+      <c r="AA59" s="3">
         <v>2199800</v>
       </c>
-      <c r="AA59" s="3">
+      <c r="AB59" s="3">
         <v>2064700</v>
       </c>
-      <c r="AB59" s="3">
+      <c r="AC59" s="3">
         <v>2149400</v>
       </c>
-      <c r="AC59" s="3">
+      <c r="AD59" s="3">
         <v>1989900</v>
       </c>
-      <c r="AD59" s="3">
+      <c r="AE59" s="3">
         <v>1798500</v>
       </c>
-      <c r="AE59" s="3">
+      <c r="AF59" s="3">
         <v>1649500</v>
       </c>
-      <c r="AF59" s="3">
+      <c r="AG59" s="3">
         <v>1642100</v>
       </c>
-      <c r="AG59" s="3">
+      <c r="AH59" s="3">
         <v>2008600</v>
       </c>
-      <c r="AH59" s="3">
+      <c r="AI59" s="3">
         <v>2057400</v>
       </c>
-      <c r="AI59" s="3">
+      <c r="AJ59" s="3">
         <v>1681400</v>
       </c>
-      <c r="AJ59" s="3">
+      <c r="AK59" s="3">
         <v>1880000</v>
       </c>
-      <c r="AK59" s="3">
+      <c r="AL59" s="3">
         <v>2004400</v>
       </c>
-      <c r="AL59" s="3">
+      <c r="AM59" s="3">
         <v>1813400</v>
       </c>
     </row>
-    <row r="60" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="60" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C60" s="1" t="s">
         <v>53</v>
       </c>
       <c r="D60" s="3">
+        <v>301362800</v>
+      </c>
+      <c r="E60" s="3">
         <v>276760100</v>
       </c>
-      <c r="E60" s="3">
+      <c r="F60" s="3">
         <v>269522700</v>
       </c>
-      <c r="F60" s="3">
+      <c r="G60" s="3">
         <v>318811800</v>
       </c>
-      <c r="G60" s="3">
+      <c r="H60" s="3">
         <v>283969800</v>
       </c>
-      <c r="H60" s="3">
+      <c r="I60" s="3">
         <v>288965400</v>
       </c>
-      <c r="I60" s="3">
+      <c r="J60" s="3">
         <v>297751000</v>
       </c>
-      <c r="J60" s="3">
+      <c r="K60" s="3">
         <v>272946300</v>
       </c>
-      <c r="K60" s="3">
+      <c r="L60" s="3">
         <v>277365200</v>
       </c>
-      <c r="L60" s="3">
+      <c r="M60" s="3">
         <v>273486900</v>
       </c>
-      <c r="M60" s="3">
-        <v>0</v>
-      </c>
       <c r="N60" s="3">
         <v>0</v>
       </c>
@@ -5911,228 +6050,237 @@
       <c r="AL60" s="3">
         <v>0</v>
       </c>
+      <c r="AM60" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="61" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="61" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C61" s="1" t="s">
         <v>54</v>
       </c>
       <c r="D61" s="3">
+        <v>58864300</v>
+      </c>
+      <c r="E61" s="3">
         <v>51786600</v>
       </c>
-      <c r="E61" s="3">
+      <c r="F61" s="3">
         <v>52292900</v>
       </c>
-      <c r="F61" s="3">
+      <c r="G61" s="3">
         <v>57884900</v>
       </c>
-      <c r="G61" s="3">
+      <c r="H61" s="3">
         <v>51737100</v>
       </c>
-      <c r="H61" s="3">
+      <c r="I61" s="3">
         <v>52671400</v>
       </c>
-      <c r="I61" s="3">
+      <c r="J61" s="3">
         <v>54929200</v>
       </c>
-      <c r="J61" s="3">
+      <c r="K61" s="3">
         <v>53360000</v>
       </c>
-      <c r="K61" s="3">
+      <c r="L61" s="3">
         <v>54858600</v>
       </c>
-      <c r="L61" s="3">
+      <c r="M61" s="3">
         <v>55629400</v>
       </c>
-      <c r="M61" s="3">
+      <c r="N61" s="3">
         <v>52670100</v>
       </c>
-      <c r="N61" s="3">
+      <c r="O61" s="3">
         <v>58817800</v>
       </c>
-      <c r="O61" s="3">
+      <c r="P61" s="3">
         <v>58413400</v>
       </c>
-      <c r="P61" s="3">
+      <c r="Q61" s="3">
         <v>54512100</v>
       </c>
-      <c r="Q61" s="3">
+      <c r="R61" s="3">
         <v>51506600</v>
       </c>
-      <c r="R61" s="3">
+      <c r="S61" s="3">
         <v>49335300</v>
       </c>
-      <c r="S61" s="3">
+      <c r="T61" s="3">
         <v>46999300</v>
       </c>
-      <c r="T61" s="3">
+      <c r="U61" s="3">
         <v>43329900</v>
       </c>
-      <c r="U61" s="3">
+      <c r="V61" s="3">
         <v>42586400</v>
       </c>
-      <c r="V61" s="3">
+      <c r="W61" s="3">
         <v>38230600</v>
       </c>
-      <c r="W61" s="3">
+      <c r="X61" s="3">
         <v>39214800</v>
       </c>
-      <c r="X61" s="3">
+      <c r="Y61" s="3">
         <v>43080800</v>
       </c>
-      <c r="Y61" s="3">
+      <c r="Z61" s="3">
         <v>42129500</v>
       </c>
-      <c r="Z61" s="3">
+      <c r="AA61" s="3">
         <v>44185000</v>
       </c>
-      <c r="AA61" s="3">
+      <c r="AB61" s="3">
         <v>43142100</v>
       </c>
-      <c r="AB61" s="3">
+      <c r="AC61" s="3">
         <v>40307800</v>
       </c>
-      <c r="AC61" s="3">
+      <c r="AD61" s="3">
         <v>36868700</v>
       </c>
-      <c r="AD61" s="3">
+      <c r="AE61" s="3">
         <v>34955700</v>
       </c>
-      <c r="AE61" s="3">
+      <c r="AF61" s="3">
         <v>35115500</v>
       </c>
-      <c r="AF61" s="3">
+      <c r="AG61" s="3">
         <v>34009900</v>
       </c>
-      <c r="AG61" s="3">
+      <c r="AH61" s="3">
         <v>36941800</v>
       </c>
-      <c r="AH61" s="3">
+      <c r="AI61" s="3">
         <v>37408900</v>
       </c>
-      <c r="AI61" s="3">
+      <c r="AJ61" s="3">
         <v>35000000</v>
       </c>
-      <c r="AJ61" s="3">
+      <c r="AK61" s="3">
         <v>33280700</v>
       </c>
-      <c r="AK61" s="3">
+      <c r="AL61" s="3">
         <v>34538700</v>
       </c>
-      <c r="AL61" s="3">
+      <c r="AM61" s="3">
         <v>33926000</v>
       </c>
     </row>
-    <row r="62" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="62" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C62" s="1" t="s">
         <v>55</v>
       </c>
       <c r="D62" s="3">
+        <v>6912600</v>
+      </c>
+      <c r="E62" s="3">
         <v>7918500</v>
       </c>
-      <c r="E62" s="3">
+      <c r="F62" s="3">
         <v>8428000</v>
       </c>
-      <c r="F62" s="3">
+      <c r="G62" s="3">
         <v>8065900</v>
       </c>
-      <c r="G62" s="3">
+      <c r="H62" s="3">
         <v>6973100</v>
       </c>
-      <c r="H62" s="3">
+      <c r="I62" s="3">
         <v>7766400</v>
       </c>
-      <c r="I62" s="3">
+      <c r="J62" s="3">
         <v>4724200</v>
       </c>
-      <c r="J62" s="3">
+      <c r="K62" s="3">
         <v>8885900</v>
       </c>
-      <c r="K62" s="3">
+      <c r="L62" s="3">
         <v>8657200</v>
       </c>
-      <c r="L62" s="3">
+      <c r="M62" s="3">
         <v>11788800</v>
       </c>
-      <c r="M62" s="3">
+      <c r="N62" s="3">
         <v>459600</v>
       </c>
-      <c r="N62" s="3">
+      <c r="O62" s="3">
         <v>438000</v>
       </c>
-      <c r="O62" s="3">
+      <c r="P62" s="3">
         <v>469900</v>
       </c>
-      <c r="P62" s="3">
+      <c r="Q62" s="3">
         <v>523500</v>
       </c>
-      <c r="Q62" s="3">
+      <c r="R62" s="3">
         <v>608300</v>
       </c>
-      <c r="R62" s="3">
+      <c r="S62" s="3">
         <v>663300</v>
       </c>
-      <c r="S62" s="3">
+      <c r="T62" s="3">
         <v>620300</v>
       </c>
-      <c r="T62" s="3">
+      <c r="U62" s="3">
         <v>542300</v>
       </c>
-      <c r="U62" s="3">
+      <c r="V62" s="3">
         <v>528500</v>
       </c>
-      <c r="V62" s="3">
+      <c r="W62" s="3">
         <v>720700</v>
       </c>
-      <c r="W62" s="3">
+      <c r="X62" s="3">
         <v>691400</v>
       </c>
-      <c r="X62" s="3">
+      <c r="Y62" s="3">
         <v>680000</v>
       </c>
-      <c r="Y62" s="3">
+      <c r="Z62" s="3">
         <v>570200</v>
       </c>
-      <c r="Z62" s="3">
+      <c r="AA62" s="3">
         <v>714600</v>
       </c>
-      <c r="AA62" s="3">
+      <c r="AB62" s="3">
         <v>648100</v>
       </c>
-      <c r="AB62" s="3">
+      <c r="AC62" s="3">
         <v>618700</v>
       </c>
-      <c r="AC62" s="3">
+      <c r="AD62" s="3">
         <v>520300</v>
       </c>
-      <c r="AD62" s="3">
+      <c r="AE62" s="3">
         <v>418500</v>
       </c>
-      <c r="AE62" s="3">
+      <c r="AF62" s="3">
         <v>420800</v>
       </c>
-      <c r="AF62" s="3">
+      <c r="AG62" s="3">
         <v>527700</v>
       </c>
-      <c r="AG62" s="3">
+      <c r="AH62" s="3">
         <v>419200</v>
       </c>
-      <c r="AH62" s="3">
+      <c r="AI62" s="3">
         <v>395900</v>
       </c>
-      <c r="AI62" s="3">
+      <c r="AJ62" s="3">
         <v>382900</v>
       </c>
-      <c r="AJ62" s="3">
+      <c r="AK62" s="3">
         <v>400700</v>
       </c>
-      <c r="AK62" s="3">
+      <c r="AL62" s="3">
         <v>463600</v>
       </c>
-      <c r="AL62" s="3">
+      <c r="AM62" s="3">
         <v>459900</v>
       </c>
     </row>
-    <row r="63" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="63" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C63" s="1" t="s">
         <v>56</v>
       </c>
@@ -6241,8 +6389,11 @@
       <c r="AL63" s="3">
         <v>0</v>
       </c>
+      <c r="AM63" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="64" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="64" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C64" s="1" t="s">
         <v>20</v>
       </c>
@@ -6351,8 +6502,11 @@
       <c r="AL64" s="3">
         <v>0</v>
       </c>
+      <c r="AM64" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="65" spans="2:38" x14ac:dyDescent="0.2">
+    <row r="65" spans="2:39" x14ac:dyDescent="0.2">
       <c r="C65" s="1" t="s">
         <v>57</v>
       </c>
@@ -6461,118 +6615,124 @@
       <c r="AL65" s="3">
         <v>0</v>
       </c>
+      <c r="AM65" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="66" spans="2:38" x14ac:dyDescent="0.2">
+    <row r="66" spans="2:39" x14ac:dyDescent="0.2">
       <c r="C66" s="1" t="s">
         <v>58</v>
       </c>
       <c r="D66" s="3">
+        <v>368261100</v>
+      </c>
+      <c r="E66" s="3">
         <v>337599900</v>
       </c>
-      <c r="E66" s="3">
+      <c r="F66" s="3">
         <v>331601300</v>
       </c>
-      <c r="F66" s="3">
+      <c r="G66" s="3">
         <v>386400900</v>
       </c>
-      <c r="G66" s="3">
+      <c r="H66" s="3">
         <v>343710800</v>
       </c>
-      <c r="H66" s="3">
+      <c r="I66" s="3">
         <v>350345300</v>
       </c>
-      <c r="I66" s="3">
+      <c r="J66" s="3">
         <v>358283300</v>
       </c>
-      <c r="J66" s="3">
+      <c r="K66" s="3">
         <v>336284100</v>
       </c>
-      <c r="K66" s="3">
+      <c r="L66" s="3">
         <v>341832200</v>
       </c>
-      <c r="L66" s="3">
+      <c r="M66" s="3">
         <v>341656500</v>
       </c>
-      <c r="M66" s="3">
+      <c r="N66" s="3">
         <v>338784400</v>
       </c>
-      <c r="N66" s="3">
+      <c r="O66" s="3">
         <v>345885900</v>
       </c>
-      <c r="O66" s="3">
+      <c r="P66" s="3">
         <v>348018900</v>
       </c>
-      <c r="P66" s="3">
+      <c r="Q66" s="3">
         <v>338354200</v>
       </c>
-      <c r="Q66" s="3">
+      <c r="R66" s="3">
         <v>316006400</v>
       </c>
-      <c r="R66" s="3">
+      <c r="S66" s="3">
         <v>309651700</v>
       </c>
-      <c r="S66" s="3">
+      <c r="T66" s="3">
         <v>297533600</v>
       </c>
-      <c r="T66" s="3">
+      <c r="U66" s="3">
         <v>290517700</v>
       </c>
-      <c r="U66" s="3">
+      <c r="V66" s="3">
         <v>278260300</v>
       </c>
-      <c r="V66" s="3">
+      <c r="W66" s="3">
         <v>275726000</v>
       </c>
-      <c r="W66" s="3">
+      <c r="X66" s="3">
         <v>275487700</v>
       </c>
-      <c r="X66" s="3">
+      <c r="Y66" s="3">
         <v>288675900</v>
       </c>
-      <c r="Y66" s="3">
+      <c r="Z66" s="3">
         <v>289399800</v>
       </c>
-      <c r="Z66" s="3">
+      <c r="AA66" s="3">
         <v>297278600</v>
       </c>
-      <c r="AA66" s="3">
+      <c r="AB66" s="3">
         <v>299163500</v>
       </c>
-      <c r="AB66" s="3">
+      <c r="AC66" s="3">
         <v>296968200</v>
       </c>
-      <c r="AC66" s="3">
+      <c r="AD66" s="3">
         <v>267714100</v>
       </c>
-      <c r="AD66" s="3">
+      <c r="AE66" s="3">
         <v>249559900</v>
       </c>
-      <c r="AE66" s="3">
+      <c r="AF66" s="3">
         <v>256847800</v>
       </c>
-      <c r="AF66" s="3">
+      <c r="AG66" s="3">
         <v>256582900</v>
       </c>
-      <c r="AG66" s="3">
+      <c r="AH66" s="3">
         <v>260418000</v>
       </c>
-      <c r="AH66" s="3">
+      <c r="AI66" s="3">
         <v>261733600</v>
       </c>
-      <c r="AI66" s="3">
+      <c r="AJ66" s="3">
         <v>260311800</v>
       </c>
-      <c r="AJ66" s="3">
+      <c r="AK66" s="3">
         <v>255640700</v>
       </c>
-      <c r="AK66" s="3">
+      <c r="AL66" s="3">
         <v>261266900</v>
       </c>
-      <c r="AL66" s="3">
+      <c r="AM66" s="3">
         <v>263136400</v>
       </c>
     </row>
-    <row r="67" spans="2:38" x14ac:dyDescent="0.2">
+    <row r="67" spans="2:39" x14ac:dyDescent="0.2">
       <c r="C67" s="1" t="s">
         <v>59</v>
       </c>
@@ -6611,8 +6771,9 @@
       <c r="AJ67" s="3"/>
       <c r="AK67" s="3"/>
       <c r="AL67" s="3"/>
+      <c r="AM67" s="3"/>
     </row>
-    <row r="68" spans="2:38" x14ac:dyDescent="0.2">
+    <row r="68" spans="2:39" x14ac:dyDescent="0.2">
       <c r="C68" s="1" t="s">
         <v>60</v>
       </c>
@@ -6721,8 +6882,11 @@
       <c r="AL68" s="3">
         <v>0</v>
       </c>
+      <c r="AM68" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="69" spans="2:38" x14ac:dyDescent="0.2">
+    <row r="69" spans="2:39" x14ac:dyDescent="0.2">
       <c r="C69" s="1" t="s">
         <v>61</v>
       </c>
@@ -6831,8 +6995,11 @@
       <c r="AL69" s="3">
         <v>0</v>
       </c>
+      <c r="AM69" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="70" spans="2:38" x14ac:dyDescent="0.2">
+    <row r="70" spans="2:39" x14ac:dyDescent="0.2">
       <c r="C70" s="1" t="s">
         <v>62</v>
       </c>
@@ -6941,8 +7108,11 @@
       <c r="AL70" s="3">
         <v>0</v>
       </c>
+      <c r="AM70" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="71" spans="2:38" x14ac:dyDescent="0.2">
+    <row r="71" spans="2:39" x14ac:dyDescent="0.2">
       <c r="C71" s="1" t="s">
         <v>63</v>
       </c>
@@ -7051,118 +7221,124 @@
       <c r="AL71" s="3">
         <v>0</v>
       </c>
+      <c r="AM71" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="72" spans="2:38" x14ac:dyDescent="0.2">
+    <row r="72" spans="2:39" x14ac:dyDescent="0.2">
       <c r="C72" s="1" t="s">
         <v>64</v>
       </c>
       <c r="D72" s="3">
+        <v>20492400</v>
+      </c>
+      <c r="E72" s="3">
         <v>18322200</v>
       </c>
-      <c r="E72" s="3">
+      <c r="F72" s="3">
         <v>18243700</v>
       </c>
-      <c r="F72" s="3">
+      <c r="G72" s="3">
         <v>20282200</v>
       </c>
-      <c r="G72" s="3">
+      <c r="H72" s="3">
         <v>18807000</v>
       </c>
-      <c r="H72" s="3">
+      <c r="I72" s="3">
         <v>18719000</v>
       </c>
-      <c r="I72" s="3">
+      <c r="J72" s="3">
         <v>19268400</v>
       </c>
-      <c r="J72" s="3">
+      <c r="K72" s="3">
         <v>18710700</v>
       </c>
-      <c r="K72" s="3">
+      <c r="L72" s="3">
         <v>18565400</v>
       </c>
-      <c r="L72" s="3">
+      <c r="M72" s="3">
         <v>18299100</v>
       </c>
-      <c r="M72" s="3">
+      <c r="N72" s="3">
         <v>17812600</v>
       </c>
-      <c r="N72" s="3">
+      <c r="O72" s="3">
         <v>17007700</v>
       </c>
-      <c r="O72" s="3">
+      <c r="P72" s="3">
         <v>17130600</v>
       </c>
-      <c r="P72" s="3">
+      <c r="Q72" s="3">
         <v>16662400</v>
       </c>
-      <c r="Q72" s="3">
+      <c r="R72" s="3">
         <v>16044400</v>
       </c>
-      <c r="R72" s="3">
+      <c r="S72" s="3">
         <v>15764300</v>
       </c>
-      <c r="S72" s="3">
+      <c r="T72" s="3">
         <v>15298800</v>
       </c>
-      <c r="T72" s="3">
+      <c r="U72" s="3">
         <v>14524300</v>
       </c>
-      <c r="U72" s="3">
+      <c r="V72" s="3">
         <v>14258500</v>
       </c>
-      <c r="V72" s="3">
+      <c r="W72" s="3">
         <v>14719300</v>
       </c>
-      <c r="W72" s="3">
+      <c r="X72" s="3">
         <v>14362200</v>
       </c>
-      <c r="X72" s="3">
+      <c r="Y72" s="3">
         <v>15002800</v>
       </c>
-      <c r="Y72" s="3">
+      <c r="Z72" s="3">
         <v>15745800</v>
       </c>
-      <c r="Z72" s="3">
+      <c r="AA72" s="3">
         <v>15573800</v>
       </c>
-      <c r="AA72" s="3">
+      <c r="AB72" s="3">
         <v>15698600</v>
       </c>
-      <c r="AB72" s="3">
+      <c r="AC72" s="3">
         <v>15678000</v>
       </c>
-      <c r="AC72" s="3">
+      <c r="AD72" s="3">
         <v>14384700</v>
       </c>
-      <c r="AD72" s="3">
+      <c r="AE72" s="3">
         <v>13795900</v>
       </c>
-      <c r="AE72" s="3">
+      <c r="AF72" s="3">
         <v>13837700</v>
       </c>
-      <c r="AF72" s="3">
+      <c r="AG72" s="3">
         <v>13273900</v>
       </c>
-      <c r="AG72" s="3">
+      <c r="AH72" s="3">
         <v>13745600</v>
       </c>
-      <c r="AH72" s="3">
+      <c r="AI72" s="3">
         <v>13660700</v>
       </c>
-      <c r="AI72" s="3">
+      <c r="AJ72" s="3">
         <v>13507800</v>
       </c>
-      <c r="AJ72" s="3">
+      <c r="AK72" s="3">
         <v>13138800</v>
       </c>
-      <c r="AK72" s="3">
+      <c r="AL72" s="3">
         <v>13150400</v>
       </c>
-      <c r="AL72" s="3">
+      <c r="AM72" s="3">
         <v>13062800</v>
       </c>
     </row>
-    <row r="73" spans="2:38" x14ac:dyDescent="0.2">
+    <row r="73" spans="2:39" x14ac:dyDescent="0.2">
       <c r="C73" s="1" t="s">
         <v>65</v>
       </c>
@@ -7271,8 +7447,11 @@
       <c r="AL73" s="3">
         <v>0</v>
       </c>
+      <c r="AM73" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="74" spans="2:38" x14ac:dyDescent="0.2">
+    <row r="74" spans="2:39" x14ac:dyDescent="0.2">
       <c r="C74" s="1" t="s">
         <v>66</v>
       </c>
@@ -7381,8 +7560,11 @@
       <c r="AL74" s="3">
         <v>0</v>
       </c>
+      <c r="AM74" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="75" spans="2:38" x14ac:dyDescent="0.2">
+    <row r="75" spans="2:39" x14ac:dyDescent="0.2">
       <c r="C75" s="1" t="s">
         <v>67</v>
       </c>
@@ -7491,118 +7673,124 @@
       <c r="AL75" s="3">
         <v>0</v>
       </c>
+      <c r="AM75" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="76" spans="2:38" x14ac:dyDescent="0.2">
+    <row r="76" spans="2:39" x14ac:dyDescent="0.2">
       <c r="C76" s="1" t="s">
         <v>68</v>
       </c>
       <c r="D76" s="3">
+        <v>25252000</v>
+      </c>
+      <c r="E76" s="3">
         <v>22902500</v>
       </c>
-      <c r="E76" s="3">
+      <c r="F76" s="3">
         <v>23081300</v>
       </c>
-      <c r="F76" s="3">
+      <c r="G76" s="3">
         <v>25698700</v>
       </c>
-      <c r="G76" s="3">
+      <c r="H76" s="3">
         <v>24286300</v>
       </c>
-      <c r="H76" s="3">
+      <c r="I76" s="3">
         <v>23977100</v>
       </c>
-      <c r="I76" s="3">
+      <c r="J76" s="3">
         <v>24420000</v>
       </c>
-      <c r="J76" s="3">
+      <c r="K76" s="3">
         <v>23463000</v>
       </c>
-      <c r="K76" s="3">
+      <c r="L76" s="3">
         <v>22963400</v>
       </c>
-      <c r="L76" s="3">
+      <c r="M76" s="3">
         <v>22747400</v>
       </c>
-      <c r="M76" s="3">
+      <c r="N76" s="3">
         <v>21571400</v>
       </c>
-      <c r="N76" s="3">
+      <c r="O76" s="3">
         <v>20624400</v>
       </c>
-      <c r="O76" s="3">
+      <c r="P76" s="3">
         <v>20539800</v>
       </c>
-      <c r="P76" s="3">
+      <c r="Q76" s="3">
         <v>20238100</v>
       </c>
-      <c r="Q76" s="3">
+      <c r="R76" s="3">
         <v>19381500</v>
       </c>
-      <c r="R76" s="3">
+      <c r="S76" s="3">
         <v>18987000</v>
       </c>
-      <c r="S76" s="3">
+      <c r="T76" s="3">
         <v>18419400</v>
       </c>
-      <c r="T76" s="3">
+      <c r="U76" s="3">
         <v>17399500</v>
       </c>
-      <c r="U76" s="3">
+      <c r="V76" s="3">
         <v>17059700</v>
       </c>
-      <c r="V76" s="3">
+      <c r="W76" s="3">
         <v>17519900</v>
       </c>
-      <c r="W76" s="3">
+      <c r="X76" s="3">
         <v>17171900</v>
       </c>
-      <c r="X76" s="3">
+      <c r="Y76" s="3">
         <v>17677500</v>
       </c>
-      <c r="Y76" s="3">
+      <c r="Z76" s="3">
         <v>18283800</v>
       </c>
-      <c r="Z76" s="3">
+      <c r="AA76" s="3">
         <v>17718000</v>
       </c>
-      <c r="AA76" s="3">
+      <c r="AB76" s="3">
         <v>17110000</v>
       </c>
-      <c r="AB76" s="3">
+      <c r="AC76" s="3">
         <v>17117400</v>
       </c>
-      <c r="AC76" s="3">
+      <c r="AD76" s="3">
         <v>18261500</v>
       </c>
-      <c r="AD76" s="3">
+      <c r="AE76" s="3">
         <v>17579400</v>
       </c>
-      <c r="AE76" s="3">
+      <c r="AF76" s="3">
         <v>17463800</v>
       </c>
-      <c r="AF76" s="3">
+      <c r="AG76" s="3">
         <v>17085700</v>
       </c>
-      <c r="AG76" s="3">
+      <c r="AH76" s="3">
         <v>17922000</v>
       </c>
-      <c r="AH76" s="3">
+      <c r="AI76" s="3">
         <v>17996500</v>
       </c>
-      <c r="AI76" s="3">
+      <c r="AJ76" s="3">
         <v>17825600</v>
       </c>
-      <c r="AJ76" s="3">
+      <c r="AK76" s="3">
         <v>17960100</v>
       </c>
-      <c r="AK76" s="3">
+      <c r="AL76" s="3">
         <v>18347500</v>
       </c>
-      <c r="AL76" s="3">
+      <c r="AM76" s="3">
         <v>18412300</v>
       </c>
     </row>
-    <row r="77" spans="2:38" x14ac:dyDescent="0.2">
+    <row r="77" spans="2:39" x14ac:dyDescent="0.2">
       <c r="C77" s="1" t="s">
         <v>69</v>
       </c>
@@ -7711,233 +7899,242 @@
       <c r="AL77" s="3">
         <v>0</v>
       </c>
+      <c r="AM77" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="79" spans="2:38" x14ac:dyDescent="0.2">
+    <row r="79" spans="2:39" x14ac:dyDescent="0.2">
       <c r="B79" s="1" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="80" spans="2:38" x14ac:dyDescent="0.2">
+    <row r="80" spans="2:39" x14ac:dyDescent="0.2">
       <c r="C80" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D80" s="2">
+        <v>45838</v>
+      </c>
+      <c r="E80" s="2">
         <v>45747</v>
       </c>
-      <c r="E80" s="2">
+      <c r="F80" s="2">
         <v>45657</v>
       </c>
-      <c r="F80" s="2">
+      <c r="G80" s="2">
         <v>45565</v>
       </c>
-      <c r="G80" s="2">
+      <c r="H80" s="2">
         <v>45473</v>
       </c>
-      <c r="H80" s="2">
+      <c r="I80" s="2">
         <v>45382</v>
       </c>
-      <c r="I80" s="2">
+      <c r="J80" s="2">
         <v>45291</v>
       </c>
-      <c r="J80" s="2">
+      <c r="K80" s="2">
         <v>45199</v>
       </c>
-      <c r="K80" s="2">
+      <c r="L80" s="2">
         <v>45107</v>
       </c>
-      <c r="L80" s="2">
+      <c r="M80" s="2">
         <v>45016</v>
       </c>
-      <c r="M80" s="2">
+      <c r="N80" s="2">
         <v>44926</v>
       </c>
-      <c r="N80" s="2">
+      <c r="O80" s="2">
         <v>44834</v>
       </c>
-      <c r="O80" s="2">
+      <c r="P80" s="2">
         <v>44742</v>
       </c>
-      <c r="P80" s="2">
+      <c r="Q80" s="2">
         <v>44651</v>
       </c>
-      <c r="Q80" s="2">
+      <c r="R80" s="2">
         <v>44561</v>
       </c>
-      <c r="R80" s="2">
+      <c r="S80" s="2">
         <v>44469</v>
       </c>
-      <c r="S80" s="2">
+      <c r="T80" s="2">
         <v>44377</v>
       </c>
-      <c r="T80" s="2">
+      <c r="U80" s="2">
         <v>44286</v>
       </c>
-      <c r="U80" s="2">
+      <c r="V80" s="2">
         <v>44196</v>
       </c>
-      <c r="V80" s="2">
+      <c r="W80" s="2">
         <v>44104</v>
       </c>
-      <c r="W80" s="2">
+      <c r="X80" s="2">
         <v>44012</v>
       </c>
-      <c r="X80" s="2">
+      <c r="Y80" s="2">
         <v>43921</v>
       </c>
-      <c r="Y80" s="2">
+      <c r="Z80" s="2">
         <v>43830</v>
       </c>
-      <c r="Z80" s="2">
+      <c r="AA80" s="2">
         <v>43738</v>
       </c>
-      <c r="AA80" s="2">
+      <c r="AB80" s="2">
         <v>43646</v>
       </c>
-      <c r="AB80" s="2">
+      <c r="AC80" s="2">
         <v>43555</v>
       </c>
-      <c r="AC80" s="2">
+      <c r="AD80" s="2">
         <v>43465</v>
       </c>
-      <c r="AD80" s="2">
+      <c r="AE80" s="2">
         <v>43373</v>
       </c>
-      <c r="AE80" s="2">
+      <c r="AF80" s="2">
         <v>43281</v>
       </c>
-      <c r="AF80" s="2">
+      <c r="AG80" s="2">
         <v>43190</v>
       </c>
-      <c r="AG80" s="2">
+      <c r="AH80" s="2">
         <v>43100</v>
       </c>
-      <c r="AH80" s="2">
+      <c r="AI80" s="2">
         <v>43008</v>
       </c>
-      <c r="AI80" s="2">
+      <c r="AJ80" s="2">
         <v>42916</v>
       </c>
-      <c r="AJ80" s="2">
+      <c r="AK80" s="2">
         <v>42825</v>
       </c>
-      <c r="AK80" s="2">
+      <c r="AL80" s="2">
         <v>42735</v>
       </c>
-      <c r="AL80" s="2">
+      <c r="AM80" s="2">
         <v>42643</v>
       </c>
     </row>
-    <row r="81" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="81" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C81" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D81" s="3">
+        <v>691100</v>
+      </c>
+      <c r="E81" s="3">
         <v>418800</v>
       </c>
-      <c r="E81" s="3">
+      <c r="F81" s="3">
         <v>288500</v>
       </c>
-      <c r="F81" s="3">
+      <c r="G81" s="3">
         <v>688600</v>
       </c>
-      <c r="G81" s="3">
+      <c r="H81" s="3">
         <v>676000</v>
       </c>
-      <c r="H81" s="3">
+      <c r="I81" s="3">
         <v>613100</v>
       </c>
-      <c r="I81" s="3">
+      <c r="J81" s="3">
         <v>52500</v>
       </c>
-      <c r="J81" s="3">
+      <c r="K81" s="3">
         <v>668000</v>
       </c>
-      <c r="K81" s="3">
+      <c r="L81" s="3">
         <v>474700</v>
       </c>
-      <c r="L81" s="3">
+      <c r="M81" s="3">
         <v>700700</v>
       </c>
-      <c r="M81" s="3">
+      <c r="N81" s="3">
         <v>338800</v>
       </c>
-      <c r="N81" s="3">
+      <c r="O81" s="3">
         <v>640600</v>
       </c>
-      <c r="O81" s="3">
+      <c r="P81" s="3">
         <v>684400</v>
       </c>
-      <c r="P81" s="3">
+      <c r="Q81" s="3">
         <v>631400</v>
       </c>
-      <c r="Q81" s="3">
+      <c r="R81" s="3">
         <v>279500</v>
       </c>
-      <c r="R81" s="3">
+      <c r="S81" s="3">
         <v>570700</v>
       </c>
-      <c r="S81" s="3">
+      <c r="T81" s="3">
         <v>552600</v>
       </c>
-      <c r="T81" s="3">
+      <c r="U81" s="3">
         <v>482000</v>
       </c>
-      <c r="U81" s="3">
+      <c r="V81" s="3">
         <v>112600</v>
       </c>
-      <c r="V81" s="3">
+      <c r="W81" s="3">
         <v>358800</v>
       </c>
-      <c r="W81" s="3">
+      <c r="X81" s="3">
         <v>100500</v>
       </c>
-      <c r="X81" s="3">
+      <c r="Y81" s="3">
         <v>412900</v>
       </c>
-      <c r="Y81" s="3">
+      <c r="Z81" s="3">
         <v>174900</v>
       </c>
-      <c r="Z81" s="3">
+      <c r="AA81" s="3">
         <v>410100</v>
       </c>
-      <c r="AA81" s="3">
+      <c r="AB81" s="3">
         <v>537700</v>
       </c>
-      <c r="AB81" s="3">
+      <c r="AC81" s="3">
         <v>517500</v>
       </c>
-      <c r="AC81" s="3">
+      <c r="AD81" s="3">
         <v>76800</v>
       </c>
-      <c r="AD81" s="3">
+      <c r="AE81" s="3">
         <v>453900</v>
       </c>
-      <c r="AE81" s="3">
+      <c r="AF81" s="3">
         <v>569900</v>
       </c>
-      <c r="AF81" s="3">
+      <c r="AG81" s="3">
         <v>463600</v>
       </c>
-      <c r="AG81" s="3">
+      <c r="AH81" s="3">
         <v>84900</v>
       </c>
-      <c r="AH81" s="3">
+      <c r="AI81" s="3">
         <v>212100</v>
       </c>
-      <c r="AI81" s="3">
+      <c r="AJ81" s="3">
         <v>369000</v>
       </c>
-      <c r="AJ81" s="3">
+      <c r="AK81" s="3">
         <v>517600</v>
       </c>
-      <c r="AK81" s="3">
+      <c r="AL81" s="3">
         <v>88500</v>
       </c>
-      <c r="AL81" s="3">
+      <c r="AM81" s="3">
         <v>275700</v>
       </c>
     </row>
-    <row r="82" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="82" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C82" s="1" t="s">
         <v>71</v>
       </c>
@@ -7976,118 +8173,122 @@
       <c r="AJ82" s="3"/>
       <c r="AK82" s="3"/>
       <c r="AL82" s="3"/>
+      <c r="AM82" s="3"/>
     </row>
-    <row r="83" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="83" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C83" s="1" t="s">
         <v>72</v>
       </c>
       <c r="D83" s="3">
+        <v>204400</v>
+      </c>
+      <c r="E83" s="3">
         <v>200500</v>
       </c>
-      <c r="E83" s="3">
+      <c r="F83" s="3">
         <v>173700</v>
       </c>
-      <c r="F83" s="3">
+      <c r="G83" s="3">
         <v>150800</v>
       </c>
-      <c r="G83" s="3">
+      <c r="H83" s="3">
         <v>153800</v>
       </c>
-      <c r="H83" s="3">
+      <c r="I83" s="3">
         <v>154400</v>
       </c>
-      <c r="I83" s="3">
+      <c r="J83" s="3">
         <v>162700</v>
       </c>
-      <c r="J83" s="3">
+      <c r="K83" s="3">
         <v>133200</v>
       </c>
-      <c r="K83" s="3">
+      <c r="L83" s="3">
         <v>147300</v>
       </c>
-      <c r="L83" s="3">
+      <c r="M83" s="3">
         <v>148000</v>
       </c>
-      <c r="M83" s="3">
+      <c r="N83" s="3">
         <v>185200</v>
       </c>
-      <c r="N83" s="3">
+      <c r="O83" s="3">
         <v>169700</v>
       </c>
-      <c r="O83" s="3">
+      <c r="P83" s="3">
         <v>175600</v>
       </c>
-      <c r="P83" s="3">
+      <c r="Q83" s="3">
         <v>168600</v>
       </c>
-      <c r="Q83" s="3">
+      <c r="R83" s="3">
         <v>155900</v>
       </c>
-      <c r="R83" s="3">
+      <c r="S83" s="3">
         <v>149200</v>
       </c>
-      <c r="S83" s="3">
+      <c r="T83" s="3">
         <v>184500</v>
       </c>
-      <c r="T83" s="3">
+      <c r="U83" s="3">
         <v>102900</v>
       </c>
-      <c r="U83" s="3">
+      <c r="V83" s="3">
         <v>101300</v>
       </c>
-      <c r="V83" s="3">
+      <c r="W83" s="3">
         <v>101500</v>
       </c>
-      <c r="W83" s="3">
+      <c r="X83" s="3">
         <v>98700</v>
       </c>
-      <c r="X83" s="3">
+      <c r="Y83" s="3">
         <v>112300</v>
       </c>
-      <c r="Y83" s="3">
+      <c r="Z83" s="3">
         <v>120400</v>
       </c>
-      <c r="Z83" s="3">
+      <c r="AA83" s="3">
         <v>116900</v>
       </c>
-      <c r="AA83" s="3">
+      <c r="AB83" s="3">
         <v>108900</v>
       </c>
-      <c r="AB83" s="3">
+      <c r="AC83" s="3">
         <v>93600</v>
       </c>
-      <c r="AC83" s="3">
+      <c r="AD83" s="3">
         <v>61600</v>
       </c>
-      <c r="AD83" s="3">
+      <c r="AE83" s="3">
         <v>58600</v>
       </c>
-      <c r="AE83" s="3">
+      <c r="AF83" s="3">
         <v>56000</v>
       </c>
-      <c r="AF83" s="3">
+      <c r="AG83" s="3">
         <v>50600</v>
       </c>
-      <c r="AG83" s="3">
+      <c r="AH83" s="3">
         <v>49900</v>
       </c>
-      <c r="AH83" s="3">
+      <c r="AI83" s="3">
         <v>50800</v>
       </c>
-      <c r="AI83" s="3">
+      <c r="AJ83" s="3">
         <v>51600</v>
       </c>
-      <c r="AJ83" s="3">
+      <c r="AK83" s="3">
         <v>55200</v>
       </c>
-      <c r="AK83" s="3">
+      <c r="AL83" s="3">
         <v>54800</v>
       </c>
-      <c r="AL83" s="3">
+      <c r="AM83" s="3">
         <v>53700</v>
       </c>
     </row>
-    <row r="84" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="84" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C84" s="1" t="s">
         <v>73</v>
       </c>
@@ -8196,8 +8397,11 @@
       <c r="AL84" s="3">
         <v>0</v>
       </c>
+      <c r="AM84" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="85" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="85" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C85" s="1" t="s">
         <v>74</v>
       </c>
@@ -8306,8 +8510,11 @@
       <c r="AL85" s="3">
         <v>0</v>
       </c>
+      <c r="AM85" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="86" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="86" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C86" s="1" t="s">
         <v>75</v>
       </c>
@@ -8416,8 +8623,11 @@
       <c r="AL86" s="3">
         <v>0</v>
       </c>
+      <c r="AM86" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="87" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="87" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C87" s="1" t="s">
         <v>76</v>
       </c>
@@ -8526,8 +8736,11 @@
       <c r="AL87" s="3">
         <v>0</v>
       </c>
+      <c r="AM87" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="88" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="88" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C88" s="1" t="s">
         <v>77</v>
       </c>
@@ -8636,118 +8849,124 @@
       <c r="AL88" s="3">
         <v>0</v>
       </c>
+      <c r="AM88" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="89" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="89" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C89" s="1" t="s">
         <v>78</v>
       </c>
       <c r="D89" s="3">
+        <v>-4742200</v>
+      </c>
+      <c r="E89" s="3">
         <v>-1359600</v>
       </c>
-      <c r="E89" s="3">
+      <c r="F89" s="3">
         <v>15238500</v>
       </c>
-      <c r="F89" s="3">
+      <c r="G89" s="3">
         <v>-21513100</v>
       </c>
-      <c r="G89" s="3">
+      <c r="H89" s="3">
         <v>-5708900</v>
       </c>
-      <c r="H89" s="3">
+      <c r="I89" s="3">
         <v>3028800</v>
       </c>
-      <c r="I89" s="3">
+      <c r="J89" s="3">
         <v>-13351300</v>
       </c>
-      <c r="J89" s="3">
+      <c r="K89" s="3">
         <v>3754000</v>
       </c>
-      <c r="K89" s="3">
+      <c r="L89" s="3">
         <v>-11714900</v>
       </c>
-      <c r="L89" s="3">
+      <c r="M89" s="3">
         <v>10840700</v>
       </c>
-      <c r="M89" s="3">
+      <c r="N89" s="3">
         <v>12011900</v>
       </c>
-      <c r="N89" s="3">
+      <c r="O89" s="3">
         <v>-3350300</v>
       </c>
-      <c r="O89" s="3">
+      <c r="P89" s="3">
         <v>-2130300</v>
       </c>
-      <c r="P89" s="3">
+      <c r="Q89" s="3">
         <v>7700600</v>
       </c>
-      <c r="Q89" s="3">
+      <c r="R89" s="3">
         <v>4027400</v>
       </c>
-      <c r="R89" s="3">
+      <c r="S89" s="3">
         <v>2586700</v>
       </c>
-      <c r="S89" s="3">
+      <c r="T89" s="3">
         <v>-4607300</v>
       </c>
-      <c r="T89" s="3">
+      <c r="U89" s="3">
         <v>831700</v>
       </c>
-      <c r="U89" s="3">
+      <c r="V89" s="3">
         <v>1545900</v>
       </c>
-      <c r="V89" s="3">
+      <c r="W89" s="3">
         <v>-766500</v>
       </c>
-      <c r="W89" s="3">
+      <c r="X89" s="3">
         <v>2718500</v>
       </c>
-      <c r="X89" s="3">
+      <c r="Y89" s="3">
         <v>-824700</v>
       </c>
-      <c r="Y89" s="3">
+      <c r="Z89" s="3">
         <v>-153300</v>
       </c>
-      <c r="Z89" s="3">
+      <c r="AA89" s="3">
         <v>-428600</v>
       </c>
-      <c r="AA89" s="3">
+      <c r="AB89" s="3">
         <v>3501700</v>
       </c>
-      <c r="AB89" s="3">
+      <c r="AC89" s="3">
         <v>-1296100</v>
       </c>
-      <c r="AC89" s="3">
+      <c r="AD89" s="3">
         <v>5231600</v>
       </c>
-      <c r="AD89" s="3">
+      <c r="AE89" s="3">
         <v>908000</v>
       </c>
-      <c r="AE89" s="3">
+      <c r="AF89" s="3">
         <v>643600</v>
       </c>
-      <c r="AF89" s="3">
+      <c r="AG89" s="3">
         <v>877700</v>
       </c>
-      <c r="AG89" s="3">
+      <c r="AH89" s="3">
         <v>-506300</v>
       </c>
-      <c r="AH89" s="3">
+      <c r="AI89" s="3">
         <v>-2456000</v>
       </c>
-      <c r="AI89" s="3">
+      <c r="AJ89" s="3">
         <v>-340700</v>
       </c>
-      <c r="AJ89" s="3">
+      <c r="AK89" s="3">
         <v>1561500</v>
       </c>
-      <c r="AK89" s="3">
+      <c r="AL89" s="3">
         <v>108800</v>
       </c>
-      <c r="AL89" s="3">
+      <c r="AM89" s="3">
         <v>3807600</v>
       </c>
     </row>
-    <row r="90" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="90" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C90" s="1" t="s">
         <v>79</v>
       </c>
@@ -8786,118 +9005,122 @@
       <c r="AJ90" s="3"/>
       <c r="AK90" s="3"/>
       <c r="AL90" s="3"/>
+      <c r="AM90" s="3"/>
     </row>
-    <row r="91" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="91" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C91" s="1" t="s">
         <v>80</v>
       </c>
       <c r="D91" s="3">
+        <v>-66200</v>
+      </c>
+      <c r="E91" s="3">
         <v>-14600</v>
       </c>
-      <c r="E91" s="3">
+      <c r="F91" s="3">
         <v>-32300</v>
       </c>
-      <c r="F91" s="3">
+      <c r="G91" s="3">
         <v>-62500</v>
       </c>
-      <c r="G91" s="3">
+      <c r="H91" s="3">
         <v>-40100</v>
       </c>
-      <c r="H91" s="3">
+      <c r="I91" s="3">
         <v>-27400</v>
       </c>
-      <c r="I91" s="3">
+      <c r="J91" s="3">
         <v>-61300</v>
       </c>
-      <c r="J91" s="3">
+      <c r="K91" s="3">
         <v>-23300</v>
       </c>
-      <c r="K91" s="3">
+      <c r="L91" s="3">
         <v>-23900</v>
       </c>
-      <c r="L91" s="3">
+      <c r="M91" s="3">
         <v>-17100</v>
       </c>
-      <c r="M91" s="3">
+      <c r="N91" s="3">
         <v>-113722000</v>
       </c>
-      <c r="N91" s="3">
+      <c r="O91" s="3">
         <v>-77226000</v>
       </c>
-      <c r="O91" s="3">
+      <c r="P91" s="3">
         <v>-104059000</v>
       </c>
-      <c r="P91" s="3">
+      <c r="Q91" s="3">
         <v>-52618000</v>
       </c>
-      <c r="Q91" s="3">
+      <c r="R91" s="3">
         <v>-74615000</v>
       </c>
-      <c r="R91" s="3">
+      <c r="S91" s="3">
         <v>-81614000</v>
       </c>
-      <c r="S91" s="3">
+      <c r="T91" s="3">
         <v>-15900</v>
       </c>
-      <c r="T91" s="3">
+      <c r="U91" s="3">
         <v>-14300</v>
       </c>
-      <c r="U91" s="3">
+      <c r="V91" s="3">
         <v>-43600</v>
       </c>
-      <c r="V91" s="3">
+      <c r="W91" s="3">
         <v>-25600</v>
       </c>
-      <c r="W91" s="3">
+      <c r="X91" s="3">
         <v>-24800</v>
       </c>
-      <c r="X91" s="3">
+      <c r="Y91" s="3">
         <v>-20300</v>
       </c>
-      <c r="Y91" s="3">
+      <c r="Z91" s="3">
         <v>-190900</v>
       </c>
-      <c r="Z91" s="3">
+      <c r="AA91" s="3">
         <v>-91000</v>
       </c>
-      <c r="AA91" s="3">
+      <c r="AB91" s="3">
         <v>-55400</v>
       </c>
-      <c r="AB91" s="3">
+      <c r="AC91" s="3">
         <v>-31700</v>
       </c>
-      <c r="AC91" s="3">
+      <c r="AD91" s="3">
         <v>-43000</v>
       </c>
-      <c r="AD91" s="3">
+      <c r="AE91" s="3">
         <v>-20100</v>
       </c>
-      <c r="AE91" s="3">
+      <c r="AF91" s="3">
         <v>-18000</v>
       </c>
-      <c r="AF91" s="3">
+      <c r="AG91" s="3">
         <v>-17800</v>
       </c>
-      <c r="AG91" s="3">
+      <c r="AH91" s="3">
         <v>-25100</v>
       </c>
-      <c r="AH91" s="3">
+      <c r="AI91" s="3">
         <v>-57300</v>
       </c>
-      <c r="AI91" s="3">
+      <c r="AJ91" s="3">
         <v>-37900</v>
       </c>
-      <c r="AJ91" s="3">
+      <c r="AK91" s="3">
         <v>-22400</v>
       </c>
-      <c r="AK91" s="3">
+      <c r="AL91" s="3">
         <v>-111600</v>
       </c>
-      <c r="AL91" s="3">
+      <c r="AM91" s="3">
         <v>-90400</v>
       </c>
     </row>
-    <row r="92" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="92" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C92" s="1" t="s">
         <v>81</v>
       </c>
@@ -9006,8 +9229,11 @@
       <c r="AL92" s="3">
         <v>0</v>
       </c>
+      <c r="AM92" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="93" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="93" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C93" s="1" t="s">
         <v>82</v>
       </c>
@@ -9116,118 +9342,124 @@
       <c r="AL93" s="3">
         <v>0</v>
       </c>
+      <c r="AM93" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="94" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="94" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C94" s="1" t="s">
         <v>83</v>
       </c>
       <c r="D94" s="3">
+        <v>2605800</v>
+      </c>
+      <c r="E94" s="3">
         <v>265900</v>
       </c>
-      <c r="E94" s="3">
+      <c r="F94" s="3">
         <v>-3917800</v>
       </c>
-      <c r="F94" s="3">
+      <c r="G94" s="3">
         <v>3642700</v>
       </c>
-      <c r="G94" s="3">
+      <c r="H94" s="3">
         <v>-1092400</v>
       </c>
-      <c r="H94" s="3">
+      <c r="I94" s="3">
         <v>1841100</v>
       </c>
-      <c r="I94" s="3">
+      <c r="J94" s="3">
         <v>-625400</v>
       </c>
-      <c r="J94" s="3">
+      <c r="K94" s="3">
         <v>-1107500</v>
       </c>
-      <c r="K94" s="3">
+      <c r="L94" s="3">
         <v>-261600</v>
       </c>
-      <c r="L94" s="3">
+      <c r="M94" s="3">
         <v>300800</v>
       </c>
-      <c r="M94" s="3">
+      <c r="N94" s="3">
         <v>-2910400</v>
       </c>
-      <c r="N94" s="3">
+      <c r="O94" s="3">
         <v>-2354900</v>
       </c>
-      <c r="O94" s="3">
+      <c r="P94" s="3">
         <v>2353800</v>
       </c>
-      <c r="P94" s="3">
+      <c r="Q94" s="3">
         <v>-2278800</v>
       </c>
-      <c r="Q94" s="3">
+      <c r="R94" s="3">
         <v>-4489600</v>
       </c>
-      <c r="R94" s="3">
+      <c r="S94" s="3">
         <v>-3902300</v>
       </c>
-      <c r="S94" s="3">
+      <c r="T94" s="3">
         <v>1124900</v>
       </c>
-      <c r="T94" s="3">
+      <c r="U94" s="3">
         <v>-723400</v>
       </c>
-      <c r="U94" s="3">
+      <c r="V94" s="3">
         <v>-365200</v>
       </c>
-      <c r="V94" s="3">
+      <c r="W94" s="3">
         <v>-124500</v>
       </c>
-      <c r="W94" s="3">
+      <c r="X94" s="3">
         <v>-446100</v>
       </c>
-      <c r="X94" s="3">
+      <c r="Y94" s="3">
         <v>-179800</v>
       </c>
-      <c r="Y94" s="3">
+      <c r="Z94" s="3">
         <v>-962200</v>
       </c>
-      <c r="Z94" s="3">
+      <c r="AA94" s="3">
         <v>-913600</v>
       </c>
-      <c r="AA94" s="3">
+      <c r="AB94" s="3">
         <v>-5520900</v>
       </c>
-      <c r="AB94" s="3">
+      <c r="AC94" s="3">
         <v>-97900</v>
       </c>
-      <c r="AC94" s="3">
+      <c r="AD94" s="3">
         <v>-5105000</v>
       </c>
-      <c r="AD94" s="3">
+      <c r="AE94" s="3">
         <v>-2452600</v>
       </c>
-      <c r="AE94" s="3">
+      <c r="AF94" s="3">
         <v>-1063800</v>
       </c>
-      <c r="AF94" s="3">
+      <c r="AG94" s="3">
         <v>-587600</v>
       </c>
-      <c r="AG94" s="3">
+      <c r="AH94" s="3">
         <v>1277600</v>
       </c>
-      <c r="AH94" s="3">
+      <c r="AI94" s="3">
         <v>-195600</v>
       </c>
-      <c r="AI94" s="3">
+      <c r="AJ94" s="3">
         <v>183200</v>
       </c>
-      <c r="AJ94" s="3">
+      <c r="AK94" s="3">
         <v>392500</v>
       </c>
-      <c r="AK94" s="3">
+      <c r="AL94" s="3">
         <v>-2371700</v>
       </c>
-      <c r="AL94" s="3">
+      <c r="AM94" s="3">
         <v>694800</v>
       </c>
     </row>
-    <row r="95" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="95" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C95" s="1" t="s">
         <v>84</v>
       </c>
@@ -9266,47 +9498,48 @@
       <c r="AJ95" s="3"/>
       <c r="AK95" s="3"/>
       <c r="AL95" s="3"/>
+      <c r="AM95" s="3"/>
     </row>
-    <row r="96" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="96" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C96" s="1" t="s">
         <v>85</v>
       </c>
       <c r="D96" s="3">
+        <v>495800</v>
+      </c>
+      <c r="E96" s="3">
         <v>26800</v>
       </c>
-      <c r="E96" s="3">
+      <c r="F96" s="3">
         <v>117000</v>
       </c>
-      <c r="F96" s="3">
+      <c r="G96" s="3">
         <v>134900</v>
       </c>
-      <c r="G96" s="3">
+      <c r="H96" s="3">
         <v>473000</v>
       </c>
-      <c r="H96" s="3">
+      <c r="I96" s="3">
         <v>26200</v>
       </c>
-      <c r="I96" s="3">
+      <c r="J96" s="3">
         <v>151100</v>
       </c>
-      <c r="J96" s="3">
+      <c r="K96" s="3">
         <v>102000</v>
       </c>
-      <c r="K96" s="3">
+      <c r="L96" s="3">
         <v>566300</v>
       </c>
-      <c r="L96" s="3">
+      <c r="M96" s="3">
         <v>23300</v>
       </c>
-      <c r="M96" s="3">
-        <v>0</v>
-      </c>
       <c r="N96" s="3">
+        <v>0</v>
+      </c>
+      <c r="O96" s="3">
         <v>-79700</v>
       </c>
-      <c r="O96" s="3">
-        <v>0</v>
-      </c>
       <c r="P96" s="3">
         <v>0</v>
       </c>
@@ -9314,11 +9547,11 @@
         <v>0</v>
       </c>
       <c r="R96" s="3">
+        <v>0</v>
+      </c>
+      <c r="S96" s="3">
         <v>-81300</v>
       </c>
-      <c r="S96" s="3">
-        <v>0</v>
-      </c>
       <c r="T96" s="3">
         <v>0</v>
       </c>
@@ -9362,22 +9595,25 @@
         <v>0</v>
       </c>
       <c r="AH96" s="3">
+        <v>0</v>
+      </c>
+      <c r="AI96" s="3">
         <v>-59200</v>
       </c>
-      <c r="AI96" s="3">
+      <c r="AJ96" s="3">
         <v>-237000</v>
       </c>
-      <c r="AJ96" s="3">
-        <v>0</v>
-      </c>
       <c r="AK96" s="3">
+        <v>0</v>
+      </c>
+      <c r="AL96" s="3">
         <v>-38100</v>
       </c>
-      <c r="AL96" s="3">
+      <c r="AM96" s="3">
         <v>-22800</v>
       </c>
     </row>
-    <row r="97" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="97" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C97" s="1" t="s">
         <v>86</v>
       </c>
@@ -9486,8 +9722,11 @@
       <c r="AL97" s="3">
         <v>0</v>
       </c>
+      <c r="AM97" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="98" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="98" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C98" s="1" t="s">
         <v>87</v>
       </c>
@@ -9596,8 +9835,11 @@
       <c r="AL98" s="3">
         <v>0</v>
       </c>
+      <c r="AM98" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="99" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="99" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C99" s="1" t="s">
         <v>88</v>
       </c>
@@ -9706,334 +9948,346 @@
       <c r="AL99" s="3">
         <v>0</v>
       </c>
+      <c r="AM99" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="100" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="100" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C100" s="1" t="s">
         <v>89</v>
       </c>
       <c r="D100" s="3">
+        <v>6108300</v>
+      </c>
+      <c r="E100" s="3">
         <v>-68000</v>
       </c>
-      <c r="E100" s="3">
+      <c r="F100" s="3">
         <v>-16521000</v>
       </c>
-      <c r="F100" s="3">
+      <c r="G100" s="3">
         <v>24357600</v>
       </c>
-      <c r="G100" s="3">
+      <c r="H100" s="3">
         <v>1880400</v>
       </c>
-      <c r="H100" s="3">
+      <c r="I100" s="3">
         <v>-4107500</v>
       </c>
-      <c r="I100" s="3">
+      <c r="J100" s="3">
         <v>17753300</v>
       </c>
-      <c r="J100" s="3">
+      <c r="K100" s="3">
         <v>447300</v>
       </c>
-      <c r="K100" s="3">
+      <c r="L100" s="3">
         <v>5022900</v>
       </c>
-      <c r="L100" s="3">
+      <c r="M100" s="3">
         <v>-13746200</v>
       </c>
-      <c r="M100" s="3">
+      <c r="N100" s="3">
         <v>-5147300</v>
       </c>
-      <c r="N100" s="3">
+      <c r="O100" s="3">
         <v>1697300</v>
       </c>
-      <c r="O100" s="3">
+      <c r="P100" s="3">
         <v>3000400</v>
       </c>
-      <c r="P100" s="3">
+      <c r="Q100" s="3">
         <v>1932700</v>
       </c>
-      <c r="Q100" s="3">
+      <c r="R100" s="3">
         <v>2031800</v>
       </c>
-      <c r="R100" s="3">
+      <c r="S100" s="3">
         <v>1404600</v>
       </c>
-      <c r="S100" s="3">
+      <c r="T100" s="3">
         <v>2911000</v>
       </c>
-      <c r="T100" s="3">
+      <c r="U100" s="3">
         <v>453200</v>
       </c>
-      <c r="U100" s="3">
+      <c r="V100" s="3">
         <v>261800</v>
       </c>
-      <c r="V100" s="3">
+      <c r="W100" s="3">
         <v>553800</v>
       </c>
-      <c r="W100" s="3">
+      <c r="X100" s="3">
         <v>-2356000</v>
       </c>
-      <c r="X100" s="3">
+      <c r="Y100" s="3">
         <v>3526800</v>
       </c>
-      <c r="Y100" s="3">
+      <c r="Z100" s="3">
         <v>-950700</v>
       </c>
-      <c r="Z100" s="3">
+      <c r="AA100" s="3">
         <v>3000500</v>
       </c>
-      <c r="AA100" s="3">
+      <c r="AB100" s="3">
         <v>3588600</v>
       </c>
-      <c r="AB100" s="3">
+      <c r="AC100" s="3">
         <v>-289800</v>
       </c>
-      <c r="AC100" s="3">
+      <c r="AD100" s="3">
         <v>491400</v>
       </c>
-      <c r="AD100" s="3">
+      <c r="AE100" s="3">
         <v>1689200</v>
       </c>
-      <c r="AE100" s="3">
+      <c r="AF100" s="3">
         <v>354700</v>
       </c>
-      <c r="AF100" s="3">
+      <c r="AG100" s="3">
         <v>-1323700</v>
       </c>
-      <c r="AG100" s="3">
+      <c r="AH100" s="3">
         <v>-309500</v>
       </c>
-      <c r="AH100" s="3">
+      <c r="AI100" s="3">
         <v>2140800</v>
       </c>
-      <c r="AI100" s="3">
+      <c r="AJ100" s="3">
         <v>-384900</v>
       </c>
-      <c r="AJ100" s="3">
+      <c r="AK100" s="3">
         <v>-1500100</v>
       </c>
-      <c r="AK100" s="3">
+      <c r="AL100" s="3">
         <v>1503800</v>
       </c>
-      <c r="AL100" s="3">
+      <c r="AM100" s="3">
         <v>-1778900</v>
       </c>
     </row>
-    <row r="101" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="101" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C101" s="1" t="s">
         <v>90</v>
       </c>
       <c r="D101" s="3">
+        <v>231000</v>
+      </c>
+      <c r="E101" s="3">
         <v>262700</v>
       </c>
-      <c r="E101" s="3">
+      <c r="F101" s="3">
         <v>-179300</v>
       </c>
-      <c r="F101" s="3">
+      <c r="G101" s="3">
         <v>27300</v>
       </c>
-      <c r="G101" s="3">
+      <c r="H101" s="3">
         <v>-105100</v>
       </c>
-      <c r="H101" s="3">
+      <c r="I101" s="3">
         <v>125800</v>
       </c>
-      <c r="I101" s="3">
+      <c r="J101" s="3">
         <v>-1568200</v>
       </c>
-      <c r="J101" s="3">
+      <c r="K101" s="3">
         <v>609200</v>
       </c>
-      <c r="K101" s="3">
+      <c r="L101" s="3">
         <v>667200</v>
       </c>
-      <c r="L101" s="3">
+      <c r="M101" s="3">
         <v>217100</v>
       </c>
-      <c r="M101" s="3">
+      <c r="N101" s="3">
         <v>-1479100</v>
       </c>
-      <c r="N101" s="3">
+      <c r="O101" s="3">
         <v>638600</v>
       </c>
-      <c r="O101" s="3">
+      <c r="P101" s="3">
         <v>657000</v>
       </c>
-      <c r="P101" s="3">
+      <c r="Q101" s="3">
         <v>203100</v>
       </c>
-      <c r="Q101" s="3">
+      <c r="R101" s="3">
         <v>68900</v>
       </c>
-      <c r="R101" s="3">
+      <c r="S101" s="3">
         <v>409500</v>
       </c>
-      <c r="S101" s="3">
+      <c r="T101" s="3">
         <v>18100</v>
       </c>
-      <c r="T101" s="3">
+      <c r="U101" s="3">
         <v>295500</v>
       </c>
-      <c r="U101" s="3">
+      <c r="V101" s="3">
         <v>-571700</v>
       </c>
-      <c r="V101" s="3">
+      <c r="W101" s="3">
         <v>-142900</v>
       </c>
-      <c r="W101" s="3">
+      <c r="X101" s="3">
         <v>-159900</v>
       </c>
-      <c r="X101" s="3">
+      <c r="Y101" s="3">
         <v>200400</v>
       </c>
-      <c r="Y101" s="3">
+      <c r="Z101" s="3">
         <v>369400</v>
       </c>
-      <c r="Z101" s="3">
+      <c r="AA101" s="3">
         <v>-340600</v>
       </c>
-      <c r="AA101" s="3">
+      <c r="AB101" s="3">
         <v>51200</v>
       </c>
-      <c r="AB101" s="3">
+      <c r="AC101" s="3">
         <v>90500</v>
       </c>
-      <c r="AC101" s="3">
+      <c r="AD101" s="3">
         <v>6400</v>
       </c>
-      <c r="AD101" s="3">
+      <c r="AE101" s="3">
         <v>-76600</v>
       </c>
-      <c r="AE101" s="3">
+      <c r="AF101" s="3">
         <v>218900</v>
       </c>
-      <c r="AF101" s="3">
+      <c r="AG101" s="3">
         <v>50500</v>
       </c>
-      <c r="AG101" s="3">
+      <c r="AH101" s="3">
         <v>-377500</v>
       </c>
-      <c r="AH101" s="3">
+      <c r="AI101" s="3">
         <v>14000</v>
       </c>
-      <c r="AI101" s="3">
+      <c r="AJ101" s="3">
         <v>8400</v>
       </c>
-      <c r="AJ101" s="3">
+      <c r="AK101" s="3">
         <v>-108300</v>
       </c>
-      <c r="AK101" s="3">
+      <c r="AL101" s="3">
         <v>138000</v>
       </c>
-      <c r="AL101" s="3">
+      <c r="AM101" s="3">
         <v>-105900</v>
       </c>
     </row>
-    <row r="102" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="102" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C102" s="1" t="s">
         <v>91</v>
       </c>
       <c r="D102" s="3">
+        <v>3251800</v>
+      </c>
+      <c r="E102" s="3">
         <v>-1136400</v>
       </c>
-      <c r="E102" s="3">
+      <c r="F102" s="3">
         <v>-4200200</v>
       </c>
-      <c r="F102" s="3">
+      <c r="G102" s="3">
         <v>6101900</v>
       </c>
-      <c r="G102" s="3">
+      <c r="H102" s="3">
         <v>-4689900</v>
       </c>
-      <c r="H102" s="3">
+      <c r="I102" s="3">
         <v>1025100</v>
       </c>
-      <c r="I102" s="3">
+      <c r="J102" s="3">
         <v>3597300</v>
       </c>
-      <c r="J102" s="3">
+      <c r="K102" s="3">
         <v>3121100</v>
       </c>
-      <c r="K102" s="3">
+      <c r="L102" s="3">
         <v>-7058600</v>
       </c>
-      <c r="L102" s="3">
+      <c r="M102" s="3">
         <v>-2478800</v>
       </c>
-      <c r="M102" s="3">
+      <c r="N102" s="3">
         <v>2475100</v>
       </c>
-      <c r="N102" s="3">
+      <c r="O102" s="3">
         <v>-3369400</v>
       </c>
-      <c r="O102" s="3">
+      <c r="P102" s="3">
         <v>3880900</v>
       </c>
-      <c r="P102" s="3">
+      <c r="Q102" s="3">
         <v>7557600</v>
       </c>
-      <c r="Q102" s="3">
+      <c r="R102" s="3">
         <v>1638600</v>
       </c>
-      <c r="R102" s="3">
+      <c r="S102" s="3">
         <v>498500</v>
       </c>
-      <c r="S102" s="3">
+      <c r="T102" s="3">
         <v>-553300</v>
       </c>
-      <c r="T102" s="3">
+      <c r="U102" s="3">
         <v>857000</v>
       </c>
-      <c r="U102" s="3">
+      <c r="V102" s="3">
         <v>870800</v>
       </c>
-      <c r="V102" s="3">
+      <c r="W102" s="3">
         <v>-480000</v>
       </c>
-      <c r="W102" s="3">
+      <c r="X102" s="3">
         <v>-243500</v>
       </c>
-      <c r="X102" s="3">
+      <c r="Y102" s="3">
         <v>2722600</v>
       </c>
-      <c r="Y102" s="3">
+      <c r="Z102" s="3">
         <v>-1696800</v>
       </c>
-      <c r="Z102" s="3">
+      <c r="AA102" s="3">
         <v>1317700</v>
       </c>
-      <c r="AA102" s="3">
+      <c r="AB102" s="3">
         <v>1620600</v>
       </c>
-      <c r="AB102" s="3">
+      <c r="AC102" s="3">
         <v>-1593300</v>
       </c>
-      <c r="AC102" s="3">
+      <c r="AD102" s="3">
         <v>624400</v>
       </c>
-      <c r="AD102" s="3">
+      <c r="AE102" s="3">
         <v>68000</v>
       </c>
-      <c r="AE102" s="3">
+      <c r="AF102" s="3">
         <v>153400</v>
       </c>
-      <c r="AF102" s="3">
+      <c r="AG102" s="3">
         <v>-983000</v>
       </c>
-      <c r="AG102" s="3">
+      <c r="AH102" s="3">
         <v>84300</v>
       </c>
-      <c r="AH102" s="3">
+      <c r="AI102" s="3">
         <v>-496900</v>
       </c>
-      <c r="AI102" s="3">
+      <c r="AJ102" s="3">
         <v>-534100</v>
       </c>
-      <c r="AJ102" s="3">
+      <c r="AK102" s="3">
         <v>345600</v>
       </c>
-      <c r="AK102" s="3">
+      <c r="AL102" s="3">
         <v>-621200</v>
       </c>
-      <c r="AL102" s="3">
+      <c r="AM102" s="3">
         <v>2617600</v>
       </c>
     </row>

--- a/AAII_Financials/Quarterly/WF_QTR_FIN.xlsx
+++ b/AAII_Financials/Quarterly/WF_QTR_FIN.xlsx
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="206" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="209" uniqueCount="92">
   <si>
     <t>WF</t>
   </si>
@@ -656,302 +656,308 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet2"/>
-  <dimension ref="A5:AN102"/>
+  <dimension ref="A5:AO102"/>
   <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="5" style="1" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="26.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="69.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="14" width="16" style="1" bestFit="1" customWidth="1"/>
-    <col min="15" max="15" width="17" style="1" bestFit="1" customWidth="1"/>
-    <col min="16" max="16" width="16" style="1" bestFit="1" customWidth="1"/>
-    <col min="17" max="17" width="17" style="1" bestFit="1" customWidth="1"/>
-    <col min="18" max="40" width="16" style="1" bestFit="1" customWidth="1"/>
-    <col min="41" max="16384" width="9.140625" style="1"/>
+    <col min="4" max="15" width="16" style="1" bestFit="1" customWidth="1"/>
+    <col min="16" max="16" width="17" style="1" bestFit="1" customWidth="1"/>
+    <col min="17" max="17" width="16" style="1" bestFit="1" customWidth="1"/>
+    <col min="18" max="18" width="17" style="1" bestFit="1" customWidth="1"/>
+    <col min="19" max="41" width="16" style="1" bestFit="1" customWidth="1"/>
+    <col min="42" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
-    <row r="5" spans="1:40" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:41" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:40" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:41" x14ac:dyDescent="0.2">
       <c r="B6" s="1" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:40" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:41" x14ac:dyDescent="0.2">
       <c r="C7" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D7" s="2">
+        <v>46022</v>
+      </c>
+      <c r="E7" s="2">
         <v>45930</v>
       </c>
-      <c r="E7" s="2">
+      <c r="F7" s="2">
         <v>45838</v>
       </c>
-      <c r="F7" s="2">
+      <c r="G7" s="2">
         <v>45747</v>
       </c>
-      <c r="G7" s="2">
+      <c r="H7" s="2">
         <v>45657</v>
       </c>
-      <c r="H7" s="2">
+      <c r="I7" s="2">
         <v>45565</v>
       </c>
-      <c r="I7" s="2">
+      <c r="J7" s="2">
         <v>45473</v>
       </c>
-      <c r="J7" s="2">
+      <c r="K7" s="2">
         <v>45382</v>
       </c>
-      <c r="K7" s="2">
+      <c r="L7" s="2">
         <v>45291</v>
       </c>
-      <c r="L7" s="2">
+      <c r="M7" s="2">
         <v>45199</v>
       </c>
-      <c r="M7" s="2">
+      <c r="N7" s="2">
         <v>45107</v>
       </c>
-      <c r="N7" s="2">
+      <c r="O7" s="2">
         <v>45016</v>
       </c>
-      <c r="O7" s="2">
+      <c r="P7" s="2">
         <v>44926</v>
       </c>
-      <c r="P7" s="2">
+      <c r="Q7" s="2">
         <v>44834</v>
       </c>
-      <c r="Q7" s="2">
+      <c r="R7" s="2">
         <v>44742</v>
       </c>
-      <c r="R7" s="2">
+      <c r="S7" s="2">
         <v>44651</v>
       </c>
-      <c r="S7" s="2">
+      <c r="T7" s="2">
         <v>44561</v>
       </c>
-      <c r="T7" s="2">
+      <c r="U7" s="2">
         <v>44469</v>
       </c>
-      <c r="U7" s="2">
+      <c r="V7" s="2">
         <v>44377</v>
       </c>
-      <c r="V7" s="2">
+      <c r="W7" s="2">
         <v>44286</v>
       </c>
-      <c r="W7" s="2">
+      <c r="X7" s="2">
         <v>44196</v>
       </c>
-      <c r="X7" s="2">
+      <c r="Y7" s="2">
         <v>44104</v>
       </c>
-      <c r="Y7" s="2">
+      <c r="Z7" s="2">
         <v>44012</v>
       </c>
-      <c r="Z7" s="2">
+      <c r="AA7" s="2">
         <v>43921</v>
       </c>
-      <c r="AA7" s="2">
+      <c r="AB7" s="2">
         <v>43830</v>
       </c>
-      <c r="AB7" s="2">
+      <c r="AC7" s="2">
         <v>43738</v>
       </c>
-      <c r="AC7" s="2">
+      <c r="AD7" s="2">
         <v>43646</v>
       </c>
-      <c r="AD7" s="2">
+      <c r="AE7" s="2">
         <v>43555</v>
       </c>
-      <c r="AE7" s="2">
+      <c r="AF7" s="2">
         <v>43465</v>
       </c>
-      <c r="AF7" s="2">
+      <c r="AG7" s="2">
         <v>43373</v>
       </c>
-      <c r="AG7" s="2">
+      <c r="AH7" s="2">
         <v>43281</v>
       </c>
-      <c r="AH7" s="2">
+      <c r="AI7" s="2">
         <v>43190</v>
       </c>
-      <c r="AI7" s="2">
+      <c r="AJ7" s="2">
         <v>43100</v>
       </c>
-      <c r="AJ7" s="2">
+      <c r="AK7" s="2">
         <v>43008</v>
       </c>
-      <c r="AK7" s="2">
+      <c r="AL7" s="2">
         <v>42916</v>
       </c>
-      <c r="AL7" s="2">
+      <c r="AM7" s="2">
         <v>42825</v>
       </c>
-      <c r="AM7" s="2">
+      <c r="AN7" s="2">
         <v>42735</v>
       </c>
-      <c r="AN7" s="2">
+      <c r="AO7" s="2">
         <v>42643</v>
       </c>
     </row>
-    <row r="8" spans="1:40" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:41" x14ac:dyDescent="0.2">
       <c r="C8" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D8" s="3">
+        <v>1799400</v>
+      </c>
+      <c r="E8" s="3">
         <v>1758000</v>
       </c>
-      <c r="E8" s="3">
+      <c r="F8" s="3">
         <v>1657300</v>
       </c>
-      <c r="F8" s="3">
+      <c r="G8" s="3">
         <v>1801500</v>
       </c>
-      <c r="G8" s="3">
-        <v>2144100</v>
-      </c>
       <c r="H8" s="3">
+        <v>1663000</v>
+      </c>
+      <c r="I8" s="3">
         <v>1889100</v>
       </c>
-      <c r="I8" s="3">
+      <c r="J8" s="3">
         <v>1489700</v>
       </c>
-      <c r="J8" s="3">
+      <c r="K8" s="3">
         <v>2219900</v>
       </c>
-      <c r="K8" s="3">
+      <c r="L8" s="3">
         <v>1264600</v>
       </c>
-      <c r="L8" s="3">
+      <c r="M8" s="3">
         <v>2101400</v>
       </c>
-      <c r="M8" s="3">
+      <c r="N8" s="3">
         <v>1748600</v>
       </c>
-      <c r="N8" s="3">
+      <c r="O8" s="3">
         <v>2091700</v>
       </c>
-      <c r="O8" s="3">
+      <c r="P8" s="3">
         <v>3462200</v>
       </c>
-      <c r="P8" s="3">
+      <c r="Q8" s="3">
         <v>2792200</v>
       </c>
-      <c r="Q8" s="3">
+      <c r="R8" s="3">
         <v>2487200</v>
       </c>
-      <c r="R8" s="3">
+      <c r="S8" s="3">
         <v>2264400</v>
       </c>
-      <c r="S8" s="3">
+      <c r="T8" s="3">
         <v>2026000</v>
       </c>
-      <c r="T8" s="3">
+      <c r="U8" s="3">
         <v>1862200</v>
       </c>
-      <c r="U8" s="3">
+      <c r="V8" s="3">
         <v>1787500</v>
       </c>
-      <c r="V8" s="3">
+      <c r="W8" s="3">
         <v>1722100</v>
       </c>
-      <c r="W8" s="3">
+      <c r="X8" s="3">
         <v>1728200</v>
       </c>
-      <c r="X8" s="3">
+      <c r="Y8" s="3">
         <v>1749800</v>
       </c>
-      <c r="Y8" s="3">
+      <c r="Z8" s="3">
         <v>1857400</v>
       </c>
-      <c r="Z8" s="3">
+      <c r="AA8" s="3">
         <v>2028100</v>
       </c>
-      <c r="AA8" s="3">
+      <c r="AB8" s="3">
         <v>2216400</v>
       </c>
-      <c r="AB8" s="3">
+      <c r="AC8" s="3">
         <v>2287800</v>
       </c>
-      <c r="AC8" s="3">
+      <c r="AD8" s="3">
         <v>2353100</v>
       </c>
-      <c r="AD8" s="3">
+      <c r="AE8" s="3">
         <v>2369400</v>
       </c>
-      <c r="AE8" s="3">
+      <c r="AF8" s="3">
         <v>2154000</v>
       </c>
-      <c r="AF8" s="3">
+      <c r="AG8" s="3">
         <v>2006200</v>
       </c>
-      <c r="AG8" s="3">
+      <c r="AH8" s="3">
         <v>1989700</v>
       </c>
-      <c r="AH8" s="3">
+      <c r="AI8" s="3">
         <v>1910800</v>
       </c>
-      <c r="AI8" s="3">
+      <c r="AJ8" s="3">
         <v>1912500</v>
       </c>
-      <c r="AJ8" s="3">
+      <c r="AK8" s="3">
         <v>1925300</v>
       </c>
-      <c r="AK8" s="3">
+      <c r="AL8" s="3">
         <v>1853100</v>
       </c>
-      <c r="AL8" s="3">
+      <c r="AM8" s="3">
         <v>1833700</v>
       </c>
-      <c r="AM8" s="3">
+      <c r="AN8" s="3">
         <v>1898800</v>
       </c>
-      <c r="AN8" s="3">
+      <c r="AO8" s="3">
         <v>1898000</v>
       </c>
     </row>
-    <row r="9" spans="1:40" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:41" x14ac:dyDescent="0.2">
       <c r="C9" s="1" t="s">
         <v>4</v>
       </c>
       <c r="D9" s="3">
+        <v>6600</v>
+      </c>
+      <c r="E9" s="3">
         <v>6800</v>
       </c>
-      <c r="E9" s="3">
+      <c r="F9" s="3">
         <v>6400</v>
       </c>
-      <c r="F9" s="3">
+      <c r="G9" s="3">
         <v>5900</v>
       </c>
-      <c r="G9" s="3">
+      <c r="H9" s="3">
         <v>7000</v>
       </c>
-      <c r="H9" s="3">
+      <c r="I9" s="3">
         <v>7600</v>
       </c>
-      <c r="I9" s="3">
+      <c r="J9" s="3">
         <v>7000</v>
       </c>
-      <c r="J9" s="3">
+      <c r="K9" s="3">
         <v>7100</v>
       </c>
-      <c r="K9" s="3">
+      <c r="L9" s="3">
         <v>9400</v>
-      </c>
-      <c r="L9" s="3">
-        <v>6800</v>
       </c>
       <c r="M9" s="3">
         <v>6800</v>
       </c>
       <c r="N9" s="3">
+        <v>6800</v>
+      </c>
+      <c r="O9" s="3">
         <v>7100</v>
       </c>
-      <c r="O9" s="3" t="s">
-        <v>5</v>
-      </c>
       <c r="P9" s="3" t="s">
         <v>5</v>
       </c>
@@ -1027,47 +1033,50 @@
       <c r="AN9" s="3" t="s">
         <v>5</v>
       </c>
+      <c r="AO9" s="3" t="s">
+        <v>5</v>
+      </c>
     </row>
-    <row r="10" spans="1:40" x14ac:dyDescent="0.2">
+    <row r="10" spans="1:41" x14ac:dyDescent="0.2">
       <c r="C10" s="1" t="s">
         <v>6</v>
       </c>
       <c r="D10" s="3">
+        <v>1792700</v>
+      </c>
+      <c r="E10" s="3">
         <v>1751200</v>
       </c>
-      <c r="E10" s="3">
+      <c r="F10" s="3">
         <v>1650900</v>
       </c>
-      <c r="F10" s="3">
+      <c r="G10" s="3">
         <v>1795600</v>
       </c>
-      <c r="G10" s="3">
-        <v>2137100</v>
-      </c>
       <c r="H10" s="3">
+        <v>1656000</v>
+      </c>
+      <c r="I10" s="3">
         <v>1881500</v>
       </c>
-      <c r="I10" s="3">
+      <c r="J10" s="3">
         <v>1482800</v>
       </c>
-      <c r="J10" s="3">
+      <c r="K10" s="3">
         <v>2212800</v>
       </c>
-      <c r="K10" s="3">
+      <c r="L10" s="3">
         <v>1255200</v>
       </c>
-      <c r="L10" s="3">
+      <c r="M10" s="3">
         <v>2094600</v>
       </c>
-      <c r="M10" s="3">
+      <c r="N10" s="3">
         <v>1741800</v>
       </c>
-      <c r="N10" s="3">
+      <c r="O10" s="3">
         <v>2084600</v>
       </c>
-      <c r="O10" s="3" t="s">
-        <v>5</v>
-      </c>
       <c r="P10" s="3" t="s">
         <v>5</v>
       </c>
@@ -1143,8 +1152,11 @@
       <c r="AN10" s="3" t="s">
         <v>5</v>
       </c>
+      <c r="AO10" s="3" t="s">
+        <v>5</v>
+      </c>
     </row>
-    <row r="11" spans="1:40" x14ac:dyDescent="0.2">
+    <row r="11" spans="1:41" x14ac:dyDescent="0.2">
       <c r="C11" s="1" t="s">
         <v>7</v>
       </c>
@@ -1185,8 +1197,9 @@
       <c r="AL11" s="3"/>
       <c r="AM11" s="3"/>
       <c r="AN11" s="3"/>
+      <c r="AO11" s="3"/>
     </row>
-    <row r="12" spans="1:40" x14ac:dyDescent="0.2">
+    <row r="12" spans="1:41" x14ac:dyDescent="0.2">
       <c r="C12" s="1" t="s">
         <v>8</v>
       </c>
@@ -1301,8 +1314,11 @@
       <c r="AN12" s="3" t="s">
         <v>5</v>
       </c>
+      <c r="AO12" s="3" t="s">
+        <v>5</v>
+      </c>
     </row>
-    <row r="13" spans="1:40" x14ac:dyDescent="0.2">
+    <row r="13" spans="1:41" x14ac:dyDescent="0.2">
       <c r="C13" s="1" t="s">
         <v>9</v>
       </c>
@@ -1417,47 +1433,50 @@
       <c r="AN13" s="3">
         <v>0</v>
       </c>
+      <c r="AO13" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="14" spans="1:40" x14ac:dyDescent="0.2">
+    <row r="14" spans="1:41" x14ac:dyDescent="0.2">
       <c r="C14" s="1" t="s">
         <v>10</v>
       </c>
       <c r="D14" s="3">
+        <v>481100</v>
+      </c>
+      <c r="E14" s="3">
         <v>-385700</v>
       </c>
-      <c r="E14" s="3">
+      <c r="F14" s="3">
         <v>23100</v>
       </c>
-      <c r="F14" s="3">
+      <c r="G14" s="3">
         <v>800</v>
       </c>
-      <c r="G14" s="3">
+      <c r="H14" s="3">
         <v>6200</v>
       </c>
-      <c r="H14" s="3">
-        <v>0</v>
-      </c>
       <c r="I14" s="3">
+        <v>0</v>
+      </c>
+      <c r="J14" s="3">
         <v>8400</v>
       </c>
-      <c r="J14" s="3">
+      <c r="K14" s="3">
         <v>12300</v>
       </c>
-      <c r="K14" s="3">
+      <c r="L14" s="3">
         <v>-1700</v>
       </c>
-      <c r="L14" s="3">
-        <v>0</v>
-      </c>
       <c r="M14" s="3">
+        <v>0</v>
+      </c>
+      <c r="N14" s="3">
         <v>-200</v>
       </c>
-      <c r="N14" s="3">
+      <c r="O14" s="3">
         <v>42300</v>
       </c>
-      <c r="O14" s="3">
-        <v>0</v>
-      </c>
       <c r="P14" s="3">
         <v>0</v>
       </c>
@@ -1533,124 +1552,130 @@
       <c r="AN14" s="3">
         <v>0</v>
       </c>
+      <c r="AO14" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="15" spans="1:40" x14ac:dyDescent="0.2">
+    <row r="15" spans="1:41" x14ac:dyDescent="0.2">
       <c r="C15" s="1" t="s">
         <v>11</v>
       </c>
       <c r="D15" s="3">
+        <v>291800</v>
+      </c>
+      <c r="E15" s="3">
         <v>111700</v>
       </c>
-      <c r="E15" s="3">
+      <c r="F15" s="3">
         <v>112700</v>
       </c>
-      <c r="F15" s="3">
+      <c r="G15" s="3">
         <v>210100</v>
       </c>
-      <c r="G15" s="3">
-        <v>150600</v>
-      </c>
       <c r="H15" s="3">
+        <v>282800</v>
+      </c>
+      <c r="I15" s="3">
         <v>108500</v>
       </c>
-      <c r="I15" s="3">
+      <c r="J15" s="3">
         <v>6300</v>
       </c>
-      <c r="J15" s="3">
+      <c r="K15" s="3">
         <v>205400</v>
       </c>
-      <c r="K15" s="3">
+      <c r="L15" s="3">
         <v>144200</v>
       </c>
-      <c r="L15" s="3">
+      <c r="M15" s="3">
         <v>130600</v>
       </c>
-      <c r="M15" s="3">
+      <c r="N15" s="3">
         <v>130000</v>
       </c>
-      <c r="N15" s="3">
+      <c r="O15" s="3">
         <v>130100</v>
       </c>
-      <c r="O15" s="3">
+      <c r="P15" s="3">
         <v>-101500</v>
       </c>
-      <c r="P15" s="3">
+      <c r="Q15" s="3">
         <v>-92100</v>
       </c>
-      <c r="Q15" s="3">
+      <c r="R15" s="3">
         <v>-100700</v>
       </c>
-      <c r="R15" s="3">
+      <c r="S15" s="3">
         <v>-101400</v>
       </c>
-      <c r="S15" s="3">
+      <c r="T15" s="3">
         <v>-98200</v>
       </c>
-      <c r="T15" s="3">
+      <c r="U15" s="3">
         <v>-97600</v>
       </c>
-      <c r="U15" s="3">
+      <c r="V15" s="3">
         <v>-97400</v>
       </c>
-      <c r="V15" s="3">
+      <c r="W15" s="3">
         <v>-100600</v>
       </c>
-      <c r="W15" s="3">
+      <c r="X15" s="3">
         <v>-99400</v>
       </c>
-      <c r="X15" s="3">
+      <c r="Y15" s="3">
         <v>-99600</v>
       </c>
-      <c r="Y15" s="3">
+      <c r="Z15" s="3">
         <v>-96100</v>
       </c>
-      <c r="Z15" s="3">
+      <c r="AA15" s="3">
         <v>-109500</v>
       </c>
-      <c r="AA15" s="3">
+      <c r="AB15" s="3">
         <v>-115200</v>
       </c>
-      <c r="AB15" s="3">
+      <c r="AC15" s="3">
         <v>-112100</v>
       </c>
-      <c r="AC15" s="3">
+      <c r="AD15" s="3">
         <v>-104100</v>
       </c>
-      <c r="AD15" s="3">
+      <c r="AE15" s="3">
         <v>-88900</v>
       </c>
-      <c r="AE15" s="3">
+      <c r="AF15" s="3">
         <v>-50500</v>
       </c>
-      <c r="AF15" s="3">
+      <c r="AG15" s="3">
         <v>-47800</v>
       </c>
-      <c r="AG15" s="3">
+      <c r="AH15" s="3">
         <v>-44700</v>
       </c>
-      <c r="AH15" s="3">
+      <c r="AI15" s="3">
         <v>-40700</v>
       </c>
-      <c r="AI15" s="3">
+      <c r="AJ15" s="3">
         <v>-39500</v>
       </c>
-      <c r="AJ15" s="3">
+      <c r="AK15" s="3">
         <v>-40300</v>
       </c>
-      <c r="AK15" s="3">
+      <c r="AL15" s="3">
         <v>-40800</v>
       </c>
-      <c r="AL15" s="3">
+      <c r="AM15" s="3">
         <v>-44500</v>
       </c>
-      <c r="AM15" s="3">
+      <c r="AN15" s="3">
         <v>-54800</v>
       </c>
-      <c r="AN15" s="3">
+      <c r="AO15" s="3">
         <v>-53700</v>
       </c>
     </row>
-    <row r="16" spans="1:40" x14ac:dyDescent="0.2">
+    <row r="16" spans="1:41" x14ac:dyDescent="0.2">
       <c r="D16" s="3"/>
       <c r="E16" s="3"/>
       <c r="F16" s="3"/>
@@ -1688,240 +1713,247 @@
       <c r="AL16" s="3"/>
       <c r="AM16" s="3"/>
       <c r="AN16" s="3"/>
+      <c r="AO16" s="3"/>
     </row>
-    <row r="17" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="17" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C17" s="1" t="s">
         <v>12</v>
       </c>
       <c r="D17" s="3">
+        <v>1298800</v>
+      </c>
+      <c r="E17" s="3">
         <v>1041000</v>
       </c>
-      <c r="E17" s="3">
+      <c r="F17" s="3">
         <v>826800</v>
       </c>
-      <c r="F17" s="3">
+      <c r="G17" s="3">
         <v>1211300</v>
       </c>
-      <c r="G17" s="3">
-        <v>1684700</v>
-      </c>
       <c r="H17" s="3">
+        <v>1203500</v>
+      </c>
+      <c r="I17" s="3">
         <v>979300</v>
       </c>
-      <c r="I17" s="3">
+      <c r="J17" s="3">
         <v>578900</v>
       </c>
-      <c r="J17" s="3">
+      <c r="K17" s="3">
         <v>1363800</v>
       </c>
-      <c r="K17" s="3">
+      <c r="L17" s="3">
         <v>1160500</v>
       </c>
-      <c r="L17" s="3">
+      <c r="M17" s="3">
         <v>1189600</v>
       </c>
-      <c r="M17" s="3">
+      <c r="N17" s="3">
         <v>1049500</v>
       </c>
-      <c r="N17" s="3">
+      <c r="O17" s="3">
         <v>1131700</v>
       </c>
-      <c r="O17" s="3">
+      <c r="P17" s="3">
         <v>1897900</v>
       </c>
-      <c r="P17" s="3">
+      <c r="Q17" s="3">
         <v>1245200</v>
       </c>
-      <c r="Q17" s="3">
+      <c r="R17" s="3">
         <v>1121400</v>
       </c>
-      <c r="R17" s="3">
+      <c r="S17" s="3">
         <v>861300</v>
       </c>
-      <c r="S17" s="3">
+      <c r="T17" s="3">
         <v>772200</v>
       </c>
-      <c r="T17" s="3">
+      <c r="U17" s="3">
         <v>616800</v>
       </c>
-      <c r="U17" s="3">
+      <c r="V17" s="3">
         <v>573600</v>
       </c>
-      <c r="V17" s="3">
+      <c r="W17" s="3">
         <v>625700</v>
       </c>
-      <c r="W17" s="3">
+      <c r="X17" s="3">
         <v>727900</v>
       </c>
-      <c r="X17" s="3">
+      <c r="Y17" s="3">
         <v>721100</v>
       </c>
-      <c r="Y17" s="3">
+      <c r="Z17" s="3">
         <v>966200</v>
       </c>
-      <c r="Z17" s="3">
+      <c r="AA17" s="3">
         <v>926000</v>
       </c>
-      <c r="AA17" s="3">
+      <c r="AB17" s="3">
         <v>1019500</v>
       </c>
-      <c r="AB17" s="3">
+      <c r="AC17" s="3">
         <v>1190700</v>
       </c>
-      <c r="AC17" s="3">
+      <c r="AD17" s="3">
         <v>1111900</v>
       </c>
-      <c r="AD17" s="3">
+      <c r="AE17" s="3">
         <v>1098300</v>
       </c>
-      <c r="AE17" s="3">
+      <c r="AF17" s="3">
         <v>1157200</v>
       </c>
-      <c r="AF17" s="3">
+      <c r="AG17" s="3">
         <v>918800</v>
       </c>
-      <c r="AG17" s="3">
+      <c r="AH17" s="3">
         <v>752200</v>
       </c>
-      <c r="AH17" s="3">
+      <c r="AI17" s="3">
         <v>877900</v>
       </c>
-      <c r="AI17" s="3">
+      <c r="AJ17" s="3">
         <v>1026000</v>
       </c>
-      <c r="AJ17" s="3">
+      <c r="AK17" s="3">
         <v>926800</v>
       </c>
-      <c r="AK17" s="3">
+      <c r="AL17" s="3">
         <v>906500</v>
       </c>
-      <c r="AL17" s="3">
+      <c r="AM17" s="3">
         <v>830000</v>
       </c>
-      <c r="AM17" s="3">
+      <c r="AN17" s="3">
         <v>903100</v>
       </c>
-      <c r="AN17" s="3">
+      <c r="AO17" s="3">
         <v>963600</v>
       </c>
     </row>
-    <row r="18" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="18" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C18" s="1" t="s">
         <v>13</v>
       </c>
       <c r="D18" s="3">
+        <v>500500</v>
+      </c>
+      <c r="E18" s="3">
         <v>717000</v>
       </c>
-      <c r="E18" s="3">
+      <c r="F18" s="3">
         <v>830500</v>
       </c>
-      <c r="F18" s="3">
+      <c r="G18" s="3">
         <v>590100</v>
       </c>
-      <c r="G18" s="3">
+      <c r="H18" s="3">
         <v>459500</v>
       </c>
-      <c r="H18" s="3">
+      <c r="I18" s="3">
         <v>909700</v>
       </c>
-      <c r="I18" s="3">
+      <c r="J18" s="3">
         <v>910800</v>
       </c>
-      <c r="J18" s="3">
+      <c r="K18" s="3">
         <v>856000</v>
       </c>
-      <c r="K18" s="3">
+      <c r="L18" s="3">
         <v>104100</v>
       </c>
-      <c r="L18" s="3">
+      <c r="M18" s="3">
         <v>911700</v>
       </c>
-      <c r="M18" s="3">
+      <c r="N18" s="3">
         <v>699100</v>
       </c>
-      <c r="N18" s="3">
+      <c r="O18" s="3">
         <v>960100</v>
       </c>
-      <c r="O18" s="3">
+      <c r="P18" s="3">
         <v>1564300</v>
       </c>
-      <c r="P18" s="3">
+      <c r="Q18" s="3">
         <v>1547000</v>
       </c>
-      <c r="Q18" s="3">
+      <c r="R18" s="3">
         <v>1365800</v>
       </c>
-      <c r="R18" s="3">
+      <c r="S18" s="3">
         <v>1403000</v>
       </c>
-      <c r="S18" s="3">
+      <c r="T18" s="3">
         <v>1253800</v>
       </c>
-      <c r="T18" s="3">
+      <c r="U18" s="3">
         <v>1245400</v>
       </c>
-      <c r="U18" s="3">
+      <c r="V18" s="3">
         <v>1213900</v>
       </c>
-      <c r="V18" s="3">
+      <c r="W18" s="3">
         <v>1096400</v>
       </c>
-      <c r="W18" s="3">
+      <c r="X18" s="3">
         <v>1000300</v>
       </c>
-      <c r="X18" s="3">
+      <c r="Y18" s="3">
         <v>1028700</v>
       </c>
-      <c r="Y18" s="3">
+      <c r="Z18" s="3">
         <v>891200</v>
       </c>
-      <c r="Z18" s="3">
+      <c r="AA18" s="3">
         <v>1102100</v>
       </c>
-      <c r="AA18" s="3">
+      <c r="AB18" s="3">
         <v>1196900</v>
       </c>
-      <c r="AB18" s="3">
+      <c r="AC18" s="3">
         <v>1097100</v>
       </c>
-      <c r="AC18" s="3">
+      <c r="AD18" s="3">
         <v>1241200</v>
       </c>
-      <c r="AD18" s="3">
+      <c r="AE18" s="3">
         <v>1271100</v>
       </c>
-      <c r="AE18" s="3">
+      <c r="AF18" s="3">
         <v>996800</v>
       </c>
-      <c r="AF18" s="3">
+      <c r="AG18" s="3">
         <v>1087400</v>
       </c>
-      <c r="AG18" s="3">
+      <c r="AH18" s="3">
         <v>1237400</v>
       </c>
-      <c r="AH18" s="3">
+      <c r="AI18" s="3">
         <v>1032900</v>
       </c>
-      <c r="AI18" s="3">
+      <c r="AJ18" s="3">
         <v>886500</v>
       </c>
-      <c r="AJ18" s="3">
+      <c r="AK18" s="3">
         <v>998500</v>
       </c>
-      <c r="AK18" s="3">
+      <c r="AL18" s="3">
         <v>946600</v>
       </c>
-      <c r="AL18" s="3">
+      <c r="AM18" s="3">
         <v>1003700</v>
       </c>
-      <c r="AM18" s="3">
+      <c r="AN18" s="3">
         <v>995700</v>
       </c>
-      <c r="AN18" s="3">
+      <c r="AO18" s="3">
         <v>934400</v>
       </c>
     </row>
-    <row r="19" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="19" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C19" s="1" t="s">
         <v>14</v>
       </c>
@@ -1962,240 +1994,247 @@
       <c r="AL19" s="3"/>
       <c r="AM19" s="3"/>
       <c r="AN19" s="3"/>
+      <c r="AO19" s="3"/>
     </row>
-    <row r="20" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="20" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C20" s="1" t="s">
         <v>15</v>
       </c>
       <c r="D20" s="3">
+        <v>-333900</v>
+      </c>
+      <c r="E20" s="3">
         <v>14200</v>
       </c>
-      <c r="E20" s="3">
+      <c r="F20" s="3">
         <v>-69300</v>
       </c>
-      <c r="F20" s="3">
+      <c r="G20" s="3">
         <v>2200</v>
       </c>
-      <c r="G20" s="3">
+      <c r="H20" s="3">
         <v>26000</v>
       </c>
-      <c r="H20" s="3">
+      <c r="I20" s="3">
         <v>-4400</v>
       </c>
-      <c r="I20" s="3">
+      <c r="J20" s="3">
         <v>-2500</v>
       </c>
-      <c r="J20" s="3">
+      <c r="K20" s="3">
         <v>-7500</v>
       </c>
-      <c r="K20" s="3">
+      <c r="L20" s="3">
         <v>11600</v>
       </c>
-      <c r="L20" s="3">
+      <c r="M20" s="3">
         <v>-14500</v>
       </c>
-      <c r="M20" s="3">
+      <c r="N20" s="3">
         <v>32600</v>
       </c>
-      <c r="N20" s="3">
+      <c r="O20" s="3">
         <v>-56500</v>
       </c>
-      <c r="O20" s="3">
+      <c r="P20" s="3">
         <v>-1017300</v>
       </c>
-      <c r="P20" s="3">
+      <c r="Q20" s="3">
         <v>-606600</v>
       </c>
-      <c r="Q20" s="3">
+      <c r="R20" s="3">
         <v>-375600</v>
       </c>
-      <c r="R20" s="3">
+      <c r="S20" s="3">
         <v>-505900</v>
       </c>
-      <c r="S20" s="3">
+      <c r="T20" s="3">
         <v>-806400</v>
       </c>
-      <c r="T20" s="3">
+      <c r="U20" s="3">
         <v>-394200</v>
       </c>
-      <c r="U20" s="3">
+      <c r="V20" s="3">
         <v>-406900</v>
       </c>
-      <c r="V20" s="3">
+      <c r="W20" s="3">
         <v>-399500</v>
       </c>
-      <c r="W20" s="3">
+      <c r="X20" s="3">
         <v>-784600</v>
       </c>
-      <c r="X20" s="3">
+      <c r="Y20" s="3">
         <v>-508200</v>
       </c>
-      <c r="Y20" s="3">
+      <c r="Z20" s="3">
         <v>-674600</v>
       </c>
-      <c r="Z20" s="3">
+      <c r="AA20" s="3">
         <v>-492400</v>
       </c>
-      <c r="AA20" s="3">
+      <c r="AB20" s="3">
         <v>-920900</v>
       </c>
-      <c r="AB20" s="3">
+      <c r="AC20" s="3">
         <v>-527400</v>
       </c>
-      <c r="AC20" s="3">
+      <c r="AD20" s="3">
         <v>-447200</v>
       </c>
-      <c r="AD20" s="3">
+      <c r="AE20" s="3">
         <v>-519600</v>
       </c>
-      <c r="AE20" s="3">
+      <c r="AF20" s="3">
         <v>-847700</v>
       </c>
-      <c r="AF20" s="3">
+      <c r="AG20" s="3">
         <v>-418500</v>
       </c>
-      <c r="AG20" s="3">
+      <c r="AH20" s="3">
         <v>-401200</v>
       </c>
-      <c r="AH20" s="3">
+      <c r="AI20" s="3">
         <v>-355800</v>
       </c>
-      <c r="AI20" s="3">
+      <c r="AJ20" s="3">
         <v>-756300</v>
       </c>
-      <c r="AJ20" s="3">
+      <c r="AK20" s="3">
         <v>-671500</v>
       </c>
-      <c r="AK20" s="3">
+      <c r="AL20" s="3">
         <v>-417500</v>
       </c>
-      <c r="AL20" s="3">
+      <c r="AM20" s="3">
         <v>-274500</v>
       </c>
-      <c r="AM20" s="3">
+      <c r="AN20" s="3">
         <v>-821100</v>
       </c>
-      <c r="AN20" s="3">
+      <c r="AO20" s="3">
         <v>-531000</v>
       </c>
     </row>
-    <row r="21" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="21" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C21" s="1" t="s">
         <v>16</v>
       </c>
       <c r="D21" s="3">
+        <v>1126300</v>
+      </c>
+      <c r="E21" s="3">
         <v>814500</v>
       </c>
-      <c r="E21" s="3">
+      <c r="F21" s="3">
         <v>1012500</v>
       </c>
-      <c r="F21" s="3">
+      <c r="G21" s="3">
         <v>798100</v>
       </c>
-      <c r="G21" s="3">
-        <v>584100</v>
-      </c>
       <c r="H21" s="3">
+        <v>716400</v>
+      </c>
+      <c r="I21" s="3">
         <v>1022700</v>
       </c>
-      <c r="I21" s="3">
+      <c r="J21" s="3">
         <v>919700</v>
       </c>
-      <c r="J21" s="3">
+      <c r="K21" s="3">
         <v>1068900</v>
       </c>
-      <c r="K21" s="3">
+      <c r="L21" s="3">
         <v>236700</v>
       </c>
-      <c r="L21" s="3">
+      <c r="M21" s="3">
         <v>1056800</v>
       </c>
-      <c r="M21" s="3">
+      <c r="N21" s="3">
         <v>796500</v>
       </c>
-      <c r="N21" s="3">
+      <c r="O21" s="3">
         <v>1146700</v>
       </c>
-      <c r="O21" s="3">
+      <c r="P21" s="3">
         <v>732200</v>
       </c>
-      <c r="P21" s="3">
+      <c r="Q21" s="3">
         <v>1110000</v>
       </c>
-      <c r="Q21" s="3">
+      <c r="R21" s="3">
         <v>1165700</v>
       </c>
-      <c r="R21" s="3">
+      <c r="S21" s="3">
         <v>1065700</v>
       </c>
-      <c r="S21" s="3">
+      <c r="T21" s="3">
         <v>603300</v>
       </c>
-      <c r="T21" s="3">
+      <c r="U21" s="3">
         <v>1000500</v>
       </c>
-      <c r="U21" s="3">
+      <c r="V21" s="3">
         <v>991500</v>
       </c>
-      <c r="V21" s="3">
+      <c r="W21" s="3">
         <v>799800</v>
       </c>
-      <c r="W21" s="3">
+      <c r="X21" s="3">
         <v>316900</v>
       </c>
-      <c r="X21" s="3">
+      <c r="Y21" s="3">
         <v>622000</v>
       </c>
-      <c r="Y21" s="3">
+      <c r="Z21" s="3">
         <v>315300</v>
       </c>
-      <c r="Z21" s="3">
+      <c r="AA21" s="3">
         <v>721900</v>
       </c>
-      <c r="AA21" s="3">
+      <c r="AB21" s="3">
         <v>396300</v>
       </c>
-      <c r="AB21" s="3">
+      <c r="AC21" s="3">
         <v>686600</v>
       </c>
-      <c r="AC21" s="3">
+      <c r="AD21" s="3">
         <v>902900</v>
       </c>
-      <c r="AD21" s="3">
+      <c r="AE21" s="3">
         <v>845100</v>
       </c>
-      <c r="AE21" s="3">
+      <c r="AF21" s="3">
         <v>210800</v>
       </c>
-      <c r="AF21" s="3">
+      <c r="AG21" s="3">
         <v>727400</v>
       </c>
-      <c r="AG21" s="3">
+      <c r="AH21" s="3">
         <v>892200</v>
       </c>
-      <c r="AH21" s="3">
+      <c r="AI21" s="3">
         <v>727700</v>
       </c>
-      <c r="AI21" s="3">
+      <c r="AJ21" s="3">
         <v>180100</v>
       </c>
-      <c r="AJ21" s="3">
+      <c r="AK21" s="3">
         <v>377800</v>
       </c>
-      <c r="AK21" s="3">
+      <c r="AL21" s="3">
         <v>580800</v>
       </c>
-      <c r="AL21" s="3">
+      <c r="AM21" s="3">
         <v>784400</v>
       </c>
-      <c r="AM21" s="3">
+      <c r="AN21" s="3">
         <v>229400</v>
       </c>
-      <c r="AN21" s="3">
+      <c r="AO21" s="3">
         <v>457200</v>
       </c>
     </row>
-    <row r="22" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="22" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C22" s="1" t="s">
         <v>17</v>
       </c>
@@ -2232,8 +2271,8 @@
       <c r="N22" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="O22" s="3">
-        <v>0</v>
+      <c r="O22" s="3" t="s">
+        <v>5</v>
       </c>
       <c r="P22" s="3">
         <v>0</v>
@@ -2310,240 +2349,249 @@
       <c r="AN22" s="3">
         <v>0</v>
       </c>
+      <c r="AO22" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="23" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="23" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C23" s="1" t="s">
         <v>18</v>
       </c>
       <c r="D23" s="3">
+        <v>353300</v>
+      </c>
+      <c r="E23" s="3">
         <v>1088400</v>
       </c>
-      <c r="E23" s="3">
+      <c r="F23" s="3">
         <v>876700</v>
       </c>
-      <c r="F23" s="3">
+      <c r="G23" s="3">
         <v>587100</v>
       </c>
-      <c r="G23" s="3">
+      <c r="H23" s="3">
         <v>427300</v>
       </c>
-      <c r="H23" s="3">
+      <c r="I23" s="3">
         <v>914200</v>
       </c>
-      <c r="I23" s="3">
+      <c r="J23" s="3">
         <v>904900</v>
       </c>
-      <c r="J23" s="3">
+      <c r="K23" s="3">
         <v>851200</v>
       </c>
-      <c r="K23" s="3">
+      <c r="L23" s="3">
         <v>94200</v>
       </c>
-      <c r="L23" s="3">
+      <c r="M23" s="3">
         <v>926200</v>
       </c>
-      <c r="M23" s="3">
+      <c r="N23" s="3">
         <v>666800</v>
       </c>
-      <c r="N23" s="3">
+      <c r="O23" s="3">
         <v>974300</v>
       </c>
-      <c r="O23" s="3">
+      <c r="P23" s="3">
         <v>546900</v>
       </c>
-      <c r="P23" s="3">
+      <c r="Q23" s="3">
         <v>940400</v>
       </c>
-      <c r="Q23" s="3">
+      <c r="R23" s="3">
         <v>990200</v>
       </c>
-      <c r="R23" s="3">
+      <c r="S23" s="3">
         <v>897100</v>
       </c>
-      <c r="S23" s="3">
+      <c r="T23" s="3">
         <v>447400</v>
       </c>
-      <c r="T23" s="3">
+      <c r="U23" s="3">
         <v>851200</v>
       </c>
-      <c r="U23" s="3">
+      <c r="V23" s="3">
         <v>807000</v>
       </c>
-      <c r="V23" s="3">
+      <c r="W23" s="3">
         <v>696900</v>
       </c>
-      <c r="W23" s="3">
+      <c r="X23" s="3">
         <v>215700</v>
       </c>
-      <c r="X23" s="3">
+      <c r="Y23" s="3">
         <v>520500</v>
       </c>
-      <c r="Y23" s="3">
+      <c r="Z23" s="3">
         <v>216600</v>
       </c>
-      <c r="Z23" s="3">
+      <c r="AA23" s="3">
         <v>609600</v>
       </c>
-      <c r="AA23" s="3">
+      <c r="AB23" s="3">
         <v>276000</v>
       </c>
-      <c r="AB23" s="3">
+      <c r="AC23" s="3">
         <v>569700</v>
       </c>
-      <c r="AC23" s="3">
+      <c r="AD23" s="3">
         <v>794000</v>
       </c>
-      <c r="AD23" s="3">
+      <c r="AE23" s="3">
         <v>751500</v>
       </c>
-      <c r="AE23" s="3">
+      <c r="AF23" s="3">
         <v>149100</v>
       </c>
-      <c r="AF23" s="3">
+      <c r="AG23" s="3">
         <v>668900</v>
       </c>
-      <c r="AG23" s="3">
+      <c r="AH23" s="3">
         <v>836200</v>
       </c>
-      <c r="AH23" s="3">
+      <c r="AI23" s="3">
         <v>677100</v>
       </c>
-      <c r="AI23" s="3">
+      <c r="AJ23" s="3">
         <v>130200</v>
       </c>
-      <c r="AJ23" s="3">
+      <c r="AK23" s="3">
         <v>327000</v>
       </c>
-      <c r="AK23" s="3">
+      <c r="AL23" s="3">
         <v>529200</v>
       </c>
-      <c r="AL23" s="3">
+      <c r="AM23" s="3">
         <v>729200</v>
       </c>
-      <c r="AM23" s="3">
+      <c r="AN23" s="3">
         <v>174600</v>
       </c>
-      <c r="AN23" s="3">
+      <c r="AO23" s="3">
         <v>403400</v>
       </c>
     </row>
-    <row r="24" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="24" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C24" s="1" t="s">
         <v>19</v>
       </c>
       <c r="D24" s="3">
+        <v>116600</v>
+      </c>
+      <c r="E24" s="3">
         <v>169100</v>
       </c>
-      <c r="E24" s="3">
+      <c r="F24" s="3">
         <v>182300</v>
       </c>
-      <c r="F24" s="3">
+      <c r="G24" s="3">
         <v>142600</v>
       </c>
-      <c r="G24" s="3">
+      <c r="H24" s="3">
         <v>120000</v>
       </c>
-      <c r="H24" s="3">
+      <c r="I24" s="3">
         <v>216000</v>
       </c>
-      <c r="I24" s="3">
+      <c r="J24" s="3">
         <v>207100</v>
       </c>
-      <c r="J24" s="3">
+      <c r="K24" s="3">
         <v>227000</v>
       </c>
-      <c r="K24" s="3">
+      <c r="L24" s="3">
         <v>21000</v>
       </c>
-      <c r="L24" s="3">
+      <c r="M24" s="3">
         <v>244100</v>
       </c>
-      <c r="M24" s="3">
+      <c r="N24" s="3">
         <v>160200</v>
       </c>
-      <c r="N24" s="3">
+      <c r="O24" s="3">
         <v>248300</v>
       </c>
-      <c r="O24" s="3">
+      <c r="P24" s="3">
         <v>148500</v>
       </c>
-      <c r="P24" s="3">
+      <c r="Q24" s="3">
         <v>259000</v>
       </c>
-      <c r="Q24" s="3">
+      <c r="R24" s="3">
         <v>240200</v>
       </c>
-      <c r="R24" s="3">
+      <c r="S24" s="3">
         <v>225300</v>
       </c>
-      <c r="S24" s="3">
+      <c r="T24" s="3">
         <v>113100</v>
       </c>
-      <c r="T24" s="3">
+      <c r="U24" s="3">
         <v>232900</v>
       </c>
-      <c r="U24" s="3">
+      <c r="V24" s="3">
         <v>193200</v>
       </c>
-      <c r="V24" s="3">
+      <c r="W24" s="3">
         <v>164900</v>
       </c>
-      <c r="W24" s="3">
+      <c r="X24" s="3">
         <v>53200</v>
       </c>
-      <c r="X24" s="3">
+      <c r="Y24" s="3">
         <v>118800</v>
       </c>
-      <c r="Y24" s="3">
+      <c r="Z24" s="3">
         <v>50000</v>
       </c>
-      <c r="Z24" s="3">
+      <c r="AA24" s="3">
         <v>157800</v>
       </c>
-      <c r="AA24" s="3">
+      <c r="AB24" s="3">
         <v>79200</v>
       </c>
-      <c r="AB24" s="3">
+      <c r="AC24" s="3">
         <v>115700</v>
       </c>
-      <c r="AC24" s="3">
+      <c r="AD24" s="3">
         <v>215500</v>
       </c>
-      <c r="AD24" s="3">
+      <c r="AE24" s="3">
         <v>192300</v>
       </c>
-      <c r="AE24" s="3">
+      <c r="AF24" s="3">
         <v>39300</v>
       </c>
-      <c r="AF24" s="3">
+      <c r="AG24" s="3">
         <v>179200</v>
       </c>
-      <c r="AG24" s="3">
+      <c r="AH24" s="3">
         <v>229900</v>
       </c>
-      <c r="AH24" s="3">
+      <c r="AI24" s="3">
         <v>177700</v>
       </c>
-      <c r="AI24" s="3">
+      <c r="AJ24" s="3">
         <v>9000</v>
       </c>
-      <c r="AJ24" s="3">
+      <c r="AK24" s="3">
         <v>77600</v>
       </c>
-      <c r="AK24" s="3">
+      <c r="AL24" s="3">
         <v>118800</v>
       </c>
-      <c r="AL24" s="3">
+      <c r="AM24" s="3">
         <v>163600</v>
       </c>
-      <c r="AM24" s="3">
+      <c r="AN24" s="3">
         <v>30300</v>
       </c>
-      <c r="AN24" s="3">
+      <c r="AO24" s="3">
         <v>80000</v>
       </c>
     </row>
-    <row r="25" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="25" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C25" s="1" t="s">
         <v>20</v>
       </c>
@@ -2658,240 +2706,249 @@
       <c r="AN25" s="3">
         <v>0</v>
       </c>
+      <c r="AO25" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="26" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="26" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C26" s="1" t="s">
         <v>21</v>
       </c>
       <c r="D26" s="3">
+        <v>236700</v>
+      </c>
+      <c r="E26" s="3">
         <v>919400</v>
       </c>
-      <c r="E26" s="3">
+      <c r="F26" s="3">
         <v>694400</v>
       </c>
-      <c r="F26" s="3">
+      <c r="G26" s="3">
         <v>444500</v>
       </c>
-      <c r="G26" s="3">
+      <c r="H26" s="3">
         <v>307400</v>
       </c>
-      <c r="H26" s="3">
+      <c r="I26" s="3">
         <v>698200</v>
       </c>
-      <c r="I26" s="3">
+      <c r="J26" s="3">
         <v>697800</v>
       </c>
-      <c r="J26" s="3">
+      <c r="K26" s="3">
         <v>624200</v>
       </c>
-      <c r="K26" s="3">
+      <c r="L26" s="3">
         <v>73200</v>
       </c>
-      <c r="L26" s="3">
+      <c r="M26" s="3">
         <v>682000</v>
       </c>
-      <c r="M26" s="3">
+      <c r="N26" s="3">
         <v>506600</v>
       </c>
-      <c r="N26" s="3">
+      <c r="O26" s="3">
         <v>726000</v>
       </c>
-      <c r="O26" s="3">
+      <c r="P26" s="3">
         <v>398500</v>
       </c>
-      <c r="P26" s="3">
+      <c r="Q26" s="3">
         <v>681400</v>
       </c>
-      <c r="Q26" s="3">
+      <c r="R26" s="3">
         <v>750000</v>
       </c>
-      <c r="R26" s="3">
+      <c r="S26" s="3">
         <v>671800</v>
       </c>
-      <c r="S26" s="3">
+      <c r="T26" s="3">
         <v>334300</v>
       </c>
-      <c r="T26" s="3">
+      <c r="U26" s="3">
         <v>618300</v>
       </c>
-      <c r="U26" s="3">
+      <c r="V26" s="3">
         <v>613800</v>
       </c>
-      <c r="V26" s="3">
+      <c r="W26" s="3">
         <v>532000</v>
       </c>
-      <c r="W26" s="3">
+      <c r="X26" s="3">
         <v>162400</v>
       </c>
-      <c r="X26" s="3">
+      <c r="Y26" s="3">
         <v>401700</v>
       </c>
-      <c r="Y26" s="3">
+      <c r="Z26" s="3">
         <v>166500</v>
       </c>
-      <c r="Z26" s="3">
+      <c r="AA26" s="3">
         <v>451800</v>
       </c>
-      <c r="AA26" s="3">
+      <c r="AB26" s="3">
         <v>196800</v>
       </c>
-      <c r="AB26" s="3">
+      <c r="AC26" s="3">
         <v>454000</v>
       </c>
-      <c r="AC26" s="3">
+      <c r="AD26" s="3">
         <v>578500</v>
       </c>
-      <c r="AD26" s="3">
+      <c r="AE26" s="3">
         <v>559200</v>
       </c>
-      <c r="AE26" s="3">
+      <c r="AF26" s="3">
         <v>109900</v>
       </c>
-      <c r="AF26" s="3">
+      <c r="AG26" s="3">
         <v>489700</v>
       </c>
-      <c r="AG26" s="3">
+      <c r="AH26" s="3">
         <v>606300</v>
       </c>
-      <c r="AH26" s="3">
+      <c r="AI26" s="3">
         <v>499400</v>
       </c>
-      <c r="AI26" s="3">
+      <c r="AJ26" s="3">
         <v>121100</v>
       </c>
-      <c r="AJ26" s="3">
+      <c r="AK26" s="3">
         <v>249400</v>
       </c>
-      <c r="AK26" s="3">
+      <c r="AL26" s="3">
         <v>410300</v>
       </c>
-      <c r="AL26" s="3">
+      <c r="AM26" s="3">
         <v>565600</v>
       </c>
-      <c r="AM26" s="3">
+      <c r="AN26" s="3">
         <v>144300</v>
       </c>
-      <c r="AN26" s="3">
+      <c r="AO26" s="3">
         <v>323500</v>
       </c>
     </row>
-    <row r="27" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="27" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C27" s="1" t="s">
         <v>22</v>
       </c>
       <c r="D27" s="3">
+        <v>201700</v>
+      </c>
+      <c r="E27" s="3">
         <v>859000</v>
       </c>
-      <c r="E27" s="3">
+      <c r="F27" s="3">
         <v>664400</v>
       </c>
-      <c r="F27" s="3">
+      <c r="G27" s="3">
         <v>391900</v>
       </c>
-      <c r="G27" s="3">
+      <c r="H27" s="3">
         <v>261600</v>
       </c>
-      <c r="H27" s="3">
+      <c r="I27" s="3">
         <v>655100</v>
       </c>
-      <c r="I27" s="3">
+      <c r="J27" s="3">
         <v>647100</v>
       </c>
-      <c r="J27" s="3">
+      <c r="K27" s="3">
         <v>586900</v>
       </c>
-      <c r="K27" s="3">
+      <c r="L27" s="3">
         <v>25300</v>
       </c>
-      <c r="L27" s="3">
+      <c r="M27" s="3">
         <v>643700</v>
       </c>
-      <c r="M27" s="3">
+      <c r="N27" s="3">
         <v>449800</v>
       </c>
-      <c r="N27" s="3">
+      <c r="O27" s="3">
         <v>677400</v>
       </c>
-      <c r="O27" s="3">
+      <c r="P27" s="3">
         <v>338800</v>
       </c>
-      <c r="P27" s="3">
+      <c r="Q27" s="3">
         <v>640600</v>
       </c>
-      <c r="Q27" s="3">
+      <c r="R27" s="3">
         <v>684400</v>
       </c>
-      <c r="R27" s="3">
+      <c r="S27" s="3">
         <v>631400</v>
       </c>
-      <c r="S27" s="3">
+      <c r="T27" s="3">
         <v>279500</v>
       </c>
-      <c r="T27" s="3">
+      <c r="U27" s="3">
         <v>570700</v>
       </c>
-      <c r="U27" s="3">
+      <c r="V27" s="3">
         <v>552600</v>
       </c>
-      <c r="V27" s="3">
+      <c r="W27" s="3">
         <v>482000</v>
       </c>
-      <c r="W27" s="3">
+      <c r="X27" s="3">
         <v>112600</v>
       </c>
-      <c r="X27" s="3">
+      <c r="Y27" s="3">
         <v>358800</v>
       </c>
-      <c r="Y27" s="3">
+      <c r="Z27" s="3">
         <v>100500</v>
       </c>
-      <c r="Z27" s="3">
+      <c r="AA27" s="3">
         <v>412900</v>
       </c>
-      <c r="AA27" s="3">
+      <c r="AB27" s="3">
         <v>174900</v>
       </c>
-      <c r="AB27" s="3">
+      <c r="AC27" s="3">
         <v>410100</v>
       </c>
-      <c r="AC27" s="3">
+      <c r="AD27" s="3">
         <v>537700</v>
       </c>
-      <c r="AD27" s="3">
+      <c r="AE27" s="3">
         <v>517500</v>
       </c>
-      <c r="AE27" s="3">
+      <c r="AF27" s="3">
         <v>76800</v>
       </c>
-      <c r="AF27" s="3">
+      <c r="AG27" s="3">
         <v>453900</v>
       </c>
-      <c r="AG27" s="3">
+      <c r="AH27" s="3">
         <v>569900</v>
       </c>
-      <c r="AH27" s="3">
+      <c r="AI27" s="3">
         <v>463600</v>
       </c>
-      <c r="AI27" s="3">
+      <c r="AJ27" s="3">
         <v>84900</v>
       </c>
-      <c r="AJ27" s="3">
+      <c r="AK27" s="3">
         <v>212100</v>
       </c>
-      <c r="AK27" s="3">
+      <c r="AL27" s="3">
         <v>369000</v>
       </c>
-      <c r="AL27" s="3">
+      <c r="AM27" s="3">
         <v>517600</v>
       </c>
-      <c r="AM27" s="3">
+      <c r="AN27" s="3">
         <v>88500</v>
       </c>
-      <c r="AN27" s="3">
+      <c r="AO27" s="3">
         <v>275700</v>
       </c>
     </row>
-    <row r="28" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="28" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C28" s="1" t="s">
         <v>23</v>
       </c>
@@ -3006,8 +3063,11 @@
       <c r="AN28" s="3">
         <v>0</v>
       </c>
+      <c r="AO28" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="29" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="29" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C29" s="1" t="s">
         <v>24</v>
       </c>
@@ -3122,8 +3182,11 @@
       <c r="AN29" s="3">
         <v>0</v>
       </c>
+      <c r="AO29" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="30" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="30" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C30" s="1" t="s">
         <v>25</v>
       </c>
@@ -3238,8 +3301,11 @@
       <c r="AN30" s="3">
         <v>0</v>
       </c>
+      <c r="AO30" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="31" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="31" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C31" s="1" t="s">
         <v>26</v>
       </c>
@@ -3354,240 +3420,249 @@
       <c r="AN31" s="3">
         <v>0</v>
       </c>
+      <c r="AO31" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="32" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="32" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C32" s="1" t="s">
         <v>27</v>
       </c>
       <c r="D32" s="3">
+        <v>333900</v>
+      </c>
+      <c r="E32" s="3">
         <v>-14200</v>
       </c>
-      <c r="E32" s="3">
+      <c r="F32" s="3">
         <v>69300</v>
       </c>
-      <c r="F32" s="3">
+      <c r="G32" s="3">
         <v>-2200</v>
       </c>
-      <c r="G32" s="3">
+      <c r="H32" s="3">
         <v>-26000</v>
       </c>
-      <c r="H32" s="3">
+      <c r="I32" s="3">
         <v>4400</v>
       </c>
-      <c r="I32" s="3">
+      <c r="J32" s="3">
         <v>2500</v>
       </c>
-      <c r="J32" s="3">
+      <c r="K32" s="3">
         <v>7500</v>
       </c>
-      <c r="K32" s="3">
+      <c r="L32" s="3">
         <v>-11600</v>
       </c>
-      <c r="L32" s="3">
+      <c r="M32" s="3">
         <v>14500</v>
       </c>
-      <c r="M32" s="3">
+      <c r="N32" s="3">
         <v>-32600</v>
       </c>
-      <c r="N32" s="3">
+      <c r="O32" s="3">
         <v>56500</v>
       </c>
-      <c r="O32" s="3">
+      <c r="P32" s="3">
         <v>1017300</v>
       </c>
-      <c r="P32" s="3">
+      <c r="Q32" s="3">
         <v>606600</v>
       </c>
-      <c r="Q32" s="3">
+      <c r="R32" s="3">
         <v>375600</v>
       </c>
-      <c r="R32" s="3">
+      <c r="S32" s="3">
         <v>505900</v>
       </c>
-      <c r="S32" s="3">
+      <c r="T32" s="3">
         <v>806400</v>
       </c>
-      <c r="T32" s="3">
+      <c r="U32" s="3">
         <v>394200</v>
       </c>
-      <c r="U32" s="3">
+      <c r="V32" s="3">
         <v>406900</v>
       </c>
-      <c r="V32" s="3">
+      <c r="W32" s="3">
         <v>399500</v>
       </c>
-      <c r="W32" s="3">
+      <c r="X32" s="3">
         <v>784600</v>
       </c>
-      <c r="X32" s="3">
+      <c r="Y32" s="3">
         <v>508200</v>
       </c>
-      <c r="Y32" s="3">
+      <c r="Z32" s="3">
         <v>674600</v>
       </c>
-      <c r="Z32" s="3">
+      <c r="AA32" s="3">
         <v>492400</v>
       </c>
-      <c r="AA32" s="3">
+      <c r="AB32" s="3">
         <v>920900</v>
       </c>
-      <c r="AB32" s="3">
+      <c r="AC32" s="3">
         <v>527400</v>
       </c>
-      <c r="AC32" s="3">
+      <c r="AD32" s="3">
         <v>447200</v>
       </c>
-      <c r="AD32" s="3">
+      <c r="AE32" s="3">
         <v>519600</v>
       </c>
-      <c r="AE32" s="3">
+      <c r="AF32" s="3">
         <v>847700</v>
       </c>
-      <c r="AF32" s="3">
+      <c r="AG32" s="3">
         <v>418500</v>
       </c>
-      <c r="AG32" s="3">
+      <c r="AH32" s="3">
         <v>401200</v>
       </c>
-      <c r="AH32" s="3">
+      <c r="AI32" s="3">
         <v>355800</v>
       </c>
-      <c r="AI32" s="3">
+      <c r="AJ32" s="3">
         <v>756300</v>
       </c>
-      <c r="AJ32" s="3">
+      <c r="AK32" s="3">
         <v>671500</v>
       </c>
-      <c r="AK32" s="3">
+      <c r="AL32" s="3">
         <v>417500</v>
       </c>
-      <c r="AL32" s="3">
+      <c r="AM32" s="3">
         <v>274500</v>
       </c>
-      <c r="AM32" s="3">
+      <c r="AN32" s="3">
         <v>821100</v>
       </c>
-      <c r="AN32" s="3">
+      <c r="AO32" s="3">
         <v>531000</v>
       </c>
     </row>
-    <row r="33" spans="2:40" x14ac:dyDescent="0.2">
+    <row r="33" spans="2:41" x14ac:dyDescent="0.2">
       <c r="C33" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D33" s="3">
+        <v>227500</v>
+      </c>
+      <c r="E33" s="3">
         <v>885500</v>
       </c>
-      <c r="E33" s="3">
+      <c r="F33" s="3">
         <v>691100</v>
       </c>
-      <c r="F33" s="3">
+      <c r="G33" s="3">
         <v>418800</v>
       </c>
-      <c r="G33" s="3">
+      <c r="H33" s="3">
         <v>288500</v>
       </c>
-      <c r="H33" s="3">
+      <c r="I33" s="3">
         <v>688600</v>
       </c>
-      <c r="I33" s="3">
+      <c r="J33" s="3">
         <v>676000</v>
       </c>
-      <c r="J33" s="3">
+      <c r="K33" s="3">
         <v>613100</v>
       </c>
-      <c r="K33" s="3">
+      <c r="L33" s="3">
         <v>52500</v>
       </c>
-      <c r="L33" s="3">
+      <c r="M33" s="3">
         <v>668000</v>
       </c>
-      <c r="M33" s="3">
+      <c r="N33" s="3">
         <v>474700</v>
       </c>
-      <c r="N33" s="3">
+      <c r="O33" s="3">
         <v>700700</v>
       </c>
-      <c r="O33" s="3">
+      <c r="P33" s="3">
         <v>338800</v>
       </c>
-      <c r="P33" s="3">
+      <c r="Q33" s="3">
         <v>640600</v>
       </c>
-      <c r="Q33" s="3">
+      <c r="R33" s="3">
         <v>684400</v>
       </c>
-      <c r="R33" s="3">
+      <c r="S33" s="3">
         <v>631400</v>
       </c>
-      <c r="S33" s="3">
+      <c r="T33" s="3">
         <v>279500</v>
       </c>
-      <c r="T33" s="3">
+      <c r="U33" s="3">
         <v>570700</v>
       </c>
-      <c r="U33" s="3">
+      <c r="V33" s="3">
         <v>552600</v>
       </c>
-      <c r="V33" s="3">
+      <c r="W33" s="3">
         <v>482000</v>
       </c>
-      <c r="W33" s="3">
+      <c r="X33" s="3">
         <v>112600</v>
       </c>
-      <c r="X33" s="3">
+      <c r="Y33" s="3">
         <v>358800</v>
       </c>
-      <c r="Y33" s="3">
+      <c r="Z33" s="3">
         <v>100500</v>
       </c>
-      <c r="Z33" s="3">
+      <c r="AA33" s="3">
         <v>412900</v>
       </c>
-      <c r="AA33" s="3">
+      <c r="AB33" s="3">
         <v>174900</v>
       </c>
-      <c r="AB33" s="3">
+      <c r="AC33" s="3">
         <v>410100</v>
       </c>
-      <c r="AC33" s="3">
+      <c r="AD33" s="3">
         <v>537700</v>
       </c>
-      <c r="AD33" s="3">
+      <c r="AE33" s="3">
         <v>517500</v>
       </c>
-      <c r="AE33" s="3">
+      <c r="AF33" s="3">
         <v>76800</v>
       </c>
-      <c r="AF33" s="3">
+      <c r="AG33" s="3">
         <v>453900</v>
       </c>
-      <c r="AG33" s="3">
+      <c r="AH33" s="3">
         <v>569900</v>
       </c>
-      <c r="AH33" s="3">
+      <c r="AI33" s="3">
         <v>463600</v>
       </c>
-      <c r="AI33" s="3">
+      <c r="AJ33" s="3">
         <v>84900</v>
       </c>
-      <c r="AJ33" s="3">
+      <c r="AK33" s="3">
         <v>212100</v>
       </c>
-      <c r="AK33" s="3">
+      <c r="AL33" s="3">
         <v>369000</v>
       </c>
-      <c r="AL33" s="3">
+      <c r="AM33" s="3">
         <v>517600</v>
       </c>
-      <c r="AM33" s="3">
+      <c r="AN33" s="3">
         <v>88500</v>
       </c>
-      <c r="AN33" s="3">
+      <c r="AO33" s="3">
         <v>275700</v>
       </c>
     </row>
-    <row r="34" spans="2:40" x14ac:dyDescent="0.2">
+    <row r="34" spans="2:41" x14ac:dyDescent="0.2">
       <c r="C34" s="1" t="s">
         <v>29</v>
       </c>
@@ -3702,245 +3777,254 @@
       <c r="AN34" s="3">
         <v>0</v>
       </c>
+      <c r="AO34" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="35" spans="2:40" x14ac:dyDescent="0.2">
+    <row r="35" spans="2:41" x14ac:dyDescent="0.2">
       <c r="C35" s="1" t="s">
         <v>30</v>
       </c>
       <c r="D35" s="3">
+        <v>227500</v>
+      </c>
+      <c r="E35" s="3">
         <v>885500</v>
       </c>
-      <c r="E35" s="3">
+      <c r="F35" s="3">
         <v>691100</v>
       </c>
-      <c r="F35" s="3">
+      <c r="G35" s="3">
         <v>418800</v>
       </c>
-      <c r="G35" s="3">
+      <c r="H35" s="3">
         <v>288500</v>
       </c>
-      <c r="H35" s="3">
+      <c r="I35" s="3">
         <v>688600</v>
       </c>
-      <c r="I35" s="3">
+      <c r="J35" s="3">
         <v>676000</v>
       </c>
-      <c r="J35" s="3">
+      <c r="K35" s="3">
         <v>613100</v>
       </c>
-      <c r="K35" s="3">
+      <c r="L35" s="3">
         <v>52500</v>
       </c>
-      <c r="L35" s="3">
+      <c r="M35" s="3">
         <v>668000</v>
       </c>
-      <c r="M35" s="3">
+      <c r="N35" s="3">
         <v>474700</v>
       </c>
-      <c r="N35" s="3">
+      <c r="O35" s="3">
         <v>700700</v>
       </c>
-      <c r="O35" s="3">
+      <c r="P35" s="3">
         <v>338800</v>
       </c>
-      <c r="P35" s="3">
+      <c r="Q35" s="3">
         <v>640600</v>
       </c>
-      <c r="Q35" s="3">
+      <c r="R35" s="3">
         <v>684400</v>
       </c>
-      <c r="R35" s="3">
+      <c r="S35" s="3">
         <v>631400</v>
       </c>
-      <c r="S35" s="3">
+      <c r="T35" s="3">
         <v>279500</v>
       </c>
-      <c r="T35" s="3">
+      <c r="U35" s="3">
         <v>570700</v>
       </c>
-      <c r="U35" s="3">
+      <c r="V35" s="3">
         <v>552600</v>
       </c>
-      <c r="V35" s="3">
+      <c r="W35" s="3">
         <v>482000</v>
       </c>
-      <c r="W35" s="3">
+      <c r="X35" s="3">
         <v>112600</v>
       </c>
-      <c r="X35" s="3">
+      <c r="Y35" s="3">
         <v>358800</v>
       </c>
-      <c r="Y35" s="3">
+      <c r="Z35" s="3">
         <v>100500</v>
       </c>
-      <c r="Z35" s="3">
+      <c r="AA35" s="3">
         <v>412900</v>
       </c>
-      <c r="AA35" s="3">
+      <c r="AB35" s="3">
         <v>174900</v>
       </c>
-      <c r="AB35" s="3">
+      <c r="AC35" s="3">
         <v>410100</v>
       </c>
-      <c r="AC35" s="3">
+      <c r="AD35" s="3">
         <v>537700</v>
       </c>
-      <c r="AD35" s="3">
+      <c r="AE35" s="3">
         <v>517500</v>
       </c>
-      <c r="AE35" s="3">
+      <c r="AF35" s="3">
         <v>76800</v>
       </c>
-      <c r="AF35" s="3">
+      <c r="AG35" s="3">
         <v>453900</v>
       </c>
-      <c r="AG35" s="3">
+      <c r="AH35" s="3">
         <v>569900</v>
       </c>
-      <c r="AH35" s="3">
+      <c r="AI35" s="3">
         <v>463600</v>
       </c>
-      <c r="AI35" s="3">
+      <c r="AJ35" s="3">
         <v>84900</v>
       </c>
-      <c r="AJ35" s="3">
+      <c r="AK35" s="3">
         <v>212100</v>
       </c>
-      <c r="AK35" s="3">
+      <c r="AL35" s="3">
         <v>369000</v>
       </c>
-      <c r="AL35" s="3">
+      <c r="AM35" s="3">
         <v>517600</v>
       </c>
-      <c r="AM35" s="3">
+      <c r="AN35" s="3">
         <v>88500</v>
       </c>
-      <c r="AN35" s="3">
+      <c r="AO35" s="3">
         <v>275700</v>
       </c>
     </row>
-    <row r="37" spans="2:40" x14ac:dyDescent="0.2">
+    <row r="37" spans="2:41" x14ac:dyDescent="0.2">
       <c r="B37" s="1" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="38" spans="2:40" x14ac:dyDescent="0.2">
+    <row r="38" spans="2:41" x14ac:dyDescent="0.2">
       <c r="C38" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D38" s="2">
+        <v>46022</v>
+      </c>
+      <c r="E38" s="2">
         <v>45930</v>
       </c>
-      <c r="E38" s="2">
+      <c r="F38" s="2">
         <v>45838</v>
       </c>
-      <c r="F38" s="2">
+      <c r="G38" s="2">
         <v>45747</v>
       </c>
-      <c r="G38" s="2">
+      <c r="H38" s="2">
         <v>45657</v>
       </c>
-      <c r="H38" s="2">
+      <c r="I38" s="2">
         <v>45565</v>
       </c>
-      <c r="I38" s="2">
+      <c r="J38" s="2">
         <v>45473</v>
       </c>
-      <c r="J38" s="2">
+      <c r="K38" s="2">
         <v>45382</v>
       </c>
-      <c r="K38" s="2">
+      <c r="L38" s="2">
         <v>45291</v>
       </c>
-      <c r="L38" s="2">
+      <c r="M38" s="2">
         <v>45199</v>
       </c>
-      <c r="M38" s="2">
+      <c r="N38" s="2">
         <v>45107</v>
       </c>
-      <c r="N38" s="2">
+      <c r="O38" s="2">
         <v>45016</v>
       </c>
-      <c r="O38" s="2">
+      <c r="P38" s="2">
         <v>44926</v>
       </c>
-      <c r="P38" s="2">
+      <c r="Q38" s="2">
         <v>44834</v>
       </c>
-      <c r="Q38" s="2">
+      <c r="R38" s="2">
         <v>44742</v>
       </c>
-      <c r="R38" s="2">
+      <c r="S38" s="2">
         <v>44651</v>
       </c>
-      <c r="S38" s="2">
+      <c r="T38" s="2">
         <v>44561</v>
       </c>
-      <c r="T38" s="2">
+      <c r="U38" s="2">
         <v>44469</v>
       </c>
-      <c r="U38" s="2">
+      <c r="V38" s="2">
         <v>44377</v>
       </c>
-      <c r="V38" s="2">
+      <c r="W38" s="2">
         <v>44286</v>
       </c>
-      <c r="W38" s="2">
+      <c r="X38" s="2">
         <v>44196</v>
       </c>
-      <c r="X38" s="2">
+      <c r="Y38" s="2">
         <v>44104</v>
       </c>
-      <c r="Y38" s="2">
+      <c r="Z38" s="2">
         <v>44012</v>
       </c>
-      <c r="Z38" s="2">
+      <c r="AA38" s="2">
         <v>43921</v>
       </c>
-      <c r="AA38" s="2">
+      <c r="AB38" s="2">
         <v>43830</v>
       </c>
-      <c r="AB38" s="2">
+      <c r="AC38" s="2">
         <v>43738</v>
       </c>
-      <c r="AC38" s="2">
+      <c r="AD38" s="2">
         <v>43646</v>
       </c>
-      <c r="AD38" s="2">
+      <c r="AE38" s="2">
         <v>43555</v>
       </c>
-      <c r="AE38" s="2">
+      <c r="AF38" s="2">
         <v>43465</v>
       </c>
-      <c r="AF38" s="2">
+      <c r="AG38" s="2">
         <v>43373</v>
       </c>
-      <c r="AG38" s="2">
+      <c r="AH38" s="2">
         <v>43281</v>
       </c>
-      <c r="AH38" s="2">
+      <c r="AI38" s="2">
         <v>43190</v>
       </c>
-      <c r="AI38" s="2">
+      <c r="AJ38" s="2">
         <v>43100</v>
       </c>
-      <c r="AJ38" s="2">
+      <c r="AK38" s="2">
         <v>43008</v>
       </c>
-      <c r="AK38" s="2">
+      <c r="AL38" s="2">
         <v>42916</v>
       </c>
-      <c r="AL38" s="2">
+      <c r="AM38" s="2">
         <v>42825</v>
       </c>
-      <c r="AM38" s="2">
+      <c r="AN38" s="2">
         <v>42735</v>
       </c>
-      <c r="AN38" s="2">
+      <c r="AO38" s="2">
         <v>42643</v>
       </c>
     </row>
-    <row r="39" spans="2:40" x14ac:dyDescent="0.2">
+    <row r="39" spans="2:41" x14ac:dyDescent="0.2">
       <c r="C39" s="1" t="s">
         <v>32</v>
       </c>
@@ -3981,8 +4065,9 @@
       <c r="AL39" s="3"/>
       <c r="AM39" s="3"/>
       <c r="AN39" s="3"/>
+      <c r="AO39" s="3"/>
     </row>
-    <row r="40" spans="2:40" x14ac:dyDescent="0.2">
+    <row r="40" spans="2:41" x14ac:dyDescent="0.2">
       <c r="C40" s="1" t="s">
         <v>33</v>
       </c>
@@ -4023,279 +4108,286 @@
       <c r="AL40" s="3"/>
       <c r="AM40" s="3"/>
       <c r="AN40" s="3"/>
+      <c r="AO40" s="3"/>
     </row>
-    <row r="41" spans="2:40" x14ac:dyDescent="0.2">
+    <row r="41" spans="2:41" x14ac:dyDescent="0.2">
       <c r="C41" s="1" t="s">
         <v>34</v>
       </c>
       <c r="D41" s="3">
+        <v>10408300</v>
+      </c>
+      <c r="E41" s="3">
         <v>10043000</v>
       </c>
-      <c r="E41" s="3">
+      <c r="F41" s="3">
         <v>9721700</v>
       </c>
-      <c r="F41" s="3">
+      <c r="G41" s="3">
         <v>9800400</v>
       </c>
-      <c r="G41" s="3">
+      <c r="H41" s="3">
         <v>9892700</v>
       </c>
-      <c r="H41" s="3">
+      <c r="I41" s="3">
         <v>13834100</v>
       </c>
-      <c r="I41" s="3">
+      <c r="J41" s="3">
         <v>8534800</v>
       </c>
-      <c r="J41" s="3">
+      <c r="K41" s="3">
         <v>13129900</v>
       </c>
-      <c r="K41" s="3">
+      <c r="L41" s="3">
         <v>12476200</v>
       </c>
-      <c r="L41" s="3">
+      <c r="M41" s="3">
         <v>7157900</v>
       </c>
-      <c r="M41" s="3">
+      <c r="N41" s="3">
         <v>9809900</v>
       </c>
-      <c r="N41" s="3">
+      <c r="O41" s="3">
         <v>10234100</v>
       </c>
-      <c r="O41" s="3">
+      <c r="P41" s="3">
         <v>25596900</v>
       </c>
-      <c r="P41" s="3">
+      <c r="Q41" s="3">
         <v>6507700</v>
       </c>
-      <c r="Q41" s="3">
+      <c r="R41" s="3">
         <v>7377100</v>
       </c>
-      <c r="R41" s="3">
+      <c r="S41" s="3">
         <v>9785500</v>
       </c>
-      <c r="S41" s="3">
+      <c r="T41" s="3">
         <v>5555400</v>
       </c>
-      <c r="T41" s="3">
+      <c r="U41" s="3">
         <v>7893500</v>
       </c>
-      <c r="U41" s="3">
+      <c r="V41" s="3">
         <v>7303900</v>
       </c>
-      <c r="V41" s="3">
+      <c r="W41" s="3">
         <v>7996900</v>
       </c>
-      <c r="W41" s="3">
+      <c r="X41" s="3">
         <v>6985700</v>
       </c>
-      <c r="X41" s="3">
+      <c r="Y41" s="3">
         <v>6452400</v>
       </c>
-      <c r="Y41" s="3">
+      <c r="Z41" s="3">
         <v>6934700</v>
       </c>
-      <c r="Z41" s="3">
+      <c r="AA41" s="3">
         <v>7810800</v>
       </c>
-      <c r="AA41" s="3">
+      <c r="AB41" s="3">
         <v>5327800</v>
       </c>
-      <c r="AB41" s="3">
+      <c r="AC41" s="3">
         <v>7069900</v>
       </c>
-      <c r="AC41" s="3">
+      <c r="AD41" s="3">
         <v>5777500</v>
       </c>
-      <c r="AD41" s="3">
+      <c r="AE41" s="3">
         <v>4361000</v>
       </c>
-      <c r="AE41" s="3">
+      <c r="AF41" s="3">
         <v>5329900</v>
       </c>
-      <c r="AF41" s="3">
+      <c r="AG41" s="3">
         <v>4608100</v>
       </c>
-      <c r="AG41" s="3">
+      <c r="AH41" s="3">
         <v>4589200</v>
       </c>
-      <c r="AH41" s="3">
+      <c r="AI41" s="3">
         <v>4387400</v>
       </c>
-      <c r="AI41" s="3">
+      <c r="AJ41" s="3">
         <v>5323900</v>
       </c>
-      <c r="AJ41" s="3">
+      <c r="AK41" s="3">
         <v>5337600</v>
       </c>
-      <c r="AK41" s="3">
+      <c r="AL41" s="3">
         <v>5780800</v>
       </c>
-      <c r="AL41" s="3">
+      <c r="AM41" s="3">
         <v>6495200</v>
       </c>
-      <c r="AM41" s="3">
+      <c r="AN41" s="3">
         <v>6385500</v>
       </c>
-      <c r="AN41" s="3">
+      <c r="AO41" s="3">
         <v>7024600</v>
       </c>
     </row>
-    <row r="42" spans="2:40" x14ac:dyDescent="0.2">
+    <row r="42" spans="2:41" x14ac:dyDescent="0.2">
       <c r="C42" s="1" t="s">
         <v>35</v>
       </c>
       <c r="D42" s="3">
+        <v>30478600</v>
+      </c>
+      <c r="E42" s="3">
         <v>33934900</v>
       </c>
-      <c r="E42" s="3">
+      <c r="F42" s="3">
         <v>29338000</v>
       </c>
-      <c r="F42" s="3">
+      <c r="G42" s="3">
         <v>26987000</v>
       </c>
-      <c r="G42" s="3">
+      <c r="H42" s="3">
         <v>22818100</v>
       </c>
-      <c r="H42" s="3">
+      <c r="I42" s="3">
         <v>29370000</v>
       </c>
-      <c r="I42" s="3">
+      <c r="J42" s="3">
         <v>19283100</v>
       </c>
-      <c r="J42" s="3">
+      <c r="K42" s="3">
         <v>18486700</v>
       </c>
-      <c r="K42" s="3">
+      <c r="L42" s="3">
         <v>18215800</v>
       </c>
-      <c r="L42" s="3">
+      <c r="M42" s="3">
         <v>17492100</v>
       </c>
-      <c r="M42" s="3">
+      <c r="N42" s="3">
         <v>25108400</v>
       </c>
-      <c r="N42" s="3">
+      <c r="O42" s="3">
         <v>17703400</v>
       </c>
-      <c r="O42" s="3">
+      <c r="P42" s="3">
         <v>41084100</v>
       </c>
-      <c r="P42" s="3">
+      <c r="Q42" s="3">
         <v>48087900</v>
       </c>
-      <c r="Q42" s="3">
+      <c r="R42" s="3">
         <v>44907700</v>
       </c>
-      <c r="R42" s="3">
+      <c r="S42" s="3">
         <v>44616700</v>
       </c>
-      <c r="S42" s="3">
+      <c r="T42" s="3">
         <v>44083500</v>
       </c>
-      <c r="T42" s="3">
+      <c r="U42" s="3">
         <v>38326100</v>
       </c>
-      <c r="U42" s="3">
+      <c r="V42" s="3">
         <v>33800600</v>
       </c>
-      <c r="V42" s="3">
+      <c r="W42" s="3">
         <v>32013900</v>
       </c>
-      <c r="W42" s="3">
+      <c r="X42" s="3">
         <v>39170300</v>
       </c>
-      <c r="X42" s="3">
+      <c r="Y42" s="3">
         <v>33273800</v>
       </c>
-      <c r="Y42" s="3">
+      <c r="Z42" s="3">
         <v>36396600</v>
       </c>
-      <c r="Z42" s="3">
+      <c r="AA42" s="3">
         <v>38606200</v>
       </c>
-      <c r="AA42" s="3">
+      <c r="AB42" s="3">
         <v>37680800</v>
       </c>
-      <c r="AB42" s="3">
+      <c r="AC42" s="3">
         <v>39232200</v>
       </c>
-      <c r="AC42" s="3">
+      <c r="AD42" s="3">
         <v>36892000</v>
       </c>
-      <c r="AD42" s="3">
+      <c r="AE42" s="3">
         <v>30905300</v>
       </c>
-      <c r="AE42" s="3">
+      <c r="AF42" s="3">
         <v>29776700</v>
       </c>
-      <c r="AF42" s="3">
+      <c r="AG42" s="3">
         <v>20883600</v>
       </c>
-      <c r="AG42" s="3">
+      <c r="AH42" s="3">
         <v>22286700</v>
       </c>
-      <c r="AH42" s="3">
+      <c r="AI42" s="3">
         <v>21840100</v>
       </c>
-      <c r="AI42" s="3">
+      <c r="AJ42" s="3">
         <v>20932300</v>
       </c>
-      <c r="AJ42" s="3">
+      <c r="AK42" s="3">
         <v>12488600</v>
       </c>
-      <c r="AK42" s="3">
+      <c r="AL42" s="3">
         <v>14955900</v>
       </c>
-      <c r="AL42" s="3">
+      <c r="AM42" s="3">
         <v>13350900</v>
       </c>
-      <c r="AM42" s="3">
+      <c r="AN42" s="3">
         <v>14204100</v>
       </c>
-      <c r="AN42" s="3">
+      <c r="AO42" s="3">
         <v>16154100</v>
       </c>
     </row>
-    <row r="43" spans="2:40" x14ac:dyDescent="0.2">
+    <row r="43" spans="2:41" x14ac:dyDescent="0.2">
       <c r="C43" s="1" t="s">
         <v>36</v>
       </c>
       <c r="D43" s="3">
+        <v>7082500</v>
+      </c>
+      <c r="E43" s="3">
         <v>13780300</v>
       </c>
-      <c r="E43" s="3">
+      <c r="F43" s="3">
         <v>15335100</v>
       </c>
-      <c r="F43" s="3">
+      <c r="G43" s="3">
         <v>12353800</v>
       </c>
-      <c r="G43" s="3">
+      <c r="H43" s="3">
         <v>6099900</v>
       </c>
-      <c r="H43" s="3">
+      <c r="I43" s="3">
         <v>13077600</v>
       </c>
-      <c r="I43" s="3">
+      <c r="J43" s="3">
         <v>9540700</v>
       </c>
-      <c r="J43" s="3">
+      <c r="K43" s="3">
         <v>10078300</v>
       </c>
-      <c r="K43" s="3">
+      <c r="L43" s="3">
         <v>8598900</v>
       </c>
-      <c r="L43" s="3">
+      <c r="M43" s="3">
         <v>9843900</v>
       </c>
-      <c r="M43" s="3">
+      <c r="N43" s="3">
         <v>11594400</v>
       </c>
-      <c r="N43" s="3">
+      <c r="O43" s="3">
         <v>10468300</v>
       </c>
-      <c r="O43" s="3">
-        <v>0</v>
-      </c>
       <c r="P43" s="3">
         <v>0</v>
       </c>
@@ -4371,8 +4463,11 @@
       <c r="AN43" s="3">
         <v>0</v>
       </c>
+      <c r="AO43" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="44" spans="2:40" x14ac:dyDescent="0.2">
+    <row r="44" spans="2:41" x14ac:dyDescent="0.2">
       <c r="C44" s="1" t="s">
         <v>37</v>
       </c>
@@ -4409,8 +4504,8 @@
       <c r="N44" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="O44" s="3">
-        <v>0</v>
+      <c r="O44" s="3" t="s">
+        <v>5</v>
       </c>
       <c r="P44" s="3">
         <v>0</v>
@@ -4487,47 +4582,50 @@
       <c r="AN44" s="3">
         <v>0</v>
       </c>
+      <c r="AO44" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="45" spans="2:40" x14ac:dyDescent="0.2">
+    <row r="45" spans="2:41" x14ac:dyDescent="0.2">
       <c r="C45" s="1" t="s">
         <v>38</v>
       </c>
       <c r="D45" s="3">
+        <v>5813900</v>
+      </c>
+      <c r="E45" s="3">
         <v>2491200</v>
       </c>
-      <c r="E45" s="3">
+      <c r="F45" s="3">
         <v>2304800</v>
       </c>
-      <c r="F45" s="3">
+      <c r="G45" s="3">
         <v>1984500</v>
       </c>
-      <c r="G45" s="3">
+      <c r="H45" s="3">
         <v>3417100</v>
       </c>
-      <c r="H45" s="3">
+      <c r="I45" s="3">
         <v>2191600</v>
       </c>
-      <c r="I45" s="3">
+      <c r="J45" s="3">
         <v>2546100</v>
       </c>
-      <c r="J45" s="3">
+      <c r="K45" s="3">
         <v>2248400</v>
       </c>
-      <c r="K45" s="3">
+      <c r="L45" s="3">
         <v>3229200</v>
       </c>
-      <c r="L45" s="3">
+      <c r="M45" s="3">
         <v>2254000</v>
       </c>
-      <c r="M45" s="3">
+      <c r="N45" s="3">
         <v>2036900</v>
       </c>
-      <c r="N45" s="3">
+      <c r="O45" s="3">
         <v>1992400</v>
       </c>
-      <c r="O45" s="3">
-        <v>0</v>
-      </c>
       <c r="P45" s="3">
         <v>0</v>
       </c>
@@ -4603,47 +4701,50 @@
       <c r="AN45" s="3">
         <v>0</v>
       </c>
+      <c r="AO45" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="46" spans="2:40" x14ac:dyDescent="0.2">
+    <row r="46" spans="2:41" x14ac:dyDescent="0.2">
       <c r="C46" s="1" t="s">
         <v>39</v>
       </c>
       <c r="D46" s="3">
+        <v>70334000</v>
+      </c>
+      <c r="E46" s="3">
         <v>71300600</v>
       </c>
-      <c r="E46" s="3">
+      <c r="F46" s="3">
         <v>69444800</v>
       </c>
-      <c r="F46" s="3">
+      <c r="G46" s="3">
         <v>58995800</v>
       </c>
-      <c r="G46" s="3">
+      <c r="H46" s="3">
         <v>51046100</v>
       </c>
-      <c r="H46" s="3">
+      <c r="I46" s="3">
         <v>70438600</v>
       </c>
-      <c r="I46" s="3">
+      <c r="J46" s="3">
         <v>50125600</v>
       </c>
-      <c r="J46" s="3">
+      <c r="K46" s="3">
         <v>54875900</v>
       </c>
-      <c r="K46" s="3">
+      <c r="L46" s="3">
         <v>53874000</v>
       </c>
-      <c r="L46" s="3">
+      <c r="M46" s="3">
         <v>49079800</v>
       </c>
-      <c r="M46" s="3">
+      <c r="N46" s="3">
         <v>55527700</v>
       </c>
-      <c r="N46" s="3">
+      <c r="O46" s="3">
         <v>55109700</v>
       </c>
-      <c r="O46" s="3">
-        <v>0</v>
-      </c>
       <c r="P46" s="3">
         <v>0</v>
       </c>
@@ -4719,356 +4820,368 @@
       <c r="AN46" s="3">
         <v>0</v>
       </c>
+      <c r="AO46" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="47" spans="2:40" x14ac:dyDescent="0.2">
+    <row r="47" spans="2:41" x14ac:dyDescent="0.2">
       <c r="C47" s="1" t="s">
         <v>40</v>
       </c>
       <c r="D47" s="3">
+        <v>51061400</v>
+      </c>
+      <c r="E47" s="3">
         <v>64194100</v>
       </c>
-      <c r="E47" s="3">
+      <c r="F47" s="3">
         <v>44237900</v>
       </c>
-      <c r="F47" s="3">
+      <c r="G47" s="3">
         <v>43339500</v>
       </c>
-      <c r="G47" s="3">
-        <v>29734600</v>
-      </c>
       <c r="H47" s="3">
+        <v>29491700</v>
+      </c>
+      <c r="I47" s="3">
         <v>43909700</v>
       </c>
-      <c r="I47" s="3">
+      <c r="J47" s="3">
         <v>45684200</v>
       </c>
-      <c r="J47" s="3">
+      <c r="K47" s="3">
         <v>45083200</v>
       </c>
-      <c r="K47" s="3">
+      <c r="L47" s="3">
         <v>33573300</v>
       </c>
-      <c r="L47" s="3">
+      <c r="M47" s="3">
         <v>46697400</v>
       </c>
-      <c r="M47" s="3">
+      <c r="N47" s="3">
         <v>47231400</v>
       </c>
-      <c r="N47" s="3">
+      <c r="O47" s="3">
         <v>47653400</v>
       </c>
-      <c r="O47" s="3">
+      <c r="P47" s="3">
         <v>979200</v>
       </c>
-      <c r="P47" s="3">
+      <c r="Q47" s="3">
         <v>976800</v>
       </c>
-      <c r="Q47" s="3">
+      <c r="R47" s="3">
         <v>1035000</v>
       </c>
-      <c r="R47" s="3">
+      <c r="S47" s="3">
         <v>1011300</v>
       </c>
-      <c r="S47" s="3">
+      <c r="T47" s="3">
         <v>1001400</v>
       </c>
-      <c r="T47" s="3">
+      <c r="U47" s="3">
         <v>896000</v>
       </c>
-      <c r="U47" s="3">
+      <c r="V47" s="3">
         <v>881500</v>
       </c>
-      <c r="V47" s="3">
+      <c r="W47" s="3">
         <v>775800</v>
       </c>
-      <c r="W47" s="3">
+      <c r="X47" s="3">
         <v>735000</v>
       </c>
-      <c r="X47" s="3">
+      <c r="Y47" s="3">
         <v>829200</v>
       </c>
-      <c r="Y47" s="3">
+      <c r="Z47" s="3">
         <v>714700</v>
       </c>
-      <c r="Z47" s="3">
+      <c r="AA47" s="3">
         <v>674300</v>
       </c>
-      <c r="AA47" s="3">
+      <c r="AB47" s="3">
         <v>685400</v>
       </c>
-      <c r="AB47" s="3">
+      <c r="AC47" s="3">
         <v>322100</v>
       </c>
-      <c r="AC47" s="3">
+      <c r="AD47" s="3">
         <v>311500</v>
       </c>
-      <c r="AD47" s="3">
+      <c r="AE47" s="3">
         <v>316200</v>
       </c>
-      <c r="AE47" s="3">
+      <c r="AF47" s="3">
         <v>303600</v>
       </c>
-      <c r="AF47" s="3">
+      <c r="AG47" s="3">
         <v>276700</v>
       </c>
-      <c r="AG47" s="3">
+      <c r="AH47" s="3">
         <v>346900</v>
       </c>
-      <c r="AH47" s="3">
+      <c r="AI47" s="3">
         <v>348200</v>
       </c>
-      <c r="AI47" s="3">
+      <c r="AJ47" s="3">
         <v>367000</v>
       </c>
-      <c r="AJ47" s="3">
+      <c r="AK47" s="3">
         <v>490900</v>
       </c>
-      <c r="AK47" s="3">
+      <c r="AL47" s="3">
         <v>326300</v>
       </c>
-      <c r="AL47" s="3">
+      <c r="AM47" s="3">
         <v>351100</v>
       </c>
-      <c r="AM47" s="3">
+      <c r="AN47" s="3">
         <v>395100</v>
       </c>
-      <c r="AN47" s="3">
+      <c r="AO47" s="3">
         <v>377600</v>
       </c>
     </row>
-    <row r="48" spans="2:40" x14ac:dyDescent="0.2">
+    <row r="48" spans="2:41" x14ac:dyDescent="0.2">
       <c r="C48" s="1" t="s">
         <v>41</v>
       </c>
       <c r="D48" s="3">
+        <v>5254900</v>
+      </c>
+      <c r="E48" s="3">
         <v>5401200</v>
       </c>
-      <c r="E48" s="3">
+      <c r="F48" s="3">
         <v>5310400</v>
       </c>
-      <c r="F48" s="3">
+      <c r="G48" s="3">
         <v>4933500</v>
       </c>
-      <c r="G48" s="3">
+      <c r="H48" s="3">
         <v>4937200</v>
       </c>
-      <c r="H48" s="3">
+      <c r="I48" s="3">
         <v>5522800</v>
       </c>
-      <c r="I48" s="3">
+      <c r="J48" s="3">
         <v>5103100</v>
       </c>
-      <c r="J48" s="3">
+      <c r="K48" s="3">
         <v>4908300</v>
       </c>
-      <c r="K48" s="3">
+      <c r="L48" s="3">
         <v>4983700</v>
       </c>
-      <c r="L48" s="3">
+      <c r="M48" s="3">
         <v>4486300</v>
       </c>
-      <c r="M48" s="3">
+      <c r="N48" s="3">
         <v>4434900</v>
       </c>
-      <c r="N48" s="3">
+      <c r="O48" s="3">
         <v>4401200</v>
       </c>
-      <c r="O48" s="3">
+      <c r="P48" s="3">
         <v>2648000</v>
       </c>
-      <c r="P48" s="3">
+      <c r="Q48" s="3">
         <v>2590300</v>
       </c>
-      <c r="Q48" s="3">
+      <c r="R48" s="3">
         <v>2689200</v>
       </c>
-      <c r="R48" s="3">
+      <c r="S48" s="3">
         <v>2729900</v>
       </c>
-      <c r="S48" s="3">
+      <c r="T48" s="3">
         <v>2673200</v>
       </c>
-      <c r="T48" s="3">
+      <c r="U48" s="3">
         <v>2701000</v>
       </c>
-      <c r="U48" s="3">
+      <c r="V48" s="3">
         <v>2682600</v>
       </c>
-      <c r="V48" s="3">
+      <c r="W48" s="3">
         <v>2700600</v>
       </c>
-      <c r="W48" s="3">
+      <c r="X48" s="3">
         <v>2719200</v>
       </c>
-      <c r="X48" s="3">
+      <c r="Y48" s="3">
         <v>2764300</v>
       </c>
-      <c r="Y48" s="3">
+      <c r="Z48" s="3">
         <v>2790300</v>
       </c>
-      <c r="Z48" s="3">
+      <c r="AA48" s="3">
         <v>2961700</v>
       </c>
-      <c r="AA48" s="3">
+      <c r="AB48" s="3">
         <v>3098200</v>
       </c>
-      <c r="AB48" s="3">
+      <c r="AC48" s="3">
         <v>3089800</v>
       </c>
-      <c r="AC48" s="3">
+      <c r="AD48" s="3">
         <v>3058200</v>
       </c>
-      <c r="AD48" s="3">
+      <c r="AE48" s="3">
         <v>3080600</v>
       </c>
-      <c r="AE48" s="3">
+      <c r="AF48" s="3">
         <v>2368100</v>
       </c>
-      <c r="AF48" s="3">
+      <c r="AG48" s="3">
         <v>2284800</v>
       </c>
-      <c r="AG48" s="3">
+      <c r="AH48" s="3">
         <v>2378800</v>
       </c>
-      <c r="AH48" s="3">
+      <c r="AI48" s="3">
         <v>2384000</v>
       </c>
-      <c r="AI48" s="3">
+      <c r="AJ48" s="3">
         <v>2507000</v>
       </c>
-      <c r="AJ48" s="3">
+      <c r="AK48" s="3">
         <v>2509800</v>
       </c>
-      <c r="AK48" s="3">
+      <c r="AL48" s="3">
         <v>2480800</v>
       </c>
-      <c r="AL48" s="3">
+      <c r="AM48" s="3">
         <v>2470200</v>
       </c>
-      <c r="AM48" s="3">
+      <c r="AN48" s="3">
         <v>2534900</v>
       </c>
-      <c r="AN48" s="3">
+      <c r="AO48" s="3">
         <v>2525400</v>
       </c>
     </row>
-    <row r="49" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="49" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C49" s="1" t="s">
         <v>42</v>
       </c>
       <c r="D49" s="3">
+        <v>503500</v>
+      </c>
+      <c r="E49" s="3">
         <v>770100</v>
       </c>
-      <c r="E49" s="3">
+      <c r="F49" s="3">
         <v>788000</v>
       </c>
-      <c r="F49" s="3">
+      <c r="G49" s="3">
         <v>745500</v>
       </c>
-      <c r="G49" s="3">
+      <c r="H49" s="3">
         <v>552200</v>
       </c>
-      <c r="H49" s="3">
+      <c r="I49" s="3">
         <v>621800</v>
       </c>
-      <c r="I49" s="3">
+      <c r="J49" s="3">
         <v>557800</v>
       </c>
-      <c r="J49" s="3">
+      <c r="K49" s="3">
         <v>562600</v>
       </c>
-      <c r="K49" s="3">
+      <c r="L49" s="3">
         <v>582000</v>
       </c>
-      <c r="L49" s="3">
+      <c r="M49" s="3">
         <v>568100</v>
       </c>
-      <c r="M49" s="3">
+      <c r="N49" s="3">
         <v>586300</v>
       </c>
-      <c r="N49" s="3">
+      <c r="O49" s="3">
         <v>573300</v>
       </c>
-      <c r="O49" s="3">
+      <c r="P49" s="3">
         <v>636800</v>
       </c>
-      <c r="P49" s="3">
+      <c r="Q49" s="3">
         <v>639200</v>
       </c>
-      <c r="Q49" s="3">
+      <c r="R49" s="3">
         <v>596500</v>
       </c>
-      <c r="R49" s="3">
+      <c r="S49" s="3">
         <v>608700</v>
       </c>
-      <c r="S49" s="3">
+      <c r="T49" s="3">
         <v>589000</v>
       </c>
-      <c r="T49" s="3">
+      <c r="U49" s="3">
         <v>586400</v>
       </c>
-      <c r="U49" s="3">
+      <c r="V49" s="3">
         <v>581700</v>
       </c>
-      <c r="V49" s="3">
+      <c r="W49" s="3">
         <v>582600</v>
       </c>
-      <c r="W49" s="3">
+      <c r="X49" s="3">
         <v>586100</v>
       </c>
-      <c r="X49" s="3">
+      <c r="Y49" s="3">
         <v>615800</v>
       </c>
-      <c r="Y49" s="3">
+      <c r="Z49" s="3">
         <v>631700</v>
       </c>
-      <c r="Z49" s="3">
+      <c r="AA49" s="3">
         <v>668000</v>
       </c>
-      <c r="AA49" s="3">
+      <c r="AB49" s="3">
         <v>717500</v>
       </c>
-      <c r="AB49" s="3">
+      <c r="AC49" s="3">
         <v>590200</v>
       </c>
-      <c r="AC49" s="3">
+      <c r="AD49" s="3">
         <v>565800</v>
       </c>
-      <c r="AD49" s="3">
+      <c r="AE49" s="3">
         <v>588900</v>
       </c>
-      <c r="AE49" s="3">
+      <c r="AF49" s="3">
         <v>493300</v>
       </c>
-      <c r="AF49" s="3">
+      <c r="AG49" s="3">
         <v>502400</v>
       </c>
-      <c r="AG49" s="3">
+      <c r="AH49" s="3">
         <v>549000</v>
       </c>
-      <c r="AH49" s="3">
+      <c r="AI49" s="3">
         <v>452700</v>
       </c>
-      <c r="AI49" s="3">
+      <c r="AJ49" s="3">
         <v>456400</v>
       </c>
-      <c r="AJ49" s="3">
+      <c r="AK49" s="3">
         <v>461900</v>
       </c>
-      <c r="AK49" s="3">
+      <c r="AL49" s="3">
         <v>446100</v>
       </c>
-      <c r="AL49" s="3">
+      <c r="AM49" s="3">
         <v>415100</v>
       </c>
-      <c r="AM49" s="3">
+      <c r="AN49" s="3">
         <v>435400</v>
       </c>
-      <c r="AN49" s="3">
+      <c r="AO49" s="3">
         <v>376700</v>
       </c>
     </row>
-    <row r="50" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="50" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C50" s="1" t="s">
         <v>43</v>
       </c>
@@ -5183,8 +5296,11 @@
       <c r="AN50" s="3">
         <v>0</v>
       </c>
+      <c r="AO50" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="51" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="51" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C51" s="1" t="s">
         <v>44</v>
       </c>
@@ -5299,124 +5415,130 @@
       <c r="AN51" s="3">
         <v>0</v>
       </c>
+      <c r="AO51" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="52" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="52" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C52" s="1" t="s">
         <v>45</v>
       </c>
       <c r="D52" s="3">
+        <v>22900500</v>
+      </c>
+      <c r="E52" s="3">
         <v>5286500</v>
       </c>
-      <c r="E52" s="3">
+      <c r="F52" s="3">
         <v>1343400</v>
       </c>
-      <c r="F52" s="3">
+      <c r="G52" s="3">
         <v>1099500</v>
       </c>
-      <c r="G52" s="3">
-        <v>15193100</v>
-      </c>
       <c r="H52" s="3">
+        <v>15436000</v>
+      </c>
+      <c r="I52" s="3">
         <v>1117800</v>
       </c>
-      <c r="I52" s="3">
+      <c r="J52" s="3">
         <v>1097200</v>
       </c>
-      <c r="J52" s="3">
+      <c r="K52" s="3">
         <v>1375500</v>
       </c>
-      <c r="K52" s="3">
+      <c r="L52" s="3">
         <v>16836600</v>
       </c>
-      <c r="L52" s="3">
+      <c r="M52" s="3">
         <v>1488400</v>
       </c>
-      <c r="M52" s="3">
+      <c r="N52" s="3">
         <v>1186200</v>
       </c>
-      <c r="N52" s="3">
+      <c r="O52" s="3">
         <v>1174600</v>
       </c>
-      <c r="O52" s="3">
+      <c r="P52" s="3">
         <v>331800</v>
       </c>
-      <c r="P52" s="3">
+      <c r="Q52" s="3">
         <v>284500</v>
       </c>
-      <c r="Q52" s="3">
+      <c r="R52" s="3">
         <v>166400</v>
       </c>
-      <c r="R52" s="3">
+      <c r="S52" s="3">
         <v>58400</v>
       </c>
-      <c r="S52" s="3">
+      <c r="T52" s="3">
         <v>59100</v>
       </c>
-      <c r="T52" s="3">
+      <c r="U52" s="3">
         <v>41100</v>
       </c>
-      <c r="U52" s="3">
+      <c r="V52" s="3">
         <v>56000</v>
       </c>
-      <c r="V52" s="3">
+      <c r="W52" s="3">
         <v>73700</v>
       </c>
-      <c r="W52" s="3">
+      <c r="X52" s="3">
         <v>82700</v>
       </c>
-      <c r="X52" s="3">
+      <c r="Y52" s="3">
         <v>74500</v>
       </c>
-      <c r="Y52" s="3">
+      <c r="Z52" s="3">
         <v>37800</v>
       </c>
-      <c r="Z52" s="3">
+      <c r="AA52" s="3">
         <v>38200</v>
       </c>
-      <c r="AA52" s="3">
+      <c r="AB52" s="3">
         <v>44800</v>
       </c>
-      <c r="AB52" s="3">
+      <c r="AC52" s="3">
         <v>82300</v>
       </c>
-      <c r="AC52" s="3">
+      <c r="AD52" s="3">
         <v>69500</v>
       </c>
-      <c r="AD52" s="3">
+      <c r="AE52" s="3">
         <v>68200</v>
       </c>
-      <c r="AE52" s="3">
+      <c r="AF52" s="3">
         <v>120400</v>
       </c>
-      <c r="AF52" s="3">
+      <c r="AG52" s="3">
         <v>36800</v>
       </c>
-      <c r="AG52" s="3">
+      <c r="AH52" s="3">
         <v>91100</v>
       </c>
-      <c r="AH52" s="3">
+      <c r="AI52" s="3">
         <v>177600</v>
       </c>
-      <c r="AI52" s="3">
+      <c r="AJ52" s="3">
         <v>289300</v>
       </c>
-      <c r="AJ52" s="3">
+      <c r="AK52" s="3">
         <v>234800</v>
       </c>
-      <c r="AK52" s="3">
+      <c r="AL52" s="3">
         <v>221100</v>
       </c>
-      <c r="AL52" s="3">
+      <c r="AM52" s="3">
         <v>262700</v>
       </c>
-      <c r="AM52" s="3">
+      <c r="AN52" s="3">
         <v>274800</v>
       </c>
-      <c r="AN52" s="3">
+      <c r="AO52" s="3">
         <v>143800</v>
       </c>
     </row>
-    <row r="53" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="53" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C53" s="1" t="s">
         <v>46</v>
       </c>
@@ -5531,124 +5653,130 @@
       <c r="AN53" s="3">
         <v>0</v>
       </c>
+      <c r="AO53" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="54" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="54" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C54" s="1" t="s">
         <v>47</v>
       </c>
       <c r="D54" s="3">
+        <v>416660200</v>
+      </c>
+      <c r="E54" s="3">
         <v>417822000</v>
       </c>
-      <c r="E54" s="3">
+      <c r="F54" s="3">
         <v>394651000</v>
       </c>
-      <c r="F54" s="3">
+      <c r="G54" s="3">
         <v>361721400</v>
       </c>
-      <c r="G54" s="3">
+      <c r="H54" s="3">
         <v>355900000</v>
       </c>
-      <c r="H54" s="3">
+      <c r="I54" s="3">
         <v>413964600</v>
       </c>
-      <c r="I54" s="3">
+      <c r="J54" s="3">
         <v>369217100</v>
       </c>
-      <c r="J54" s="3">
+      <c r="K54" s="3">
         <v>375587700</v>
       </c>
-      <c r="K54" s="3">
+      <c r="L54" s="3">
         <v>384037900</v>
       </c>
-      <c r="L54" s="3">
+      <c r="M54" s="3">
         <v>360962600</v>
       </c>
-      <c r="M54" s="3">
+      <c r="N54" s="3">
         <v>366653200</v>
       </c>
-      <c r="N54" s="3">
+      <c r="O54" s="3">
         <v>366661700</v>
       </c>
-      <c r="O54" s="3">
+      <c r="P54" s="3">
         <v>360355800</v>
       </c>
-      <c r="P54" s="3">
+      <c r="Q54" s="3">
         <v>366510300</v>
       </c>
-      <c r="Q54" s="3">
+      <c r="R54" s="3">
         <v>368558700</v>
       </c>
-      <c r="R54" s="3">
+      <c r="S54" s="3">
         <v>358592300</v>
       </c>
-      <c r="S54" s="3">
+      <c r="T54" s="3">
         <v>335387900</v>
       </c>
-      <c r="T54" s="3">
+      <c r="U54" s="3">
         <v>328638700</v>
       </c>
-      <c r="U54" s="3">
+      <c r="V54" s="3">
         <v>315953000</v>
       </c>
-      <c r="V54" s="3">
+      <c r="W54" s="3">
         <v>307917200</v>
       </c>
-      <c r="W54" s="3">
+      <c r="X54" s="3">
         <v>295320000</v>
       </c>
-      <c r="X54" s="3">
+      <c r="Y54" s="3">
         <v>293246000</v>
       </c>
-      <c r="Y54" s="3">
+      <c r="Z54" s="3">
         <v>292659600</v>
       </c>
-      <c r="Z54" s="3">
+      <c r="AA54" s="3">
         <v>306353500</v>
       </c>
-      <c r="AA54" s="3">
+      <c r="AB54" s="3">
         <v>307683600</v>
       </c>
-      <c r="AB54" s="3">
+      <c r="AC54" s="3">
         <v>314996600</v>
       </c>
-      <c r="AC54" s="3">
+      <c r="AD54" s="3">
         <v>316273500</v>
       </c>
-      <c r="AD54" s="3">
+      <c r="AE54" s="3">
         <v>314085600</v>
       </c>
-      <c r="AE54" s="3">
+      <c r="AF54" s="3">
         <v>285975600</v>
       </c>
-      <c r="AF54" s="3">
+      <c r="AG54" s="3">
         <v>267139300</v>
       </c>
-      <c r="AG54" s="3">
+      <c r="AH54" s="3">
         <v>274311500</v>
       </c>
-      <c r="AH54" s="3">
+      <c r="AI54" s="3">
         <v>273668600</v>
       </c>
-      <c r="AI54" s="3">
+      <c r="AJ54" s="3">
         <v>278340000</v>
       </c>
-      <c r="AJ54" s="3">
+      <c r="AK54" s="3">
         <v>279730100</v>
       </c>
-      <c r="AK54" s="3">
+      <c r="AL54" s="3">
         <v>278137400</v>
       </c>
-      <c r="AL54" s="3">
+      <c r="AM54" s="3">
         <v>273600800</v>
       </c>
-      <c r="AM54" s="3">
+      <c r="AN54" s="3">
         <v>279614500</v>
       </c>
-      <c r="AN54" s="3">
+      <c r="AO54" s="3">
         <v>281548700</v>
       </c>
     </row>
-    <row r="55" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="55" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C55" s="1" t="s">
         <v>48</v>
       </c>
@@ -5689,8 +5817,9 @@
       <c r="AL55" s="3"/>
       <c r="AM55" s="3"/>
       <c r="AN55" s="3"/>
+      <c r="AO55" s="3"/>
     </row>
-    <row r="56" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="56" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C56" s="1" t="s">
         <v>49</v>
       </c>
@@ -5731,163 +5860,167 @@
       <c r="AL56" s="3"/>
       <c r="AM56" s="3"/>
       <c r="AN56" s="3"/>
+      <c r="AO56" s="3"/>
     </row>
-    <row r="57" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="57" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C57" s="1" t="s">
         <v>50</v>
       </c>
       <c r="D57" s="3">
+        <v>266776300</v>
+      </c>
+      <c r="E57" s="3">
         <v>276347000</v>
       </c>
-      <c r="E57" s="3">
+      <c r="F57" s="3">
         <v>287825900</v>
       </c>
-      <c r="F57" s="3">
+      <c r="G57" s="3">
         <v>262183700</v>
       </c>
-      <c r="G57" s="3">
+      <c r="H57" s="3">
         <v>253583100</v>
       </c>
-      <c r="H57" s="3">
+      <c r="I57" s="3">
         <v>303683400</v>
       </c>
-      <c r="I57" s="3">
+      <c r="J57" s="3">
         <v>269353200</v>
       </c>
-      <c r="J57" s="3">
+      <c r="K57" s="3">
         <v>273669100</v>
       </c>
-      <c r="K57" s="3">
+      <c r="L57" s="3">
         <v>283746600</v>
       </c>
-      <c r="L57" s="3">
+      <c r="M57" s="3">
         <v>257925300</v>
       </c>
-      <c r="M57" s="3">
+      <c r="N57" s="3">
         <v>263215600</v>
       </c>
-      <c r="N57" s="3">
+      <c r="O57" s="3">
         <v>259046400</v>
       </c>
-      <c r="O57" s="3">
+      <c r="P57" s="3">
         <v>8592200</v>
       </c>
-      <c r="P57" s="3">
+      <c r="Q57" s="3">
         <v>12736100</v>
       </c>
-      <c r="Q57" s="3">
+      <c r="R57" s="3">
         <v>12538100</v>
       </c>
-      <c r="R57" s="3">
+      <c r="S57" s="3">
         <v>11104000</v>
       </c>
-      <c r="S57" s="3">
+      <c r="T57" s="3">
         <v>10844700</v>
       </c>
-      <c r="T57" s="3">
+      <c r="U57" s="3">
         <v>7957500</v>
       </c>
-      <c r="U57" s="3">
+      <c r="V57" s="3">
         <v>9468900</v>
       </c>
-      <c r="V57" s="3">
+      <c r="W57" s="3">
         <v>7995800</v>
       </c>
-      <c r="W57" s="3">
+      <c r="X57" s="3">
         <v>3698600</v>
       </c>
-      <c r="X57" s="3">
+      <c r="Y57" s="3">
         <v>7530800</v>
       </c>
-      <c r="Y57" s="3">
+      <c r="Z57" s="3">
         <v>8467000</v>
       </c>
-      <c r="Z57" s="3">
+      <c r="AA57" s="3">
         <v>9538600</v>
       </c>
-      <c r="AA57" s="3">
+      <c r="AB57" s="3">
         <v>7264700</v>
       </c>
-      <c r="AB57" s="3">
+      <c r="AC57" s="3">
         <v>13339700</v>
       </c>
-      <c r="AC57" s="3">
+      <c r="AD57" s="3">
         <v>15138200</v>
       </c>
-      <c r="AD57" s="3">
+      <c r="AE57" s="3">
         <v>14778600</v>
       </c>
-      <c r="AE57" s="3">
+      <c r="AF57" s="3">
         <v>10988500</v>
       </c>
-      <c r="AF57" s="3">
+      <c r="AG57" s="3">
         <v>12068900</v>
       </c>
-      <c r="AG57" s="3">
+      <c r="AH57" s="3">
         <v>11638400</v>
       </c>
-      <c r="AH57" s="3">
+      <c r="AI57" s="3">
         <v>12317300</v>
       </c>
-      <c r="AI57" s="3">
+      <c r="AJ57" s="3">
         <v>5801500</v>
       </c>
-      <c r="AJ57" s="3">
+      <c r="AK57" s="3">
         <v>13814400</v>
       </c>
-      <c r="AK57" s="3">
+      <c r="AL57" s="3">
         <v>14756900</v>
       </c>
-      <c r="AL57" s="3">
+      <c r="AM57" s="3">
         <v>10823000</v>
       </c>
-      <c r="AM57" s="3">
+      <c r="AN57" s="3">
         <v>13329400</v>
       </c>
-      <c r="AN57" s="3">
+      <c r="AO57" s="3">
         <v>15356600</v>
       </c>
     </row>
-    <row r="58" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="58" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C58" s="1" t="s">
         <v>51</v>
       </c>
       <c r="D58" s="3">
+        <v>11198400</v>
+      </c>
+      <c r="E58" s="3">
         <v>9091100</v>
       </c>
-      <c r="E58" s="3">
+      <c r="F58" s="3">
         <v>8966800</v>
       </c>
-      <c r="F58" s="3">
+      <c r="G58" s="3">
         <v>10611200</v>
       </c>
-      <c r="G58" s="3">
+      <c r="H58" s="3">
         <v>12014400</v>
       </c>
-      <c r="H58" s="3">
+      <c r="I58" s="3">
         <v>10388900</v>
       </c>
-      <c r="I58" s="3">
+      <c r="J58" s="3">
         <v>10701400</v>
       </c>
-      <c r="J58" s="3">
+      <c r="K58" s="3">
         <v>11337600</v>
       </c>
-      <c r="K58" s="3">
+      <c r="L58" s="3">
         <v>9863100</v>
       </c>
-      <c r="L58" s="3">
+      <c r="M58" s="3">
         <v>11103300</v>
       </c>
-      <c r="M58" s="3">
+      <c r="N58" s="3">
         <v>10559700</v>
       </c>
-      <c r="N58" s="3">
+      <c r="O58" s="3">
         <v>10550500</v>
       </c>
-      <c r="O58" s="3">
-        <v>0</v>
-      </c>
       <c r="P58" s="3">
         <v>0</v>
       </c>
@@ -5963,163 +6096,169 @@
       <c r="AN58" s="3">
         <v>0</v>
       </c>
+      <c r="AO58" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="59" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="59" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C59" s="1" t="s">
         <v>52</v>
       </c>
       <c r="D59" s="3">
+        <v>1226800</v>
+      </c>
+      <c r="E59" s="3">
         <v>1113600</v>
       </c>
-      <c r="E59" s="3">
+      <c r="F59" s="3">
         <v>1084300</v>
       </c>
-      <c r="F59" s="3">
+      <c r="G59" s="3">
         <v>825800</v>
       </c>
-      <c r="G59" s="3">
+      <c r="H59" s="3">
         <v>747300</v>
       </c>
-      <c r="H59" s="3">
+      <c r="I59" s="3">
         <v>917100</v>
       </c>
-      <c r="I59" s="3">
+      <c r="J59" s="3">
         <v>585700</v>
       </c>
-      <c r="J59" s="3">
+      <c r="K59" s="3">
         <v>748600</v>
       </c>
-      <c r="K59" s="3">
+      <c r="L59" s="3">
         <v>795100</v>
       </c>
-      <c r="L59" s="3">
+      <c r="M59" s="3">
         <v>581800</v>
       </c>
-      <c r="M59" s="3">
+      <c r="N59" s="3">
         <v>593500</v>
       </c>
-      <c r="N59" s="3">
+      <c r="O59" s="3">
         <v>1203800</v>
       </c>
-      <c r="O59" s="3">
+      <c r="P59" s="3">
         <v>3047200</v>
       </c>
-      <c r="P59" s="3">
+      <c r="Q59" s="3">
         <v>2229700</v>
       </c>
-      <c r="Q59" s="3">
+      <c r="R59" s="3">
         <v>1968300</v>
       </c>
-      <c r="R59" s="3">
+      <c r="S59" s="3">
         <v>2093100</v>
       </c>
-      <c r="S59" s="3">
+      <c r="T59" s="3">
         <v>1991300</v>
       </c>
-      <c r="T59" s="3">
+      <c r="U59" s="3">
         <v>1538600</v>
       </c>
-      <c r="U59" s="3">
+      <c r="V59" s="3">
         <v>1446500</v>
       </c>
-      <c r="V59" s="3">
+      <c r="W59" s="3">
         <v>1600800</v>
       </c>
-      <c r="W59" s="3">
+      <c r="X59" s="3">
         <v>1790900</v>
       </c>
-      <c r="X59" s="3">
+      <c r="Y59" s="3">
         <v>1521700</v>
       </c>
-      <c r="Y59" s="3">
+      <c r="Z59" s="3">
         <v>1545300</v>
       </c>
-      <c r="Z59" s="3">
+      <c r="AA59" s="3">
         <v>1892000</v>
       </c>
-      <c r="AA59" s="3">
+      <c r="AB59" s="3">
         <v>2294100</v>
       </c>
-      <c r="AB59" s="3">
+      <c r="AC59" s="3">
         <v>2199800</v>
       </c>
-      <c r="AC59" s="3">
+      <c r="AD59" s="3">
         <v>2064700</v>
       </c>
-      <c r="AD59" s="3">
+      <c r="AE59" s="3">
         <v>2149400</v>
       </c>
-      <c r="AE59" s="3">
+      <c r="AF59" s="3">
         <v>1989900</v>
       </c>
-      <c r="AF59" s="3">
+      <c r="AG59" s="3">
         <v>1798500</v>
       </c>
-      <c r="AG59" s="3">
+      <c r="AH59" s="3">
         <v>1649500</v>
       </c>
-      <c r="AH59" s="3">
+      <c r="AI59" s="3">
         <v>1642100</v>
       </c>
-      <c r="AI59" s="3">
+      <c r="AJ59" s="3">
         <v>2008600</v>
       </c>
-      <c r="AJ59" s="3">
+      <c r="AK59" s="3">
         <v>2057400</v>
       </c>
-      <c r="AK59" s="3">
+      <c r="AL59" s="3">
         <v>1681400</v>
       </c>
-      <c r="AL59" s="3">
+      <c r="AM59" s="3">
         <v>1880000</v>
       </c>
-      <c r="AM59" s="3">
+      <c r="AN59" s="3">
         <v>2004400</v>
       </c>
-      <c r="AN59" s="3">
+      <c r="AO59" s="3">
         <v>1813400</v>
       </c>
     </row>
-    <row r="60" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="60" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C60" s="1" t="s">
         <v>53</v>
       </c>
       <c r="D60" s="3">
+        <v>282288500</v>
+      </c>
+      <c r="E60" s="3">
         <v>289912100</v>
       </c>
-      <c r="E60" s="3">
+      <c r="F60" s="3">
         <v>301362800</v>
       </c>
-      <c r="F60" s="3">
+      <c r="G60" s="3">
         <v>276760100</v>
       </c>
-      <c r="G60" s="3">
+      <c r="H60" s="3">
         <v>269522700</v>
       </c>
-      <c r="H60" s="3">
+      <c r="I60" s="3">
         <v>318811800</v>
       </c>
-      <c r="I60" s="3">
+      <c r="J60" s="3">
         <v>283969800</v>
       </c>
-      <c r="J60" s="3">
+      <c r="K60" s="3">
         <v>288965400</v>
       </c>
-      <c r="K60" s="3">
+      <c r="L60" s="3">
         <v>297751000</v>
       </c>
-      <c r="L60" s="3">
+      <c r="M60" s="3">
         <v>272946300</v>
       </c>
-      <c r="M60" s="3">
+      <c r="N60" s="3">
         <v>277365200</v>
       </c>
-      <c r="N60" s="3">
+      <c r="O60" s="3">
         <v>273486900</v>
       </c>
-      <c r="O60" s="3">
-        <v>0</v>
-      </c>
       <c r="P60" s="3">
         <v>0</v>
       </c>
@@ -6195,240 +6334,249 @@
       <c r="AN60" s="3">
         <v>0</v>
       </c>
+      <c r="AO60" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="61" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="61" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C61" s="1" t="s">
         <v>54</v>
       </c>
       <c r="D61" s="3">
+        <v>61015700</v>
+      </c>
+      <c r="E61" s="3">
         <v>57103900</v>
       </c>
-      <c r="E61" s="3">
+      <c r="F61" s="3">
         <v>58864300</v>
       </c>
-      <c r="F61" s="3">
+      <c r="G61" s="3">
         <v>51786600</v>
       </c>
-      <c r="G61" s="3">
+      <c r="H61" s="3">
         <v>52292900</v>
       </c>
-      <c r="H61" s="3">
+      <c r="I61" s="3">
         <v>57884900</v>
       </c>
-      <c r="I61" s="3">
+      <c r="J61" s="3">
         <v>51737100</v>
       </c>
-      <c r="J61" s="3">
+      <c r="K61" s="3">
         <v>52671400</v>
       </c>
-      <c r="K61" s="3">
+      <c r="L61" s="3">
         <v>54929200</v>
       </c>
-      <c r="L61" s="3">
+      <c r="M61" s="3">
         <v>53360000</v>
       </c>
-      <c r="M61" s="3">
+      <c r="N61" s="3">
         <v>54858600</v>
       </c>
-      <c r="N61" s="3">
+      <c r="O61" s="3">
         <v>55629400</v>
       </c>
-      <c r="O61" s="3">
+      <c r="P61" s="3">
         <v>52670100</v>
       </c>
-      <c r="P61" s="3">
+      <c r="Q61" s="3">
         <v>58817800</v>
       </c>
-      <c r="Q61" s="3">
+      <c r="R61" s="3">
         <v>58413400</v>
       </c>
-      <c r="R61" s="3">
+      <c r="S61" s="3">
         <v>54512100</v>
       </c>
-      <c r="S61" s="3">
+      <c r="T61" s="3">
         <v>51506600</v>
       </c>
-      <c r="T61" s="3">
+      <c r="U61" s="3">
         <v>49335300</v>
       </c>
-      <c r="U61" s="3">
+      <c r="V61" s="3">
         <v>46999300</v>
       </c>
-      <c r="V61" s="3">
+      <c r="W61" s="3">
         <v>43329900</v>
       </c>
-      <c r="W61" s="3">
+      <c r="X61" s="3">
         <v>42586400</v>
       </c>
-      <c r="X61" s="3">
+      <c r="Y61" s="3">
         <v>38230600</v>
       </c>
-      <c r="Y61" s="3">
+      <c r="Z61" s="3">
         <v>39214800</v>
       </c>
-      <c r="Z61" s="3">
+      <c r="AA61" s="3">
         <v>43080800</v>
       </c>
-      <c r="AA61" s="3">
+      <c r="AB61" s="3">
         <v>42129500</v>
       </c>
-      <c r="AB61" s="3">
+      <c r="AC61" s="3">
         <v>44185000</v>
       </c>
-      <c r="AC61" s="3">
+      <c r="AD61" s="3">
         <v>43142100</v>
       </c>
-      <c r="AD61" s="3">
+      <c r="AE61" s="3">
         <v>40307800</v>
       </c>
-      <c r="AE61" s="3">
+      <c r="AF61" s="3">
         <v>36868700</v>
       </c>
-      <c r="AF61" s="3">
+      <c r="AG61" s="3">
         <v>34955700</v>
       </c>
-      <c r="AG61" s="3">
+      <c r="AH61" s="3">
         <v>35115500</v>
       </c>
-      <c r="AH61" s="3">
+      <c r="AI61" s="3">
         <v>34009900</v>
       </c>
-      <c r="AI61" s="3">
+      <c r="AJ61" s="3">
         <v>36941800</v>
       </c>
-      <c r="AJ61" s="3">
+      <c r="AK61" s="3">
         <v>37408900</v>
       </c>
-      <c r="AK61" s="3">
+      <c r="AL61" s="3">
         <v>35000000</v>
       </c>
-      <c r="AL61" s="3">
+      <c r="AM61" s="3">
         <v>33280700</v>
       </c>
-      <c r="AM61" s="3">
+      <c r="AN61" s="3">
         <v>34538700</v>
       </c>
-      <c r="AN61" s="3">
+      <c r="AO61" s="3">
         <v>33926000</v>
       </c>
     </row>
-    <row r="62" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="62" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C62" s="1" t="s">
         <v>55</v>
       </c>
       <c r="D62" s="3">
+        <v>46041700</v>
+      </c>
+      <c r="E62" s="3">
         <v>42772800</v>
       </c>
-      <c r="E62" s="3">
+      <c r="F62" s="3">
         <v>6912600</v>
       </c>
-      <c r="F62" s="3">
+      <c r="G62" s="3">
         <v>7918500</v>
       </c>
-      <c r="G62" s="3">
+      <c r="H62" s="3">
         <v>8428000</v>
       </c>
-      <c r="H62" s="3">
+      <c r="I62" s="3">
         <v>8065900</v>
       </c>
-      <c r="I62" s="3">
+      <c r="J62" s="3">
         <v>6973100</v>
       </c>
-      <c r="J62" s="3">
+      <c r="K62" s="3">
         <v>7766400</v>
       </c>
-      <c r="K62" s="3">
+      <c r="L62" s="3">
         <v>4724200</v>
       </c>
-      <c r="L62" s="3">
+      <c r="M62" s="3">
         <v>8885900</v>
       </c>
-      <c r="M62" s="3">
+      <c r="N62" s="3">
         <v>8657200</v>
       </c>
-      <c r="N62" s="3">
+      <c r="O62" s="3">
         <v>11788800</v>
       </c>
-      <c r="O62" s="3">
+      <c r="P62" s="3">
         <v>459600</v>
       </c>
-      <c r="P62" s="3">
+      <c r="Q62" s="3">
         <v>438000</v>
       </c>
-      <c r="Q62" s="3">
+      <c r="R62" s="3">
         <v>469900</v>
       </c>
-      <c r="R62" s="3">
+      <c r="S62" s="3">
         <v>523500</v>
       </c>
-      <c r="S62" s="3">
+      <c r="T62" s="3">
         <v>608300</v>
       </c>
-      <c r="T62" s="3">
+      <c r="U62" s="3">
         <v>663300</v>
       </c>
-      <c r="U62" s="3">
+      <c r="V62" s="3">
         <v>620300</v>
       </c>
-      <c r="V62" s="3">
+      <c r="W62" s="3">
         <v>542300</v>
       </c>
-      <c r="W62" s="3">
+      <c r="X62" s="3">
         <v>528500</v>
       </c>
-      <c r="X62" s="3">
+      <c r="Y62" s="3">
         <v>720700</v>
       </c>
-      <c r="Y62" s="3">
+      <c r="Z62" s="3">
         <v>691400</v>
       </c>
-      <c r="Z62" s="3">
+      <c r="AA62" s="3">
         <v>680000</v>
       </c>
-      <c r="AA62" s="3">
+      <c r="AB62" s="3">
         <v>570200</v>
       </c>
-      <c r="AB62" s="3">
+      <c r="AC62" s="3">
         <v>714600</v>
       </c>
-      <c r="AC62" s="3">
+      <c r="AD62" s="3">
         <v>648100</v>
       </c>
-      <c r="AD62" s="3">
+      <c r="AE62" s="3">
         <v>618700</v>
       </c>
-      <c r="AE62" s="3">
+      <c r="AF62" s="3">
         <v>520300</v>
       </c>
-      <c r="AF62" s="3">
+      <c r="AG62" s="3">
         <v>418500</v>
       </c>
-      <c r="AG62" s="3">
+      <c r="AH62" s="3">
         <v>420800</v>
       </c>
-      <c r="AH62" s="3">
+      <c r="AI62" s="3">
         <v>527700</v>
       </c>
-      <c r="AI62" s="3">
+      <c r="AJ62" s="3">
         <v>419200</v>
       </c>
-      <c r="AJ62" s="3">
+      <c r="AK62" s="3">
         <v>395900</v>
       </c>
-      <c r="AK62" s="3">
+      <c r="AL62" s="3">
         <v>382900</v>
       </c>
-      <c r="AL62" s="3">
+      <c r="AM62" s="3">
         <v>400700</v>
       </c>
-      <c r="AM62" s="3">
+      <c r="AN62" s="3">
         <v>463600</v>
       </c>
-      <c r="AN62" s="3">
+      <c r="AO62" s="3">
         <v>459900</v>
       </c>
     </row>
-    <row r="63" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="63" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C63" s="1" t="s">
         <v>56</v>
       </c>
@@ -6543,8 +6691,11 @@
       <c r="AN63" s="3">
         <v>0</v>
       </c>
+      <c r="AO63" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="64" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="64" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C64" s="1" t="s">
         <v>20</v>
       </c>
@@ -6659,8 +6810,11 @@
       <c r="AN64" s="3">
         <v>0</v>
       </c>
+      <c r="AO64" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="65" spans="2:40" x14ac:dyDescent="0.2">
+    <row r="65" spans="2:41" x14ac:dyDescent="0.2">
       <c r="C65" s="1" t="s">
         <v>57</v>
       </c>
@@ -6775,124 +6929,130 @@
       <c r="AN65" s="3">
         <v>0</v>
       </c>
+      <c r="AO65" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="66" spans="2:40" x14ac:dyDescent="0.2">
+    <row r="66" spans="2:41" x14ac:dyDescent="0.2">
       <c r="C66" s="1" t="s">
         <v>58</v>
       </c>
       <c r="D66" s="3">
+        <v>390433100</v>
+      </c>
+      <c r="E66" s="3">
         <v>391375900</v>
       </c>
-      <c r="E66" s="3">
+      <c r="F66" s="3">
         <v>368261100</v>
       </c>
-      <c r="F66" s="3">
+      <c r="G66" s="3">
         <v>337599900</v>
       </c>
-      <c r="G66" s="3">
+      <c r="H66" s="3">
         <v>331601300</v>
       </c>
-      <c r="H66" s="3">
+      <c r="I66" s="3">
         <v>386400900</v>
       </c>
-      <c r="I66" s="3">
+      <c r="J66" s="3">
         <v>343710800</v>
       </c>
-      <c r="J66" s="3">
+      <c r="K66" s="3">
         <v>350345300</v>
       </c>
-      <c r="K66" s="3">
+      <c r="L66" s="3">
         <v>358283300</v>
       </c>
-      <c r="L66" s="3">
+      <c r="M66" s="3">
         <v>336284100</v>
       </c>
-      <c r="M66" s="3">
+      <c r="N66" s="3">
         <v>341832200</v>
       </c>
-      <c r="N66" s="3">
+      <c r="O66" s="3">
         <v>341656500</v>
       </c>
-      <c r="O66" s="3">
+      <c r="P66" s="3">
         <v>338784400</v>
       </c>
-      <c r="P66" s="3">
+      <c r="Q66" s="3">
         <v>345885900</v>
       </c>
-      <c r="Q66" s="3">
+      <c r="R66" s="3">
         <v>348018900</v>
       </c>
-      <c r="R66" s="3">
+      <c r="S66" s="3">
         <v>338354200</v>
       </c>
-      <c r="S66" s="3">
+      <c r="T66" s="3">
         <v>316006400</v>
       </c>
-      <c r="T66" s="3">
+      <c r="U66" s="3">
         <v>309651700</v>
       </c>
-      <c r="U66" s="3">
+      <c r="V66" s="3">
         <v>297533600</v>
       </c>
-      <c r="V66" s="3">
+      <c r="W66" s="3">
         <v>290517700</v>
       </c>
-      <c r="W66" s="3">
+      <c r="X66" s="3">
         <v>278260300</v>
       </c>
-      <c r="X66" s="3">
+      <c r="Y66" s="3">
         <v>275726000</v>
       </c>
-      <c r="Y66" s="3">
+      <c r="Z66" s="3">
         <v>275487700</v>
       </c>
-      <c r="Z66" s="3">
+      <c r="AA66" s="3">
         <v>288675900</v>
       </c>
-      <c r="AA66" s="3">
+      <c r="AB66" s="3">
         <v>289399800</v>
       </c>
-      <c r="AB66" s="3">
+      <c r="AC66" s="3">
         <v>297278600</v>
       </c>
-      <c r="AC66" s="3">
+      <c r="AD66" s="3">
         <v>299163500</v>
       </c>
-      <c r="AD66" s="3">
+      <c r="AE66" s="3">
         <v>296968200</v>
       </c>
-      <c r="AE66" s="3">
+      <c r="AF66" s="3">
         <v>267714100</v>
       </c>
-      <c r="AF66" s="3">
+      <c r="AG66" s="3">
         <v>249559900</v>
       </c>
-      <c r="AG66" s="3">
+      <c r="AH66" s="3">
         <v>256847800</v>
       </c>
-      <c r="AH66" s="3">
+      <c r="AI66" s="3">
         <v>256582900</v>
       </c>
-      <c r="AI66" s="3">
+      <c r="AJ66" s="3">
         <v>260418000</v>
       </c>
-      <c r="AJ66" s="3">
+      <c r="AK66" s="3">
         <v>261733600</v>
       </c>
-      <c r="AK66" s="3">
+      <c r="AL66" s="3">
         <v>260311800</v>
       </c>
-      <c r="AL66" s="3">
+      <c r="AM66" s="3">
         <v>255640700</v>
       </c>
-      <c r="AM66" s="3">
+      <c r="AN66" s="3">
         <v>261266900</v>
       </c>
-      <c r="AN66" s="3">
+      <c r="AO66" s="3">
         <v>263136400</v>
       </c>
     </row>
-    <row r="67" spans="2:40" x14ac:dyDescent="0.2">
+    <row r="67" spans="2:41" x14ac:dyDescent="0.2">
       <c r="C67" s="1" t="s">
         <v>59</v>
       </c>
@@ -6933,8 +7093,9 @@
       <c r="AL67" s="3"/>
       <c r="AM67" s="3"/>
       <c r="AN67" s="3"/>
+      <c r="AO67" s="3"/>
     </row>
-    <row r="68" spans="2:40" x14ac:dyDescent="0.2">
+    <row r="68" spans="2:41" x14ac:dyDescent="0.2">
       <c r="C68" s="1" t="s">
         <v>60</v>
       </c>
@@ -7049,8 +7210,11 @@
       <c r="AN68" s="3">
         <v>0</v>
       </c>
+      <c r="AO68" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="69" spans="2:40" x14ac:dyDescent="0.2">
+    <row r="69" spans="2:41" x14ac:dyDescent="0.2">
       <c r="C69" s="1" t="s">
         <v>61</v>
       </c>
@@ -7165,8 +7329,11 @@
       <c r="AN69" s="3">
         <v>0</v>
       </c>
+      <c r="AO69" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="70" spans="2:40" x14ac:dyDescent="0.2">
+    <row r="70" spans="2:41" x14ac:dyDescent="0.2">
       <c r="C70" s="1" t="s">
         <v>62</v>
       </c>
@@ -7281,8 +7448,11 @@
       <c r="AN70" s="3">
         <v>0</v>
       </c>
+      <c r="AO70" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="71" spans="2:40" x14ac:dyDescent="0.2">
+    <row r="71" spans="2:41" x14ac:dyDescent="0.2">
       <c r="C71" s="1" t="s">
         <v>63</v>
       </c>
@@ -7397,124 +7567,130 @@
       <c r="AN71" s="3">
         <v>0</v>
       </c>
+      <c r="AO71" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="72" spans="2:40" x14ac:dyDescent="0.2">
+    <row r="72" spans="2:41" x14ac:dyDescent="0.2">
       <c r="C72" s="1" t="s">
         <v>64</v>
       </c>
       <c r="D72" s="3">
+        <v>19944300</v>
+      </c>
+      <c r="E72" s="3">
         <v>20390800</v>
       </c>
-      <c r="E72" s="3">
+      <c r="F72" s="3">
         <v>20492400</v>
       </c>
-      <c r="F72" s="3">
+      <c r="G72" s="3">
         <v>18322200</v>
       </c>
-      <c r="G72" s="3">
+      <c r="H72" s="3">
         <v>18243700</v>
       </c>
-      <c r="H72" s="3">
+      <c r="I72" s="3">
         <v>20282200</v>
       </c>
-      <c r="I72" s="3">
+      <c r="J72" s="3">
         <v>18807000</v>
       </c>
-      <c r="J72" s="3">
+      <c r="K72" s="3">
         <v>18719000</v>
       </c>
-      <c r="K72" s="3">
+      <c r="L72" s="3">
         <v>19268400</v>
       </c>
-      <c r="L72" s="3">
+      <c r="M72" s="3">
         <v>18710700</v>
       </c>
-      <c r="M72" s="3">
+      <c r="N72" s="3">
         <v>18565400</v>
       </c>
-      <c r="N72" s="3">
+      <c r="O72" s="3">
         <v>18299100</v>
       </c>
-      <c r="O72" s="3">
+      <c r="P72" s="3">
         <v>17812600</v>
       </c>
-      <c r="P72" s="3">
+      <c r="Q72" s="3">
         <v>17007700</v>
       </c>
-      <c r="Q72" s="3">
+      <c r="R72" s="3">
         <v>17130600</v>
       </c>
-      <c r="R72" s="3">
+      <c r="S72" s="3">
         <v>16662400</v>
       </c>
-      <c r="S72" s="3">
+      <c r="T72" s="3">
         <v>16044400</v>
       </c>
-      <c r="T72" s="3">
+      <c r="U72" s="3">
         <v>15764300</v>
       </c>
-      <c r="U72" s="3">
+      <c r="V72" s="3">
         <v>15298800</v>
       </c>
-      <c r="V72" s="3">
+      <c r="W72" s="3">
         <v>14524300</v>
       </c>
-      <c r="W72" s="3">
+      <c r="X72" s="3">
         <v>14258500</v>
       </c>
-      <c r="X72" s="3">
+      <c r="Y72" s="3">
         <v>14719300</v>
       </c>
-      <c r="Y72" s="3">
+      <c r="Z72" s="3">
         <v>14362200</v>
       </c>
-      <c r="Z72" s="3">
+      <c r="AA72" s="3">
         <v>15002800</v>
       </c>
-      <c r="AA72" s="3">
+      <c r="AB72" s="3">
         <v>15745800</v>
       </c>
-      <c r="AB72" s="3">
+      <c r="AC72" s="3">
         <v>15573800</v>
       </c>
-      <c r="AC72" s="3">
+      <c r="AD72" s="3">
         <v>15698600</v>
       </c>
-      <c r="AD72" s="3">
+      <c r="AE72" s="3">
         <v>15678000</v>
       </c>
-      <c r="AE72" s="3">
+      <c r="AF72" s="3">
         <v>14384700</v>
       </c>
-      <c r="AF72" s="3">
+      <c r="AG72" s="3">
         <v>13795900</v>
       </c>
-      <c r="AG72" s="3">
+      <c r="AH72" s="3">
         <v>13837700</v>
       </c>
-      <c r="AH72" s="3">
+      <c r="AI72" s="3">
         <v>13273900</v>
       </c>
-      <c r="AI72" s="3">
+      <c r="AJ72" s="3">
         <v>13745600</v>
       </c>
-      <c r="AJ72" s="3">
+      <c r="AK72" s="3">
         <v>13660700</v>
       </c>
-      <c r="AK72" s="3">
+      <c r="AL72" s="3">
         <v>13507800</v>
       </c>
-      <c r="AL72" s="3">
+      <c r="AM72" s="3">
         <v>13138800</v>
       </c>
-      <c r="AM72" s="3">
+      <c r="AN72" s="3">
         <v>13150400</v>
       </c>
-      <c r="AN72" s="3">
+      <c r="AO72" s="3">
         <v>13062800</v>
       </c>
     </row>
-    <row r="73" spans="2:40" x14ac:dyDescent="0.2">
+    <row r="73" spans="2:41" x14ac:dyDescent="0.2">
       <c r="C73" s="1" t="s">
         <v>65</v>
       </c>
@@ -7629,8 +7805,11 @@
       <c r="AN73" s="3">
         <v>0</v>
       </c>
+      <c r="AO73" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="74" spans="2:40" x14ac:dyDescent="0.2">
+    <row r="74" spans="2:41" x14ac:dyDescent="0.2">
       <c r="C74" s="1" t="s">
         <v>66</v>
       </c>
@@ -7745,8 +7924,11 @@
       <c r="AN74" s="3">
         <v>0</v>
       </c>
+      <c r="AO74" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="75" spans="2:40" x14ac:dyDescent="0.2">
+    <row r="75" spans="2:41" x14ac:dyDescent="0.2">
       <c r="C75" s="1" t="s">
         <v>67</v>
       </c>
@@ -7861,124 +8043,130 @@
       <c r="AN75" s="3">
         <v>0</v>
       </c>
+      <c r="AO75" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="76" spans="2:40" x14ac:dyDescent="0.2">
+    <row r="76" spans="2:41" x14ac:dyDescent="0.2">
       <c r="C76" s="1" t="s">
         <v>68</v>
       </c>
       <c r="D76" s="3">
+        <v>24951000</v>
+      </c>
+      <c r="E76" s="3">
         <v>25167700</v>
       </c>
-      <c r="E76" s="3">
+      <c r="F76" s="3">
         <v>25252000</v>
       </c>
-      <c r="F76" s="3">
+      <c r="G76" s="3">
         <v>22902500</v>
       </c>
-      <c r="G76" s="3">
+      <c r="H76" s="3">
         <v>23081300</v>
       </c>
-      <c r="H76" s="3">
+      <c r="I76" s="3">
         <v>25698700</v>
       </c>
-      <c r="I76" s="3">
+      <c r="J76" s="3">
         <v>24286300</v>
       </c>
-      <c r="J76" s="3">
+      <c r="K76" s="3">
         <v>23977100</v>
       </c>
-      <c r="K76" s="3">
+      <c r="L76" s="3">
         <v>24420000</v>
       </c>
-      <c r="L76" s="3">
+      <c r="M76" s="3">
         <v>23463000</v>
       </c>
-      <c r="M76" s="3">
+      <c r="N76" s="3">
         <v>22963400</v>
       </c>
-      <c r="N76" s="3">
+      <c r="O76" s="3">
         <v>22747400</v>
       </c>
-      <c r="O76" s="3">
+      <c r="P76" s="3">
         <v>21571400</v>
       </c>
-      <c r="P76" s="3">
+      <c r="Q76" s="3">
         <v>20624400</v>
       </c>
-      <c r="Q76" s="3">
+      <c r="R76" s="3">
         <v>20539800</v>
       </c>
-      <c r="R76" s="3">
+      <c r="S76" s="3">
         <v>20238100</v>
       </c>
-      <c r="S76" s="3">
+      <c r="T76" s="3">
         <v>19381500</v>
       </c>
-      <c r="T76" s="3">
+      <c r="U76" s="3">
         <v>18987000</v>
       </c>
-      <c r="U76" s="3">
+      <c r="V76" s="3">
         <v>18419400</v>
       </c>
-      <c r="V76" s="3">
+      <c r="W76" s="3">
         <v>17399500</v>
       </c>
-      <c r="W76" s="3">
+      <c r="X76" s="3">
         <v>17059700</v>
       </c>
-      <c r="X76" s="3">
+      <c r="Y76" s="3">
         <v>17519900</v>
       </c>
-      <c r="Y76" s="3">
+      <c r="Z76" s="3">
         <v>17171900</v>
       </c>
-      <c r="Z76" s="3">
+      <c r="AA76" s="3">
         <v>17677500</v>
       </c>
-      <c r="AA76" s="3">
+      <c r="AB76" s="3">
         <v>18283800</v>
       </c>
-      <c r="AB76" s="3">
+      <c r="AC76" s="3">
         <v>17718000</v>
       </c>
-      <c r="AC76" s="3">
+      <c r="AD76" s="3">
         <v>17110000</v>
       </c>
-      <c r="AD76" s="3">
+      <c r="AE76" s="3">
         <v>17117400</v>
       </c>
-      <c r="AE76" s="3">
+      <c r="AF76" s="3">
         <v>18261500</v>
       </c>
-      <c r="AF76" s="3">
+      <c r="AG76" s="3">
         <v>17579400</v>
       </c>
-      <c r="AG76" s="3">
+      <c r="AH76" s="3">
         <v>17463800</v>
       </c>
-      <c r="AH76" s="3">
+      <c r="AI76" s="3">
         <v>17085700</v>
       </c>
-      <c r="AI76" s="3">
+      <c r="AJ76" s="3">
         <v>17922000</v>
       </c>
-      <c r="AJ76" s="3">
+      <c r="AK76" s="3">
         <v>17996500</v>
       </c>
-      <c r="AK76" s="3">
+      <c r="AL76" s="3">
         <v>17825600</v>
       </c>
-      <c r="AL76" s="3">
+      <c r="AM76" s="3">
         <v>17960100</v>
       </c>
-      <c r="AM76" s="3">
+      <c r="AN76" s="3">
         <v>18347500</v>
       </c>
-      <c r="AN76" s="3">
+      <c r="AO76" s="3">
         <v>18412300</v>
       </c>
     </row>
-    <row r="77" spans="2:40" x14ac:dyDescent="0.2">
+    <row r="77" spans="2:41" x14ac:dyDescent="0.2">
       <c r="C77" s="1" t="s">
         <v>69</v>
       </c>
@@ -8093,245 +8281,254 @@
       <c r="AN77" s="3">
         <v>0</v>
       </c>
+      <c r="AO77" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="79" spans="2:40" x14ac:dyDescent="0.2">
+    <row r="79" spans="2:41" x14ac:dyDescent="0.2">
       <c r="B79" s="1" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="80" spans="2:40" x14ac:dyDescent="0.2">
+    <row r="80" spans="2:41" x14ac:dyDescent="0.2">
       <c r="C80" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D80" s="2">
+        <v>46022</v>
+      </c>
+      <c r="E80" s="2">
         <v>45930</v>
       </c>
-      <c r="E80" s="2">
+      <c r="F80" s="2">
         <v>45838</v>
       </c>
-      <c r="F80" s="2">
+      <c r="G80" s="2">
         <v>45747</v>
       </c>
-      <c r="G80" s="2">
+      <c r="H80" s="2">
         <v>45657</v>
       </c>
-      <c r="H80" s="2">
+      <c r="I80" s="2">
         <v>45565</v>
       </c>
-      <c r="I80" s="2">
+      <c r="J80" s="2">
         <v>45473</v>
       </c>
-      <c r="J80" s="2">
+      <c r="K80" s="2">
         <v>45382</v>
       </c>
-      <c r="K80" s="2">
+      <c r="L80" s="2">
         <v>45291</v>
       </c>
-      <c r="L80" s="2">
+      <c r="M80" s="2">
         <v>45199</v>
       </c>
-      <c r="M80" s="2">
+      <c r="N80" s="2">
         <v>45107</v>
       </c>
-      <c r="N80" s="2">
+      <c r="O80" s="2">
         <v>45016</v>
       </c>
-      <c r="O80" s="2">
+      <c r="P80" s="2">
         <v>44926</v>
       </c>
-      <c r="P80" s="2">
+      <c r="Q80" s="2">
         <v>44834</v>
       </c>
-      <c r="Q80" s="2">
+      <c r="R80" s="2">
         <v>44742</v>
       </c>
-      <c r="R80" s="2">
+      <c r="S80" s="2">
         <v>44651</v>
       </c>
-      <c r="S80" s="2">
+      <c r="T80" s="2">
         <v>44561</v>
       </c>
-      <c r="T80" s="2">
+      <c r="U80" s="2">
         <v>44469</v>
       </c>
-      <c r="U80" s="2">
+      <c r="V80" s="2">
         <v>44377</v>
       </c>
-      <c r="V80" s="2">
+      <c r="W80" s="2">
         <v>44286</v>
       </c>
-      <c r="W80" s="2">
+      <c r="X80" s="2">
         <v>44196</v>
       </c>
-      <c r="X80" s="2">
+      <c r="Y80" s="2">
         <v>44104</v>
       </c>
-      <c r="Y80" s="2">
+      <c r="Z80" s="2">
         <v>44012</v>
       </c>
-      <c r="Z80" s="2">
+      <c r="AA80" s="2">
         <v>43921</v>
       </c>
-      <c r="AA80" s="2">
+      <c r="AB80" s="2">
         <v>43830</v>
       </c>
-      <c r="AB80" s="2">
+      <c r="AC80" s="2">
         <v>43738</v>
       </c>
-      <c r="AC80" s="2">
+      <c r="AD80" s="2">
         <v>43646</v>
       </c>
-      <c r="AD80" s="2">
+      <c r="AE80" s="2">
         <v>43555</v>
       </c>
-      <c r="AE80" s="2">
+      <c r="AF80" s="2">
         <v>43465</v>
       </c>
-      <c r="AF80" s="2">
+      <c r="AG80" s="2">
         <v>43373</v>
       </c>
-      <c r="AG80" s="2">
+      <c r="AH80" s="2">
         <v>43281</v>
       </c>
-      <c r="AH80" s="2">
+      <c r="AI80" s="2">
         <v>43190</v>
       </c>
-      <c r="AI80" s="2">
+      <c r="AJ80" s="2">
         <v>43100</v>
       </c>
-      <c r="AJ80" s="2">
+      <c r="AK80" s="2">
         <v>43008</v>
       </c>
-      <c r="AK80" s="2">
+      <c r="AL80" s="2">
         <v>42916</v>
       </c>
-      <c r="AL80" s="2">
+      <c r="AM80" s="2">
         <v>42825</v>
       </c>
-      <c r="AM80" s="2">
+      <c r="AN80" s="2">
         <v>42735</v>
       </c>
-      <c r="AN80" s="2">
+      <c r="AO80" s="2">
         <v>42643</v>
       </c>
     </row>
-    <row r="81" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="81" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C81" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D81" s="3">
+        <v>227500</v>
+      </c>
+      <c r="E81" s="3">
         <v>885500</v>
       </c>
-      <c r="E81" s="3">
+      <c r="F81" s="3">
         <v>691100</v>
       </c>
-      <c r="F81" s="3">
+      <c r="G81" s="3">
         <v>418800</v>
       </c>
-      <c r="G81" s="3">
+      <c r="H81" s="3">
         <v>288500</v>
       </c>
-      <c r="H81" s="3">
+      <c r="I81" s="3">
         <v>688600</v>
       </c>
-      <c r="I81" s="3">
+      <c r="J81" s="3">
         <v>676000</v>
       </c>
-      <c r="J81" s="3">
+      <c r="K81" s="3">
         <v>613100</v>
       </c>
-      <c r="K81" s="3">
+      <c r="L81" s="3">
         <v>52500</v>
       </c>
-      <c r="L81" s="3">
+      <c r="M81" s="3">
         <v>668000</v>
       </c>
-      <c r="M81" s="3">
+      <c r="N81" s="3">
         <v>474700</v>
       </c>
-      <c r="N81" s="3">
+      <c r="O81" s="3">
         <v>700700</v>
       </c>
-      <c r="O81" s="3">
+      <c r="P81" s="3">
         <v>338800</v>
       </c>
-      <c r="P81" s="3">
+      <c r="Q81" s="3">
         <v>640600</v>
       </c>
-      <c r="Q81" s="3">
+      <c r="R81" s="3">
         <v>684400</v>
       </c>
-      <c r="R81" s="3">
+      <c r="S81" s="3">
         <v>631400</v>
       </c>
-      <c r="S81" s="3">
+      <c r="T81" s="3">
         <v>279500</v>
       </c>
-      <c r="T81" s="3">
+      <c r="U81" s="3">
         <v>570700</v>
       </c>
-      <c r="U81" s="3">
+      <c r="V81" s="3">
         <v>552600</v>
       </c>
-      <c r="V81" s="3">
+      <c r="W81" s="3">
         <v>482000</v>
       </c>
-      <c r="W81" s="3">
+      <c r="X81" s="3">
         <v>112600</v>
       </c>
-      <c r="X81" s="3">
+      <c r="Y81" s="3">
         <v>358800</v>
       </c>
-      <c r="Y81" s="3">
+      <c r="Z81" s="3">
         <v>100500</v>
       </c>
-      <c r="Z81" s="3">
+      <c r="AA81" s="3">
         <v>412900</v>
       </c>
-      <c r="AA81" s="3">
+      <c r="AB81" s="3">
         <v>174900</v>
       </c>
-      <c r="AB81" s="3">
+      <c r="AC81" s="3">
         <v>410100</v>
       </c>
-      <c r="AC81" s="3">
+      <c r="AD81" s="3">
         <v>537700</v>
       </c>
-      <c r="AD81" s="3">
+      <c r="AE81" s="3">
         <v>517500</v>
       </c>
-      <c r="AE81" s="3">
+      <c r="AF81" s="3">
         <v>76800</v>
       </c>
-      <c r="AF81" s="3">
+      <c r="AG81" s="3">
         <v>453900</v>
       </c>
-      <c r="AG81" s="3">
+      <c r="AH81" s="3">
         <v>569900</v>
       </c>
-      <c r="AH81" s="3">
+      <c r="AI81" s="3">
         <v>463600</v>
       </c>
-      <c r="AI81" s="3">
+      <c r="AJ81" s="3">
         <v>84900</v>
       </c>
-      <c r="AJ81" s="3">
+      <c r="AK81" s="3">
         <v>212100</v>
       </c>
-      <c r="AK81" s="3">
+      <c r="AL81" s="3">
         <v>369000</v>
       </c>
-      <c r="AL81" s="3">
+      <c r="AM81" s="3">
         <v>517600</v>
       </c>
-      <c r="AM81" s="3">
+      <c r="AN81" s="3">
         <v>88500</v>
       </c>
-      <c r="AN81" s="3">
+      <c r="AO81" s="3">
         <v>275700</v>
       </c>
     </row>
-    <row r="82" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="82" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C82" s="1" t="s">
         <v>71</v>
       </c>
@@ -8372,124 +8569,128 @@
       <c r="AL82" s="3"/>
       <c r="AM82" s="3"/>
       <c r="AN82" s="3"/>
+      <c r="AO82" s="3"/>
     </row>
-    <row r="83" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="83" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C83" s="1" t="s">
         <v>72</v>
       </c>
       <c r="D83" s="3">
+        <v>106200</v>
+      </c>
+      <c r="E83" s="3">
         <v>218200</v>
       </c>
-      <c r="E83" s="3">
+      <c r="F83" s="3">
         <v>204400</v>
       </c>
-      <c r="F83" s="3">
+      <c r="G83" s="3">
         <v>200500</v>
       </c>
-      <c r="G83" s="3">
+      <c r="H83" s="3">
         <v>173700</v>
       </c>
-      <c r="H83" s="3">
+      <c r="I83" s="3">
         <v>150800</v>
       </c>
-      <c r="I83" s="3">
+      <c r="J83" s="3">
         <v>153800</v>
       </c>
-      <c r="J83" s="3">
+      <c r="K83" s="3">
         <v>154400</v>
       </c>
-      <c r="K83" s="3">
+      <c r="L83" s="3">
         <v>162700</v>
       </c>
-      <c r="L83" s="3">
+      <c r="M83" s="3">
         <v>133200</v>
       </c>
-      <c r="M83" s="3">
+      <c r="N83" s="3">
         <v>147300</v>
       </c>
-      <c r="N83" s="3">
+      <c r="O83" s="3">
         <v>148000</v>
       </c>
-      <c r="O83" s="3">
+      <c r="P83" s="3">
         <v>185200</v>
       </c>
-      <c r="P83" s="3">
+      <c r="Q83" s="3">
         <v>169700</v>
       </c>
-      <c r="Q83" s="3">
+      <c r="R83" s="3">
         <v>175600</v>
       </c>
-      <c r="R83" s="3">
+      <c r="S83" s="3">
         <v>168600</v>
       </c>
-      <c r="S83" s="3">
+      <c r="T83" s="3">
         <v>155900</v>
       </c>
-      <c r="T83" s="3">
+      <c r="U83" s="3">
         <v>149200</v>
       </c>
-      <c r="U83" s="3">
+      <c r="V83" s="3">
         <v>184500</v>
       </c>
-      <c r="V83" s="3">
+      <c r="W83" s="3">
         <v>102900</v>
       </c>
-      <c r="W83" s="3">
+      <c r="X83" s="3">
         <v>101300</v>
       </c>
-      <c r="X83" s="3">
+      <c r="Y83" s="3">
         <v>101500</v>
       </c>
-      <c r="Y83" s="3">
+      <c r="Z83" s="3">
         <v>98700</v>
       </c>
-      <c r="Z83" s="3">
+      <c r="AA83" s="3">
         <v>112300</v>
       </c>
-      <c r="AA83" s="3">
+      <c r="AB83" s="3">
         <v>120400</v>
       </c>
-      <c r="AB83" s="3">
+      <c r="AC83" s="3">
         <v>116900</v>
       </c>
-      <c r="AC83" s="3">
+      <c r="AD83" s="3">
         <v>108900</v>
       </c>
-      <c r="AD83" s="3">
+      <c r="AE83" s="3">
         <v>93600</v>
       </c>
-      <c r="AE83" s="3">
+      <c r="AF83" s="3">
         <v>61600</v>
       </c>
-      <c r="AF83" s="3">
+      <c r="AG83" s="3">
         <v>58600</v>
       </c>
-      <c r="AG83" s="3">
+      <c r="AH83" s="3">
         <v>56000</v>
       </c>
-      <c r="AH83" s="3">
+      <c r="AI83" s="3">
         <v>50600</v>
       </c>
-      <c r="AI83" s="3">
+      <c r="AJ83" s="3">
         <v>49900</v>
       </c>
-      <c r="AJ83" s="3">
+      <c r="AK83" s="3">
         <v>50800</v>
       </c>
-      <c r="AK83" s="3">
+      <c r="AL83" s="3">
         <v>51600</v>
       </c>
-      <c r="AL83" s="3">
+      <c r="AM83" s="3">
         <v>55200</v>
       </c>
-      <c r="AM83" s="3">
+      <c r="AN83" s="3">
         <v>54800</v>
       </c>
-      <c r="AN83" s="3">
+      <c r="AO83" s="3">
         <v>53700</v>
       </c>
     </row>
-    <row r="84" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="84" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C84" s="1" t="s">
         <v>73</v>
       </c>
@@ -8604,8 +8805,11 @@
       <c r="AN84" s="3">
         <v>0</v>
       </c>
+      <c r="AO84" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="85" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="85" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C85" s="1" t="s">
         <v>74</v>
       </c>
@@ -8720,8 +8924,11 @@
       <c r="AN85" s="3">
         <v>0</v>
       </c>
+      <c r="AO85" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="86" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="86" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C86" s="1" t="s">
         <v>75</v>
       </c>
@@ -8836,8 +9043,11 @@
       <c r="AN86" s="3">
         <v>0</v>
       </c>
+      <c r="AO86" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="87" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="87" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C87" s="1" t="s">
         <v>76</v>
       </c>
@@ -8952,8 +9162,11 @@
       <c r="AN87" s="3">
         <v>0</v>
       </c>
+      <c r="AO87" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="88" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="88" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C88" s="1" t="s">
         <v>77</v>
       </c>
@@ -9068,124 +9281,130 @@
       <c r="AN88" s="3">
         <v>0</v>
       </c>
+      <c r="AO88" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="89" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="89" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C89" s="1" t="s">
         <v>78</v>
       </c>
       <c r="D89" s="3">
+        <v>-342000</v>
+      </c>
+      <c r="E89" s="3">
         <v>6204800</v>
       </c>
-      <c r="E89" s="3">
+      <c r="F89" s="3">
         <v>-4742200</v>
       </c>
-      <c r="F89" s="3">
+      <c r="G89" s="3">
         <v>-1359600</v>
       </c>
-      <c r="G89" s="3">
+      <c r="H89" s="3">
         <v>15238500</v>
       </c>
-      <c r="H89" s="3">
+      <c r="I89" s="3">
         <v>-21513100</v>
       </c>
-      <c r="I89" s="3">
+      <c r="J89" s="3">
         <v>-5708900</v>
       </c>
-      <c r="J89" s="3">
+      <c r="K89" s="3">
         <v>3028800</v>
       </c>
-      <c r="K89" s="3">
+      <c r="L89" s="3">
         <v>-13351300</v>
       </c>
-      <c r="L89" s="3">
+      <c r="M89" s="3">
         <v>3754000</v>
       </c>
-      <c r="M89" s="3">
+      <c r="N89" s="3">
         <v>-11714900</v>
       </c>
-      <c r="N89" s="3">
+      <c r="O89" s="3">
         <v>10840700</v>
       </c>
-      <c r="O89" s="3">
+      <c r="P89" s="3">
         <v>12011900</v>
       </c>
-      <c r="P89" s="3">
+      <c r="Q89" s="3">
         <v>-3350300</v>
       </c>
-      <c r="Q89" s="3">
+      <c r="R89" s="3">
         <v>-2130300</v>
       </c>
-      <c r="R89" s="3">
+      <c r="S89" s="3">
         <v>7700600</v>
       </c>
-      <c r="S89" s="3">
+      <c r="T89" s="3">
         <v>4027400</v>
       </c>
-      <c r="T89" s="3">
+      <c r="U89" s="3">
         <v>2586700</v>
       </c>
-      <c r="U89" s="3">
+      <c r="V89" s="3">
         <v>-4607300</v>
       </c>
-      <c r="V89" s="3">
+      <c r="W89" s="3">
         <v>831700</v>
       </c>
-      <c r="W89" s="3">
+      <c r="X89" s="3">
         <v>1545900</v>
       </c>
-      <c r="X89" s="3">
+      <c r="Y89" s="3">
         <v>-766500</v>
       </c>
-      <c r="Y89" s="3">
+      <c r="Z89" s="3">
         <v>2718500</v>
       </c>
-      <c r="Z89" s="3">
+      <c r="AA89" s="3">
         <v>-824700</v>
       </c>
-      <c r="AA89" s="3">
+      <c r="AB89" s="3">
         <v>-153300</v>
       </c>
-      <c r="AB89" s="3">
+      <c r="AC89" s="3">
         <v>-428600</v>
       </c>
-      <c r="AC89" s="3">
+      <c r="AD89" s="3">
         <v>3501700</v>
       </c>
-      <c r="AD89" s="3">
+      <c r="AE89" s="3">
         <v>-1296100</v>
       </c>
-      <c r="AE89" s="3">
+      <c r="AF89" s="3">
         <v>5231600</v>
       </c>
-      <c r="AF89" s="3">
+      <c r="AG89" s="3">
         <v>908000</v>
       </c>
-      <c r="AG89" s="3">
+      <c r="AH89" s="3">
         <v>643600</v>
       </c>
-      <c r="AH89" s="3">
+      <c r="AI89" s="3">
         <v>877700</v>
       </c>
-      <c r="AI89" s="3">
+      <c r="AJ89" s="3">
         <v>-506300</v>
       </c>
-      <c r="AJ89" s="3">
+      <c r="AK89" s="3">
         <v>-2456000</v>
       </c>
-      <c r="AK89" s="3">
+      <c r="AL89" s="3">
         <v>-340700</v>
       </c>
-      <c r="AL89" s="3">
+      <c r="AM89" s="3">
         <v>1561500</v>
       </c>
-      <c r="AM89" s="3">
+      <c r="AN89" s="3">
         <v>108800</v>
       </c>
-      <c r="AN89" s="3">
+      <c r="AO89" s="3">
         <v>3807600</v>
       </c>
     </row>
-    <row r="90" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="90" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C90" s="1" t="s">
         <v>79</v>
       </c>
@@ -9226,124 +9445,128 @@
       <c r="AL90" s="3"/>
       <c r="AM90" s="3"/>
       <c r="AN90" s="3"/>
+      <c r="AO90" s="3"/>
     </row>
-    <row r="91" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="91" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C91" s="1" t="s">
         <v>80</v>
       </c>
       <c r="D91" s="3">
+        <v>-142900</v>
+      </c>
+      <c r="E91" s="3">
         <v>-6100</v>
       </c>
-      <c r="E91" s="3">
+      <c r="F91" s="3">
         <v>-66200</v>
       </c>
-      <c r="F91" s="3">
+      <c r="G91" s="3">
         <v>-14600</v>
       </c>
-      <c r="G91" s="3">
+      <c r="H91" s="3">
         <v>-32300</v>
       </c>
-      <c r="H91" s="3">
+      <c r="I91" s="3">
         <v>-62500</v>
       </c>
-      <c r="I91" s="3">
+      <c r="J91" s="3">
         <v>-40100</v>
       </c>
-      <c r="J91" s="3">
+      <c r="K91" s="3">
         <v>-27400</v>
       </c>
-      <c r="K91" s="3">
+      <c r="L91" s="3">
         <v>-61300</v>
       </c>
-      <c r="L91" s="3">
+      <c r="M91" s="3">
         <v>-23300</v>
       </c>
-      <c r="M91" s="3">
+      <c r="N91" s="3">
         <v>-23900</v>
       </c>
-      <c r="N91" s="3">
+      <c r="O91" s="3">
         <v>-17100</v>
       </c>
-      <c r="O91" s="3">
+      <c r="P91" s="3">
         <v>-113722000</v>
       </c>
-      <c r="P91" s="3">
+      <c r="Q91" s="3">
         <v>-77226000</v>
       </c>
-      <c r="Q91" s="3">
+      <c r="R91" s="3">
         <v>-104059000</v>
       </c>
-      <c r="R91" s="3">
+      <c r="S91" s="3">
         <v>-52618000</v>
       </c>
-      <c r="S91" s="3">
+      <c r="T91" s="3">
         <v>-74615000</v>
       </c>
-      <c r="T91" s="3">
+      <c r="U91" s="3">
         <v>-81614000</v>
       </c>
-      <c r="U91" s="3">
+      <c r="V91" s="3">
         <v>-15900</v>
       </c>
-      <c r="V91" s="3">
+      <c r="W91" s="3">
         <v>-14300</v>
       </c>
-      <c r="W91" s="3">
+      <c r="X91" s="3">
         <v>-43600</v>
       </c>
-      <c r="X91" s="3">
+      <c r="Y91" s="3">
         <v>-25600</v>
       </c>
-      <c r="Y91" s="3">
+      <c r="Z91" s="3">
         <v>-24800</v>
       </c>
-      <c r="Z91" s="3">
+      <c r="AA91" s="3">
         <v>-20300</v>
       </c>
-      <c r="AA91" s="3">
+      <c r="AB91" s="3">
         <v>-190900</v>
       </c>
-      <c r="AB91" s="3">
+      <c r="AC91" s="3">
         <v>-91000</v>
       </c>
-      <c r="AC91" s="3">
+      <c r="AD91" s="3">
         <v>-55400</v>
       </c>
-      <c r="AD91" s="3">
+      <c r="AE91" s="3">
         <v>-31700</v>
       </c>
-      <c r="AE91" s="3">
+      <c r="AF91" s="3">
         <v>-43000</v>
       </c>
-      <c r="AF91" s="3">
+      <c r="AG91" s="3">
         <v>-20100</v>
       </c>
-      <c r="AG91" s="3">
+      <c r="AH91" s="3">
         <v>-18000</v>
       </c>
-      <c r="AH91" s="3">
+      <c r="AI91" s="3">
         <v>-17800</v>
       </c>
-      <c r="AI91" s="3">
+      <c r="AJ91" s="3">
         <v>-25100</v>
       </c>
-      <c r="AJ91" s="3">
+      <c r="AK91" s="3">
         <v>-57300</v>
       </c>
-      <c r="AK91" s="3">
+      <c r="AL91" s="3">
         <v>-37900</v>
       </c>
-      <c r="AL91" s="3">
+      <c r="AM91" s="3">
         <v>-22400</v>
       </c>
-      <c r="AM91" s="3">
+      <c r="AN91" s="3">
         <v>-111600</v>
       </c>
-      <c r="AN91" s="3">
+      <c r="AO91" s="3">
         <v>-90400</v>
       </c>
     </row>
-    <row r="92" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="92" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C92" s="1" t="s">
         <v>81</v>
       </c>
@@ -9458,8 +9681,11 @@
       <c r="AN92" s="3">
         <v>0</v>
       </c>
+      <c r="AO92" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="93" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="93" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C93" s="1" t="s">
         <v>82</v>
       </c>
@@ -9574,124 +9800,130 @@
       <c r="AN93" s="3">
         <v>0</v>
       </c>
+      <c r="AO93" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="94" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="94" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C94" s="1" t="s">
         <v>83</v>
       </c>
       <c r="D94" s="3">
+        <v>-7655100</v>
+      </c>
+      <c r="E94" s="3">
         <v>-1956500</v>
       </c>
-      <c r="E94" s="3">
+      <c r="F94" s="3">
         <v>2605800</v>
       </c>
-      <c r="F94" s="3">
+      <c r="G94" s="3">
         <v>265900</v>
       </c>
-      <c r="G94" s="3">
+      <c r="H94" s="3">
         <v>-3917800</v>
       </c>
-      <c r="H94" s="3">
+      <c r="I94" s="3">
         <v>3642700</v>
       </c>
-      <c r="I94" s="3">
+      <c r="J94" s="3">
         <v>-1092400</v>
       </c>
-      <c r="J94" s="3">
+      <c r="K94" s="3">
         <v>1841100</v>
       </c>
-      <c r="K94" s="3">
+      <c r="L94" s="3">
         <v>-625400</v>
       </c>
-      <c r="L94" s="3">
+      <c r="M94" s="3">
         <v>-1107500</v>
       </c>
-      <c r="M94" s="3">
+      <c r="N94" s="3">
         <v>-261600</v>
       </c>
-      <c r="N94" s="3">
+      <c r="O94" s="3">
         <v>300800</v>
       </c>
-      <c r="O94" s="3">
+      <c r="P94" s="3">
         <v>-2910400</v>
       </c>
-      <c r="P94" s="3">
+      <c r="Q94" s="3">
         <v>-2354900</v>
       </c>
-      <c r="Q94" s="3">
+      <c r="R94" s="3">
         <v>2353800</v>
       </c>
-      <c r="R94" s="3">
+      <c r="S94" s="3">
         <v>-2278800</v>
       </c>
-      <c r="S94" s="3">
+      <c r="T94" s="3">
         <v>-4489600</v>
       </c>
-      <c r="T94" s="3">
+      <c r="U94" s="3">
         <v>-3902300</v>
       </c>
-      <c r="U94" s="3">
+      <c r="V94" s="3">
         <v>1124900</v>
       </c>
-      <c r="V94" s="3">
+      <c r="W94" s="3">
         <v>-723400</v>
       </c>
-      <c r="W94" s="3">
+      <c r="X94" s="3">
         <v>-365200</v>
       </c>
-      <c r="X94" s="3">
+      <c r="Y94" s="3">
         <v>-124500</v>
       </c>
-      <c r="Y94" s="3">
+      <c r="Z94" s="3">
         <v>-446100</v>
       </c>
-      <c r="Z94" s="3">
+      <c r="AA94" s="3">
         <v>-179800</v>
       </c>
-      <c r="AA94" s="3">
+      <c r="AB94" s="3">
         <v>-962200</v>
       </c>
-      <c r="AB94" s="3">
+      <c r="AC94" s="3">
         <v>-913600</v>
       </c>
-      <c r="AC94" s="3">
+      <c r="AD94" s="3">
         <v>-5520900</v>
       </c>
-      <c r="AD94" s="3">
+      <c r="AE94" s="3">
         <v>-97900</v>
       </c>
-      <c r="AE94" s="3">
+      <c r="AF94" s="3">
         <v>-5105000</v>
       </c>
-      <c r="AF94" s="3">
+      <c r="AG94" s="3">
         <v>-2452600</v>
       </c>
-      <c r="AG94" s="3">
+      <c r="AH94" s="3">
         <v>-1063800</v>
       </c>
-      <c r="AH94" s="3">
+      <c r="AI94" s="3">
         <v>-587600</v>
       </c>
-      <c r="AI94" s="3">
+      <c r="AJ94" s="3">
         <v>1277600</v>
       </c>
-      <c r="AJ94" s="3">
+      <c r="AK94" s="3">
         <v>-195600</v>
       </c>
-      <c r="AK94" s="3">
+      <c r="AL94" s="3">
         <v>183200</v>
       </c>
-      <c r="AL94" s="3">
+      <c r="AM94" s="3">
         <v>392500</v>
       </c>
-      <c r="AM94" s="3">
+      <c r="AN94" s="3">
         <v>-2371700</v>
       </c>
-      <c r="AN94" s="3">
+      <c r="AO94" s="3">
         <v>694800</v>
       </c>
     </row>
-    <row r="95" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="95" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C95" s="1" t="s">
         <v>84</v>
       </c>
@@ -9732,53 +9964,54 @@
       <c r="AL95" s="3"/>
       <c r="AM95" s="3"/>
       <c r="AN95" s="3"/>
+      <c r="AO95" s="3"/>
     </row>
-    <row r="96" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="96" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C96" s="1" t="s">
         <v>85</v>
       </c>
       <c r="D96" s="3">
+        <v>127000</v>
+      </c>
+      <c r="E96" s="3">
         <v>130500</v>
       </c>
-      <c r="E96" s="3">
+      <c r="F96" s="3">
         <v>495800</v>
       </c>
-      <c r="F96" s="3">
+      <c r="G96" s="3">
         <v>26800</v>
       </c>
-      <c r="G96" s="3">
+      <c r="H96" s="3">
         <v>117000</v>
       </c>
-      <c r="H96" s="3">
+      <c r="I96" s="3">
         <v>134900</v>
       </c>
-      <c r="I96" s="3">
+      <c r="J96" s="3">
         <v>473000</v>
       </c>
-      <c r="J96" s="3">
+      <c r="K96" s="3">
         <v>26200</v>
       </c>
-      <c r="K96" s="3">
+      <c r="L96" s="3">
         <v>151100</v>
       </c>
-      <c r="L96" s="3">
+      <c r="M96" s="3">
         <v>102000</v>
       </c>
-      <c r="M96" s="3">
+      <c r="N96" s="3">
         <v>566300</v>
       </c>
-      <c r="N96" s="3">
+      <c r="O96" s="3">
         <v>23300</v>
       </c>
-      <c r="O96" s="3">
-        <v>0</v>
-      </c>
       <c r="P96" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q96" s="3">
         <v>-79700</v>
       </c>
-      <c r="Q96" s="3">
-        <v>0</v>
-      </c>
       <c r="R96" s="3">
         <v>0</v>
       </c>
@@ -9786,11 +10019,11 @@
         <v>0</v>
       </c>
       <c r="T96" s="3">
+        <v>0</v>
+      </c>
+      <c r="U96" s="3">
         <v>-81300</v>
       </c>
-      <c r="U96" s="3">
-        <v>0</v>
-      </c>
       <c r="V96" s="3">
         <v>0</v>
       </c>
@@ -9834,22 +10067,25 @@
         <v>0</v>
       </c>
       <c r="AJ96" s="3">
+        <v>0</v>
+      </c>
+      <c r="AK96" s="3">
         <v>-59200</v>
       </c>
-      <c r="AK96" s="3">
+      <c r="AL96" s="3">
         <v>-237000</v>
       </c>
-      <c r="AL96" s="3">
-        <v>0</v>
-      </c>
       <c r="AM96" s="3">
+        <v>0</v>
+      </c>
+      <c r="AN96" s="3">
         <v>-38100</v>
       </c>
-      <c r="AN96" s="3">
+      <c r="AO96" s="3">
         <v>-22800</v>
       </c>
     </row>
-    <row r="97" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="97" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C97" s="1" t="s">
         <v>86</v>
       </c>
@@ -9964,8 +10200,11 @@
       <c r="AN97" s="3">
         <v>0</v>
       </c>
+      <c r="AO97" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="98" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="98" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C98" s="1" t="s">
         <v>87</v>
       </c>
@@ -10080,8 +10319,11 @@
       <c r="AN98" s="3">
         <v>0</v>
       </c>
+      <c r="AO98" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="99" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="99" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C99" s="1" t="s">
         <v>88</v>
       </c>
@@ -10196,352 +10438,364 @@
       <c r="AN99" s="3">
         <v>0</v>
       </c>
+      <c r="AO99" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="100" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="100" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C100" s="1" t="s">
         <v>89</v>
       </c>
       <c r="D100" s="3">
+        <v>14210100</v>
+      </c>
+      <c r="E100" s="3">
         <v>-5092600</v>
       </c>
-      <c r="E100" s="3">
+      <c r="F100" s="3">
         <v>6108300</v>
       </c>
-      <c r="F100" s="3">
+      <c r="G100" s="3">
         <v>-68000</v>
       </c>
-      <c r="G100" s="3">
+      <c r="H100" s="3">
         <v>-16521000</v>
       </c>
-      <c r="H100" s="3">
+      <c r="I100" s="3">
         <v>24357600</v>
       </c>
-      <c r="I100" s="3">
+      <c r="J100" s="3">
         <v>1880400</v>
       </c>
-      <c r="J100" s="3">
+      <c r="K100" s="3">
         <v>-4107500</v>
       </c>
-      <c r="K100" s="3">
+      <c r="L100" s="3">
         <v>17753300</v>
       </c>
-      <c r="L100" s="3">
+      <c r="M100" s="3">
         <v>447300</v>
       </c>
-      <c r="M100" s="3">
+      <c r="N100" s="3">
         <v>5022900</v>
       </c>
-      <c r="N100" s="3">
+      <c r="O100" s="3">
         <v>-13746200</v>
       </c>
-      <c r="O100" s="3">
+      <c r="P100" s="3">
         <v>-5147300</v>
       </c>
-      <c r="P100" s="3">
+      <c r="Q100" s="3">
         <v>1697300</v>
       </c>
-      <c r="Q100" s="3">
+      <c r="R100" s="3">
         <v>3000400</v>
       </c>
-      <c r="R100" s="3">
+      <c r="S100" s="3">
         <v>1932700</v>
       </c>
-      <c r="S100" s="3">
+      <c r="T100" s="3">
         <v>2031800</v>
       </c>
-      <c r="T100" s="3">
+      <c r="U100" s="3">
         <v>1404600</v>
       </c>
-      <c r="U100" s="3">
+      <c r="V100" s="3">
         <v>2911000</v>
       </c>
-      <c r="V100" s="3">
+      <c r="W100" s="3">
         <v>453200</v>
       </c>
-      <c r="W100" s="3">
+      <c r="X100" s="3">
         <v>261800</v>
       </c>
-      <c r="X100" s="3">
+      <c r="Y100" s="3">
         <v>553800</v>
       </c>
-      <c r="Y100" s="3">
+      <c r="Z100" s="3">
         <v>-2356000</v>
       </c>
-      <c r="Z100" s="3">
+      <c r="AA100" s="3">
         <v>3526800</v>
       </c>
-      <c r="AA100" s="3">
+      <c r="AB100" s="3">
         <v>-950700</v>
       </c>
-      <c r="AB100" s="3">
+      <c r="AC100" s="3">
         <v>3000500</v>
       </c>
-      <c r="AC100" s="3">
+      <c r="AD100" s="3">
         <v>3588600</v>
       </c>
-      <c r="AD100" s="3">
+      <c r="AE100" s="3">
         <v>-289800</v>
       </c>
-      <c r="AE100" s="3">
+      <c r="AF100" s="3">
         <v>491400</v>
       </c>
-      <c r="AF100" s="3">
+      <c r="AG100" s="3">
         <v>1689200</v>
       </c>
-      <c r="AG100" s="3">
+      <c r="AH100" s="3">
         <v>354700</v>
       </c>
-      <c r="AH100" s="3">
+      <c r="AI100" s="3">
         <v>-1323700</v>
       </c>
-      <c r="AI100" s="3">
+      <c r="AJ100" s="3">
         <v>-309500</v>
       </c>
-      <c r="AJ100" s="3">
+      <c r="AK100" s="3">
         <v>2140800</v>
       </c>
-      <c r="AK100" s="3">
+      <c r="AL100" s="3">
         <v>-384900</v>
       </c>
-      <c r="AL100" s="3">
+      <c r="AM100" s="3">
         <v>-1500100</v>
       </c>
-      <c r="AM100" s="3">
+      <c r="AN100" s="3">
         <v>1503800</v>
       </c>
-      <c r="AN100" s="3">
+      <c r="AO100" s="3">
         <v>-1778900</v>
       </c>
     </row>
-    <row r="101" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="101" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C101" s="1" t="s">
         <v>90</v>
       </c>
       <c r="D101" s="3">
+        <v>1000100</v>
+      </c>
+      <c r="E101" s="3">
         <v>-385300</v>
       </c>
-      <c r="E101" s="3">
+      <c r="F101" s="3">
         <v>231000</v>
       </c>
-      <c r="F101" s="3">
+      <c r="G101" s="3">
         <v>262700</v>
       </c>
-      <c r="G101" s="3">
+      <c r="H101" s="3">
         <v>-179300</v>
       </c>
-      <c r="H101" s="3">
+      <c r="I101" s="3">
         <v>27300</v>
       </c>
-      <c r="I101" s="3">
+      <c r="J101" s="3">
         <v>-105100</v>
       </c>
-      <c r="J101" s="3">
+      <c r="K101" s="3">
         <v>125800</v>
       </c>
-      <c r="K101" s="3">
+      <c r="L101" s="3">
         <v>-1568200</v>
       </c>
-      <c r="L101" s="3">
+      <c r="M101" s="3">
         <v>609200</v>
       </c>
-      <c r="M101" s="3">
+      <c r="N101" s="3">
         <v>667200</v>
       </c>
-      <c r="N101" s="3">
+      <c r="O101" s="3">
         <v>217100</v>
       </c>
-      <c r="O101" s="3">
+      <c r="P101" s="3">
         <v>-1479100</v>
       </c>
-      <c r="P101" s="3">
+      <c r="Q101" s="3">
         <v>638600</v>
       </c>
-      <c r="Q101" s="3">
+      <c r="R101" s="3">
         <v>657000</v>
       </c>
-      <c r="R101" s="3">
+      <c r="S101" s="3">
         <v>203100</v>
       </c>
-      <c r="S101" s="3">
+      <c r="T101" s="3">
         <v>68900</v>
       </c>
-      <c r="T101" s="3">
+      <c r="U101" s="3">
         <v>409500</v>
       </c>
-      <c r="U101" s="3">
+      <c r="V101" s="3">
         <v>18100</v>
       </c>
-      <c r="V101" s="3">
+      <c r="W101" s="3">
         <v>295500</v>
       </c>
-      <c r="W101" s="3">
+      <c r="X101" s="3">
         <v>-571700</v>
       </c>
-      <c r="X101" s="3">
+      <c r="Y101" s="3">
         <v>-142900</v>
       </c>
-      <c r="Y101" s="3">
+      <c r="Z101" s="3">
         <v>-159900</v>
       </c>
-      <c r="Z101" s="3">
+      <c r="AA101" s="3">
         <v>200400</v>
       </c>
-      <c r="AA101" s="3">
+      <c r="AB101" s="3">
         <v>369400</v>
       </c>
-      <c r="AB101" s="3">
+      <c r="AC101" s="3">
         <v>-340600</v>
       </c>
-      <c r="AC101" s="3">
+      <c r="AD101" s="3">
         <v>51200</v>
       </c>
-      <c r="AD101" s="3">
+      <c r="AE101" s="3">
         <v>90500</v>
       </c>
-      <c r="AE101" s="3">
+      <c r="AF101" s="3">
         <v>6400</v>
       </c>
-      <c r="AF101" s="3">
+      <c r="AG101" s="3">
         <v>-76600</v>
       </c>
-      <c r="AG101" s="3">
+      <c r="AH101" s="3">
         <v>218900</v>
       </c>
-      <c r="AH101" s="3">
+      <c r="AI101" s="3">
         <v>50500</v>
       </c>
-      <c r="AI101" s="3">
+      <c r="AJ101" s="3">
         <v>-377500</v>
       </c>
-      <c r="AJ101" s="3">
+      <c r="AK101" s="3">
         <v>14000</v>
       </c>
-      <c r="AK101" s="3">
+      <c r="AL101" s="3">
         <v>8400</v>
       </c>
-      <c r="AL101" s="3">
+      <c r="AM101" s="3">
         <v>-108300</v>
       </c>
-      <c r="AM101" s="3">
+      <c r="AN101" s="3">
         <v>138000</v>
       </c>
-      <c r="AN101" s="3">
+      <c r="AO101" s="3">
         <v>-105900</v>
       </c>
     </row>
-    <row r="102" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="102" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C102" s="1" t="s">
         <v>91</v>
       </c>
       <c r="D102" s="3">
+        <v>6419800</v>
+      </c>
+      <c r="E102" s="3">
         <v>-552400</v>
       </c>
-      <c r="E102" s="3">
+      <c r="F102" s="3">
         <v>3251800</v>
       </c>
-      <c r="F102" s="3">
+      <c r="G102" s="3">
         <v>-1136400</v>
       </c>
-      <c r="G102" s="3">
+      <c r="H102" s="3">
         <v>-4200200</v>
       </c>
-      <c r="H102" s="3">
+      <c r="I102" s="3">
         <v>6101900</v>
       </c>
-      <c r="I102" s="3">
+      <c r="J102" s="3">
         <v>-4689900</v>
       </c>
-      <c r="J102" s="3">
+      <c r="K102" s="3">
         <v>1025100</v>
       </c>
-      <c r="K102" s="3">
+      <c r="L102" s="3">
         <v>3597300</v>
       </c>
-      <c r="L102" s="3">
+      <c r="M102" s="3">
         <v>3121100</v>
       </c>
-      <c r="M102" s="3">
+      <c r="N102" s="3">
         <v>-7058600</v>
       </c>
-      <c r="N102" s="3">
+      <c r="O102" s="3">
         <v>-2478800</v>
       </c>
-      <c r="O102" s="3">
+      <c r="P102" s="3">
         <v>2475100</v>
       </c>
-      <c r="P102" s="3">
+      <c r="Q102" s="3">
         <v>-3369400</v>
       </c>
-      <c r="Q102" s="3">
+      <c r="R102" s="3">
         <v>3880900</v>
       </c>
-      <c r="R102" s="3">
+      <c r="S102" s="3">
         <v>7557600</v>
       </c>
-      <c r="S102" s="3">
+      <c r="T102" s="3">
         <v>1638600</v>
       </c>
-      <c r="T102" s="3">
+      <c r="U102" s="3">
         <v>498500</v>
       </c>
-      <c r="U102" s="3">
+      <c r="V102" s="3">
         <v>-553300</v>
       </c>
-      <c r="V102" s="3">
+      <c r="W102" s="3">
         <v>857000</v>
       </c>
-      <c r="W102" s="3">
+      <c r="X102" s="3">
         <v>870800</v>
       </c>
-      <c r="X102" s="3">
+      <c r="Y102" s="3">
         <v>-480000</v>
       </c>
-      <c r="Y102" s="3">
+      <c r="Z102" s="3">
         <v>-243500</v>
       </c>
-      <c r="Z102" s="3">
+      <c r="AA102" s="3">
         <v>2722600</v>
       </c>
-      <c r="AA102" s="3">
+      <c r="AB102" s="3">
         <v>-1696800</v>
       </c>
-      <c r="AB102" s="3">
+      <c r="AC102" s="3">
         <v>1317700</v>
       </c>
-      <c r="AC102" s="3">
+      <c r="AD102" s="3">
         <v>1620600</v>
       </c>
-      <c r="AD102" s="3">
+      <c r="AE102" s="3">
         <v>-1593300</v>
       </c>
-      <c r="AE102" s="3">
+      <c r="AF102" s="3">
         <v>624400</v>
       </c>
-      <c r="AF102" s="3">
+      <c r="AG102" s="3">
         <v>68000</v>
       </c>
-      <c r="AG102" s="3">
+      <c r="AH102" s="3">
         <v>153400</v>
       </c>
-      <c r="AH102" s="3">
+      <c r="AI102" s="3">
         <v>-983000</v>
       </c>
-      <c r="AI102" s="3">
+      <c r="AJ102" s="3">
         <v>84300</v>
       </c>
-      <c r="AJ102" s="3">
+      <c r="AK102" s="3">
         <v>-496900</v>
       </c>
-      <c r="AK102" s="3">
+      <c r="AL102" s="3">
         <v>-534100</v>
       </c>
-      <c r="AL102" s="3">
+      <c r="AM102" s="3">
         <v>345600</v>
       </c>
-      <c r="AM102" s="3">
+      <c r="AN102" s="3">
         <v>-621200</v>
       </c>
-      <c r="AN102" s="3">
+      <c r="AO102" s="3">
         <v>2617600</v>
       </c>
     </row>

--- a/AAII_Financials/Quarterly/WF_QTR_FIN.xlsx
+++ b/AAII_Financials/Quarterly/WF_QTR_FIN.xlsx
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="209" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="212" uniqueCount="92">
   <si>
     <t>WF</t>
   </si>
@@ -656,311 +656,317 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet2"/>
-  <dimension ref="A5:AO102"/>
+  <dimension ref="A5:AP102"/>
   <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="5" style="1" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="26.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="69.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="15" width="16" style="1" bestFit="1" customWidth="1"/>
-    <col min="16" max="16" width="17" style="1" bestFit="1" customWidth="1"/>
-    <col min="17" max="17" width="16" style="1" bestFit="1" customWidth="1"/>
-    <col min="18" max="18" width="17" style="1" bestFit="1" customWidth="1"/>
-    <col min="19" max="41" width="16" style="1" bestFit="1" customWidth="1"/>
-    <col min="42" max="16384" width="9.140625" style="1"/>
+    <col min="4" max="16" width="16" style="1" bestFit="1" customWidth="1"/>
+    <col min="17" max="17" width="17" style="1" bestFit="1" customWidth="1"/>
+    <col min="18" max="18" width="16" style="1" bestFit="1" customWidth="1"/>
+    <col min="19" max="19" width="17" style="1" bestFit="1" customWidth="1"/>
+    <col min="20" max="42" width="16" style="1" bestFit="1" customWidth="1"/>
+    <col min="43" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
-    <row r="5" spans="1:41" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:42" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:41" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:42" x14ac:dyDescent="0.2">
       <c r="B6" s="1" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:41" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:42" x14ac:dyDescent="0.2">
       <c r="C7" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D7" s="2">
+        <v>46112</v>
+      </c>
+      <c r="E7" s="2">
         <v>46022</v>
       </c>
-      <c r="E7" s="2">
+      <c r="F7" s="2">
         <v>45930</v>
       </c>
-      <c r="F7" s="2">
+      <c r="G7" s="2">
         <v>45838</v>
       </c>
-      <c r="G7" s="2">
+      <c r="H7" s="2">
         <v>45747</v>
       </c>
-      <c r="H7" s="2">
+      <c r="I7" s="2">
         <v>45657</v>
       </c>
-      <c r="I7" s="2">
+      <c r="J7" s="2">
         <v>45565</v>
       </c>
-      <c r="J7" s="2">
+      <c r="K7" s="2">
         <v>45473</v>
       </c>
-      <c r="K7" s="2">
+      <c r="L7" s="2">
         <v>45382</v>
       </c>
-      <c r="L7" s="2">
+      <c r="M7" s="2">
         <v>45291</v>
       </c>
-      <c r="M7" s="2">
+      <c r="N7" s="2">
         <v>45199</v>
       </c>
-      <c r="N7" s="2">
+      <c r="O7" s="2">
         <v>45107</v>
       </c>
-      <c r="O7" s="2">
+      <c r="P7" s="2">
         <v>45016</v>
       </c>
-      <c r="P7" s="2">
+      <c r="Q7" s="2">
         <v>44926</v>
       </c>
-      <c r="Q7" s="2">
+      <c r="R7" s="2">
         <v>44834</v>
       </c>
-      <c r="R7" s="2">
+      <c r="S7" s="2">
         <v>44742</v>
       </c>
-      <c r="S7" s="2">
+      <c r="T7" s="2">
         <v>44651</v>
       </c>
-      <c r="T7" s="2">
+      <c r="U7" s="2">
         <v>44561</v>
       </c>
-      <c r="U7" s="2">
+      <c r="V7" s="2">
         <v>44469</v>
       </c>
-      <c r="V7" s="2">
+      <c r="W7" s="2">
         <v>44377</v>
       </c>
-      <c r="W7" s="2">
+      <c r="X7" s="2">
         <v>44286</v>
       </c>
-      <c r="X7" s="2">
+      <c r="Y7" s="2">
         <v>44196</v>
       </c>
-      <c r="Y7" s="2">
+      <c r="Z7" s="2">
         <v>44104</v>
       </c>
-      <c r="Z7" s="2">
+      <c r="AA7" s="2">
         <v>44012</v>
       </c>
-      <c r="AA7" s="2">
+      <c r="AB7" s="2">
         <v>43921</v>
       </c>
-      <c r="AB7" s="2">
+      <c r="AC7" s="2">
         <v>43830</v>
       </c>
-      <c r="AC7" s="2">
+      <c r="AD7" s="2">
         <v>43738</v>
       </c>
-      <c r="AD7" s="2">
+      <c r="AE7" s="2">
         <v>43646</v>
       </c>
-      <c r="AE7" s="2">
+      <c r="AF7" s="2">
         <v>43555</v>
       </c>
-      <c r="AF7" s="2">
+      <c r="AG7" s="2">
         <v>43465</v>
       </c>
-      <c r="AG7" s="2">
+      <c r="AH7" s="2">
         <v>43373</v>
       </c>
-      <c r="AH7" s="2">
+      <c r="AI7" s="2">
         <v>43281</v>
       </c>
-      <c r="AI7" s="2">
+      <c r="AJ7" s="2">
         <v>43190</v>
       </c>
-      <c r="AJ7" s="2">
+      <c r="AK7" s="2">
         <v>43100</v>
       </c>
-      <c r="AK7" s="2">
+      <c r="AL7" s="2">
         <v>43008</v>
       </c>
-      <c r="AL7" s="2">
+      <c r="AM7" s="2">
         <v>42916</v>
       </c>
-      <c r="AM7" s="2">
+      <c r="AN7" s="2">
         <v>42825</v>
       </c>
-      <c r="AN7" s="2">
+      <c r="AO7" s="2">
         <v>42735</v>
       </c>
-      <c r="AO7" s="2">
+      <c r="AP7" s="2">
         <v>42643</v>
       </c>
     </row>
-    <row r="8" spans="1:41" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:42" x14ac:dyDescent="0.2">
       <c r="C8" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D8" s="3">
+        <v>1705600</v>
+      </c>
+      <c r="E8" s="3">
         <v>1799400</v>
       </c>
-      <c r="E8" s="3">
+      <c r="F8" s="3">
         <v>1758000</v>
       </c>
-      <c r="F8" s="3">
+      <c r="G8" s="3">
         <v>1657300</v>
       </c>
-      <c r="G8" s="3">
-        <v>1801500</v>
-      </c>
       <c r="H8" s="3">
+        <v>1664100</v>
+      </c>
+      <c r="I8" s="3">
         <v>1663000</v>
       </c>
-      <c r="I8" s="3">
+      <c r="J8" s="3">
         <v>1889100</v>
       </c>
-      <c r="J8" s="3">
+      <c r="K8" s="3">
         <v>1489700</v>
       </c>
-      <c r="K8" s="3">
+      <c r="L8" s="3">
         <v>2219900</v>
       </c>
-      <c r="L8" s="3">
+      <c r="M8" s="3">
         <v>1264600</v>
       </c>
-      <c r="M8" s="3">
+      <c r="N8" s="3">
         <v>2101400</v>
       </c>
-      <c r="N8" s="3">
+      <c r="O8" s="3">
         <v>1748600</v>
       </c>
-      <c r="O8" s="3">
+      <c r="P8" s="3">
         <v>2091700</v>
       </c>
-      <c r="P8" s="3">
+      <c r="Q8" s="3">
         <v>3462200</v>
       </c>
-      <c r="Q8" s="3">
+      <c r="R8" s="3">
         <v>2792200</v>
       </c>
-      <c r="R8" s="3">
+      <c r="S8" s="3">
         <v>2487200</v>
       </c>
-      <c r="S8" s="3">
+      <c r="T8" s="3">
         <v>2264400</v>
       </c>
-      <c r="T8" s="3">
+      <c r="U8" s="3">
         <v>2026000</v>
       </c>
-      <c r="U8" s="3">
+      <c r="V8" s="3">
         <v>1862200</v>
       </c>
-      <c r="V8" s="3">
+      <c r="W8" s="3">
         <v>1787500</v>
       </c>
-      <c r="W8" s="3">
+      <c r="X8" s="3">
         <v>1722100</v>
       </c>
-      <c r="X8" s="3">
+      <c r="Y8" s="3">
         <v>1728200</v>
       </c>
-      <c r="Y8" s="3">
+      <c r="Z8" s="3">
         <v>1749800</v>
       </c>
-      <c r="Z8" s="3">
+      <c r="AA8" s="3">
         <v>1857400</v>
       </c>
-      <c r="AA8" s="3">
+      <c r="AB8" s="3">
         <v>2028100</v>
       </c>
-      <c r="AB8" s="3">
+      <c r="AC8" s="3">
         <v>2216400</v>
       </c>
-      <c r="AC8" s="3">
+      <c r="AD8" s="3">
         <v>2287800</v>
       </c>
-      <c r="AD8" s="3">
+      <c r="AE8" s="3">
         <v>2353100</v>
       </c>
-      <c r="AE8" s="3">
+      <c r="AF8" s="3">
         <v>2369400</v>
       </c>
-      <c r="AF8" s="3">
+      <c r="AG8" s="3">
         <v>2154000</v>
       </c>
-      <c r="AG8" s="3">
+      <c r="AH8" s="3">
         <v>2006200</v>
       </c>
-      <c r="AH8" s="3">
+      <c r="AI8" s="3">
         <v>1989700</v>
       </c>
-      <c r="AI8" s="3">
+      <c r="AJ8" s="3">
         <v>1910800</v>
       </c>
-      <c r="AJ8" s="3">
+      <c r="AK8" s="3">
         <v>1912500</v>
       </c>
-      <c r="AK8" s="3">
+      <c r="AL8" s="3">
         <v>1925300</v>
       </c>
-      <c r="AL8" s="3">
+      <c r="AM8" s="3">
         <v>1853100</v>
       </c>
-      <c r="AM8" s="3">
+      <c r="AN8" s="3">
         <v>1833700</v>
       </c>
-      <c r="AN8" s="3">
+      <c r="AO8" s="3">
         <v>1898800</v>
       </c>
-      <c r="AO8" s="3">
+      <c r="AP8" s="3">
         <v>1898000</v>
       </c>
     </row>
-    <row r="9" spans="1:41" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:42" x14ac:dyDescent="0.2">
       <c r="C9" s="1" t="s">
         <v>4</v>
       </c>
       <c r="D9" s="3">
+        <v>5700</v>
+      </c>
+      <c r="E9" s="3">
         <v>6600</v>
       </c>
-      <c r="E9" s="3">
+      <c r="F9" s="3">
         <v>6800</v>
       </c>
-      <c r="F9" s="3">
+      <c r="G9" s="3">
         <v>6400</v>
       </c>
-      <c r="G9" s="3">
+      <c r="H9" s="3">
         <v>5900</v>
       </c>
-      <c r="H9" s="3">
+      <c r="I9" s="3">
         <v>7000</v>
       </c>
-      <c r="I9" s="3">
+      <c r="J9" s="3">
         <v>7600</v>
       </c>
-      <c r="J9" s="3">
+      <c r="K9" s="3">
         <v>7000</v>
       </c>
-      <c r="K9" s="3">
+      <c r="L9" s="3">
         <v>7100</v>
       </c>
-      <c r="L9" s="3">
+      <c r="M9" s="3">
         <v>9400</v>
-      </c>
-      <c r="M9" s="3">
-        <v>6800</v>
       </c>
       <c r="N9" s="3">
         <v>6800</v>
       </c>
       <c r="O9" s="3">
+        <v>6800</v>
+      </c>
+      <c r="P9" s="3">
         <v>7100</v>
       </c>
-      <c r="P9" s="3" t="s">
-        <v>5</v>
-      </c>
       <c r="Q9" s="3" t="s">
         <v>5</v>
       </c>
@@ -1036,50 +1042,53 @@
       <c r="AO9" s="3" t="s">
         <v>5</v>
       </c>
+      <c r="AP9" s="3" t="s">
+        <v>5</v>
+      </c>
     </row>
-    <row r="10" spans="1:41" x14ac:dyDescent="0.2">
+    <row r="10" spans="1:42" x14ac:dyDescent="0.2">
       <c r="C10" s="1" t="s">
         <v>6</v>
       </c>
       <c r="D10" s="3">
+        <v>1700000</v>
+      </c>
+      <c r="E10" s="3">
         <v>1792700</v>
       </c>
-      <c r="E10" s="3">
+      <c r="F10" s="3">
         <v>1751200</v>
       </c>
-      <c r="F10" s="3">
+      <c r="G10" s="3">
         <v>1650900</v>
       </c>
-      <c r="G10" s="3">
-        <v>1795600</v>
-      </c>
       <c r="H10" s="3">
+        <v>1658200</v>
+      </c>
+      <c r="I10" s="3">
         <v>1656000</v>
       </c>
-      <c r="I10" s="3">
+      <c r="J10" s="3">
         <v>1881500</v>
       </c>
-      <c r="J10" s="3">
+      <c r="K10" s="3">
         <v>1482800</v>
       </c>
-      <c r="K10" s="3">
+      <c r="L10" s="3">
         <v>2212800</v>
       </c>
-      <c r="L10" s="3">
+      <c r="M10" s="3">
         <v>1255200</v>
       </c>
-      <c r="M10" s="3">
+      <c r="N10" s="3">
         <v>2094600</v>
       </c>
-      <c r="N10" s="3">
+      <c r="O10" s="3">
         <v>1741800</v>
       </c>
-      <c r="O10" s="3">
+      <c r="P10" s="3">
         <v>2084600</v>
       </c>
-      <c r="P10" s="3" t="s">
-        <v>5</v>
-      </c>
       <c r="Q10" s="3" t="s">
         <v>5</v>
       </c>
@@ -1155,8 +1164,11 @@
       <c r="AO10" s="3" t="s">
         <v>5</v>
       </c>
+      <c r="AP10" s="3" t="s">
+        <v>5</v>
+      </c>
     </row>
-    <row r="11" spans="1:41" x14ac:dyDescent="0.2">
+    <row r="11" spans="1:42" x14ac:dyDescent="0.2">
       <c r="C11" s="1" t="s">
         <v>7</v>
       </c>
@@ -1198,8 +1210,9 @@
       <c r="AM11" s="3"/>
       <c r="AN11" s="3"/>
       <c r="AO11" s="3"/>
+      <c r="AP11" s="3"/>
     </row>
-    <row r="12" spans="1:41" x14ac:dyDescent="0.2">
+    <row r="12" spans="1:42" x14ac:dyDescent="0.2">
       <c r="C12" s="1" t="s">
         <v>8</v>
       </c>
@@ -1317,8 +1330,11 @@
       <c r="AO12" s="3" t="s">
         <v>5</v>
       </c>
+      <c r="AP12" s="3" t="s">
+        <v>5</v>
+      </c>
     </row>
-    <row r="13" spans="1:41" x14ac:dyDescent="0.2">
+    <row r="13" spans="1:42" x14ac:dyDescent="0.2">
       <c r="C13" s="1" t="s">
         <v>9</v>
       </c>
@@ -1436,50 +1452,53 @@
       <c r="AO13" s="3">
         <v>0</v>
       </c>
+      <c r="AP13" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="14" spans="1:41" x14ac:dyDescent="0.2">
+    <row r="14" spans="1:42" x14ac:dyDescent="0.2">
       <c r="C14" s="1" t="s">
         <v>10</v>
       </c>
       <c r="D14" s="3">
-        <v>481100</v>
+        <v>4100</v>
       </c>
       <c r="E14" s="3">
+        <v>78600</v>
+      </c>
+      <c r="F14" s="3">
         <v>-385700</v>
       </c>
-      <c r="F14" s="3">
+      <c r="G14" s="3">
         <v>23100</v>
       </c>
-      <c r="G14" s="3">
-        <v>800</v>
-      </c>
       <c r="H14" s="3">
+        <v>200</v>
+      </c>
+      <c r="I14" s="3">
         <v>6200</v>
       </c>
-      <c r="I14" s="3">
-        <v>0</v>
-      </c>
       <c r="J14" s="3">
+        <v>0</v>
+      </c>
+      <c r="K14" s="3">
         <v>8400</v>
       </c>
-      <c r="K14" s="3">
+      <c r="L14" s="3">
         <v>12300</v>
       </c>
-      <c r="L14" s="3">
+      <c r="M14" s="3">
         <v>-1700</v>
       </c>
-      <c r="M14" s="3">
-        <v>0</v>
-      </c>
       <c r="N14" s="3">
+        <v>0</v>
+      </c>
+      <c r="O14" s="3">
         <v>-200</v>
       </c>
-      <c r="O14" s="3">
+      <c r="P14" s="3">
         <v>42300</v>
       </c>
-      <c r="P14" s="3">
-        <v>0</v>
-      </c>
       <c r="Q14" s="3">
         <v>0</v>
       </c>
@@ -1555,127 +1574,133 @@
       <c r="AO14" s="3">
         <v>0</v>
       </c>
+      <c r="AP14" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="15" spans="1:41" x14ac:dyDescent="0.2">
+    <row r="15" spans="1:42" x14ac:dyDescent="0.2">
       <c r="C15" s="1" t="s">
         <v>11</v>
       </c>
       <c r="D15" s="3">
+        <v>208900</v>
+      </c>
+      <c r="E15" s="3">
         <v>291800</v>
       </c>
-      <c r="E15" s="3">
+      <c r="F15" s="3">
         <v>111700</v>
       </c>
-      <c r="F15" s="3">
+      <c r="G15" s="3">
         <v>112700</v>
       </c>
-      <c r="G15" s="3">
+      <c r="H15" s="3">
         <v>210100</v>
       </c>
-      <c r="H15" s="3">
+      <c r="I15" s="3">
         <v>282800</v>
       </c>
-      <c r="I15" s="3">
+      <c r="J15" s="3">
         <v>108500</v>
       </c>
-      <c r="J15" s="3">
+      <c r="K15" s="3">
         <v>6300</v>
       </c>
-      <c r="K15" s="3">
+      <c r="L15" s="3">
         <v>205400</v>
       </c>
-      <c r="L15" s="3">
+      <c r="M15" s="3">
         <v>144200</v>
       </c>
-      <c r="M15" s="3">
+      <c r="N15" s="3">
         <v>130600</v>
       </c>
-      <c r="N15" s="3">
+      <c r="O15" s="3">
         <v>130000</v>
       </c>
-      <c r="O15" s="3">
+      <c r="P15" s="3">
         <v>130100</v>
       </c>
-      <c r="P15" s="3">
+      <c r="Q15" s="3">
         <v>-101500</v>
       </c>
-      <c r="Q15" s="3">
+      <c r="R15" s="3">
         <v>-92100</v>
       </c>
-      <c r="R15" s="3">
+      <c r="S15" s="3">
         <v>-100700</v>
       </c>
-      <c r="S15" s="3">
+      <c r="T15" s="3">
         <v>-101400</v>
       </c>
-      <c r="T15" s="3">
+      <c r="U15" s="3">
         <v>-98200</v>
       </c>
-      <c r="U15" s="3">
+      <c r="V15" s="3">
         <v>-97600</v>
       </c>
-      <c r="V15" s="3">
+      <c r="W15" s="3">
         <v>-97400</v>
       </c>
-      <c r="W15" s="3">
+      <c r="X15" s="3">
         <v>-100600</v>
       </c>
-      <c r="X15" s="3">
+      <c r="Y15" s="3">
         <v>-99400</v>
       </c>
-      <c r="Y15" s="3">
+      <c r="Z15" s="3">
         <v>-99600</v>
       </c>
-      <c r="Z15" s="3">
+      <c r="AA15" s="3">
         <v>-96100</v>
       </c>
-      <c r="AA15" s="3">
+      <c r="AB15" s="3">
         <v>-109500</v>
       </c>
-      <c r="AB15" s="3">
+      <c r="AC15" s="3">
         <v>-115200</v>
       </c>
-      <c r="AC15" s="3">
+      <c r="AD15" s="3">
         <v>-112100</v>
       </c>
-      <c r="AD15" s="3">
+      <c r="AE15" s="3">
         <v>-104100</v>
       </c>
-      <c r="AE15" s="3">
+      <c r="AF15" s="3">
         <v>-88900</v>
       </c>
-      <c r="AF15" s="3">
+      <c r="AG15" s="3">
         <v>-50500</v>
       </c>
-      <c r="AG15" s="3">
+      <c r="AH15" s="3">
         <v>-47800</v>
       </c>
-      <c r="AH15" s="3">
+      <c r="AI15" s="3">
         <v>-44700</v>
       </c>
-      <c r="AI15" s="3">
+      <c r="AJ15" s="3">
         <v>-40700</v>
       </c>
-      <c r="AJ15" s="3">
+      <c r="AK15" s="3">
         <v>-39500</v>
       </c>
-      <c r="AK15" s="3">
+      <c r="AL15" s="3">
         <v>-40300</v>
       </c>
-      <c r="AL15" s="3">
+      <c r="AM15" s="3">
         <v>-40800</v>
       </c>
-      <c r="AM15" s="3">
+      <c r="AN15" s="3">
         <v>-44500</v>
       </c>
-      <c r="AN15" s="3">
+      <c r="AO15" s="3">
         <v>-54800</v>
       </c>
-      <c r="AO15" s="3">
+      <c r="AP15" s="3">
         <v>-53700</v>
       </c>
     </row>
-    <row r="16" spans="1:41" x14ac:dyDescent="0.2">
+    <row r="16" spans="1:42" x14ac:dyDescent="0.2">
       <c r="D16" s="3"/>
       <c r="E16" s="3"/>
       <c r="F16" s="3"/>
@@ -1714,246 +1739,253 @@
       <c r="AM16" s="3"/>
       <c r="AN16" s="3"/>
       <c r="AO16" s="3"/>
+      <c r="AP16" s="3"/>
     </row>
-    <row r="17" spans="3:41" x14ac:dyDescent="0.2">
+    <row r="17" spans="3:42" x14ac:dyDescent="0.2">
       <c r="C17" s="1" t="s">
         <v>12</v>
       </c>
       <c r="D17" s="3">
+        <v>1164700</v>
+      </c>
+      <c r="E17" s="3">
         <v>1298800</v>
       </c>
-      <c r="E17" s="3">
+      <c r="F17" s="3">
         <v>1041000</v>
       </c>
-      <c r="F17" s="3">
+      <c r="G17" s="3">
         <v>826800</v>
       </c>
-      <c r="G17" s="3">
-        <v>1211300</v>
-      </c>
       <c r="H17" s="3">
+        <v>1073900</v>
+      </c>
+      <c r="I17" s="3">
         <v>1203500</v>
       </c>
-      <c r="I17" s="3">
+      <c r="J17" s="3">
         <v>979300</v>
       </c>
-      <c r="J17" s="3">
+      <c r="K17" s="3">
         <v>578900</v>
       </c>
-      <c r="K17" s="3">
+      <c r="L17" s="3">
         <v>1363800</v>
       </c>
-      <c r="L17" s="3">
+      <c r="M17" s="3">
         <v>1160500</v>
       </c>
-      <c r="M17" s="3">
+      <c r="N17" s="3">
         <v>1189600</v>
       </c>
-      <c r="N17" s="3">
+      <c r="O17" s="3">
         <v>1049500</v>
       </c>
-      <c r="O17" s="3">
+      <c r="P17" s="3">
         <v>1131700</v>
       </c>
-      <c r="P17" s="3">
+      <c r="Q17" s="3">
         <v>1897900</v>
       </c>
-      <c r="Q17" s="3">
+      <c r="R17" s="3">
         <v>1245200</v>
       </c>
-      <c r="R17" s="3">
+      <c r="S17" s="3">
         <v>1121400</v>
       </c>
-      <c r="S17" s="3">
+      <c r="T17" s="3">
         <v>861300</v>
       </c>
-      <c r="T17" s="3">
+      <c r="U17" s="3">
         <v>772200</v>
       </c>
-      <c r="U17" s="3">
+      <c r="V17" s="3">
         <v>616800</v>
       </c>
-      <c r="V17" s="3">
+      <c r="W17" s="3">
         <v>573600</v>
       </c>
-      <c r="W17" s="3">
+      <c r="X17" s="3">
         <v>625700</v>
       </c>
-      <c r="X17" s="3">
+      <c r="Y17" s="3">
         <v>727900</v>
       </c>
-      <c r="Y17" s="3">
+      <c r="Z17" s="3">
         <v>721100</v>
       </c>
-      <c r="Z17" s="3">
+      <c r="AA17" s="3">
         <v>966200</v>
       </c>
-      <c r="AA17" s="3">
+      <c r="AB17" s="3">
         <v>926000</v>
       </c>
-      <c r="AB17" s="3">
+      <c r="AC17" s="3">
         <v>1019500</v>
       </c>
-      <c r="AC17" s="3">
+      <c r="AD17" s="3">
         <v>1190700</v>
       </c>
-      <c r="AD17" s="3">
+      <c r="AE17" s="3">
         <v>1111900</v>
       </c>
-      <c r="AE17" s="3">
+      <c r="AF17" s="3">
         <v>1098300</v>
       </c>
-      <c r="AF17" s="3">
+      <c r="AG17" s="3">
         <v>1157200</v>
       </c>
-      <c r="AG17" s="3">
+      <c r="AH17" s="3">
         <v>918800</v>
       </c>
-      <c r="AH17" s="3">
+      <c r="AI17" s="3">
         <v>752200</v>
       </c>
-      <c r="AI17" s="3">
+      <c r="AJ17" s="3">
         <v>877900</v>
       </c>
-      <c r="AJ17" s="3">
+      <c r="AK17" s="3">
         <v>1026000</v>
       </c>
-      <c r="AK17" s="3">
+      <c r="AL17" s="3">
         <v>926800</v>
       </c>
-      <c r="AL17" s="3">
+      <c r="AM17" s="3">
         <v>906500</v>
       </c>
-      <c r="AM17" s="3">
+      <c r="AN17" s="3">
         <v>830000</v>
       </c>
-      <c r="AN17" s="3">
+      <c r="AO17" s="3">
         <v>903100</v>
       </c>
-      <c r="AO17" s="3">
+      <c r="AP17" s="3">
         <v>963600</v>
       </c>
     </row>
-    <row r="18" spans="3:41" x14ac:dyDescent="0.2">
+    <row r="18" spans="3:42" x14ac:dyDescent="0.2">
       <c r="C18" s="1" t="s">
         <v>13</v>
       </c>
       <c r="D18" s="3">
+        <v>540900</v>
+      </c>
+      <c r="E18" s="3">
         <v>500500</v>
       </c>
-      <c r="E18" s="3">
+      <c r="F18" s="3">
         <v>717000</v>
       </c>
-      <c r="F18" s="3">
+      <c r="G18" s="3">
         <v>830500</v>
       </c>
-      <c r="G18" s="3">
+      <c r="H18" s="3">
         <v>590100</v>
       </c>
-      <c r="H18" s="3">
+      <c r="I18" s="3">
         <v>459500</v>
       </c>
-      <c r="I18" s="3">
+      <c r="J18" s="3">
         <v>909700</v>
       </c>
-      <c r="J18" s="3">
+      <c r="K18" s="3">
         <v>910800</v>
       </c>
-      <c r="K18" s="3">
+      <c r="L18" s="3">
         <v>856000</v>
       </c>
-      <c r="L18" s="3">
+      <c r="M18" s="3">
         <v>104100</v>
       </c>
-      <c r="M18" s="3">
+      <c r="N18" s="3">
         <v>911700</v>
       </c>
-      <c r="N18" s="3">
+      <c r="O18" s="3">
         <v>699100</v>
       </c>
-      <c r="O18" s="3">
+      <c r="P18" s="3">
         <v>960100</v>
       </c>
-      <c r="P18" s="3">
+      <c r="Q18" s="3">
         <v>1564300</v>
       </c>
-      <c r="Q18" s="3">
+      <c r="R18" s="3">
         <v>1547000</v>
       </c>
-      <c r="R18" s="3">
+      <c r="S18" s="3">
         <v>1365800</v>
       </c>
-      <c r="S18" s="3">
+      <c r="T18" s="3">
         <v>1403000</v>
       </c>
-      <c r="T18" s="3">
+      <c r="U18" s="3">
         <v>1253800</v>
       </c>
-      <c r="U18" s="3">
+      <c r="V18" s="3">
         <v>1245400</v>
       </c>
-      <c r="V18" s="3">
+      <c r="W18" s="3">
         <v>1213900</v>
       </c>
-      <c r="W18" s="3">
+      <c r="X18" s="3">
         <v>1096400</v>
       </c>
-      <c r="X18" s="3">
+      <c r="Y18" s="3">
         <v>1000300</v>
       </c>
-      <c r="Y18" s="3">
+      <c r="Z18" s="3">
         <v>1028700</v>
       </c>
-      <c r="Z18" s="3">
+      <c r="AA18" s="3">
         <v>891200</v>
       </c>
-      <c r="AA18" s="3">
+      <c r="AB18" s="3">
         <v>1102100</v>
       </c>
-      <c r="AB18" s="3">
+      <c r="AC18" s="3">
         <v>1196900</v>
       </c>
-      <c r="AC18" s="3">
+      <c r="AD18" s="3">
         <v>1097100</v>
       </c>
-      <c r="AD18" s="3">
+      <c r="AE18" s="3">
         <v>1241200</v>
       </c>
-      <c r="AE18" s="3">
+      <c r="AF18" s="3">
         <v>1271100</v>
       </c>
-      <c r="AF18" s="3">
+      <c r="AG18" s="3">
         <v>996800</v>
       </c>
-      <c r="AG18" s="3">
+      <c r="AH18" s="3">
         <v>1087400</v>
       </c>
-      <c r="AH18" s="3">
+      <c r="AI18" s="3">
         <v>1237400</v>
       </c>
-      <c r="AI18" s="3">
+      <c r="AJ18" s="3">
         <v>1032900</v>
       </c>
-      <c r="AJ18" s="3">
+      <c r="AK18" s="3">
         <v>886500</v>
       </c>
-      <c r="AK18" s="3">
+      <c r="AL18" s="3">
         <v>998500</v>
       </c>
-      <c r="AL18" s="3">
+      <c r="AM18" s="3">
         <v>946600</v>
       </c>
-      <c r="AM18" s="3">
+      <c r="AN18" s="3">
         <v>1003700</v>
       </c>
-      <c r="AN18" s="3">
+      <c r="AO18" s="3">
         <v>995700</v>
       </c>
-      <c r="AO18" s="3">
+      <c r="AP18" s="3">
         <v>934400</v>
       </c>
     </row>
-    <row r="19" spans="3:41" x14ac:dyDescent="0.2">
+    <row r="19" spans="3:42" x14ac:dyDescent="0.2">
       <c r="C19" s="1" t="s">
         <v>14</v>
       </c>
@@ -1995,246 +2027,253 @@
       <c r="AM19" s="3"/>
       <c r="AN19" s="3"/>
       <c r="AO19" s="3"/>
+      <c r="AP19" s="3"/>
     </row>
-    <row r="20" spans="3:41" x14ac:dyDescent="0.2">
+    <row r="20" spans="3:42" x14ac:dyDescent="0.2">
       <c r="C20" s="1" t="s">
         <v>15</v>
       </c>
       <c r="D20" s="3">
-        <v>-333900</v>
+        <v>-20400</v>
       </c>
       <c r="E20" s="3">
+        <v>68600</v>
+      </c>
+      <c r="F20" s="3">
         <v>14200</v>
       </c>
-      <c r="F20" s="3">
+      <c r="G20" s="3">
         <v>-69300</v>
       </c>
-      <c r="G20" s="3">
-        <v>2200</v>
-      </c>
       <c r="H20" s="3">
+        <v>2800</v>
+      </c>
+      <c r="I20" s="3">
         <v>26000</v>
       </c>
-      <c r="I20" s="3">
+      <c r="J20" s="3">
         <v>-4400</v>
       </c>
-      <c r="J20" s="3">
+      <c r="K20" s="3">
         <v>-2500</v>
       </c>
-      <c r="K20" s="3">
+      <c r="L20" s="3">
         <v>-7500</v>
       </c>
-      <c r="L20" s="3">
+      <c r="M20" s="3">
         <v>11600</v>
       </c>
-      <c r="M20" s="3">
+      <c r="N20" s="3">
         <v>-14500</v>
       </c>
-      <c r="N20" s="3">
+      <c r="O20" s="3">
         <v>32600</v>
       </c>
-      <c r="O20" s="3">
+      <c r="P20" s="3">
         <v>-56500</v>
       </c>
-      <c r="P20" s="3">
+      <c r="Q20" s="3">
         <v>-1017300</v>
       </c>
-      <c r="Q20" s="3">
+      <c r="R20" s="3">
         <v>-606600</v>
       </c>
-      <c r="R20" s="3">
+      <c r="S20" s="3">
         <v>-375600</v>
       </c>
-      <c r="S20" s="3">
+      <c r="T20" s="3">
         <v>-505900</v>
       </c>
-      <c r="T20" s="3">
+      <c r="U20" s="3">
         <v>-806400</v>
       </c>
-      <c r="U20" s="3">
+      <c r="V20" s="3">
         <v>-394200</v>
       </c>
-      <c r="V20" s="3">
+      <c r="W20" s="3">
         <v>-406900</v>
       </c>
-      <c r="W20" s="3">
+      <c r="X20" s="3">
         <v>-399500</v>
       </c>
-      <c r="X20" s="3">
+      <c r="Y20" s="3">
         <v>-784600</v>
       </c>
-      <c r="Y20" s="3">
+      <c r="Z20" s="3">
         <v>-508200</v>
       </c>
-      <c r="Z20" s="3">
+      <c r="AA20" s="3">
         <v>-674600</v>
       </c>
-      <c r="AA20" s="3">
+      <c r="AB20" s="3">
         <v>-492400</v>
       </c>
-      <c r="AB20" s="3">
+      <c r="AC20" s="3">
         <v>-920900</v>
       </c>
-      <c r="AC20" s="3">
+      <c r="AD20" s="3">
         <v>-527400</v>
       </c>
-      <c r="AD20" s="3">
+      <c r="AE20" s="3">
         <v>-447200</v>
       </c>
-      <c r="AE20" s="3">
+      <c r="AF20" s="3">
         <v>-519600</v>
       </c>
-      <c r="AF20" s="3">
+      <c r="AG20" s="3">
         <v>-847700</v>
       </c>
-      <c r="AG20" s="3">
+      <c r="AH20" s="3">
         <v>-418500</v>
       </c>
-      <c r="AH20" s="3">
+      <c r="AI20" s="3">
         <v>-401200</v>
       </c>
-      <c r="AI20" s="3">
+      <c r="AJ20" s="3">
         <v>-355800</v>
       </c>
-      <c r="AJ20" s="3">
+      <c r="AK20" s="3">
         <v>-756300</v>
       </c>
-      <c r="AK20" s="3">
+      <c r="AL20" s="3">
         <v>-671500</v>
       </c>
-      <c r="AL20" s="3">
+      <c r="AM20" s="3">
         <v>-417500</v>
       </c>
-      <c r="AM20" s="3">
+      <c r="AN20" s="3">
         <v>-274500</v>
       </c>
-      <c r="AN20" s="3">
+      <c r="AO20" s="3">
         <v>-821100</v>
       </c>
-      <c r="AO20" s="3">
+      <c r="AP20" s="3">
         <v>-531000</v>
       </c>
     </row>
-    <row r="21" spans="3:41" x14ac:dyDescent="0.2">
+    <row r="21" spans="3:42" x14ac:dyDescent="0.2">
       <c r="C21" s="1" t="s">
         <v>16</v>
       </c>
       <c r="D21" s="3">
-        <v>1126300</v>
+        <v>770300</v>
       </c>
       <c r="E21" s="3">
+        <v>723800</v>
+      </c>
+      <c r="F21" s="3">
         <v>814500</v>
       </c>
-      <c r="F21" s="3">
+      <c r="G21" s="3">
         <v>1012500</v>
       </c>
-      <c r="G21" s="3">
-        <v>798100</v>
-      </c>
       <c r="H21" s="3">
+        <v>797400</v>
+      </c>
+      <c r="I21" s="3">
         <v>716400</v>
       </c>
-      <c r="I21" s="3">
+      <c r="J21" s="3">
         <v>1022700</v>
       </c>
-      <c r="J21" s="3">
+      <c r="K21" s="3">
         <v>919700</v>
       </c>
-      <c r="K21" s="3">
+      <c r="L21" s="3">
         <v>1068900</v>
       </c>
-      <c r="L21" s="3">
+      <c r="M21" s="3">
         <v>236700</v>
       </c>
-      <c r="M21" s="3">
+      <c r="N21" s="3">
         <v>1056800</v>
       </c>
-      <c r="N21" s="3">
+      <c r="O21" s="3">
         <v>796500</v>
       </c>
-      <c r="O21" s="3">
+      <c r="P21" s="3">
         <v>1146700</v>
       </c>
-      <c r="P21" s="3">
+      <c r="Q21" s="3">
         <v>732200</v>
       </c>
-      <c r="Q21" s="3">
+      <c r="R21" s="3">
         <v>1110000</v>
       </c>
-      <c r="R21" s="3">
+      <c r="S21" s="3">
         <v>1165700</v>
       </c>
-      <c r="S21" s="3">
+      <c r="T21" s="3">
         <v>1065700</v>
       </c>
-      <c r="T21" s="3">
+      <c r="U21" s="3">
         <v>603300</v>
       </c>
-      <c r="U21" s="3">
+      <c r="V21" s="3">
         <v>1000500</v>
       </c>
-      <c r="V21" s="3">
+      <c r="W21" s="3">
         <v>991500</v>
       </c>
-      <c r="W21" s="3">
+      <c r="X21" s="3">
         <v>799800</v>
       </c>
-      <c r="X21" s="3">
+      <c r="Y21" s="3">
         <v>316900</v>
       </c>
-      <c r="Y21" s="3">
+      <c r="Z21" s="3">
         <v>622000</v>
       </c>
-      <c r="Z21" s="3">
+      <c r="AA21" s="3">
         <v>315300</v>
       </c>
-      <c r="AA21" s="3">
+      <c r="AB21" s="3">
         <v>721900</v>
       </c>
-      <c r="AB21" s="3">
+      <c r="AC21" s="3">
         <v>396300</v>
       </c>
-      <c r="AC21" s="3">
+      <c r="AD21" s="3">
         <v>686600</v>
       </c>
-      <c r="AD21" s="3">
+      <c r="AE21" s="3">
         <v>902900</v>
       </c>
-      <c r="AE21" s="3">
+      <c r="AF21" s="3">
         <v>845100</v>
       </c>
-      <c r="AF21" s="3">
+      <c r="AG21" s="3">
         <v>210800</v>
       </c>
-      <c r="AG21" s="3">
+      <c r="AH21" s="3">
         <v>727400</v>
       </c>
-      <c r="AH21" s="3">
+      <c r="AI21" s="3">
         <v>892200</v>
       </c>
-      <c r="AI21" s="3">
+      <c r="AJ21" s="3">
         <v>727700</v>
       </c>
-      <c r="AJ21" s="3">
+      <c r="AK21" s="3">
         <v>180100</v>
       </c>
-      <c r="AK21" s="3">
+      <c r="AL21" s="3">
         <v>377800</v>
       </c>
-      <c r="AL21" s="3">
+      <c r="AM21" s="3">
         <v>580800</v>
       </c>
-      <c r="AM21" s="3">
+      <c r="AN21" s="3">
         <v>784400</v>
       </c>
-      <c r="AN21" s="3">
+      <c r="AO21" s="3">
         <v>229400</v>
       </c>
-      <c r="AO21" s="3">
+      <c r="AP21" s="3">
         <v>457200</v>
       </c>
     </row>
-    <row r="22" spans="3:41" x14ac:dyDescent="0.2">
+    <row r="22" spans="3:42" x14ac:dyDescent="0.2">
       <c r="C22" s="1" t="s">
         <v>17</v>
       </c>
@@ -2274,8 +2313,8 @@
       <c r="O22" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="P22" s="3">
-        <v>0</v>
+      <c r="P22" s="3" t="s">
+        <v>5</v>
       </c>
       <c r="Q22" s="3">
         <v>0</v>
@@ -2352,246 +2391,255 @@
       <c r="AO22" s="3">
         <v>0</v>
       </c>
+      <c r="AP22" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="23" spans="3:41" x14ac:dyDescent="0.2">
+    <row r="23" spans="3:42" x14ac:dyDescent="0.2">
       <c r="C23" s="1" t="s">
         <v>18</v>
       </c>
       <c r="D23" s="3">
+        <v>557200</v>
+      </c>
+      <c r="E23" s="3">
         <v>353300</v>
       </c>
-      <c r="E23" s="3">
+      <c r="F23" s="3">
         <v>1088400</v>
       </c>
-      <c r="F23" s="3">
+      <c r="G23" s="3">
         <v>876700</v>
       </c>
-      <c r="G23" s="3">
+      <c r="H23" s="3">
         <v>587100</v>
       </c>
-      <c r="H23" s="3">
+      <c r="I23" s="3">
         <v>427300</v>
       </c>
-      <c r="I23" s="3">
+      <c r="J23" s="3">
         <v>914200</v>
       </c>
-      <c r="J23" s="3">
+      <c r="K23" s="3">
         <v>904900</v>
       </c>
-      <c r="K23" s="3">
+      <c r="L23" s="3">
         <v>851200</v>
       </c>
-      <c r="L23" s="3">
+      <c r="M23" s="3">
         <v>94200</v>
       </c>
-      <c r="M23" s="3">
+      <c r="N23" s="3">
         <v>926200</v>
       </c>
-      <c r="N23" s="3">
+      <c r="O23" s="3">
         <v>666800</v>
       </c>
-      <c r="O23" s="3">
+      <c r="P23" s="3">
         <v>974300</v>
       </c>
-      <c r="P23" s="3">
+      <c r="Q23" s="3">
         <v>546900</v>
       </c>
-      <c r="Q23" s="3">
+      <c r="R23" s="3">
         <v>940400</v>
       </c>
-      <c r="R23" s="3">
+      <c r="S23" s="3">
         <v>990200</v>
       </c>
-      <c r="S23" s="3">
+      <c r="T23" s="3">
         <v>897100</v>
       </c>
-      <c r="T23" s="3">
+      <c r="U23" s="3">
         <v>447400</v>
       </c>
-      <c r="U23" s="3">
+      <c r="V23" s="3">
         <v>851200</v>
       </c>
-      <c r="V23" s="3">
+      <c r="W23" s="3">
         <v>807000</v>
       </c>
-      <c r="W23" s="3">
+      <c r="X23" s="3">
         <v>696900</v>
       </c>
-      <c r="X23" s="3">
+      <c r="Y23" s="3">
         <v>215700</v>
       </c>
-      <c r="Y23" s="3">
+      <c r="Z23" s="3">
         <v>520500</v>
       </c>
-      <c r="Z23" s="3">
+      <c r="AA23" s="3">
         <v>216600</v>
       </c>
-      <c r="AA23" s="3">
+      <c r="AB23" s="3">
         <v>609600</v>
       </c>
-      <c r="AB23" s="3">
+      <c r="AC23" s="3">
         <v>276000</v>
       </c>
-      <c r="AC23" s="3">
+      <c r="AD23" s="3">
         <v>569700</v>
       </c>
-      <c r="AD23" s="3">
+      <c r="AE23" s="3">
         <v>794000</v>
       </c>
-      <c r="AE23" s="3">
+      <c r="AF23" s="3">
         <v>751500</v>
       </c>
-      <c r="AF23" s="3">
+      <c r="AG23" s="3">
         <v>149100</v>
       </c>
-      <c r="AG23" s="3">
+      <c r="AH23" s="3">
         <v>668900</v>
       </c>
-      <c r="AH23" s="3">
+      <c r="AI23" s="3">
         <v>836200</v>
       </c>
-      <c r="AI23" s="3">
+      <c r="AJ23" s="3">
         <v>677100</v>
       </c>
-      <c r="AJ23" s="3">
+      <c r="AK23" s="3">
         <v>130200</v>
       </c>
-      <c r="AK23" s="3">
+      <c r="AL23" s="3">
         <v>327000</v>
       </c>
-      <c r="AL23" s="3">
+      <c r="AM23" s="3">
         <v>529200</v>
       </c>
-      <c r="AM23" s="3">
+      <c r="AN23" s="3">
         <v>729200</v>
       </c>
-      <c r="AN23" s="3">
+      <c r="AO23" s="3">
         <v>174600</v>
       </c>
-      <c r="AO23" s="3">
+      <c r="AP23" s="3">
         <v>403400</v>
       </c>
     </row>
-    <row r="24" spans="3:41" x14ac:dyDescent="0.2">
+    <row r="24" spans="3:42" x14ac:dyDescent="0.2">
       <c r="C24" s="1" t="s">
         <v>19</v>
       </c>
       <c r="D24" s="3">
+        <v>137100</v>
+      </c>
+      <c r="E24" s="3">
         <v>116600</v>
       </c>
-      <c r="E24" s="3">
+      <c r="F24" s="3">
         <v>169100</v>
       </c>
-      <c r="F24" s="3">
+      <c r="G24" s="3">
         <v>182300</v>
       </c>
-      <c r="G24" s="3">
+      <c r="H24" s="3">
         <v>142600</v>
       </c>
-      <c r="H24" s="3">
+      <c r="I24" s="3">
         <v>120000</v>
       </c>
-      <c r="I24" s="3">
+      <c r="J24" s="3">
         <v>216000</v>
       </c>
-      <c r="J24" s="3">
+      <c r="K24" s="3">
         <v>207100</v>
       </c>
-      <c r="K24" s="3">
+      <c r="L24" s="3">
         <v>227000</v>
       </c>
-      <c r="L24" s="3">
+      <c r="M24" s="3">
         <v>21000</v>
       </c>
-      <c r="M24" s="3">
+      <c r="N24" s="3">
         <v>244100</v>
       </c>
-      <c r="N24" s="3">
+      <c r="O24" s="3">
         <v>160200</v>
       </c>
-      <c r="O24" s="3">
+      <c r="P24" s="3">
         <v>248300</v>
       </c>
-      <c r="P24" s="3">
+      <c r="Q24" s="3">
         <v>148500</v>
       </c>
-      <c r="Q24" s="3">
+      <c r="R24" s="3">
         <v>259000</v>
       </c>
-      <c r="R24" s="3">
+      <c r="S24" s="3">
         <v>240200</v>
       </c>
-      <c r="S24" s="3">
+      <c r="T24" s="3">
         <v>225300</v>
       </c>
-      <c r="T24" s="3">
+      <c r="U24" s="3">
         <v>113100</v>
       </c>
-      <c r="U24" s="3">
+      <c r="V24" s="3">
         <v>232900</v>
       </c>
-      <c r="V24" s="3">
+      <c r="W24" s="3">
         <v>193200</v>
       </c>
-      <c r="W24" s="3">
+      <c r="X24" s="3">
         <v>164900</v>
       </c>
-      <c r="X24" s="3">
+      <c r="Y24" s="3">
         <v>53200</v>
       </c>
-      <c r="Y24" s="3">
+      <c r="Z24" s="3">
         <v>118800</v>
       </c>
-      <c r="Z24" s="3">
+      <c r="AA24" s="3">
         <v>50000</v>
       </c>
-      <c r="AA24" s="3">
+      <c r="AB24" s="3">
         <v>157800</v>
       </c>
-      <c r="AB24" s="3">
+      <c r="AC24" s="3">
         <v>79200</v>
       </c>
-      <c r="AC24" s="3">
+      <c r="AD24" s="3">
         <v>115700</v>
       </c>
-      <c r="AD24" s="3">
+      <c r="AE24" s="3">
         <v>215500</v>
       </c>
-      <c r="AE24" s="3">
+      <c r="AF24" s="3">
         <v>192300</v>
       </c>
-      <c r="AF24" s="3">
+      <c r="AG24" s="3">
         <v>39300</v>
       </c>
-      <c r="AG24" s="3">
+      <c r="AH24" s="3">
         <v>179200</v>
       </c>
-      <c r="AH24" s="3">
+      <c r="AI24" s="3">
         <v>229900</v>
       </c>
-      <c r="AI24" s="3">
+      <c r="AJ24" s="3">
         <v>177700</v>
       </c>
-      <c r="AJ24" s="3">
+      <c r="AK24" s="3">
         <v>9000</v>
       </c>
-      <c r="AK24" s="3">
+      <c r="AL24" s="3">
         <v>77600</v>
       </c>
-      <c r="AL24" s="3">
+      <c r="AM24" s="3">
         <v>118800</v>
       </c>
-      <c r="AM24" s="3">
+      <c r="AN24" s="3">
         <v>163600</v>
       </c>
-      <c r="AN24" s="3">
+      <c r="AO24" s="3">
         <v>30300</v>
       </c>
-      <c r="AO24" s="3">
+      <c r="AP24" s="3">
         <v>80000</v>
       </c>
     </row>
-    <row r="25" spans="3:41" x14ac:dyDescent="0.2">
+    <row r="25" spans="3:42" x14ac:dyDescent="0.2">
       <c r="C25" s="1" t="s">
         <v>20</v>
       </c>
@@ -2709,246 +2757,255 @@
       <c r="AO25" s="3">
         <v>0</v>
       </c>
+      <c r="AP25" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="26" spans="3:41" x14ac:dyDescent="0.2">
+    <row r="26" spans="3:42" x14ac:dyDescent="0.2">
       <c r="C26" s="1" t="s">
         <v>21</v>
       </c>
       <c r="D26" s="3">
+        <v>420100</v>
+      </c>
+      <c r="E26" s="3">
         <v>236700</v>
       </c>
-      <c r="E26" s="3">
+      <c r="F26" s="3">
         <v>919400</v>
       </c>
-      <c r="F26" s="3">
+      <c r="G26" s="3">
         <v>694400</v>
       </c>
-      <c r="G26" s="3">
+      <c r="H26" s="3">
         <v>444500</v>
       </c>
-      <c r="H26" s="3">
+      <c r="I26" s="3">
         <v>307400</v>
       </c>
-      <c r="I26" s="3">
+      <c r="J26" s="3">
         <v>698200</v>
       </c>
-      <c r="J26" s="3">
+      <c r="K26" s="3">
         <v>697800</v>
       </c>
-      <c r="K26" s="3">
+      <c r="L26" s="3">
         <v>624200</v>
       </c>
-      <c r="L26" s="3">
+      <c r="M26" s="3">
         <v>73200</v>
       </c>
-      <c r="M26" s="3">
+      <c r="N26" s="3">
         <v>682000</v>
       </c>
-      <c r="N26" s="3">
+      <c r="O26" s="3">
         <v>506600</v>
       </c>
-      <c r="O26" s="3">
+      <c r="P26" s="3">
         <v>726000</v>
       </c>
-      <c r="P26" s="3">
+      <c r="Q26" s="3">
         <v>398500</v>
       </c>
-      <c r="Q26" s="3">
+      <c r="R26" s="3">
         <v>681400</v>
       </c>
-      <c r="R26" s="3">
+      <c r="S26" s="3">
         <v>750000</v>
       </c>
-      <c r="S26" s="3">
+      <c r="T26" s="3">
         <v>671800</v>
       </c>
-      <c r="T26" s="3">
+      <c r="U26" s="3">
         <v>334300</v>
       </c>
-      <c r="U26" s="3">
+      <c r="V26" s="3">
         <v>618300</v>
       </c>
-      <c r="V26" s="3">
+      <c r="W26" s="3">
         <v>613800</v>
       </c>
-      <c r="W26" s="3">
+      <c r="X26" s="3">
         <v>532000</v>
       </c>
-      <c r="X26" s="3">
+      <c r="Y26" s="3">
         <v>162400</v>
       </c>
-      <c r="Y26" s="3">
+      <c r="Z26" s="3">
         <v>401700</v>
       </c>
-      <c r="Z26" s="3">
+      <c r="AA26" s="3">
         <v>166500</v>
       </c>
-      <c r="AA26" s="3">
+      <c r="AB26" s="3">
         <v>451800</v>
       </c>
-      <c r="AB26" s="3">
+      <c r="AC26" s="3">
         <v>196800</v>
       </c>
-      <c r="AC26" s="3">
+      <c r="AD26" s="3">
         <v>454000</v>
       </c>
-      <c r="AD26" s="3">
+      <c r="AE26" s="3">
         <v>578500</v>
       </c>
-      <c r="AE26" s="3">
+      <c r="AF26" s="3">
         <v>559200</v>
       </c>
-      <c r="AF26" s="3">
+      <c r="AG26" s="3">
         <v>109900</v>
       </c>
-      <c r="AG26" s="3">
+      <c r="AH26" s="3">
         <v>489700</v>
       </c>
-      <c r="AH26" s="3">
+      <c r="AI26" s="3">
         <v>606300</v>
       </c>
-      <c r="AI26" s="3">
+      <c r="AJ26" s="3">
         <v>499400</v>
       </c>
-      <c r="AJ26" s="3">
+      <c r="AK26" s="3">
         <v>121100</v>
       </c>
-      <c r="AK26" s="3">
+      <c r="AL26" s="3">
         <v>249400</v>
       </c>
-      <c r="AL26" s="3">
+      <c r="AM26" s="3">
         <v>410300</v>
       </c>
-      <c r="AM26" s="3">
+      <c r="AN26" s="3">
         <v>565600</v>
       </c>
-      <c r="AN26" s="3">
+      <c r="AO26" s="3">
         <v>144300</v>
       </c>
-      <c r="AO26" s="3">
+      <c r="AP26" s="3">
         <v>323500</v>
       </c>
     </row>
-    <row r="27" spans="3:41" x14ac:dyDescent="0.2">
+    <row r="27" spans="3:42" x14ac:dyDescent="0.2">
       <c r="C27" s="1" t="s">
         <v>22</v>
       </c>
       <c r="D27" s="3">
+        <v>371400</v>
+      </c>
+      <c r="E27" s="3">
         <v>201700</v>
       </c>
-      <c r="E27" s="3">
+      <c r="F27" s="3">
         <v>859000</v>
       </c>
-      <c r="F27" s="3">
+      <c r="G27" s="3">
         <v>664400</v>
       </c>
-      <c r="G27" s="3">
+      <c r="H27" s="3">
         <v>391900</v>
       </c>
-      <c r="H27" s="3">
+      <c r="I27" s="3">
         <v>261600</v>
       </c>
-      <c r="I27" s="3">
+      <c r="J27" s="3">
         <v>655100</v>
       </c>
-      <c r="J27" s="3">
+      <c r="K27" s="3">
         <v>647100</v>
       </c>
-      <c r="K27" s="3">
+      <c r="L27" s="3">
         <v>586900</v>
       </c>
-      <c r="L27" s="3">
+      <c r="M27" s="3">
         <v>25300</v>
       </c>
-      <c r="M27" s="3">
+      <c r="N27" s="3">
         <v>643700</v>
       </c>
-      <c r="N27" s="3">
+      <c r="O27" s="3">
         <v>449800</v>
       </c>
-      <c r="O27" s="3">
+      <c r="P27" s="3">
         <v>677400</v>
       </c>
-      <c r="P27" s="3">
+      <c r="Q27" s="3">
         <v>338800</v>
       </c>
-      <c r="Q27" s="3">
+      <c r="R27" s="3">
         <v>640600</v>
       </c>
-      <c r="R27" s="3">
+      <c r="S27" s="3">
         <v>684400</v>
       </c>
-      <c r="S27" s="3">
+      <c r="T27" s="3">
         <v>631400</v>
       </c>
-      <c r="T27" s="3">
+      <c r="U27" s="3">
         <v>279500</v>
       </c>
-      <c r="U27" s="3">
+      <c r="V27" s="3">
         <v>570700</v>
       </c>
-      <c r="V27" s="3">
+      <c r="W27" s="3">
         <v>552600</v>
       </c>
-      <c r="W27" s="3">
+      <c r="X27" s="3">
         <v>482000</v>
       </c>
-      <c r="X27" s="3">
+      <c r="Y27" s="3">
         <v>112600</v>
       </c>
-      <c r="Y27" s="3">
+      <c r="Z27" s="3">
         <v>358800</v>
       </c>
-      <c r="Z27" s="3">
+      <c r="AA27" s="3">
         <v>100500</v>
       </c>
-      <c r="AA27" s="3">
+      <c r="AB27" s="3">
         <v>412900</v>
       </c>
-      <c r="AB27" s="3">
+      <c r="AC27" s="3">
         <v>174900</v>
       </c>
-      <c r="AC27" s="3">
+      <c r="AD27" s="3">
         <v>410100</v>
       </c>
-      <c r="AD27" s="3">
+      <c r="AE27" s="3">
         <v>537700</v>
       </c>
-      <c r="AE27" s="3">
+      <c r="AF27" s="3">
         <v>517500</v>
       </c>
-      <c r="AF27" s="3">
+      <c r="AG27" s="3">
         <v>76800</v>
       </c>
-      <c r="AG27" s="3">
+      <c r="AH27" s="3">
         <v>453900</v>
       </c>
-      <c r="AH27" s="3">
+      <c r="AI27" s="3">
         <v>569900</v>
       </c>
-      <c r="AI27" s="3">
+      <c r="AJ27" s="3">
         <v>463600</v>
       </c>
-      <c r="AJ27" s="3">
+      <c r="AK27" s="3">
         <v>84900</v>
       </c>
-      <c r="AK27" s="3">
+      <c r="AL27" s="3">
         <v>212100</v>
       </c>
-      <c r="AL27" s="3">
+      <c r="AM27" s="3">
         <v>369000</v>
       </c>
-      <c r="AM27" s="3">
+      <c r="AN27" s="3">
         <v>517600</v>
       </c>
-      <c r="AN27" s="3">
+      <c r="AO27" s="3">
         <v>88500</v>
       </c>
-      <c r="AO27" s="3">
+      <c r="AP27" s="3">
         <v>275700</v>
       </c>
     </row>
-    <row r="28" spans="3:41" x14ac:dyDescent="0.2">
+    <row r="28" spans="3:42" x14ac:dyDescent="0.2">
       <c r="C28" s="1" t="s">
         <v>23</v>
       </c>
@@ -3066,8 +3123,11 @@
       <c r="AO28" s="3">
         <v>0</v>
       </c>
+      <c r="AP28" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="29" spans="3:41" x14ac:dyDescent="0.2">
+    <row r="29" spans="3:42" x14ac:dyDescent="0.2">
       <c r="C29" s="1" t="s">
         <v>24</v>
       </c>
@@ -3185,8 +3245,11 @@
       <c r="AO29" s="3">
         <v>0</v>
       </c>
+      <c r="AP29" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="30" spans="3:41" x14ac:dyDescent="0.2">
+    <row r="30" spans="3:42" x14ac:dyDescent="0.2">
       <c r="C30" s="1" t="s">
         <v>25</v>
       </c>
@@ -3304,8 +3367,11 @@
       <c r="AO30" s="3">
         <v>0</v>
       </c>
+      <c r="AP30" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="31" spans="3:41" x14ac:dyDescent="0.2">
+    <row r="31" spans="3:42" x14ac:dyDescent="0.2">
       <c r="C31" s="1" t="s">
         <v>26</v>
       </c>
@@ -3423,246 +3489,255 @@
       <c r="AO31" s="3">
         <v>0</v>
       </c>
+      <c r="AP31" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="32" spans="3:41" x14ac:dyDescent="0.2">
+    <row r="32" spans="3:42" x14ac:dyDescent="0.2">
       <c r="C32" s="1" t="s">
         <v>27</v>
       </c>
       <c r="D32" s="3">
-        <v>333900</v>
+        <v>20400</v>
       </c>
       <c r="E32" s="3">
+        <v>-68600</v>
+      </c>
+      <c r="F32" s="3">
         <v>-14200</v>
       </c>
-      <c r="F32" s="3">
+      <c r="G32" s="3">
         <v>69300</v>
       </c>
-      <c r="G32" s="3">
-        <v>-2200</v>
-      </c>
       <c r="H32" s="3">
+        <v>-2800</v>
+      </c>
+      <c r="I32" s="3">
         <v>-26000</v>
       </c>
-      <c r="I32" s="3">
+      <c r="J32" s="3">
         <v>4400</v>
       </c>
-      <c r="J32" s="3">
+      <c r="K32" s="3">
         <v>2500</v>
       </c>
-      <c r="K32" s="3">
+      <c r="L32" s="3">
         <v>7500</v>
       </c>
-      <c r="L32" s="3">
+      <c r="M32" s="3">
         <v>-11600</v>
       </c>
-      <c r="M32" s="3">
+      <c r="N32" s="3">
         <v>14500</v>
       </c>
-      <c r="N32" s="3">
+      <c r="O32" s="3">
         <v>-32600</v>
       </c>
-      <c r="O32" s="3">
+      <c r="P32" s="3">
         <v>56500</v>
       </c>
-      <c r="P32" s="3">
+      <c r="Q32" s="3">
         <v>1017300</v>
       </c>
-      <c r="Q32" s="3">
+      <c r="R32" s="3">
         <v>606600</v>
       </c>
-      <c r="R32" s="3">
+      <c r="S32" s="3">
         <v>375600</v>
       </c>
-      <c r="S32" s="3">
+      <c r="T32" s="3">
         <v>505900</v>
       </c>
-      <c r="T32" s="3">
+      <c r="U32" s="3">
         <v>806400</v>
       </c>
-      <c r="U32" s="3">
+      <c r="V32" s="3">
         <v>394200</v>
       </c>
-      <c r="V32" s="3">
+      <c r="W32" s="3">
         <v>406900</v>
       </c>
-      <c r="W32" s="3">
+      <c r="X32" s="3">
         <v>399500</v>
       </c>
-      <c r="X32" s="3">
+      <c r="Y32" s="3">
         <v>784600</v>
       </c>
-      <c r="Y32" s="3">
+      <c r="Z32" s="3">
         <v>508200</v>
       </c>
-      <c r="Z32" s="3">
+      <c r="AA32" s="3">
         <v>674600</v>
       </c>
-      <c r="AA32" s="3">
+      <c r="AB32" s="3">
         <v>492400</v>
       </c>
-      <c r="AB32" s="3">
+      <c r="AC32" s="3">
         <v>920900</v>
       </c>
-      <c r="AC32" s="3">
+      <c r="AD32" s="3">
         <v>527400</v>
       </c>
-      <c r="AD32" s="3">
+      <c r="AE32" s="3">
         <v>447200</v>
       </c>
-      <c r="AE32" s="3">
+      <c r="AF32" s="3">
         <v>519600</v>
       </c>
-      <c r="AF32" s="3">
+      <c r="AG32" s="3">
         <v>847700</v>
       </c>
-      <c r="AG32" s="3">
+      <c r="AH32" s="3">
         <v>418500</v>
       </c>
-      <c r="AH32" s="3">
+      <c r="AI32" s="3">
         <v>401200</v>
       </c>
-      <c r="AI32" s="3">
+      <c r="AJ32" s="3">
         <v>355800</v>
       </c>
-      <c r="AJ32" s="3">
+      <c r="AK32" s="3">
         <v>756300</v>
       </c>
-      <c r="AK32" s="3">
+      <c r="AL32" s="3">
         <v>671500</v>
       </c>
-      <c r="AL32" s="3">
+      <c r="AM32" s="3">
         <v>417500</v>
       </c>
-      <c r="AM32" s="3">
+      <c r="AN32" s="3">
         <v>274500</v>
       </c>
-      <c r="AN32" s="3">
+      <c r="AO32" s="3">
         <v>821100</v>
       </c>
-      <c r="AO32" s="3">
+      <c r="AP32" s="3">
         <v>531000</v>
       </c>
     </row>
-    <row r="33" spans="2:41" x14ac:dyDescent="0.2">
+    <row r="33" spans="2:42" x14ac:dyDescent="0.2">
       <c r="C33" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D33" s="3">
+        <v>397000</v>
+      </c>
+      <c r="E33" s="3">
         <v>227500</v>
       </c>
-      <c r="E33" s="3">
+      <c r="F33" s="3">
         <v>885500</v>
       </c>
-      <c r="F33" s="3">
+      <c r="G33" s="3">
         <v>691100</v>
       </c>
-      <c r="G33" s="3">
+      <c r="H33" s="3">
         <v>418800</v>
       </c>
-      <c r="H33" s="3">
+      <c r="I33" s="3">
         <v>288500</v>
       </c>
-      <c r="I33" s="3">
+      <c r="J33" s="3">
         <v>688600</v>
       </c>
-      <c r="J33" s="3">
+      <c r="K33" s="3">
         <v>676000</v>
       </c>
-      <c r="K33" s="3">
+      <c r="L33" s="3">
         <v>613100</v>
       </c>
-      <c r="L33" s="3">
+      <c r="M33" s="3">
         <v>52500</v>
       </c>
-      <c r="M33" s="3">
+      <c r="N33" s="3">
         <v>668000</v>
       </c>
-      <c r="N33" s="3">
+      <c r="O33" s="3">
         <v>474700</v>
       </c>
-      <c r="O33" s="3">
+      <c r="P33" s="3">
         <v>700700</v>
       </c>
-      <c r="P33" s="3">
+      <c r="Q33" s="3">
         <v>338800</v>
       </c>
-      <c r="Q33" s="3">
+      <c r="R33" s="3">
         <v>640600</v>
       </c>
-      <c r="R33" s="3">
+      <c r="S33" s="3">
         <v>684400</v>
       </c>
-      <c r="S33" s="3">
+      <c r="T33" s="3">
         <v>631400</v>
       </c>
-      <c r="T33" s="3">
+      <c r="U33" s="3">
         <v>279500</v>
       </c>
-      <c r="U33" s="3">
+      <c r="V33" s="3">
         <v>570700</v>
       </c>
-      <c r="V33" s="3">
+      <c r="W33" s="3">
         <v>552600</v>
       </c>
-      <c r="W33" s="3">
+      <c r="X33" s="3">
         <v>482000</v>
       </c>
-      <c r="X33" s="3">
+      <c r="Y33" s="3">
         <v>112600</v>
       </c>
-      <c r="Y33" s="3">
+      <c r="Z33" s="3">
         <v>358800</v>
       </c>
-      <c r="Z33" s="3">
+      <c r="AA33" s="3">
         <v>100500</v>
       </c>
-      <c r="AA33" s="3">
+      <c r="AB33" s="3">
         <v>412900</v>
       </c>
-      <c r="AB33" s="3">
+      <c r="AC33" s="3">
         <v>174900</v>
       </c>
-      <c r="AC33" s="3">
+      <c r="AD33" s="3">
         <v>410100</v>
       </c>
-      <c r="AD33" s="3">
+      <c r="AE33" s="3">
         <v>537700</v>
       </c>
-      <c r="AE33" s="3">
+      <c r="AF33" s="3">
         <v>517500</v>
       </c>
-      <c r="AF33" s="3">
+      <c r="AG33" s="3">
         <v>76800</v>
       </c>
-      <c r="AG33" s="3">
+      <c r="AH33" s="3">
         <v>453900</v>
       </c>
-      <c r="AH33" s="3">
+      <c r="AI33" s="3">
         <v>569900</v>
       </c>
-      <c r="AI33" s="3">
+      <c r="AJ33" s="3">
         <v>463600</v>
       </c>
-      <c r="AJ33" s="3">
+      <c r="AK33" s="3">
         <v>84900</v>
       </c>
-      <c r="AK33" s="3">
+      <c r="AL33" s="3">
         <v>212100</v>
       </c>
-      <c r="AL33" s="3">
+      <c r="AM33" s="3">
         <v>369000</v>
       </c>
-      <c r="AM33" s="3">
+      <c r="AN33" s="3">
         <v>517600</v>
       </c>
-      <c r="AN33" s="3">
+      <c r="AO33" s="3">
         <v>88500</v>
       </c>
-      <c r="AO33" s="3">
+      <c r="AP33" s="3">
         <v>275700</v>
       </c>
     </row>
-    <row r="34" spans="2:41" x14ac:dyDescent="0.2">
+    <row r="34" spans="2:42" x14ac:dyDescent="0.2">
       <c r="C34" s="1" t="s">
         <v>29</v>
       </c>
@@ -3780,251 +3855,260 @@
       <c r="AO34" s="3">
         <v>0</v>
       </c>
+      <c r="AP34" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="35" spans="2:41" x14ac:dyDescent="0.2">
+    <row r="35" spans="2:42" x14ac:dyDescent="0.2">
       <c r="C35" s="1" t="s">
         <v>30</v>
       </c>
       <c r="D35" s="3">
+        <v>397000</v>
+      </c>
+      <c r="E35" s="3">
         <v>227500</v>
       </c>
-      <c r="E35" s="3">
+      <c r="F35" s="3">
         <v>885500</v>
       </c>
-      <c r="F35" s="3">
+      <c r="G35" s="3">
         <v>691100</v>
       </c>
-      <c r="G35" s="3">
+      <c r="H35" s="3">
         <v>418800</v>
       </c>
-      <c r="H35" s="3">
+      <c r="I35" s="3">
         <v>288500</v>
       </c>
-      <c r="I35" s="3">
+      <c r="J35" s="3">
         <v>688600</v>
       </c>
-      <c r="J35" s="3">
+      <c r="K35" s="3">
         <v>676000</v>
       </c>
-      <c r="K35" s="3">
+      <c r="L35" s="3">
         <v>613100</v>
       </c>
-      <c r="L35" s="3">
+      <c r="M35" s="3">
         <v>52500</v>
       </c>
-      <c r="M35" s="3">
+      <c r="N35" s="3">
         <v>668000</v>
       </c>
-      <c r="N35" s="3">
+      <c r="O35" s="3">
         <v>474700</v>
       </c>
-      <c r="O35" s="3">
+      <c r="P35" s="3">
         <v>700700</v>
       </c>
-      <c r="P35" s="3">
+      <c r="Q35" s="3">
         <v>338800</v>
       </c>
-      <c r="Q35" s="3">
+      <c r="R35" s="3">
         <v>640600</v>
       </c>
-      <c r="R35" s="3">
+      <c r="S35" s="3">
         <v>684400</v>
       </c>
-      <c r="S35" s="3">
+      <c r="T35" s="3">
         <v>631400</v>
       </c>
-      <c r="T35" s="3">
+      <c r="U35" s="3">
         <v>279500</v>
       </c>
-      <c r="U35" s="3">
+      <c r="V35" s="3">
         <v>570700</v>
       </c>
-      <c r="V35" s="3">
+      <c r="W35" s="3">
         <v>552600</v>
       </c>
-      <c r="W35" s="3">
+      <c r="X35" s="3">
         <v>482000</v>
       </c>
-      <c r="X35" s="3">
+      <c r="Y35" s="3">
         <v>112600</v>
       </c>
-      <c r="Y35" s="3">
+      <c r="Z35" s="3">
         <v>358800</v>
       </c>
-      <c r="Z35" s="3">
+      <c r="AA35" s="3">
         <v>100500</v>
       </c>
-      <c r="AA35" s="3">
+      <c r="AB35" s="3">
         <v>412900</v>
       </c>
-      <c r="AB35" s="3">
+      <c r="AC35" s="3">
         <v>174900</v>
       </c>
-      <c r="AC35" s="3">
+      <c r="AD35" s="3">
         <v>410100</v>
       </c>
-      <c r="AD35" s="3">
+      <c r="AE35" s="3">
         <v>537700</v>
       </c>
-      <c r="AE35" s="3">
+      <c r="AF35" s="3">
         <v>517500</v>
       </c>
-      <c r="AF35" s="3">
+      <c r="AG35" s="3">
         <v>76800</v>
       </c>
-      <c r="AG35" s="3">
+      <c r="AH35" s="3">
         <v>453900</v>
       </c>
-      <c r="AH35" s="3">
+      <c r="AI35" s="3">
         <v>569900</v>
       </c>
-      <c r="AI35" s="3">
+      <c r="AJ35" s="3">
         <v>463600</v>
       </c>
-      <c r="AJ35" s="3">
+      <c r="AK35" s="3">
         <v>84900</v>
       </c>
-      <c r="AK35" s="3">
+      <c r="AL35" s="3">
         <v>212100</v>
       </c>
-      <c r="AL35" s="3">
+      <c r="AM35" s="3">
         <v>369000</v>
       </c>
-      <c r="AM35" s="3">
+      <c r="AN35" s="3">
         <v>517600</v>
       </c>
-      <c r="AN35" s="3">
+      <c r="AO35" s="3">
         <v>88500</v>
       </c>
-      <c r="AO35" s="3">
+      <c r="AP35" s="3">
         <v>275700</v>
       </c>
     </row>
-    <row r="37" spans="2:41" x14ac:dyDescent="0.2">
+    <row r="37" spans="2:42" x14ac:dyDescent="0.2">
       <c r="B37" s="1" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="38" spans="2:41" x14ac:dyDescent="0.2">
+    <row r="38" spans="2:42" x14ac:dyDescent="0.2">
       <c r="C38" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D38" s="2">
+        <v>46112</v>
+      </c>
+      <c r="E38" s="2">
         <v>46022</v>
       </c>
-      <c r="E38" s="2">
+      <c r="F38" s="2">
         <v>45930</v>
       </c>
-      <c r="F38" s="2">
+      <c r="G38" s="2">
         <v>45838</v>
       </c>
-      <c r="G38" s="2">
+      <c r="H38" s="2">
         <v>45747</v>
       </c>
-      <c r="H38" s="2">
+      <c r="I38" s="2">
         <v>45657</v>
       </c>
-      <c r="I38" s="2">
+      <c r="J38" s="2">
         <v>45565</v>
       </c>
-      <c r="J38" s="2">
+      <c r="K38" s="2">
         <v>45473</v>
       </c>
-      <c r="K38" s="2">
+      <c r="L38" s="2">
         <v>45382</v>
       </c>
-      <c r="L38" s="2">
+      <c r="M38" s="2">
         <v>45291</v>
       </c>
-      <c r="M38" s="2">
+      <c r="N38" s="2">
         <v>45199</v>
       </c>
-      <c r="N38" s="2">
+      <c r="O38" s="2">
         <v>45107</v>
       </c>
-      <c r="O38" s="2">
+      <c r="P38" s="2">
         <v>45016</v>
       </c>
-      <c r="P38" s="2">
+      <c r="Q38" s="2">
         <v>44926</v>
       </c>
-      <c r="Q38" s="2">
+      <c r="R38" s="2">
         <v>44834</v>
       </c>
-      <c r="R38" s="2">
+      <c r="S38" s="2">
         <v>44742</v>
       </c>
-      <c r="S38" s="2">
+      <c r="T38" s="2">
         <v>44651</v>
       </c>
-      <c r="T38" s="2">
+      <c r="U38" s="2">
         <v>44561</v>
       </c>
-      <c r="U38" s="2">
+      <c r="V38" s="2">
         <v>44469</v>
       </c>
-      <c r="V38" s="2">
+      <c r="W38" s="2">
         <v>44377</v>
       </c>
-      <c r="W38" s="2">
+      <c r="X38" s="2">
         <v>44286</v>
       </c>
-      <c r="X38" s="2">
+      <c r="Y38" s="2">
         <v>44196</v>
       </c>
-      <c r="Y38" s="2">
+      <c r="Z38" s="2">
         <v>44104</v>
       </c>
-      <c r="Z38" s="2">
+      <c r="AA38" s="2">
         <v>44012</v>
       </c>
-      <c r="AA38" s="2">
+      <c r="AB38" s="2">
         <v>43921</v>
       </c>
-      <c r="AB38" s="2">
+      <c r="AC38" s="2">
         <v>43830</v>
       </c>
-      <c r="AC38" s="2">
+      <c r="AD38" s="2">
         <v>43738</v>
       </c>
-      <c r="AD38" s="2">
+      <c r="AE38" s="2">
         <v>43646</v>
       </c>
-      <c r="AE38" s="2">
+      <c r="AF38" s="2">
         <v>43555</v>
       </c>
-      <c r="AF38" s="2">
+      <c r="AG38" s="2">
         <v>43465</v>
       </c>
-      <c r="AG38" s="2">
+      <c r="AH38" s="2">
         <v>43373</v>
       </c>
-      <c r="AH38" s="2">
+      <c r="AI38" s="2">
         <v>43281</v>
       </c>
-      <c r="AI38" s="2">
+      <c r="AJ38" s="2">
         <v>43190</v>
       </c>
-      <c r="AJ38" s="2">
+      <c r="AK38" s="2">
         <v>43100</v>
       </c>
-      <c r="AK38" s="2">
+      <c r="AL38" s="2">
         <v>43008</v>
       </c>
-      <c r="AL38" s="2">
+      <c r="AM38" s="2">
         <v>42916</v>
       </c>
-      <c r="AM38" s="2">
+      <c r="AN38" s="2">
         <v>42825</v>
       </c>
-      <c r="AN38" s="2">
+      <c r="AO38" s="2">
         <v>42735</v>
       </c>
-      <c r="AO38" s="2">
+      <c r="AP38" s="2">
         <v>42643</v>
       </c>
     </row>
-    <row r="39" spans="2:41" x14ac:dyDescent="0.2">
+    <row r="39" spans="2:42" x14ac:dyDescent="0.2">
       <c r="C39" s="1" t="s">
         <v>32</v>
       </c>
@@ -4066,8 +4150,9 @@
       <c r="AM39" s="3"/>
       <c r="AN39" s="3"/>
       <c r="AO39" s="3"/>
+      <c r="AP39" s="3"/>
     </row>
-    <row r="40" spans="2:41" x14ac:dyDescent="0.2">
+    <row r="40" spans="2:42" x14ac:dyDescent="0.2">
       <c r="C40" s="1" t="s">
         <v>33</v>
       </c>
@@ -4109,288 +4194,295 @@
       <c r="AM40" s="3"/>
       <c r="AN40" s="3"/>
       <c r="AO40" s="3"/>
+      <c r="AP40" s="3"/>
     </row>
-    <row r="41" spans="2:41" x14ac:dyDescent="0.2">
+    <row r="41" spans="2:42" x14ac:dyDescent="0.2">
       <c r="C41" s="1" t="s">
         <v>34</v>
       </c>
       <c r="D41" s="3">
+        <v>12856600</v>
+      </c>
+      <c r="E41" s="3">
         <v>10408300</v>
       </c>
-      <c r="E41" s="3">
+      <c r="F41" s="3">
         <v>10043000</v>
       </c>
-      <c r="F41" s="3">
+      <c r="G41" s="3">
         <v>9721700</v>
       </c>
-      <c r="G41" s="3">
+      <c r="H41" s="3">
         <v>9800400</v>
       </c>
-      <c r="H41" s="3">
+      <c r="I41" s="3">
         <v>9892700</v>
       </c>
-      <c r="I41" s="3">
+      <c r="J41" s="3">
         <v>13834100</v>
       </c>
-      <c r="J41" s="3">
+      <c r="K41" s="3">
         <v>8534800</v>
       </c>
-      <c r="K41" s="3">
+      <c r="L41" s="3">
         <v>13129900</v>
       </c>
-      <c r="L41" s="3">
+      <c r="M41" s="3">
         <v>12476200</v>
       </c>
-      <c r="M41" s="3">
+      <c r="N41" s="3">
         <v>7157900</v>
       </c>
-      <c r="N41" s="3">
+      <c r="O41" s="3">
         <v>9809900</v>
       </c>
-      <c r="O41" s="3">
+      <c r="P41" s="3">
         <v>10234100</v>
       </c>
-      <c r="P41" s="3">
+      <c r="Q41" s="3">
         <v>25596900</v>
       </c>
-      <c r="Q41" s="3">
+      <c r="R41" s="3">
         <v>6507700</v>
       </c>
-      <c r="R41" s="3">
+      <c r="S41" s="3">
         <v>7377100</v>
       </c>
-      <c r="S41" s="3">
+      <c r="T41" s="3">
         <v>9785500</v>
       </c>
-      <c r="T41" s="3">
+      <c r="U41" s="3">
         <v>5555400</v>
       </c>
-      <c r="U41" s="3">
+      <c r="V41" s="3">
         <v>7893500</v>
       </c>
-      <c r="V41" s="3">
+      <c r="W41" s="3">
         <v>7303900</v>
       </c>
-      <c r="W41" s="3">
+      <c r="X41" s="3">
         <v>7996900</v>
       </c>
-      <c r="X41" s="3">
+      <c r="Y41" s="3">
         <v>6985700</v>
       </c>
-      <c r="Y41" s="3">
+      <c r="Z41" s="3">
         <v>6452400</v>
       </c>
-      <c r="Z41" s="3">
+      <c r="AA41" s="3">
         <v>6934700</v>
       </c>
-      <c r="AA41" s="3">
+      <c r="AB41" s="3">
         <v>7810800</v>
       </c>
-      <c r="AB41" s="3">
+      <c r="AC41" s="3">
         <v>5327800</v>
       </c>
-      <c r="AC41" s="3">
+      <c r="AD41" s="3">
         <v>7069900</v>
       </c>
-      <c r="AD41" s="3">
+      <c r="AE41" s="3">
         <v>5777500</v>
       </c>
-      <c r="AE41" s="3">
+      <c r="AF41" s="3">
         <v>4361000</v>
       </c>
-      <c r="AF41" s="3">
+      <c r="AG41" s="3">
         <v>5329900</v>
       </c>
-      <c r="AG41" s="3">
+      <c r="AH41" s="3">
         <v>4608100</v>
       </c>
-      <c r="AH41" s="3">
+      <c r="AI41" s="3">
         <v>4589200</v>
       </c>
-      <c r="AI41" s="3">
+      <c r="AJ41" s="3">
         <v>4387400</v>
       </c>
-      <c r="AJ41" s="3">
+      <c r="AK41" s="3">
         <v>5323900</v>
       </c>
-      <c r="AK41" s="3">
+      <c r="AL41" s="3">
         <v>5337600</v>
       </c>
-      <c r="AL41" s="3">
+      <c r="AM41" s="3">
         <v>5780800</v>
       </c>
-      <c r="AM41" s="3">
+      <c r="AN41" s="3">
         <v>6495200</v>
       </c>
-      <c r="AN41" s="3">
+      <c r="AO41" s="3">
         <v>6385500</v>
       </c>
-      <c r="AO41" s="3">
+      <c r="AP41" s="3">
         <v>7024600</v>
       </c>
     </row>
-    <row r="42" spans="2:41" x14ac:dyDescent="0.2">
+    <row r="42" spans="2:42" x14ac:dyDescent="0.2">
       <c r="C42" s="1" t="s">
         <v>35</v>
       </c>
       <c r="D42" s="3">
+        <v>29672100</v>
+      </c>
+      <c r="E42" s="3">
         <v>30478600</v>
       </c>
-      <c r="E42" s="3">
+      <c r="F42" s="3">
         <v>33934900</v>
       </c>
-      <c r="F42" s="3">
+      <c r="G42" s="3">
         <v>29338000</v>
       </c>
-      <c r="G42" s="3">
+      <c r="H42" s="3">
         <v>26987000</v>
       </c>
-      <c r="H42" s="3">
+      <c r="I42" s="3">
         <v>22818100</v>
       </c>
-      <c r="I42" s="3">
+      <c r="J42" s="3">
         <v>29370000</v>
       </c>
-      <c r="J42" s="3">
+      <c r="K42" s="3">
         <v>19283100</v>
       </c>
-      <c r="K42" s="3">
+      <c r="L42" s="3">
         <v>18486700</v>
       </c>
-      <c r="L42" s="3">
+      <c r="M42" s="3">
         <v>18215800</v>
       </c>
-      <c r="M42" s="3">
+      <c r="N42" s="3">
         <v>17492100</v>
       </c>
-      <c r="N42" s="3">
+      <c r="O42" s="3">
         <v>25108400</v>
       </c>
-      <c r="O42" s="3">
+      <c r="P42" s="3">
         <v>17703400</v>
       </c>
-      <c r="P42" s="3">
+      <c r="Q42" s="3">
         <v>41084100</v>
       </c>
-      <c r="Q42" s="3">
+      <c r="R42" s="3">
         <v>48087900</v>
       </c>
-      <c r="R42" s="3">
+      <c r="S42" s="3">
         <v>44907700</v>
       </c>
-      <c r="S42" s="3">
+      <c r="T42" s="3">
         <v>44616700</v>
       </c>
-      <c r="T42" s="3">
+      <c r="U42" s="3">
         <v>44083500</v>
       </c>
-      <c r="U42" s="3">
+      <c r="V42" s="3">
         <v>38326100</v>
       </c>
-      <c r="V42" s="3">
+      <c r="W42" s="3">
         <v>33800600</v>
       </c>
-      <c r="W42" s="3">
+      <c r="X42" s="3">
         <v>32013900</v>
       </c>
-      <c r="X42" s="3">
+      <c r="Y42" s="3">
         <v>39170300</v>
       </c>
-      <c r="Y42" s="3">
+      <c r="Z42" s="3">
         <v>33273800</v>
       </c>
-      <c r="Z42" s="3">
+      <c r="AA42" s="3">
         <v>36396600</v>
       </c>
-      <c r="AA42" s="3">
+      <c r="AB42" s="3">
         <v>38606200</v>
       </c>
-      <c r="AB42" s="3">
+      <c r="AC42" s="3">
         <v>37680800</v>
       </c>
-      <c r="AC42" s="3">
+      <c r="AD42" s="3">
         <v>39232200</v>
       </c>
-      <c r="AD42" s="3">
+      <c r="AE42" s="3">
         <v>36892000</v>
       </c>
-      <c r="AE42" s="3">
+      <c r="AF42" s="3">
         <v>30905300</v>
       </c>
-      <c r="AF42" s="3">
+      <c r="AG42" s="3">
         <v>29776700</v>
       </c>
-      <c r="AG42" s="3">
+      <c r="AH42" s="3">
         <v>20883600</v>
       </c>
-      <c r="AH42" s="3">
+      <c r="AI42" s="3">
         <v>22286700</v>
       </c>
-      <c r="AI42" s="3">
+      <c r="AJ42" s="3">
         <v>21840100</v>
       </c>
-      <c r="AJ42" s="3">
+      <c r="AK42" s="3">
         <v>20932300</v>
       </c>
-      <c r="AK42" s="3">
+      <c r="AL42" s="3">
         <v>12488600</v>
       </c>
-      <c r="AL42" s="3">
+      <c r="AM42" s="3">
         <v>14955900</v>
       </c>
-      <c r="AM42" s="3">
+      <c r="AN42" s="3">
         <v>13350900</v>
       </c>
-      <c r="AN42" s="3">
+      <c r="AO42" s="3">
         <v>14204100</v>
       </c>
-      <c r="AO42" s="3">
+      <c r="AP42" s="3">
         <v>16154100</v>
       </c>
     </row>
-    <row r="43" spans="2:41" x14ac:dyDescent="0.2">
+    <row r="43" spans="2:42" x14ac:dyDescent="0.2">
       <c r="C43" s="1" t="s">
         <v>36</v>
       </c>
       <c r="D43" s="3">
+        <v>14652700</v>
+      </c>
+      <c r="E43" s="3">
         <v>7082500</v>
       </c>
-      <c r="E43" s="3">
+      <c r="F43" s="3">
         <v>13780300</v>
       </c>
-      <c r="F43" s="3">
+      <c r="G43" s="3">
         <v>15335100</v>
       </c>
-      <c r="G43" s="3">
+      <c r="H43" s="3">
         <v>12353800</v>
       </c>
-      <c r="H43" s="3">
+      <c r="I43" s="3">
         <v>6099900</v>
       </c>
-      <c r="I43" s="3">
+      <c r="J43" s="3">
         <v>13077600</v>
       </c>
-      <c r="J43" s="3">
+      <c r="K43" s="3">
         <v>9540700</v>
       </c>
-      <c r="K43" s="3">
+      <c r="L43" s="3">
         <v>10078300</v>
       </c>
-      <c r="L43" s="3">
+      <c r="M43" s="3">
         <v>8598900</v>
       </c>
-      <c r="M43" s="3">
+      <c r="N43" s="3">
         <v>9843900</v>
       </c>
-      <c r="N43" s="3">
+      <c r="O43" s="3">
         <v>11594400</v>
       </c>
-      <c r="O43" s="3">
+      <c r="P43" s="3">
         <v>10468300</v>
       </c>
-      <c r="P43" s="3">
-        <v>0</v>
-      </c>
       <c r="Q43" s="3">
         <v>0</v>
       </c>
@@ -4466,8 +4558,11 @@
       <c r="AO43" s="3">
         <v>0</v>
       </c>
+      <c r="AP43" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="44" spans="2:41" x14ac:dyDescent="0.2">
+    <row r="44" spans="2:42" x14ac:dyDescent="0.2">
       <c r="C44" s="1" t="s">
         <v>37</v>
       </c>
@@ -4507,8 +4602,8 @@
       <c r="O44" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="P44" s="3">
-        <v>0</v>
+      <c r="P44" s="3" t="s">
+        <v>5</v>
       </c>
       <c r="Q44" s="3">
         <v>0</v>
@@ -4585,50 +4680,53 @@
       <c r="AO44" s="3">
         <v>0</v>
       </c>
+      <c r="AP44" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="45" spans="2:41" x14ac:dyDescent="0.2">
+    <row r="45" spans="2:42" x14ac:dyDescent="0.2">
       <c r="C45" s="1" t="s">
         <v>38</v>
       </c>
       <c r="D45" s="3">
+        <v>2425900</v>
+      </c>
+      <c r="E45" s="3">
         <v>5813900</v>
       </c>
-      <c r="E45" s="3">
+      <c r="F45" s="3">
         <v>2491200</v>
       </c>
-      <c r="F45" s="3">
+      <c r="G45" s="3">
         <v>2304800</v>
       </c>
-      <c r="G45" s="3">
+      <c r="H45" s="3">
         <v>1984500</v>
       </c>
-      <c r="H45" s="3">
+      <c r="I45" s="3">
         <v>3417100</v>
       </c>
-      <c r="I45" s="3">
+      <c r="J45" s="3">
         <v>2191600</v>
       </c>
-      <c r="J45" s="3">
+      <c r="K45" s="3">
         <v>2546100</v>
       </c>
-      <c r="K45" s="3">
+      <c r="L45" s="3">
         <v>2248400</v>
       </c>
-      <c r="L45" s="3">
+      <c r="M45" s="3">
         <v>3229200</v>
       </c>
-      <c r="M45" s="3">
+      <c r="N45" s="3">
         <v>2254000</v>
       </c>
-      <c r="N45" s="3">
+      <c r="O45" s="3">
         <v>2036900</v>
       </c>
-      <c r="O45" s="3">
+      <c r="P45" s="3">
         <v>1992400</v>
       </c>
-      <c r="P45" s="3">
-        <v>0</v>
-      </c>
       <c r="Q45" s="3">
         <v>0</v>
       </c>
@@ -4704,50 +4802,53 @@
       <c r="AO45" s="3">
         <v>0</v>
       </c>
+      <c r="AP45" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="46" spans="2:41" x14ac:dyDescent="0.2">
+    <row r="46" spans="2:42" x14ac:dyDescent="0.2">
       <c r="C46" s="1" t="s">
         <v>39</v>
       </c>
       <c r="D46" s="3">
+        <v>69807000</v>
+      </c>
+      <c r="E46" s="3">
         <v>70334000</v>
       </c>
-      <c r="E46" s="3">
+      <c r="F46" s="3">
         <v>71300600</v>
       </c>
-      <c r="F46" s="3">
+      <c r="G46" s="3">
         <v>69444800</v>
       </c>
-      <c r="G46" s="3">
+      <c r="H46" s="3">
         <v>58995800</v>
       </c>
-      <c r="H46" s="3">
+      <c r="I46" s="3">
         <v>51046100</v>
       </c>
-      <c r="I46" s="3">
+      <c r="J46" s="3">
         <v>70438600</v>
       </c>
-      <c r="J46" s="3">
+      <c r="K46" s="3">
         <v>50125600</v>
       </c>
-      <c r="K46" s="3">
+      <c r="L46" s="3">
         <v>54875900</v>
       </c>
-      <c r="L46" s="3">
+      <c r="M46" s="3">
         <v>53874000</v>
       </c>
-      <c r="M46" s="3">
+      <c r="N46" s="3">
         <v>49079800</v>
       </c>
-      <c r="N46" s="3">
+      <c r="O46" s="3">
         <v>55527700</v>
       </c>
-      <c r="O46" s="3">
+      <c r="P46" s="3">
         <v>55109700</v>
       </c>
-      <c r="P46" s="3">
-        <v>0</v>
-      </c>
       <c r="Q46" s="3">
         <v>0</v>
       </c>
@@ -4823,365 +4924,377 @@
       <c r="AO46" s="3">
         <v>0</v>
       </c>
+      <c r="AP46" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="47" spans="2:41" x14ac:dyDescent="0.2">
+    <row r="47" spans="2:42" x14ac:dyDescent="0.2">
       <c r="C47" s="1" t="s">
         <v>40</v>
       </c>
       <c r="D47" s="3">
+        <v>64066400</v>
+      </c>
+      <c r="E47" s="3">
         <v>51061400</v>
       </c>
-      <c r="E47" s="3">
+      <c r="F47" s="3">
         <v>64194100</v>
       </c>
-      <c r="F47" s="3">
+      <c r="G47" s="3">
         <v>44237900</v>
       </c>
-      <c r="G47" s="3">
+      <c r="H47" s="3">
         <v>43339500</v>
       </c>
-      <c r="H47" s="3">
+      <c r="I47" s="3">
         <v>29491700</v>
       </c>
-      <c r="I47" s="3">
+      <c r="J47" s="3">
         <v>43909700</v>
       </c>
-      <c r="J47" s="3">
+      <c r="K47" s="3">
         <v>45684200</v>
       </c>
-      <c r="K47" s="3">
+      <c r="L47" s="3">
         <v>45083200</v>
       </c>
-      <c r="L47" s="3">
+      <c r="M47" s="3">
         <v>33573300</v>
       </c>
-      <c r="M47" s="3">
+      <c r="N47" s="3">
         <v>46697400</v>
       </c>
-      <c r="N47" s="3">
+      <c r="O47" s="3">
         <v>47231400</v>
       </c>
-      <c r="O47" s="3">
+      <c r="P47" s="3">
         <v>47653400</v>
       </c>
-      <c r="P47" s="3">
+      <c r="Q47" s="3">
         <v>979200</v>
       </c>
-      <c r="Q47" s="3">
+      <c r="R47" s="3">
         <v>976800</v>
       </c>
-      <c r="R47" s="3">
+      <c r="S47" s="3">
         <v>1035000</v>
       </c>
-      <c r="S47" s="3">
+      <c r="T47" s="3">
         <v>1011300</v>
       </c>
-      <c r="T47" s="3">
+      <c r="U47" s="3">
         <v>1001400</v>
       </c>
-      <c r="U47" s="3">
+      <c r="V47" s="3">
         <v>896000</v>
       </c>
-      <c r="V47" s="3">
+      <c r="W47" s="3">
         <v>881500</v>
       </c>
-      <c r="W47" s="3">
+      <c r="X47" s="3">
         <v>775800</v>
       </c>
-      <c r="X47" s="3">
+      <c r="Y47" s="3">
         <v>735000</v>
       </c>
-      <c r="Y47" s="3">
+      <c r="Z47" s="3">
         <v>829200</v>
       </c>
-      <c r="Z47" s="3">
+      <c r="AA47" s="3">
         <v>714700</v>
       </c>
-      <c r="AA47" s="3">
+      <c r="AB47" s="3">
         <v>674300</v>
       </c>
-      <c r="AB47" s="3">
+      <c r="AC47" s="3">
         <v>685400</v>
       </c>
-      <c r="AC47" s="3">
+      <c r="AD47" s="3">
         <v>322100</v>
       </c>
-      <c r="AD47" s="3">
+      <c r="AE47" s="3">
         <v>311500</v>
       </c>
-      <c r="AE47" s="3">
+      <c r="AF47" s="3">
         <v>316200</v>
       </c>
-      <c r="AF47" s="3">
+      <c r="AG47" s="3">
         <v>303600</v>
       </c>
-      <c r="AG47" s="3">
+      <c r="AH47" s="3">
         <v>276700</v>
       </c>
-      <c r="AH47" s="3">
+      <c r="AI47" s="3">
         <v>346900</v>
       </c>
-      <c r="AI47" s="3">
+      <c r="AJ47" s="3">
         <v>348200</v>
       </c>
-      <c r="AJ47" s="3">
+      <c r="AK47" s="3">
         <v>367000</v>
       </c>
-      <c r="AK47" s="3">
+      <c r="AL47" s="3">
         <v>490900</v>
       </c>
-      <c r="AL47" s="3">
+      <c r="AM47" s="3">
         <v>326300</v>
       </c>
-      <c r="AM47" s="3">
+      <c r="AN47" s="3">
         <v>351100</v>
       </c>
-      <c r="AN47" s="3">
+      <c r="AO47" s="3">
         <v>395100</v>
       </c>
-      <c r="AO47" s="3">
+      <c r="AP47" s="3">
         <v>377600</v>
       </c>
     </row>
-    <row r="48" spans="2:41" x14ac:dyDescent="0.2">
+    <row r="48" spans="2:42" x14ac:dyDescent="0.2">
       <c r="C48" s="1" t="s">
         <v>41</v>
       </c>
       <c r="D48" s="3">
+        <v>6456400</v>
+      </c>
+      <c r="E48" s="3">
         <v>5254900</v>
       </c>
-      <c r="E48" s="3">
+      <c r="F48" s="3">
         <v>5401200</v>
       </c>
-      <c r="F48" s="3">
+      <c r="G48" s="3">
         <v>5310400</v>
       </c>
-      <c r="G48" s="3">
+      <c r="H48" s="3">
         <v>4933500</v>
       </c>
-      <c r="H48" s="3">
+      <c r="I48" s="3">
         <v>4937200</v>
       </c>
-      <c r="I48" s="3">
+      <c r="J48" s="3">
         <v>5522800</v>
       </c>
-      <c r="J48" s="3">
+      <c r="K48" s="3">
         <v>5103100</v>
       </c>
-      <c r="K48" s="3">
+      <c r="L48" s="3">
         <v>4908300</v>
       </c>
-      <c r="L48" s="3">
+      <c r="M48" s="3">
         <v>4983700</v>
       </c>
-      <c r="M48" s="3">
+      <c r="N48" s="3">
         <v>4486300</v>
       </c>
-      <c r="N48" s="3">
+      <c r="O48" s="3">
         <v>4434900</v>
       </c>
-      <c r="O48" s="3">
+      <c r="P48" s="3">
         <v>4401200</v>
       </c>
-      <c r="P48" s="3">
+      <c r="Q48" s="3">
         <v>2648000</v>
       </c>
-      <c r="Q48" s="3">
+      <c r="R48" s="3">
         <v>2590300</v>
       </c>
-      <c r="R48" s="3">
+      <c r="S48" s="3">
         <v>2689200</v>
       </c>
-      <c r="S48" s="3">
+      <c r="T48" s="3">
         <v>2729900</v>
       </c>
-      <c r="T48" s="3">
+      <c r="U48" s="3">
         <v>2673200</v>
       </c>
-      <c r="U48" s="3">
+      <c r="V48" s="3">
         <v>2701000</v>
       </c>
-      <c r="V48" s="3">
+      <c r="W48" s="3">
         <v>2682600</v>
       </c>
-      <c r="W48" s="3">
+      <c r="X48" s="3">
         <v>2700600</v>
       </c>
-      <c r="X48" s="3">
+      <c r="Y48" s="3">
         <v>2719200</v>
       </c>
-      <c r="Y48" s="3">
+      <c r="Z48" s="3">
         <v>2764300</v>
       </c>
-      <c r="Z48" s="3">
+      <c r="AA48" s="3">
         <v>2790300</v>
       </c>
-      <c r="AA48" s="3">
+      <c r="AB48" s="3">
         <v>2961700</v>
       </c>
-      <c r="AB48" s="3">
+      <c r="AC48" s="3">
         <v>3098200</v>
       </c>
-      <c r="AC48" s="3">
+      <c r="AD48" s="3">
         <v>3089800</v>
       </c>
-      <c r="AD48" s="3">
+      <c r="AE48" s="3">
         <v>3058200</v>
       </c>
-      <c r="AE48" s="3">
+      <c r="AF48" s="3">
         <v>3080600</v>
       </c>
-      <c r="AF48" s="3">
+      <c r="AG48" s="3">
         <v>2368100</v>
       </c>
-      <c r="AG48" s="3">
+      <c r="AH48" s="3">
         <v>2284800</v>
       </c>
-      <c r="AH48" s="3">
+      <c r="AI48" s="3">
         <v>2378800</v>
       </c>
-      <c r="AI48" s="3">
+      <c r="AJ48" s="3">
         <v>2384000</v>
       </c>
-      <c r="AJ48" s="3">
+      <c r="AK48" s="3">
         <v>2507000</v>
       </c>
-      <c r="AK48" s="3">
+      <c r="AL48" s="3">
         <v>2509800</v>
       </c>
-      <c r="AL48" s="3">
+      <c r="AM48" s="3">
         <v>2480800</v>
       </c>
-      <c r="AM48" s="3">
+      <c r="AN48" s="3">
         <v>2470200</v>
       </c>
-      <c r="AN48" s="3">
+      <c r="AO48" s="3">
         <v>2534900</v>
       </c>
-      <c r="AO48" s="3">
+      <c r="AP48" s="3">
         <v>2525400</v>
       </c>
     </row>
-    <row r="49" spans="3:41" x14ac:dyDescent="0.2">
+    <row r="49" spans="3:42" x14ac:dyDescent="0.2">
       <c r="C49" s="1" t="s">
         <v>42</v>
       </c>
       <c r="D49" s="3">
+        <v>697900</v>
+      </c>
+      <c r="E49" s="3">
         <v>503500</v>
       </c>
-      <c r="E49" s="3">
+      <c r="F49" s="3">
         <v>770100</v>
       </c>
-      <c r="F49" s="3">
+      <c r="G49" s="3">
         <v>788000</v>
       </c>
-      <c r="G49" s="3">
+      <c r="H49" s="3">
         <v>745500</v>
       </c>
-      <c r="H49" s="3">
+      <c r="I49" s="3">
         <v>552200</v>
       </c>
-      <c r="I49" s="3">
+      <c r="J49" s="3">
         <v>621800</v>
       </c>
-      <c r="J49" s="3">
+      <c r="K49" s="3">
         <v>557800</v>
       </c>
-      <c r="K49" s="3">
+      <c r="L49" s="3">
         <v>562600</v>
       </c>
-      <c r="L49" s="3">
+      <c r="M49" s="3">
         <v>582000</v>
       </c>
-      <c r="M49" s="3">
+      <c r="N49" s="3">
         <v>568100</v>
       </c>
-      <c r="N49" s="3">
+      <c r="O49" s="3">
         <v>586300</v>
       </c>
-      <c r="O49" s="3">
+      <c r="P49" s="3">
         <v>573300</v>
       </c>
-      <c r="P49" s="3">
+      <c r="Q49" s="3">
         <v>636800</v>
       </c>
-      <c r="Q49" s="3">
+      <c r="R49" s="3">
         <v>639200</v>
       </c>
-      <c r="R49" s="3">
+      <c r="S49" s="3">
         <v>596500</v>
       </c>
-      <c r="S49" s="3">
+      <c r="T49" s="3">
         <v>608700</v>
       </c>
-      <c r="T49" s="3">
+      <c r="U49" s="3">
         <v>589000</v>
       </c>
-      <c r="U49" s="3">
+      <c r="V49" s="3">
         <v>586400</v>
       </c>
-      <c r="V49" s="3">
+      <c r="W49" s="3">
         <v>581700</v>
       </c>
-      <c r="W49" s="3">
+      <c r="X49" s="3">
         <v>582600</v>
       </c>
-      <c r="X49" s="3">
+      <c r="Y49" s="3">
         <v>586100</v>
       </c>
-      <c r="Y49" s="3">
+      <c r="Z49" s="3">
         <v>615800</v>
       </c>
-      <c r="Z49" s="3">
+      <c r="AA49" s="3">
         <v>631700</v>
       </c>
-      <c r="AA49" s="3">
+      <c r="AB49" s="3">
         <v>668000</v>
       </c>
-      <c r="AB49" s="3">
+      <c r="AC49" s="3">
         <v>717500</v>
       </c>
-      <c r="AC49" s="3">
+      <c r="AD49" s="3">
         <v>590200</v>
       </c>
-      <c r="AD49" s="3">
+      <c r="AE49" s="3">
         <v>565800</v>
       </c>
-      <c r="AE49" s="3">
+      <c r="AF49" s="3">
         <v>588900</v>
       </c>
-      <c r="AF49" s="3">
+      <c r="AG49" s="3">
         <v>493300</v>
       </c>
-      <c r="AG49" s="3">
+      <c r="AH49" s="3">
         <v>502400</v>
       </c>
-      <c r="AH49" s="3">
+      <c r="AI49" s="3">
         <v>549000</v>
       </c>
-      <c r="AI49" s="3">
+      <c r="AJ49" s="3">
         <v>452700</v>
       </c>
-      <c r="AJ49" s="3">
+      <c r="AK49" s="3">
         <v>456400</v>
       </c>
-      <c r="AK49" s="3">
+      <c r="AL49" s="3">
         <v>461900</v>
       </c>
-      <c r="AL49" s="3">
+      <c r="AM49" s="3">
         <v>446100</v>
       </c>
-      <c r="AM49" s="3">
+      <c r="AN49" s="3">
         <v>415100</v>
       </c>
-      <c r="AN49" s="3">
+      <c r="AO49" s="3">
         <v>435400</v>
       </c>
-      <c r="AO49" s="3">
+      <c r="AP49" s="3">
         <v>376700</v>
       </c>
     </row>
-    <row r="50" spans="3:41" x14ac:dyDescent="0.2">
+    <row r="50" spans="3:42" x14ac:dyDescent="0.2">
       <c r="C50" s="1" t="s">
         <v>43</v>
       </c>
@@ -5299,8 +5412,11 @@
       <c r="AO50" s="3">
         <v>0</v>
       </c>
+      <c r="AP50" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="51" spans="3:41" x14ac:dyDescent="0.2">
+    <row r="51" spans="3:42" x14ac:dyDescent="0.2">
       <c r="C51" s="1" t="s">
         <v>44</v>
       </c>
@@ -5418,127 +5534,133 @@
       <c r="AO51" s="3">
         <v>0</v>
       </c>
+      <c r="AP51" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="52" spans="3:41" x14ac:dyDescent="0.2">
+    <row r="52" spans="3:42" x14ac:dyDescent="0.2">
       <c r="C52" s="1" t="s">
         <v>45</v>
       </c>
       <c r="D52" s="3">
+        <v>5004100</v>
+      </c>
+      <c r="E52" s="3">
         <v>22900500</v>
       </c>
-      <c r="E52" s="3">
+      <c r="F52" s="3">
         <v>5286500</v>
       </c>
-      <c r="F52" s="3">
+      <c r="G52" s="3">
         <v>1343400</v>
       </c>
-      <c r="G52" s="3">
+      <c r="H52" s="3">
         <v>1099500</v>
       </c>
-      <c r="H52" s="3">
+      <c r="I52" s="3">
         <v>15436000</v>
       </c>
-      <c r="I52" s="3">
+      <c r="J52" s="3">
         <v>1117800</v>
       </c>
-      <c r="J52" s="3">
+      <c r="K52" s="3">
         <v>1097200</v>
       </c>
-      <c r="K52" s="3">
+      <c r="L52" s="3">
         <v>1375500</v>
       </c>
-      <c r="L52" s="3">
+      <c r="M52" s="3">
         <v>16836600</v>
       </c>
-      <c r="M52" s="3">
+      <c r="N52" s="3">
         <v>1488400</v>
       </c>
-      <c r="N52" s="3">
+      <c r="O52" s="3">
         <v>1186200</v>
       </c>
-      <c r="O52" s="3">
+      <c r="P52" s="3">
         <v>1174600</v>
       </c>
-      <c r="P52" s="3">
+      <c r="Q52" s="3">
         <v>331800</v>
       </c>
-      <c r="Q52" s="3">
+      <c r="R52" s="3">
         <v>284500</v>
       </c>
-      <c r="R52" s="3">
+      <c r="S52" s="3">
         <v>166400</v>
       </c>
-      <c r="S52" s="3">
+      <c r="T52" s="3">
         <v>58400</v>
       </c>
-      <c r="T52" s="3">
+      <c r="U52" s="3">
         <v>59100</v>
       </c>
-      <c r="U52" s="3">
+      <c r="V52" s="3">
         <v>41100</v>
       </c>
-      <c r="V52" s="3">
+      <c r="W52" s="3">
         <v>56000</v>
       </c>
-      <c r="W52" s="3">
+      <c r="X52" s="3">
         <v>73700</v>
       </c>
-      <c r="X52" s="3">
+      <c r="Y52" s="3">
         <v>82700</v>
       </c>
-      <c r="Y52" s="3">
+      <c r="Z52" s="3">
         <v>74500</v>
       </c>
-      <c r="Z52" s="3">
+      <c r="AA52" s="3">
         <v>37800</v>
       </c>
-      <c r="AA52" s="3">
+      <c r="AB52" s="3">
         <v>38200</v>
       </c>
-      <c r="AB52" s="3">
+      <c r="AC52" s="3">
         <v>44800</v>
       </c>
-      <c r="AC52" s="3">
+      <c r="AD52" s="3">
         <v>82300</v>
       </c>
-      <c r="AD52" s="3">
+      <c r="AE52" s="3">
         <v>69500</v>
       </c>
-      <c r="AE52" s="3">
+      <c r="AF52" s="3">
         <v>68200</v>
       </c>
-      <c r="AF52" s="3">
+      <c r="AG52" s="3">
         <v>120400</v>
       </c>
-      <c r="AG52" s="3">
+      <c r="AH52" s="3">
         <v>36800</v>
       </c>
-      <c r="AH52" s="3">
+      <c r="AI52" s="3">
         <v>91100</v>
       </c>
-      <c r="AI52" s="3">
+      <c r="AJ52" s="3">
         <v>177600</v>
       </c>
-      <c r="AJ52" s="3">
+      <c r="AK52" s="3">
         <v>289300</v>
       </c>
-      <c r="AK52" s="3">
+      <c r="AL52" s="3">
         <v>234800</v>
       </c>
-      <c r="AL52" s="3">
+      <c r="AM52" s="3">
         <v>221100</v>
       </c>
-      <c r="AM52" s="3">
+      <c r="AN52" s="3">
         <v>262700</v>
       </c>
-      <c r="AN52" s="3">
+      <c r="AO52" s="3">
         <v>274800</v>
       </c>
-      <c r="AO52" s="3">
+      <c r="AP52" s="3">
         <v>143800</v>
       </c>
     </row>
-    <row r="53" spans="3:41" x14ac:dyDescent="0.2">
+    <row r="53" spans="3:42" x14ac:dyDescent="0.2">
       <c r="C53" s="1" t="s">
         <v>46</v>
       </c>
@@ -5656,127 +5778,133 @@
       <c r="AO53" s="3">
         <v>0</v>
       </c>
+      <c r="AP53" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="54" spans="3:41" x14ac:dyDescent="0.2">
+    <row r="54" spans="3:42" x14ac:dyDescent="0.2">
       <c r="C54" s="1" t="s">
         <v>47</v>
       </c>
       <c r="D54" s="3">
+        <v>402432700</v>
+      </c>
+      <c r="E54" s="3">
         <v>416660200</v>
       </c>
-      <c r="E54" s="3">
+      <c r="F54" s="3">
         <v>417822000</v>
       </c>
-      <c r="F54" s="3">
+      <c r="G54" s="3">
         <v>394651000</v>
       </c>
-      <c r="G54" s="3">
+      <c r="H54" s="3">
         <v>361721400</v>
       </c>
-      <c r="H54" s="3">
+      <c r="I54" s="3">
         <v>355900000</v>
       </c>
-      <c r="I54" s="3">
+      <c r="J54" s="3">
         <v>413964600</v>
       </c>
-      <c r="J54" s="3">
+      <c r="K54" s="3">
         <v>369217100</v>
       </c>
-      <c r="K54" s="3">
+      <c r="L54" s="3">
         <v>375587700</v>
       </c>
-      <c r="L54" s="3">
+      <c r="M54" s="3">
         <v>384037900</v>
       </c>
-      <c r="M54" s="3">
+      <c r="N54" s="3">
         <v>360962600</v>
       </c>
-      <c r="N54" s="3">
+      <c r="O54" s="3">
         <v>366653200</v>
       </c>
-      <c r="O54" s="3">
+      <c r="P54" s="3">
         <v>366661700</v>
       </c>
-      <c r="P54" s="3">
+      <c r="Q54" s="3">
         <v>360355800</v>
       </c>
-      <c r="Q54" s="3">
+      <c r="R54" s="3">
         <v>366510300</v>
       </c>
-      <c r="R54" s="3">
+      <c r="S54" s="3">
         <v>368558700</v>
       </c>
-      <c r="S54" s="3">
+      <c r="T54" s="3">
         <v>358592300</v>
       </c>
-      <c r="T54" s="3">
+      <c r="U54" s="3">
         <v>335387900</v>
       </c>
-      <c r="U54" s="3">
+      <c r="V54" s="3">
         <v>328638700</v>
       </c>
-      <c r="V54" s="3">
+      <c r="W54" s="3">
         <v>315953000</v>
       </c>
-      <c r="W54" s="3">
+      <c r="X54" s="3">
         <v>307917200</v>
       </c>
-      <c r="X54" s="3">
+      <c r="Y54" s="3">
         <v>295320000</v>
       </c>
-      <c r="Y54" s="3">
+      <c r="Z54" s="3">
         <v>293246000</v>
       </c>
-      <c r="Z54" s="3">
+      <c r="AA54" s="3">
         <v>292659600</v>
       </c>
-      <c r="AA54" s="3">
+      <c r="AB54" s="3">
         <v>306353500</v>
       </c>
-      <c r="AB54" s="3">
+      <c r="AC54" s="3">
         <v>307683600</v>
       </c>
-      <c r="AC54" s="3">
+      <c r="AD54" s="3">
         <v>314996600</v>
       </c>
-      <c r="AD54" s="3">
+      <c r="AE54" s="3">
         <v>316273500</v>
       </c>
-      <c r="AE54" s="3">
+      <c r="AF54" s="3">
         <v>314085600</v>
       </c>
-      <c r="AF54" s="3">
+      <c r="AG54" s="3">
         <v>285975600</v>
       </c>
-      <c r="AG54" s="3">
+      <c r="AH54" s="3">
         <v>267139300</v>
       </c>
-      <c r="AH54" s="3">
+      <c r="AI54" s="3">
         <v>274311500</v>
       </c>
-      <c r="AI54" s="3">
+      <c r="AJ54" s="3">
         <v>273668600</v>
       </c>
-      <c r="AJ54" s="3">
+      <c r="AK54" s="3">
         <v>278340000</v>
       </c>
-      <c r="AK54" s="3">
+      <c r="AL54" s="3">
         <v>279730100</v>
       </c>
-      <c r="AL54" s="3">
+      <c r="AM54" s="3">
         <v>278137400</v>
       </c>
-      <c r="AM54" s="3">
+      <c r="AN54" s="3">
         <v>273600800</v>
       </c>
-      <c r="AN54" s="3">
+      <c r="AO54" s="3">
         <v>279614500</v>
       </c>
-      <c r="AO54" s="3">
+      <c r="AP54" s="3">
         <v>281548700</v>
       </c>
     </row>
-    <row r="55" spans="3:41" x14ac:dyDescent="0.2">
+    <row r="55" spans="3:42" x14ac:dyDescent="0.2">
       <c r="C55" s="1" t="s">
         <v>48</v>
       </c>
@@ -5818,8 +5946,9 @@
       <c r="AM55" s="3"/>
       <c r="AN55" s="3"/>
       <c r="AO55" s="3"/>
+      <c r="AP55" s="3"/>
     </row>
-    <row r="56" spans="3:41" x14ac:dyDescent="0.2">
+    <row r="56" spans="3:42" x14ac:dyDescent="0.2">
       <c r="C56" s="1" t="s">
         <v>49</v>
       </c>
@@ -5861,169 +5990,173 @@
       <c r="AM56" s="3"/>
       <c r="AN56" s="3"/>
       <c r="AO56" s="3"/>
+      <c r="AP56" s="3"/>
     </row>
-    <row r="57" spans="3:41" x14ac:dyDescent="0.2">
+    <row r="57" spans="3:42" x14ac:dyDescent="0.2">
       <c r="C57" s="1" t="s">
         <v>50</v>
       </c>
       <c r="D57" s="3">
+        <v>258292200</v>
+      </c>
+      <c r="E57" s="3">
         <v>266776300</v>
       </c>
-      <c r="E57" s="3">
+      <c r="F57" s="3">
         <v>276347000</v>
       </c>
-      <c r="F57" s="3">
+      <c r="G57" s="3">
         <v>287825900</v>
       </c>
-      <c r="G57" s="3">
+      <c r="H57" s="3">
         <v>262183700</v>
       </c>
-      <c r="H57" s="3">
+      <c r="I57" s="3">
         <v>253583100</v>
       </c>
-      <c r="I57" s="3">
+      <c r="J57" s="3">
         <v>303683400</v>
       </c>
-      <c r="J57" s="3">
+      <c r="K57" s="3">
         <v>269353200</v>
       </c>
-      <c r="K57" s="3">
+      <c r="L57" s="3">
         <v>273669100</v>
       </c>
-      <c r="L57" s="3">
+      <c r="M57" s="3">
         <v>283746600</v>
       </c>
-      <c r="M57" s="3">
+      <c r="N57" s="3">
         <v>257925300</v>
       </c>
-      <c r="N57" s="3">
+      <c r="O57" s="3">
         <v>263215600</v>
       </c>
-      <c r="O57" s="3">
+      <c r="P57" s="3">
         <v>259046400</v>
       </c>
-      <c r="P57" s="3">
+      <c r="Q57" s="3">
         <v>8592200</v>
       </c>
-      <c r="Q57" s="3">
+      <c r="R57" s="3">
         <v>12736100</v>
       </c>
-      <c r="R57" s="3">
+      <c r="S57" s="3">
         <v>12538100</v>
       </c>
-      <c r="S57" s="3">
+      <c r="T57" s="3">
         <v>11104000</v>
       </c>
-      <c r="T57" s="3">
+      <c r="U57" s="3">
         <v>10844700</v>
       </c>
-      <c r="U57" s="3">
+      <c r="V57" s="3">
         <v>7957500</v>
       </c>
-      <c r="V57" s="3">
+      <c r="W57" s="3">
         <v>9468900</v>
       </c>
-      <c r="W57" s="3">
+      <c r="X57" s="3">
         <v>7995800</v>
       </c>
-      <c r="X57" s="3">
+      <c r="Y57" s="3">
         <v>3698600</v>
       </c>
-      <c r="Y57" s="3">
+      <c r="Z57" s="3">
         <v>7530800</v>
       </c>
-      <c r="Z57" s="3">
+      <c r="AA57" s="3">
         <v>8467000</v>
       </c>
-      <c r="AA57" s="3">
+      <c r="AB57" s="3">
         <v>9538600</v>
       </c>
-      <c r="AB57" s="3">
+      <c r="AC57" s="3">
         <v>7264700</v>
       </c>
-      <c r="AC57" s="3">
+      <c r="AD57" s="3">
         <v>13339700</v>
       </c>
-      <c r="AD57" s="3">
+      <c r="AE57" s="3">
         <v>15138200</v>
       </c>
-      <c r="AE57" s="3">
+      <c r="AF57" s="3">
         <v>14778600</v>
       </c>
-      <c r="AF57" s="3">
+      <c r="AG57" s="3">
         <v>10988500</v>
       </c>
-      <c r="AG57" s="3">
+      <c r="AH57" s="3">
         <v>12068900</v>
       </c>
-      <c r="AH57" s="3">
+      <c r="AI57" s="3">
         <v>11638400</v>
       </c>
-      <c r="AI57" s="3">
+      <c r="AJ57" s="3">
         <v>12317300</v>
       </c>
-      <c r="AJ57" s="3">
+      <c r="AK57" s="3">
         <v>5801500</v>
       </c>
-      <c r="AK57" s="3">
+      <c r="AL57" s="3">
         <v>13814400</v>
       </c>
-      <c r="AL57" s="3">
+      <c r="AM57" s="3">
         <v>14756900</v>
       </c>
-      <c r="AM57" s="3">
+      <c r="AN57" s="3">
         <v>10823000</v>
       </c>
-      <c r="AN57" s="3">
+      <c r="AO57" s="3">
         <v>13329400</v>
       </c>
-      <c r="AO57" s="3">
+      <c r="AP57" s="3">
         <v>15356600</v>
       </c>
     </row>
-    <row r="58" spans="3:41" x14ac:dyDescent="0.2">
+    <row r="58" spans="3:42" x14ac:dyDescent="0.2">
       <c r="C58" s="1" t="s">
         <v>51</v>
       </c>
       <c r="D58" s="3">
+        <v>11982900</v>
+      </c>
+      <c r="E58" s="3">
         <v>11198400</v>
       </c>
-      <c r="E58" s="3">
+      <c r="F58" s="3">
         <v>9091100</v>
       </c>
-      <c r="F58" s="3">
+      <c r="G58" s="3">
         <v>8966800</v>
       </c>
-      <c r="G58" s="3">
+      <c r="H58" s="3">
         <v>10611200</v>
       </c>
-      <c r="H58" s="3">
+      <c r="I58" s="3">
         <v>12014400</v>
       </c>
-      <c r="I58" s="3">
+      <c r="J58" s="3">
         <v>10388900</v>
       </c>
-      <c r="J58" s="3">
+      <c r="K58" s="3">
         <v>10701400</v>
       </c>
-      <c r="K58" s="3">
+      <c r="L58" s="3">
         <v>11337600</v>
       </c>
-      <c r="L58" s="3">
+      <c r="M58" s="3">
         <v>9863100</v>
       </c>
-      <c r="M58" s="3">
+      <c r="N58" s="3">
         <v>11103300</v>
       </c>
-      <c r="N58" s="3">
+      <c r="O58" s="3">
         <v>10559700</v>
       </c>
-      <c r="O58" s="3">
+      <c r="P58" s="3">
         <v>10550500</v>
       </c>
-      <c r="P58" s="3">
-        <v>0</v>
-      </c>
       <c r="Q58" s="3">
         <v>0</v>
       </c>
@@ -6099,169 +6232,175 @@
       <c r="AO58" s="3">
         <v>0</v>
       </c>
+      <c r="AP58" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="59" spans="3:41" x14ac:dyDescent="0.2">
+    <row r="59" spans="3:42" x14ac:dyDescent="0.2">
       <c r="C59" s="1" t="s">
         <v>52</v>
       </c>
       <c r="D59" s="3">
+        <v>1190800</v>
+      </c>
+      <c r="E59" s="3">
         <v>1226800</v>
       </c>
-      <c r="E59" s="3">
+      <c r="F59" s="3">
         <v>1113600</v>
       </c>
-      <c r="F59" s="3">
+      <c r="G59" s="3">
         <v>1084300</v>
       </c>
-      <c r="G59" s="3">
+      <c r="H59" s="3">
         <v>825800</v>
       </c>
-      <c r="H59" s="3">
+      <c r="I59" s="3">
         <v>747300</v>
       </c>
-      <c r="I59" s="3">
+      <c r="J59" s="3">
         <v>917100</v>
       </c>
-      <c r="J59" s="3">
+      <c r="K59" s="3">
         <v>585700</v>
       </c>
-      <c r="K59" s="3">
+      <c r="L59" s="3">
         <v>748600</v>
       </c>
-      <c r="L59" s="3">
+      <c r="M59" s="3">
         <v>795100</v>
       </c>
-      <c r="M59" s="3">
+      <c r="N59" s="3">
         <v>581800</v>
       </c>
-      <c r="N59" s="3">
+      <c r="O59" s="3">
         <v>593500</v>
       </c>
-      <c r="O59" s="3">
+      <c r="P59" s="3">
         <v>1203800</v>
       </c>
-      <c r="P59" s="3">
+      <c r="Q59" s="3">
         <v>3047200</v>
       </c>
-      <c r="Q59" s="3">
+      <c r="R59" s="3">
         <v>2229700</v>
       </c>
-      <c r="R59" s="3">
+      <c r="S59" s="3">
         <v>1968300</v>
       </c>
-      <c r="S59" s="3">
+      <c r="T59" s="3">
         <v>2093100</v>
       </c>
-      <c r="T59" s="3">
+      <c r="U59" s="3">
         <v>1991300</v>
       </c>
-      <c r="U59" s="3">
+      <c r="V59" s="3">
         <v>1538600</v>
       </c>
-      <c r="V59" s="3">
+      <c r="W59" s="3">
         <v>1446500</v>
       </c>
-      <c r="W59" s="3">
+      <c r="X59" s="3">
         <v>1600800</v>
       </c>
-      <c r="X59" s="3">
+      <c r="Y59" s="3">
         <v>1790900</v>
       </c>
-      <c r="Y59" s="3">
+      <c r="Z59" s="3">
         <v>1521700</v>
       </c>
-      <c r="Z59" s="3">
+      <c r="AA59" s="3">
         <v>1545300</v>
       </c>
-      <c r="AA59" s="3">
+      <c r="AB59" s="3">
         <v>1892000</v>
       </c>
-      <c r="AB59" s="3">
+      <c r="AC59" s="3">
         <v>2294100</v>
       </c>
-      <c r="AC59" s="3">
+      <c r="AD59" s="3">
         <v>2199800</v>
       </c>
-      <c r="AD59" s="3">
+      <c r="AE59" s="3">
         <v>2064700</v>
       </c>
-      <c r="AE59" s="3">
+      <c r="AF59" s="3">
         <v>2149400</v>
       </c>
-      <c r="AF59" s="3">
+      <c r="AG59" s="3">
         <v>1989900</v>
       </c>
-      <c r="AG59" s="3">
+      <c r="AH59" s="3">
         <v>1798500</v>
       </c>
-      <c r="AH59" s="3">
+      <c r="AI59" s="3">
         <v>1649500</v>
       </c>
-      <c r="AI59" s="3">
+      <c r="AJ59" s="3">
         <v>1642100</v>
       </c>
-      <c r="AJ59" s="3">
+      <c r="AK59" s="3">
         <v>2008600</v>
       </c>
-      <c r="AK59" s="3">
+      <c r="AL59" s="3">
         <v>2057400</v>
       </c>
-      <c r="AL59" s="3">
+      <c r="AM59" s="3">
         <v>1681400</v>
       </c>
-      <c r="AM59" s="3">
+      <c r="AN59" s="3">
         <v>1880000</v>
       </c>
-      <c r="AN59" s="3">
+      <c r="AO59" s="3">
         <v>2004400</v>
       </c>
-      <c r="AO59" s="3">
+      <c r="AP59" s="3">
         <v>1813400</v>
       </c>
     </row>
-    <row r="60" spans="3:41" x14ac:dyDescent="0.2">
+    <row r="60" spans="3:42" x14ac:dyDescent="0.2">
       <c r="C60" s="1" t="s">
         <v>53</v>
       </c>
       <c r="D60" s="3">
+        <v>274242200</v>
+      </c>
+      <c r="E60" s="3">
         <v>282288500</v>
       </c>
-      <c r="E60" s="3">
+      <c r="F60" s="3">
         <v>289912100</v>
       </c>
-      <c r="F60" s="3">
+      <c r="G60" s="3">
         <v>301362800</v>
       </c>
-      <c r="G60" s="3">
+      <c r="H60" s="3">
         <v>276760100</v>
       </c>
-      <c r="H60" s="3">
+      <c r="I60" s="3">
         <v>269522700</v>
       </c>
-      <c r="I60" s="3">
+      <c r="J60" s="3">
         <v>318811800</v>
       </c>
-      <c r="J60" s="3">
+      <c r="K60" s="3">
         <v>283969800</v>
       </c>
-      <c r="K60" s="3">
+      <c r="L60" s="3">
         <v>288965400</v>
       </c>
-      <c r="L60" s="3">
+      <c r="M60" s="3">
         <v>297751000</v>
       </c>
-      <c r="M60" s="3">
+      <c r="N60" s="3">
         <v>272946300</v>
       </c>
-      <c r="N60" s="3">
+      <c r="O60" s="3">
         <v>277365200</v>
       </c>
-      <c r="O60" s="3">
+      <c r="P60" s="3">
         <v>273486900</v>
       </c>
-      <c r="P60" s="3">
-        <v>0</v>
-      </c>
       <c r="Q60" s="3">
         <v>0</v>
       </c>
@@ -6337,246 +6476,255 @@
       <c r="AO60" s="3">
         <v>0</v>
       </c>
+      <c r="AP60" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="61" spans="3:41" x14ac:dyDescent="0.2">
+    <row r="61" spans="3:42" x14ac:dyDescent="0.2">
       <c r="C61" s="1" t="s">
         <v>54</v>
       </c>
       <c r="D61" s="3">
+        <v>56538600</v>
+      </c>
+      <c r="E61" s="3">
         <v>61015700</v>
       </c>
-      <c r="E61" s="3">
+      <c r="F61" s="3">
         <v>57103900</v>
       </c>
-      <c r="F61" s="3">
+      <c r="G61" s="3">
         <v>58864300</v>
       </c>
-      <c r="G61" s="3">
+      <c r="H61" s="3">
         <v>51786600</v>
       </c>
-      <c r="H61" s="3">
+      <c r="I61" s="3">
         <v>52292900</v>
       </c>
-      <c r="I61" s="3">
+      <c r="J61" s="3">
         <v>57884900</v>
       </c>
-      <c r="J61" s="3">
+      <c r="K61" s="3">
         <v>51737100</v>
       </c>
-      <c r="K61" s="3">
+      <c r="L61" s="3">
         <v>52671400</v>
       </c>
-      <c r="L61" s="3">
+      <c r="M61" s="3">
         <v>54929200</v>
       </c>
-      <c r="M61" s="3">
+      <c r="N61" s="3">
         <v>53360000</v>
       </c>
-      <c r="N61" s="3">
+      <c r="O61" s="3">
         <v>54858600</v>
       </c>
-      <c r="O61" s="3">
+      <c r="P61" s="3">
         <v>55629400</v>
       </c>
-      <c r="P61" s="3">
+      <c r="Q61" s="3">
         <v>52670100</v>
       </c>
-      <c r="Q61" s="3">
+      <c r="R61" s="3">
         <v>58817800</v>
       </c>
-      <c r="R61" s="3">
+      <c r="S61" s="3">
         <v>58413400</v>
       </c>
-      <c r="S61" s="3">
+      <c r="T61" s="3">
         <v>54512100</v>
       </c>
-      <c r="T61" s="3">
+      <c r="U61" s="3">
         <v>51506600</v>
       </c>
-      <c r="U61" s="3">
+      <c r="V61" s="3">
         <v>49335300</v>
       </c>
-      <c r="V61" s="3">
+      <c r="W61" s="3">
         <v>46999300</v>
       </c>
-      <c r="W61" s="3">
+      <c r="X61" s="3">
         <v>43329900</v>
       </c>
-      <c r="X61" s="3">
+      <c r="Y61" s="3">
         <v>42586400</v>
       </c>
-      <c r="Y61" s="3">
+      <c r="Z61" s="3">
         <v>38230600</v>
       </c>
-      <c r="Z61" s="3">
+      <c r="AA61" s="3">
         <v>39214800</v>
       </c>
-      <c r="AA61" s="3">
+      <c r="AB61" s="3">
         <v>43080800</v>
       </c>
-      <c r="AB61" s="3">
+      <c r="AC61" s="3">
         <v>42129500</v>
       </c>
-      <c r="AC61" s="3">
+      <c r="AD61" s="3">
         <v>44185000</v>
       </c>
-      <c r="AD61" s="3">
+      <c r="AE61" s="3">
         <v>43142100</v>
       </c>
-      <c r="AE61" s="3">
+      <c r="AF61" s="3">
         <v>40307800</v>
       </c>
-      <c r="AF61" s="3">
+      <c r="AG61" s="3">
         <v>36868700</v>
       </c>
-      <c r="AG61" s="3">
+      <c r="AH61" s="3">
         <v>34955700</v>
       </c>
-      <c r="AH61" s="3">
+      <c r="AI61" s="3">
         <v>35115500</v>
       </c>
-      <c r="AI61" s="3">
+      <c r="AJ61" s="3">
         <v>34009900</v>
       </c>
-      <c r="AJ61" s="3">
+      <c r="AK61" s="3">
         <v>36941800</v>
       </c>
-      <c r="AK61" s="3">
+      <c r="AL61" s="3">
         <v>37408900</v>
       </c>
-      <c r="AL61" s="3">
+      <c r="AM61" s="3">
         <v>35000000</v>
       </c>
-      <c r="AM61" s="3">
+      <c r="AN61" s="3">
         <v>33280700</v>
       </c>
-      <c r="AN61" s="3">
+      <c r="AO61" s="3">
         <v>34538700</v>
       </c>
-      <c r="AO61" s="3">
+      <c r="AP61" s="3">
         <v>33926000</v>
       </c>
     </row>
-    <row r="62" spans="3:41" x14ac:dyDescent="0.2">
+    <row r="62" spans="3:42" x14ac:dyDescent="0.2">
       <c r="C62" s="1" t="s">
         <v>55</v>
       </c>
       <c r="D62" s="3">
+        <v>43878000</v>
+      </c>
+      <c r="E62" s="3">
         <v>46041700</v>
       </c>
-      <c r="E62" s="3">
+      <c r="F62" s="3">
         <v>42772800</v>
       </c>
-      <c r="F62" s="3">
+      <c r="G62" s="3">
         <v>6912600</v>
       </c>
-      <c r="G62" s="3">
+      <c r="H62" s="3">
         <v>7918500</v>
       </c>
-      <c r="H62" s="3">
+      <c r="I62" s="3">
         <v>8428000</v>
       </c>
-      <c r="I62" s="3">
+      <c r="J62" s="3">
         <v>8065900</v>
       </c>
-      <c r="J62" s="3">
+      <c r="K62" s="3">
         <v>6973100</v>
       </c>
-      <c r="K62" s="3">
+      <c r="L62" s="3">
         <v>7766400</v>
       </c>
-      <c r="L62" s="3">
+      <c r="M62" s="3">
         <v>4724200</v>
       </c>
-      <c r="M62" s="3">
+      <c r="N62" s="3">
         <v>8885900</v>
       </c>
-      <c r="N62" s="3">
+      <c r="O62" s="3">
         <v>8657200</v>
       </c>
-      <c r="O62" s="3">
+      <c r="P62" s="3">
         <v>11788800</v>
       </c>
-      <c r="P62" s="3">
+      <c r="Q62" s="3">
         <v>459600</v>
       </c>
-      <c r="Q62" s="3">
+      <c r="R62" s="3">
         <v>438000</v>
       </c>
-      <c r="R62" s="3">
+      <c r="S62" s="3">
         <v>469900</v>
       </c>
-      <c r="S62" s="3">
+      <c r="T62" s="3">
         <v>523500</v>
       </c>
-      <c r="T62" s="3">
+      <c r="U62" s="3">
         <v>608300</v>
       </c>
-      <c r="U62" s="3">
+      <c r="V62" s="3">
         <v>663300</v>
       </c>
-      <c r="V62" s="3">
+      <c r="W62" s="3">
         <v>620300</v>
       </c>
-      <c r="W62" s="3">
+      <c r="X62" s="3">
         <v>542300</v>
       </c>
-      <c r="X62" s="3">
+      <c r="Y62" s="3">
         <v>528500</v>
       </c>
-      <c r="Y62" s="3">
+      <c r="Z62" s="3">
         <v>720700</v>
       </c>
-      <c r="Z62" s="3">
+      <c r="AA62" s="3">
         <v>691400</v>
       </c>
-      <c r="AA62" s="3">
+      <c r="AB62" s="3">
         <v>680000</v>
       </c>
-      <c r="AB62" s="3">
+      <c r="AC62" s="3">
         <v>570200</v>
       </c>
-      <c r="AC62" s="3">
+      <c r="AD62" s="3">
         <v>714600</v>
       </c>
-      <c r="AD62" s="3">
+      <c r="AE62" s="3">
         <v>648100</v>
       </c>
-      <c r="AE62" s="3">
+      <c r="AF62" s="3">
         <v>618700</v>
       </c>
-      <c r="AF62" s="3">
+      <c r="AG62" s="3">
         <v>520300</v>
       </c>
-      <c r="AG62" s="3">
+      <c r="AH62" s="3">
         <v>418500</v>
       </c>
-      <c r="AH62" s="3">
+      <c r="AI62" s="3">
         <v>420800</v>
       </c>
-      <c r="AI62" s="3">
+      <c r="AJ62" s="3">
         <v>527700</v>
       </c>
-      <c r="AJ62" s="3">
+      <c r="AK62" s="3">
         <v>419200</v>
       </c>
-      <c r="AK62" s="3">
+      <c r="AL62" s="3">
         <v>395900</v>
       </c>
-      <c r="AL62" s="3">
+      <c r="AM62" s="3">
         <v>382900</v>
       </c>
-      <c r="AM62" s="3">
+      <c r="AN62" s="3">
         <v>400700</v>
       </c>
-      <c r="AN62" s="3">
+      <c r="AO62" s="3">
         <v>463600</v>
       </c>
-      <c r="AO62" s="3">
+      <c r="AP62" s="3">
         <v>459900</v>
       </c>
     </row>
-    <row r="63" spans="3:41" x14ac:dyDescent="0.2">
+    <row r="63" spans="3:42" x14ac:dyDescent="0.2">
       <c r="C63" s="1" t="s">
         <v>56</v>
       </c>
@@ -6694,8 +6842,11 @@
       <c r="AO63" s="3">
         <v>0</v>
       </c>
+      <c r="AP63" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="64" spans="3:41" x14ac:dyDescent="0.2">
+    <row r="64" spans="3:42" x14ac:dyDescent="0.2">
       <c r="C64" s="1" t="s">
         <v>20</v>
       </c>
@@ -6813,8 +6964,11 @@
       <c r="AO64" s="3">
         <v>0</v>
       </c>
+      <c r="AP64" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="65" spans="2:41" x14ac:dyDescent="0.2">
+    <row r="65" spans="2:42" x14ac:dyDescent="0.2">
       <c r="C65" s="1" t="s">
         <v>57</v>
       </c>
@@ -6932,127 +7086,133 @@
       <c r="AO65" s="3">
         <v>0</v>
       </c>
+      <c r="AP65" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="66" spans="2:41" x14ac:dyDescent="0.2">
+    <row r="66" spans="2:42" x14ac:dyDescent="0.2">
       <c r="C66" s="1" t="s">
         <v>58</v>
       </c>
       <c r="D66" s="3">
+        <v>376216600</v>
+      </c>
+      <c r="E66" s="3">
         <v>390433100</v>
       </c>
-      <c r="E66" s="3">
+      <c r="F66" s="3">
         <v>391375900</v>
       </c>
-      <c r="F66" s="3">
+      <c r="G66" s="3">
         <v>368261100</v>
       </c>
-      <c r="G66" s="3">
+      <c r="H66" s="3">
         <v>337599900</v>
       </c>
-      <c r="H66" s="3">
+      <c r="I66" s="3">
         <v>331601300</v>
       </c>
-      <c r="I66" s="3">
+      <c r="J66" s="3">
         <v>386400900</v>
       </c>
-      <c r="J66" s="3">
+      <c r="K66" s="3">
         <v>343710800</v>
       </c>
-      <c r="K66" s="3">
+      <c r="L66" s="3">
         <v>350345300</v>
       </c>
-      <c r="L66" s="3">
+      <c r="M66" s="3">
         <v>358283300</v>
       </c>
-      <c r="M66" s="3">
+      <c r="N66" s="3">
         <v>336284100</v>
       </c>
-      <c r="N66" s="3">
+      <c r="O66" s="3">
         <v>341832200</v>
       </c>
-      <c r="O66" s="3">
+      <c r="P66" s="3">
         <v>341656500</v>
       </c>
-      <c r="P66" s="3">
+      <c r="Q66" s="3">
         <v>338784400</v>
       </c>
-      <c r="Q66" s="3">
+      <c r="R66" s="3">
         <v>345885900</v>
       </c>
-      <c r="R66" s="3">
+      <c r="S66" s="3">
         <v>348018900</v>
       </c>
-      <c r="S66" s="3">
+      <c r="T66" s="3">
         <v>338354200</v>
       </c>
-      <c r="T66" s="3">
+      <c r="U66" s="3">
         <v>316006400</v>
       </c>
-      <c r="U66" s="3">
+      <c r="V66" s="3">
         <v>309651700</v>
       </c>
-      <c r="V66" s="3">
+      <c r="W66" s="3">
         <v>297533600</v>
       </c>
-      <c r="W66" s="3">
+      <c r="X66" s="3">
         <v>290517700</v>
       </c>
-      <c r="X66" s="3">
+      <c r="Y66" s="3">
         <v>278260300</v>
       </c>
-      <c r="Y66" s="3">
+      <c r="Z66" s="3">
         <v>275726000</v>
       </c>
-      <c r="Z66" s="3">
+      <c r="AA66" s="3">
         <v>275487700</v>
       </c>
-      <c r="AA66" s="3">
+      <c r="AB66" s="3">
         <v>288675900</v>
       </c>
-      <c r="AB66" s="3">
+      <c r="AC66" s="3">
         <v>289399800</v>
       </c>
-      <c r="AC66" s="3">
+      <c r="AD66" s="3">
         <v>297278600</v>
       </c>
-      <c r="AD66" s="3">
+      <c r="AE66" s="3">
         <v>299163500</v>
       </c>
-      <c r="AE66" s="3">
+      <c r="AF66" s="3">
         <v>296968200</v>
       </c>
-      <c r="AF66" s="3">
+      <c r="AG66" s="3">
         <v>267714100</v>
       </c>
-      <c r="AG66" s="3">
+      <c r="AH66" s="3">
         <v>249559900</v>
       </c>
-      <c r="AH66" s="3">
+      <c r="AI66" s="3">
         <v>256847800</v>
       </c>
-      <c r="AI66" s="3">
+      <c r="AJ66" s="3">
         <v>256582900</v>
       </c>
-      <c r="AJ66" s="3">
+      <c r="AK66" s="3">
         <v>260418000</v>
       </c>
-      <c r="AK66" s="3">
+      <c r="AL66" s="3">
         <v>261733600</v>
       </c>
-      <c r="AL66" s="3">
+      <c r="AM66" s="3">
         <v>260311800</v>
       </c>
-      <c r="AM66" s="3">
+      <c r="AN66" s="3">
         <v>255640700</v>
       </c>
-      <c r="AN66" s="3">
+      <c r="AO66" s="3">
         <v>261266900</v>
       </c>
-      <c r="AO66" s="3">
+      <c r="AP66" s="3">
         <v>263136400</v>
       </c>
     </row>
-    <row r="67" spans="2:41" x14ac:dyDescent="0.2">
+    <row r="67" spans="2:42" x14ac:dyDescent="0.2">
       <c r="C67" s="1" t="s">
         <v>59</v>
       </c>
@@ -7094,8 +7254,9 @@
       <c r="AM67" s="3"/>
       <c r="AN67" s="3"/>
       <c r="AO67" s="3"/>
+      <c r="AP67" s="3"/>
     </row>
-    <row r="68" spans="2:41" x14ac:dyDescent="0.2">
+    <row r="68" spans="2:42" x14ac:dyDescent="0.2">
       <c r="C68" s="1" t="s">
         <v>60</v>
       </c>
@@ -7213,8 +7374,11 @@
       <c r="AO68" s="3">
         <v>0</v>
       </c>
+      <c r="AP68" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="69" spans="2:41" x14ac:dyDescent="0.2">
+    <row r="69" spans="2:42" x14ac:dyDescent="0.2">
       <c r="C69" s="1" t="s">
         <v>61</v>
       </c>
@@ -7332,8 +7496,11 @@
       <c r="AO69" s="3">
         <v>0</v>
       </c>
+      <c r="AP69" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="70" spans="2:41" x14ac:dyDescent="0.2">
+    <row r="70" spans="2:42" x14ac:dyDescent="0.2">
       <c r="C70" s="1" t="s">
         <v>62</v>
       </c>
@@ -7451,8 +7618,11 @@
       <c r="AO70" s="3">
         <v>0</v>
       </c>
+      <c r="AP70" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="71" spans="2:41" x14ac:dyDescent="0.2">
+    <row r="71" spans="2:42" x14ac:dyDescent="0.2">
       <c r="C71" s="1" t="s">
         <v>63</v>
       </c>
@@ -7570,127 +7740,133 @@
       <c r="AO71" s="3">
         <v>0</v>
       </c>
+      <c r="AP71" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="72" spans="2:41" x14ac:dyDescent="0.2">
+    <row r="72" spans="2:42" x14ac:dyDescent="0.2">
       <c r="C72" s="1" t="s">
         <v>64</v>
       </c>
       <c r="D72" s="3">
+        <v>18918300</v>
+      </c>
+      <c r="E72" s="3">
         <v>19944300</v>
       </c>
-      <c r="E72" s="3">
+      <c r="F72" s="3">
         <v>20390800</v>
       </c>
-      <c r="F72" s="3">
+      <c r="G72" s="3">
         <v>20492400</v>
       </c>
-      <c r="G72" s="3">
+      <c r="H72" s="3">
         <v>18322200</v>
       </c>
-      <c r="H72" s="3">
+      <c r="I72" s="3">
         <v>18243700</v>
       </c>
-      <c r="I72" s="3">
+      <c r="J72" s="3">
         <v>20282200</v>
       </c>
-      <c r="J72" s="3">
+      <c r="K72" s="3">
         <v>18807000</v>
       </c>
-      <c r="K72" s="3">
+      <c r="L72" s="3">
         <v>18719000</v>
       </c>
-      <c r="L72" s="3">
+      <c r="M72" s="3">
         <v>19268400</v>
       </c>
-      <c r="M72" s="3">
+      <c r="N72" s="3">
         <v>18710700</v>
       </c>
-      <c r="N72" s="3">
+      <c r="O72" s="3">
         <v>18565400</v>
       </c>
-      <c r="O72" s="3">
+      <c r="P72" s="3">
         <v>18299100</v>
       </c>
-      <c r="P72" s="3">
+      <c r="Q72" s="3">
         <v>17812600</v>
       </c>
-      <c r="Q72" s="3">
+      <c r="R72" s="3">
         <v>17007700</v>
       </c>
-      <c r="R72" s="3">
+      <c r="S72" s="3">
         <v>17130600</v>
       </c>
-      <c r="S72" s="3">
+      <c r="T72" s="3">
         <v>16662400</v>
       </c>
-      <c r="T72" s="3">
+      <c r="U72" s="3">
         <v>16044400</v>
       </c>
-      <c r="U72" s="3">
+      <c r="V72" s="3">
         <v>15764300</v>
       </c>
-      <c r="V72" s="3">
+      <c r="W72" s="3">
         <v>15298800</v>
       </c>
-      <c r="W72" s="3">
+      <c r="X72" s="3">
         <v>14524300</v>
       </c>
-      <c r="X72" s="3">
+      <c r="Y72" s="3">
         <v>14258500</v>
       </c>
-      <c r="Y72" s="3">
+      <c r="Z72" s="3">
         <v>14719300</v>
       </c>
-      <c r="Z72" s="3">
+      <c r="AA72" s="3">
         <v>14362200</v>
       </c>
-      <c r="AA72" s="3">
+      <c r="AB72" s="3">
         <v>15002800</v>
       </c>
-      <c r="AB72" s="3">
+      <c r="AC72" s="3">
         <v>15745800</v>
       </c>
-      <c r="AC72" s="3">
+      <c r="AD72" s="3">
         <v>15573800</v>
       </c>
-      <c r="AD72" s="3">
+      <c r="AE72" s="3">
         <v>15698600</v>
       </c>
-      <c r="AE72" s="3">
+      <c r="AF72" s="3">
         <v>15678000</v>
       </c>
-      <c r="AF72" s="3">
+      <c r="AG72" s="3">
         <v>14384700</v>
       </c>
-      <c r="AG72" s="3">
+      <c r="AH72" s="3">
         <v>13795900</v>
       </c>
-      <c r="AH72" s="3">
+      <c r="AI72" s="3">
         <v>13837700</v>
       </c>
-      <c r="AI72" s="3">
+      <c r="AJ72" s="3">
         <v>13273900</v>
       </c>
-      <c r="AJ72" s="3">
+      <c r="AK72" s="3">
         <v>13745600</v>
       </c>
-      <c r="AK72" s="3">
+      <c r="AL72" s="3">
         <v>13660700</v>
       </c>
-      <c r="AL72" s="3">
+      <c r="AM72" s="3">
         <v>13507800</v>
       </c>
-      <c r="AM72" s="3">
+      <c r="AN72" s="3">
         <v>13138800</v>
       </c>
-      <c r="AN72" s="3">
+      <c r="AO72" s="3">
         <v>13150400</v>
       </c>
-      <c r="AO72" s="3">
+      <c r="AP72" s="3">
         <v>13062800</v>
       </c>
     </row>
-    <row r="73" spans="2:41" x14ac:dyDescent="0.2">
+    <row r="73" spans="2:42" x14ac:dyDescent="0.2">
       <c r="C73" s="1" t="s">
         <v>65</v>
       </c>
@@ -7808,8 +7984,11 @@
       <c r="AO73" s="3">
         <v>0</v>
       </c>
+      <c r="AP73" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="74" spans="2:41" x14ac:dyDescent="0.2">
+    <row r="74" spans="2:42" x14ac:dyDescent="0.2">
       <c r="C74" s="1" t="s">
         <v>66</v>
       </c>
@@ -7927,8 +8106,11 @@
       <c r="AO74" s="3">
         <v>0</v>
       </c>
+      <c r="AP74" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="75" spans="2:41" x14ac:dyDescent="0.2">
+    <row r="75" spans="2:42" x14ac:dyDescent="0.2">
       <c r="C75" s="1" t="s">
         <v>67</v>
       </c>
@@ -8046,127 +8228,133 @@
       <c r="AO75" s="3">
         <v>0</v>
       </c>
+      <c r="AP75" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="76" spans="2:41" x14ac:dyDescent="0.2">
+    <row r="76" spans="2:42" x14ac:dyDescent="0.2">
       <c r="C76" s="1" t="s">
         <v>68</v>
       </c>
       <c r="D76" s="3">
+        <v>24969000</v>
+      </c>
+      <c r="E76" s="3">
         <v>24951000</v>
       </c>
-      <c r="E76" s="3">
+      <c r="F76" s="3">
         <v>25167700</v>
       </c>
-      <c r="F76" s="3">
+      <c r="G76" s="3">
         <v>25252000</v>
       </c>
-      <c r="G76" s="3">
+      <c r="H76" s="3">
         <v>22902500</v>
       </c>
-      <c r="H76" s="3">
+      <c r="I76" s="3">
         <v>23081300</v>
       </c>
-      <c r="I76" s="3">
+      <c r="J76" s="3">
         <v>25698700</v>
       </c>
-      <c r="J76" s="3">
+      <c r="K76" s="3">
         <v>24286300</v>
       </c>
-      <c r="K76" s="3">
+      <c r="L76" s="3">
         <v>23977100</v>
       </c>
-      <c r="L76" s="3">
+      <c r="M76" s="3">
         <v>24420000</v>
       </c>
-      <c r="M76" s="3">
+      <c r="N76" s="3">
         <v>23463000</v>
       </c>
-      <c r="N76" s="3">
+      <c r="O76" s="3">
         <v>22963400</v>
       </c>
-      <c r="O76" s="3">
+      <c r="P76" s="3">
         <v>22747400</v>
       </c>
-      <c r="P76" s="3">
+      <c r="Q76" s="3">
         <v>21571400</v>
       </c>
-      <c r="Q76" s="3">
+      <c r="R76" s="3">
         <v>20624400</v>
       </c>
-      <c r="R76" s="3">
+      <c r="S76" s="3">
         <v>20539800</v>
       </c>
-      <c r="S76" s="3">
+      <c r="T76" s="3">
         <v>20238100</v>
       </c>
-      <c r="T76" s="3">
+      <c r="U76" s="3">
         <v>19381500</v>
       </c>
-      <c r="U76" s="3">
+      <c r="V76" s="3">
         <v>18987000</v>
       </c>
-      <c r="V76" s="3">
+      <c r="W76" s="3">
         <v>18419400</v>
       </c>
-      <c r="W76" s="3">
+      <c r="X76" s="3">
         <v>17399500</v>
       </c>
-      <c r="X76" s="3">
+      <c r="Y76" s="3">
         <v>17059700</v>
       </c>
-      <c r="Y76" s="3">
+      <c r="Z76" s="3">
         <v>17519900</v>
       </c>
-      <c r="Z76" s="3">
+      <c r="AA76" s="3">
         <v>17171900</v>
       </c>
-      <c r="AA76" s="3">
+      <c r="AB76" s="3">
         <v>17677500</v>
       </c>
-      <c r="AB76" s="3">
+      <c r="AC76" s="3">
         <v>18283800</v>
       </c>
-      <c r="AC76" s="3">
+      <c r="AD76" s="3">
         <v>17718000</v>
       </c>
-      <c r="AD76" s="3">
+      <c r="AE76" s="3">
         <v>17110000</v>
       </c>
-      <c r="AE76" s="3">
+      <c r="AF76" s="3">
         <v>17117400</v>
       </c>
-      <c r="AF76" s="3">
+      <c r="AG76" s="3">
         <v>18261500</v>
       </c>
-      <c r="AG76" s="3">
+      <c r="AH76" s="3">
         <v>17579400</v>
       </c>
-      <c r="AH76" s="3">
+      <c r="AI76" s="3">
         <v>17463800</v>
       </c>
-      <c r="AI76" s="3">
+      <c r="AJ76" s="3">
         <v>17085700</v>
       </c>
-      <c r="AJ76" s="3">
+      <c r="AK76" s="3">
         <v>17922000</v>
       </c>
-      <c r="AK76" s="3">
+      <c r="AL76" s="3">
         <v>17996500</v>
       </c>
-      <c r="AL76" s="3">
+      <c r="AM76" s="3">
         <v>17825600</v>
       </c>
-      <c r="AM76" s="3">
+      <c r="AN76" s="3">
         <v>17960100</v>
       </c>
-      <c r="AN76" s="3">
+      <c r="AO76" s="3">
         <v>18347500</v>
       </c>
-      <c r="AO76" s="3">
+      <c r="AP76" s="3">
         <v>18412300</v>
       </c>
     </row>
-    <row r="77" spans="2:41" x14ac:dyDescent="0.2">
+    <row r="77" spans="2:42" x14ac:dyDescent="0.2">
       <c r="C77" s="1" t="s">
         <v>69</v>
       </c>
@@ -8284,251 +8472,260 @@
       <c r="AO77" s="3">
         <v>0</v>
       </c>
+      <c r="AP77" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="79" spans="2:41" x14ac:dyDescent="0.2">
+    <row r="79" spans="2:42" x14ac:dyDescent="0.2">
       <c r="B79" s="1" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="80" spans="2:41" x14ac:dyDescent="0.2">
+    <row r="80" spans="2:42" x14ac:dyDescent="0.2">
       <c r="C80" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D80" s="2">
+        <v>46112</v>
+      </c>
+      <c r="E80" s="2">
         <v>46022</v>
       </c>
-      <c r="E80" s="2">
+      <c r="F80" s="2">
         <v>45930</v>
       </c>
-      <c r="F80" s="2">
+      <c r="G80" s="2">
         <v>45838</v>
       </c>
-      <c r="G80" s="2">
+      <c r="H80" s="2">
         <v>45747</v>
       </c>
-      <c r="H80" s="2">
+      <c r="I80" s="2">
         <v>45657</v>
       </c>
-      <c r="I80" s="2">
+      <c r="J80" s="2">
         <v>45565</v>
       </c>
-      <c r="J80" s="2">
+      <c r="K80" s="2">
         <v>45473</v>
       </c>
-      <c r="K80" s="2">
+      <c r="L80" s="2">
         <v>45382</v>
       </c>
-      <c r="L80" s="2">
+      <c r="M80" s="2">
         <v>45291</v>
       </c>
-      <c r="M80" s="2">
+      <c r="N80" s="2">
         <v>45199</v>
       </c>
-      <c r="N80" s="2">
+      <c r="O80" s="2">
         <v>45107</v>
       </c>
-      <c r="O80" s="2">
+      <c r="P80" s="2">
         <v>45016</v>
       </c>
-      <c r="P80" s="2">
+      <c r="Q80" s="2">
         <v>44926</v>
       </c>
-      <c r="Q80" s="2">
+      <c r="R80" s="2">
         <v>44834</v>
       </c>
-      <c r="R80" s="2">
+      <c r="S80" s="2">
         <v>44742</v>
       </c>
-      <c r="S80" s="2">
+      <c r="T80" s="2">
         <v>44651</v>
       </c>
-      <c r="T80" s="2">
+      <c r="U80" s="2">
         <v>44561</v>
       </c>
-      <c r="U80" s="2">
+      <c r="V80" s="2">
         <v>44469</v>
       </c>
-      <c r="V80" s="2">
+      <c r="W80" s="2">
         <v>44377</v>
       </c>
-      <c r="W80" s="2">
+      <c r="X80" s="2">
         <v>44286</v>
       </c>
-      <c r="X80" s="2">
+      <c r="Y80" s="2">
         <v>44196</v>
       </c>
-      <c r="Y80" s="2">
+      <c r="Z80" s="2">
         <v>44104</v>
       </c>
-      <c r="Z80" s="2">
+      <c r="AA80" s="2">
         <v>44012</v>
       </c>
-      <c r="AA80" s="2">
+      <c r="AB80" s="2">
         <v>43921</v>
       </c>
-      <c r="AB80" s="2">
+      <c r="AC80" s="2">
         <v>43830</v>
       </c>
-      <c r="AC80" s="2">
+      <c r="AD80" s="2">
         <v>43738</v>
       </c>
-      <c r="AD80" s="2">
+      <c r="AE80" s="2">
         <v>43646</v>
       </c>
-      <c r="AE80" s="2">
+      <c r="AF80" s="2">
         <v>43555</v>
       </c>
-      <c r="AF80" s="2">
+      <c r="AG80" s="2">
         <v>43465</v>
       </c>
-      <c r="AG80" s="2">
+      <c r="AH80" s="2">
         <v>43373</v>
       </c>
-      <c r="AH80" s="2">
+      <c r="AI80" s="2">
         <v>43281</v>
       </c>
-      <c r="AI80" s="2">
+      <c r="AJ80" s="2">
         <v>43190</v>
       </c>
-      <c r="AJ80" s="2">
+      <c r="AK80" s="2">
         <v>43100</v>
       </c>
-      <c r="AK80" s="2">
+      <c r="AL80" s="2">
         <v>43008</v>
       </c>
-      <c r="AL80" s="2">
+      <c r="AM80" s="2">
         <v>42916</v>
       </c>
-      <c r="AM80" s="2">
+      <c r="AN80" s="2">
         <v>42825</v>
       </c>
-      <c r="AN80" s="2">
+      <c r="AO80" s="2">
         <v>42735</v>
       </c>
-      <c r="AO80" s="2">
+      <c r="AP80" s="2">
         <v>42643</v>
       </c>
     </row>
-    <row r="81" spans="3:41" x14ac:dyDescent="0.2">
+    <row r="81" spans="3:42" x14ac:dyDescent="0.2">
       <c r="C81" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D81" s="3">
+        <v>397000</v>
+      </c>
+      <c r="E81" s="3">
         <v>227500</v>
       </c>
-      <c r="E81" s="3">
+      <c r="F81" s="3">
         <v>885500</v>
       </c>
-      <c r="F81" s="3">
+      <c r="G81" s="3">
         <v>691100</v>
       </c>
-      <c r="G81" s="3">
+      <c r="H81" s="3">
         <v>418800</v>
       </c>
-      <c r="H81" s="3">
+      <c r="I81" s="3">
         <v>288500</v>
       </c>
-      <c r="I81" s="3">
+      <c r="J81" s="3">
         <v>688600</v>
       </c>
-      <c r="J81" s="3">
+      <c r="K81" s="3">
         <v>676000</v>
       </c>
-      <c r="K81" s="3">
+      <c r="L81" s="3">
         <v>613100</v>
       </c>
-      <c r="L81" s="3">
+      <c r="M81" s="3">
         <v>52500</v>
       </c>
-      <c r="M81" s="3">
+      <c r="N81" s="3">
         <v>668000</v>
       </c>
-      <c r="N81" s="3">
+      <c r="O81" s="3">
         <v>474700</v>
       </c>
-      <c r="O81" s="3">
+      <c r="P81" s="3">
         <v>700700</v>
       </c>
-      <c r="P81" s="3">
+      <c r="Q81" s="3">
         <v>338800</v>
       </c>
-      <c r="Q81" s="3">
+      <c r="R81" s="3">
         <v>640600</v>
       </c>
-      <c r="R81" s="3">
+      <c r="S81" s="3">
         <v>684400</v>
       </c>
-      <c r="S81" s="3">
+      <c r="T81" s="3">
         <v>631400</v>
       </c>
-      <c r="T81" s="3">
+      <c r="U81" s="3">
         <v>279500</v>
       </c>
-      <c r="U81" s="3">
+      <c r="V81" s="3">
         <v>570700</v>
       </c>
-      <c r="V81" s="3">
+      <c r="W81" s="3">
         <v>552600</v>
       </c>
-      <c r="W81" s="3">
+      <c r="X81" s="3">
         <v>482000</v>
       </c>
-      <c r="X81" s="3">
+      <c r="Y81" s="3">
         <v>112600</v>
       </c>
-      <c r="Y81" s="3">
+      <c r="Z81" s="3">
         <v>358800</v>
       </c>
-      <c r="Z81" s="3">
+      <c r="AA81" s="3">
         <v>100500</v>
       </c>
-      <c r="AA81" s="3">
+      <c r="AB81" s="3">
         <v>412900</v>
       </c>
-      <c r="AB81" s="3">
+      <c r="AC81" s="3">
         <v>174900</v>
       </c>
-      <c r="AC81" s="3">
+      <c r="AD81" s="3">
         <v>410100</v>
       </c>
-      <c r="AD81" s="3">
+      <c r="AE81" s="3">
         <v>537700</v>
       </c>
-      <c r="AE81" s="3">
+      <c r="AF81" s="3">
         <v>517500</v>
       </c>
-      <c r="AF81" s="3">
+      <c r="AG81" s="3">
         <v>76800</v>
       </c>
-      <c r="AG81" s="3">
+      <c r="AH81" s="3">
         <v>453900</v>
       </c>
-      <c r="AH81" s="3">
+      <c r="AI81" s="3">
         <v>569900</v>
       </c>
-      <c r="AI81" s="3">
+      <c r="AJ81" s="3">
         <v>463600</v>
       </c>
-      <c r="AJ81" s="3">
+      <c r="AK81" s="3">
         <v>84900</v>
       </c>
-      <c r="AK81" s="3">
+      <c r="AL81" s="3">
         <v>212100</v>
       </c>
-      <c r="AL81" s="3">
+      <c r="AM81" s="3">
         <v>369000</v>
       </c>
-      <c r="AM81" s="3">
+      <c r="AN81" s="3">
         <v>517600</v>
       </c>
-      <c r="AN81" s="3">
+      <c r="AO81" s="3">
         <v>88500</v>
       </c>
-      <c r="AO81" s="3">
+      <c r="AP81" s="3">
         <v>275700</v>
       </c>
     </row>
-    <row r="82" spans="3:41" x14ac:dyDescent="0.2">
+    <row r="82" spans="3:42" x14ac:dyDescent="0.2">
       <c r="C82" s="1" t="s">
         <v>71</v>
       </c>
@@ -8570,127 +8767,131 @@
       <c r="AM82" s="3"/>
       <c r="AN82" s="3"/>
       <c r="AO82" s="3"/>
+      <c r="AP82" s="3"/>
     </row>
-    <row r="83" spans="3:41" x14ac:dyDescent="0.2">
+    <row r="83" spans="3:42" x14ac:dyDescent="0.2">
       <c r="C83" s="1" t="s">
         <v>72</v>
       </c>
       <c r="D83" s="3">
+        <v>204600</v>
+      </c>
+      <c r="E83" s="3">
         <v>106200</v>
       </c>
-      <c r="E83" s="3">
+      <c r="F83" s="3">
         <v>218200</v>
       </c>
-      <c r="F83" s="3">
+      <c r="G83" s="3">
         <v>204400</v>
       </c>
-      <c r="G83" s="3">
+      <c r="H83" s="3">
         <v>200500</v>
       </c>
-      <c r="H83" s="3">
+      <c r="I83" s="3">
         <v>173700</v>
       </c>
-      <c r="I83" s="3">
+      <c r="J83" s="3">
         <v>150800</v>
       </c>
-      <c r="J83" s="3">
+      <c r="K83" s="3">
         <v>153800</v>
       </c>
-      <c r="K83" s="3">
+      <c r="L83" s="3">
         <v>154400</v>
       </c>
-      <c r="L83" s="3">
+      <c r="M83" s="3">
         <v>162700</v>
       </c>
-      <c r="M83" s="3">
+      <c r="N83" s="3">
         <v>133200</v>
       </c>
-      <c r="N83" s="3">
+      <c r="O83" s="3">
         <v>147300</v>
       </c>
-      <c r="O83" s="3">
+      <c r="P83" s="3">
         <v>148000</v>
       </c>
-      <c r="P83" s="3">
+      <c r="Q83" s="3">
         <v>185200</v>
       </c>
-      <c r="Q83" s="3">
+      <c r="R83" s="3">
         <v>169700</v>
       </c>
-      <c r="R83" s="3">
+      <c r="S83" s="3">
         <v>175600</v>
       </c>
-      <c r="S83" s="3">
+      <c r="T83" s="3">
         <v>168600</v>
       </c>
-      <c r="T83" s="3">
+      <c r="U83" s="3">
         <v>155900</v>
       </c>
-      <c r="U83" s="3">
+      <c r="V83" s="3">
         <v>149200</v>
       </c>
-      <c r="V83" s="3">
+      <c r="W83" s="3">
         <v>184500</v>
       </c>
-      <c r="W83" s="3">
+      <c r="X83" s="3">
         <v>102900</v>
       </c>
-      <c r="X83" s="3">
+      <c r="Y83" s="3">
         <v>101300</v>
       </c>
-      <c r="Y83" s="3">
+      <c r="Z83" s="3">
         <v>101500</v>
       </c>
-      <c r="Z83" s="3">
+      <c r="AA83" s="3">
         <v>98700</v>
       </c>
-      <c r="AA83" s="3">
+      <c r="AB83" s="3">
         <v>112300</v>
       </c>
-      <c r="AB83" s="3">
+      <c r="AC83" s="3">
         <v>120400</v>
       </c>
-      <c r="AC83" s="3">
+      <c r="AD83" s="3">
         <v>116900</v>
       </c>
-      <c r="AD83" s="3">
+      <c r="AE83" s="3">
         <v>108900</v>
       </c>
-      <c r="AE83" s="3">
+      <c r="AF83" s="3">
         <v>93600</v>
       </c>
-      <c r="AF83" s="3">
+      <c r="AG83" s="3">
         <v>61600</v>
       </c>
-      <c r="AG83" s="3">
+      <c r="AH83" s="3">
         <v>58600</v>
       </c>
-      <c r="AH83" s="3">
+      <c r="AI83" s="3">
         <v>56000</v>
       </c>
-      <c r="AI83" s="3">
+      <c r="AJ83" s="3">
         <v>50600</v>
       </c>
-      <c r="AJ83" s="3">
+      <c r="AK83" s="3">
         <v>49900</v>
       </c>
-      <c r="AK83" s="3">
+      <c r="AL83" s="3">
         <v>50800</v>
       </c>
-      <c r="AL83" s="3">
+      <c r="AM83" s="3">
         <v>51600</v>
       </c>
-      <c r="AM83" s="3">
+      <c r="AN83" s="3">
         <v>55200</v>
       </c>
-      <c r="AN83" s="3">
+      <c r="AO83" s="3">
         <v>54800</v>
       </c>
-      <c r="AO83" s="3">
+      <c r="AP83" s="3">
         <v>53700</v>
       </c>
     </row>
-    <row r="84" spans="3:41" x14ac:dyDescent="0.2">
+    <row r="84" spans="3:42" x14ac:dyDescent="0.2">
       <c r="C84" s="1" t="s">
         <v>73</v>
       </c>
@@ -8808,8 +9009,11 @@
       <c r="AO84" s="3">
         <v>0</v>
       </c>
+      <c r="AP84" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="85" spans="3:41" x14ac:dyDescent="0.2">
+    <row r="85" spans="3:42" x14ac:dyDescent="0.2">
       <c r="C85" s="1" t="s">
         <v>74</v>
       </c>
@@ -8927,8 +9131,11 @@
       <c r="AO85" s="3">
         <v>0</v>
       </c>
+      <c r="AP85" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="86" spans="3:41" x14ac:dyDescent="0.2">
+    <row r="86" spans="3:42" x14ac:dyDescent="0.2">
       <c r="C86" s="1" t="s">
         <v>75</v>
       </c>
@@ -9046,8 +9253,11 @@
       <c r="AO86" s="3">
         <v>0</v>
       </c>
+      <c r="AP86" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="87" spans="3:41" x14ac:dyDescent="0.2">
+    <row r="87" spans="3:42" x14ac:dyDescent="0.2">
       <c r="C87" s="1" t="s">
         <v>76</v>
       </c>
@@ -9165,8 +9375,11 @@
       <c r="AO87" s="3">
         <v>0</v>
       </c>
+      <c r="AP87" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="88" spans="3:41" x14ac:dyDescent="0.2">
+    <row r="88" spans="3:42" x14ac:dyDescent="0.2">
       <c r="C88" s="1" t="s">
         <v>77</v>
       </c>
@@ -9284,127 +9497,133 @@
       <c r="AO88" s="3">
         <v>0</v>
       </c>
+      <c r="AP88" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="89" spans="3:41" x14ac:dyDescent="0.2">
+    <row r="89" spans="3:42" x14ac:dyDescent="0.2">
       <c r="C89" s="1" t="s">
         <v>78</v>
       </c>
       <c r="D89" s="3">
+        <v>2570700</v>
+      </c>
+      <c r="E89" s="3">
         <v>-342000</v>
       </c>
-      <c r="E89" s="3">
+      <c r="F89" s="3">
         <v>6204800</v>
       </c>
-      <c r="F89" s="3">
+      <c r="G89" s="3">
         <v>-4742200</v>
       </c>
-      <c r="G89" s="3">
+      <c r="H89" s="3">
         <v>-1359600</v>
       </c>
-      <c r="H89" s="3">
+      <c r="I89" s="3">
         <v>15238500</v>
       </c>
-      <c r="I89" s="3">
+      <c r="J89" s="3">
         <v>-21513100</v>
       </c>
-      <c r="J89" s="3">
+      <c r="K89" s="3">
         <v>-5708900</v>
       </c>
-      <c r="K89" s="3">
+      <c r="L89" s="3">
         <v>3028800</v>
       </c>
-      <c r="L89" s="3">
+      <c r="M89" s="3">
         <v>-13351300</v>
       </c>
-      <c r="M89" s="3">
+      <c r="N89" s="3">
         <v>3754000</v>
       </c>
-      <c r="N89" s="3">
+      <c r="O89" s="3">
         <v>-11714900</v>
       </c>
-      <c r="O89" s="3">
+      <c r="P89" s="3">
         <v>10840700</v>
       </c>
-      <c r="P89" s="3">
+      <c r="Q89" s="3">
         <v>12011900</v>
       </c>
-      <c r="Q89" s="3">
+      <c r="R89" s="3">
         <v>-3350300</v>
       </c>
-      <c r="R89" s="3">
+      <c r="S89" s="3">
         <v>-2130300</v>
       </c>
-      <c r="S89" s="3">
+      <c r="T89" s="3">
         <v>7700600</v>
       </c>
-      <c r="T89" s="3">
+      <c r="U89" s="3">
         <v>4027400</v>
       </c>
-      <c r="U89" s="3">
+      <c r="V89" s="3">
         <v>2586700</v>
       </c>
-      <c r="V89" s="3">
+      <c r="W89" s="3">
         <v>-4607300</v>
       </c>
-      <c r="W89" s="3">
+      <c r="X89" s="3">
         <v>831700</v>
       </c>
-      <c r="X89" s="3">
+      <c r="Y89" s="3">
         <v>1545900</v>
       </c>
-      <c r="Y89" s="3">
+      <c r="Z89" s="3">
         <v>-766500</v>
       </c>
-      <c r="Z89" s="3">
+      <c r="AA89" s="3">
         <v>2718500</v>
       </c>
-      <c r="AA89" s="3">
+      <c r="AB89" s="3">
         <v>-824700</v>
       </c>
-      <c r="AB89" s="3">
+      <c r="AC89" s="3">
         <v>-153300</v>
       </c>
-      <c r="AC89" s="3">
+      <c r="AD89" s="3">
         <v>-428600</v>
       </c>
-      <c r="AD89" s="3">
+      <c r="AE89" s="3">
         <v>3501700</v>
       </c>
-      <c r="AE89" s="3">
+      <c r="AF89" s="3">
         <v>-1296100</v>
       </c>
-      <c r="AF89" s="3">
+      <c r="AG89" s="3">
         <v>5231600</v>
       </c>
-      <c r="AG89" s="3">
+      <c r="AH89" s="3">
         <v>908000</v>
       </c>
-      <c r="AH89" s="3">
+      <c r="AI89" s="3">
         <v>643600</v>
       </c>
-      <c r="AI89" s="3">
+      <c r="AJ89" s="3">
         <v>877700</v>
       </c>
-      <c r="AJ89" s="3">
+      <c r="AK89" s="3">
         <v>-506300</v>
       </c>
-      <c r="AK89" s="3">
+      <c r="AL89" s="3">
         <v>-2456000</v>
       </c>
-      <c r="AL89" s="3">
+      <c r="AM89" s="3">
         <v>-340700</v>
       </c>
-      <c r="AM89" s="3">
+      <c r="AN89" s="3">
         <v>1561500</v>
       </c>
-      <c r="AN89" s="3">
+      <c r="AO89" s="3">
         <v>108800</v>
       </c>
-      <c r="AO89" s="3">
+      <c r="AP89" s="3">
         <v>3807600</v>
       </c>
     </row>
-    <row r="90" spans="3:41" x14ac:dyDescent="0.2">
+    <row r="90" spans="3:42" x14ac:dyDescent="0.2">
       <c r="C90" s="1" t="s">
         <v>79</v>
       </c>
@@ -9446,127 +9665,131 @@
       <c r="AM90" s="3"/>
       <c r="AN90" s="3"/>
       <c r="AO90" s="3"/>
+      <c r="AP90" s="3"/>
     </row>
-    <row r="91" spans="3:41" x14ac:dyDescent="0.2">
+    <row r="91" spans="3:42" x14ac:dyDescent="0.2">
       <c r="C91" s="1" t="s">
         <v>80</v>
       </c>
       <c r="D91" s="3">
+        <v>-28900</v>
+      </c>
+      <c r="E91" s="3">
         <v>-142900</v>
       </c>
-      <c r="E91" s="3">
+      <c r="F91" s="3">
         <v>-6100</v>
       </c>
-      <c r="F91" s="3">
+      <c r="G91" s="3">
         <v>-66200</v>
       </c>
-      <c r="G91" s="3">
+      <c r="H91" s="3">
         <v>-14600</v>
       </c>
-      <c r="H91" s="3">
+      <c r="I91" s="3">
         <v>-32300</v>
       </c>
-      <c r="I91" s="3">
+      <c r="J91" s="3">
         <v>-62500</v>
       </c>
-      <c r="J91" s="3">
+      <c r="K91" s="3">
         <v>-40100</v>
       </c>
-      <c r="K91" s="3">
+      <c r="L91" s="3">
         <v>-27400</v>
       </c>
-      <c r="L91" s="3">
+      <c r="M91" s="3">
         <v>-61300</v>
       </c>
-      <c r="M91" s="3">
+      <c r="N91" s="3">
         <v>-23300</v>
       </c>
-      <c r="N91" s="3">
+      <c r="O91" s="3">
         <v>-23900</v>
       </c>
-      <c r="O91" s="3">
+      <c r="P91" s="3">
         <v>-17100</v>
       </c>
-      <c r="P91" s="3">
+      <c r="Q91" s="3">
         <v>-113722000</v>
       </c>
-      <c r="Q91" s="3">
+      <c r="R91" s="3">
         <v>-77226000</v>
       </c>
-      <c r="R91" s="3">
+      <c r="S91" s="3">
         <v>-104059000</v>
       </c>
-      <c r="S91" s="3">
+      <c r="T91" s="3">
         <v>-52618000</v>
       </c>
-      <c r="T91" s="3">
+      <c r="U91" s="3">
         <v>-74615000</v>
       </c>
-      <c r="U91" s="3">
+      <c r="V91" s="3">
         <v>-81614000</v>
       </c>
-      <c r="V91" s="3">
+      <c r="W91" s="3">
         <v>-15900</v>
       </c>
-      <c r="W91" s="3">
+      <c r="X91" s="3">
         <v>-14300</v>
       </c>
-      <c r="X91" s="3">
+      <c r="Y91" s="3">
         <v>-43600</v>
       </c>
-      <c r="Y91" s="3">
+      <c r="Z91" s="3">
         <v>-25600</v>
       </c>
-      <c r="Z91" s="3">
+      <c r="AA91" s="3">
         <v>-24800</v>
       </c>
-      <c r="AA91" s="3">
+      <c r="AB91" s="3">
         <v>-20300</v>
       </c>
-      <c r="AB91" s="3">
+      <c r="AC91" s="3">
         <v>-190900</v>
       </c>
-      <c r="AC91" s="3">
+      <c r="AD91" s="3">
         <v>-91000</v>
       </c>
-      <c r="AD91" s="3">
+      <c r="AE91" s="3">
         <v>-55400</v>
       </c>
-      <c r="AE91" s="3">
+      <c r="AF91" s="3">
         <v>-31700</v>
       </c>
-      <c r="AF91" s="3">
+      <c r="AG91" s="3">
         <v>-43000</v>
       </c>
-      <c r="AG91" s="3">
+      <c r="AH91" s="3">
         <v>-20100</v>
       </c>
-      <c r="AH91" s="3">
+      <c r="AI91" s="3">
         <v>-18000</v>
       </c>
-      <c r="AI91" s="3">
+      <c r="AJ91" s="3">
         <v>-17800</v>
       </c>
-      <c r="AJ91" s="3">
+      <c r="AK91" s="3">
         <v>-25100</v>
       </c>
-      <c r="AK91" s="3">
+      <c r="AL91" s="3">
         <v>-57300</v>
       </c>
-      <c r="AL91" s="3">
+      <c r="AM91" s="3">
         <v>-37900</v>
       </c>
-      <c r="AM91" s="3">
+      <c r="AN91" s="3">
         <v>-22400</v>
       </c>
-      <c r="AN91" s="3">
+      <c r="AO91" s="3">
         <v>-111600</v>
       </c>
-      <c r="AO91" s="3">
+      <c r="AP91" s="3">
         <v>-90400</v>
       </c>
     </row>
-    <row r="92" spans="3:41" x14ac:dyDescent="0.2">
+    <row r="92" spans="3:42" x14ac:dyDescent="0.2">
       <c r="C92" s="1" t="s">
         <v>81</v>
       </c>
@@ -9684,8 +9907,11 @@
       <c r="AO92" s="3">
         <v>0</v>
       </c>
+      <c r="AP92" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="93" spans="3:41" x14ac:dyDescent="0.2">
+    <row r="93" spans="3:42" x14ac:dyDescent="0.2">
       <c r="C93" s="1" t="s">
         <v>82</v>
       </c>
@@ -9803,127 +10029,133 @@
       <c r="AO93" s="3">
         <v>0</v>
       </c>
+      <c r="AP93" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="94" spans="3:41" x14ac:dyDescent="0.2">
+    <row r="94" spans="3:42" x14ac:dyDescent="0.2">
       <c r="C94" s="1" t="s">
         <v>83</v>
       </c>
       <c r="D94" s="3">
+        <v>647000</v>
+      </c>
+      <c r="E94" s="3">
         <v>-7655100</v>
       </c>
-      <c r="E94" s="3">
+      <c r="F94" s="3">
         <v>-1956500</v>
       </c>
-      <c r="F94" s="3">
+      <c r="G94" s="3">
         <v>2605800</v>
       </c>
-      <c r="G94" s="3">
+      <c r="H94" s="3">
         <v>265900</v>
       </c>
-      <c r="H94" s="3">
+      <c r="I94" s="3">
         <v>-3917800</v>
       </c>
-      <c r="I94" s="3">
+      <c r="J94" s="3">
         <v>3642700</v>
       </c>
-      <c r="J94" s="3">
+      <c r="K94" s="3">
         <v>-1092400</v>
       </c>
-      <c r="K94" s="3">
+      <c r="L94" s="3">
         <v>1841100</v>
       </c>
-      <c r="L94" s="3">
+      <c r="M94" s="3">
         <v>-625400</v>
       </c>
-      <c r="M94" s="3">
+      <c r="N94" s="3">
         <v>-1107500</v>
       </c>
-      <c r="N94" s="3">
+      <c r="O94" s="3">
         <v>-261600</v>
       </c>
-      <c r="O94" s="3">
+      <c r="P94" s="3">
         <v>300800</v>
       </c>
-      <c r="P94" s="3">
+      <c r="Q94" s="3">
         <v>-2910400</v>
       </c>
-      <c r="Q94" s="3">
+      <c r="R94" s="3">
         <v>-2354900</v>
       </c>
-      <c r="R94" s="3">
+      <c r="S94" s="3">
         <v>2353800</v>
       </c>
-      <c r="S94" s="3">
+      <c r="T94" s="3">
         <v>-2278800</v>
       </c>
-      <c r="T94" s="3">
+      <c r="U94" s="3">
         <v>-4489600</v>
       </c>
-      <c r="U94" s="3">
+      <c r="V94" s="3">
         <v>-3902300</v>
       </c>
-      <c r="V94" s="3">
+      <c r="W94" s="3">
         <v>1124900</v>
       </c>
-      <c r="W94" s="3">
+      <c r="X94" s="3">
         <v>-723400</v>
       </c>
-      <c r="X94" s="3">
+      <c r="Y94" s="3">
         <v>-365200</v>
       </c>
-      <c r="Y94" s="3">
+      <c r="Z94" s="3">
         <v>-124500</v>
       </c>
-      <c r="Z94" s="3">
+      <c r="AA94" s="3">
         <v>-446100</v>
       </c>
-      <c r="AA94" s="3">
+      <c r="AB94" s="3">
         <v>-179800</v>
       </c>
-      <c r="AB94" s="3">
+      <c r="AC94" s="3">
         <v>-962200</v>
       </c>
-      <c r="AC94" s="3">
+      <c r="AD94" s="3">
         <v>-913600</v>
       </c>
-      <c r="AD94" s="3">
+      <c r="AE94" s="3">
         <v>-5520900</v>
       </c>
-      <c r="AE94" s="3">
+      <c r="AF94" s="3">
         <v>-97900</v>
       </c>
-      <c r="AF94" s="3">
+      <c r="AG94" s="3">
         <v>-5105000</v>
       </c>
-      <c r="AG94" s="3">
+      <c r="AH94" s="3">
         <v>-2452600</v>
       </c>
-      <c r="AH94" s="3">
+      <c r="AI94" s="3">
         <v>-1063800</v>
       </c>
-      <c r="AI94" s="3">
+      <c r="AJ94" s="3">
         <v>-587600</v>
       </c>
-      <c r="AJ94" s="3">
+      <c r="AK94" s="3">
         <v>1277600</v>
       </c>
-      <c r="AK94" s="3">
+      <c r="AL94" s="3">
         <v>-195600</v>
       </c>
-      <c r="AL94" s="3">
+      <c r="AM94" s="3">
         <v>183200</v>
       </c>
-      <c r="AM94" s="3">
+      <c r="AN94" s="3">
         <v>392500</v>
       </c>
-      <c r="AN94" s="3">
+      <c r="AO94" s="3">
         <v>-2371700</v>
       </c>
-      <c r="AO94" s="3">
+      <c r="AP94" s="3">
         <v>694800</v>
       </c>
     </row>
-    <row r="95" spans="3:41" x14ac:dyDescent="0.2">
+    <row r="95" spans="3:42" x14ac:dyDescent="0.2">
       <c r="C95" s="1" t="s">
         <v>84</v>
       </c>
@@ -9965,56 +10197,57 @@
       <c r="AM95" s="3"/>
       <c r="AN95" s="3"/>
       <c r="AO95" s="3"/>
+      <c r="AP95" s="3"/>
     </row>
-    <row r="96" spans="3:41" x14ac:dyDescent="0.2">
+    <row r="96" spans="3:42" x14ac:dyDescent="0.2">
       <c r="C96" s="1" t="s">
         <v>85</v>
       </c>
       <c r="D96" s="3">
+        <v>25600</v>
+      </c>
+      <c r="E96" s="3">
         <v>127000</v>
       </c>
-      <c r="E96" s="3">
+      <c r="F96" s="3">
         <v>130500</v>
       </c>
-      <c r="F96" s="3">
+      <c r="G96" s="3">
         <v>495800</v>
       </c>
-      <c r="G96" s="3">
+      <c r="H96" s="3">
         <v>26800</v>
       </c>
-      <c r="H96" s="3">
+      <c r="I96" s="3">
         <v>117000</v>
       </c>
-      <c r="I96" s="3">
+      <c r="J96" s="3">
         <v>134900</v>
       </c>
-      <c r="J96" s="3">
+      <c r="K96" s="3">
         <v>473000</v>
       </c>
-      <c r="K96" s="3">
+      <c r="L96" s="3">
         <v>26200</v>
       </c>
-      <c r="L96" s="3">
+      <c r="M96" s="3">
         <v>151100</v>
       </c>
-      <c r="M96" s="3">
+      <c r="N96" s="3">
         <v>102000</v>
       </c>
-      <c r="N96" s="3">
+      <c r="O96" s="3">
         <v>566300</v>
       </c>
-      <c r="O96" s="3">
+      <c r="P96" s="3">
         <v>23300</v>
       </c>
-      <c r="P96" s="3">
-        <v>0</v>
-      </c>
       <c r="Q96" s="3">
+        <v>0</v>
+      </c>
+      <c r="R96" s="3">
         <v>-79700</v>
       </c>
-      <c r="R96" s="3">
-        <v>0</v>
-      </c>
       <c r="S96" s="3">
         <v>0</v>
       </c>
@@ -10022,11 +10255,11 @@
         <v>0</v>
       </c>
       <c r="U96" s="3">
+        <v>0</v>
+      </c>
+      <c r="V96" s="3">
         <v>-81300</v>
       </c>
-      <c r="V96" s="3">
-        <v>0</v>
-      </c>
       <c r="W96" s="3">
         <v>0</v>
       </c>
@@ -10070,22 +10303,25 @@
         <v>0</v>
       </c>
       <c r="AK96" s="3">
+        <v>0</v>
+      </c>
+      <c r="AL96" s="3">
         <v>-59200</v>
       </c>
-      <c r="AL96" s="3">
+      <c r="AM96" s="3">
         <v>-237000</v>
       </c>
-      <c r="AM96" s="3">
-        <v>0</v>
-      </c>
       <c r="AN96" s="3">
+        <v>0</v>
+      </c>
+      <c r="AO96" s="3">
         <v>-38100</v>
       </c>
-      <c r="AO96" s="3">
+      <c r="AP96" s="3">
         <v>-22800</v>
       </c>
     </row>
-    <row r="97" spans="3:41" x14ac:dyDescent="0.2">
+    <row r="97" spans="3:42" x14ac:dyDescent="0.2">
       <c r="C97" s="1" t="s">
         <v>86</v>
       </c>
@@ -10203,8 +10439,11 @@
       <c r="AO97" s="3">
         <v>0</v>
       </c>
+      <c r="AP97" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="98" spans="3:41" x14ac:dyDescent="0.2">
+    <row r="98" spans="3:42" x14ac:dyDescent="0.2">
       <c r="C98" s="1" t="s">
         <v>87</v>
       </c>
@@ -10322,8 +10561,11 @@
       <c r="AO98" s="3">
         <v>0</v>
       </c>
+      <c r="AP98" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="99" spans="3:41" x14ac:dyDescent="0.2">
+    <row r="99" spans="3:42" x14ac:dyDescent="0.2">
       <c r="C99" s="1" t="s">
         <v>88</v>
       </c>
@@ -10441,361 +10683,373 @@
       <c r="AO99" s="3">
         <v>0</v>
       </c>
+      <c r="AP99" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="100" spans="3:41" x14ac:dyDescent="0.2">
+    <row r="100" spans="3:42" x14ac:dyDescent="0.2">
       <c r="C100" s="1" t="s">
         <v>89</v>
       </c>
       <c r="D100" s="3">
+        <v>-6514600</v>
+      </c>
+      <c r="E100" s="3">
         <v>14210100</v>
       </c>
-      <c r="E100" s="3">
+      <c r="F100" s="3">
         <v>-5092600</v>
       </c>
-      <c r="F100" s="3">
+      <c r="G100" s="3">
         <v>6108300</v>
       </c>
-      <c r="G100" s="3">
+      <c r="H100" s="3">
         <v>-68000</v>
       </c>
-      <c r="H100" s="3">
+      <c r="I100" s="3">
         <v>-16521000</v>
       </c>
-      <c r="I100" s="3">
+      <c r="J100" s="3">
         <v>24357600</v>
       </c>
-      <c r="J100" s="3">
+      <c r="K100" s="3">
         <v>1880400</v>
       </c>
-      <c r="K100" s="3">
+      <c r="L100" s="3">
         <v>-4107500</v>
       </c>
-      <c r="L100" s="3">
+      <c r="M100" s="3">
         <v>17753300</v>
       </c>
-      <c r="M100" s="3">
+      <c r="N100" s="3">
         <v>447300</v>
       </c>
-      <c r="N100" s="3">
+      <c r="O100" s="3">
         <v>5022900</v>
       </c>
-      <c r="O100" s="3">
+      <c r="P100" s="3">
         <v>-13746200</v>
       </c>
-      <c r="P100" s="3">
+      <c r="Q100" s="3">
         <v>-5147300</v>
       </c>
-      <c r="Q100" s="3">
+      <c r="R100" s="3">
         <v>1697300</v>
       </c>
-      <c r="R100" s="3">
+      <c r="S100" s="3">
         <v>3000400</v>
       </c>
-      <c r="S100" s="3">
+      <c r="T100" s="3">
         <v>1932700</v>
       </c>
-      <c r="T100" s="3">
+      <c r="U100" s="3">
         <v>2031800</v>
       </c>
-      <c r="U100" s="3">
+      <c r="V100" s="3">
         <v>1404600</v>
       </c>
-      <c r="V100" s="3">
+      <c r="W100" s="3">
         <v>2911000</v>
       </c>
-      <c r="W100" s="3">
+      <c r="X100" s="3">
         <v>453200</v>
       </c>
-      <c r="X100" s="3">
+      <c r="Y100" s="3">
         <v>261800</v>
       </c>
-      <c r="Y100" s="3">
+      <c r="Z100" s="3">
         <v>553800</v>
       </c>
-      <c r="Z100" s="3">
+      <c r="AA100" s="3">
         <v>-2356000</v>
       </c>
-      <c r="AA100" s="3">
+      <c r="AB100" s="3">
         <v>3526800</v>
       </c>
-      <c r="AB100" s="3">
+      <c r="AC100" s="3">
         <v>-950700</v>
       </c>
-      <c r="AC100" s="3">
+      <c r="AD100" s="3">
         <v>3000500</v>
       </c>
-      <c r="AD100" s="3">
+      <c r="AE100" s="3">
         <v>3588600</v>
       </c>
-      <c r="AE100" s="3">
+      <c r="AF100" s="3">
         <v>-289800</v>
       </c>
-      <c r="AF100" s="3">
+      <c r="AG100" s="3">
         <v>491400</v>
       </c>
-      <c r="AG100" s="3">
+      <c r="AH100" s="3">
         <v>1689200</v>
       </c>
-      <c r="AH100" s="3">
+      <c r="AI100" s="3">
         <v>354700</v>
       </c>
-      <c r="AI100" s="3">
+      <c r="AJ100" s="3">
         <v>-1323700</v>
       </c>
-      <c r="AJ100" s="3">
+      <c r="AK100" s="3">
         <v>-309500</v>
       </c>
-      <c r="AK100" s="3">
+      <c r="AL100" s="3">
         <v>2140800</v>
       </c>
-      <c r="AL100" s="3">
+      <c r="AM100" s="3">
         <v>-384900</v>
       </c>
-      <c r="AM100" s="3">
+      <c r="AN100" s="3">
         <v>-1500100</v>
       </c>
-      <c r="AN100" s="3">
+      <c r="AO100" s="3">
         <v>1503800</v>
       </c>
-      <c r="AO100" s="3">
+      <c r="AP100" s="3">
         <v>-1778900</v>
       </c>
     </row>
-    <row r="101" spans="3:41" x14ac:dyDescent="0.2">
+    <row r="101" spans="3:42" x14ac:dyDescent="0.2">
       <c r="C101" s="1" t="s">
         <v>90</v>
       </c>
       <c r="D101" s="3">
+        <v>25300</v>
+      </c>
+      <c r="E101" s="3">
         <v>1000100</v>
       </c>
-      <c r="E101" s="3">
+      <c r="F101" s="3">
         <v>-385300</v>
       </c>
-      <c r="F101" s="3">
+      <c r="G101" s="3">
         <v>231000</v>
       </c>
-      <c r="G101" s="3">
+      <c r="H101" s="3">
         <v>262700</v>
       </c>
-      <c r="H101" s="3">
+      <c r="I101" s="3">
         <v>-179300</v>
       </c>
-      <c r="I101" s="3">
+      <c r="J101" s="3">
         <v>27300</v>
       </c>
-      <c r="J101" s="3">
+      <c r="K101" s="3">
         <v>-105100</v>
       </c>
-      <c r="K101" s="3">
+      <c r="L101" s="3">
         <v>125800</v>
       </c>
-      <c r="L101" s="3">
+      <c r="M101" s="3">
         <v>-1568200</v>
       </c>
-      <c r="M101" s="3">
+      <c r="N101" s="3">
         <v>609200</v>
       </c>
-      <c r="N101" s="3">
+      <c r="O101" s="3">
         <v>667200</v>
       </c>
-      <c r="O101" s="3">
+      <c r="P101" s="3">
         <v>217100</v>
       </c>
-      <c r="P101" s="3">
+      <c r="Q101" s="3">
         <v>-1479100</v>
       </c>
-      <c r="Q101" s="3">
+      <c r="R101" s="3">
         <v>638600</v>
       </c>
-      <c r="R101" s="3">
+      <c r="S101" s="3">
         <v>657000</v>
       </c>
-      <c r="S101" s="3">
+      <c r="T101" s="3">
         <v>203100</v>
       </c>
-      <c r="T101" s="3">
+      <c r="U101" s="3">
         <v>68900</v>
       </c>
-      <c r="U101" s="3">
+      <c r="V101" s="3">
         <v>409500</v>
       </c>
-      <c r="V101" s="3">
+      <c r="W101" s="3">
         <v>18100</v>
       </c>
-      <c r="W101" s="3">
+      <c r="X101" s="3">
         <v>295500</v>
       </c>
-      <c r="X101" s="3">
+      <c r="Y101" s="3">
         <v>-571700</v>
       </c>
-      <c r="Y101" s="3">
+      <c r="Z101" s="3">
         <v>-142900</v>
       </c>
-      <c r="Z101" s="3">
+      <c r="AA101" s="3">
         <v>-159900</v>
       </c>
-      <c r="AA101" s="3">
+      <c r="AB101" s="3">
         <v>200400</v>
       </c>
-      <c r="AB101" s="3">
+      <c r="AC101" s="3">
         <v>369400</v>
       </c>
-      <c r="AC101" s="3">
+      <c r="AD101" s="3">
         <v>-340600</v>
       </c>
-      <c r="AD101" s="3">
+      <c r="AE101" s="3">
         <v>51200</v>
       </c>
-      <c r="AE101" s="3">
+      <c r="AF101" s="3">
         <v>90500</v>
       </c>
-      <c r="AF101" s="3">
+      <c r="AG101" s="3">
         <v>6400</v>
       </c>
-      <c r="AG101" s="3">
+      <c r="AH101" s="3">
         <v>-76600</v>
       </c>
-      <c r="AH101" s="3">
+      <c r="AI101" s="3">
         <v>218900</v>
       </c>
-      <c r="AI101" s="3">
+      <c r="AJ101" s="3">
         <v>50500</v>
       </c>
-      <c r="AJ101" s="3">
+      <c r="AK101" s="3">
         <v>-377500</v>
       </c>
-      <c r="AK101" s="3">
+      <c r="AL101" s="3">
         <v>14000</v>
       </c>
-      <c r="AL101" s="3">
+      <c r="AM101" s="3">
         <v>8400</v>
       </c>
-      <c r="AM101" s="3">
+      <c r="AN101" s="3">
         <v>-108300</v>
       </c>
-      <c r="AN101" s="3">
+      <c r="AO101" s="3">
         <v>138000</v>
       </c>
-      <c r="AO101" s="3">
+      <c r="AP101" s="3">
         <v>-105900</v>
       </c>
     </row>
-    <row r="102" spans="3:41" x14ac:dyDescent="0.2">
+    <row r="102" spans="3:42" x14ac:dyDescent="0.2">
       <c r="C102" s="1" t="s">
         <v>91</v>
       </c>
       <c r="D102" s="3">
+        <v>-2581300</v>
+      </c>
+      <c r="E102" s="3">
         <v>6419800</v>
       </c>
-      <c r="E102" s="3">
+      <c r="F102" s="3">
         <v>-552400</v>
       </c>
-      <c r="F102" s="3">
+      <c r="G102" s="3">
         <v>3251800</v>
       </c>
-      <c r="G102" s="3">
+      <c r="H102" s="3">
         <v>-1136400</v>
       </c>
-      <c r="H102" s="3">
+      <c r="I102" s="3">
         <v>-4200200</v>
       </c>
-      <c r="I102" s="3">
+      <c r="J102" s="3">
         <v>6101900</v>
       </c>
-      <c r="J102" s="3">
+      <c r="K102" s="3">
         <v>-4689900</v>
       </c>
-      <c r="K102" s="3">
+      <c r="L102" s="3">
         <v>1025100</v>
       </c>
-      <c r="L102" s="3">
+      <c r="M102" s="3">
         <v>3597300</v>
       </c>
-      <c r="M102" s="3">
+      <c r="N102" s="3">
         <v>3121100</v>
       </c>
-      <c r="N102" s="3">
+      <c r="O102" s="3">
         <v>-7058600</v>
       </c>
-      <c r="O102" s="3">
+      <c r="P102" s="3">
         <v>-2478800</v>
       </c>
-      <c r="P102" s="3">
+      <c r="Q102" s="3">
         <v>2475100</v>
       </c>
-      <c r="Q102" s="3">
+      <c r="R102" s="3">
         <v>-3369400</v>
       </c>
-      <c r="R102" s="3">
+      <c r="S102" s="3">
         <v>3880900</v>
       </c>
-      <c r="S102" s="3">
+      <c r="T102" s="3">
         <v>7557600</v>
       </c>
-      <c r="T102" s="3">
+      <c r="U102" s="3">
         <v>1638600</v>
       </c>
-      <c r="U102" s="3">
+      <c r="V102" s="3">
         <v>498500</v>
       </c>
-      <c r="V102" s="3">
+      <c r="W102" s="3">
         <v>-553300</v>
       </c>
-      <c r="W102" s="3">
+      <c r="X102" s="3">
         <v>857000</v>
       </c>
-      <c r="X102" s="3">
+      <c r="Y102" s="3">
         <v>870800</v>
       </c>
-      <c r="Y102" s="3">
+      <c r="Z102" s="3">
         <v>-480000</v>
       </c>
-      <c r="Z102" s="3">
+      <c r="AA102" s="3">
         <v>-243500</v>
       </c>
-      <c r="AA102" s="3">
+      <c r="AB102" s="3">
         <v>2722600</v>
       </c>
-      <c r="AB102" s="3">
+      <c r="AC102" s="3">
         <v>-1696800</v>
       </c>
-      <c r="AC102" s="3">
+      <c r="AD102" s="3">
         <v>1317700</v>
       </c>
-      <c r="AD102" s="3">
+      <c r="AE102" s="3">
         <v>1620600</v>
       </c>
-      <c r="AE102" s="3">
+      <c r="AF102" s="3">
         <v>-1593300</v>
       </c>
-      <c r="AF102" s="3">
+      <c r="AG102" s="3">
         <v>624400</v>
       </c>
-      <c r="AG102" s="3">
+      <c r="AH102" s="3">
         <v>68000</v>
       </c>
-      <c r="AH102" s="3">
+      <c r="AI102" s="3">
         <v>153400</v>
       </c>
-      <c r="AI102" s="3">
+      <c r="AJ102" s="3">
         <v>-983000</v>
       </c>
-      <c r="AJ102" s="3">
+      <c r="AK102" s="3">
         <v>84300</v>
       </c>
-      <c r="AK102" s="3">
+      <c r="AL102" s="3">
         <v>-496900</v>
       </c>
-      <c r="AL102" s="3">
+      <c r="AM102" s="3">
         <v>-534100</v>
       </c>
-      <c r="AM102" s="3">
+      <c r="AN102" s="3">
         <v>345600</v>
       </c>
-      <c r="AN102" s="3">
+      <c r="AO102" s="3">
         <v>-621200</v>
       </c>
-      <c r="AO102" s="3">
+      <c r="AP102" s="3">
         <v>2617600</v>
       </c>
     </row>
